--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F31F53A6-131B-4BA5-B745-517804E24EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965A7F54-B8A6-423C-BE57-E5EC946E6E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -38,8 +38,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
+  </authors>
+  <commentList>
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Iru produces only 17 MW in 2025 not 0.207 GW</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="148">
   <si>
     <t>~fi_t</t>
   </si>
@@ -459,19 +477,58 @@
   </si>
   <si>
     <t>ccs retrofit of -- Kiisa ERPP power station_1 &amp; 2 -- operating</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Additions by Kristopher</t>
+  </si>
+  <si>
+    <t>ep_oil_auvere</t>
+  </si>
+  <si>
+    <t>Auvere elektrijaam</t>
+  </si>
+  <si>
+    <t>ep_oil_balti</t>
+  </si>
+  <si>
+    <t>Balti elektrijaam</t>
+  </si>
+  <si>
+    <t>ep_oil_enefit</t>
+  </si>
+  <si>
+    <t>Enefit elektrijaam</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -494,8 +551,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,6 +569,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Kristopher Raik" id="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" userId="S::krraik@taltech.ee::b956339b-354b-46f9-8dd3-3584d8dbf762" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -828,12 +892,25 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F13" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047CB67-FC18-43CA-8AA0-0CA09A11D4D8}">
   <dimension ref="B9:T15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="73.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -841,7 +918,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -897,7 +974,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>130</v>
       </c>
@@ -953,7 +1030,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>131</v>
       </c>
@@ -1009,7 +1086,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>132</v>
       </c>
@@ -1065,7 +1142,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>133</v>
       </c>
@@ -1121,7 +1198,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>134</v>
       </c>
@@ -1185,9 +1262,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4FEF-80F2-457D-B441-6C3DD45005FF}">
   <dimension ref="B9:T28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -1195,7 +1276,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1251,7 +1332,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>84</v>
       </c>
@@ -1304,7 +1385,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>85</v>
       </c>
@@ -1357,7 +1438,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>86</v>
       </c>
@@ -1413,7 +1494,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>89</v>
       </c>
@@ -1469,7 +1550,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>91</v>
       </c>
@@ -1525,7 +1606,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>93</v>
       </c>
@@ -1581,7 +1662,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>94</v>
       </c>
@@ -1637,7 +1718,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>95</v>
       </c>
@@ -1693,7 +1774,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>96</v>
       </c>
@@ -1749,7 +1830,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>97</v>
       </c>
@@ -1799,7 +1880,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>98</v>
       </c>
@@ -1849,7 +1930,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>99</v>
       </c>
@@ -1905,7 +1986,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>100</v>
       </c>
@@ -1961,7 +2042,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>101</v>
       </c>
@@ -2017,7 +2098,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>103</v>
       </c>
@@ -2073,7 +2154,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>105</v>
       </c>
@@ -2129,7 +2210,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>106</v>
       </c>
@@ -2185,7 +2266,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>107</v>
       </c>
@@ -2247,11 +2328,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:T47"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
+  <dimension ref="B9:T51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -2259,7 +2348,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -2315,7 +2404,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>12</v>
       </c>
@@ -2368,7 +2457,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>15</v>
       </c>
@@ -2409,7 +2498,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>17</v>
       </c>
@@ -2462,7 +2551,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>18</v>
       </c>
@@ -2503,7 +2592,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>20</v>
       </c>
@@ -2556,7 +2645,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>22</v>
       </c>
@@ -2600,7 +2689,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>25</v>
       </c>
@@ -2644,7 +2733,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>27</v>
       </c>
@@ -2688,7 +2777,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>29</v>
       </c>
@@ -2744,7 +2833,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>29</v>
       </c>
@@ -2800,7 +2889,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>30</v>
       </c>
@@ -2856,7 +2945,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>32</v>
       </c>
@@ -2912,7 +3001,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>34</v>
       </c>
@@ -2968,7 +3057,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>34</v>
       </c>
@@ -3024,7 +3113,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>35</v>
       </c>
@@ -3080,7 +3169,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>37</v>
       </c>
@@ -3136,7 +3225,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>39</v>
       </c>
@@ -3192,7 +3281,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>40</v>
       </c>
@@ -3248,7 +3337,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>40</v>
       </c>
@@ -3304,7 +3393,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>42</v>
       </c>
@@ -3360,7 +3449,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>44</v>
       </c>
@@ -3404,7 +3493,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>47</v>
       </c>
@@ -3448,7 +3537,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>49</v>
       </c>
@@ -3492,7 +3581,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>51</v>
       </c>
@@ -3548,7 +3637,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>53</v>
       </c>
@@ -3604,7 +3693,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>53</v>
       </c>
@@ -3660,7 +3749,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>53</v>
       </c>
@@ -3694,8 +3783,14 @@
       <c r="L37">
         <v>0.47814004703314078</v>
       </c>
-    </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="N37" t="s">
+        <v>140</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>55</v>
       </c>
@@ -3729,8 +3824,17 @@
       <c r="L38">
         <v>0.40144059976798208</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="N38" t="s">
+        <v>69</v>
+      </c>
+      <c r="O38" t="s">
+        <v>142</v>
+      </c>
+      <c r="P38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>55</v>
       </c>
@@ -3764,8 +3868,17 @@
       <c r="L39">
         <v>0.40144059976798202</v>
       </c>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="N39" t="s">
+        <v>69</v>
+      </c>
+      <c r="O39" t="s">
+        <v>144</v>
+      </c>
+      <c r="P39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>55</v>
       </c>
@@ -3799,8 +3912,17 @@
       <c r="L40">
         <v>0.40144059976798202</v>
       </c>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="N40" t="s">
+        <v>69</v>
+      </c>
+      <c r="O40" t="s">
+        <v>146</v>
+      </c>
+      <c r="P40" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>55</v>
       </c>
@@ -3835,7 +3957,7 @@
         <v>0.40144059976798208</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>55</v>
       </c>
@@ -3870,7 +3992,7 @@
         <v>0.40144059976798202</v>
       </c>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>57</v>
       </c>
@@ -3905,7 +4027,7 @@
         <v>0.365520596150406</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>59</v>
       </c>
@@ -3940,7 +4062,7 @@
         <v>0.41047488326249421</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>59</v>
       </c>
@@ -3975,7 +4097,7 @@
         <v>0.41047488326249421</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>59</v>
       </c>
@@ -4010,7 +4132,7 @@
         <v>0.41047488326249421</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>61</v>
       </c>
@@ -4045,15 +4167,120 @@
         <v>0.365520596150406</v>
       </c>
     </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49">
+        <v>2025</v>
+      </c>
+      <c r="F49">
+        <v>0.26</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>1265</v>
+      </c>
+      <c r="I49">
+        <v>48.4</v>
+      </c>
+      <c r="J49">
+        <v>7.5075000000000003</v>
+      </c>
+      <c r="K49">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50">
+        <v>2025</v>
+      </c>
+      <c r="F50">
+        <v>0.185</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>1265</v>
+      </c>
+      <c r="I50">
+        <v>48.4</v>
+      </c>
+      <c r="J50">
+        <v>7.5075000000000003</v>
+      </c>
+      <c r="K50">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51">
+        <v>2025</v>
+      </c>
+      <c r="F51">
+        <v>0.01</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>1265</v>
+      </c>
+      <c r="I51">
+        <v>48.4</v>
+      </c>
+      <c r="J51">
+        <v>7.5075000000000003</v>
+      </c>
+      <c r="K51">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CEAB3BD-FD82-4128-8F02-FA58B77D374D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965A7F54-B8A6-423C-BE57-E5EC946E6E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE697EC1-CFB2-4669-B3A3-8064FC9B7C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="151">
   <si>
     <t>~fi_t</t>
   </si>
@@ -501,6 +501,15 @@
   </si>
   <si>
     <t>Enefit elektrijaam</t>
+  </si>
+  <si>
+    <t>ep_oil_internal_combustion_auvere</t>
+  </si>
+  <si>
+    <t>ep_oil_internal_combustion_balti</t>
+  </si>
+  <si>
+    <t>ep_oil_internal_combustion_enefit</t>
   </si>
 </sst>
 </file>
@@ -4177,7 +4186,7 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
         <v>21</v>
@@ -4209,7 +4218,7 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C50" t="s">
         <v>21</v>
@@ -4241,7 +4250,7 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C51" t="s">
         <v>21</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE697EC1-CFB2-4669-B3A3-8064FC9B7C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74863C6-8B33-463B-9104-D27CBEABF2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="148">
   <si>
     <t>~fi_t</t>
   </si>
@@ -485,19 +485,10 @@
     <t>Additions by Kristopher</t>
   </si>
   <si>
-    <t>ep_oil_auvere</t>
-  </si>
-  <si>
     <t>Auvere elektrijaam</t>
   </si>
   <si>
-    <t>ep_oil_balti</t>
-  </si>
-  <si>
     <t>Balti elektrijaam</t>
-  </si>
-  <si>
-    <t>ep_oil_enefit</t>
   </si>
   <si>
     <t>Enefit elektrijaam</t>
@@ -3837,10 +3828,10 @@
         <v>69</v>
       </c>
       <c r="O38" t="s">
+        <v>145</v>
+      </c>
+      <c r="P38" t="s">
         <v>142</v>
-      </c>
-      <c r="P38" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
@@ -3881,10 +3872,10 @@
         <v>69</v>
       </c>
       <c r="O39" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="P39" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
@@ -3925,10 +3916,10 @@
         <v>69</v>
       </c>
       <c r="O40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P40" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
@@ -4186,7 +4177,7 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s">
         <v>21</v>
@@ -4218,7 +4209,7 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C50" t="s">
         <v>21</v>
@@ -4250,7 +4241,7 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
         <v>21</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74863C6-8B33-463B-9104-D27CBEABF2FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2ACDC1-770D-471A-9965-86EBEAA75F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="148">
   <si>
     <t>~fi_t</t>
   </si>
@@ -507,7 +507,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,13 +522,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3833,6 +3826,18 @@
       <c r="P38" t="s">
         <v>142</v>
       </c>
+      <c r="Q38" t="s">
+        <v>71</v>
+      </c>
+      <c r="R38" t="s">
+        <v>72</v>
+      </c>
+      <c r="S38" t="s">
+        <v>80</v>
+      </c>
+      <c r="T38" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
@@ -3877,6 +3882,18 @@
       <c r="P39" t="s">
         <v>143</v>
       </c>
+      <c r="Q39" t="s">
+        <v>71</v>
+      </c>
+      <c r="R39" t="s">
+        <v>72</v>
+      </c>
+      <c r="S39" t="s">
+        <v>80</v>
+      </c>
+      <c r="T39" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
@@ -3921,6 +3938,18 @@
       <c r="P40" t="s">
         <v>144</v>
       </c>
+      <c r="Q40" t="s">
+        <v>71</v>
+      </c>
+      <c r="R40" t="s">
+        <v>72</v>
+      </c>
+      <c r="S40" t="s">
+        <v>80</v>
+      </c>
+      <c r="T40" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
@@ -4186,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F49">
         <v>0.26</v>
@@ -4218,7 +4247,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F50">
         <v>0.185</v>
@@ -4250,7 +4279,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F51">
         <v>0.01</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2ACDC1-770D-471A-9965-86EBEAA75F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E0C23C-4758-420D-871A-97A950AFB2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -41,10 +41,19 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
     <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
   </authors>
   <commentList>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    From 9,24 to 6</t>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -507,7 +516,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,6 +531,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -887,6 +902,9 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="J11" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <text>From 9,24 to 6</text>
+  </threadedComment>
   <threadedComment ref="F13" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
@@ -2326,9 +2344,13 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="40.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="64.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2423,7 +2445,7 @@
         <v>157.30000000000001</v>
       </c>
       <c r="J11">
-        <v>9.240000000000002</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>50</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E0C23C-4758-420D-871A-97A950AFB2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B2FAC8-88CE-4056-A720-FCCA62D973FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -41,11 +41,56 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
+    <author>tc={06D70610-96F7-4BDA-B071-69925D70228B}</author>
+    <author>tc={A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}</author>
+    <author>tc={4E0E017D-BAC7-4AA8-B401-A7330F2C0996}</author>
+    <author>tc={1905391B-2A5F-4643-B2AC-720AD8410CDA}</author>
     <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
-    <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Iru produces only 17 MW in 2025 not 0.207 GW</t>
+      </text>
+    </comment>
+    <comment ref="G46" authorId="1" shapeId="0" xr:uid="{06D70610-96F7-4BDA-B071-69925D70228B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Danish Energy agency - coal CHP 2020</t>
+      </text>
+    </comment>
+    <comment ref="G49" authorId="2" shapeId="0" xr:uid="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    DAE - gas engines 2020
+</t>
+      </text>
+    </comment>
+    <comment ref="G50" authorId="3" shapeId="0" xr:uid="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    DAE - Wood pellets, Medium 2020</t>
+      </text>
+    </comment>
+    <comment ref="N77" authorId="4" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Frequency reserve</t>
+      </text>
+    </comment>
+    <comment ref="J80" authorId="5" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -53,20 +98,12 @@
     From 9,24 to 6</t>
       </text>
     </comment>
-    <comment ref="F13" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Iru produces only 17 MW in 2025 not 0.207 GW</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="201">
   <si>
     <t>~fi_t</t>
   </si>
@@ -494,28 +531,190 @@
     <t>Additions by Kristopher</t>
   </si>
   <si>
-    <t>Auvere elektrijaam</t>
-  </si>
-  <si>
-    <t>Balti elektrijaam</t>
-  </si>
-  <si>
-    <t>Enefit elektrijaam</t>
-  </si>
-  <si>
-    <t>ep_oil_internal_combustion_auvere</t>
-  </si>
-  <si>
-    <t>ep_oil_internal_combustion_balti</t>
-  </si>
-  <si>
-    <t>ep_oil_internal_combustion_enefit</t>
+    <t>ep_gas_combined_cycle_pohja</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_tlnutilitas</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_tartu</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_parnu</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_horizon</t>
+  </si>
+  <si>
+    <t>Horizon Tselluloosi ja paberi AS</t>
+  </si>
+  <si>
+    <t>Balti PP</t>
+  </si>
+  <si>
+    <t>Enefit PP</t>
+  </si>
+  <si>
+    <t>Eesti PP</t>
+  </si>
+  <si>
+    <t>Utilitas Tallinna PP</t>
+  </si>
+  <si>
+    <t>Tartu PP</t>
+  </si>
+  <si>
+    <t>Parnu PP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_imavere</t>
+  </si>
+  <si>
+    <t>Imavere CHP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_osula</t>
+  </si>
+  <si>
+    <t>Osula CHP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_sillamae1</t>
+  </si>
+  <si>
+    <t>Sillamae 1 CHP</t>
+  </si>
+  <si>
+    <t>Sillamae 2 CHP</t>
+  </si>
+  <si>
+    <t>Pohja TPP</t>
+  </si>
+  <si>
+    <t>Sillamae TPP</t>
+  </si>
+  <si>
+    <t>Auvere PP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_helme</t>
+  </si>
+  <si>
+    <t>Helme CHP</t>
+  </si>
+  <si>
+    <t>Grune Fee Eesti AS</t>
+  </si>
+  <si>
+    <t>Kivioli Keemiatoostuse OU TPP</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_grune</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_sillamae2</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_mustamae</t>
+  </si>
+  <si>
+    <t>Mustamae CHP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_kuressaare</t>
+  </si>
+  <si>
+    <t>Kuressare CHP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_paide</t>
+  </si>
+  <si>
+    <t>Paide CHP</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_jamejala</t>
+  </si>
+  <si>
+    <t>Jamejala CHP</t>
+  </si>
+  <si>
+    <t>ep_gas_gas_turbine_pussi</t>
+  </si>
+  <si>
+    <t>Pussi CHP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_ilmatsalu</t>
+  </si>
+  <si>
+    <t>Ilmatsalu CHP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_vinni</t>
+  </si>
+  <si>
+    <t>Vinni CHP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_oisu</t>
+  </si>
+  <si>
+    <t>Oisu CHP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_tlnprugilagaas</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_rakverepaikese</t>
+  </si>
+  <si>
+    <t>Tallinna Prugilagaas OU CHP</t>
+  </si>
+  <si>
+    <t>Rakvere Paikese CHP</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_tartuaardlapalu</t>
+  </si>
+  <si>
+    <t>Tartu Aardlapalu CHP</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>ep_coal_cfb_balti</t>
+  </si>
+  <si>
+    <t>ep_coal_cfb_auvere</t>
+  </si>
+  <si>
+    <t>ep_coal_cfb_enefit</t>
+  </si>
+  <si>
+    <t>ep_coal_cfb_eesti</t>
+  </si>
+  <si>
+    <t>ep_coal_cfb_sillamae</t>
+  </si>
+  <si>
+    <t>ep_coal_cfb_kivioli</t>
+  </si>
+  <si>
+    <t>en_a_coal_cfb_G100001030965</t>
+  </si>
+  <si>
+    <t>en_a_coal_cfb_G100001030961</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -559,9 +758,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,18 +1104,31 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J11" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+  <threadedComment ref="F11" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
+  </threadedComment>
+  <threadedComment ref="G46" dT="2026-01-28T09:05:36.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{06D70610-96F7-4BDA-B071-69925D70228B}">
+    <text>Danish Energy agency - coal CHP 2020</text>
+  </threadedComment>
+  <threadedComment ref="G49" dT="2026-01-28T11:16:21.05" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
+    <text xml:space="preserve">DAE - gas engines 2020
+</text>
+  </threadedComment>
+  <threadedComment ref="G50" dT="2026-01-28T11:17:46.06" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
+    <text>DAE - Wood pellets, Medium 2020</text>
+  </threadedComment>
+  <threadedComment ref="N77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <text>Frequency reserve</text>
+  </threadedComment>
+  <threadedComment ref="J80" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
     <text>From 9,24 to 6</text>
-  </threadedComment>
-  <threadedComment ref="F13" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
-    <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047CB67-FC18-43CA-8AA0-0CA09A11D4D8}">
-  <dimension ref="B9:T15"/>
+  <dimension ref="B9:T17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
@@ -985,121 +1200,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11">
-        <v>0.52272499999999988</v>
-      </c>
-      <c r="F11">
-        <v>1365</v>
-      </c>
-      <c r="G11">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H11">
-        <v>3.75</v>
-      </c>
-      <c r="I11">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J11" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>20</v>
-      </c>
-      <c r="N11" t="s">
-        <v>69</v>
-      </c>
-      <c r="O11" t="s">
-        <v>130</v>
-      </c>
-      <c r="P11" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>71</v>
-      </c>
-      <c r="R11" t="s">
-        <v>72</v>
-      </c>
-      <c r="S11" t="s">
-        <v>73</v>
-      </c>
-      <c r="T11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12">
-        <v>0.52272499999999988</v>
-      </c>
-      <c r="F12">
-        <v>1365</v>
-      </c>
-      <c r="G12">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="H12">
-        <v>3.75</v>
-      </c>
-      <c r="I12">
-        <v>0.84455000000000002</v>
-      </c>
-      <c r="J12" t="s">
-        <v>85</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <v>20</v>
-      </c>
-      <c r="N12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O12" t="s">
-        <v>131</v>
-      </c>
-      <c r="P12" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>71</v>
-      </c>
-      <c r="R12" t="s">
-        <v>72</v>
-      </c>
-      <c r="S12" t="s">
-        <v>73</v>
-      </c>
-      <c r="T12" t="s">
-        <v>77</v>
-      </c>
-    </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1108,7 +1211,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.28982625000000001</v>
+        <v>0.52272499999999988</v>
       </c>
       <c r="F13">
         <v>1365</v>
@@ -1123,7 +1226,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1135,10 +1238,10 @@
         <v>69</v>
       </c>
       <c r="O13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="P13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Q13" t="s">
         <v>71</v>
@@ -1155,7 +1258,7 @@
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
@@ -1164,7 +1267,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.38753750000000003</v>
+        <v>0.52272499999999988</v>
       </c>
       <c r="F14">
         <v>1365</v>
@@ -1179,7 +1282,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1191,10 +1294,10 @@
         <v>69</v>
       </c>
       <c r="O14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q14" t="s">
         <v>71</v>
@@ -1211,16 +1314,16 @@
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.31543749999999998</v>
+        <v>0.28982625000000001</v>
       </c>
       <c r="F15">
         <v>1365</v>
@@ -1235,7 +1338,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -1247,10 +1350,10 @@
         <v>69</v>
       </c>
       <c r="O15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q15" t="s">
         <v>71</v>
@@ -1262,6 +1365,118 @@
         <v>73</v>
       </c>
       <c r="T15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16">
+        <v>0.38753750000000003</v>
+      </c>
+      <c r="F16">
+        <v>1365</v>
+      </c>
+      <c r="G16">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="H16">
+        <v>3.75</v>
+      </c>
+      <c r="I16">
+        <v>0.84455000000000002</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>20</v>
+      </c>
+      <c r="N16" t="s">
+        <v>69</v>
+      </c>
+      <c r="O16" t="s">
+        <v>133</v>
+      </c>
+      <c r="P16" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>71</v>
+      </c>
+      <c r="R16" t="s">
+        <v>72</v>
+      </c>
+      <c r="S16" t="s">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17">
+        <v>0.31543749999999998</v>
+      </c>
+      <c r="F17">
+        <v>1365</v>
+      </c>
+      <c r="G17">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="H17">
+        <v>3.75</v>
+      </c>
+      <c r="I17">
+        <v>0.84455000000000002</v>
+      </c>
+      <c r="J17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>20</v>
+      </c>
+      <c r="N17" t="s">
+        <v>69</v>
+      </c>
+      <c r="O17" t="s">
+        <v>134</v>
+      </c>
+      <c r="P17" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>71</v>
+      </c>
+      <c r="R17" t="s">
+        <v>72</v>
+      </c>
+      <c r="S17" t="s">
+        <v>73</v>
+      </c>
+      <c r="T17" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1276,6 +1491,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="48.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1345,10 +1561,10 @@
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -1363,13 +1579,13 @@
         <v>0.59739999999999993</v>
       </c>
       <c r="H11">
-        <v>1265</v>
-      </c>
-      <c r="I11">
-        <v>36.300000000000004</v>
+        <v>2150</v>
+      </c>
+      <c r="I11" s="3">
+        <v>35.053609999999999</v>
       </c>
       <c r="J11">
-        <v>3.4650000000000007</v>
+        <v>3.28</v>
       </c>
       <c r="K11">
         <v>50</v>
@@ -1378,7 +1594,7 @@
         <v>69</v>
       </c>
       <c r="O11" t="s">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="P11" t="s">
         <v>108</v>
@@ -1398,10 +1614,10 @@
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>85</v>
+        <v>199</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -1416,13 +1632,13 @@
         <v>0.59739999999999993</v>
       </c>
       <c r="H12">
-        <v>1265</v>
-      </c>
-      <c r="I12">
-        <v>36.300000000000004</v>
+        <v>2150</v>
+      </c>
+      <c r="I12" s="3">
+        <v>35.053609999999999</v>
       </c>
       <c r="J12">
-        <v>3.4650000000000007</v>
+        <v>3.28</v>
       </c>
       <c r="K12">
         <v>50</v>
@@ -1431,7 +1647,7 @@
         <v>69</v>
       </c>
       <c r="O12" t="s">
-        <v>85</v>
+        <v>199</v>
       </c>
       <c r="P12" t="s">
         <v>109</v>
@@ -2340,17 +2556,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:T51"/>
+  <dimension ref="B9:T80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="40.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="64.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2385,7 +2603,7 @@
       <c r="H10" t="s">
         <v>7</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J10" t="s">
@@ -2421,43 +2639,43 @@
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
       </c>
       <c r="E11">
-        <v>2022</v>
+        <v>1982</v>
       </c>
       <c r="F11">
-        <v>0.3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="G11">
-        <v>0.33990000000000004</v>
+        <v>0.44290000000000002</v>
       </c>
       <c r="H11">
-        <v>4427.5</v>
-      </c>
-      <c r="I11">
-        <v>157.30000000000001</v>
+        <v>1265</v>
+      </c>
+      <c r="I11" s="3">
+        <v>36.300000000000004</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K11">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="N11" t="s">
         <v>69</v>
       </c>
       <c r="O11" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="P11" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="Q11" t="s">
         <v>71</v>
@@ -2469,36 +2687,39 @@
         <v>73</v>
       </c>
       <c r="T11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E12">
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.21299999999999999</v>
+        <v>4.3091615634383719E-2</v>
       </c>
       <c r="G12">
         <v>0.33123000000000002</v>
       </c>
+      <c r="L12">
+        <v>0.14986856628506873</v>
+      </c>
       <c r="N12" t="s">
         <v>69</v>
       </c>
       <c r="O12" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q12" t="s">
         <v>71</v>
@@ -2507,7 +2728,7 @@
         <v>72</v>
       </c>
       <c r="S12" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="T12" t="s">
         <v>74</v>
@@ -2515,43 +2736,34 @@
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E13">
-        <v>1982</v>
+        <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.20699999999999999</v>
+        <v>4.3344722222460344E-2</v>
       </c>
       <c r="G13">
-        <v>0.44290000000000002</v>
-      </c>
-      <c r="H13">
-        <v>1265</v>
-      </c>
-      <c r="I13">
-        <v>36.300000000000004</v>
-      </c>
-      <c r="J13">
-        <v>3.4650000000000007</v>
-      </c>
-      <c r="K13">
-        <v>73</v>
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L13">
+        <v>0.14986856628506873</v>
       </c>
       <c r="N13" t="s">
         <v>69</v>
       </c>
       <c r="O13" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="P13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q13" t="s">
         <v>71</v>
@@ -2560,36 +2772,39 @@
         <v>72</v>
       </c>
       <c r="S13" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E14">
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>8.0000000000000002E-3</v>
+        <v>3.9363662143155967E-2</v>
       </c>
       <c r="G14">
         <v>0.33123000000000002</v>
       </c>
+      <c r="L14">
+        <v>0.14986856628506873</v>
+      </c>
       <c r="N14" t="s">
         <v>69</v>
       </c>
       <c r="O14" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="P14" t="s">
         <v>78</v>
@@ -2601,7 +2816,7 @@
         <v>72</v>
       </c>
       <c r="S14" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="T14" t="s">
         <v>74</v>
@@ -2609,43 +2824,46 @@
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E15">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="F15">
-        <v>0.25109999999999999</v>
+        <v>7.6700000000000004E-2</v>
       </c>
       <c r="G15">
-        <v>0.36049999999999999</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>1265</v>
-      </c>
-      <c r="I15">
-        <v>48.400000000000006</v>
+        <v>1336.4999999999998</v>
+      </c>
+      <c r="I15" s="3">
+        <v>21.45</v>
       </c>
       <c r="J15">
-        <v>7.5075000000000003</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="L15">
+        <v>0.1461854238754417</v>
       </c>
       <c r="N15" t="s">
         <v>69</v>
       </c>
       <c r="O15" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="P15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q15" t="s">
         <v>71</v>
@@ -2654,15 +2872,15 @@
         <v>72</v>
       </c>
       <c r="S15" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="T15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
@@ -2671,22 +2889,34 @@
         <v>24</v>
       </c>
       <c r="E16">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F16">
-        <v>4.3091615634383719E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="G16">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1336.5</v>
+      </c>
+      <c r="I16" s="3">
+        <v>21.450000000000003</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>32</v>
       </c>
       <c r="L16">
-        <v>0.14986856628506873</v>
+        <v>0.1461854238754417</v>
       </c>
       <c r="N16" t="s">
         <v>69</v>
       </c>
       <c r="O16" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="P16" t="s">
         <v>78</v>
@@ -2706,31 +2936,43 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E17">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F17">
-        <v>4.3344722222460344E-2</v>
+        <v>5.8200000000000002E-2</v>
       </c>
       <c r="G17">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1336.5</v>
+      </c>
+      <c r="I17" s="3">
+        <v>21.450000000000003</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>40</v>
       </c>
       <c r="L17">
-        <v>0.14986856628506873</v>
+        <v>0.14867925344692126</v>
       </c>
       <c r="N17" t="s">
         <v>69</v>
       </c>
       <c r="O17" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="P17" t="s">
         <v>78</v>
@@ -2750,31 +2992,43 @@
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E18">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F18">
-        <v>3.9363662143155967E-2</v>
+        <v>2.9599999999999998E-2</v>
       </c>
       <c r="G18">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1336.5000000000002</v>
+      </c>
+      <c r="I18" s="3">
+        <v>21.450000000000003</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>40</v>
       </c>
       <c r="L18">
-        <v>0.14986856628506873</v>
+        <v>0.14701259708091721</v>
       </c>
       <c r="N18" t="s">
         <v>69</v>
       </c>
       <c r="O18" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="P18" t="s">
         <v>78</v>
@@ -2794,19 +3048,19 @@
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E19">
         <v>2015</v>
       </c>
       <c r="F19">
-        <v>7.6700000000000004E-2</v>
+        <v>5.3800000000000008E-2</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -2814,7 +3068,7 @@
       <c r="H19">
         <v>1336.4999999999998</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="3">
         <v>21.45</v>
       </c>
       <c r="J19">
@@ -2824,13 +3078,13 @@
         <v>40</v>
       </c>
       <c r="L19">
-        <v>0.1461854238754417</v>
+        <v>0.15309859852159369</v>
       </c>
       <c r="N19" t="s">
         <v>69</v>
       </c>
       <c r="O19" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="P19" t="s">
         <v>78</v>
@@ -2850,43 +3104,43 @@
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E20">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F20">
-        <v>3.2000000000000001E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>1336.5</v>
-      </c>
-      <c r="I20">
-        <v>21.450000000000003</v>
+        <v>1138.5</v>
+      </c>
+      <c r="I20" s="3">
+        <v>18.150000000000002</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L20">
-        <v>0.1461854238754417</v>
+        <v>0.15309859852159369</v>
       </c>
       <c r="N20" t="s">
         <v>69</v>
       </c>
       <c r="O20" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="P20" t="s">
         <v>78</v>
@@ -2906,19 +3160,19 @@
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E21">
         <v>2015</v>
       </c>
       <c r="F21">
-        <v>5.8200000000000002E-2</v>
+        <v>7.3000000000000009E-3</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -2926,8 +3180,8 @@
       <c r="H21">
         <v>1336.5</v>
       </c>
-      <c r="I21">
-        <v>21.450000000000003</v>
+      <c r="I21" s="3">
+        <v>21.45</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2936,13 +3190,13 @@
         <v>40</v>
       </c>
       <c r="L21">
-        <v>0.14867925344692126</v>
+        <v>0.15619560585976827</v>
       </c>
       <c r="N21" t="s">
         <v>69</v>
       </c>
       <c r="O21" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="P21" t="s">
         <v>78</v>
@@ -2962,27 +3216,27 @@
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E22">
         <v>2015</v>
       </c>
       <c r="F22">
-        <v>2.9599999999999998E-2</v>
+        <v>2.81E-2</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>1336.5000000000002</v>
-      </c>
-      <c r="I22">
+        <v>1336.5</v>
+      </c>
+      <c r="I22" s="3">
         <v>21.450000000000003</v>
       </c>
       <c r="J22">
@@ -2992,13 +3246,13 @@
         <v>40</v>
       </c>
       <c r="L22">
-        <v>0.14701259708091721</v>
+        <v>0.14537310453496291</v>
       </c>
       <c r="N22" t="s">
         <v>69</v>
       </c>
       <c r="O22" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="P22" t="s">
         <v>78</v>
@@ -3018,28 +3272,28 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E23">
         <v>2015</v>
       </c>
       <c r="F23">
-        <v>5.3800000000000008E-2</v>
+        <v>8.4900000000000003E-2</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>1336.4999999999998</v>
-      </c>
-      <c r="I23">
-        <v>21.45</v>
+        <v>1336.5</v>
+      </c>
+      <c r="I23" s="3">
+        <v>21.450000000000003</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3048,13 +3302,13 @@
         <v>40</v>
       </c>
       <c r="L23">
-        <v>0.15309859852159369</v>
+        <v>0.14763873655681015</v>
       </c>
       <c r="N23" t="s">
         <v>69</v>
       </c>
       <c r="O23" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="P23" t="s">
         <v>78</v>
@@ -3074,43 +3328,43 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E24">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="F24">
-        <v>7.0000000000000007E-2</v>
+        <v>5.2399999999999995E-2</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24">
-        <v>1138.5</v>
-      </c>
-      <c r="I24">
-        <v>18.150000000000002</v>
+        <v>1336.5000000000002</v>
+      </c>
+      <c r="I24" s="3">
+        <v>21.45</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L24">
-        <v>0.15309859852159369</v>
+        <v>0.1532628310027955</v>
       </c>
       <c r="N24" t="s">
         <v>69</v>
       </c>
       <c r="O24" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="P24" t="s">
         <v>78</v>
@@ -3130,19 +3384,19 @@
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E25">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="F25">
-        <v>7.3000000000000009E-3</v>
+        <v>0.02</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3150,23 +3404,23 @@
       <c r="H25">
         <v>1336.5</v>
       </c>
-      <c r="I25">
-        <v>21.45</v>
+      <c r="I25" s="3">
+        <v>21.450000000000003</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L25">
-        <v>0.15619560585976827</v>
+        <v>0.1532628310027955</v>
       </c>
       <c r="N25" t="s">
         <v>69</v>
       </c>
       <c r="O25" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="P25" t="s">
         <v>78</v>
@@ -3186,19 +3440,19 @@
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E26">
         <v>2015</v>
       </c>
       <c r="F26">
-        <v>2.81E-2</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3206,7 +3460,7 @@
       <c r="H26">
         <v>1336.5</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="3">
         <v>21.450000000000003</v>
       </c>
       <c r="J26">
@@ -3216,13 +3470,13 @@
         <v>40</v>
       </c>
       <c r="L26">
-        <v>0.14537310453496291</v>
+        <v>0.1451997589052581</v>
       </c>
       <c r="N26" t="s">
         <v>69</v>
       </c>
       <c r="O26" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="P26" t="s">
         <v>78</v>
@@ -3242,43 +3496,31 @@
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E27">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F27">
-        <v>8.4900000000000003E-2</v>
+        <v>1.5040605442498314E-2</v>
       </c>
       <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>1336.5</v>
-      </c>
-      <c r="I27">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>40</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L27">
-        <v>0.14763873655681015</v>
+        <v>0.42012333946150526</v>
       </c>
       <c r="N27" t="s">
         <v>69</v>
       </c>
       <c r="O27" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P27" t="s">
         <v>78</v>
@@ -3298,43 +3540,31 @@
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E28">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F28">
-        <v>5.2399999999999995E-2</v>
+        <v>1.5497656626156837E-2</v>
       </c>
       <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28">
-        <v>1336.5000000000002</v>
-      </c>
-      <c r="I28">
-        <v>21.45</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>40</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L28">
-        <v>0.1532628310027955</v>
+        <v>0.42012333946150526</v>
       </c>
       <c r="N28" t="s">
         <v>69</v>
       </c>
       <c r="O28" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="P28" t="s">
         <v>78</v>
@@ -3354,43 +3584,31 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E29">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.02</v>
+        <v>1.4461737931344828E-2</v>
       </c>
       <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>1336.5</v>
-      </c>
-      <c r="I29">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>32</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L29">
-        <v>0.1532628310027955</v>
+        <v>0.42012333946150526</v>
       </c>
       <c r="N29" t="s">
         <v>69</v>
       </c>
       <c r="O29" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="P29" t="s">
         <v>78</v>
@@ -3410,43 +3628,43 @@
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E30">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="F30">
-        <v>3.2000000000000002E-3</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>1336.5</v>
-      </c>
-      <c r="I30">
-        <v>21.450000000000003</v>
+        <v>2376</v>
+      </c>
+      <c r="I30" s="3">
+        <v>57.2</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="K30">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L30">
-        <v>0.1451997589052581</v>
+        <v>0.47763777043344691</v>
       </c>
       <c r="N30" t="s">
         <v>69</v>
       </c>
       <c r="O30" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="P30" t="s">
         <v>78</v>
@@ -3466,31 +3684,43 @@
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E31">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="F31">
-        <v>1.5040605442498314E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G31">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>2376</v>
+      </c>
+      <c r="I31" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J31">
+        <v>2.52</v>
+      </c>
+      <c r="K31">
+        <v>45</v>
       </c>
       <c r="L31">
-        <v>0.42012333946150526</v>
+        <v>0.47814004703314078</v>
       </c>
       <c r="N31" t="s">
         <v>69</v>
       </c>
       <c r="O31" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="P31" t="s">
         <v>78</v>
@@ -3510,34 +3740,46 @@
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E32">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F32">
-        <v>1.5497656626156837E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G32">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>2376</v>
+      </c>
+      <c r="I32" s="3">
+        <v>57.20000000000001</v>
+      </c>
+      <c r="J32">
+        <v>2.52</v>
+      </c>
+      <c r="K32">
+        <v>40</v>
       </c>
       <c r="L32">
-        <v>0.42012333946150526</v>
+        <v>0.47814004703314084</v>
       </c>
       <c r="N32" t="s">
         <v>69</v>
       </c>
       <c r="O32" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="P32" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q32" t="s">
         <v>71</v>
@@ -3549,68 +3791,65 @@
         <v>80</v>
       </c>
       <c r="T32" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E33">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F33">
-        <v>1.4461737931344828E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G33">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>2376</v>
+      </c>
+      <c r="I33" s="3">
+        <v>57.20000000000001</v>
+      </c>
+      <c r="J33">
+        <v>2.52</v>
+      </c>
+      <c r="K33">
+        <v>35</v>
       </c>
       <c r="L33">
-        <v>0.42012333946150526</v>
+        <v>0.47814004703314078</v>
       </c>
       <c r="N33" t="s">
-        <v>69</v>
-      </c>
-      <c r="O33" t="s">
-        <v>55</v>
-      </c>
-      <c r="P33" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>71</v>
-      </c>
-      <c r="R33" t="s">
-        <v>72</v>
-      </c>
-      <c r="S33" t="s">
-        <v>80</v>
-      </c>
-      <c r="T33" t="s">
-        <v>74</v>
+        <v>140</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E34">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="F34">
-        <v>3.9E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -3618,26 +3857,26 @@
       <c r="H34">
         <v>2376</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="3">
         <v>57.2</v>
       </c>
       <c r="J34">
         <v>2.52</v>
       </c>
       <c r="K34">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L34">
-        <v>0.47763777043344691</v>
+        <v>0.40144059976798208</v>
       </c>
       <c r="N34" t="s">
         <v>69</v>
       </c>
       <c r="O34" t="s">
-        <v>57</v>
+        <v>194</v>
       </c>
       <c r="P34" t="s">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="Q34" t="s">
         <v>71</v>
@@ -3649,24 +3888,24 @@
         <v>80</v>
       </c>
       <c r="T34" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
         <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E35">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="F35">
-        <v>1.6E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -3674,26 +3913,26 @@
       <c r="H35">
         <v>2376</v>
       </c>
-      <c r="I35">
-        <v>57.2</v>
+      <c r="I35" s="3">
+        <v>57.20000000000001</v>
       </c>
       <c r="J35">
         <v>2.52</v>
       </c>
       <c r="K35">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L35">
-        <v>0.47814004703314078</v>
+        <v>0.40144059976798202</v>
       </c>
       <c r="N35" t="s">
         <v>69</v>
       </c>
       <c r="O35" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="P35" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Q35" t="s">
         <v>71</v>
@@ -3705,24 +3944,24 @@
         <v>80</v>
       </c>
       <c r="T35" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
         <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E36">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="F36">
-        <v>1.7999999999999999E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -3730,26 +3969,26 @@
       <c r="H36">
         <v>2376</v>
       </c>
-      <c r="I36">
-        <v>57.20000000000001</v>
+      <c r="I36" s="3">
+        <v>57.2</v>
       </c>
       <c r="J36">
         <v>2.52</v>
       </c>
       <c r="K36">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L36">
-        <v>0.47814004703314084</v>
+        <v>0.40144059976798202</v>
       </c>
       <c r="N36" t="s">
         <v>69</v>
       </c>
       <c r="O36" t="s">
-        <v>61</v>
+        <v>195</v>
       </c>
       <c r="P36" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="Q36" t="s">
         <v>71</v>
@@ -3766,19 +4005,19 @@
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
         <v>45</v>
       </c>
       <c r="D37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E37">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="F37">
-        <v>1.2E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -3786,23 +4025,38 @@
       <c r="H37">
         <v>2376</v>
       </c>
-      <c r="I37">
-        <v>57.20000000000001</v>
+      <c r="I37" s="3">
+        <v>57.2</v>
       </c>
       <c r="J37">
         <v>2.52</v>
       </c>
       <c r="K37">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L37">
-        <v>0.47814004703314078</v>
+        <v>0.40144059976798208</v>
       </c>
       <c r="N37" t="s">
-        <v>140</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>141</v>
+        <v>69</v>
+      </c>
+      <c r="O37" t="s">
+        <v>196</v>
+      </c>
+      <c r="P37" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>71</v>
+      </c>
+      <c r="R37" t="s">
+        <v>72</v>
+      </c>
+      <c r="S37" t="s">
+        <v>80</v>
+      </c>
+      <c r="T37" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
@@ -3816,37 +4070,37 @@
         <v>56</v>
       </c>
       <c r="E38">
-        <v>2007</v>
+        <v>2024</v>
       </c>
       <c r="F38">
-        <v>2.1000000000000001E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>2376</v>
-      </c>
-      <c r="I38">
-        <v>57.2</v>
+        <v>2024</v>
+      </c>
+      <c r="I38" s="3">
+        <v>48.4</v>
       </c>
       <c r="J38">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K38">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L38">
-        <v>0.40144059976798208</v>
+        <v>0.40144059976798202</v>
       </c>
       <c r="N38" t="s">
         <v>69</v>
       </c>
       <c r="O38" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P38" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="Q38" t="s">
         <v>71</v>
@@ -3863,19 +4117,19 @@
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
         <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E39">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="F39">
-        <v>2.4E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -3883,26 +4137,26 @@
       <c r="H39">
         <v>2376</v>
       </c>
-      <c r="I39">
-        <v>57.20000000000001</v>
+      <c r="I39" s="3">
+        <v>57.2</v>
       </c>
       <c r="J39">
         <v>2.52</v>
       </c>
       <c r="K39">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L39">
-        <v>0.40144059976798202</v>
+        <v>0.365520596150406</v>
       </c>
       <c r="N39" t="s">
         <v>69</v>
       </c>
       <c r="O39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="P39" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="Q39" t="s">
         <v>71</v>
@@ -3919,19 +4173,19 @@
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
         <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E40">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="F40">
-        <v>7.9000000000000001E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -3939,26 +4193,26 @@
       <c r="H40">
         <v>2376</v>
       </c>
-      <c r="I40">
-        <v>57.2</v>
+      <c r="I40" s="3">
+        <v>57.20000000000001</v>
       </c>
       <c r="J40">
         <v>2.52</v>
       </c>
       <c r="K40">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L40">
-        <v>0.40144059976798202</v>
+        <v>0.41047488326249421</v>
       </c>
       <c r="N40" t="s">
         <v>69</v>
       </c>
       <c r="O40" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P40" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="Q40" t="s">
         <v>71</v>
@@ -3975,19 +4229,19 @@
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
         <v>45</v>
       </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E41">
-        <v>2023</v>
+        <v>2012</v>
       </c>
       <c r="F41">
-        <v>2.1000000000000001E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -3995,57 +4249,99 @@
       <c r="H41">
         <v>2376</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="3">
         <v>57.2</v>
       </c>
       <c r="J41">
         <v>2.52</v>
       </c>
       <c r="K41">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L41">
-        <v>0.40144059976798208</v>
+        <v>0.41047488326249421</v>
+      </c>
+      <c r="N41" t="s">
+        <v>69</v>
+      </c>
+      <c r="O41" t="s">
+        <v>145</v>
+      </c>
+      <c r="P41" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>71</v>
+      </c>
+      <c r="R41" t="s">
+        <v>72</v>
+      </c>
+      <c r="S41" t="s">
+        <v>80</v>
+      </c>
+      <c r="T41" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
         <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E42">
-        <v>2024</v>
+        <v>2013</v>
       </c>
       <c r="F42">
-        <v>0.10199999999999999</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>2024</v>
-      </c>
-      <c r="I42">
-        <v>48.4</v>
+        <v>2376</v>
+      </c>
+      <c r="I42" s="3">
+        <v>57.2</v>
       </c>
       <c r="J42">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K42">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="L42">
-        <v>0.40144059976798202</v>
+        <v>0.41047488326249421</v>
+      </c>
+      <c r="N42" t="s">
+        <v>69</v>
+      </c>
+      <c r="O42" t="s">
+        <v>146</v>
+      </c>
+      <c r="P42" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>71</v>
+      </c>
+      <c r="R42" t="s">
+        <v>72</v>
+      </c>
+      <c r="S42" t="s">
+        <v>80</v>
+      </c>
+      <c r="T42" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
         <v>45</v>
@@ -4054,184 +4350,298 @@
         <v>58</v>
       </c>
       <c r="E43">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F43">
-        <v>3.9E-2</v>
+        <v>0.255</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="H43">
-        <v>2376</v>
-      </c>
-      <c r="I43">
-        <v>57.2</v>
+        <v>2024</v>
+      </c>
+      <c r="I43" s="3">
+        <v>48.400000000000006</v>
       </c>
       <c r="J43">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K43">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L43">
         <v>0.365520596150406</v>
       </c>
+      <c r="N43" t="s">
+        <v>69</v>
+      </c>
+      <c r="O43" t="s">
+        <v>197</v>
+      </c>
+      <c r="P43" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>71</v>
+      </c>
+      <c r="R43" t="s">
+        <v>72</v>
+      </c>
+      <c r="S43" t="s">
+        <v>80</v>
+      </c>
+      <c r="T43" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" t="s">
-        <v>60</v>
-      </c>
-      <c r="E44">
-        <v>2005</v>
-      </c>
-      <c r="F44">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>2376</v>
-      </c>
-      <c r="I44">
-        <v>57.20000000000001</v>
-      </c>
-      <c r="J44">
-        <v>2.52</v>
-      </c>
-      <c r="K44">
-        <v>50</v>
-      </c>
-      <c r="L44">
-        <v>0.41047488326249421</v>
+        <v>140</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="N44" t="s">
+        <v>69</v>
+      </c>
+      <c r="O44" t="s">
+        <v>154</v>
+      </c>
+      <c r="P44" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>71</v>
+      </c>
+      <c r="R44" t="s">
+        <v>72</v>
+      </c>
+      <c r="S44" t="s">
+        <v>80</v>
+      </c>
+      <c r="T44" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="E45">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="F45">
-        <v>2.1999999999999999E-2</v>
+        <v>0.77</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>0.49</v>
       </c>
       <c r="H45">
-        <v>2376</v>
-      </c>
-      <c r="I45">
-        <v>57.2</v>
+        <v>2150</v>
+      </c>
+      <c r="I45" s="3">
+        <v>35.053609999999999</v>
       </c>
       <c r="J45">
-        <v>2.52</v>
+        <v>3.28</v>
       </c>
       <c r="K45">
-        <v>43</v>
-      </c>
-      <c r="L45">
-        <v>0.41047488326249421</v>
+        <v>40</v>
+      </c>
+      <c r="N45" t="s">
+        <v>69</v>
+      </c>
+      <c r="O45" t="s">
+        <v>156</v>
+      </c>
+      <c r="P45" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>71</v>
+      </c>
+      <c r="R45" t="s">
+        <v>72</v>
+      </c>
+      <c r="S45" t="s">
+        <v>80</v>
+      </c>
+      <c r="T45" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="D46" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="E46">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="F46">
-        <v>2.1999999999999999E-2</v>
+        <v>0.26</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0.49</v>
       </c>
       <c r="H46">
-        <v>2376</v>
-      </c>
-      <c r="I46">
-        <v>57.2</v>
+        <v>2150</v>
+      </c>
+      <c r="I46" s="3">
+        <v>35.053609999999999</v>
       </c>
       <c r="J46">
-        <v>2.52</v>
+        <v>3.28</v>
       </c>
       <c r="K46">
-        <v>42</v>
-      </c>
-      <c r="L46">
-        <v>0.41047488326249421</v>
+        <v>40</v>
+      </c>
+      <c r="N46" t="s">
+        <v>69</v>
+      </c>
+      <c r="O46" t="s">
+        <v>170</v>
+      </c>
+      <c r="P46" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>71</v>
+      </c>
+      <c r="R46" t="s">
+        <v>72</v>
+      </c>
+      <c r="S46" t="s">
+        <v>80</v>
+      </c>
+      <c r="T46" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>61</v>
+        <v>193</v>
       </c>
       <c r="C47" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="E47">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F47">
-        <v>0.255</v>
+        <v>0.185</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0.49</v>
       </c>
       <c r="H47">
-        <v>2024</v>
-      </c>
-      <c r="I47">
-        <v>48.400000000000006</v>
+        <v>2150</v>
+      </c>
+      <c r="I47" s="3">
+        <v>35.053609999999999</v>
       </c>
       <c r="J47">
-        <v>2.3100000000000005</v>
+        <v>3.28</v>
       </c>
       <c r="K47">
-        <v>31</v>
-      </c>
-      <c r="L47">
-        <v>0.365520596150406</v>
+        <v>37</v>
+      </c>
+      <c r="N47" t="s">
+        <v>69</v>
+      </c>
+      <c r="O47" t="s">
+        <v>158</v>
+      </c>
+      <c r="P47" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>71</v>
+      </c>
+      <c r="R47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S47" t="s">
+        <v>80</v>
+      </c>
+      <c r="T47" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>140</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+      <c r="C48" t="s">
+        <v>192</v>
+      </c>
+      <c r="D48" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48">
+        <v>2022</v>
+      </c>
+      <c r="F48">
+        <v>0.01</v>
+      </c>
+      <c r="G48">
+        <v>0.49</v>
+      </c>
+      <c r="H48">
+        <v>2150</v>
+      </c>
+      <c r="I48" s="3">
+        <v>35.053609999999999</v>
+      </c>
+      <c r="J48">
+        <v>3.28</v>
+      </c>
+      <c r="K48">
+        <v>40</v>
+      </c>
+      <c r="N48" t="s">
+        <v>69</v>
+      </c>
+      <c r="O48" t="s">
+        <v>169</v>
+      </c>
+      <c r="P48" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>71</v>
+      </c>
+      <c r="R48" t="s">
+        <v>72</v>
+      </c>
+      <c r="S48" t="s">
+        <v>80</v>
+      </c>
+      <c r="T48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
@@ -4240,30 +4650,51 @@
         <v>2022</v>
       </c>
       <c r="F49">
-        <v>0.26</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>0.41</v>
       </c>
       <c r="H49">
-        <v>1265</v>
-      </c>
-      <c r="I49">
-        <v>48.4</v>
+        <v>360</v>
+      </c>
+      <c r="I49" s="3">
+        <v>9.3576800000000002</v>
       </c>
       <c r="J49">
-        <v>7.5075000000000003</v>
+        <v>6.38</v>
       </c>
       <c r="K49">
         <v>40</v>
       </c>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="N49" t="s">
+        <v>69</v>
+      </c>
+      <c r="O49" t="s">
+        <v>164</v>
+      </c>
+      <c r="P49" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>71</v>
+      </c>
+      <c r="R49" t="s">
+        <v>72</v>
+      </c>
+      <c r="S49" t="s">
+        <v>80</v>
+      </c>
+      <c r="T49" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
         <v>14</v>
@@ -4272,30 +4703,51 @@
         <v>2022</v>
       </c>
       <c r="F50">
-        <v>0.185</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G50">
-        <v>1</v>
-      </c>
-      <c r="H50">
-        <v>1265</v>
-      </c>
-      <c r="I50">
-        <v>48.4</v>
-      </c>
-      <c r="J50">
-        <v>7.5075000000000003</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H50" s="2">
+        <v>3200.7518811800001</v>
+      </c>
+      <c r="I50" s="3">
+        <v>131.85821703200003</v>
+      </c>
+      <c r="J50" s="4">
+        <v>1.9778732554800003</v>
       </c>
       <c r="K50">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="N50" t="s">
+        <v>69</v>
+      </c>
+      <c r="O50" t="s">
+        <v>168</v>
+      </c>
+      <c r="P50" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>71</v>
+      </c>
+      <c r="R50" t="s">
+        <v>72</v>
+      </c>
+      <c r="S50" t="s">
+        <v>80</v>
+      </c>
+      <c r="T50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
         <v>14</v>
@@ -4304,22 +4756,1113 @@
         <v>2022</v>
       </c>
       <c r="F51">
-        <v>0.01</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="G51">
-        <v>1</v>
-      </c>
-      <c r="H51">
-        <v>1265</v>
-      </c>
-      <c r="I51">
-        <v>48.4</v>
-      </c>
-      <c r="J51">
-        <v>7.5075000000000003</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H51" s="2">
+        <v>3200.7518811800001</v>
+      </c>
+      <c r="I51" s="3">
+        <v>131.85821703200003</v>
+      </c>
+      <c r="J51" s="4">
+        <v>1.9778732554800003</v>
       </c>
       <c r="K51">
         <v>40</v>
+      </c>
+      <c r="N51" t="s">
+        <v>69</v>
+      </c>
+      <c r="O51" t="s">
+        <v>198</v>
+      </c>
+      <c r="P51" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>71</v>
+      </c>
+      <c r="R51" t="s">
+        <v>72</v>
+      </c>
+      <c r="S51" t="s">
+        <v>80</v>
+      </c>
+      <c r="T51" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52">
+        <v>2022</v>
+      </c>
+      <c r="F52">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="G52">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H52" s="2">
+        <v>3200.7518811800001</v>
+      </c>
+      <c r="I52" s="3">
+        <v>131.85821703200003</v>
+      </c>
+      <c r="J52" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="K52">
+        <v>40</v>
+      </c>
+      <c r="N52" t="s">
+        <v>69</v>
+      </c>
+      <c r="O52" t="s">
+        <v>172</v>
+      </c>
+      <c r="P52" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>71</v>
+      </c>
+      <c r="R52" t="s">
+        <v>72</v>
+      </c>
+      <c r="S52" t="s">
+        <v>80</v>
+      </c>
+      <c r="T52" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>146</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53">
+        <v>2022</v>
+      </c>
+      <c r="F53">
+        <v>1.3900000000000001E-2</v>
+      </c>
+      <c r="G53">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H53" s="2">
+        <v>3200.7518811800001</v>
+      </c>
+      <c r="I53" s="3">
+        <v>131.85821703200003</v>
+      </c>
+      <c r="J53" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="K53">
+        <v>40</v>
+      </c>
+      <c r="N53" t="s">
+        <v>69</v>
+      </c>
+      <c r="O53" t="s">
+        <v>174</v>
+      </c>
+      <c r="P53" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>71</v>
+      </c>
+      <c r="R53" t="s">
+        <v>72</v>
+      </c>
+      <c r="S53" t="s">
+        <v>80</v>
+      </c>
+      <c r="T53" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>197</v>
+      </c>
+      <c r="C54" t="s">
+        <v>192</v>
+      </c>
+      <c r="D54" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54">
+        <v>2022</v>
+      </c>
+      <c r="F54">
+        <v>0.01</v>
+      </c>
+      <c r="G54">
+        <v>0.49</v>
+      </c>
+      <c r="H54" s="2">
+        <v>2150</v>
+      </c>
+      <c r="I54" s="3">
+        <v>35.053609999999999</v>
+      </c>
+      <c r="J54" s="4">
+        <v>3.28</v>
+      </c>
+      <c r="K54">
+        <v>40</v>
+      </c>
+      <c r="N54" t="s">
+        <v>69</v>
+      </c>
+      <c r="O54" t="s">
+        <v>176</v>
+      </c>
+      <c r="P54" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>71</v>
+      </c>
+      <c r="R54" t="s">
+        <v>72</v>
+      </c>
+      <c r="S54" t="s">
+        <v>80</v>
+      </c>
+      <c r="T54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>154</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55">
+        <v>2022</v>
+      </c>
+      <c r="F55">
+        <v>0.01</v>
+      </c>
+      <c r="G55">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H55" s="2">
+        <v>3200.7518811800001</v>
+      </c>
+      <c r="I55" s="3">
+        <v>131.85821703200003</v>
+      </c>
+      <c r="J55" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="K55">
+        <v>40</v>
+      </c>
+      <c r="N55" t="s">
+        <v>69</v>
+      </c>
+      <c r="O55" t="s">
+        <v>178</v>
+      </c>
+      <c r="P55" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>71</v>
+      </c>
+      <c r="R55" t="s">
+        <v>72</v>
+      </c>
+      <c r="S55" t="s">
+        <v>80</v>
+      </c>
+      <c r="T55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>156</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56">
+        <v>2022</v>
+      </c>
+      <c r="F56">
+        <v>0.01</v>
+      </c>
+      <c r="G56">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H56" s="2">
+        <v>3200.7518811800001</v>
+      </c>
+      <c r="I56" s="3">
+        <v>131.85821703200003</v>
+      </c>
+      <c r="J56" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="K56">
+        <v>40</v>
+      </c>
+      <c r="N56" t="s">
+        <v>69</v>
+      </c>
+      <c r="O56" t="s">
+        <v>180</v>
+      </c>
+      <c r="P56" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>71</v>
+      </c>
+      <c r="R56" t="s">
+        <v>72</v>
+      </c>
+      <c r="S56" t="s">
+        <v>80</v>
+      </c>
+      <c r="T56" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>170</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57">
+        <v>2022</v>
+      </c>
+      <c r="F57">
+        <v>9.300000000000001E-3</v>
+      </c>
+      <c r="G57">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H57" s="2">
+        <v>3200.7518811800001</v>
+      </c>
+      <c r="I57" s="3">
+        <v>131.85821703200003</v>
+      </c>
+      <c r="J57" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="K57">
+        <v>40</v>
+      </c>
+      <c r="N57" t="s">
+        <v>69</v>
+      </c>
+      <c r="O57" t="s">
+        <v>182</v>
+      </c>
+      <c r="P57" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>71</v>
+      </c>
+      <c r="R57" t="s">
+        <v>72</v>
+      </c>
+      <c r="S57" t="s">
+        <v>80</v>
+      </c>
+      <c r="T57" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>158</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58">
+        <v>2022</v>
+      </c>
+      <c r="F58">
+        <v>7.0999999999999995E-3</v>
+      </c>
+      <c r="G58">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H58" s="2">
+        <v>3200.7518811800001</v>
+      </c>
+      <c r="I58" s="3">
+        <v>131.85821703200003</v>
+      </c>
+      <c r="J58" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="K58">
+        <v>40</v>
+      </c>
+      <c r="N58" t="s">
+        <v>69</v>
+      </c>
+      <c r="O58" t="s">
+        <v>184</v>
+      </c>
+      <c r="P58" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>71</v>
+      </c>
+      <c r="R58" t="s">
+        <v>72</v>
+      </c>
+      <c r="S58" t="s">
+        <v>80</v>
+      </c>
+      <c r="T58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59">
+        <v>2022</v>
+      </c>
+      <c r="F59">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="G59">
+        <v>0.41</v>
+      </c>
+      <c r="H59" s="2">
+        <v>521.0526318200001</v>
+      </c>
+      <c r="I59" s="3">
+        <v>6.9119226670000007</v>
+      </c>
+      <c r="J59" s="4">
+        <v>6.38</v>
+      </c>
+      <c r="K59">
+        <v>40</v>
+      </c>
+      <c r="N59" t="s">
+        <v>69</v>
+      </c>
+      <c r="O59" t="s">
+        <v>186</v>
+      </c>
+      <c r="P59" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>71</v>
+      </c>
+      <c r="R59" t="s">
+        <v>72</v>
+      </c>
+      <c r="S59" t="s">
+        <v>80</v>
+      </c>
+      <c r="T59" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>164</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60">
+        <v>2022</v>
+      </c>
+      <c r="F60">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="G60">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H60" s="2">
+        <v>3200.7518811800001</v>
+      </c>
+      <c r="I60" s="3">
+        <v>131.85821703200003</v>
+      </c>
+      <c r="J60" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="K60">
+        <v>40</v>
+      </c>
+      <c r="N60" t="s">
+        <v>69</v>
+      </c>
+      <c r="O60" t="s">
+        <v>187</v>
+      </c>
+      <c r="P60" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>71</v>
+      </c>
+      <c r="R60" t="s">
+        <v>72</v>
+      </c>
+      <c r="S60" t="s">
+        <v>80</v>
+      </c>
+      <c r="T60" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>168</v>
+      </c>
+      <c r="C61" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61">
+        <v>2022</v>
+      </c>
+      <c r="F61">
+        <v>4.0999999999999995E-3</v>
+      </c>
+      <c r="G61">
+        <v>0.41</v>
+      </c>
+      <c r="H61" s="2">
+        <v>521.0526318200001</v>
+      </c>
+      <c r="I61" s="3">
+        <v>6.9119226670000007</v>
+      </c>
+      <c r="J61" s="4">
+        <v>6.38</v>
+      </c>
+      <c r="K61">
+        <v>40</v>
+      </c>
+      <c r="N61" t="s">
+        <v>69</v>
+      </c>
+      <c r="O61" t="s">
+        <v>190</v>
+      </c>
+      <c r="P61" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>71</v>
+      </c>
+      <c r="R61" t="s">
+        <v>72</v>
+      </c>
+      <c r="S61" t="s">
+        <v>80</v>
+      </c>
+      <c r="T61" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>198</v>
+      </c>
+      <c r="C62" t="s">
+        <v>192</v>
+      </c>
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62">
+        <v>2022</v>
+      </c>
+      <c r="F62">
+        <v>1.4E-3</v>
+      </c>
+      <c r="G62">
+        <v>0.49</v>
+      </c>
+      <c r="H62" s="2">
+        <v>2150</v>
+      </c>
+      <c r="I62" s="3">
+        <v>35.053609999999999</v>
+      </c>
+      <c r="J62" s="4">
+        <v>3.28</v>
+      </c>
+      <c r="K62">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>172</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63">
+        <v>2022</v>
+      </c>
+      <c r="F63">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G63">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H63" s="2">
+        <v>6444.0386710800003</v>
+      </c>
+      <c r="I63" s="3">
+        <v>288.17400657800005</v>
+      </c>
+      <c r="J63" s="4">
+        <v>4.1365198730200001</v>
+      </c>
+      <c r="K63">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64">
+        <v>2022</v>
+      </c>
+      <c r="F64">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="G64">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H64" s="2">
+        <v>6444.0386710800003</v>
+      </c>
+      <c r="I64" s="3">
+        <v>288.17400657800005</v>
+      </c>
+      <c r="J64" s="4">
+        <v>4.1365198730200001</v>
+      </c>
+      <c r="K64">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>176</v>
+      </c>
+      <c r="C65" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65">
+        <v>2022</v>
+      </c>
+      <c r="F65">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G65">
+        <v>0.41</v>
+      </c>
+      <c r="H65" s="2">
+        <v>521.0526318200001</v>
+      </c>
+      <c r="I65" s="3">
+        <v>6.9119226670000007</v>
+      </c>
+      <c r="J65" s="4">
+        <v>6.38</v>
+      </c>
+      <c r="K65">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>178</v>
+      </c>
+      <c r="C66" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66">
+        <v>2022</v>
+      </c>
+      <c r="F66">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G66">
+        <v>0.41</v>
+      </c>
+      <c r="H66" s="2">
+        <v>521.0526318200001</v>
+      </c>
+      <c r="I66" s="3">
+        <v>6.9119226670000007</v>
+      </c>
+      <c r="J66" s="4">
+        <v>6.38</v>
+      </c>
+      <c r="K66">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>180</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67">
+        <v>2022</v>
+      </c>
+      <c r="F67">
+        <v>1.5E-3</v>
+      </c>
+      <c r="G67">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H67" s="2">
+        <v>1010.2040821000001</v>
+      </c>
+      <c r="I67" s="3">
+        <v>10.3678840005</v>
+      </c>
+      <c r="J67" s="4">
+        <v>7.9752953850000008</v>
+      </c>
+      <c r="K67">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>182</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68">
+        <v>2022</v>
+      </c>
+      <c r="F68">
+        <v>1.4E-3</v>
+      </c>
+      <c r="G68">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H68" s="2">
+        <v>1010.2040821000001</v>
+      </c>
+      <c r="I68" s="3">
+        <v>10.3678840005</v>
+      </c>
+      <c r="J68" s="4">
+        <v>7.9752953850000008</v>
+      </c>
+      <c r="K68">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>184</v>
+      </c>
+      <c r="C69" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69">
+        <v>2022</v>
+      </c>
+      <c r="F69">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="G69">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H69" s="2">
+        <v>1010.2040821000001</v>
+      </c>
+      <c r="I69" s="3">
+        <v>10.3678840005</v>
+      </c>
+      <c r="J69" s="4">
+        <v>7.9752953850000008</v>
+      </c>
+      <c r="K69">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>186</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70">
+        <v>2022</v>
+      </c>
+      <c r="F70">
+        <v>1.9E-3</v>
+      </c>
+      <c r="G70">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H70" s="2">
+        <v>11048.442540020002</v>
+      </c>
+      <c r="I70" s="3">
+        <v>437.04618709800002</v>
+      </c>
+      <c r="J70" s="4">
+        <v>27.520085941840001</v>
+      </c>
+      <c r="K70">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>187</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71">
+        <v>2022</v>
+      </c>
+      <c r="F71">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="G71">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H71" s="2">
+        <v>6444.0386710800003</v>
+      </c>
+      <c r="I71" s="3">
+        <v>288.17400657800005</v>
+      </c>
+      <c r="J71" s="4">
+        <v>4.1365198730200001</v>
+      </c>
+      <c r="K71">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>190</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72">
+        <v>2022</v>
+      </c>
+      <c r="F72">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="G72">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H72" s="2">
+        <v>11048.442540020002</v>
+      </c>
+      <c r="I72" s="3">
+        <v>437.04618709800002</v>
+      </c>
+      <c r="J72" s="4">
+        <v>27.520085941840001</v>
+      </c>
+      <c r="K72">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77">
+        <v>2013</v>
+      </c>
+      <c r="F77">
+        <v>0.25109999999999999</v>
+      </c>
+      <c r="G77">
+        <v>0.36049999999999999</v>
+      </c>
+      <c r="H77">
+        <v>1265</v>
+      </c>
+      <c r="I77" s="3">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="J77">
+        <v>7.5075000000000003</v>
+      </c>
+      <c r="K77">
+        <v>42</v>
+      </c>
+      <c r="N77" t="s">
+        <v>69</v>
+      </c>
+      <c r="O77" t="s">
+        <v>20</v>
+      </c>
+      <c r="P77" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>71</v>
+      </c>
+      <c r="R77" t="s">
+        <v>72</v>
+      </c>
+      <c r="S77" t="s">
+        <v>73</v>
+      </c>
+      <c r="T77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78">
+        <v>2022</v>
+      </c>
+      <c r="F78">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="G78">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="N78" t="s">
+        <v>69</v>
+      </c>
+      <c r="O78" t="s">
+        <v>15</v>
+      </c>
+      <c r="P78" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>71</v>
+      </c>
+      <c r="R78" t="s">
+        <v>72</v>
+      </c>
+      <c r="S78" t="s">
+        <v>73</v>
+      </c>
+      <c r="T78" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79">
+        <v>2022</v>
+      </c>
+      <c r="F79">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G79">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="N79" t="s">
+        <v>69</v>
+      </c>
+      <c r="O79" t="s">
+        <v>18</v>
+      </c>
+      <c r="P79" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>71</v>
+      </c>
+      <c r="R79" t="s">
+        <v>72</v>
+      </c>
+      <c r="S79" t="s">
+        <v>73</v>
+      </c>
+      <c r="T79" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80">
+        <v>2022</v>
+      </c>
+      <c r="F80">
+        <v>0.3</v>
+      </c>
+      <c r="G80">
+        <v>0.33990000000000004</v>
+      </c>
+      <c r="H80">
+        <v>4427.5</v>
+      </c>
+      <c r="I80" s="3">
+        <v>157.30000000000001</v>
+      </c>
+      <c r="J80">
+        <v>9.24</v>
+      </c>
+      <c r="K80">
+        <v>50</v>
+      </c>
+      <c r="N80" t="s">
+        <v>69</v>
+      </c>
+      <c r="O80" t="s">
+        <v>12</v>
+      </c>
+      <c r="P80" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>71</v>
+      </c>
+      <c r="R80" t="s">
+        <v>72</v>
+      </c>
+      <c r="S80" t="s">
+        <v>73</v>
+      </c>
+      <c r="T80" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B2FAC8-88CE-4056-A720-FCCA62D973FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386015BB-A0C3-4542-B481-AC4342815862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -713,9 +713,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -730,12 +730,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -762,7 +756,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1491,6 +1485,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="48.140625" bestFit="1" customWidth="1"/>
   </cols>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386015BB-A0C3-4542-B481-AC4342815862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF99D7B-4C1B-4CC1-9323-B322FFD6BBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -39,6 +39,33 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={45C46737-1944-45AD-99CE-B8535D314683}</author>
+    <author>tc={E4726566-8322-459A-B187-5632353FCAD0}</author>
+  </authors>
+  <commentList>
+    <comment ref="B29" authorId="0" shapeId="0" xr:uid="{45C46737-1944-45AD-99CE-B8535D314683}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Testing_FERMI's idea</t>
+      </text>
+    </comment>
+    <comment ref="O29" authorId="1" shapeId="0" xr:uid="{E4726566-8322-459A-B187-5632353FCAD0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Testing_FERMI's idea</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
@@ -103,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="204">
   <si>
     <t>~fi_t</t>
   </si>
@@ -706,6 +733,15 @@
   </si>
   <si>
     <t>en_a_coal_cfb_G100001030961</t>
+  </si>
+  <si>
+    <t>en_a_nuclear_smr</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>Fermi's small nuclear reactor</t>
   </si>
 </sst>
 </file>
@@ -715,7 +751,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -730,6 +766,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1098,6 +1140,17 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B29" dT="2026-01-28T14:50:45.09" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{45C46737-1944-45AD-99CE-B8535D314683}">
+    <text>Testing_FERMI's idea</text>
+  </threadedComment>
+  <threadedComment ref="O29" dT="2026-01-28T14:50:45.09" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E4726566-8322-459A-B187-5632353FCAD0}">
+    <text>Testing_FERMI's idea</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="F11" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
@@ -1480,8 +1533,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4FEF-80F2-457D-B441-6C3DD45005FF}">
-  <dimension ref="B9:T28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4FEF-80F2-457D-B441-6C3DD45005FF}">
+  <dimension ref="B9:T29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
@@ -2544,8 +2597,62 @@
         <v>77</v>
       </c>
     </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>201</v>
+      </c>
+      <c r="C29" t="s">
+        <v>202</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29">
+        <v>2035</v>
+      </c>
+      <c r="F29">
+        <v>0.3</v>
+      </c>
+      <c r="G29">
+        <v>0.35</v>
+      </c>
+      <c r="H29">
+        <v>6000</v>
+      </c>
+      <c r="I29">
+        <v>150</v>
+      </c>
+      <c r="J29">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="K29">
+        <v>50</v>
+      </c>
+      <c r="N29" t="s">
+        <v>69</v>
+      </c>
+      <c r="O29" t="s">
+        <v>201</v>
+      </c>
+      <c r="P29" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>71</v>
+      </c>
+      <c r="R29" t="s">
+        <v>72</v>
+      </c>
+      <c r="S29" t="s">
+        <v>80</v>
+      </c>
+      <c r="T29" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF99D7B-4C1B-4CC1-9323-B322FFD6BBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC64D7C-6183-4BE9-8A7A-7FE1B408D8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -69,6 +69,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
+    <author>tc={5D0B02A9-24B3-4F36-8683-2AD26D1E0821}</author>
     <author>tc={06D70610-96F7-4BDA-B071-69925D70228B}</author>
     <author>tc={A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}</author>
     <author>tc={4E0E017D-BAC7-4AA8-B401-A7330F2C0996}</author>
@@ -84,7 +85,15 @@
     Iru produces only 17 MW in 2025 not 0.207 GW</t>
       </text>
     </comment>
-    <comment ref="G46" authorId="1" shapeId="0" xr:uid="{06D70610-96F7-4BDA-B071-69925D70228B}">
+    <comment ref="B45" authorId="1" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    TODO: set their actual start date and then add how much they produce in 2025</t>
+      </text>
+    </comment>
+    <comment ref="G46" authorId="2" shapeId="0" xr:uid="{06D70610-96F7-4BDA-B071-69925D70228B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -92,7 +101,7 @@
     Danish Energy agency - coal CHP 2020</t>
       </text>
     </comment>
-    <comment ref="G49" authorId="2" shapeId="0" xr:uid="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
+    <comment ref="G49" authorId="3" shapeId="0" xr:uid="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -101,7 +110,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="G50" authorId="3" shapeId="0" xr:uid="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
+    <comment ref="G50" authorId="4" shapeId="0" xr:uid="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -109,7 +118,7 @@
     DAE - Wood pellets, Medium 2020</t>
       </text>
     </comment>
-    <comment ref="N77" authorId="4" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <comment ref="N77" authorId="5" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -117,7 +126,7 @@
     Frequency reserve</t>
       </text>
     </comment>
-    <comment ref="J80" authorId="5" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <comment ref="J80" authorId="6" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1154,6 +1163,9 @@
   <threadedComment ref="F11" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
+  <threadedComment ref="B45" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+    <text>TODO: set their actual start date and then add how much they produce in 2025</text>
+  </threadedComment>
   <threadedComment ref="G46" dT="2026-01-28T09:05:36.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{06D70610-96F7-4BDA-B071-69925D70228B}">
     <text>Danish Energy agency - coal CHP 2020</text>
   </threadedComment>
@@ -2647,7 +2659,7 @@
         <v>80</v>
       </c>
       <c r="T29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -3990,7 +4002,7 @@
         <v>80</v>
       </c>
       <c r="T34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
@@ -4046,7 +4058,7 @@
         <v>80</v>
       </c>
       <c r="T35" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
@@ -4102,7 +4114,7 @@
         <v>80</v>
       </c>
       <c r="T36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
@@ -4158,7 +4170,7 @@
         <v>80</v>
       </c>
       <c r="T37" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
@@ -4214,7 +4226,7 @@
         <v>80</v>
       </c>
       <c r="T38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.25">
@@ -4270,7 +4282,7 @@
         <v>80</v>
       </c>
       <c r="T39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.25">
@@ -4326,7 +4338,7 @@
         <v>80</v>
       </c>
       <c r="T40" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.25">
@@ -4382,7 +4394,7 @@
         <v>80</v>
       </c>
       <c r="T41" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.25">
@@ -4438,7 +4450,7 @@
         <v>80</v>
       </c>
       <c r="T42" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.25">
@@ -4494,7 +4506,7 @@
         <v>80</v>
       </c>
       <c r="T43" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.25">
@@ -4523,7 +4535,7 @@
         <v>80</v>
       </c>
       <c r="T44" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.25">
@@ -4537,7 +4549,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F45">
         <v>0.77</v>
@@ -4576,7 +4588,7 @@
         <v>80</v>
       </c>
       <c r="T45" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.25">
@@ -4590,7 +4602,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F46">
         <v>0.26</v>
@@ -4629,7 +4641,7 @@
         <v>80</v>
       </c>
       <c r="T46" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.25">
@@ -4643,7 +4655,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F47">
         <v>0.185</v>
@@ -4661,7 +4673,7 @@
         <v>3.28</v>
       </c>
       <c r="K47">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N47" t="s">
         <v>69</v>
@@ -4682,7 +4694,7 @@
         <v>80</v>
       </c>
       <c r="T47" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.25">
@@ -4696,7 +4708,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F48">
         <v>0.01</v>
@@ -4735,7 +4747,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.25">
@@ -4749,7 +4761,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F49">
         <v>7.6999999999999999E-2</v>
@@ -4788,7 +4800,7 @@
         <v>80</v>
       </c>
       <c r="T49" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
@@ -4802,7 +4814,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F50">
         <v>3.9E-2</v>
@@ -4841,7 +4853,7 @@
         <v>80</v>
       </c>
       <c r="T50" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.25">
@@ -4855,7 +4867,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F51">
         <v>2.2100000000000002E-2</v>
@@ -4894,7 +4906,7 @@
         <v>80</v>
       </c>
       <c r="T51" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.25">
@@ -4908,7 +4920,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F52">
         <v>2.0500000000000001E-2</v>
@@ -4947,7 +4959,7 @@
         <v>80</v>
       </c>
       <c r="T52" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.25">
@@ -4961,7 +4973,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F53">
         <v>1.3900000000000001E-2</v>
@@ -5000,7 +5012,7 @@
         <v>80</v>
       </c>
       <c r="T53" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.25">
@@ -5014,7 +5026,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F54">
         <v>0.01</v>
@@ -5053,7 +5065,7 @@
         <v>80</v>
       </c>
       <c r="T54" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.25">
@@ -5067,7 +5079,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F55">
         <v>0.01</v>
@@ -5106,7 +5118,7 @@
         <v>80</v>
       </c>
       <c r="T55" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.25">
@@ -5120,7 +5132,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F56">
         <v>0.01</v>
@@ -5159,7 +5171,7 @@
         <v>80</v>
       </c>
       <c r="T56" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.25">
@@ -5173,7 +5185,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F57">
         <v>9.300000000000001E-3</v>
@@ -5212,7 +5224,7 @@
         <v>80</v>
       </c>
       <c r="T57" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.25">
@@ -5226,7 +5238,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F58">
         <v>7.0999999999999995E-3</v>
@@ -5265,7 +5277,7 @@
         <v>80</v>
       </c>
       <c r="T58" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
@@ -5279,7 +5291,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F59">
         <v>5.7999999999999996E-3</v>
@@ -5318,7 +5330,7 @@
         <v>80</v>
       </c>
       <c r="T59" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.25">
@@ -5332,7 +5344,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F60">
         <v>6.4999999999999997E-3</v>
@@ -5371,7 +5383,7 @@
         <v>80</v>
       </c>
       <c r="T60" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.25">
@@ -5385,7 +5397,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F61">
         <v>4.0999999999999995E-3</v>
@@ -5424,7 +5436,7 @@
         <v>80</v>
       </c>
       <c r="T61" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.25">
@@ -5438,7 +5450,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F62">
         <v>1.4E-3</v>
@@ -5470,7 +5482,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F63">
         <v>1.8E-3</v>
@@ -5502,7 +5514,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F64">
         <v>1.6999999999999999E-3</v>
@@ -5534,7 +5546,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F65">
         <v>1.8E-3</v>
@@ -5566,7 +5578,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F66">
         <v>1.8E-3</v>
@@ -5598,7 +5610,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F67">
         <v>1.5E-3</v>
@@ -5630,7 +5642,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F68">
         <v>1.4E-3</v>
@@ -5662,7 +5674,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F69">
         <v>1.1999999999999999E-3</v>
@@ -5694,7 +5706,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F70">
         <v>1.9E-3</v>
@@ -5726,7 +5738,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F71">
         <v>8.9999999999999998E-4</v>
@@ -5758,7 +5770,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F72">
         <v>5.0000000000000001E-4</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC64D7C-6183-4BE9-8A7A-7FE1B408D8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5799CF-688A-4AD3-892E-93B97A30D83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -118,7 +118,7 @@
     DAE - Wood pellets, Medium 2020</t>
       </text>
     </comment>
-    <comment ref="N77" authorId="5" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <comment ref="O77" authorId="5" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -760,7 +760,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -775,12 +775,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1176,7 +1170,7 @@
   <threadedComment ref="G50" dT="2026-01-28T11:17:46.06" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
     <text>DAE - Wood pellets, Medium 2020</text>
   </threadedComment>
-  <threadedComment ref="N77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+  <threadedComment ref="O77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
   </threadedComment>
   <threadedComment ref="J80" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
@@ -1188,14 +1182,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047CB67-FC18-43CA-8AA0-0CA09A11D4D8}">
   <dimension ref="B9:T17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="73.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="73.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -1203,7 +1197,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1259,7 +1253,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>130</v>
       </c>
@@ -1315,7 +1309,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>131</v>
       </c>
@@ -1371,7 +1365,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>132</v>
       </c>
@@ -1427,7 +1421,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>133</v>
       </c>
@@ -1483,7 +1477,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>134</v>
       </c>
@@ -1547,15 +1541,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4FEF-80F2-457D-B441-6C3DD45005FF}">
   <dimension ref="B9:T29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -1563,7 +1557,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1619,7 +1613,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>200</v>
       </c>
@@ -1672,7 +1666,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>199</v>
       </c>
@@ -1725,7 +1719,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>86</v>
       </c>
@@ -1781,7 +1775,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>89</v>
       </c>
@@ -1837,7 +1831,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>91</v>
       </c>
@@ -1893,7 +1887,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>93</v>
       </c>
@@ -1949,7 +1943,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>94</v>
       </c>
@@ -2005,7 +1999,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>95</v>
       </c>
@@ -2061,7 +2055,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>96</v>
       </c>
@@ -2117,7 +2111,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>97</v>
       </c>
@@ -2167,7 +2161,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>98</v>
       </c>
@@ -2217,7 +2211,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>99</v>
       </c>
@@ -2273,7 +2267,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>100</v>
       </c>
@@ -2329,7 +2323,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>101</v>
       </c>
@@ -2385,7 +2379,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>103</v>
       </c>
@@ -2441,7 +2435,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>105</v>
       </c>
@@ -2497,7 +2491,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>106</v>
       </c>
@@ -2553,7 +2547,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>107</v>
       </c>
@@ -2609,7 +2603,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>201</v>
       </c>
@@ -2670,32 +2664,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:T80"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B9:U80"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -2729,29 +2725,29 @@
       <c r="L10" t="s">
         <v>11</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>63</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>1</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>64</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>65</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>66</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>67</v>
       </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -2782,29 +2778,29 @@
       <c r="K11">
         <v>73</v>
       </c>
-      <c r="N11" t="s">
-        <v>69</v>
-      </c>
       <c r="O11" t="s">
+        <v>69</v>
+      </c>
+      <c r="P11" t="s">
         <v>17</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>76</v>
       </c>
-      <c r="Q11" t="s">
-        <v>71</v>
-      </c>
       <c r="R11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S11" t="s">
+        <v>72</v>
+      </c>
+      <c r="T11" t="s">
         <v>73</v>
       </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>22</v>
       </c>
@@ -2826,29 +2822,29 @@
       <c r="L12">
         <v>0.14986856628506873</v>
       </c>
-      <c r="N12" t="s">
-        <v>69</v>
-      </c>
       <c r="O12" t="s">
+        <v>69</v>
+      </c>
+      <c r="P12" t="s">
         <v>22</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>78</v>
       </c>
-      <c r="Q12" t="s">
-        <v>71</v>
-      </c>
       <c r="R12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T12" t="s">
+        <v>80</v>
+      </c>
+      <c r="U12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>25</v>
       </c>
@@ -2870,29 +2866,29 @@
       <c r="L13">
         <v>0.14986856628506873</v>
       </c>
-      <c r="N13" t="s">
-        <v>69</v>
-      </c>
       <c r="O13" t="s">
+        <v>69</v>
+      </c>
+      <c r="P13" t="s">
         <v>25</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>78</v>
       </c>
-      <c r="Q13" t="s">
-        <v>71</v>
-      </c>
       <c r="R13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S13" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T13" t="s">
+        <v>80</v>
+      </c>
+      <c r="U13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -2914,29 +2910,29 @@
       <c r="L14">
         <v>0.14986856628506873</v>
       </c>
-      <c r="N14" t="s">
-        <v>69</v>
-      </c>
       <c r="O14" t="s">
+        <v>69</v>
+      </c>
+      <c r="P14" t="s">
         <v>27</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>78</v>
       </c>
-      <c r="Q14" t="s">
-        <v>71</v>
-      </c>
       <c r="R14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S14" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T14" t="s">
+        <v>80</v>
+      </c>
+      <c r="U14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -2970,29 +2966,29 @@
       <c r="L15">
         <v>0.1461854238754417</v>
       </c>
-      <c r="N15" t="s">
-        <v>69</v>
-      </c>
       <c r="O15" t="s">
+        <v>69</v>
+      </c>
+      <c r="P15" t="s">
         <v>29</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>78</v>
       </c>
-      <c r="Q15" t="s">
-        <v>71</v>
-      </c>
       <c r="R15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S15" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T15" t="s">
+        <v>80</v>
+      </c>
+      <c r="U15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>29</v>
       </c>
@@ -3026,29 +3022,29 @@
       <c r="L16">
         <v>0.1461854238754417</v>
       </c>
-      <c r="N16" t="s">
-        <v>69</v>
-      </c>
       <c r="O16" t="s">
+        <v>69</v>
+      </c>
+      <c r="P16" t="s">
         <v>30</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>78</v>
       </c>
-      <c r="Q16" t="s">
-        <v>71</v>
-      </c>
       <c r="R16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S16" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T16" t="s">
+        <v>80</v>
+      </c>
+      <c r="U16" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>30</v>
       </c>
@@ -3082,29 +3078,29 @@
       <c r="L17">
         <v>0.14867925344692126</v>
       </c>
-      <c r="N17" t="s">
-        <v>69</v>
-      </c>
       <c r="O17" t="s">
+        <v>69</v>
+      </c>
+      <c r="P17" t="s">
         <v>32</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>78</v>
       </c>
-      <c r="Q17" t="s">
-        <v>71</v>
-      </c>
       <c r="R17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S17" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T17" t="s">
+        <v>80</v>
+      </c>
+      <c r="U17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>32</v>
       </c>
@@ -3138,29 +3134,29 @@
       <c r="L18">
         <v>0.14701259708091721</v>
       </c>
-      <c r="N18" t="s">
-        <v>69</v>
-      </c>
       <c r="O18" t="s">
+        <v>69</v>
+      </c>
+      <c r="P18" t="s">
         <v>34</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>78</v>
       </c>
-      <c r="Q18" t="s">
-        <v>71</v>
-      </c>
       <c r="R18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S18" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T18" t="s">
+        <v>80</v>
+      </c>
+      <c r="U18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3194,29 +3190,29 @@
       <c r="L19">
         <v>0.15309859852159369</v>
       </c>
-      <c r="N19" t="s">
-        <v>69</v>
-      </c>
       <c r="O19" t="s">
+        <v>69</v>
+      </c>
+      <c r="P19" t="s">
         <v>35</v>
       </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>78</v>
       </c>
-      <c r="Q19" t="s">
-        <v>71</v>
-      </c>
       <c r="R19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S19" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T19" t="s">
+        <v>80</v>
+      </c>
+      <c r="U19" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -3250,29 +3246,29 @@
       <c r="L20">
         <v>0.15309859852159369</v>
       </c>
-      <c r="N20" t="s">
-        <v>69</v>
-      </c>
       <c r="O20" t="s">
+        <v>69</v>
+      </c>
+      <c r="P20" t="s">
         <v>37</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>78</v>
       </c>
-      <c r="Q20" t="s">
-        <v>71</v>
-      </c>
       <c r="R20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S20" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T20" t="s">
+        <v>80</v>
+      </c>
+      <c r="U20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>35</v>
       </c>
@@ -3306,29 +3302,29 @@
       <c r="L21">
         <v>0.15619560585976827</v>
       </c>
-      <c r="N21" t="s">
-        <v>69</v>
-      </c>
       <c r="O21" t="s">
+        <v>69</v>
+      </c>
+      <c r="P21" t="s">
         <v>39</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>78</v>
       </c>
-      <c r="Q21" t="s">
-        <v>71</v>
-      </c>
       <c r="R21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S21" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T21" t="s">
+        <v>80</v>
+      </c>
+      <c r="U21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>37</v>
       </c>
@@ -3362,29 +3358,29 @@
       <c r="L22">
         <v>0.14537310453496291</v>
       </c>
-      <c r="N22" t="s">
-        <v>69</v>
-      </c>
       <c r="O22" t="s">
+        <v>69</v>
+      </c>
+      <c r="P22" t="s">
         <v>40</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>78</v>
       </c>
-      <c r="Q22" t="s">
-        <v>71</v>
-      </c>
       <c r="R22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S22" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T22" t="s">
+        <v>80</v>
+      </c>
+      <c r="U22" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>39</v>
       </c>
@@ -3418,29 +3414,29 @@
       <c r="L23">
         <v>0.14763873655681015</v>
       </c>
-      <c r="N23" t="s">
-        <v>69</v>
-      </c>
       <c r="O23" t="s">
+        <v>69</v>
+      </c>
+      <c r="P23" t="s">
         <v>42</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>78</v>
       </c>
-      <c r="Q23" t="s">
-        <v>71</v>
-      </c>
       <c r="R23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S23" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T23" t="s">
+        <v>80</v>
+      </c>
+      <c r="U23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>40</v>
       </c>
@@ -3474,29 +3470,29 @@
       <c r="L24">
         <v>0.1532628310027955</v>
       </c>
-      <c r="N24" t="s">
-        <v>69</v>
-      </c>
       <c r="O24" t="s">
+        <v>69</v>
+      </c>
+      <c r="P24" t="s">
         <v>44</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>78</v>
       </c>
-      <c r="Q24" t="s">
-        <v>71</v>
-      </c>
       <c r="R24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S24" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T24" t="s">
+        <v>80</v>
+      </c>
+      <c r="U24" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>40</v>
       </c>
@@ -3530,29 +3526,29 @@
       <c r="L25">
         <v>0.1532628310027955</v>
       </c>
-      <c r="N25" t="s">
-        <v>69</v>
-      </c>
       <c r="O25" t="s">
+        <v>69</v>
+      </c>
+      <c r="P25" t="s">
         <v>47</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>78</v>
       </c>
-      <c r="Q25" t="s">
-        <v>71</v>
-      </c>
       <c r="R25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S25" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T25" t="s">
+        <v>80</v>
+      </c>
+      <c r="U25" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>42</v>
       </c>
@@ -3586,29 +3582,29 @@
       <c r="L26">
         <v>0.1451997589052581</v>
       </c>
-      <c r="N26" t="s">
-        <v>69</v>
-      </c>
       <c r="O26" t="s">
+        <v>69</v>
+      </c>
+      <c r="P26" t="s">
         <v>49</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>78</v>
       </c>
-      <c r="Q26" t="s">
-        <v>71</v>
-      </c>
       <c r="R26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S26" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T26" t="s">
+        <v>80</v>
+      </c>
+      <c r="U26" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>44</v>
       </c>
@@ -3627,32 +3623,32 @@
       <c r="G27">
         <v>0.33123000000000002</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>0.42012333946150526</v>
       </c>
-      <c r="N27" t="s">
-        <v>69</v>
-      </c>
       <c r="O27" t="s">
+        <v>69</v>
+      </c>
+      <c r="P27" t="s">
         <v>51</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>78</v>
       </c>
-      <c r="Q27" t="s">
-        <v>71</v>
-      </c>
       <c r="R27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S27" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T27" t="s">
+        <v>80</v>
+      </c>
+      <c r="U27" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>47</v>
       </c>
@@ -3671,32 +3667,32 @@
       <c r="G28">
         <v>0.33123000000000002</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>0.42012333946150526</v>
       </c>
-      <c r="N28" t="s">
-        <v>69</v>
-      </c>
       <c r="O28" t="s">
+        <v>69</v>
+      </c>
+      <c r="P28" t="s">
         <v>53</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>78</v>
       </c>
-      <c r="Q28" t="s">
-        <v>71</v>
-      </c>
       <c r="R28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S28" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T28" t="s">
+        <v>80</v>
+      </c>
+      <c r="U28" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>49</v>
       </c>
@@ -3715,32 +3711,32 @@
       <c r="G29">
         <v>0.33123000000000002</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>0.42012333946150526</v>
       </c>
-      <c r="N29" t="s">
-        <v>69</v>
-      </c>
       <c r="O29" t="s">
+        <v>69</v>
+      </c>
+      <c r="P29" t="s">
         <v>55</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>78</v>
       </c>
-      <c r="Q29" t="s">
-        <v>71</v>
-      </c>
       <c r="R29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S29" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T29" t="s">
+        <v>80</v>
+      </c>
+      <c r="U29" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>51</v>
       </c>
@@ -3771,32 +3767,32 @@
       <c r="K30">
         <v>46</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>0.47763777043344691</v>
       </c>
-      <c r="N30" t="s">
-        <v>69</v>
-      </c>
       <c r="O30" t="s">
+        <v>69</v>
+      </c>
+      <c r="P30" t="s">
         <v>57</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>78</v>
       </c>
-      <c r="Q30" t="s">
-        <v>71</v>
-      </c>
       <c r="R30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S30" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T30" t="s">
+        <v>80</v>
+      </c>
+      <c r="U30" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>53</v>
       </c>
@@ -3827,32 +3823,32 @@
       <c r="K31">
         <v>45</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>0.47814004703314078</v>
       </c>
-      <c r="N31" t="s">
-        <v>69</v>
-      </c>
       <c r="O31" t="s">
+        <v>69</v>
+      </c>
+      <c r="P31" t="s">
         <v>59</v>
       </c>
-      <c r="P31" t="s">
+      <c r="Q31" t="s">
         <v>78</v>
       </c>
-      <c r="Q31" t="s">
-        <v>71</v>
-      </c>
       <c r="R31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S31" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T31" t="s">
+        <v>80</v>
+      </c>
+      <c r="U31" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>53</v>
       </c>
@@ -3883,32 +3879,32 @@
       <c r="K32">
         <v>40</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>0.47814004703314084</v>
       </c>
-      <c r="N32" t="s">
-        <v>69</v>
-      </c>
       <c r="O32" t="s">
+        <v>69</v>
+      </c>
+      <c r="P32" t="s">
         <v>61</v>
       </c>
-      <c r="P32" t="s">
+      <c r="Q32" t="s">
         <v>81</v>
       </c>
-      <c r="Q32" t="s">
-        <v>71</v>
-      </c>
       <c r="R32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S32" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T32" t="s">
+        <v>80</v>
+      </c>
+      <c r="U32" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>53</v>
       </c>
@@ -3939,17 +3935,17 @@
       <c r="K33">
         <v>35</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>0.47814004703314078</v>
       </c>
-      <c r="N33" t="s">
+      <c r="O33" t="s">
         <v>140</v>
       </c>
-      <c r="O33" s="1" t="s">
+      <c r="P33" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>55</v>
       </c>
@@ -3980,32 +3976,32 @@
       <c r="K34">
         <v>48</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>0.40144059976798208</v>
       </c>
-      <c r="N34" t="s">
-        <v>69</v>
-      </c>
       <c r="O34" t="s">
+        <v>69</v>
+      </c>
+      <c r="P34" t="s">
         <v>194</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>163</v>
       </c>
-      <c r="Q34" t="s">
-        <v>71</v>
-      </c>
       <c r="R34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S34" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T34" t="s">
+        <v>80</v>
+      </c>
+      <c r="U34" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>55</v>
       </c>
@@ -4036,32 +4032,32 @@
       <c r="K35">
         <v>44</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>0.40144059976798202</v>
       </c>
-      <c r="N35" t="s">
-        <v>69</v>
-      </c>
       <c r="O35" t="s">
+        <v>69</v>
+      </c>
+      <c r="P35" t="s">
         <v>193</v>
       </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
         <v>148</v>
       </c>
-      <c r="Q35" t="s">
-        <v>71</v>
-      </c>
       <c r="R35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S35" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T35" t="s">
+        <v>80</v>
+      </c>
+      <c r="U35" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>55</v>
       </c>
@@ -4092,32 +4088,32 @@
       <c r="K36">
         <v>43</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>0.40144059976798202</v>
       </c>
-      <c r="N36" t="s">
-        <v>69</v>
-      </c>
       <c r="O36" t="s">
+        <v>69</v>
+      </c>
+      <c r="P36" t="s">
         <v>195</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
         <v>149</v>
       </c>
-      <c r="Q36" t="s">
-        <v>71</v>
-      </c>
       <c r="R36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S36" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T36" t="s">
+        <v>80</v>
+      </c>
+      <c r="U36" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>55</v>
       </c>
@@ -4148,32 +4144,32 @@
       <c r="K37">
         <v>32</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>0.40144059976798208</v>
       </c>
-      <c r="N37" t="s">
-        <v>69</v>
-      </c>
       <c r="O37" t="s">
+        <v>69</v>
+      </c>
+      <c r="P37" t="s">
         <v>196</v>
       </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
         <v>150</v>
       </c>
-      <c r="Q37" t="s">
-        <v>71</v>
-      </c>
       <c r="R37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S37" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T37" t="s">
+        <v>80</v>
+      </c>
+      <c r="U37" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>55</v>
       </c>
@@ -4204,32 +4200,32 @@
       <c r="K38">
         <v>31</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>0.40144059976798202</v>
       </c>
-      <c r="N38" t="s">
-        <v>69</v>
-      </c>
       <c r="O38" t="s">
+        <v>69</v>
+      </c>
+      <c r="P38" t="s">
         <v>142</v>
       </c>
-      <c r="P38" t="s">
+      <c r="Q38" t="s">
         <v>161</v>
       </c>
-      <c r="Q38" t="s">
-        <v>71</v>
-      </c>
       <c r="R38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S38" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T38" t="s">
+        <v>80</v>
+      </c>
+      <c r="U38" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>57</v>
       </c>
@@ -4260,32 +4256,32 @@
       <c r="K39">
         <v>32</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>0.365520596150406</v>
       </c>
-      <c r="N39" t="s">
-        <v>69</v>
-      </c>
       <c r="O39" t="s">
+        <v>69</v>
+      </c>
+      <c r="P39" t="s">
         <v>143</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>151</v>
       </c>
-      <c r="Q39" t="s">
-        <v>71</v>
-      </c>
       <c r="R39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S39" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T39" t="s">
+        <v>80</v>
+      </c>
+      <c r="U39" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>59</v>
       </c>
@@ -4316,32 +4312,32 @@
       <c r="K40">
         <v>50</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>0.41047488326249421</v>
       </c>
-      <c r="N40" t="s">
-        <v>69</v>
-      </c>
       <c r="O40" t="s">
+        <v>69</v>
+      </c>
+      <c r="P40" t="s">
         <v>144</v>
       </c>
-      <c r="P40" t="s">
+      <c r="Q40" t="s">
         <v>152</v>
       </c>
-      <c r="Q40" t="s">
-        <v>71</v>
-      </c>
       <c r="R40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S40" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T40" t="s">
+        <v>80</v>
+      </c>
+      <c r="U40" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>59</v>
       </c>
@@ -4372,32 +4368,32 @@
       <c r="K41">
         <v>43</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>0.41047488326249421</v>
       </c>
-      <c r="N41" t="s">
-        <v>69</v>
-      </c>
       <c r="O41" t="s">
+        <v>69</v>
+      </c>
+      <c r="P41" t="s">
         <v>145</v>
       </c>
-      <c r="P41" t="s">
+      <c r="Q41" t="s">
         <v>153</v>
       </c>
-      <c r="Q41" t="s">
-        <v>71</v>
-      </c>
       <c r="R41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S41" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T41" t="s">
+        <v>80</v>
+      </c>
+      <c r="U41" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>59</v>
       </c>
@@ -4428,32 +4424,32 @@
       <c r="K42">
         <v>42</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>0.41047488326249421</v>
       </c>
-      <c r="N42" t="s">
-        <v>69</v>
-      </c>
       <c r="O42" t="s">
+        <v>69</v>
+      </c>
+      <c r="P42" t="s">
         <v>146</v>
       </c>
-      <c r="P42" t="s">
+      <c r="Q42" t="s">
         <v>147</v>
       </c>
-      <c r="Q42" t="s">
-        <v>71</v>
-      </c>
       <c r="R42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S42" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T42" t="s">
+        <v>80</v>
+      </c>
+      <c r="U42" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>61</v>
       </c>
@@ -4484,61 +4480,61 @@
       <c r="K43">
         <v>31</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>0.365520596150406</v>
       </c>
-      <c r="N43" t="s">
-        <v>69</v>
-      </c>
       <c r="O43" t="s">
+        <v>69</v>
+      </c>
+      <c r="P43" t="s">
         <v>197</v>
       </c>
-      <c r="P43" t="s">
+      <c r="Q43" t="s">
         <v>162</v>
       </c>
-      <c r="Q43" t="s">
-        <v>71</v>
-      </c>
       <c r="R43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S43" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T43" t="s">
+        <v>80</v>
+      </c>
+      <c r="U43" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>140</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="N44" t="s">
-        <v>69</v>
-      </c>
       <c r="O44" t="s">
+        <v>69</v>
+      </c>
+      <c r="P44" t="s">
         <v>154</v>
       </c>
-      <c r="P44" t="s">
+      <c r="Q44" t="s">
         <v>155</v>
       </c>
-      <c r="Q44" t="s">
-        <v>71</v>
-      </c>
       <c r="R44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S44" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T44" t="s">
+        <v>80</v>
+      </c>
+      <c r="U44" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>196</v>
       </c>
@@ -4569,29 +4565,29 @@
       <c r="K45">
         <v>40</v>
       </c>
-      <c r="N45" t="s">
-        <v>69</v>
-      </c>
       <c r="O45" t="s">
+        <v>69</v>
+      </c>
+      <c r="P45" t="s">
         <v>156</v>
       </c>
-      <c r="P45" t="s">
+      <c r="Q45" t="s">
         <v>157</v>
       </c>
-      <c r="Q45" t="s">
-        <v>71</v>
-      </c>
       <c r="R45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S45" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T45" t="s">
+        <v>80</v>
+      </c>
+      <c r="U45" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>194</v>
       </c>
@@ -4622,29 +4618,29 @@
       <c r="K46">
         <v>40</v>
       </c>
-      <c r="N46" t="s">
-        <v>69</v>
-      </c>
       <c r="O46" t="s">
+        <v>69</v>
+      </c>
+      <c r="P46" t="s">
         <v>170</v>
       </c>
-      <c r="P46" t="s">
+      <c r="Q46" t="s">
         <v>171</v>
       </c>
-      <c r="Q46" t="s">
-        <v>71</v>
-      </c>
       <c r="R46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S46" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T46" t="s">
+        <v>80</v>
+      </c>
+      <c r="U46" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>193</v>
       </c>
@@ -4675,29 +4671,29 @@
       <c r="K47">
         <v>40</v>
       </c>
-      <c r="N47" t="s">
-        <v>69</v>
-      </c>
       <c r="O47" t="s">
+        <v>69</v>
+      </c>
+      <c r="P47" t="s">
         <v>158</v>
       </c>
-      <c r="P47" t="s">
+      <c r="Q47" t="s">
         <v>159</v>
       </c>
-      <c r="Q47" t="s">
-        <v>71</v>
-      </c>
       <c r="R47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S47" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T47" t="s">
+        <v>80</v>
+      </c>
+      <c r="U47" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>195</v>
       </c>
@@ -4728,29 +4724,29 @@
       <c r="K48">
         <v>40</v>
       </c>
-      <c r="N48" t="s">
-        <v>69</v>
-      </c>
       <c r="O48" t="s">
+        <v>69</v>
+      </c>
+      <c r="P48" t="s">
         <v>169</v>
       </c>
-      <c r="P48" t="s">
+      <c r="Q48" t="s">
         <v>160</v>
       </c>
-      <c r="Q48" t="s">
-        <v>71</v>
-      </c>
       <c r="R48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S48" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T48" t="s">
+        <v>80</v>
+      </c>
+      <c r="U48" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>142</v>
       </c>
@@ -4781,29 +4777,29 @@
       <c r="K49">
         <v>40</v>
       </c>
-      <c r="N49" t="s">
-        <v>69</v>
-      </c>
       <c r="O49" t="s">
+        <v>69</v>
+      </c>
+      <c r="P49" t="s">
         <v>164</v>
       </c>
-      <c r="P49" t="s">
+      <c r="Q49" t="s">
         <v>165</v>
       </c>
-      <c r="Q49" t="s">
-        <v>71</v>
-      </c>
       <c r="R49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S49" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T49" t="s">
+        <v>80</v>
+      </c>
+      <c r="U49" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>143</v>
       </c>
@@ -4834,29 +4830,29 @@
       <c r="K50">
         <v>40</v>
       </c>
-      <c r="N50" t="s">
-        <v>69</v>
-      </c>
       <c r="O50" t="s">
+        <v>69</v>
+      </c>
+      <c r="P50" t="s">
         <v>168</v>
       </c>
-      <c r="P50" t="s">
+      <c r="Q50" t="s">
         <v>166</v>
       </c>
-      <c r="Q50" t="s">
-        <v>71</v>
-      </c>
       <c r="R50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S50" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T50" t="s">
+        <v>80</v>
+      </c>
+      <c r="U50" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>144</v>
       </c>
@@ -4887,29 +4883,29 @@
       <c r="K51">
         <v>40</v>
       </c>
-      <c r="N51" t="s">
-        <v>69</v>
-      </c>
       <c r="O51" t="s">
+        <v>69</v>
+      </c>
+      <c r="P51" t="s">
         <v>198</v>
       </c>
-      <c r="P51" t="s">
+      <c r="Q51" t="s">
         <v>167</v>
       </c>
-      <c r="Q51" t="s">
-        <v>71</v>
-      </c>
       <c r="R51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S51" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T51" t="s">
+        <v>80</v>
+      </c>
+      <c r="U51" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>145</v>
       </c>
@@ -4940,29 +4936,29 @@
       <c r="K52">
         <v>40</v>
       </c>
-      <c r="N52" t="s">
-        <v>69</v>
-      </c>
       <c r="O52" t="s">
+        <v>69</v>
+      </c>
+      <c r="P52" t="s">
         <v>172</v>
       </c>
-      <c r="P52" t="s">
+      <c r="Q52" t="s">
         <v>173</v>
       </c>
-      <c r="Q52" t="s">
-        <v>71</v>
-      </c>
       <c r="R52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S52" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T52" t="s">
+        <v>80</v>
+      </c>
+      <c r="U52" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>146</v>
       </c>
@@ -4993,29 +4989,29 @@
       <c r="K53">
         <v>40</v>
       </c>
-      <c r="N53" t="s">
-        <v>69</v>
-      </c>
       <c r="O53" t="s">
+        <v>69</v>
+      </c>
+      <c r="P53" t="s">
         <v>174</v>
       </c>
-      <c r="P53" t="s">
+      <c r="Q53" t="s">
         <v>175</v>
       </c>
-      <c r="Q53" t="s">
-        <v>71</v>
-      </c>
       <c r="R53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S53" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T53" t="s">
+        <v>80</v>
+      </c>
+      <c r="U53" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>197</v>
       </c>
@@ -5046,29 +5042,29 @@
       <c r="K54">
         <v>40</v>
       </c>
-      <c r="N54" t="s">
-        <v>69</v>
-      </c>
       <c r="O54" t="s">
+        <v>69</v>
+      </c>
+      <c r="P54" t="s">
         <v>176</v>
       </c>
-      <c r="P54" t="s">
+      <c r="Q54" t="s">
         <v>177</v>
       </c>
-      <c r="Q54" t="s">
-        <v>71</v>
-      </c>
       <c r="R54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S54" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T54" t="s">
+        <v>80</v>
+      </c>
+      <c r="U54" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>154</v>
       </c>
@@ -5099,29 +5095,29 @@
       <c r="K55">
         <v>40</v>
       </c>
-      <c r="N55" t="s">
-        <v>69</v>
-      </c>
       <c r="O55" t="s">
+        <v>69</v>
+      </c>
+      <c r="P55" t="s">
         <v>178</v>
       </c>
-      <c r="P55" t="s">
+      <c r="Q55" t="s">
         <v>179</v>
       </c>
-      <c r="Q55" t="s">
-        <v>71</v>
-      </c>
       <c r="R55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S55" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T55" t="s">
+        <v>80</v>
+      </c>
+      <c r="U55" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>156</v>
       </c>
@@ -5152,29 +5148,29 @@
       <c r="K56">
         <v>40</v>
       </c>
-      <c r="N56" t="s">
-        <v>69</v>
-      </c>
       <c r="O56" t="s">
+        <v>69</v>
+      </c>
+      <c r="P56" t="s">
         <v>180</v>
       </c>
-      <c r="P56" t="s">
+      <c r="Q56" t="s">
         <v>181</v>
       </c>
-      <c r="Q56" t="s">
-        <v>71</v>
-      </c>
       <c r="R56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S56" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T56" t="s">
+        <v>80</v>
+      </c>
+      <c r="U56" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="57" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>170</v>
       </c>
@@ -5205,29 +5201,29 @@
       <c r="K57">
         <v>40</v>
       </c>
-      <c r="N57" t="s">
-        <v>69</v>
-      </c>
       <c r="O57" t="s">
+        <v>69</v>
+      </c>
+      <c r="P57" t="s">
         <v>182</v>
       </c>
-      <c r="P57" t="s">
+      <c r="Q57" t="s">
         <v>183</v>
       </c>
-      <c r="Q57" t="s">
-        <v>71</v>
-      </c>
       <c r="R57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S57" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T57" t="s">
+        <v>80</v>
+      </c>
+      <c r="U57" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="58" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>158</v>
       </c>
@@ -5258,29 +5254,29 @@
       <c r="K58">
         <v>40</v>
       </c>
-      <c r="N58" t="s">
-        <v>69</v>
-      </c>
       <c r="O58" t="s">
+        <v>69</v>
+      </c>
+      <c r="P58" t="s">
         <v>184</v>
       </c>
-      <c r="P58" t="s">
+      <c r="Q58" t="s">
         <v>185</v>
       </c>
-      <c r="Q58" t="s">
-        <v>71</v>
-      </c>
       <c r="R58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S58" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T58" t="s">
+        <v>80</v>
+      </c>
+      <c r="U58" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>169</v>
       </c>
@@ -5311,29 +5307,29 @@
       <c r="K59">
         <v>40</v>
       </c>
-      <c r="N59" t="s">
-        <v>69</v>
-      </c>
       <c r="O59" t="s">
+        <v>69</v>
+      </c>
+      <c r="P59" t="s">
         <v>186</v>
       </c>
-      <c r="P59" t="s">
+      <c r="Q59" t="s">
         <v>188</v>
       </c>
-      <c r="Q59" t="s">
-        <v>71</v>
-      </c>
       <c r="R59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S59" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T59" t="s">
+        <v>80</v>
+      </c>
+      <c r="U59" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>164</v>
       </c>
@@ -5364,29 +5360,29 @@
       <c r="K60">
         <v>40</v>
       </c>
-      <c r="N60" t="s">
-        <v>69</v>
-      </c>
       <c r="O60" t="s">
+        <v>69</v>
+      </c>
+      <c r="P60" t="s">
         <v>187</v>
       </c>
-      <c r="P60" t="s">
+      <c r="Q60" t="s">
         <v>189</v>
       </c>
-      <c r="Q60" t="s">
-        <v>71</v>
-      </c>
       <c r="R60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S60" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T60" t="s">
+        <v>80</v>
+      </c>
+      <c r="U60" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>168</v>
       </c>
@@ -5417,29 +5413,29 @@
       <c r="K61">
         <v>40</v>
       </c>
-      <c r="N61" t="s">
-        <v>69</v>
-      </c>
       <c r="O61" t="s">
+        <v>69</v>
+      </c>
+      <c r="P61" t="s">
         <v>190</v>
       </c>
-      <c r="P61" t="s">
+      <c r="Q61" t="s">
         <v>191</v>
       </c>
-      <c r="Q61" t="s">
-        <v>71</v>
-      </c>
       <c r="R61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S61" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="T61" t="s">
+        <v>80</v>
+      </c>
+      <c r="U61" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>198</v>
       </c>
@@ -5471,7 +5467,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="63" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>172</v>
       </c>
@@ -5503,7 +5499,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>174</v>
       </c>
@@ -5535,7 +5531,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>176</v>
       </c>
@@ -5567,7 +5563,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>178</v>
       </c>
@@ -5599,7 +5595,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>180</v>
       </c>
@@ -5631,7 +5627,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>182</v>
       </c>
@@ -5663,7 +5659,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>184</v>
       </c>
@@ -5695,7 +5691,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>186</v>
       </c>
@@ -5727,7 +5723,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>187</v>
       </c>
@@ -5759,7 +5755,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>190</v>
       </c>
@@ -5791,7 +5787,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>20</v>
       </c>
@@ -5822,29 +5818,29 @@
       <c r="K77">
         <v>42</v>
       </c>
-      <c r="N77" t="s">
-        <v>69</v>
-      </c>
       <c r="O77" t="s">
+        <v>69</v>
+      </c>
+      <c r="P77" t="s">
         <v>20</v>
       </c>
-      <c r="P77" t="s">
+      <c r="Q77" t="s">
         <v>79</v>
       </c>
-      <c r="Q77" t="s">
-        <v>71</v>
-      </c>
       <c r="R77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S77" t="s">
+        <v>72</v>
+      </c>
+      <c r="T77" t="s">
         <v>73</v>
       </c>
-      <c r="T77" t="s">
+      <c r="U77" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>15</v>
       </c>
@@ -5863,29 +5859,29 @@
       <c r="G78">
         <v>0.33123000000000002</v>
       </c>
-      <c r="N78" t="s">
-        <v>69</v>
-      </c>
       <c r="O78" t="s">
+        <v>69</v>
+      </c>
+      <c r="P78" t="s">
         <v>15</v>
       </c>
-      <c r="P78" t="s">
+      <c r="Q78" t="s">
         <v>75</v>
       </c>
-      <c r="Q78" t="s">
-        <v>71</v>
-      </c>
       <c r="R78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S78" t="s">
+        <v>72</v>
+      </c>
+      <c r="T78" t="s">
         <v>73</v>
       </c>
-      <c r="T78" t="s">
+      <c r="U78" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>18</v>
       </c>
@@ -5904,29 +5900,29 @@
       <c r="G79">
         <v>0.33123000000000002</v>
       </c>
-      <c r="N79" t="s">
-        <v>69</v>
-      </c>
       <c r="O79" t="s">
+        <v>69</v>
+      </c>
+      <c r="P79" t="s">
         <v>18</v>
       </c>
-      <c r="P79" t="s">
+      <c r="Q79" t="s">
         <v>78</v>
       </c>
-      <c r="Q79" t="s">
-        <v>71</v>
-      </c>
       <c r="R79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S79" t="s">
+        <v>72</v>
+      </c>
+      <c r="T79" t="s">
         <v>73</v>
       </c>
-      <c r="T79" t="s">
+      <c r="U79" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>12</v>
       </c>
@@ -5957,25 +5953,25 @@
       <c r="K80">
         <v>50</v>
       </c>
-      <c r="N80" t="s">
-        <v>69</v>
-      </c>
       <c r="O80" t="s">
+        <v>69</v>
+      </c>
+      <c r="P80" t="s">
         <v>12</v>
       </c>
-      <c r="P80" t="s">
+      <c r="Q80" t="s">
         <v>70</v>
       </c>
-      <c r="Q80" t="s">
-        <v>71</v>
-      </c>
       <c r="R80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S80" t="s">
+        <v>72</v>
+      </c>
+      <c r="T80" t="s">
         <v>73</v>
       </c>
-      <c r="T80" t="s">
+      <c r="U80" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5988,7 +5984,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CEAB3BD-FD82-4128-8F02-FA58B77D374D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5799CF-688A-4AD3-892E-93B97A30D83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3EB01F-46C1-4939-A353-B5D5BB70EDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -3623,8 +3623,12 @@
       <c r="G27">
         <v>0.33123000000000002</v>
       </c>
+      <c r="L27">
+        <v>0.42012333946150526</v>
+      </c>
       <c r="M27">
-        <v>0.42012333946150526</v>
+        <f>F27*L27*G27</f>
+        <v>2.0930123559331545E-3</v>
       </c>
       <c r="O27" t="s">
         <v>69</v>
@@ -3667,7 +3671,7 @@
       <c r="G28">
         <v>0.33123000000000002</v>
       </c>
-      <c r="M28">
+      <c r="L28">
         <v>0.42012333946150526</v>
       </c>
       <c r="O28" t="s">
@@ -3711,7 +3715,7 @@
       <c r="G29">
         <v>0.33123000000000002</v>
       </c>
-      <c r="M29">
+      <c r="L29">
         <v>0.42012333946150526</v>
       </c>
       <c r="O29" t="s">
@@ -3767,7 +3771,7 @@
       <c r="K30">
         <v>46</v>
       </c>
-      <c r="M30">
+      <c r="L30">
         <v>0.47763777043344691</v>
       </c>
       <c r="O30" t="s">
@@ -3823,7 +3827,7 @@
       <c r="K31">
         <v>45</v>
       </c>
-      <c r="M31">
+      <c r="L31">
         <v>0.47814004703314078</v>
       </c>
       <c r="O31" t="s">
@@ -3879,7 +3883,7 @@
       <c r="K32">
         <v>40</v>
       </c>
-      <c r="M32">
+      <c r="L32">
         <v>0.47814004703314084</v>
       </c>
       <c r="O32" t="s">
@@ -3935,7 +3939,7 @@
       <c r="K33">
         <v>35</v>
       </c>
-      <c r="M33">
+      <c r="L33">
         <v>0.47814004703314078</v>
       </c>
       <c r="O33" t="s">
@@ -3976,7 +3980,7 @@
       <c r="K34">
         <v>48</v>
       </c>
-      <c r="M34">
+      <c r="L34">
         <v>0.40144059976798208</v>
       </c>
       <c r="O34" t="s">
@@ -4032,7 +4036,7 @@
       <c r="K35">
         <v>44</v>
       </c>
-      <c r="M35">
+      <c r="L35">
         <v>0.40144059976798202</v>
       </c>
       <c r="O35" t="s">
@@ -4088,7 +4092,7 @@
       <c r="K36">
         <v>43</v>
       </c>
-      <c r="M36">
+      <c r="L36">
         <v>0.40144059976798202</v>
       </c>
       <c r="O36" t="s">
@@ -4144,7 +4148,7 @@
       <c r="K37">
         <v>32</v>
       </c>
-      <c r="M37">
+      <c r="L37">
         <v>0.40144059976798208</v>
       </c>
       <c r="O37" t="s">
@@ -4200,7 +4204,7 @@
       <c r="K38">
         <v>31</v>
       </c>
-      <c r="M38">
+      <c r="L38">
         <v>0.40144059976798202</v>
       </c>
       <c r="O38" t="s">
@@ -4256,7 +4260,7 @@
       <c r="K39">
         <v>32</v>
       </c>
-      <c r="M39">
+      <c r="L39">
         <v>0.365520596150406</v>
       </c>
       <c r="O39" t="s">
@@ -4312,7 +4316,7 @@
       <c r="K40">
         <v>50</v>
       </c>
-      <c r="M40">
+      <c r="L40">
         <v>0.41047488326249421</v>
       </c>
       <c r="O40" t="s">
@@ -4368,7 +4372,7 @@
       <c r="K41">
         <v>43</v>
       </c>
-      <c r="M41">
+      <c r="L41">
         <v>0.41047488326249421</v>
       </c>
       <c r="O41" t="s">
@@ -4424,7 +4428,7 @@
       <c r="K42">
         <v>42</v>
       </c>
-      <c r="M42">
+      <c r="L42">
         <v>0.41047488326249421</v>
       </c>
       <c r="O42" t="s">
@@ -4480,7 +4484,7 @@
       <c r="K43">
         <v>31</v>
       </c>
-      <c r="M43">
+      <c r="L43">
         <v>0.365520596150406</v>
       </c>
       <c r="O43" t="s">

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3EB01F-46C1-4939-A353-B5D5BB70EDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74A987E-9E0B-4551-9B53-262E94BE8FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <author>tc={E4726566-8322-459A-B187-5632353FCAD0}</author>
   </authors>
   <commentList>
-    <comment ref="B29" authorId="0" shapeId="0" xr:uid="{45C46737-1944-45AD-99CE-B8535D314683}">
+    <comment ref="B30" authorId="0" shapeId="0" xr:uid="{45C46737-1944-45AD-99CE-B8535D314683}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -53,7 +53,7 @@
     Testing_FERMI's idea</t>
       </text>
     </comment>
-    <comment ref="O29" authorId="1" shapeId="0" xr:uid="{E4726566-8322-459A-B187-5632353FCAD0}">
+    <comment ref="O30" authorId="1" shapeId="0" xr:uid="{E4726566-8322-459A-B187-5632353FCAD0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1143,10 +1143,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B29" dT="2026-01-28T14:50:45.09" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{45C46737-1944-45AD-99CE-B8535D314683}">
+  <threadedComment ref="B30" dT="2026-01-28T14:50:45.09" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{45C46737-1944-45AD-99CE-B8535D314683}">
     <text>Testing_FERMI's idea</text>
   </threadedComment>
-  <threadedComment ref="O29" dT="2026-01-28T14:50:45.09" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E4726566-8322-459A-B187-5632353FCAD0}">
+  <threadedComment ref="O30" dT="2026-01-28T14:50:45.09" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E4726566-8322-459A-B187-5632353FCAD0}">
     <text>Testing_FERMI's idea</text>
   </threadedComment>
 </ThreadedComments>
@@ -1540,7 +1540,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4FEF-80F2-457D-B441-6C3DD45005FF}">
-  <dimension ref="B9:T29"/>
+  <dimension ref="B9:T30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="39.26953125" bestFit="1" customWidth="1"/>
@@ -2603,56 +2603,56 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B29" t="s">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
         <v>201</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>202</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>14</v>
       </c>
-      <c r="E29">
+      <c r="E30">
         <v>2035</v>
       </c>
-      <c r="F29">
+      <c r="F30">
         <v>0.3</v>
       </c>
-      <c r="G29">
+      <c r="G30">
         <v>0.35</v>
       </c>
-      <c r="H29">
+      <c r="H30">
         <v>6000</v>
       </c>
-      <c r="I29">
+      <c r="I30">
         <v>150</v>
       </c>
-      <c r="J29">
+      <c r="J30">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="K29">
+      <c r="K30">
         <v>50</v>
       </c>
-      <c r="N29" t="s">
-        <v>69</v>
-      </c>
-      <c r="O29" t="s">
+      <c r="N30" t="s">
+        <v>69</v>
+      </c>
+      <c r="O30" t="s">
         <v>201</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P30" t="s">
         <v>203</v>
       </c>
-      <c r="Q29" t="s">
-        <v>71</v>
-      </c>
-      <c r="R29" t="s">
-        <v>72</v>
-      </c>
-      <c r="S29" t="s">
-        <v>80</v>
-      </c>
-      <c r="T29" t="s">
+      <c r="Q30" t="s">
+        <v>71</v>
+      </c>
+      <c r="R30" t="s">
+        <v>72</v>
+      </c>
+      <c r="S30" t="s">
+        <v>80</v>
+      </c>
+      <c r="T30" t="s">
         <v>74</v>
       </c>
     </row>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74A987E-9E0B-4551-9B53-262E94BE8FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1EA550-FEFE-4F7F-B1AC-92482F0CFE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -5470,6 +5470,27 @@
       <c r="K62">
         <v>40</v>
       </c>
+      <c r="O62" t="s">
+        <v>69</v>
+      </c>
+      <c r="P62" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>78</v>
+      </c>
+      <c r="R62" t="s">
+        <v>71</v>
+      </c>
+      <c r="S62" t="s">
+        <v>72</v>
+      </c>
+      <c r="T62" t="s">
+        <v>73</v>
+      </c>
+      <c r="U62" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
@@ -5791,6 +5812,26 @@
         <v>40</v>
       </c>
     </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73">
+        <v>2022</v>
+      </c>
+      <c r="F73">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G73">
+        <v>0.33123000000000002</v>
+      </c>
+    </row>
     <row r="77" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>20</v>
@@ -5882,47 +5923,6 @@
         <v>73</v>
       </c>
       <c r="U78" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.35">
-      <c r="B79" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" t="s">
-        <v>19</v>
-      </c>
-      <c r="D79" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79">
-        <v>2022</v>
-      </c>
-      <c r="F79">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G79">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="O79" t="s">
-        <v>69</v>
-      </c>
-      <c r="P79" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>78</v>
-      </c>
-      <c r="R79" t="s">
-        <v>71</v>
-      </c>
-      <c r="S79" t="s">
-        <v>72</v>
-      </c>
-      <c r="T79" t="s">
-        <v>73</v>
-      </c>
-      <c r="U79" t="s">
         <v>74</v>
       </c>
     </row>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krraik\OneDrive - Tallinna Tehnikaülikool\Desktop\TIMES\safe_save\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1EA550-FEFE-4F7F-B1AC-92482F0CFE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AAB29E-D831-4B02-B0BF-35238ADFE3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
-    <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
-    <sheet name="new_options" sheetId="3" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
+    <sheet name="new_options" sheetId="3" state="hidden" r:id="rId2"/>
     <sheet name="existing_stock" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -139,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="206">
   <si>
     <t>~fi_t</t>
   </si>
@@ -751,6 +750,12 @@
   </si>
   <si>
     <t>Fermi's small nuclear reactor</t>
+  </si>
+  <si>
+    <t>fi_process</t>
+  </si>
+  <si>
+    <t>fi_t</t>
   </si>
 </sst>
 </file>
@@ -1182,22 +1187,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047CB67-FC18-43CA-8AA0-0CA09A11D4D8}">
   <dimension ref="B9:T17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="46.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="73.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="73.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="N9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1253,7 +1258,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>130</v>
       </c>
@@ -1309,7 +1314,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>131</v>
       </c>
@@ -1365,7 +1370,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>132</v>
       </c>
@@ -1421,7 +1426,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>133</v>
       </c>
@@ -1477,7 +1482,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>134</v>
       </c>
@@ -1541,23 +1546,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4FEF-80F2-457D-B441-6C3DD45005FF}">
   <dimension ref="B9:T30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="39.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="39.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="48.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="N9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1613,7 +1618,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>200</v>
       </c>
@@ -1666,7 +1671,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>199</v>
       </c>
@@ -1719,7 +1724,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>86</v>
       </c>
@@ -1775,7 +1780,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>89</v>
       </c>
@@ -1831,7 +1836,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>91</v>
       </c>
@@ -1887,7 +1892,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>93</v>
       </c>
@@ -1943,7 +1948,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>94</v>
       </c>
@@ -1999,7 +2004,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>95</v>
       </c>
@@ -2055,7 +2060,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>96</v>
       </c>
@@ -2111,7 +2116,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>97</v>
       </c>
@@ -2161,7 +2166,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>98</v>
       </c>
@@ -2211,7 +2216,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>99</v>
       </c>
@@ -2267,7 +2272,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>100</v>
       </c>
@@ -2323,7 +2328,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>101</v>
       </c>
@@ -2379,7 +2384,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>103</v>
       </c>
@@ -2435,7 +2440,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>105</v>
       </c>
@@ -2491,7 +2496,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>106</v>
       </c>
@@ -2547,7 +2552,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>107</v>
       </c>
@@ -2603,7 +2608,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>201</v>
       </c>
@@ -2665,25 +2670,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
   <dimension ref="B9:U80"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="40.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="64.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -2691,7 +2696,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -2747,7 +2752,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -2797,10 +2802,10 @@
         <v>73</v>
       </c>
       <c r="U11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>22</v>
       </c>
@@ -2844,7 +2849,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>25</v>
       </c>
@@ -2888,7 +2893,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -2932,7 +2937,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -2988,7 +2993,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>29</v>
       </c>
@@ -3044,7 +3049,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>30</v>
       </c>
@@ -3100,7 +3105,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>32</v>
       </c>
@@ -3156,7 +3161,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3212,7 +3217,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -3268,7 +3273,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>35</v>
       </c>
@@ -3324,7 +3329,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>37</v>
       </c>
@@ -3380,7 +3385,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>39</v>
       </c>
@@ -3436,7 +3441,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>40</v>
       </c>
@@ -3492,7 +3497,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>40</v>
       </c>
@@ -3548,7 +3553,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>42</v>
       </c>
@@ -3604,7 +3609,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>44</v>
       </c>
@@ -3652,7 +3657,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>47</v>
       </c>
@@ -3696,7 +3701,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>49</v>
       </c>
@@ -3740,7 +3745,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>51</v>
       </c>
@@ -3796,7 +3801,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>53</v>
       </c>
@@ -3852,7 +3857,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>53</v>
       </c>
@@ -3905,10 +3910,10 @@
         <v>80</v>
       </c>
       <c r="U32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>53</v>
       </c>
@@ -3949,7 +3954,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>55</v>
       </c>
@@ -4005,7 +4010,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>55</v>
       </c>
@@ -4061,7 +4066,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>55</v>
       </c>
@@ -4117,7 +4122,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>55</v>
       </c>
@@ -4173,7 +4178,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>55</v>
       </c>
@@ -4229,7 +4234,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>57</v>
       </c>
@@ -4285,7 +4290,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>59</v>
       </c>
@@ -4341,7 +4346,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>59</v>
       </c>
@@ -4397,7 +4402,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>59</v>
       </c>
@@ -4453,7 +4458,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>61</v>
       </c>
@@ -4509,7 +4514,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>140</v>
       </c>
@@ -4538,7 +4543,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>196</v>
       </c>
@@ -4591,7 +4596,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>194</v>
       </c>
@@ -4644,7 +4649,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>193</v>
       </c>
@@ -4697,7 +4702,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>195</v>
       </c>
@@ -4750,7 +4755,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>142</v>
       </c>
@@ -4803,7 +4808,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>143</v>
       </c>
@@ -4856,7 +4861,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>144</v>
       </c>
@@ -4909,7 +4914,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>145</v>
       </c>
@@ -4962,7 +4967,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>146</v>
       </c>
@@ -5015,7 +5020,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>197</v>
       </c>
@@ -5068,7 +5073,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>154</v>
       </c>
@@ -5121,7 +5126,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>156</v>
       </c>
@@ -5174,7 +5179,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>170</v>
       </c>
@@ -5227,7 +5232,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="58" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>158</v>
       </c>
@@ -5280,7 +5285,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>169</v>
       </c>
@@ -5333,7 +5338,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>164</v>
       </c>
@@ -5386,7 +5391,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>168</v>
       </c>
@@ -5439,7 +5444,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>198</v>
       </c>
@@ -5492,7 +5497,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>172</v>
       </c>
@@ -5524,7 +5529,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>174</v>
       </c>
@@ -5556,7 +5561,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>176</v>
       </c>
@@ -5588,7 +5593,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>178</v>
       </c>
@@ -5620,7 +5625,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>180</v>
       </c>
@@ -5652,7 +5657,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>182</v>
       </c>
@@ -5684,7 +5689,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>184</v>
       </c>
@@ -5716,7 +5721,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>186</v>
       </c>
@@ -5748,7 +5753,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>187</v>
       </c>
@@ -5780,7 +5785,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>190</v>
       </c>
@@ -5812,7 +5817,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>18</v>
       </c>
@@ -5832,7 +5837,7 @@
         <v>0.33123000000000002</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>20</v>
       </c>
@@ -5885,7 +5890,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>15</v>
       </c>
@@ -5926,7 +5931,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>12</v>
       </c>
@@ -5983,13 +5988,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CEAB3BD-FD82-4128-8F02-FA58B77D374D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krraik\OneDrive - Tallinna Tehnikaülikool\Desktop\TIMES\safe_save\ee-times\VerveStacks_EST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AAB29E-D831-4B02-B0BF-35238ADFE3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51ED127A-8553-4582-935B-6420084AD8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
-    <sheet name="new_options" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="new_options" sheetId="3" r:id="rId2"/>
     <sheet name="existing_stock" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -72,11 +72,12 @@
     <author>tc={06D70610-96F7-4BDA-B071-69925D70228B}</author>
     <author>tc={A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}</author>
     <author>tc={4E0E017D-BAC7-4AA8-B401-A7330F2C0996}</author>
+    <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
     <author>tc={1905391B-2A5F-4643-B2AC-720AD8410CDA}</author>
     <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
   </authors>
   <commentList>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -84,7 +85,7 @@
     Iru produces only 17 MW in 2025 not 0.207 GW</t>
       </text>
     </comment>
-    <comment ref="B45" authorId="1" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+    <comment ref="B46" authorId="1" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -92,7 +93,7 @@
     TODO: set their actual start date and then add how much they produce in 2025</t>
       </text>
     </comment>
-    <comment ref="G46" authorId="2" shapeId="0" xr:uid="{06D70610-96F7-4BDA-B071-69925D70228B}">
+    <comment ref="G47" authorId="2" shapeId="0" xr:uid="{06D70610-96F7-4BDA-B071-69925D70228B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -117,7 +118,16 @@
     DAE - Wood pellets, Medium 2020</t>
       </text>
     </comment>
-    <comment ref="O77" authorId="5" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <comment ref="E53" authorId="5" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Ei tea
+</t>
+      </text>
+    </comment>
+    <comment ref="O77" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -125,7 +135,7 @@
     Frequency reserve</t>
       </text>
     </comment>
-    <comment ref="J80" authorId="6" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <comment ref="J80" authorId="7" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -138,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="206">
   <si>
     <t>~fi_t</t>
   </si>
@@ -765,7 +775,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -780,6 +790,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1159,13 +1175,13 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F11" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+  <threadedComment ref="F45" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
-  <threadedComment ref="B45" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+  <threadedComment ref="B46" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
     <text>TODO: set their actual start date and then add how much they produce in 2025</text>
   </threadedComment>
-  <threadedComment ref="G46" dT="2026-01-28T09:05:36.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{06D70610-96F7-4BDA-B071-69925D70228B}">
+  <threadedComment ref="G47" dT="2026-01-28T09:05:36.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{06D70610-96F7-4BDA-B071-69925D70228B}">
     <text>Danish Energy agency - coal CHP 2020</text>
   </threadedComment>
   <threadedComment ref="G49" dT="2026-01-28T11:16:21.05" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
@@ -1174,6 +1190,10 @@
   </threadedComment>
   <threadedComment ref="G50" dT="2026-01-28T11:17:46.06" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
     <text>DAE - Wood pellets, Medium 2020</text>
+  </threadedComment>
+  <threadedComment ref="E53" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
+    <text xml:space="preserve">Ei tea
+</text>
   </threadedComment>
   <threadedComment ref="O77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
@@ -2753,36 +2773,6 @@
       </c>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11">
-        <v>1982</v>
-      </c>
-      <c r="F11">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="G11">
-        <v>0.44290000000000002</v>
-      </c>
-      <c r="H11">
-        <v>1265</v>
-      </c>
-      <c r="I11" s="3">
-        <v>36.300000000000004</v>
-      </c>
-      <c r="J11">
-        <v>3.4650000000000007</v>
-      </c>
-      <c r="K11">
-        <v>73</v>
-      </c>
       <c r="O11" t="s">
         <v>69</v>
       </c>
@@ -4545,34 +4535,34 @@
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>196</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
       </c>
       <c r="E45">
-        <v>2021</v>
+        <v>1982</v>
       </c>
       <c r="F45">
-        <v>0.77</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="G45">
-        <v>0.49</v>
+        <v>0.44290000000000002</v>
       </c>
       <c r="H45">
-        <v>2150</v>
+        <v>1265</v>
       </c>
       <c r="I45" s="3">
-        <v>35.053609999999999</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="J45">
-        <v>3.28</v>
+        <v>3.4650000000000007</v>
       </c>
       <c r="K45">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="O45" t="s">
         <v>69</v>
@@ -4598,7 +4588,7 @@
     </row>
     <row r="46" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C46" t="s">
         <v>192</v>
@@ -4607,10 +4597,10 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>2021</v>
+        <v>1965</v>
       </c>
       <c r="F46">
-        <v>0.26</v>
+        <v>0.77</v>
       </c>
       <c r="G46">
         <v>0.49</v>
@@ -4625,7 +4615,7 @@
         <v>3.28</v>
       </c>
       <c r="K46">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="O46" t="s">
         <v>69</v>
@@ -4651,7 +4641,7 @@
     </row>
     <row r="47" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C47" t="s">
         <v>192</v>
@@ -4660,10 +4650,10 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="F47">
-        <v>0.185</v>
+        <v>0.26</v>
       </c>
       <c r="G47">
         <v>0.49</v>
@@ -4704,7 +4694,7 @@
     </row>
     <row r="48" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C48" t="s">
         <v>192</v>
@@ -4713,10 +4703,10 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>2021</v>
+        <v>1956</v>
       </c>
       <c r="F48">
-        <v>0.01</v>
+        <v>0.185</v>
       </c>
       <c r="G48">
         <v>0.49</v>
@@ -4731,7 +4721,7 @@
         <v>3.28</v>
       </c>
       <c r="K48">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="O48" t="s">
         <v>69</v>
@@ -4819,7 +4809,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="F50">
         <v>3.9E-2</v>
@@ -4872,7 +4862,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>2021</v>
+        <v>2009</v>
       </c>
       <c r="F51">
         <v>2.2100000000000002E-2</v>
@@ -4925,7 +4915,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="F52">
         <v>2.0500000000000001E-2</v>
@@ -4978,7 +4968,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>2021</v>
+        <v>2010</v>
       </c>
       <c r="F53">
         <v>1.3900000000000001E-2</v>
@@ -5031,7 +5021,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>2021</v>
+        <v>1997</v>
       </c>
       <c r="F54">
         <v>0.01</v>
@@ -5084,7 +5074,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="F55">
         <v>0.01</v>
@@ -5137,7 +5127,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="F56">
         <v>0.01</v>
@@ -5190,7 +5180,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="F57">
         <v>9.300000000000001E-3</v>
@@ -5243,7 +5233,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>2021</v>
+        <v>1963</v>
       </c>
       <c r="F58">
         <v>7.0999999999999995E-3</v>
@@ -5261,7 +5251,7 @@
         <v>1.9778732554800003</v>
       </c>
       <c r="K58">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="O58" t="s">
         <v>69</v>
@@ -5296,7 +5286,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F59">
         <v>5.7999999999999996E-3</v>
@@ -5349,7 +5339,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="F60">
         <v>6.4999999999999997E-3</v>
@@ -5402,7 +5392,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="F61">
         <v>4.0999999999999995E-3</v>
@@ -5455,7 +5445,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="F62">
         <v>1.4E-3</v>
@@ -5508,7 +5498,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="F63">
         <v>1.8E-3</v>
@@ -5540,7 +5530,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="F64">
         <v>1.6999999999999999E-3</v>
@@ -5572,7 +5562,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>2021</v>
+        <v>2009</v>
       </c>
       <c r="F65">
         <v>1.8E-3</v>
@@ -5604,7 +5594,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="F66">
         <v>1.8E-3</v>
@@ -5636,7 +5626,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="F67">
         <v>1.5E-3</v>
@@ -5668,7 +5658,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="F68">
         <v>1.4E-3</v>
@@ -5700,7 +5690,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="F69">
         <v>1.1999999999999999E-3</v>
@@ -5732,7 +5722,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>2021</v>
+        <v>2009</v>
       </c>
       <c r="F70">
         <v>1.9E-3</v>
@@ -5764,7 +5754,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="F71">
         <v>8.9999999999999998E-4</v>
@@ -5796,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="F72">
         <v>5.0000000000000001E-4</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51ED127A-8553-4582-935B-6420084AD8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F74BA55-79F9-4208-A8DD-5D96FD3C5C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -77,7 +77,7 @@
     <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
   </authors>
   <commentList>
-    <comment ref="F45" authorId="0" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +85,7 @@
     Iru produces only 17 MW in 2025 not 0.207 GW</t>
       </text>
     </comment>
-    <comment ref="B46" authorId="1" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+    <comment ref="B45" authorId="1" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -93,7 +93,7 @@
     TODO: set their actual start date and then add how much they produce in 2025</t>
       </text>
     </comment>
-    <comment ref="G47" authorId="2" shapeId="0" xr:uid="{06D70610-96F7-4BDA-B071-69925D70228B}">
+    <comment ref="G46" authorId="2" shapeId="0" xr:uid="{06D70610-96F7-4BDA-B071-69925D70228B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -101,7 +101,7 @@
     Danish Energy agency - coal CHP 2020</t>
       </text>
     </comment>
-    <comment ref="G49" authorId="3" shapeId="0" xr:uid="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
+    <comment ref="G48" authorId="3" shapeId="0" xr:uid="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -110,7 +110,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="G50" authorId="4" shapeId="0" xr:uid="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
+    <comment ref="G49" authorId="4" shapeId="0" xr:uid="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -118,7 +118,7 @@
     DAE - Wood pellets, Medium 2020</t>
       </text>
     </comment>
-    <comment ref="E53" authorId="5" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
+    <comment ref="E52" authorId="5" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -135,7 +135,7 @@
     Frequency reserve</t>
       </text>
     </comment>
-    <comment ref="J80" authorId="7" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <comment ref="J79" authorId="7" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1175,30 +1175,30 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="F45" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+  <threadedComment ref="F44" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
-  <threadedComment ref="B46" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+  <threadedComment ref="B45" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
     <text>TODO: set their actual start date and then add how much they produce in 2025</text>
   </threadedComment>
-  <threadedComment ref="G47" dT="2026-01-28T09:05:36.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{06D70610-96F7-4BDA-B071-69925D70228B}">
+  <threadedComment ref="G46" dT="2026-01-28T09:05:36.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{06D70610-96F7-4BDA-B071-69925D70228B}">
     <text>Danish Energy agency - coal CHP 2020</text>
   </threadedComment>
-  <threadedComment ref="G49" dT="2026-01-28T11:16:21.05" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
+  <threadedComment ref="G48" dT="2026-01-28T11:16:21.05" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
     <text xml:space="preserve">DAE - gas engines 2020
 </text>
   </threadedComment>
-  <threadedComment ref="G50" dT="2026-01-28T11:17:46.06" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
+  <threadedComment ref="G49" dT="2026-01-28T11:17:46.06" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
     <text>DAE - Wood pellets, Medium 2020</text>
   </threadedComment>
-  <threadedComment ref="E53" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
+  <threadedComment ref="E52" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
     <text xml:space="preserve">Ei tea
 </text>
   </threadedComment>
   <threadedComment ref="O77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
   </threadedComment>
-  <threadedComment ref="J80" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+  <threadedComment ref="J79" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
     <text>From 9,24 to 6</text>
   </threadedComment>
 </ThreadedComments>
@@ -2773,6 +2773,27 @@
       </c>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11">
+        <v>2022</v>
+      </c>
+      <c r="F11">
+        <v>4.3091615634383719E-2</v>
+      </c>
+      <c r="G11">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L11">
+        <v>0.14986856628506873</v>
+      </c>
       <c r="O11" t="s">
         <v>69</v>
       </c>
@@ -2797,19 +2818,19 @@
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
         <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E12">
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>4.3091615634383719E-2</v>
+        <v>4.3344722222460344E-2</v>
       </c>
       <c r="G12">
         <v>0.33123000000000002</v>
@@ -2841,19 +2862,19 @@
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13">
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>4.3344722222460344E-2</v>
+        <v>3.9363662143155967E-2</v>
       </c>
       <c r="G13">
         <v>0.33123000000000002</v>
@@ -2885,25 +2906,37 @@
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F14">
-        <v>3.9363662143155967E-2</v>
+        <v>7.6700000000000004E-2</v>
       </c>
       <c r="G14">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1336.4999999999998</v>
+      </c>
+      <c r="I14" s="3">
+        <v>21.45</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>40</v>
       </c>
       <c r="L14">
-        <v>0.14986856628506873</v>
+        <v>0.1461854238754417</v>
       </c>
       <c r="O14" t="s">
         <v>69</v>
@@ -2938,25 +2971,25 @@
         <v>24</v>
       </c>
       <c r="E15">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="F15">
-        <v>7.6700000000000004E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>1336.4999999999998</v>
+        <v>1336.5</v>
       </c>
       <c r="I15" s="3">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L15">
         <v>0.1461854238754417</v>
@@ -2985,19 +3018,19 @@
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
         <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E16">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="F16">
-        <v>3.2000000000000001E-2</v>
+        <v>5.8200000000000002E-2</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -3012,10 +3045,10 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L16">
-        <v>0.1461854238754417</v>
+        <v>0.14867925344692126</v>
       </c>
       <c r="O16" t="s">
         <v>69</v>
@@ -3041,25 +3074,25 @@
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E17">
         <v>2015</v>
       </c>
       <c r="F17">
-        <v>5.8200000000000002E-2</v>
+        <v>2.9599999999999998E-2</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I17" s="3">
         <v>21.450000000000003</v>
@@ -3071,7 +3104,7 @@
         <v>40</v>
       </c>
       <c r="L17">
-        <v>0.14867925344692126</v>
+        <v>0.14701259708091721</v>
       </c>
       <c r="O17" t="s">
         <v>69</v>
@@ -3097,28 +3130,28 @@
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E18">
         <v>2015</v>
       </c>
       <c r="F18">
-        <v>2.9599999999999998E-2</v>
+        <v>5.3800000000000008E-2</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>1336.5000000000002</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I18" s="3">
-        <v>21.450000000000003</v>
+        <v>21.45</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3127,7 +3160,7 @@
         <v>40</v>
       </c>
       <c r="L18">
-        <v>0.14701259708091721</v>
+        <v>0.15309859852159369</v>
       </c>
       <c r="O18" t="s">
         <v>69</v>
@@ -3162,25 +3195,25 @@
         <v>26</v>
       </c>
       <c r="E19">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="F19">
-        <v>5.3800000000000008E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19">
-        <v>1336.4999999999998</v>
+        <v>1138.5</v>
       </c>
       <c r="I19" s="3">
-        <v>21.45</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L19">
         <v>0.15309859852159369</v>
@@ -3209,37 +3242,37 @@
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E20">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="F20">
-        <v>7.0000000000000007E-2</v>
+        <v>7.3000000000000009E-3</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>1138.5</v>
+        <v>1336.5</v>
       </c>
       <c r="I20" s="3">
-        <v>18.150000000000002</v>
+        <v>21.45</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L20">
-        <v>0.15309859852159369</v>
+        <v>0.15619560585976827</v>
       </c>
       <c r="O20" t="s">
         <v>69</v>
@@ -3265,19 +3298,19 @@
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E21">
         <v>2015</v>
       </c>
       <c r="F21">
-        <v>7.3000000000000009E-3</v>
+        <v>2.81E-2</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -3286,7 +3319,7 @@
         <v>1336.5</v>
       </c>
       <c r="I21" s="3">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3295,7 +3328,7 @@
         <v>40</v>
       </c>
       <c r="L21">
-        <v>0.15619560585976827</v>
+        <v>0.14537310453496291</v>
       </c>
       <c r="O21" t="s">
         <v>69</v>
@@ -3321,19 +3354,19 @@
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E22">
         <v>2015</v>
       </c>
       <c r="F22">
-        <v>2.81E-2</v>
+        <v>8.4900000000000003E-2</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -3351,7 +3384,7 @@
         <v>40</v>
       </c>
       <c r="L22">
-        <v>0.14537310453496291</v>
+        <v>0.14763873655681015</v>
       </c>
       <c r="O22" t="s">
         <v>69</v>
@@ -3377,28 +3410,28 @@
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E23">
         <v>2015</v>
       </c>
       <c r="F23">
-        <v>8.4900000000000003E-2</v>
+        <v>5.2399999999999995E-2</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I23" s="3">
-        <v>21.450000000000003</v>
+        <v>21.45</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3407,7 +3440,7 @@
         <v>40</v>
       </c>
       <c r="L23">
-        <v>0.14763873655681015</v>
+        <v>0.1532628310027955</v>
       </c>
       <c r="O23" t="s">
         <v>69</v>
@@ -3442,25 +3475,25 @@
         <v>41</v>
       </c>
       <c r="E24">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="F24">
-        <v>5.2399999999999995E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I24" s="3">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L24">
         <v>0.1532628310027955</v>
@@ -3489,19 +3522,19 @@
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
         <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E25">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="F25">
-        <v>0.02</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3516,10 +3549,10 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L25">
-        <v>0.1532628310027955</v>
+        <v>0.1451997589052581</v>
       </c>
       <c r="O25" t="s">
         <v>69</v>
@@ -3545,37 +3578,25 @@
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E26">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F26">
-        <v>3.2000000000000002E-3</v>
+        <v>1.5040605442498314E-2</v>
       </c>
       <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>1336.5</v>
-      </c>
-      <c r="I26" s="3">
-        <v>21.450000000000003</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>40</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="L26">
-        <v>0.1451997589052581</v>
+        <v>0.42012333946150526</v>
       </c>
       <c r="O26" t="s">
         <v>69</v>
@@ -3601,19 +3622,19 @@
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
         <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E27">
         <v>2022</v>
       </c>
       <c r="F27">
-        <v>1.5040605442498314E-2</v>
+        <v>1.5497656626156837E-2</v>
       </c>
       <c r="G27">
         <v>0.33123000000000002</v>
@@ -3622,7 +3643,7 @@
         <v>0.42012333946150526</v>
       </c>
       <c r="M27">
-        <f>F27*L27*G27</f>
+        <f>F26*L26*G26</f>
         <v>2.0930123559331545E-3</v>
       </c>
       <c r="O27" t="s">
@@ -3649,19 +3670,19 @@
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E28">
         <v>2022</v>
       </c>
       <c r="F28">
-        <v>1.5497656626156837E-2</v>
+        <v>1.4461737931344828E-2</v>
       </c>
       <c r="G28">
         <v>0.33123000000000002</v>
@@ -3693,25 +3714,37 @@
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
         <v>45</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E29">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="F29">
-        <v>1.4461737931344828E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G29">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>2376</v>
+      </c>
+      <c r="I29" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J29">
+        <v>2.52</v>
+      </c>
+      <c r="K29">
+        <v>46</v>
       </c>
       <c r="L29">
-        <v>0.42012333946150526</v>
+        <v>0.47763777043344691</v>
       </c>
       <c r="O29" t="s">
         <v>69</v>
@@ -3737,19 +3770,19 @@
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E30">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="F30">
-        <v>3.9E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3764,10 +3797,10 @@
         <v>2.52</v>
       </c>
       <c r="K30">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L30">
-        <v>0.47763777043344691</v>
+        <v>0.47814004703314078</v>
       </c>
       <c r="O30" t="s">
         <v>69</v>
@@ -3802,10 +3835,10 @@
         <v>54</v>
       </c>
       <c r="E31">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="F31">
-        <v>1.6E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -3814,16 +3847,16 @@
         <v>2376</v>
       </c>
       <c r="I31" s="3">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J31">
         <v>2.52</v>
       </c>
       <c r="K31">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L31">
-        <v>0.47814004703314078</v>
+        <v>0.47814004703314084</v>
       </c>
       <c r="O31" t="s">
         <v>69</v>
@@ -3858,10 +3891,10 @@
         <v>54</v>
       </c>
       <c r="E32">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="F32">
-        <v>1.7999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -3876,10 +3909,10 @@
         <v>2.52</v>
       </c>
       <c r="K32">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L32">
-        <v>0.47814004703314084</v>
+        <v>0.47814004703314078</v>
       </c>
       <c r="O32" t="s">
         <v>69</v>
@@ -3905,19 +3938,19 @@
     </row>
     <row r="33" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E33">
-        <v>2020</v>
+        <v>2007</v>
       </c>
       <c r="F33">
-        <v>1.2E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3926,16 +3959,16 @@
         <v>2376</v>
       </c>
       <c r="I33" s="3">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J33">
         <v>2.52</v>
       </c>
       <c r="K33">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L33">
-        <v>0.47814004703314078</v>
+        <v>0.40144059976798208</v>
       </c>
       <c r="O33" t="s">
         <v>140</v>
@@ -3955,10 +3988,10 @@
         <v>56</v>
       </c>
       <c r="E34">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="F34">
-        <v>2.1000000000000001E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -3967,16 +4000,16 @@
         <v>2376</v>
       </c>
       <c r="I34" s="3">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J34">
         <v>2.52</v>
       </c>
       <c r="K34">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L34">
-        <v>0.40144059976798208</v>
+        <v>0.40144059976798202</v>
       </c>
       <c r="O34" t="s">
         <v>69</v>
@@ -4011,10 +4044,10 @@
         <v>56</v>
       </c>
       <c r="E35">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="F35">
-        <v>2.4E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -4023,13 +4056,13 @@
         <v>2376</v>
       </c>
       <c r="I35" s="3">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J35">
         <v>2.52</v>
       </c>
       <c r="K35">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L35">
         <v>0.40144059976798202</v>
@@ -4067,10 +4100,10 @@
         <v>56</v>
       </c>
       <c r="E36">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="F36">
-        <v>7.9000000000000001E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -4085,10 +4118,10 @@
         <v>2.52</v>
       </c>
       <c r="K36">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L36">
-        <v>0.40144059976798202</v>
+        <v>0.40144059976798208</v>
       </c>
       <c r="O36" t="s">
         <v>69</v>
@@ -4123,28 +4156,28 @@
         <v>56</v>
       </c>
       <c r="E37">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F37">
-        <v>2.1000000000000001E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>2376</v>
+        <v>2024</v>
       </c>
       <c r="I37" s="3">
-        <v>57.2</v>
+        <v>48.4</v>
       </c>
       <c r="J37">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K37">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L37">
-        <v>0.40144059976798208</v>
+        <v>0.40144059976798202</v>
       </c>
       <c r="O37" t="s">
         <v>69</v>
@@ -4170,37 +4203,37 @@
     </row>
     <row r="38" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
         <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E38">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F38">
-        <v>0.10199999999999999</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38">
-        <v>2024</v>
+        <v>2376</v>
       </c>
       <c r="I38" s="3">
-        <v>48.4</v>
+        <v>57.2</v>
       </c>
       <c r="J38">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K38">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L38">
-        <v>0.40144059976798202</v>
+        <v>0.365520596150406</v>
       </c>
       <c r="O38" t="s">
         <v>69</v>
@@ -4226,19 +4259,19 @@
     </row>
     <row r="39" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C39" t="s">
         <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E39">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="F39">
-        <v>3.9E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -4247,16 +4280,16 @@
         <v>2376</v>
       </c>
       <c r="I39" s="3">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J39">
         <v>2.52</v>
       </c>
       <c r="K39">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="L39">
-        <v>0.365520596150406</v>
+        <v>0.41047488326249421</v>
       </c>
       <c r="O39" t="s">
         <v>69</v>
@@ -4291,10 +4324,10 @@
         <v>60</v>
       </c>
       <c r="E40">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="F40">
-        <v>1.7999999999999999E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -4303,13 +4336,13 @@
         <v>2376</v>
       </c>
       <c r="I40" s="3">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J40">
         <v>2.52</v>
       </c>
       <c r="K40">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="L40">
         <v>0.41047488326249421</v>
@@ -4347,7 +4380,7 @@
         <v>60</v>
       </c>
       <c r="E41">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="F41">
         <v>2.1999999999999999E-2</v>
@@ -4365,7 +4398,7 @@
         <v>2.52</v>
       </c>
       <c r="K41">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L41">
         <v>0.41047488326249421</v>
@@ -4394,37 +4427,37 @@
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
         <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E42">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F42">
-        <v>2.1999999999999999E-2</v>
+        <v>0.255</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>2376</v>
+        <v>2024</v>
       </c>
       <c r="I42" s="3">
-        <v>57.2</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="J42">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K42">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="L42">
-        <v>0.41047488326249421</v>
+        <v>0.365520596150406</v>
       </c>
       <c r="O42" t="s">
         <v>69</v>
@@ -4450,37 +4483,10 @@
     </row>
     <row r="43" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" t="s">
-        <v>45</v>
-      </c>
-      <c r="D43" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43">
-        <v>2024</v>
-      </c>
-      <c r="F43">
-        <v>0.255</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <v>2024</v>
-      </c>
-      <c r="I43" s="3">
-        <v>48.400000000000006</v>
-      </c>
-      <c r="J43">
-        <v>2.3100000000000005</v>
-      </c>
-      <c r="K43">
-        <v>31</v>
-      </c>
-      <c r="L43">
-        <v>0.365520596150406</v>
+        <v>140</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="O43" t="s">
         <v>69</v>
@@ -4506,10 +4512,34 @@
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>140</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>141</v>
+        <v>17</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44">
+        <v>1982</v>
+      </c>
+      <c r="F44">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="G44">
+        <v>0.44290000000000002</v>
+      </c>
+      <c r="H44">
+        <v>1265</v>
+      </c>
+      <c r="I44" s="3">
+        <v>36.300000000000004</v>
+      </c>
+      <c r="J44">
+        <v>3.4650000000000007</v>
+      </c>
+      <c r="K44">
+        <v>53</v>
       </c>
       <c r="O44" t="s">
         <v>69</v>
@@ -4535,34 +4565,34 @@
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
       </c>
       <c r="E45">
-        <v>1982</v>
+        <v>1965</v>
       </c>
       <c r="F45">
-        <v>1.6999999999999999E-3</v>
+        <v>0.77</v>
       </c>
       <c r="G45">
-        <v>0.44290000000000002</v>
+        <v>0.49</v>
       </c>
       <c r="H45">
-        <v>1265</v>
+        <v>2150</v>
       </c>
       <c r="I45" s="3">
-        <v>36.300000000000004</v>
+        <v>35.053609999999999</v>
       </c>
       <c r="J45">
-        <v>3.4650000000000007</v>
+        <v>3.28</v>
       </c>
       <c r="K45">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="O45" t="s">
         <v>69</v>
@@ -4588,7 +4618,7 @@
     </row>
     <row r="46" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C46" t="s">
         <v>192</v>
@@ -4597,10 +4627,10 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>1965</v>
+        <v>2015</v>
       </c>
       <c r="F46">
-        <v>0.77</v>
+        <v>0.26</v>
       </c>
       <c r="G46">
         <v>0.49</v>
@@ -4615,7 +4645,7 @@
         <v>3.28</v>
       </c>
       <c r="K46">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="O46" t="s">
         <v>69</v>
@@ -4641,7 +4671,7 @@
     </row>
     <row r="47" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C47" t="s">
         <v>192</v>
@@ -4650,10 +4680,10 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>2015</v>
+        <v>1956</v>
       </c>
       <c r="F47">
-        <v>0.26</v>
+        <v>0.185</v>
       </c>
       <c r="G47">
         <v>0.49</v>
@@ -4668,7 +4698,7 @@
         <v>3.28</v>
       </c>
       <c r="K47">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="O47" t="s">
         <v>69</v>
@@ -4694,34 +4724,34 @@
     </row>
     <row r="48" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>193</v>
+        <v>142</v>
       </c>
       <c r="C48" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
       <c r="D48" t="s">
         <v>14</v>
       </c>
       <c r="E48">
-        <v>1956</v>
+        <v>2021</v>
       </c>
       <c r="F48">
-        <v>0.185</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G48">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="H48">
-        <v>2150</v>
+        <v>360</v>
       </c>
       <c r="I48" s="3">
-        <v>35.053609999999999</v>
+        <v>9.3576800000000002</v>
       </c>
       <c r="J48">
-        <v>3.28</v>
+        <v>6.38</v>
       </c>
       <c r="K48">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="O48" t="s">
         <v>69</v>
@@ -4747,31 +4777,31 @@
     </row>
     <row r="49" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
       </c>
       <c r="E49">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="F49">
-        <v>7.6999999999999999E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G49">
-        <v>0.41</v>
-      </c>
-      <c r="H49">
-        <v>360</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H49" s="2">
+        <v>3200.7518811800001</v>
       </c>
       <c r="I49" s="3">
-        <v>9.3576800000000002</v>
-      </c>
-      <c r="J49">
-        <v>6.38</v>
+        <v>131.85821703200003</v>
+      </c>
+      <c r="J49" s="4">
+        <v>1.9778732554800003</v>
       </c>
       <c r="K49">
         <v>40</v>
@@ -4800,7 +4830,7 @@
     </row>
     <row r="50" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
@@ -4809,10 +4839,10 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="F50">
-        <v>3.9E-2</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="G50">
         <v>0.28999999999999998</v>
@@ -4853,7 +4883,7 @@
     </row>
     <row r="51" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
         <v>13</v>
@@ -4862,10 +4892,10 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="F51">
-        <v>2.2100000000000002E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="G51">
         <v>0.28999999999999998</v>
@@ -4906,7 +4936,7 @@
     </row>
     <row r="52" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
@@ -4915,10 +4945,10 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="F52">
-        <v>2.0500000000000001E-2</v>
+        <v>1.3900000000000001E-2</v>
       </c>
       <c r="G52">
         <v>0.28999999999999998</v>
@@ -4959,31 +4989,31 @@
     </row>
     <row r="53" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>192</v>
       </c>
       <c r="D53" t="s">
         <v>14</v>
       </c>
       <c r="E53">
-        <v>2010</v>
+        <v>1997</v>
       </c>
       <c r="F53">
-        <v>1.3900000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G53">
-        <v>0.28999999999999998</v>
+        <v>0.49</v>
       </c>
       <c r="H53" s="2">
-        <v>3200.7518811800001</v>
+        <v>2150</v>
       </c>
       <c r="I53" s="3">
-        <v>131.85821703200003</v>
+        <v>35.053609999999999</v>
       </c>
       <c r="J53" s="4">
-        <v>1.9778732554800003</v>
+        <v>3.28</v>
       </c>
       <c r="K53">
         <v>40</v>
@@ -5012,31 +5042,31 @@
     </row>
     <row r="54" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="C54" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="D54" t="s">
         <v>14</v>
       </c>
       <c r="E54">
-        <v>1997</v>
+        <v>2016</v>
       </c>
       <c r="F54">
         <v>0.01</v>
       </c>
       <c r="G54">
-        <v>0.49</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H54" s="2">
-        <v>2150</v>
+        <v>3200.7518811800001</v>
       </c>
       <c r="I54" s="3">
-        <v>35.053609999999999</v>
+        <v>131.85821703200003</v>
       </c>
       <c r="J54" s="4">
-        <v>3.28</v>
+        <v>1.9778732554800003</v>
       </c>
       <c r="K54">
         <v>40</v>
@@ -5065,7 +5095,7 @@
     </row>
     <row r="55" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
@@ -5074,7 +5104,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F55">
         <v>0.01</v>
@@ -5118,7 +5148,7 @@
     </row>
     <row r="56" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -5127,10 +5157,10 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F56">
-        <v>0.01</v>
+        <v>9.300000000000001E-3</v>
       </c>
       <c r="G56">
         <v>0.28999999999999998</v>
@@ -5171,7 +5201,7 @@
     </row>
     <row r="57" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
@@ -5180,10 +5210,10 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>2019</v>
+        <v>1963</v>
       </c>
       <c r="F57">
-        <v>9.300000000000001E-3</v>
+        <v>7.0999999999999995E-3</v>
       </c>
       <c r="G57">
         <v>0.28999999999999998</v>
@@ -5198,7 +5228,7 @@
         <v>1.9778732554800003</v>
       </c>
       <c r="K57">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="O57" t="s">
         <v>69</v>
@@ -5224,34 +5254,34 @@
     </row>
     <row r="58" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D58" t="s">
         <v>14</v>
       </c>
       <c r="E58">
-        <v>1963</v>
+        <v>2020</v>
       </c>
       <c r="F58">
-        <v>7.0999999999999995E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="G58">
-        <v>0.28999999999999998</v>
+        <v>0.41</v>
       </c>
       <c r="H58" s="2">
-        <v>3200.7518811800001</v>
+        <v>521.0526318200001</v>
       </c>
       <c r="I58" s="3">
-        <v>131.85821703200003</v>
+        <v>6.9119226670000007</v>
       </c>
       <c r="J58" s="4">
-        <v>1.9778732554800003</v>
+        <v>6.38</v>
       </c>
       <c r="K58">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="O58" t="s">
         <v>69</v>
@@ -5277,31 +5307,31 @@
     </row>
     <row r="59" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
         <v>14</v>
       </c>
       <c r="E59">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="F59">
-        <v>5.7999999999999996E-3</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="G59">
-        <v>0.41</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H59" s="2">
-        <v>521.0526318200001</v>
+        <v>3200.7518811800001</v>
       </c>
       <c r="I59" s="3">
-        <v>6.9119226670000007</v>
+        <v>131.85821703200003</v>
       </c>
       <c r="J59" s="4">
-        <v>6.38</v>
+        <v>1.9778732554800003</v>
       </c>
       <c r="K59">
         <v>40</v>
@@ -5330,31 +5360,31 @@
     </row>
     <row r="60" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D60" t="s">
         <v>14</v>
       </c>
       <c r="E60">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="F60">
-        <v>6.4999999999999997E-3</v>
+        <v>4.0999999999999995E-3</v>
       </c>
       <c r="G60">
-        <v>0.28999999999999998</v>
+        <v>0.41</v>
       </c>
       <c r="H60" s="2">
-        <v>3200.7518811800001</v>
+        <v>521.0526318200001</v>
       </c>
       <c r="I60" s="3">
-        <v>131.85821703200003</v>
+        <v>6.9119226670000007</v>
       </c>
       <c r="J60" s="4">
-        <v>1.9778732554800003</v>
+        <v>6.38</v>
       </c>
       <c r="K60">
         <v>40</v>
@@ -5383,31 +5413,31 @@
     </row>
     <row r="61" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="D61" t="s">
         <v>14</v>
       </c>
       <c r="E61">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="F61">
-        <v>4.0999999999999995E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G61">
-        <v>0.41</v>
+        <v>0.49</v>
       </c>
       <c r="H61" s="2">
-        <v>521.0526318200001</v>
+        <v>2150</v>
       </c>
       <c r="I61" s="3">
-        <v>6.9119226670000007</v>
+        <v>35.053609999999999</v>
       </c>
       <c r="J61" s="4">
-        <v>6.38</v>
+        <v>3.28</v>
       </c>
       <c r="K61">
         <v>40</v>
@@ -5436,31 +5466,31 @@
     </row>
     <row r="62" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="C62" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
       </c>
       <c r="E62">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="F62">
-        <v>1.4E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G62">
-        <v>0.49</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H62" s="2">
-        <v>2150</v>
+        <v>6444.0386710800003</v>
       </c>
       <c r="I62" s="3">
-        <v>35.053609999999999</v>
+        <v>288.17400657800005</v>
       </c>
       <c r="J62" s="4">
-        <v>3.28</v>
+        <v>4.1365198730200001</v>
       </c>
       <c r="K62">
         <v>40</v>
@@ -5489,7 +5519,7 @@
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
@@ -5498,10 +5528,10 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="F63">
-        <v>1.8E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="G63">
         <v>0.28999999999999998</v>
@@ -5521,31 +5551,31 @@
     </row>
     <row r="64" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
       </c>
       <c r="E64">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="F64">
-        <v>1.6999999999999999E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G64">
-        <v>0.28999999999999998</v>
+        <v>0.41</v>
       </c>
       <c r="H64" s="2">
-        <v>6444.0386710800003</v>
+        <v>521.0526318200001</v>
       </c>
       <c r="I64" s="3">
-        <v>288.17400657800005</v>
+        <v>6.9119226670000007</v>
       </c>
       <c r="J64" s="4">
-        <v>4.1365198730200001</v>
+        <v>6.38</v>
       </c>
       <c r="K64">
         <v>40</v>
@@ -5553,7 +5583,7 @@
     </row>
     <row r="65" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C65" t="s">
         <v>16</v>
@@ -5562,7 +5592,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="F65">
         <v>1.8E-3</v>
@@ -5585,31 +5615,31 @@
     </row>
     <row r="66" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
         <v>14</v>
       </c>
       <c r="E66">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F66">
-        <v>1.8E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G66">
-        <v>0.41</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H66" s="2">
-        <v>521.0526318200001</v>
+        <v>1010.2040821000001</v>
       </c>
       <c r="I66" s="3">
-        <v>6.9119226670000007</v>
+        <v>10.3678840005</v>
       </c>
       <c r="J66" s="4">
-        <v>6.38</v>
+        <v>7.9752953850000008</v>
       </c>
       <c r="K66">
         <v>40</v>
@@ -5617,7 +5647,7 @@
     </row>
     <row r="67" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C67" t="s">
         <v>13</v>
@@ -5626,10 +5656,10 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="F67">
-        <v>1.5E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G67">
         <v>0.28999999999999998</v>
@@ -5649,7 +5679,7 @@
     </row>
     <row r="68" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C68" t="s">
         <v>13</v>
@@ -5658,10 +5688,10 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="F68">
-        <v>1.4E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G68">
         <v>0.28999999999999998</v>
@@ -5681,7 +5711,7 @@
     </row>
     <row r="69" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
@@ -5690,22 +5720,22 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="F69">
-        <v>1.1999999999999999E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G69">
         <v>0.28999999999999998</v>
       </c>
       <c r="H69" s="2">
-        <v>1010.2040821000001</v>
+        <v>11048.442540020002</v>
       </c>
       <c r="I69" s="3">
-        <v>10.3678840005</v>
+        <v>437.04618709800002</v>
       </c>
       <c r="J69" s="4">
-        <v>7.9752953850000008</v>
+        <v>27.520085941840001</v>
       </c>
       <c r="K69">
         <v>40</v>
@@ -5713,7 +5743,7 @@
     </row>
     <row r="70" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
@@ -5722,22 +5752,22 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="F70">
-        <v>1.9E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="G70">
         <v>0.28999999999999998</v>
       </c>
       <c r="H70" s="2">
-        <v>11048.442540020002</v>
+        <v>6444.0386710800003</v>
       </c>
       <c r="I70" s="3">
-        <v>437.04618709800002</v>
+        <v>288.17400657800005</v>
       </c>
       <c r="J70" s="4">
-        <v>27.520085941840001</v>
+        <v>4.1365198730200001</v>
       </c>
       <c r="K70">
         <v>40</v>
@@ -5745,7 +5775,7 @@
     </row>
     <row r="71" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C71" t="s">
         <v>13</v>
@@ -5754,22 +5784,22 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="F71">
-        <v>8.9999999999999998E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="G71">
         <v>0.28999999999999998</v>
       </c>
       <c r="H71" s="2">
-        <v>6444.0386710800003</v>
+        <v>11048.442540020002</v>
       </c>
       <c r="I71" s="3">
-        <v>288.17400657800005</v>
+        <v>437.04618709800002</v>
       </c>
       <c r="J71" s="4">
-        <v>4.1365198730200001</v>
+        <v>27.520085941840001</v>
       </c>
       <c r="K71">
         <v>40</v>
@@ -5777,86 +5807,74 @@
     </row>
     <row r="72" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D72" t="s">
         <v>14</v>
       </c>
       <c r="E72">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F72">
-        <v>5.0000000000000001E-4</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G72">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H72" s="2">
-        <v>11048.442540020002</v>
-      </c>
-      <c r="I72" s="3">
-        <v>437.04618709800002</v>
-      </c>
-      <c r="J72" s="4">
-        <v>27.520085941840001</v>
-      </c>
-      <c r="K72">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
-        <v>18</v>
-      </c>
-      <c r="C73" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" t="s">
+        <v>0.33123000000000002</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" t="s">
         <v>14</v>
       </c>
-      <c r="E73">
-        <v>2022</v>
-      </c>
-      <c r="F73">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G73">
-        <v>0.33123000000000002</v>
+      <c r="E76">
+        <v>2013</v>
+      </c>
+      <c r="F76">
+        <v>0.25109999999999999</v>
+      </c>
+      <c r="G76">
+        <v>0.36049999999999999</v>
+      </c>
+      <c r="H76">
+        <v>1265</v>
+      </c>
+      <c r="I76" s="3">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="J76">
+        <v>7.5075000000000003</v>
+      </c>
+      <c r="K76">
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D77" t="s">
         <v>14</v>
       </c>
       <c r="E77">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="F77">
-        <v>0.25109999999999999</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="G77">
-        <v>0.36049999999999999</v>
-      </c>
-      <c r="H77">
-        <v>1265</v>
-      </c>
-      <c r="I77" s="3">
-        <v>48.400000000000006</v>
-      </c>
-      <c r="J77">
-        <v>7.5075000000000003</v>
-      </c>
-      <c r="K77">
-        <v>42</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="O77" t="s">
         <v>69</v>
@@ -5881,24 +5899,6 @@
       </c>
     </row>
     <row r="78" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>15</v>
-      </c>
-      <c r="C78" t="s">
-        <v>16</v>
-      </c>
-      <c r="D78" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78">
-        <v>2022</v>
-      </c>
-      <c r="F78">
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="G78">
-        <v>0.33123000000000002</v>
-      </c>
       <c r="O78" t="s">
         <v>69</v>
       </c>
@@ -5921,37 +5921,39 @@
         <v>74</v>
       </c>
     </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79">
+        <v>2022</v>
+      </c>
+      <c r="F79">
+        <v>0.3</v>
+      </c>
+      <c r="G79">
+        <v>0.33990000000000004</v>
+      </c>
+      <c r="H79">
+        <v>4427.5</v>
+      </c>
+      <c r="I79" s="3">
+        <v>157.30000000000001</v>
+      </c>
+      <c r="J79">
+        <v>9.24</v>
+      </c>
+      <c r="K79">
+        <v>50</v>
+      </c>
+    </row>
     <row r="80" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" t="s">
-        <v>14</v>
-      </c>
-      <c r="E80">
-        <v>2022</v>
-      </c>
-      <c r="F80">
-        <v>0.3</v>
-      </c>
-      <c r="G80">
-        <v>0.33990000000000004</v>
-      </c>
-      <c r="H80">
-        <v>4427.5</v>
-      </c>
-      <c r="I80" s="3">
-        <v>157.30000000000001</v>
-      </c>
-      <c r="J80">
-        <v>9.24</v>
-      </c>
-      <c r="K80">
-        <v>50</v>
-      </c>
       <c r="O80" t="s">
         <v>69</v>
       </c>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F74BA55-79F9-4208-A8DD-5D96FD3C5C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0A5F67-D97C-4A31-9F28-9DE87309EC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -4798,13 +4798,16 @@
         <v>3200.7518811800001</v>
       </c>
       <c r="I49" s="3">
-        <v>131.85821703200003</v>
+        <v>20</v>
       </c>
       <c r="J49" s="4">
         <v>1.9778732554800003</v>
       </c>
       <c r="K49">
         <v>40</v>
+      </c>
+      <c r="M49" s="3">
+        <v>131.85821703200003</v>
       </c>
       <c r="O49" t="s">
         <v>69</v>
@@ -4851,13 +4854,16 @@
         <v>3200.7518811800001</v>
       </c>
       <c r="I50" s="3">
-        <v>131.85821703200003</v>
+        <v>20</v>
       </c>
       <c r="J50" s="4">
         <v>1.9778732554800003</v>
       </c>
       <c r="K50">
         <v>40</v>
+      </c>
+      <c r="M50" s="3">
+        <v>131.85821703200003</v>
       </c>
       <c r="O50" t="s">
         <v>69</v>
@@ -4904,13 +4910,16 @@
         <v>3200.7518811800001</v>
       </c>
       <c r="I51" s="3">
-        <v>131.85821703200003</v>
+        <v>20</v>
       </c>
       <c r="J51" s="4">
         <v>1.9778732554800003</v>
       </c>
       <c r="K51">
         <v>40</v>
+      </c>
+      <c r="M51" s="3">
+        <v>131.85821703200003</v>
       </c>
       <c r="O51" t="s">
         <v>69</v>
@@ -4957,13 +4966,16 @@
         <v>3200.7518811800001</v>
       </c>
       <c r="I52" s="3">
-        <v>131.85821703200003</v>
+        <v>20</v>
       </c>
       <c r="J52" s="4">
         <v>1.9778732554800003</v>
       </c>
       <c r="K52">
         <v>40</v>
+      </c>
+      <c r="M52" s="3">
+        <v>131.85821703200003</v>
       </c>
       <c r="O52" t="s">
         <v>69</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0A5F67-D97C-4A31-9F28-9DE87309EC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A505B9-3D88-425F-AEE8-4CD71FCCC70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="G49" authorId="4" shapeId="0" xr:uid="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
+    <comment ref="M49" authorId="4" shapeId="0" xr:uid="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -127,7 +127,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="O77" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <comment ref="Q77" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1188,14 +1188,14 @@
     <text xml:space="preserve">DAE - gas engines 2020
 </text>
   </threadedComment>
-  <threadedComment ref="G49" dT="2026-01-28T11:17:46.06" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
+  <threadedComment ref="M49" dT="2026-01-28T11:17:46.06" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
     <text>DAE - Wood pellets, Medium 2020</text>
   </threadedComment>
   <threadedComment ref="E52" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
     <text xml:space="preserve">Ei tea
 </text>
   </threadedComment>
-  <threadedComment ref="O77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+  <threadedComment ref="Q77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
   </threadedComment>
   <threadedComment ref="J79" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
@@ -2689,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:U80"/>
+  <dimension ref="B9:W80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
@@ -2708,15 +2708,15 @@
     <col min="17" max="17" width="64.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
+      <c r="Q9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -2750,29 +2750,29 @@
       <c r="L10" t="s">
         <v>11</v>
       </c>
-      <c r="O10" t="s">
+      <c r="Q10" t="s">
         <v>63</v>
       </c>
-      <c r="P10" t="s">
+      <c r="R10" t="s">
         <v>1</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="S10" t="s">
         <v>64</v>
       </c>
-      <c r="R10" t="s">
+      <c r="T10" t="s">
         <v>65</v>
       </c>
-      <c r="S10" t="s">
+      <c r="U10" t="s">
         <v>66</v>
       </c>
-      <c r="T10" t="s">
+      <c r="V10" t="s">
         <v>67</v>
       </c>
-      <c r="U10" t="s">
+      <c r="W10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>22</v>
       </c>
@@ -2794,29 +2794,29 @@
       <c r="L11">
         <v>0.14986856628506873</v>
       </c>
-      <c r="O11" t="s">
-        <v>69</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
+        <v>69</v>
+      </c>
+      <c r="R11" t="s">
         <v>17</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="S11" t="s">
         <v>76</v>
       </c>
-      <c r="R11" t="s">
-        <v>71</v>
-      </c>
-      <c r="S11" t="s">
-        <v>72</v>
-      </c>
       <c r="T11" t="s">
+        <v>71</v>
+      </c>
+      <c r="U11" t="s">
+        <v>72</v>
+      </c>
+      <c r="V11" t="s">
         <v>73</v>
       </c>
-      <c r="U11" t="s">
+      <c r="W11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>25</v>
       </c>
@@ -2838,29 +2838,29 @@
       <c r="L12">
         <v>0.14986856628506873</v>
       </c>
-      <c r="O12" t="s">
-        <v>69</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
+        <v>69</v>
+      </c>
+      <c r="R12" t="s">
         <v>22</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="S12" t="s">
         <v>78</v>
       </c>
-      <c r="R12" t="s">
-        <v>71</v>
-      </c>
-      <c r="S12" t="s">
-        <v>72</v>
-      </c>
       <c r="T12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U12" t="s">
+        <v>72</v>
+      </c>
+      <c r="V12" t="s">
+        <v>80</v>
+      </c>
+      <c r="W12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -2882,29 +2882,29 @@
       <c r="L13">
         <v>0.14986856628506873</v>
       </c>
-      <c r="O13" t="s">
-        <v>69</v>
-      </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
+        <v>69</v>
+      </c>
+      <c r="R13" t="s">
         <v>25</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="S13" t="s">
         <v>78</v>
       </c>
-      <c r="R13" t="s">
-        <v>71</v>
-      </c>
-      <c r="S13" t="s">
-        <v>72</v>
-      </c>
       <c r="T13" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U13" t="s">
+        <v>72</v>
+      </c>
+      <c r="V13" t="s">
+        <v>80</v>
+      </c>
+      <c r="W13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>29</v>
       </c>
@@ -2938,29 +2938,29 @@
       <c r="L14">
         <v>0.1461854238754417</v>
       </c>
-      <c r="O14" t="s">
-        <v>69</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
+        <v>69</v>
+      </c>
+      <c r="R14" t="s">
         <v>27</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="S14" t="s">
         <v>78</v>
       </c>
-      <c r="R14" t="s">
-        <v>71</v>
-      </c>
-      <c r="S14" t="s">
-        <v>72</v>
-      </c>
       <c r="T14" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U14" t="s">
+        <v>72</v>
+      </c>
+      <c r="V14" t="s">
+        <v>80</v>
+      </c>
+      <c r="W14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -2994,29 +2994,29 @@
       <c r="L15">
         <v>0.1461854238754417</v>
       </c>
-      <c r="O15" t="s">
-        <v>69</v>
-      </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
+        <v>69</v>
+      </c>
+      <c r="R15" t="s">
         <v>29</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="S15" t="s">
         <v>78</v>
       </c>
-      <c r="R15" t="s">
-        <v>71</v>
-      </c>
-      <c r="S15" t="s">
-        <v>72</v>
-      </c>
       <c r="T15" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V15" t="s">
+        <v>80</v>
+      </c>
+      <c r="W15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>30</v>
       </c>
@@ -3050,29 +3050,29 @@
       <c r="L16">
         <v>0.14867925344692126</v>
       </c>
-      <c r="O16" t="s">
-        <v>69</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
+        <v>69</v>
+      </c>
+      <c r="R16" t="s">
         <v>30</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="S16" t="s">
         <v>78</v>
       </c>
-      <c r="R16" t="s">
-        <v>71</v>
-      </c>
-      <c r="S16" t="s">
-        <v>72</v>
-      </c>
       <c r="T16" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U16" t="s">
+        <v>72</v>
+      </c>
+      <c r="V16" t="s">
+        <v>80</v>
+      </c>
+      <c r="W16" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>32</v>
       </c>
@@ -3106,29 +3106,29 @@
       <c r="L17">
         <v>0.14701259708091721</v>
       </c>
-      <c r="O17" t="s">
-        <v>69</v>
-      </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
+        <v>69</v>
+      </c>
+      <c r="R17" t="s">
         <v>32</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="S17" t="s">
         <v>78</v>
       </c>
-      <c r="R17" t="s">
-        <v>71</v>
-      </c>
-      <c r="S17" t="s">
-        <v>72</v>
-      </c>
       <c r="T17" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U17" t="s">
+        <v>72</v>
+      </c>
+      <c r="V17" t="s">
+        <v>80</v>
+      </c>
+      <c r="W17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>34</v>
       </c>
@@ -3162,29 +3162,29 @@
       <c r="L18">
         <v>0.15309859852159369</v>
       </c>
-      <c r="O18" t="s">
-        <v>69</v>
-      </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
+        <v>69</v>
+      </c>
+      <c r="R18" t="s">
         <v>34</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="S18" t="s">
         <v>78</v>
       </c>
-      <c r="R18" t="s">
-        <v>71</v>
-      </c>
-      <c r="S18" t="s">
-        <v>72</v>
-      </c>
       <c r="T18" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U18" t="s">
+        <v>72</v>
+      </c>
+      <c r="V18" t="s">
+        <v>80</v>
+      </c>
+      <c r="W18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3218,29 +3218,29 @@
       <c r="L19">
         <v>0.15309859852159369</v>
       </c>
-      <c r="O19" t="s">
-        <v>69</v>
-      </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
+        <v>69</v>
+      </c>
+      <c r="R19" t="s">
         <v>35</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="S19" t="s">
         <v>78</v>
       </c>
-      <c r="R19" t="s">
-        <v>71</v>
-      </c>
-      <c r="S19" t="s">
-        <v>72</v>
-      </c>
       <c r="T19" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U19" t="s">
+        <v>72</v>
+      </c>
+      <c r="V19" t="s">
+        <v>80</v>
+      </c>
+      <c r="W19" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>35</v>
       </c>
@@ -3274,29 +3274,29 @@
       <c r="L20">
         <v>0.15619560585976827</v>
       </c>
-      <c r="O20" t="s">
-        <v>69</v>
-      </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
+        <v>69</v>
+      </c>
+      <c r="R20" t="s">
         <v>37</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="S20" t="s">
         <v>78</v>
       </c>
-      <c r="R20" t="s">
-        <v>71</v>
-      </c>
-      <c r="S20" t="s">
-        <v>72</v>
-      </c>
       <c r="T20" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U20" t="s">
+        <v>72</v>
+      </c>
+      <c r="V20" t="s">
+        <v>80</v>
+      </c>
+      <c r="W20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>37</v>
       </c>
@@ -3330,29 +3330,29 @@
       <c r="L21">
         <v>0.14537310453496291</v>
       </c>
-      <c r="O21" t="s">
-        <v>69</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
+        <v>69</v>
+      </c>
+      <c r="R21" t="s">
         <v>39</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="S21" t="s">
         <v>78</v>
       </c>
-      <c r="R21" t="s">
-        <v>71</v>
-      </c>
-      <c r="S21" t="s">
-        <v>72</v>
-      </c>
       <c r="T21" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U21" t="s">
+        <v>72</v>
+      </c>
+      <c r="V21" t="s">
+        <v>80</v>
+      </c>
+      <c r="W21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>39</v>
       </c>
@@ -3386,29 +3386,29 @@
       <c r="L22">
         <v>0.14763873655681015</v>
       </c>
-      <c r="O22" t="s">
-        <v>69</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
+        <v>69</v>
+      </c>
+      <c r="R22" t="s">
         <v>40</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="S22" t="s">
         <v>78</v>
       </c>
-      <c r="R22" t="s">
-        <v>71</v>
-      </c>
-      <c r="S22" t="s">
-        <v>72</v>
-      </c>
       <c r="T22" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U22" t="s">
+        <v>72</v>
+      </c>
+      <c r="V22" t="s">
+        <v>80</v>
+      </c>
+      <c r="W22" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>40</v>
       </c>
@@ -3442,29 +3442,29 @@
       <c r="L23">
         <v>0.1532628310027955</v>
       </c>
-      <c r="O23" t="s">
-        <v>69</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
+        <v>69</v>
+      </c>
+      <c r="R23" t="s">
         <v>42</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="S23" t="s">
         <v>78</v>
       </c>
-      <c r="R23" t="s">
-        <v>71</v>
-      </c>
-      <c r="S23" t="s">
-        <v>72</v>
-      </c>
       <c r="T23" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U23" t="s">
+        <v>72</v>
+      </c>
+      <c r="V23" t="s">
+        <v>80</v>
+      </c>
+      <c r="W23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>40</v>
       </c>
@@ -3498,29 +3498,29 @@
       <c r="L24">
         <v>0.1532628310027955</v>
       </c>
-      <c r="O24" t="s">
-        <v>69</v>
-      </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
+        <v>69</v>
+      </c>
+      <c r="R24" t="s">
         <v>44</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="S24" t="s">
         <v>78</v>
       </c>
-      <c r="R24" t="s">
-        <v>71</v>
-      </c>
-      <c r="S24" t="s">
-        <v>72</v>
-      </c>
       <c r="T24" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U24" t="s">
+        <v>72</v>
+      </c>
+      <c r="V24" t="s">
+        <v>80</v>
+      </c>
+      <c r="W24" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>42</v>
       </c>
@@ -3554,29 +3554,29 @@
       <c r="L25">
         <v>0.1451997589052581</v>
       </c>
-      <c r="O25" t="s">
-        <v>69</v>
-      </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
+        <v>69</v>
+      </c>
+      <c r="R25" t="s">
         <v>47</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="S25" t="s">
         <v>78</v>
       </c>
-      <c r="R25" t="s">
-        <v>71</v>
-      </c>
-      <c r="S25" t="s">
-        <v>72</v>
-      </c>
       <c r="T25" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U25" t="s">
+        <v>72</v>
+      </c>
+      <c r="V25" t="s">
+        <v>80</v>
+      </c>
+      <c r="W25" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>44</v>
       </c>
@@ -3598,29 +3598,29 @@
       <c r="L26">
         <v>0.42012333946150526</v>
       </c>
-      <c r="O26" t="s">
-        <v>69</v>
-      </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
+        <v>69</v>
+      </c>
+      <c r="R26" t="s">
         <v>49</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="S26" t="s">
         <v>78</v>
       </c>
-      <c r="R26" t="s">
-        <v>71</v>
-      </c>
-      <c r="S26" t="s">
-        <v>72</v>
-      </c>
       <c r="T26" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U26" t="s">
+        <v>72</v>
+      </c>
+      <c r="V26" t="s">
+        <v>80</v>
+      </c>
+      <c r="W26" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>47</v>
       </c>
@@ -3646,29 +3646,29 @@
         <f>F26*L26*G26</f>
         <v>2.0930123559331545E-3</v>
       </c>
-      <c r="O27" t="s">
-        <v>69</v>
-      </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
+        <v>69</v>
+      </c>
+      <c r="R27" t="s">
         <v>51</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="S27" t="s">
         <v>78</v>
       </c>
-      <c r="R27" t="s">
-        <v>71</v>
-      </c>
-      <c r="S27" t="s">
-        <v>72</v>
-      </c>
       <c r="T27" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U27" t="s">
+        <v>72</v>
+      </c>
+      <c r="V27" t="s">
+        <v>80</v>
+      </c>
+      <c r="W27" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>49</v>
       </c>
@@ -3690,29 +3690,29 @@
       <c r="L28">
         <v>0.42012333946150526</v>
       </c>
-      <c r="O28" t="s">
-        <v>69</v>
-      </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
+        <v>69</v>
+      </c>
+      <c r="R28" t="s">
         <v>53</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="S28" t="s">
         <v>78</v>
       </c>
-      <c r="R28" t="s">
-        <v>71</v>
-      </c>
-      <c r="S28" t="s">
-        <v>72</v>
-      </c>
       <c r="T28" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U28" t="s">
+        <v>72</v>
+      </c>
+      <c r="V28" t="s">
+        <v>80</v>
+      </c>
+      <c r="W28" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>51</v>
       </c>
@@ -3746,29 +3746,29 @@
       <c r="L29">
         <v>0.47763777043344691</v>
       </c>
-      <c r="O29" t="s">
-        <v>69</v>
-      </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
+        <v>69</v>
+      </c>
+      <c r="R29" t="s">
         <v>55</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="S29" t="s">
         <v>78</v>
       </c>
-      <c r="R29" t="s">
-        <v>71</v>
-      </c>
-      <c r="S29" t="s">
-        <v>72</v>
-      </c>
       <c r="T29" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U29" t="s">
+        <v>72</v>
+      </c>
+      <c r="V29" t="s">
+        <v>80</v>
+      </c>
+      <c r="W29" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>53</v>
       </c>
@@ -3802,29 +3802,29 @@
       <c r="L30">
         <v>0.47814004703314078</v>
       </c>
-      <c r="O30" t="s">
-        <v>69</v>
-      </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
+        <v>69</v>
+      </c>
+      <c r="R30" t="s">
         <v>57</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="S30" t="s">
         <v>78</v>
       </c>
-      <c r="R30" t="s">
-        <v>71</v>
-      </c>
-      <c r="S30" t="s">
-        <v>72</v>
-      </c>
       <c r="T30" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U30" t="s">
+        <v>72</v>
+      </c>
+      <c r="V30" t="s">
+        <v>80</v>
+      </c>
+      <c r="W30" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>53</v>
       </c>
@@ -3858,29 +3858,29 @@
       <c r="L31">
         <v>0.47814004703314084</v>
       </c>
-      <c r="O31" t="s">
-        <v>69</v>
-      </c>
-      <c r="P31" t="s">
+      <c r="Q31" t="s">
+        <v>69</v>
+      </c>
+      <c r="R31" t="s">
         <v>59</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="S31" t="s">
         <v>78</v>
       </c>
-      <c r="R31" t="s">
-        <v>71</v>
-      </c>
-      <c r="S31" t="s">
-        <v>72</v>
-      </c>
       <c r="T31" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U31" t="s">
+        <v>72</v>
+      </c>
+      <c r="V31" t="s">
+        <v>80</v>
+      </c>
+      <c r="W31" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>53</v>
       </c>
@@ -3914,29 +3914,29 @@
       <c r="L32">
         <v>0.47814004703314078</v>
       </c>
-      <c r="O32" t="s">
-        <v>69</v>
-      </c>
-      <c r="P32" t="s">
+      <c r="Q32" t="s">
+        <v>69</v>
+      </c>
+      <c r="R32" t="s">
         <v>61</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="S32" t="s">
         <v>81</v>
       </c>
-      <c r="R32" t="s">
-        <v>71</v>
-      </c>
-      <c r="S32" t="s">
-        <v>72</v>
-      </c>
       <c r="T32" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U32" t="s">
+        <v>72</v>
+      </c>
+      <c r="V32" t="s">
+        <v>80</v>
+      </c>
+      <c r="W32" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>55</v>
       </c>
@@ -3970,14 +3970,14 @@
       <c r="L33">
         <v>0.40144059976798208</v>
       </c>
-      <c r="O33" t="s">
+      <c r="Q33" t="s">
         <v>140</v>
       </c>
-      <c r="P33" s="1" t="s">
+      <c r="R33" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>55</v>
       </c>
@@ -4011,29 +4011,29 @@
       <c r="L34">
         <v>0.40144059976798202</v>
       </c>
-      <c r="O34" t="s">
-        <v>69</v>
-      </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
+        <v>69</v>
+      </c>
+      <c r="R34" t="s">
         <v>194</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="S34" t="s">
         <v>163</v>
       </c>
-      <c r="R34" t="s">
-        <v>71</v>
-      </c>
-      <c r="S34" t="s">
-        <v>72</v>
-      </c>
       <c r="T34" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U34" t="s">
+        <v>72</v>
+      </c>
+      <c r="V34" t="s">
+        <v>80</v>
+      </c>
+      <c r="W34" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>55</v>
       </c>
@@ -4067,29 +4067,29 @@
       <c r="L35">
         <v>0.40144059976798202</v>
       </c>
-      <c r="O35" t="s">
-        <v>69</v>
-      </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
+        <v>69</v>
+      </c>
+      <c r="R35" t="s">
         <v>193</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="S35" t="s">
         <v>148</v>
       </c>
-      <c r="R35" t="s">
-        <v>71</v>
-      </c>
-      <c r="S35" t="s">
-        <v>72</v>
-      </c>
       <c r="T35" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U35" t="s">
+        <v>72</v>
+      </c>
+      <c r="V35" t="s">
+        <v>80</v>
+      </c>
+      <c r="W35" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>55</v>
       </c>
@@ -4123,29 +4123,29 @@
       <c r="L36">
         <v>0.40144059976798208</v>
       </c>
-      <c r="O36" t="s">
-        <v>69</v>
-      </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
+        <v>69</v>
+      </c>
+      <c r="R36" t="s">
         <v>195</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="S36" t="s">
         <v>149</v>
       </c>
-      <c r="R36" t="s">
-        <v>71</v>
-      </c>
-      <c r="S36" t="s">
-        <v>72</v>
-      </c>
       <c r="T36" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U36" t="s">
+        <v>72</v>
+      </c>
+      <c r="V36" t="s">
+        <v>80</v>
+      </c>
+      <c r="W36" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>55</v>
       </c>
@@ -4179,29 +4179,29 @@
       <c r="L37">
         <v>0.40144059976798202</v>
       </c>
-      <c r="O37" t="s">
-        <v>69</v>
-      </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
+        <v>69</v>
+      </c>
+      <c r="R37" t="s">
         <v>196</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="S37" t="s">
         <v>150</v>
       </c>
-      <c r="R37" t="s">
-        <v>71</v>
-      </c>
-      <c r="S37" t="s">
-        <v>72</v>
-      </c>
       <c r="T37" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U37" t="s">
+        <v>72</v>
+      </c>
+      <c r="V37" t="s">
+        <v>80</v>
+      </c>
+      <c r="W37" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>57</v>
       </c>
@@ -4235,29 +4235,29 @@
       <c r="L38">
         <v>0.365520596150406</v>
       </c>
-      <c r="O38" t="s">
-        <v>69</v>
-      </c>
-      <c r="P38" t="s">
+      <c r="Q38" t="s">
+        <v>69</v>
+      </c>
+      <c r="R38" t="s">
         <v>142</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="S38" t="s">
         <v>161</v>
       </c>
-      <c r="R38" t="s">
-        <v>71</v>
-      </c>
-      <c r="S38" t="s">
-        <v>72</v>
-      </c>
       <c r="T38" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U38" t="s">
+        <v>72</v>
+      </c>
+      <c r="V38" t="s">
+        <v>80</v>
+      </c>
+      <c r="W38" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>59</v>
       </c>
@@ -4291,29 +4291,29 @@
       <c r="L39">
         <v>0.41047488326249421</v>
       </c>
-      <c r="O39" t="s">
-        <v>69</v>
-      </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
+        <v>69</v>
+      </c>
+      <c r="R39" t="s">
         <v>143</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="S39" t="s">
         <v>151</v>
       </c>
-      <c r="R39" t="s">
-        <v>71</v>
-      </c>
-      <c r="S39" t="s">
-        <v>72</v>
-      </c>
       <c r="T39" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U39" t="s">
+        <v>72</v>
+      </c>
+      <c r="V39" t="s">
+        <v>80</v>
+      </c>
+      <c r="W39" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>59</v>
       </c>
@@ -4347,29 +4347,29 @@
       <c r="L40">
         <v>0.41047488326249421</v>
       </c>
-      <c r="O40" t="s">
-        <v>69</v>
-      </c>
-      <c r="P40" t="s">
+      <c r="Q40" t="s">
+        <v>69</v>
+      </c>
+      <c r="R40" t="s">
         <v>144</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="S40" t="s">
         <v>152</v>
       </c>
-      <c r="R40" t="s">
-        <v>71</v>
-      </c>
-      <c r="S40" t="s">
-        <v>72</v>
-      </c>
       <c r="T40" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U40" t="s">
+        <v>72</v>
+      </c>
+      <c r="V40" t="s">
+        <v>80</v>
+      </c>
+      <c r="W40" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>59</v>
       </c>
@@ -4403,29 +4403,29 @@
       <c r="L41">
         <v>0.41047488326249421</v>
       </c>
-      <c r="O41" t="s">
-        <v>69</v>
-      </c>
-      <c r="P41" t="s">
+      <c r="Q41" t="s">
+        <v>69</v>
+      </c>
+      <c r="R41" t="s">
         <v>145</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="S41" t="s">
         <v>153</v>
       </c>
-      <c r="R41" t="s">
-        <v>71</v>
-      </c>
-      <c r="S41" t="s">
-        <v>72</v>
-      </c>
       <c r="T41" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U41" t="s">
+        <v>72</v>
+      </c>
+      <c r="V41" t="s">
+        <v>80</v>
+      </c>
+      <c r="W41" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>61</v>
       </c>
@@ -4459,58 +4459,58 @@
       <c r="L42">
         <v>0.365520596150406</v>
       </c>
-      <c r="O42" t="s">
-        <v>69</v>
-      </c>
-      <c r="P42" t="s">
+      <c r="Q42" t="s">
+        <v>69</v>
+      </c>
+      <c r="R42" t="s">
         <v>146</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="S42" t="s">
         <v>147</v>
       </c>
-      <c r="R42" t="s">
-        <v>71</v>
-      </c>
-      <c r="S42" t="s">
-        <v>72</v>
-      </c>
       <c r="T42" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U42" t="s">
+        <v>72</v>
+      </c>
+      <c r="V42" t="s">
+        <v>80</v>
+      </c>
+      <c r="W42" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>140</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="O43" t="s">
-        <v>69</v>
-      </c>
-      <c r="P43" t="s">
+      <c r="Q43" t="s">
+        <v>69</v>
+      </c>
+      <c r="R43" t="s">
         <v>197</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="S43" t="s">
         <v>162</v>
       </c>
-      <c r="R43" t="s">
-        <v>71</v>
-      </c>
-      <c r="S43" t="s">
-        <v>72</v>
-      </c>
       <c r="T43" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U43" t="s">
+        <v>72</v>
+      </c>
+      <c r="V43" t="s">
+        <v>80</v>
+      </c>
+      <c r="W43" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>17</v>
       </c>
@@ -4541,29 +4541,29 @@
       <c r="K44">
         <v>53</v>
       </c>
-      <c r="O44" t="s">
-        <v>69</v>
-      </c>
-      <c r="P44" t="s">
+      <c r="Q44" t="s">
+        <v>69</v>
+      </c>
+      <c r="R44" t="s">
         <v>154</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="S44" t="s">
         <v>155</v>
       </c>
-      <c r="R44" t="s">
-        <v>71</v>
-      </c>
-      <c r="S44" t="s">
-        <v>72</v>
-      </c>
       <c r="T44" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U44" t="s">
+        <v>72</v>
+      </c>
+      <c r="V44" t="s">
+        <v>80</v>
+      </c>
+      <c r="W44" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>196</v>
       </c>
@@ -4594,29 +4594,29 @@
       <c r="K45">
         <v>70</v>
       </c>
-      <c r="O45" t="s">
-        <v>69</v>
-      </c>
-      <c r="P45" t="s">
+      <c r="Q45" t="s">
+        <v>69</v>
+      </c>
+      <c r="R45" t="s">
         <v>156</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="S45" t="s">
         <v>157</v>
       </c>
-      <c r="R45" t="s">
-        <v>71</v>
-      </c>
-      <c r="S45" t="s">
-        <v>72</v>
-      </c>
       <c r="T45" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U45" t="s">
+        <v>72</v>
+      </c>
+      <c r="V45" t="s">
+        <v>80</v>
+      </c>
+      <c r="W45" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>194</v>
       </c>
@@ -4647,29 +4647,29 @@
       <c r="K46">
         <v>40</v>
       </c>
-      <c r="O46" t="s">
-        <v>69</v>
-      </c>
-      <c r="P46" t="s">
+      <c r="Q46" t="s">
+        <v>69</v>
+      </c>
+      <c r="R46" t="s">
         <v>170</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="S46" t="s">
         <v>171</v>
       </c>
-      <c r="R46" t="s">
-        <v>71</v>
-      </c>
-      <c r="S46" t="s">
-        <v>72</v>
-      </c>
       <c r="T46" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U46" t="s">
+        <v>72</v>
+      </c>
+      <c r="V46" t="s">
+        <v>80</v>
+      </c>
+      <c r="W46" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>193</v>
       </c>
@@ -4700,29 +4700,29 @@
       <c r="K47">
         <v>79</v>
       </c>
-      <c r="O47" t="s">
-        <v>69</v>
-      </c>
-      <c r="P47" t="s">
+      <c r="Q47" t="s">
+        <v>69</v>
+      </c>
+      <c r="R47" t="s">
         <v>158</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="S47" t="s">
         <v>159</v>
       </c>
-      <c r="R47" t="s">
-        <v>71</v>
-      </c>
-      <c r="S47" t="s">
-        <v>72</v>
-      </c>
       <c r="T47" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U47" t="s">
+        <v>72</v>
+      </c>
+      <c r="V47" t="s">
+        <v>80</v>
+      </c>
+      <c r="W47" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>142</v>
       </c>
@@ -4753,29 +4753,29 @@
       <c r="K48">
         <v>40</v>
       </c>
-      <c r="O48" t="s">
-        <v>69</v>
-      </c>
-      <c r="P48" t="s">
+      <c r="Q48" t="s">
+        <v>69</v>
+      </c>
+      <c r="R48" t="s">
         <v>169</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="S48" t="s">
         <v>160</v>
       </c>
-      <c r="R48" t="s">
-        <v>71</v>
-      </c>
-      <c r="S48" t="s">
-        <v>72</v>
-      </c>
       <c r="T48" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U48" t="s">
+        <v>72</v>
+      </c>
+      <c r="V48" t="s">
+        <v>80</v>
+      </c>
+      <c r="W48" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>143</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="G49">
-        <v>0.28999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="H49" s="2">
         <v>3200.7518811800001</v>
@@ -4800,38 +4800,44 @@
       <c r="I49" s="3">
         <v>20</v>
       </c>
-      <c r="J49" s="4">
-        <v>1.9778732554800003</v>
+      <c r="J49">
+        <v>0.01</v>
       </c>
       <c r="K49">
         <v>40</v>
       </c>
-      <c r="M49" s="3">
+      <c r="M49">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N49" s="3">
         <v>131.85821703200003</v>
       </c>
-      <c r="O49" t="s">
-        <v>69</v>
-      </c>
-      <c r="P49" t="s">
+      <c r="O49" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>69</v>
+      </c>
+      <c r="R49" t="s">
         <v>164</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="S49" t="s">
         <v>165</v>
       </c>
-      <c r="R49" t="s">
-        <v>71</v>
-      </c>
-      <c r="S49" t="s">
-        <v>72</v>
-      </c>
       <c r="T49" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V49" t="s">
+        <v>80</v>
+      </c>
+      <c r="W49" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>144</v>
       </c>
@@ -4848,7 +4854,7 @@
         <v>2.2100000000000002E-2</v>
       </c>
       <c r="G50">
-        <v>0.28999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="H50" s="2">
         <v>3200.7518811800001</v>
@@ -4856,38 +4862,44 @@
       <c r="I50" s="3">
         <v>20</v>
       </c>
-      <c r="J50" s="4">
-        <v>1.9778732554800003</v>
+      <c r="J50">
+        <v>0.01</v>
       </c>
       <c r="K50">
         <v>40</v>
       </c>
-      <c r="M50" s="3">
+      <c r="M50">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N50" s="3">
         <v>131.85821703200003</v>
       </c>
-      <c r="O50" t="s">
-        <v>69</v>
-      </c>
-      <c r="P50" t="s">
+      <c r="O50" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>69</v>
+      </c>
+      <c r="R50" t="s">
         <v>168</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="S50" t="s">
         <v>166</v>
       </c>
-      <c r="R50" t="s">
-        <v>71</v>
-      </c>
-      <c r="S50" t="s">
-        <v>72</v>
-      </c>
       <c r="T50" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U50" t="s">
+        <v>72</v>
+      </c>
+      <c r="V50" t="s">
+        <v>80</v>
+      </c>
+      <c r="W50" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>145</v>
       </c>
@@ -4904,7 +4916,7 @@
         <v>2.0500000000000001E-2</v>
       </c>
       <c r="G51">
-        <v>0.28999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="H51" s="2">
         <v>3200.7518811800001</v>
@@ -4912,38 +4924,44 @@
       <c r="I51" s="3">
         <v>20</v>
       </c>
-      <c r="J51" s="4">
-        <v>1.9778732554800003</v>
+      <c r="J51">
+        <v>0.01</v>
       </c>
       <c r="K51">
         <v>40</v>
       </c>
-      <c r="M51" s="3">
+      <c r="M51">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N51" s="3">
         <v>131.85821703200003</v>
       </c>
-      <c r="O51" t="s">
-        <v>69</v>
-      </c>
-      <c r="P51" t="s">
+      <c r="O51" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>69</v>
+      </c>
+      <c r="R51" t="s">
         <v>198</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="S51" t="s">
         <v>167</v>
       </c>
-      <c r="R51" t="s">
-        <v>71</v>
-      </c>
-      <c r="S51" t="s">
-        <v>72</v>
-      </c>
       <c r="T51" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U51" t="s">
+        <v>72</v>
+      </c>
+      <c r="V51" t="s">
+        <v>80</v>
+      </c>
+      <c r="W51" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>146</v>
       </c>
@@ -4960,7 +4978,7 @@
         <v>1.3900000000000001E-2</v>
       </c>
       <c r="G52">
-        <v>0.28999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="H52" s="2">
         <v>3200.7518811800001</v>
@@ -4968,38 +4986,44 @@
       <c r="I52" s="3">
         <v>20</v>
       </c>
-      <c r="J52" s="4">
-        <v>1.9778732554800003</v>
+      <c r="J52">
+        <v>0.01</v>
       </c>
       <c r="K52">
         <v>40</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="N52" s="3">
         <v>131.85821703200003</v>
       </c>
-      <c r="O52" t="s">
-        <v>69</v>
-      </c>
-      <c r="P52" t="s">
+      <c r="O52" s="4">
+        <v>1.9778732554800003</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>69</v>
+      </c>
+      <c r="R52" t="s">
         <v>172</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="S52" t="s">
         <v>173</v>
       </c>
-      <c r="R52" t="s">
-        <v>71</v>
-      </c>
-      <c r="S52" t="s">
-        <v>72</v>
-      </c>
       <c r="T52" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U52" t="s">
+        <v>72</v>
+      </c>
+      <c r="V52" t="s">
+        <v>80</v>
+      </c>
+      <c r="W52" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>197</v>
       </c>
@@ -5030,29 +5054,29 @@
       <c r="K53">
         <v>40</v>
       </c>
-      <c r="O53" t="s">
-        <v>69</v>
-      </c>
-      <c r="P53" t="s">
+      <c r="Q53" t="s">
+        <v>69</v>
+      </c>
+      <c r="R53" t="s">
         <v>174</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="S53" t="s">
         <v>175</v>
       </c>
-      <c r="R53" t="s">
-        <v>71</v>
-      </c>
-      <c r="S53" t="s">
-        <v>72</v>
-      </c>
       <c r="T53" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U53" t="s">
+        <v>72</v>
+      </c>
+      <c r="V53" t="s">
+        <v>80</v>
+      </c>
+      <c r="W53" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>154</v>
       </c>
@@ -5083,29 +5107,29 @@
       <c r="K54">
         <v>40</v>
       </c>
-      <c r="O54" t="s">
-        <v>69</v>
-      </c>
-      <c r="P54" t="s">
+      <c r="Q54" t="s">
+        <v>69</v>
+      </c>
+      <c r="R54" t="s">
         <v>176</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="S54" t="s">
         <v>177</v>
       </c>
-      <c r="R54" t="s">
-        <v>71</v>
-      </c>
-      <c r="S54" t="s">
-        <v>72</v>
-      </c>
       <c r="T54" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U54" t="s">
+        <v>72</v>
+      </c>
+      <c r="V54" t="s">
+        <v>80</v>
+      </c>
+      <c r="W54" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>156</v>
       </c>
@@ -5136,29 +5160,29 @@
       <c r="K55">
         <v>40</v>
       </c>
-      <c r="O55" t="s">
-        <v>69</v>
-      </c>
-      <c r="P55" t="s">
+      <c r="Q55" t="s">
+        <v>69</v>
+      </c>
+      <c r="R55" t="s">
         <v>178</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="S55" t="s">
         <v>179</v>
       </c>
-      <c r="R55" t="s">
-        <v>71</v>
-      </c>
-      <c r="S55" t="s">
-        <v>72</v>
-      </c>
       <c r="T55" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U55" t="s">
+        <v>72</v>
+      </c>
+      <c r="V55" t="s">
+        <v>80</v>
+      </c>
+      <c r="W55" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>170</v>
       </c>
@@ -5189,29 +5213,29 @@
       <c r="K56">
         <v>40</v>
       </c>
-      <c r="O56" t="s">
-        <v>69</v>
-      </c>
-      <c r="P56" t="s">
+      <c r="Q56" t="s">
+        <v>69</v>
+      </c>
+      <c r="R56" t="s">
         <v>180</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="S56" t="s">
         <v>181</v>
       </c>
-      <c r="R56" t="s">
-        <v>71</v>
-      </c>
-      <c r="S56" t="s">
-        <v>72</v>
-      </c>
       <c r="T56" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U56" t="s">
+        <v>72</v>
+      </c>
+      <c r="V56" t="s">
+        <v>80</v>
+      </c>
+      <c r="W56" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>158</v>
       </c>
@@ -5242,29 +5266,29 @@
       <c r="K57">
         <v>72</v>
       </c>
-      <c r="O57" t="s">
-        <v>69</v>
-      </c>
-      <c r="P57" t="s">
+      <c r="Q57" t="s">
+        <v>69</v>
+      </c>
+      <c r="R57" t="s">
         <v>182</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="S57" t="s">
         <v>183</v>
       </c>
-      <c r="R57" t="s">
-        <v>71</v>
-      </c>
-      <c r="S57" t="s">
-        <v>72</v>
-      </c>
       <c r="T57" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U57" t="s">
+        <v>72</v>
+      </c>
+      <c r="V57" t="s">
+        <v>80</v>
+      </c>
+      <c r="W57" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="58" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>169</v>
       </c>
@@ -5295,29 +5319,29 @@
       <c r="K58">
         <v>40</v>
       </c>
-      <c r="O58" t="s">
-        <v>69</v>
-      </c>
-      <c r="P58" t="s">
+      <c r="Q58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R58" t="s">
         <v>184</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="S58" t="s">
         <v>185</v>
       </c>
-      <c r="R58" t="s">
-        <v>71</v>
-      </c>
-      <c r="S58" t="s">
-        <v>72</v>
-      </c>
       <c r="T58" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U58" t="s">
+        <v>72</v>
+      </c>
+      <c r="V58" t="s">
+        <v>80</v>
+      </c>
+      <c r="W58" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>164</v>
       </c>
@@ -5348,29 +5372,29 @@
       <c r="K59">
         <v>40</v>
       </c>
-      <c r="O59" t="s">
-        <v>69</v>
-      </c>
-      <c r="P59" t="s">
+      <c r="Q59" t="s">
+        <v>69</v>
+      </c>
+      <c r="R59" t="s">
         <v>186</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="S59" t="s">
         <v>188</v>
       </c>
-      <c r="R59" t="s">
-        <v>71</v>
-      </c>
-      <c r="S59" t="s">
-        <v>72</v>
-      </c>
       <c r="T59" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U59" t="s">
+        <v>72</v>
+      </c>
+      <c r="V59" t="s">
+        <v>80</v>
+      </c>
+      <c r="W59" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>168</v>
       </c>
@@ -5401,29 +5425,29 @@
       <c r="K60">
         <v>40</v>
       </c>
-      <c r="O60" t="s">
-        <v>69</v>
-      </c>
-      <c r="P60" t="s">
+      <c r="Q60" t="s">
+        <v>69</v>
+      </c>
+      <c r="R60" t="s">
         <v>187</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="S60" t="s">
         <v>189</v>
       </c>
-      <c r="R60" t="s">
-        <v>71</v>
-      </c>
-      <c r="S60" t="s">
-        <v>72</v>
-      </c>
       <c r="T60" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U60" t="s">
+        <v>72</v>
+      </c>
+      <c r="V60" t="s">
+        <v>80</v>
+      </c>
+      <c r="W60" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>198</v>
       </c>
@@ -5454,29 +5478,29 @@
       <c r="K61">
         <v>40</v>
       </c>
-      <c r="O61" t="s">
-        <v>69</v>
-      </c>
-      <c r="P61" t="s">
+      <c r="Q61" t="s">
+        <v>69</v>
+      </c>
+      <c r="R61" t="s">
         <v>190</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="S61" t="s">
         <v>191</v>
       </c>
-      <c r="R61" t="s">
-        <v>71</v>
-      </c>
-      <c r="S61" t="s">
-        <v>72</v>
-      </c>
       <c r="T61" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="U61" t="s">
+        <v>72</v>
+      </c>
+      <c r="V61" t="s">
+        <v>80</v>
+      </c>
+      <c r="W61" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>172</v>
       </c>
@@ -5507,29 +5531,29 @@
       <c r="K62">
         <v>40</v>
       </c>
-      <c r="O62" t="s">
-        <v>69</v>
-      </c>
-      <c r="P62" t="s">
+      <c r="Q62" t="s">
+        <v>69</v>
+      </c>
+      <c r="R62" t="s">
         <v>18</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="S62" t="s">
         <v>78</v>
       </c>
-      <c r="R62" t="s">
-        <v>71</v>
-      </c>
-      <c r="S62" t="s">
-        <v>72</v>
-      </c>
       <c r="T62" t="s">
+        <v>71</v>
+      </c>
+      <c r="U62" t="s">
+        <v>72</v>
+      </c>
+      <c r="V62" t="s">
         <v>73</v>
       </c>
-      <c r="U62" t="s">
+      <c r="W62" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>174</v>
       </c>
@@ -5561,7 +5585,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>176</v>
       </c>
@@ -5593,7 +5617,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>178</v>
       </c>
@@ -5625,7 +5649,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>180</v>
       </c>
@@ -5657,7 +5681,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>182</v>
       </c>
@@ -5689,7 +5713,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>184</v>
       </c>
@@ -5721,7 +5745,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>186</v>
       </c>
@@ -5753,7 +5777,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>187</v>
       </c>
@@ -5785,7 +5809,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>190</v>
       </c>
@@ -5817,7 +5841,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>18</v>
       </c>
@@ -5837,7 +5861,7 @@
         <v>0.33123000000000002</v>
       </c>
     </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>20</v>
       </c>
@@ -5869,7 +5893,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>15</v>
       </c>
@@ -5888,52 +5912,52 @@
       <c r="G77">
         <v>0.33123000000000002</v>
       </c>
-      <c r="O77" t="s">
-        <v>69</v>
-      </c>
-      <c r="P77" t="s">
+      <c r="Q77" t="s">
+        <v>69</v>
+      </c>
+      <c r="R77" t="s">
         <v>20</v>
       </c>
-      <c r="Q77" t="s">
+      <c r="S77" t="s">
         <v>79</v>
       </c>
-      <c r="R77" t="s">
-        <v>71</v>
-      </c>
-      <c r="S77" t="s">
-        <v>72</v>
-      </c>
       <c r="T77" t="s">
+        <v>71</v>
+      </c>
+      <c r="U77" t="s">
+        <v>72</v>
+      </c>
+      <c r="V77" t="s">
         <v>73</v>
       </c>
-      <c r="U77" t="s">
+      <c r="W77" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O78" t="s">
-        <v>69</v>
-      </c>
-      <c r="P78" t="s">
+    <row r="78" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q78" t="s">
+        <v>69</v>
+      </c>
+      <c r="R78" t="s">
         <v>15</v>
       </c>
-      <c r="Q78" t="s">
+      <c r="S78" t="s">
         <v>75</v>
       </c>
-      <c r="R78" t="s">
-        <v>71</v>
-      </c>
-      <c r="S78" t="s">
-        <v>72</v>
-      </c>
       <c r="T78" t="s">
+        <v>71</v>
+      </c>
+      <c r="U78" t="s">
+        <v>72</v>
+      </c>
+      <c r="V78" t="s">
         <v>73</v>
       </c>
-      <c r="U78" t="s">
+      <c r="W78" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>12</v>
       </c>
@@ -5965,26 +5989,26 @@
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="O80" t="s">
-        <v>69</v>
-      </c>
-      <c r="P80" t="s">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Q80" t="s">
+        <v>69</v>
+      </c>
+      <c r="R80" t="s">
         <v>12</v>
       </c>
-      <c r="Q80" t="s">
+      <c r="S80" t="s">
         <v>70</v>
       </c>
-      <c r="R80" t="s">
-        <v>71</v>
-      </c>
-      <c r="S80" t="s">
-        <v>72</v>
-      </c>
       <c r="T80" t="s">
+        <v>71</v>
+      </c>
+      <c r="U80" t="s">
+        <v>72</v>
+      </c>
+      <c r="V80" t="s">
         <v>73</v>
       </c>
-      <c r="U80" t="s">
+      <c r="W80" t="s">
         <v>74</v>
       </c>
     </row>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A505B9-3D88-425F-AEE8-4CD71FCCC70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F92CB5-29B4-4D2A-8E66-3AF8BFFF3685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -67,17 +67,34 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={D3B26940-5207-4925-84BA-C36AB3766D74}</author>
+    <author>tc={C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}</author>
     <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
     <author>tc={5D0B02A9-24B3-4F36-8683-2AD26D1E0821}</author>
-    <author>tc={06D70610-96F7-4BDA-B071-69925D70228B}</author>
-    <author>tc={A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}</author>
-    <author>tc={4E0E017D-BAC7-4AA8-B401-A7330F2C0996}</author>
+    <author>tc={C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}</author>
     <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
     <author>tc={1905391B-2A5F-4643-B2AC-720AD8410CDA}</author>
     <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
   </authors>
   <commentList>
-    <comment ref="F44" authorId="0" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <comment ref="Y11" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Miks daynite (hydro samuti)</t>
+      </text>
+    </comment>
+    <comment ref="N43" authorId="1" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)
+</t>
+      </text>
+    </comment>
+    <comment ref="F44" authorId="2" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +102,7 @@
     Iru produces only 17 MW in 2025 not 0.207 GW</t>
       </text>
     </comment>
-    <comment ref="B45" authorId="1" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+    <comment ref="B45" authorId="3" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -93,29 +110,12 @@
     TODO: set their actual start date and then add how much they produce in 2025</t>
       </text>
     </comment>
-    <comment ref="G46" authorId="2" shapeId="0" xr:uid="{06D70610-96F7-4BDA-B071-69925D70228B}">
+    <comment ref="Q47" authorId="4" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Danish Energy agency - coal CHP 2020</t>
-      </text>
-    </comment>
-    <comment ref="G48" authorId="3" shapeId="0" xr:uid="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    DAE - gas engines 2020
-</t>
-      </text>
-    </comment>
-    <comment ref="M49" authorId="4" shapeId="0" xr:uid="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    DAE - Wood pellets, Medium 2020</t>
+    Took same as chp</t>
       </text>
     </comment>
     <comment ref="E52" authorId="5" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
@@ -127,7 +127,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="Q77" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <comment ref="T77" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="216">
   <si>
     <t>~fi_t</t>
   </si>
@@ -766,6 +766,36 @@
   </si>
   <si>
     <t>fi_t</t>
+  </si>
+  <si>
+    <t>fom (%/year)</t>
+  </si>
+  <si>
+    <t>​</t>
+  </si>
+  <si>
+    <t>NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>biomass chp</t>
+  </si>
+  <si>
+    <t>CCGT (combined)</t>
+  </si>
+  <si>
+    <t>OCGT (open cycle)</t>
+  </si>
+  <si>
+    <t>inv (kw_e)</t>
+  </si>
+  <si>
+    <t>eff</t>
+  </si>
+  <si>
+    <t>vom (€/MWh_e)</t>
   </si>
 </sst>
 </file>
@@ -775,7 +805,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -796,6 +826,13 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1175,27 +1212,27 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="Y11" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+    <text>Miks daynite (hydro samuti)</text>
+  </threadedComment>
+  <threadedComment ref="N43" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+    <text xml:space="preserve">NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)
+</text>
+  </threadedComment>
   <threadedComment ref="F44" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
   <threadedComment ref="B45" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
     <text>TODO: set their actual start date and then add how much they produce in 2025</text>
   </threadedComment>
-  <threadedComment ref="G46" dT="2026-01-28T09:05:36.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{06D70610-96F7-4BDA-B071-69925D70228B}">
-    <text>Danish Energy agency - coal CHP 2020</text>
-  </threadedComment>
-  <threadedComment ref="G48" dT="2026-01-28T11:16:21.05" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{A1B9CC12-DC46-488C-9BF3-3F8DFC23199D}">
-    <text xml:space="preserve">DAE - gas engines 2020
-</text>
-  </threadedComment>
-  <threadedComment ref="M49" dT="2026-01-28T11:17:46.06" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{4E0E017D-BAC7-4AA8-B401-A7330F2C0996}">
-    <text>DAE - Wood pellets, Medium 2020</text>
+  <threadedComment ref="Q47" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+    <text>Took same as chp</text>
   </threadedComment>
   <threadedComment ref="E52" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
     <text xml:space="preserve">Ei tea
 </text>
   </threadedComment>
-  <threadedComment ref="Q77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+  <threadedComment ref="T77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
   </threadedComment>
   <threadedComment ref="J79" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
@@ -2689,7 +2726,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:W80"/>
+  <dimension ref="B9:Z90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
@@ -2702,21 +2739,24 @@
     <col min="9" max="9" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="40.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="64.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="T9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -2750,29 +2790,29 @@
       <c r="L10" t="s">
         <v>11</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="T10" t="s">
         <v>63</v>
       </c>
-      <c r="R10" t="s">
+      <c r="U10" t="s">
         <v>1</v>
       </c>
-      <c r="S10" t="s">
+      <c r="V10" t="s">
         <v>64</v>
       </c>
-      <c r="T10" t="s">
+      <c r="W10" t="s">
         <v>65</v>
       </c>
-      <c r="U10" t="s">
+      <c r="X10" t="s">
         <v>66</v>
       </c>
-      <c r="V10" t="s">
+      <c r="Y10" t="s">
         <v>67</v>
       </c>
-      <c r="W10" t="s">
+      <c r="Z10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>22</v>
       </c>
@@ -2794,29 +2834,29 @@
       <c r="L11">
         <v>0.14986856628506873</v>
       </c>
-      <c r="Q11" t="s">
-        <v>69</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="T11" t="s">
+        <v>69</v>
+      </c>
+      <c r="U11" t="s">
         <v>17</v>
       </c>
-      <c r="S11" t="s">
+      <c r="V11" t="s">
         <v>76</v>
       </c>
-      <c r="T11" t="s">
-        <v>71</v>
-      </c>
-      <c r="U11" t="s">
-        <v>72</v>
-      </c>
-      <c r="V11" t="s">
+      <c r="W11" t="s">
+        <v>71</v>
+      </c>
+      <c r="X11" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y11" t="s">
         <v>73</v>
       </c>
-      <c r="W11" t="s">
+      <c r="Z11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>25</v>
       </c>
@@ -2838,29 +2878,29 @@
       <c r="L12">
         <v>0.14986856628506873</v>
       </c>
-      <c r="Q12" t="s">
-        <v>69</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="T12" t="s">
+        <v>69</v>
+      </c>
+      <c r="U12" t="s">
         <v>22</v>
       </c>
-      <c r="S12" t="s">
+      <c r="V12" t="s">
         <v>78</v>
       </c>
-      <c r="T12" t="s">
-        <v>71</v>
-      </c>
-      <c r="U12" t="s">
-        <v>72</v>
-      </c>
-      <c r="V12" t="s">
-        <v>80</v>
-      </c>
       <c r="W12" t="s">
+        <v>71</v>
+      </c>
+      <c r="X12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -2882,29 +2922,29 @@
       <c r="L13">
         <v>0.14986856628506873</v>
       </c>
-      <c r="Q13" t="s">
-        <v>69</v>
-      </c>
-      <c r="R13" t="s">
+      <c r="T13" t="s">
+        <v>69</v>
+      </c>
+      <c r="U13" t="s">
         <v>25</v>
       </c>
-      <c r="S13" t="s">
+      <c r="V13" t="s">
         <v>78</v>
       </c>
-      <c r="T13" t="s">
-        <v>71</v>
-      </c>
-      <c r="U13" t="s">
-        <v>72</v>
-      </c>
-      <c r="V13" t="s">
-        <v>80</v>
-      </c>
       <c r="W13" t="s">
+        <v>71</v>
+      </c>
+      <c r="X13" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>29</v>
       </c>
@@ -2938,29 +2978,29 @@
       <c r="L14">
         <v>0.1461854238754417</v>
       </c>
-      <c r="Q14" t="s">
-        <v>69</v>
-      </c>
-      <c r="R14" t="s">
+      <c r="T14" t="s">
+        <v>69</v>
+      </c>
+      <c r="U14" t="s">
         <v>27</v>
       </c>
-      <c r="S14" t="s">
+      <c r="V14" t="s">
         <v>78</v>
       </c>
-      <c r="T14" t="s">
-        <v>71</v>
-      </c>
-      <c r="U14" t="s">
-        <v>72</v>
-      </c>
-      <c r="V14" t="s">
-        <v>80</v>
-      </c>
       <c r="W14" t="s">
+        <v>71</v>
+      </c>
+      <c r="X14" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -2994,29 +3034,29 @@
       <c r="L15">
         <v>0.1461854238754417</v>
       </c>
-      <c r="Q15" t="s">
-        <v>69</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="T15" t="s">
+        <v>69</v>
+      </c>
+      <c r="U15" t="s">
         <v>29</v>
       </c>
-      <c r="S15" t="s">
+      <c r="V15" t="s">
         <v>78</v>
       </c>
-      <c r="T15" t="s">
-        <v>71</v>
-      </c>
-      <c r="U15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V15" t="s">
-        <v>80</v>
-      </c>
       <c r="W15" t="s">
+        <v>71</v>
+      </c>
+      <c r="X15" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>30</v>
       </c>
@@ -3050,29 +3090,29 @@
       <c r="L16">
         <v>0.14867925344692126</v>
       </c>
-      <c r="Q16" t="s">
-        <v>69</v>
-      </c>
-      <c r="R16" t="s">
+      <c r="T16" t="s">
+        <v>69</v>
+      </c>
+      <c r="U16" t="s">
         <v>30</v>
       </c>
-      <c r="S16" t="s">
+      <c r="V16" t="s">
         <v>78</v>
       </c>
-      <c r="T16" t="s">
-        <v>71</v>
-      </c>
-      <c r="U16" t="s">
-        <v>72</v>
-      </c>
-      <c r="V16" t="s">
-        <v>80</v>
-      </c>
       <c r="W16" t="s">
+        <v>71</v>
+      </c>
+      <c r="X16" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z16" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>32</v>
       </c>
@@ -3106,29 +3146,29 @@
       <c r="L17">
         <v>0.14701259708091721</v>
       </c>
-      <c r="Q17" t="s">
-        <v>69</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="T17" t="s">
+        <v>69</v>
+      </c>
+      <c r="U17" t="s">
         <v>32</v>
       </c>
-      <c r="S17" t="s">
+      <c r="V17" t="s">
         <v>78</v>
       </c>
-      <c r="T17" t="s">
-        <v>71</v>
-      </c>
-      <c r="U17" t="s">
-        <v>72</v>
-      </c>
-      <c r="V17" t="s">
-        <v>80</v>
-      </c>
       <c r="W17" t="s">
+        <v>71</v>
+      </c>
+      <c r="X17" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>34</v>
       </c>
@@ -3162,29 +3202,29 @@
       <c r="L18">
         <v>0.15309859852159369</v>
       </c>
-      <c r="Q18" t="s">
-        <v>69</v>
-      </c>
-      <c r="R18" t="s">
+      <c r="T18" t="s">
+        <v>69</v>
+      </c>
+      <c r="U18" t="s">
         <v>34</v>
       </c>
-      <c r="S18" t="s">
+      <c r="V18" t="s">
         <v>78</v>
       </c>
-      <c r="T18" t="s">
-        <v>71</v>
-      </c>
-      <c r="U18" t="s">
-        <v>72</v>
-      </c>
-      <c r="V18" t="s">
-        <v>80</v>
-      </c>
       <c r="W18" t="s">
+        <v>71</v>
+      </c>
+      <c r="X18" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3218,29 +3258,29 @@
       <c r="L19">
         <v>0.15309859852159369</v>
       </c>
-      <c r="Q19" t="s">
-        <v>69</v>
-      </c>
-      <c r="R19" t="s">
+      <c r="T19" t="s">
+        <v>69</v>
+      </c>
+      <c r="U19" t="s">
         <v>35</v>
       </c>
-      <c r="S19" t="s">
+      <c r="V19" t="s">
         <v>78</v>
       </c>
-      <c r="T19" t="s">
-        <v>71</v>
-      </c>
-      <c r="U19" t="s">
-        <v>72</v>
-      </c>
-      <c r="V19" t="s">
-        <v>80</v>
-      </c>
       <c r="W19" t="s">
+        <v>71</v>
+      </c>
+      <c r="X19" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z19" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>35</v>
       </c>
@@ -3274,29 +3314,29 @@
       <c r="L20">
         <v>0.15619560585976827</v>
       </c>
-      <c r="Q20" t="s">
-        <v>69</v>
-      </c>
-      <c r="R20" t="s">
+      <c r="T20" t="s">
+        <v>69</v>
+      </c>
+      <c r="U20" t="s">
         <v>37</v>
       </c>
-      <c r="S20" t="s">
+      <c r="V20" t="s">
         <v>78</v>
       </c>
-      <c r="T20" t="s">
-        <v>71</v>
-      </c>
-      <c r="U20" t="s">
-        <v>72</v>
-      </c>
-      <c r="V20" t="s">
-        <v>80</v>
-      </c>
       <c r="W20" t="s">
+        <v>71</v>
+      </c>
+      <c r="X20" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>37</v>
       </c>
@@ -3330,29 +3370,29 @@
       <c r="L21">
         <v>0.14537310453496291</v>
       </c>
-      <c r="Q21" t="s">
-        <v>69</v>
-      </c>
-      <c r="R21" t="s">
+      <c r="T21" t="s">
+        <v>69</v>
+      </c>
+      <c r="U21" t="s">
         <v>39</v>
       </c>
-      <c r="S21" t="s">
+      <c r="V21" t="s">
         <v>78</v>
       </c>
-      <c r="T21" t="s">
-        <v>71</v>
-      </c>
-      <c r="U21" t="s">
-        <v>72</v>
-      </c>
-      <c r="V21" t="s">
-        <v>80</v>
-      </c>
       <c r="W21" t="s">
+        <v>71</v>
+      </c>
+      <c r="X21" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>39</v>
       </c>
@@ -3386,29 +3426,29 @@
       <c r="L22">
         <v>0.14763873655681015</v>
       </c>
-      <c r="Q22" t="s">
-        <v>69</v>
-      </c>
-      <c r="R22" t="s">
+      <c r="T22" t="s">
+        <v>69</v>
+      </c>
+      <c r="U22" t="s">
         <v>40</v>
       </c>
-      <c r="S22" t="s">
+      <c r="V22" t="s">
         <v>78</v>
       </c>
-      <c r="T22" t="s">
-        <v>71</v>
-      </c>
-      <c r="U22" t="s">
-        <v>72</v>
-      </c>
-      <c r="V22" t="s">
-        <v>80</v>
-      </c>
       <c r="W22" t="s">
+        <v>71</v>
+      </c>
+      <c r="X22" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z22" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>40</v>
       </c>
@@ -3442,29 +3482,29 @@
       <c r="L23">
         <v>0.1532628310027955</v>
       </c>
-      <c r="Q23" t="s">
-        <v>69</v>
-      </c>
-      <c r="R23" t="s">
+      <c r="T23" t="s">
+        <v>69</v>
+      </c>
+      <c r="U23" t="s">
         <v>42</v>
       </c>
-      <c r="S23" t="s">
+      <c r="V23" t="s">
         <v>78</v>
       </c>
-      <c r="T23" t="s">
-        <v>71</v>
-      </c>
-      <c r="U23" t="s">
-        <v>72</v>
-      </c>
-      <c r="V23" t="s">
-        <v>80</v>
-      </c>
       <c r="W23" t="s">
+        <v>71</v>
+      </c>
+      <c r="X23" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>40</v>
       </c>
@@ -3498,29 +3538,29 @@
       <c r="L24">
         <v>0.1532628310027955</v>
       </c>
-      <c r="Q24" t="s">
-        <v>69</v>
-      </c>
-      <c r="R24" t="s">
+      <c r="T24" t="s">
+        <v>69</v>
+      </c>
+      <c r="U24" t="s">
         <v>44</v>
       </c>
-      <c r="S24" t="s">
+      <c r="V24" t="s">
         <v>78</v>
       </c>
-      <c r="T24" t="s">
-        <v>71</v>
-      </c>
-      <c r="U24" t="s">
-        <v>72</v>
-      </c>
-      <c r="V24" t="s">
-        <v>80</v>
-      </c>
       <c r="W24" t="s">
+        <v>71</v>
+      </c>
+      <c r="X24" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z24" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>42</v>
       </c>
@@ -3554,29 +3594,29 @@
       <c r="L25">
         <v>0.1451997589052581</v>
       </c>
-      <c r="Q25" t="s">
-        <v>69</v>
-      </c>
-      <c r="R25" t="s">
+      <c r="T25" t="s">
+        <v>69</v>
+      </c>
+      <c r="U25" t="s">
         <v>47</v>
       </c>
-      <c r="S25" t="s">
+      <c r="V25" t="s">
         <v>78</v>
       </c>
-      <c r="T25" t="s">
-        <v>71</v>
-      </c>
-      <c r="U25" t="s">
-        <v>72</v>
-      </c>
-      <c r="V25" t="s">
-        <v>80</v>
-      </c>
       <c r="W25" t="s">
+        <v>71</v>
+      </c>
+      <c r="X25" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z25" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>44</v>
       </c>
@@ -3598,29 +3638,29 @@
       <c r="L26">
         <v>0.42012333946150526</v>
       </c>
-      <c r="Q26" t="s">
-        <v>69</v>
-      </c>
-      <c r="R26" t="s">
+      <c r="T26" t="s">
+        <v>69</v>
+      </c>
+      <c r="U26" t="s">
         <v>49</v>
       </c>
-      <c r="S26" t="s">
+      <c r="V26" t="s">
         <v>78</v>
       </c>
-      <c r="T26" t="s">
-        <v>71</v>
-      </c>
-      <c r="U26" t="s">
-        <v>72</v>
-      </c>
-      <c r="V26" t="s">
-        <v>80</v>
-      </c>
       <c r="W26" t="s">
+        <v>71</v>
+      </c>
+      <c r="X26" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z26" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>47</v>
       </c>
@@ -3646,29 +3686,29 @@
         <f>F26*L26*G26</f>
         <v>2.0930123559331545E-3</v>
       </c>
-      <c r="Q27" t="s">
-        <v>69</v>
-      </c>
-      <c r="R27" t="s">
+      <c r="T27" t="s">
+        <v>69</v>
+      </c>
+      <c r="U27" t="s">
         <v>51</v>
       </c>
-      <c r="S27" t="s">
+      <c r="V27" t="s">
         <v>78</v>
       </c>
-      <c r="T27" t="s">
-        <v>71</v>
-      </c>
-      <c r="U27" t="s">
-        <v>72</v>
-      </c>
-      <c r="V27" t="s">
-        <v>80</v>
-      </c>
       <c r="W27" t="s">
+        <v>71</v>
+      </c>
+      <c r="X27" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z27" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>49</v>
       </c>
@@ -3690,29 +3730,29 @@
       <c r="L28">
         <v>0.42012333946150526</v>
       </c>
-      <c r="Q28" t="s">
-        <v>69</v>
-      </c>
-      <c r="R28" t="s">
+      <c r="T28" t="s">
+        <v>69</v>
+      </c>
+      <c r="U28" t="s">
         <v>53</v>
       </c>
-      <c r="S28" t="s">
+      <c r="V28" t="s">
         <v>78</v>
       </c>
-      <c r="T28" t="s">
-        <v>71</v>
-      </c>
-      <c r="U28" t="s">
-        <v>72</v>
-      </c>
-      <c r="V28" t="s">
-        <v>80</v>
-      </c>
       <c r="W28" t="s">
+        <v>71</v>
+      </c>
+      <c r="X28" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z28" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>51</v>
       </c>
@@ -3746,29 +3786,29 @@
       <c r="L29">
         <v>0.47763777043344691</v>
       </c>
-      <c r="Q29" t="s">
-        <v>69</v>
-      </c>
-      <c r="R29" t="s">
+      <c r="T29" t="s">
+        <v>69</v>
+      </c>
+      <c r="U29" t="s">
         <v>55</v>
       </c>
-      <c r="S29" t="s">
+      <c r="V29" t="s">
         <v>78</v>
       </c>
-      <c r="T29" t="s">
-        <v>71</v>
-      </c>
-      <c r="U29" t="s">
-        <v>72</v>
-      </c>
-      <c r="V29" t="s">
-        <v>80</v>
-      </c>
       <c r="W29" t="s">
+        <v>71</v>
+      </c>
+      <c r="X29" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z29" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>53</v>
       </c>
@@ -3802,29 +3842,29 @@
       <c r="L30">
         <v>0.47814004703314078</v>
       </c>
-      <c r="Q30" t="s">
-        <v>69</v>
-      </c>
-      <c r="R30" t="s">
+      <c r="T30" t="s">
+        <v>69</v>
+      </c>
+      <c r="U30" t="s">
         <v>57</v>
       </c>
-      <c r="S30" t="s">
+      <c r="V30" t="s">
         <v>78</v>
       </c>
-      <c r="T30" t="s">
-        <v>71</v>
-      </c>
-      <c r="U30" t="s">
-        <v>72</v>
-      </c>
-      <c r="V30" t="s">
-        <v>80</v>
-      </c>
       <c r="W30" t="s">
+        <v>71</v>
+      </c>
+      <c r="X30" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z30" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>53</v>
       </c>
@@ -3858,29 +3898,29 @@
       <c r="L31">
         <v>0.47814004703314084</v>
       </c>
-      <c r="Q31" t="s">
-        <v>69</v>
-      </c>
-      <c r="R31" t="s">
+      <c r="T31" t="s">
+        <v>69</v>
+      </c>
+      <c r="U31" t="s">
         <v>59</v>
       </c>
-      <c r="S31" t="s">
+      <c r="V31" t="s">
         <v>78</v>
       </c>
-      <c r="T31" t="s">
-        <v>71</v>
-      </c>
-      <c r="U31" t="s">
-        <v>72</v>
-      </c>
-      <c r="V31" t="s">
-        <v>80</v>
-      </c>
       <c r="W31" t="s">
+        <v>71</v>
+      </c>
+      <c r="X31" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z31" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>53</v>
       </c>
@@ -3914,29 +3954,29 @@
       <c r="L32">
         <v>0.47814004703314078</v>
       </c>
-      <c r="Q32" t="s">
-        <v>69</v>
-      </c>
-      <c r="R32" t="s">
+      <c r="T32" t="s">
+        <v>69</v>
+      </c>
+      <c r="U32" t="s">
         <v>61</v>
       </c>
-      <c r="S32" t="s">
+      <c r="V32" t="s">
         <v>81</v>
       </c>
-      <c r="T32" t="s">
-        <v>71</v>
-      </c>
-      <c r="U32" t="s">
-        <v>72</v>
-      </c>
-      <c r="V32" t="s">
-        <v>80</v>
-      </c>
       <c r="W32" t="s">
+        <v>71</v>
+      </c>
+      <c r="X32" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z32" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>55</v>
       </c>
@@ -3970,14 +4010,14 @@
       <c r="L33">
         <v>0.40144059976798208</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="T33" t="s">
         <v>140</v>
       </c>
-      <c r="R33" s="1" t="s">
+      <c r="U33" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>55</v>
       </c>
@@ -4011,29 +4051,29 @@
       <c r="L34">
         <v>0.40144059976798202</v>
       </c>
-      <c r="Q34" t="s">
-        <v>69</v>
-      </c>
-      <c r="R34" t="s">
+      <c r="T34" t="s">
+        <v>69</v>
+      </c>
+      <c r="U34" t="s">
         <v>194</v>
       </c>
-      <c r="S34" t="s">
+      <c r="V34" t="s">
         <v>163</v>
       </c>
-      <c r="T34" t="s">
-        <v>71</v>
-      </c>
-      <c r="U34" t="s">
-        <v>72</v>
-      </c>
-      <c r="V34" t="s">
-        <v>80</v>
-      </c>
       <c r="W34" t="s">
+        <v>71</v>
+      </c>
+      <c r="X34" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z34" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>55</v>
       </c>
@@ -4067,29 +4107,29 @@
       <c r="L35">
         <v>0.40144059976798202</v>
       </c>
-      <c r="Q35" t="s">
-        <v>69</v>
-      </c>
-      <c r="R35" t="s">
+      <c r="T35" t="s">
+        <v>69</v>
+      </c>
+      <c r="U35" t="s">
         <v>193</v>
       </c>
-      <c r="S35" t="s">
+      <c r="V35" t="s">
         <v>148</v>
       </c>
-      <c r="T35" t="s">
-        <v>71</v>
-      </c>
-      <c r="U35" t="s">
-        <v>72</v>
-      </c>
-      <c r="V35" t="s">
-        <v>80</v>
-      </c>
       <c r="W35" t="s">
+        <v>71</v>
+      </c>
+      <c r="X35" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z35" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>55</v>
       </c>
@@ -4123,29 +4163,29 @@
       <c r="L36">
         <v>0.40144059976798208</v>
       </c>
-      <c r="Q36" t="s">
-        <v>69</v>
-      </c>
-      <c r="R36" t="s">
+      <c r="T36" t="s">
+        <v>69</v>
+      </c>
+      <c r="U36" t="s">
         <v>195</v>
       </c>
-      <c r="S36" t="s">
+      <c r="V36" t="s">
         <v>149</v>
       </c>
-      <c r="T36" t="s">
-        <v>71</v>
-      </c>
-      <c r="U36" t="s">
-        <v>72</v>
-      </c>
-      <c r="V36" t="s">
-        <v>80</v>
-      </c>
       <c r="W36" t="s">
+        <v>71</v>
+      </c>
+      <c r="X36" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z36" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>55</v>
       </c>
@@ -4179,29 +4219,29 @@
       <c r="L37">
         <v>0.40144059976798202</v>
       </c>
-      <c r="Q37" t="s">
-        <v>69</v>
-      </c>
-      <c r="R37" t="s">
+      <c r="T37" t="s">
+        <v>69</v>
+      </c>
+      <c r="U37" t="s">
         <v>196</v>
       </c>
-      <c r="S37" t="s">
+      <c r="V37" t="s">
         <v>150</v>
       </c>
-      <c r="T37" t="s">
-        <v>71</v>
-      </c>
-      <c r="U37" t="s">
-        <v>72</v>
-      </c>
-      <c r="V37" t="s">
-        <v>80</v>
-      </c>
       <c r="W37" t="s">
+        <v>71</v>
+      </c>
+      <c r="X37" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z37" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>57</v>
       </c>
@@ -4235,29 +4275,29 @@
       <c r="L38">
         <v>0.365520596150406</v>
       </c>
-      <c r="Q38" t="s">
-        <v>69</v>
-      </c>
-      <c r="R38" t="s">
+      <c r="T38" t="s">
+        <v>69</v>
+      </c>
+      <c r="U38" t="s">
         <v>142</v>
       </c>
-      <c r="S38" t="s">
+      <c r="V38" t="s">
         <v>161</v>
       </c>
-      <c r="T38" t="s">
-        <v>71</v>
-      </c>
-      <c r="U38" t="s">
-        <v>72</v>
-      </c>
-      <c r="V38" t="s">
-        <v>80</v>
-      </c>
       <c r="W38" t="s">
+        <v>71</v>
+      </c>
+      <c r="X38" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z38" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>59</v>
       </c>
@@ -4291,29 +4331,29 @@
       <c r="L39">
         <v>0.41047488326249421</v>
       </c>
-      <c r="Q39" t="s">
-        <v>69</v>
-      </c>
-      <c r="R39" t="s">
+      <c r="T39" t="s">
+        <v>69</v>
+      </c>
+      <c r="U39" t="s">
         <v>143</v>
       </c>
-      <c r="S39" t="s">
+      <c r="V39" t="s">
         <v>151</v>
       </c>
-      <c r="T39" t="s">
-        <v>71</v>
-      </c>
-      <c r="U39" t="s">
-        <v>72</v>
-      </c>
-      <c r="V39" t="s">
-        <v>80</v>
-      </c>
       <c r="W39" t="s">
+        <v>71</v>
+      </c>
+      <c r="X39" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z39" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>59</v>
       </c>
@@ -4347,29 +4387,29 @@
       <c r="L40">
         <v>0.41047488326249421</v>
       </c>
-      <c r="Q40" t="s">
-        <v>69</v>
-      </c>
-      <c r="R40" t="s">
+      <c r="T40" t="s">
+        <v>69</v>
+      </c>
+      <c r="U40" t="s">
         <v>144</v>
       </c>
-      <c r="S40" t="s">
+      <c r="V40" t="s">
         <v>152</v>
       </c>
-      <c r="T40" t="s">
-        <v>71</v>
-      </c>
-      <c r="U40" t="s">
-        <v>72</v>
-      </c>
-      <c r="V40" t="s">
-        <v>80</v>
-      </c>
       <c r="W40" t="s">
+        <v>71</v>
+      </c>
+      <c r="X40" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z40" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>59</v>
       </c>
@@ -4403,29 +4443,29 @@
       <c r="L41">
         <v>0.41047488326249421</v>
       </c>
-      <c r="Q41" t="s">
-        <v>69</v>
-      </c>
-      <c r="R41" t="s">
+      <c r="T41" t="s">
+        <v>69</v>
+      </c>
+      <c r="U41" t="s">
         <v>145</v>
       </c>
-      <c r="S41" t="s">
+      <c r="V41" t="s">
         <v>153</v>
       </c>
-      <c r="T41" t="s">
-        <v>71</v>
-      </c>
-      <c r="U41" t="s">
-        <v>72</v>
-      </c>
-      <c r="V41" t="s">
-        <v>80</v>
-      </c>
       <c r="W41" t="s">
+        <v>71</v>
+      </c>
+      <c r="X41" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z41" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>61</v>
       </c>
@@ -4459,58 +4499,70 @@
       <c r="L42">
         <v>0.365520596150406</v>
       </c>
-      <c r="Q42" t="s">
-        <v>69</v>
-      </c>
-      <c r="R42" t="s">
+      <c r="T42" t="s">
+        <v>69</v>
+      </c>
+      <c r="U42" t="s">
         <v>146</v>
       </c>
-      <c r="S42" t="s">
+      <c r="V42" t="s">
         <v>147</v>
       </c>
-      <c r="T42" t="s">
-        <v>71</v>
-      </c>
-      <c r="U42" t="s">
-        <v>72</v>
-      </c>
-      <c r="V42" t="s">
-        <v>80</v>
-      </c>
       <c r="W42" t="s">
+        <v>71</v>
+      </c>
+      <c r="X42" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z42" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>140</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>141</v>
       </c>
+      <c r="N43" t="s">
+        <v>206</v>
+      </c>
+      <c r="O43" t="s">
+        <v>213</v>
+      </c>
+      <c r="P43" t="s">
+        <v>214</v>
+      </c>
       <c r="Q43" t="s">
-        <v>69</v>
-      </c>
-      <c r="R43" t="s">
+        <v>215</v>
+      </c>
+      <c r="T43" t="s">
+        <v>69</v>
+      </c>
+      <c r="U43" t="s">
         <v>197</v>
       </c>
-      <c r="S43" t="s">
+      <c r="V43" t="s">
         <v>162</v>
       </c>
-      <c r="T43" t="s">
-        <v>71</v>
-      </c>
-      <c r="U43" t="s">
-        <v>72</v>
-      </c>
-      <c r="V43" t="s">
-        <v>80</v>
-      </c>
       <c r="W43" t="s">
+        <v>71</v>
+      </c>
+      <c r="X43" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z43" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>17</v>
       </c>
@@ -4527,43 +4579,61 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="G44">
-        <v>0.44290000000000002</v>
-      </c>
-      <c r="H44">
-        <v>1265</v>
+        <f>P45</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H44" s="2">
+        <v>1175.5066999999999</v>
       </c>
       <c r="I44" s="3">
-        <v>36.300000000000004</v>
+        <f>(N45/100)*H45</f>
+        <v>160.216352398</v>
       </c>
       <c r="J44">
-        <v>3.4650000000000007</v>
+        <f>Q45</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K44">
         <v>53</v>
       </c>
-      <c r="Q44" t="s">
-        <v>69</v>
-      </c>
-      <c r="R44" t="s">
+      <c r="M44" t="s">
+        <v>192</v>
+      </c>
+      <c r="N44" s="4">
+        <v>1.31</v>
+      </c>
+      <c r="O44" s="2">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="P44">
+        <v>0.33</v>
+      </c>
+      <c r="Q44">
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="T44" t="s">
+        <v>69</v>
+      </c>
+      <c r="U44" t="s">
         <v>154</v>
       </c>
-      <c r="S44" t="s">
+      <c r="V44" t="s">
         <v>155</v>
       </c>
-      <c r="T44" t="s">
-        <v>71</v>
-      </c>
-      <c r="U44" t="s">
-        <v>72</v>
-      </c>
-      <c r="V44" t="s">
-        <v>80</v>
-      </c>
       <c r="W44" t="s">
+        <v>71</v>
+      </c>
+      <c r="X44" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z44" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>196</v>
       </c>
@@ -4580,43 +4650,61 @@
         <v>0.77</v>
       </c>
       <c r="G45">
-        <v>0.49</v>
-      </c>
-      <c r="H45">
-        <v>2150</v>
+        <f>$P$44</f>
+        <v>0.33</v>
+      </c>
+      <c r="H45" s="2">
+        <v>4812.0244000000002</v>
       </c>
       <c r="I45" s="3">
-        <v>35.053609999999999</v>
+        <f>(1.31/100)*H45</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J45">
-        <v>3.28</v>
+        <f>$Q$44</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K45">
         <v>70</v>
       </c>
-      <c r="Q45" t="s">
-        <v>69</v>
-      </c>
-      <c r="R45" t="s">
+      <c r="M45" t="s">
+        <v>211</v>
+      </c>
+      <c r="N45" s="4">
+        <v>3.3294999999999999</v>
+      </c>
+      <c r="O45" s="2">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="P45">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="Q45">
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="T45" t="s">
+        <v>69</v>
+      </c>
+      <c r="U45" t="s">
         <v>156</v>
       </c>
-      <c r="S45" t="s">
+      <c r="V45" t="s">
         <v>157</v>
       </c>
-      <c r="T45" t="s">
-        <v>71</v>
-      </c>
-      <c r="U45" t="s">
-        <v>72</v>
-      </c>
-      <c r="V45" t="s">
-        <v>80</v>
-      </c>
       <c r="W45" t="s">
+        <v>71</v>
+      </c>
+      <c r="X45" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z45" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>194</v>
       </c>
@@ -4633,43 +4721,51 @@
         <v>0.26</v>
       </c>
       <c r="G46">
-        <v>0.49</v>
-      </c>
-      <c r="H46">
-        <v>2150</v>
+        <f t="shared" ref="G46:G47" si="0">$P$44</f>
+        <v>0.33</v>
+      </c>
+      <c r="H46" s="2">
+        <v>4812.0244000000002</v>
       </c>
       <c r="I46" s="3">
-        <v>35.053609999999999</v>
+        <f>(1.31/100)*H46</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J46">
-        <v>3.28</v>
+        <f t="shared" ref="J46:J71" si="1">$Q$44</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K46">
         <v>40</v>
       </c>
-      <c r="Q46" t="s">
-        <v>69</v>
-      </c>
-      <c r="R46" t="s">
+      <c r="M46" t="s">
+        <v>212</v>
+      </c>
+      <c r="N46" s="4"/>
+      <c r="O46" s="2"/>
+      <c r="T46" t="s">
+        <v>69</v>
+      </c>
+      <c r="U46" t="s">
         <v>170</v>
       </c>
-      <c r="S46" t="s">
+      <c r="V46" t="s">
         <v>171</v>
       </c>
-      <c r="T46" t="s">
-        <v>71</v>
-      </c>
-      <c r="U46" t="s">
-        <v>72</v>
-      </c>
-      <c r="V46" t="s">
-        <v>80</v>
-      </c>
       <c r="W46" t="s">
+        <v>71</v>
+      </c>
+      <c r="X46" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z46" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>193</v>
       </c>
@@ -4686,43 +4782,61 @@
         <v>0.185</v>
       </c>
       <c r="G47">
-        <v>0.49</v>
-      </c>
-      <c r="H47">
-        <v>2150</v>
+        <f t="shared" si="0"/>
+        <v>0.33</v>
+      </c>
+      <c r="H47" s="2">
+        <v>4812.0244000000002</v>
       </c>
       <c r="I47" s="3">
-        <v>35.053609999999999</v>
+        <f>(1.31/100)*H47</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J47">
-        <v>3.28</v>
+        <f t="shared" si="1"/>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K47">
         <v>79</v>
       </c>
-      <c r="Q47" t="s">
-        <v>69</v>
-      </c>
-      <c r="R47" t="s">
+      <c r="M47" t="s">
+        <v>209</v>
+      </c>
+      <c r="N47">
+        <v>4.5269000000000004</v>
+      </c>
+      <c r="O47" s="2">
+        <v>2950.7891</v>
+      </c>
+      <c r="P47">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="Q47">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="T47" t="s">
+        <v>69</v>
+      </c>
+      <c r="U47" t="s">
         <v>158</v>
       </c>
-      <c r="S47" t="s">
+      <c r="V47" t="s">
         <v>159</v>
       </c>
-      <c r="T47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U47" t="s">
-        <v>72</v>
-      </c>
-      <c r="V47" t="s">
-        <v>80</v>
-      </c>
       <c r="W47" t="s">
+        <v>71</v>
+      </c>
+      <c r="X47" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z47" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>142</v>
       </c>
@@ -4739,43 +4853,62 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="G48">
-        <v>0.41</v>
-      </c>
-      <c r="H48">
-        <v>360</v>
+        <f>P45</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H48" s="2">
+        <f>O45</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I48" s="3">
-        <v>9.3576800000000002</v>
+        <f>(N45/100)*H48</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J48">
-        <v>6.38</v>
+        <f>$Q$45</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K48">
         <v>40</v>
       </c>
-      <c r="Q48" t="s">
-        <v>69</v>
-      </c>
-      <c r="R48" t="s">
+      <c r="M48" t="s">
+        <v>210</v>
+      </c>
+      <c r="N48">
+        <v>3.6080999999999999</v>
+      </c>
+      <c r="O48" s="2">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="P48">
+        <v>0.2994</v>
+      </c>
+      <c r="Q48">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="T48" t="s">
+        <v>69</v>
+      </c>
+      <c r="U48" t="s">
         <v>169</v>
       </c>
-      <c r="S48" t="s">
+      <c r="V48" t="s">
         <v>160</v>
       </c>
-      <c r="T48" t="s">
-        <v>71</v>
-      </c>
-      <c r="U48" t="s">
-        <v>72</v>
-      </c>
-      <c r="V48" t="s">
-        <v>80</v>
-      </c>
       <c r="W48" t="s">
+        <v>71</v>
+      </c>
+      <c r="X48" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z48" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>143</v>
       </c>
@@ -4792,52 +4925,49 @@
         <v>3.9E-2</v>
       </c>
       <c r="G49">
-        <v>0.6</v>
+        <f>P47</f>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H49" s="2">
-        <v>3200.7518811800001</v>
+        <f>$O$47</f>
+        <v>2950.7891</v>
       </c>
       <c r="I49" s="3">
-        <v>20</v>
+        <f>(4.5269/100)*H49</f>
+        <v>133.5792717679</v>
       </c>
       <c r="J49">
-        <v>0.01</v>
+        <f>$Q$47</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K49">
         <v>40</v>
       </c>
-      <c r="M49">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N49" s="3">
-        <v>131.85821703200003</v>
-      </c>
-      <c r="O49" s="4">
-        <v>1.9778732554800003</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>69</v>
-      </c>
-      <c r="R49" t="s">
+      <c r="N49" s="3"/>
+      <c r="O49" s="4"/>
+      <c r="T49" t="s">
+        <v>69</v>
+      </c>
+      <c r="U49" t="s">
         <v>164</v>
       </c>
-      <c r="S49" t="s">
+      <c r="V49" t="s">
         <v>165</v>
       </c>
-      <c r="T49" t="s">
-        <v>71</v>
-      </c>
-      <c r="U49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V49" t="s">
-        <v>80</v>
-      </c>
       <c r="W49" t="s">
+        <v>71</v>
+      </c>
+      <c r="X49" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z49" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>144</v>
       </c>
@@ -4854,52 +4984,48 @@
         <v>2.2100000000000002E-2</v>
       </c>
       <c r="G50">
-        <v>0.6</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H50" s="2">
-        <v>3200.7518811800001</v>
+        <f t="shared" ref="H50:H52" si="2">$O$47</f>
+        <v>2950.7891</v>
       </c>
       <c r="I50" s="3">
-        <v>20</v>
+        <f t="shared" ref="I50:I53" si="3">(4.5269/100)*H50</f>
+        <v>133.5792717679</v>
       </c>
       <c r="J50">
-        <v>0.01</v>
+        <f t="shared" ref="J50:J52" si="4">$Q$47</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K50">
         <v>40</v>
       </c>
-      <c r="M50">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N50" s="3">
-        <v>131.85821703200003</v>
-      </c>
-      <c r="O50" s="4">
-        <v>1.9778732554800003</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>69</v>
-      </c>
-      <c r="R50" t="s">
+      <c r="N50" s="3"/>
+      <c r="O50" s="4"/>
+      <c r="T50" t="s">
+        <v>69</v>
+      </c>
+      <c r="U50" t="s">
         <v>168</v>
       </c>
-      <c r="S50" t="s">
+      <c r="V50" t="s">
         <v>166</v>
       </c>
-      <c r="T50" t="s">
-        <v>71</v>
-      </c>
-      <c r="U50" t="s">
-        <v>72</v>
-      </c>
-      <c r="V50" t="s">
-        <v>80</v>
-      </c>
       <c r="W50" t="s">
+        <v>71</v>
+      </c>
+      <c r="X50" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z50" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>145</v>
       </c>
@@ -4916,52 +5042,48 @@
         <v>2.0500000000000001E-2</v>
       </c>
       <c r="G51">
-        <v>0.6</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H51" s="2">
-        <v>3200.7518811800001</v>
+        <f t="shared" si="2"/>
+        <v>2950.7891</v>
       </c>
       <c r="I51" s="3">
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>133.5792717679</v>
       </c>
       <c r="J51">
-        <v>0.01</v>
+        <f t="shared" si="4"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K51">
         <v>40</v>
       </c>
-      <c r="M51">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N51" s="3">
-        <v>131.85821703200003</v>
-      </c>
-      <c r="O51" s="4">
-        <v>1.9778732554800003</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>69</v>
-      </c>
-      <c r="R51" t="s">
+      <c r="N51" s="3"/>
+      <c r="O51" s="4"/>
+      <c r="T51" t="s">
+        <v>69</v>
+      </c>
+      <c r="U51" t="s">
         <v>198</v>
       </c>
-      <c r="S51" t="s">
+      <c r="V51" t="s">
         <v>167</v>
       </c>
-      <c r="T51" t="s">
-        <v>71</v>
-      </c>
-      <c r="U51" t="s">
-        <v>72</v>
-      </c>
-      <c r="V51" t="s">
-        <v>80</v>
-      </c>
       <c r="W51" t="s">
+        <v>71</v>
+      </c>
+      <c r="X51" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z51" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>146</v>
       </c>
@@ -4978,52 +5100,48 @@
         <v>1.3900000000000001E-2</v>
       </c>
       <c r="G52">
-        <v>0.6</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H52" s="2">
-        <v>3200.7518811800001</v>
+        <f t="shared" si="2"/>
+        <v>2950.7891</v>
       </c>
       <c r="I52" s="3">
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>133.5792717679</v>
       </c>
       <c r="J52">
-        <v>0.01</v>
+        <f t="shared" si="4"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K52">
         <v>40</v>
       </c>
-      <c r="M52">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N52" s="3">
-        <v>131.85821703200003</v>
-      </c>
-      <c r="O52" s="4">
-        <v>1.9778732554800003</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>69</v>
-      </c>
-      <c r="R52" t="s">
+      <c r="N52" s="3"/>
+      <c r="O52" s="4"/>
+      <c r="T52" t="s">
+        <v>69</v>
+      </c>
+      <c r="U52" t="s">
         <v>172</v>
       </c>
-      <c r="S52" t="s">
+      <c r="V52" t="s">
         <v>173</v>
       </c>
-      <c r="T52" t="s">
-        <v>71</v>
-      </c>
-      <c r="U52" t="s">
-        <v>72</v>
-      </c>
-      <c r="V52" t="s">
-        <v>80</v>
-      </c>
       <c r="W52" t="s">
+        <v>71</v>
+      </c>
+      <c r="X52" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z52" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>197</v>
       </c>
@@ -5040,43 +5158,47 @@
         <v>0.01</v>
       </c>
       <c r="G53">
-        <v>0.49</v>
+        <f>P44</f>
+        <v>0.33</v>
       </c>
       <c r="H53" s="2">
-        <v>2150</v>
+        <f>O44</f>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I53" s="3">
-        <v>35.053609999999999</v>
-      </c>
-      <c r="J53" s="4">
-        <v>3.28</v>
+        <f>($N$44/100)*H53</f>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J53">
+        <f>$Q$44</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K53">
         <v>40</v>
       </c>
-      <c r="Q53" t="s">
-        <v>69</v>
-      </c>
-      <c r="R53" t="s">
+      <c r="T53" t="s">
+        <v>69</v>
+      </c>
+      <c r="U53" t="s">
         <v>174</v>
       </c>
-      <c r="S53" t="s">
+      <c r="V53" t="s">
         <v>175</v>
       </c>
-      <c r="T53" t="s">
-        <v>71</v>
-      </c>
-      <c r="U53" t="s">
-        <v>72</v>
-      </c>
-      <c r="V53" t="s">
-        <v>80</v>
-      </c>
       <c r="W53" t="s">
+        <v>71</v>
+      </c>
+      <c r="X53" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z53" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>154</v>
       </c>
@@ -5096,40 +5218,43 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H54" s="2">
-        <v>3200.7518811800001</v>
+        <f>$O$48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I54" s="3">
-        <v>131.85821703200003</v>
-      </c>
-      <c r="J54" s="4">
-        <v>1.9778732554800003</v>
+        <f>($N$48/100)*H54</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J54">
+        <f>$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K54">
         <v>40</v>
       </c>
-      <c r="Q54" t="s">
-        <v>69</v>
-      </c>
-      <c r="R54" t="s">
+      <c r="T54" t="s">
+        <v>69</v>
+      </c>
+      <c r="U54" t="s">
         <v>176</v>
       </c>
-      <c r="S54" t="s">
+      <c r="V54" t="s">
         <v>177</v>
       </c>
-      <c r="T54" t="s">
-        <v>71</v>
-      </c>
-      <c r="U54" t="s">
-        <v>72</v>
-      </c>
-      <c r="V54" t="s">
-        <v>80</v>
-      </c>
       <c r="W54" t="s">
+        <v>71</v>
+      </c>
+      <c r="X54" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z54" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>156</v>
       </c>
@@ -5149,40 +5274,43 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H55" s="2">
-        <v>3200.7518811800001</v>
+        <f t="shared" ref="H55:H57" si="5">$O$48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I55" s="3">
-        <v>131.85821703200003</v>
-      </c>
-      <c r="J55" s="4">
-        <v>1.9778732554800003</v>
+        <f t="shared" ref="I55:I58" si="6">($N$48/100)*H55</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J55">
+        <f t="shared" ref="J55:J57" si="7">$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K55">
         <v>40</v>
       </c>
-      <c r="Q55" t="s">
-        <v>69</v>
-      </c>
-      <c r="R55" t="s">
+      <c r="T55" t="s">
+        <v>69</v>
+      </c>
+      <c r="U55" t="s">
         <v>178</v>
       </c>
-      <c r="S55" t="s">
+      <c r="V55" t="s">
         <v>179</v>
       </c>
-      <c r="T55" t="s">
-        <v>71</v>
-      </c>
-      <c r="U55" t="s">
-        <v>72</v>
-      </c>
-      <c r="V55" t="s">
-        <v>80</v>
-      </c>
       <c r="W55" t="s">
+        <v>71</v>
+      </c>
+      <c r="X55" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z55" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>170</v>
       </c>
@@ -5202,40 +5330,43 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H56" s="2">
-        <v>3200.7518811800001</v>
+        <f t="shared" si="5"/>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I56" s="3">
-        <v>131.85821703200003</v>
-      </c>
-      <c r="J56" s="4">
-        <v>1.9778732554800003</v>
+        <f t="shared" si="6"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="7"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K56">
         <v>40</v>
       </c>
-      <c r="Q56" t="s">
-        <v>69</v>
-      </c>
-      <c r="R56" t="s">
+      <c r="T56" t="s">
+        <v>69</v>
+      </c>
+      <c r="U56" t="s">
         <v>180</v>
       </c>
-      <c r="S56" t="s">
+      <c r="V56" t="s">
         <v>181</v>
       </c>
-      <c r="T56" t="s">
-        <v>71</v>
-      </c>
-      <c r="U56" t="s">
-        <v>72</v>
-      </c>
-      <c r="V56" t="s">
-        <v>80</v>
-      </c>
       <c r="W56" t="s">
+        <v>71</v>
+      </c>
+      <c r="X56" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z56" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="57" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>158</v>
       </c>
@@ -5255,40 +5386,43 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H57" s="2">
-        <v>3200.7518811800001</v>
+        <f t="shared" si="5"/>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I57" s="3">
-        <v>131.85821703200003</v>
-      </c>
-      <c r="J57" s="4">
-        <v>1.9778732554800003</v>
+        <f t="shared" si="6"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="7"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K57">
         <v>72</v>
       </c>
-      <c r="Q57" t="s">
-        <v>69</v>
-      </c>
-      <c r="R57" t="s">
+      <c r="T57" t="s">
+        <v>69</v>
+      </c>
+      <c r="U57" t="s">
         <v>182</v>
       </c>
-      <c r="S57" t="s">
+      <c r="V57" t="s">
         <v>183</v>
       </c>
-      <c r="T57" t="s">
-        <v>71</v>
-      </c>
-      <c r="U57" t="s">
-        <v>72</v>
-      </c>
-      <c r="V57" t="s">
-        <v>80</v>
-      </c>
       <c r="W57" t="s">
+        <v>71</v>
+      </c>
+      <c r="X57" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z57" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="58" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>169</v>
       </c>
@@ -5305,43 +5439,47 @@
         <v>5.7999999999999996E-3</v>
       </c>
       <c r="G58">
-        <v>0.41</v>
+        <f>P45</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H58" s="2">
-        <v>521.0526318200001</v>
+        <f>O45</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I58" s="3">
-        <v>6.9119226670000007</v>
-      </c>
-      <c r="J58" s="4">
-        <v>6.38</v>
+        <f>($N$45/100)*H58</f>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J58">
+        <f>$Q$45</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K58">
         <v>40</v>
       </c>
-      <c r="Q58" t="s">
-        <v>69</v>
-      </c>
-      <c r="R58" t="s">
+      <c r="T58" t="s">
+        <v>69</v>
+      </c>
+      <c r="U58" t="s">
         <v>184</v>
       </c>
-      <c r="S58" t="s">
+      <c r="V58" t="s">
         <v>185</v>
       </c>
-      <c r="T58" t="s">
-        <v>71</v>
-      </c>
-      <c r="U58" t="s">
-        <v>72</v>
-      </c>
-      <c r="V58" t="s">
-        <v>80</v>
-      </c>
       <c r="W58" t="s">
+        <v>71</v>
+      </c>
+      <c r="X58" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z58" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>164</v>
       </c>
@@ -5361,40 +5499,43 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H59" s="2">
-        <v>3200.7518811800001</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I59" s="3">
-        <v>131.85821703200003</v>
-      </c>
-      <c r="J59" s="4">
-        <v>1.9778732554800003</v>
+        <f>($N$48/100)*H59</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J59">
+        <f>$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K59">
         <v>40</v>
       </c>
-      <c r="Q59" t="s">
-        <v>69</v>
-      </c>
-      <c r="R59" t="s">
+      <c r="T59" t="s">
+        <v>69</v>
+      </c>
+      <c r="U59" t="s">
         <v>186</v>
       </c>
-      <c r="S59" t="s">
+      <c r="V59" t="s">
         <v>188</v>
       </c>
-      <c r="T59" t="s">
-        <v>71</v>
-      </c>
-      <c r="U59" t="s">
-        <v>72</v>
-      </c>
-      <c r="V59" t="s">
-        <v>80</v>
-      </c>
       <c r="W59" t="s">
+        <v>71</v>
+      </c>
+      <c r="X59" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z59" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>168</v>
       </c>
@@ -5411,43 +5552,47 @@
         <v>4.0999999999999995E-3</v>
       </c>
       <c r="G60">
-        <v>0.41</v>
+        <f>P45</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H60" s="2">
-        <v>521.0526318200001</v>
+        <f>O45</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I60" s="3">
-        <v>6.9119226670000007</v>
-      </c>
-      <c r="J60" s="4">
-        <v>6.38</v>
+        <f>($N$45/100)*H60</f>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J60">
+        <f>$Q$45</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K60">
         <v>40</v>
       </c>
-      <c r="Q60" t="s">
-        <v>69</v>
-      </c>
-      <c r="R60" t="s">
+      <c r="T60" t="s">
+        <v>69</v>
+      </c>
+      <c r="U60" t="s">
         <v>187</v>
       </c>
-      <c r="S60" t="s">
+      <c r="V60" t="s">
         <v>189</v>
       </c>
-      <c r="T60" t="s">
-        <v>71</v>
-      </c>
-      <c r="U60" t="s">
-        <v>72</v>
-      </c>
-      <c r="V60" t="s">
-        <v>80</v>
-      </c>
       <c r="W60" t="s">
+        <v>71</v>
+      </c>
+      <c r="X60" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z60" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>198</v>
       </c>
@@ -5464,43 +5609,47 @@
         <v>1.4E-3</v>
       </c>
       <c r="G61">
-        <v>0.49</v>
+        <f>P44</f>
+        <v>0.33</v>
       </c>
       <c r="H61" s="2">
-        <v>2150</v>
+        <f>O44</f>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I61" s="3">
-        <v>35.053609999999999</v>
-      </c>
-      <c r="J61" s="4">
-        <v>3.28</v>
+        <f>($N$48/100)*H61</f>
+        <v>173.62265237640003</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="1"/>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K61">
         <v>40</v>
       </c>
-      <c r="Q61" t="s">
-        <v>69</v>
-      </c>
-      <c r="R61" t="s">
+      <c r="T61" t="s">
+        <v>69</v>
+      </c>
+      <c r="U61" t="s">
         <v>190</v>
       </c>
-      <c r="S61" t="s">
+      <c r="V61" t="s">
         <v>191</v>
       </c>
-      <c r="T61" t="s">
-        <v>71</v>
-      </c>
-      <c r="U61" t="s">
-        <v>72</v>
-      </c>
-      <c r="V61" t="s">
-        <v>80</v>
-      </c>
       <c r="W61" t="s">
+        <v>71</v>
+      </c>
+      <c r="X61" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z61" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>172</v>
       </c>
@@ -5520,40 +5669,43 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H62" s="2">
-        <v>6444.0386710800003</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I62" s="3">
-        <v>288.17400657800005</v>
-      </c>
-      <c r="J62" s="4">
-        <v>4.1365198730200001</v>
+        <f>($N$48/100)*H62</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J62">
+        <f>$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K62">
         <v>40</v>
       </c>
-      <c r="Q62" t="s">
-        <v>69</v>
-      </c>
-      <c r="R62" t="s">
+      <c r="T62" t="s">
+        <v>69</v>
+      </c>
+      <c r="U62" t="s">
         <v>18</v>
       </c>
-      <c r="S62" t="s">
+      <c r="V62" t="s">
         <v>78</v>
       </c>
-      <c r="T62" t="s">
-        <v>71</v>
-      </c>
-      <c r="U62" t="s">
-        <v>72</v>
-      </c>
-      <c r="V62" t="s">
+      <c r="W62" t="s">
+        <v>71</v>
+      </c>
+      <c r="X62" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y62" t="s">
         <v>73</v>
       </c>
-      <c r="W62" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="63" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="Z62" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>174</v>
       </c>
@@ -5573,19 +5725,22 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H63" s="2">
-        <v>6444.0386710800003</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I63" s="3">
-        <v>288.17400657800005</v>
-      </c>
-      <c r="J63" s="4">
-        <v>4.1365198730200001</v>
+        <f>($N$48/100)*H63</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J63">
+        <f>$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K63">
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>176</v>
       </c>
@@ -5602,22 +5757,26 @@
         <v>1.8E-3</v>
       </c>
       <c r="G64">
-        <v>0.41</v>
+        <f>P45</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H64" s="2">
-        <v>521.0526318200001</v>
+        <f>O45</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I64" s="3">
-        <v>6.9119226670000007</v>
-      </c>
-      <c r="J64" s="4">
-        <v>6.38</v>
+        <f t="shared" ref="I59:I71" si="8">($N$45/100)*H64</f>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J64">
+        <f>$Q$45</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K64">
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>178</v>
       </c>
@@ -5634,22 +5793,26 @@
         <v>1.8E-3</v>
       </c>
       <c r="G65">
-        <v>0.41</v>
+        <f>P45</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H65" s="2">
-        <v>521.0526318200001</v>
+        <f>O45</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I65" s="3">
-        <v>6.9119226670000007</v>
-      </c>
-      <c r="J65" s="4">
-        <v>6.38</v>
+        <f t="shared" si="8"/>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J65">
+        <f>$Q$45</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K65">
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>180</v>
       </c>
@@ -5669,19 +5832,22 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H66" s="2">
-        <v>1010.2040821000001</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I66" s="3">
-        <v>10.3678840005</v>
-      </c>
-      <c r="J66" s="4">
-        <v>7.9752953850000008</v>
+        <f>($N$48/100)*H66</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J66">
+        <f>$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K66">
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>182</v>
       </c>
@@ -5701,19 +5867,22 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H67" s="2">
-        <v>1010.2040821000001</v>
+        <f>$O$48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I67" s="3">
-        <v>10.3678840005</v>
-      </c>
-      <c r="J67" s="4">
-        <v>7.9752953850000008</v>
+        <f t="shared" ref="I67:I71" si="9">($N$48/100)*H67</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J67">
+        <f t="shared" ref="J67:J71" si="10">$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K67">
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>184</v>
       </c>
@@ -5733,19 +5902,25 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H68" s="2">
-        <v>1010.2040821000001</v>
+        <f>$O$48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I68" s="3">
-        <v>10.3678840005</v>
-      </c>
-      <c r="J68" s="4">
-        <v>7.9752953850000008</v>
+        <f t="shared" si="9"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="10"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K68">
         <v>40</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="U68" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>186</v>
       </c>
@@ -5765,19 +5940,22 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H69" s="2">
-        <v>11048.442540020002</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I69" s="3">
-        <v>437.04618709800002</v>
-      </c>
-      <c r="J69" s="4">
-        <v>27.520085941840001</v>
+        <f t="shared" si="9"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="10"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K69">
         <v>40</v>
       </c>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>187</v>
       </c>
@@ -5797,19 +5975,22 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H70" s="2">
-        <v>6444.0386710800003</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I70" s="3">
-        <v>288.17400657800005</v>
-      </c>
-      <c r="J70" s="4">
-        <v>4.1365198730200001</v>
+        <f t="shared" si="9"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="10"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K70">
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>190</v>
       </c>
@@ -5829,19 +6010,22 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H71" s="2">
-        <v>11048.442540020002</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I71" s="3">
-        <v>437.04618709800002</v>
-      </c>
-      <c r="J71" s="4">
-        <v>27.520085941840001</v>
+        <f t="shared" si="9"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="10"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K71">
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>18</v>
       </c>
@@ -5861,7 +6045,7 @@
         <v>0.33123000000000002</v>
       </c>
     </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>20</v>
       </c>
@@ -5893,7 +6077,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>15</v>
       </c>
@@ -5912,52 +6096,52 @@
       <c r="G77">
         <v>0.33123000000000002</v>
       </c>
-      <c r="Q77" t="s">
-        <v>69</v>
-      </c>
-      <c r="R77" t="s">
+      <c r="T77" t="s">
+        <v>69</v>
+      </c>
+      <c r="U77" t="s">
         <v>20</v>
       </c>
-      <c r="S77" t="s">
+      <c r="V77" t="s">
         <v>79</v>
       </c>
-      <c r="T77" t="s">
-        <v>71</v>
-      </c>
-      <c r="U77" t="s">
-        <v>72</v>
-      </c>
-      <c r="V77" t="s">
+      <c r="W77" t="s">
+        <v>71</v>
+      </c>
+      <c r="X77" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y77" t="s">
         <v>73</v>
       </c>
-      <c r="W77" t="s">
+      <c r="Z77" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="Q78" t="s">
-        <v>69</v>
-      </c>
-      <c r="R78" t="s">
+    <row r="78" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T78" t="s">
+        <v>69</v>
+      </c>
+      <c r="U78" t="s">
         <v>15</v>
       </c>
-      <c r="S78" t="s">
+      <c r="V78" t="s">
         <v>75</v>
       </c>
-      <c r="T78" t="s">
-        <v>71</v>
-      </c>
-      <c r="U78" t="s">
-        <v>72</v>
-      </c>
-      <c r="V78" t="s">
+      <c r="W78" t="s">
+        <v>71</v>
+      </c>
+      <c r="X78" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y78" t="s">
         <v>73</v>
       </c>
-      <c r="W78" t="s">
+      <c r="Z78" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>12</v>
       </c>
@@ -5989,31 +6173,40 @@
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="Q80" t="s">
-        <v>69</v>
-      </c>
-      <c r="R80" t="s">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T80" t="s">
+        <v>69</v>
+      </c>
+      <c r="U80" t="s">
         <v>12</v>
       </c>
-      <c r="S80" t="s">
+      <c r="V80" t="s">
         <v>70</v>
       </c>
-      <c r="T80" t="s">
-        <v>71</v>
-      </c>
-      <c r="U80" t="s">
-        <v>72</v>
-      </c>
-      <c r="V80" t="s">
+      <c r="W80" t="s">
+        <v>71</v>
+      </c>
+      <c r="X80" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y80" t="s">
         <v>73</v>
       </c>
-      <c r="W80" t="s">
+      <c r="Z80" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="90" spans="16:16" x14ac:dyDescent="0.25">
+      <c r="P90" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="I58 I60" formula="1"/>
+  </ignoredErrors>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F92CB5-29B4-4D2A-8E66-3AF8BFFF3685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D0FBD3-4A06-4882-ABEC-CB14D89A0503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -4797,7 +4797,7 @@
         <v>4.1005000000000003</v>
       </c>
       <c r="K47">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="M47" t="s">
         <v>209</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D0FBD3-4A06-4882-ABEC-CB14D89A0503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6733E1-09C3-4ECB-9991-608C0A41B910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -4797,7 +4797,7 @@
         <v>4.1005000000000003</v>
       </c>
       <c r="K47">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M47" t="s">
         <v>209</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6733E1-09C3-4ECB-9991-608C0A41B910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FEB176-2FE1-43D5-9914-074449323CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-10340" yWindow="11740" windowWidth="19180" windowHeight="11260" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -118,7 +118,7 @@
     Took same as chp</t>
       </text>
     </comment>
-    <comment ref="E52" authorId="5" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
+    <comment ref="E53" authorId="5" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -135,7 +135,7 @@
     Frequency reserve</t>
       </text>
     </comment>
-    <comment ref="J79" authorId="7" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <comment ref="J80" authorId="7" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="216">
   <si>
     <t>~fi_t</t>
   </si>
@@ -805,7 +805,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -820,19 +820,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1228,14 +1215,14 @@
   <threadedComment ref="Q47" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
     <text>Took same as chp</text>
   </threadedComment>
-  <threadedComment ref="E52" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
+  <threadedComment ref="E53" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
     <text xml:space="preserve">Ei tea
 </text>
   </threadedComment>
   <threadedComment ref="T77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
   </threadedComment>
-  <threadedComment ref="J79" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+  <threadedComment ref="J80" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
     <text>From 9,24 to 6</text>
   </threadedComment>
 </ThreadedComments>
@@ -2745,6 +2732,7 @@
     <col min="17" max="17" width="64.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="64.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4576,7 +4564,7 @@
         <v>1982</v>
       </c>
       <c r="F44">
-        <v>1.6999999999999999E-3</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G44">
         <f>P45</f>
@@ -4721,7 +4709,7 @@
         <v>0.26</v>
       </c>
       <c r="G46">
-        <f t="shared" ref="G46:G47" si="0">$P$44</f>
+        <f t="shared" ref="G46:G48" si="0">$P$44</f>
         <v>0.33</v>
       </c>
       <c r="H46" s="2">
@@ -4732,7 +4720,7 @@
         <v>63.037519640000006</v>
       </c>
       <c r="J46">
-        <f t="shared" ref="J46:J71" si="1">$Q$44</f>
+        <f t="shared" ref="J46:J62" si="1">$Q$44</f>
         <v>4.1005000000000003</v>
       </c>
       <c r="K46">
@@ -4767,7 +4755,7 @@
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C47" t="s">
         <v>192</v>
@@ -4776,13 +4764,13 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>1956</v>
+        <v>2025</v>
       </c>
       <c r="F47">
-        <v>0.185</v>
+        <f>0.01</f>
+        <v>0.01</v>
       </c>
       <c r="G47">
-        <f t="shared" si="0"/>
         <v>0.33</v>
       </c>
       <c r="H47" s="2">
@@ -4793,152 +4781,151 @@
         <v>63.037519640000006</v>
       </c>
       <c r="J47">
+        <f>$Q$44</f>
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="K47">
+        <v>40</v>
+      </c>
+      <c r="M47" t="s">
+        <v>209</v>
+      </c>
+      <c r="N47">
+        <v>4.5269000000000004</v>
+      </c>
+      <c r="O47" s="2">
+        <v>2950.7891</v>
+      </c>
+      <c r="P47">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="Q47">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="T47" t="s">
+        <v>69</v>
+      </c>
+      <c r="U47" t="s">
+        <v>158</v>
+      </c>
+      <c r="V47" t="s">
+        <v>159</v>
+      </c>
+      <c r="W47" t="s">
+        <v>71</v>
+      </c>
+      <c r="X47" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>193</v>
+      </c>
+      <c r="C48" t="s">
+        <v>192</v>
+      </c>
+      <c r="D48" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48">
+        <v>1956</v>
+      </c>
+      <c r="F48">
+        <v>0.185</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="0"/>
+        <v>0.33</v>
+      </c>
+      <c r="H48" s="2">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I48" s="3">
+        <f>(1.31/100)*H48</f>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J48">
         <f t="shared" si="1"/>
         <v>4.1005000000000003</v>
       </c>
-      <c r="K47">
+      <c r="K48">
         <v>73</v>
       </c>
-      <c r="M47" t="s">
-        <v>209</v>
-      </c>
-      <c r="N47">
-        <v>4.5269000000000004</v>
-      </c>
-      <c r="O47" s="2">
-        <v>2950.7891</v>
-      </c>
-      <c r="P47">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="Q47">
+      <c r="M48" t="s">
+        <v>210</v>
+      </c>
+      <c r="N48">
+        <v>3.6080999999999999</v>
+      </c>
+      <c r="O48" s="2">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="P48">
+        <v>0.2994</v>
+      </c>
+      <c r="Q48">
         <v>2.8138000000000001</v>
       </c>
-      <c r="T47" t="s">
-        <v>69</v>
-      </c>
-      <c r="U47" t="s">
-        <v>158</v>
-      </c>
-      <c r="V47" t="s">
-        <v>159</v>
-      </c>
-      <c r="W47" t="s">
-        <v>71</v>
-      </c>
-      <c r="X47" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z47" t="s">
+      <c r="T48" t="s">
+        <v>69</v>
+      </c>
+      <c r="U48" t="s">
+        <v>169</v>
+      </c>
+      <c r="V48" t="s">
+        <v>160</v>
+      </c>
+      <c r="W48" t="s">
+        <v>71</v>
+      </c>
+      <c r="X48" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z48" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
+    <row r="49" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
         <v>142</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>16</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>14</v>
       </c>
-      <c r="E48">
+      <c r="E49">
         <v>2021</v>
       </c>
-      <c r="F48">
+      <c r="F49">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="G48">
+      <c r="G49">
         <f>P45</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H49" s="2">
         <f>O45</f>
         <v>1175.5066999999999</v>
       </c>
-      <c r="I48" s="3">
-        <f>(N45/100)*H48</f>
+      <c r="I49" s="3">
+        <f>(N45/100)*H49</f>
         <v>39.138495576499992</v>
       </c>
-      <c r="J48">
+      <c r="J49">
         <f>$Q$45</f>
         <v>5.8775000000000004</v>
-      </c>
-      <c r="K48">
-        <v>40</v>
-      </c>
-      <c r="M48" t="s">
-        <v>210</v>
-      </c>
-      <c r="N48">
-        <v>3.6080999999999999</v>
-      </c>
-      <c r="O48" s="2">
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="P48">
-        <v>0.2994</v>
-      </c>
-      <c r="Q48">
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="T48" t="s">
-        <v>69</v>
-      </c>
-      <c r="U48" t="s">
-        <v>169</v>
-      </c>
-      <c r="V48" t="s">
-        <v>160</v>
-      </c>
-      <c r="W48" t="s">
-        <v>71</v>
-      </c>
-      <c r="X48" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y48" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
-        <v>143</v>
-      </c>
-      <c r="C49" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49">
-        <v>2018</v>
-      </c>
-      <c r="F49">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G49">
-        <f>P47</f>
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="H49" s="2">
-        <f>$O$47</f>
-        <v>2950.7891</v>
-      </c>
-      <c r="I49" s="3">
-        <f>(4.5269/100)*H49</f>
-        <v>133.5792717679</v>
-      </c>
-      <c r="J49">
-        <f>$Q$47</f>
-        <v>2.8138000000000001</v>
       </c>
       <c r="K49">
         <v>40</v>
@@ -4969,7 +4956,7 @@
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
@@ -4978,24 +4965,25 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>2009</v>
+        <v>2018</v>
       </c>
       <c r="F50">
-        <v>2.2100000000000002E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G50">
+        <f>P47</f>
         <v>0.46800000000000003</v>
       </c>
       <c r="H50" s="2">
-        <f t="shared" ref="H50:H52" si="2">$O$47</f>
+        <f>$O$47</f>
         <v>2950.7891</v>
       </c>
       <c r="I50" s="3">
-        <f t="shared" ref="I50:I53" si="3">(4.5269/100)*H50</f>
+        <f>(4.5269/100)*H50</f>
         <v>133.5792717679</v>
       </c>
       <c r="J50">
-        <f t="shared" ref="J50:J52" si="4">$Q$47</f>
+        <f>$Q$47</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K50">
@@ -5027,7 +5015,7 @@
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s">
         <v>13</v>
@@ -5036,24 +5024,24 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="F51">
-        <v>2.0500000000000001E-2</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="G51">
         <v>0.46800000000000003</v>
       </c>
       <c r="H51" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H51:H53" si="2">$O$47</f>
         <v>2950.7891</v>
       </c>
       <c r="I51" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="I51:I53" si="3">(4.5269/100)*H51</f>
         <v>133.5792717679</v>
       </c>
       <c r="J51">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="J51:J53" si="4">$Q$47</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K51">
@@ -5085,7 +5073,7 @@
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
@@ -5094,10 +5082,10 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="F52">
-        <v>1.3900000000000001E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="G52">
         <v>0.46800000000000003</v>
@@ -5143,148 +5131,148 @@
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>197</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="D53" t="s">
         <v>14</v>
       </c>
       <c r="E53">
+        <v>2010</v>
+      </c>
+      <c r="F53">
+        <v>1.3900000000000001E-2</v>
+      </c>
+      <c r="G53">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="H53" s="2">
+        <f t="shared" si="2"/>
+        <v>2950.7891</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>133.5792717679</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="4"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K53">
+        <v>40</v>
+      </c>
+      <c r="T53" t="s">
+        <v>69</v>
+      </c>
+      <c r="U53" t="s">
+        <v>174</v>
+      </c>
+      <c r="V53" t="s">
+        <v>175</v>
+      </c>
+      <c r="W53" t="s">
+        <v>71</v>
+      </c>
+      <c r="X53" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>197</v>
+      </c>
+      <c r="C54" t="s">
+        <v>192</v>
+      </c>
+      <c r="D54" t="s">
+        <v>14</v>
+      </c>
+      <c r="E54">
         <v>1997</v>
       </c>
-      <c r="F53">
+      <c r="F54">
         <v>0.01</v>
       </c>
-      <c r="G53">
+      <c r="G54">
         <f>P44</f>
         <v>0.33</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H54" s="2">
         <f>O44</f>
         <v>4812.0244000000002</v>
       </c>
-      <c r="I53" s="3">
-        <f>($N$44/100)*H53</f>
+      <c r="I54" s="3">
+        <f>($N$44/100)*H54</f>
         <v>63.037519640000006</v>
       </c>
-      <c r="J53">
+      <c r="J54">
         <f>$Q$44</f>
         <v>4.1005000000000003</v>
       </c>
-      <c r="K53">
+      <c r="K54">
         <v>40</v>
       </c>
-      <c r="T53" t="s">
-        <v>69</v>
-      </c>
-      <c r="U53" t="s">
-        <v>174</v>
-      </c>
-      <c r="V53" t="s">
-        <v>175</v>
-      </c>
-      <c r="W53" t="s">
-        <v>71</v>
-      </c>
-      <c r="X53" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z53" t="s">
+      <c r="T54" t="s">
+        <v>69</v>
+      </c>
+      <c r="U54" t="s">
+        <v>176</v>
+      </c>
+      <c r="V54" t="s">
+        <v>177</v>
+      </c>
+      <c r="W54" t="s">
+        <v>71</v>
+      </c>
+      <c r="X54" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z54" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
+    <row r="55" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
         <v>154</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" t="s">
         <v>13</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D55" t="s">
         <v>14</v>
       </c>
-      <c r="E54">
+      <c r="E55">
         <v>2016</v>
       </c>
-      <c r="F54">
+      <c r="F55">
         <v>0.01</v>
       </c>
-      <c r="G54">
+      <c r="G55">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H55" s="2">
         <f>$O$48</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I54" s="3">
-        <f>($N$48/100)*H54</f>
+      <c r="I55" s="3">
+        <f>($N$48/100)*H55</f>
         <v>162.96753257730003</v>
       </c>
-      <c r="J54">
+      <c r="J55">
         <f>$Q$48</f>
         <v>2.8138000000000001</v>
       </c>
-      <c r="K54">
-        <v>40</v>
-      </c>
-      <c r="T54" t="s">
-        <v>69</v>
-      </c>
-      <c r="U54" t="s">
-        <v>176</v>
-      </c>
-      <c r="V54" t="s">
-        <v>177</v>
-      </c>
-      <c r="W54" t="s">
-        <v>71</v>
-      </c>
-      <c r="X54" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>156</v>
-      </c>
-      <c r="C55" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55">
-        <v>2017</v>
-      </c>
-      <c r="F55">
-        <v>0.01</v>
-      </c>
-      <c r="G55">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H55" s="2">
-        <f t="shared" ref="H55:H57" si="5">$O$48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I55" s="3">
-        <f t="shared" ref="I55:I58" si="6">($N$48/100)*H55</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J55">
-        <f t="shared" ref="J55:J57" si="7">$Q$48</f>
-        <v>2.8138000000000001</v>
-      </c>
       <c r="K55">
         <v>40</v>
       </c>
@@ -5312,7 +5300,7 @@
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -5321,24 +5309,24 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="F56">
-        <v>9.300000000000001E-3</v>
+        <v>0.01</v>
       </c>
       <c r="G56">
         <v>0.28999999999999998</v>
       </c>
       <c r="H56" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="H56:H58" si="5">$O$48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I56" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I56:I58" si="6">($N$48/100)*H56</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J56">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J56:J58" si="7">$Q$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K56">
@@ -5368,7 +5356,7 @@
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
@@ -5377,10 +5365,10 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>1963</v>
+        <v>2019</v>
       </c>
       <c r="F57">
-        <v>7.0999999999999995E-3</v>
+        <v>9.300000000000001E-3</v>
       </c>
       <c r="G57">
         <v>0.28999999999999998</v>
@@ -5398,7 +5386,7 @@
         <v>2.8138000000000001</v>
       </c>
       <c r="K57">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="T57" t="s">
         <v>69</v>
@@ -5424,262 +5412,262 @@
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D58" t="s">
         <v>14</v>
       </c>
       <c r="E58">
+        <v>1963</v>
+      </c>
+      <c r="F58">
+        <v>7.0999999999999995E-3</v>
+      </c>
+      <c r="G58">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="5"/>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I58" s="3">
+        <f t="shared" si="6"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="7"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K58">
+        <v>72</v>
+      </c>
+      <c r="T58" t="s">
+        <v>69</v>
+      </c>
+      <c r="U58" t="s">
+        <v>184</v>
+      </c>
+      <c r="V58" t="s">
+        <v>185</v>
+      </c>
+      <c r="W58" t="s">
+        <v>71</v>
+      </c>
+      <c r="X58" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59">
         <v>2020</v>
       </c>
-      <c r="F58">
+      <c r="F59">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="G58">
+      <c r="G59">
         <f>P45</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H59" s="2">
         <f>O45</f>
         <v>1175.5066999999999</v>
       </c>
-      <c r="I58" s="3">
-        <f>($N$45/100)*H58</f>
+      <c r="I59" s="3">
+        <f>($N$45/100)*H59</f>
         <v>39.138495576499992</v>
       </c>
-      <c r="J58">
+      <c r="J59">
         <f>$Q$45</f>
         <v>5.8775000000000004</v>
       </c>
-      <c r="K58">
+      <c r="K59">
         <v>40</v>
       </c>
-      <c r="T58" t="s">
-        <v>69</v>
-      </c>
-      <c r="U58" t="s">
-        <v>184</v>
-      </c>
-      <c r="V58" t="s">
-        <v>185</v>
-      </c>
-      <c r="W58" t="s">
-        <v>71</v>
-      </c>
-      <c r="X58" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y58" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z58" t="s">
+      <c r="T59" t="s">
+        <v>69</v>
+      </c>
+      <c r="U59" t="s">
+        <v>186</v>
+      </c>
+      <c r="V59" t="s">
+        <v>188</v>
+      </c>
+      <c r="W59" t="s">
+        <v>71</v>
+      </c>
+      <c r="X59" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z59" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
+    <row r="60" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
         <v>164</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C60" t="s">
         <v>13</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D60" t="s">
         <v>14</v>
       </c>
-      <c r="E59">
+      <c r="E60">
         <v>2013</v>
       </c>
-      <c r="F59">
+      <c r="F60">
         <v>6.4999999999999997E-3</v>
       </c>
-      <c r="G59">
+      <c r="G60">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H60" s="2">
         <f>O48</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I59" s="3">
-        <f>($N$48/100)*H59</f>
+      <c r="I60" s="3">
+        <f>($N$48/100)*H60</f>
         <v>162.96753257730003</v>
       </c>
-      <c r="J59">
+      <c r="J60">
         <f>$Q$48</f>
         <v>2.8138000000000001</v>
       </c>
-      <c r="K59">
+      <c r="K60">
         <v>40</v>
       </c>
-      <c r="T59" t="s">
-        <v>69</v>
-      </c>
-      <c r="U59" t="s">
-        <v>186</v>
-      </c>
-      <c r="V59" t="s">
-        <v>188</v>
-      </c>
-      <c r="W59" t="s">
-        <v>71</v>
-      </c>
-      <c r="X59" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z59" t="s">
+      <c r="T60" t="s">
+        <v>69</v>
+      </c>
+      <c r="U60" t="s">
+        <v>187</v>
+      </c>
+      <c r="V60" t="s">
+        <v>189</v>
+      </c>
+      <c r="W60" t="s">
+        <v>71</v>
+      </c>
+      <c r="X60" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z60" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="60" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
+    <row r="61" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
         <v>168</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C61" t="s">
         <v>16</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D61" t="s">
         <v>14</v>
       </c>
-      <c r="E60">
+      <c r="E61">
         <v>2015</v>
       </c>
-      <c r="F60">
+      <c r="F61">
         <v>4.0999999999999995E-3</v>
       </c>
-      <c r="G60">
+      <c r="G61">
         <f>P45</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H61" s="2">
         <f>O45</f>
         <v>1175.5066999999999</v>
       </c>
-      <c r="I60" s="3">
-        <f>($N$45/100)*H60</f>
+      <c r="I61" s="3">
+        <f>($N$45/100)*H61</f>
         <v>39.138495576499992</v>
       </c>
-      <c r="J60">
+      <c r="J61">
         <f>$Q$45</f>
         <v>5.8775000000000004</v>
       </c>
-      <c r="K60">
+      <c r="K61">
         <v>40</v>
       </c>
-      <c r="T60" t="s">
-        <v>69</v>
-      </c>
-      <c r="U60" t="s">
-        <v>187</v>
-      </c>
-      <c r="V60" t="s">
-        <v>189</v>
-      </c>
-      <c r="W60" t="s">
-        <v>71</v>
-      </c>
-      <c r="X60" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y60" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z60" t="s">
+      <c r="T61" t="s">
+        <v>69</v>
+      </c>
+      <c r="U61" t="s">
+        <v>190</v>
+      </c>
+      <c r="V61" t="s">
+        <v>191</v>
+      </c>
+      <c r="W61" t="s">
+        <v>71</v>
+      </c>
+      <c r="X61" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z61" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
+    <row r="62" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
         <v>198</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>192</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D62" t="s">
         <v>14</v>
       </c>
-      <c r="E61">
+      <c r="E62">
         <v>2012</v>
       </c>
-      <c r="F61">
+      <c r="F62">
         <v>1.4E-3</v>
       </c>
-      <c r="G61">
+      <c r="G62">
         <f>P44</f>
         <v>0.33</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H62" s="2">
         <f>O44</f>
         <v>4812.0244000000002</v>
       </c>
-      <c r="I61" s="3">
-        <f>($N$48/100)*H61</f>
+      <c r="I62" s="3">
+        <f>($N$48/100)*H62</f>
         <v>173.62265237640003</v>
       </c>
-      <c r="J61">
+      <c r="J62">
         <f t="shared" si="1"/>
         <v>4.1005000000000003</v>
       </c>
-      <c r="K61">
-        <v>40</v>
-      </c>
-      <c r="T61" t="s">
-        <v>69</v>
-      </c>
-      <c r="U61" t="s">
-        <v>190</v>
-      </c>
-      <c r="V61" t="s">
-        <v>191</v>
-      </c>
-      <c r="W61" t="s">
-        <v>71</v>
-      </c>
-      <c r="X61" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y61" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
-        <v>172</v>
-      </c>
-      <c r="C62" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62">
-        <v>2013</v>
-      </c>
-      <c r="F62">
-        <v>1.8E-3</v>
-      </c>
-      <c r="G62">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H62" s="2">
-        <f>O48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I62" s="3">
-        <f>($N$48/100)*H62</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J62">
-        <f>$Q$48</f>
-        <v>2.8138000000000001</v>
-      </c>
       <c r="K62">
         <v>40</v>
       </c>
@@ -5707,7 +5695,7 @@
     </row>
     <row r="63" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
@@ -5716,10 +5704,10 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="F63">
-        <v>1.6999999999999999E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G63">
         <v>0.28999999999999998</v>
@@ -5742,35 +5730,34 @@
     </row>
     <row r="64" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C64" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
       </c>
       <c r="E64">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="F64">
-        <v>1.8E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="G64">
-        <f>P45</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H64" s="2">
-        <f>O45</f>
-        <v>1175.5066999999999</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I64" s="3">
-        <f t="shared" ref="I59:I71" si="8">($N$45/100)*H64</f>
-        <v>39.138495576499992</v>
+        <f>($N$48/100)*H64</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J64">
-        <f>$Q$45</f>
-        <v>5.8775000000000004</v>
+        <f>$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K64">
         <v>40</v>
@@ -5778,7 +5765,7 @@
     </row>
     <row r="65" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C65" t="s">
         <v>16</v>
@@ -5787,7 +5774,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="F65">
         <v>1.8E-3</v>
@@ -5801,7 +5788,7 @@
         <v>1175.5066999999999</v>
       </c>
       <c r="I65" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I65:I66" si="8">($N$45/100)*H65</f>
         <v>39.138495576499992</v>
       </c>
       <c r="J65">
@@ -5814,77 +5801,78 @@
     </row>
     <row r="66" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D66" t="s">
         <v>14</v>
       </c>
       <c r="E66">
+        <v>2015</v>
+      </c>
+      <c r="F66">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G66">
+        <f>P45</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H66" s="2">
+        <f>O45</f>
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="I66" s="3">
+        <f t="shared" si="8"/>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J66">
+        <f>$Q$45</f>
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="K66">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>180</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67">
         <v>2022</v>
       </c>
-      <c r="F66">
+      <c r="F67">
         <v>1.5E-3</v>
       </c>
-      <c r="G66">
+      <c r="G67">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H67" s="2">
         <f>O48</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I66" s="3">
-        <f>($N$48/100)*H66</f>
+      <c r="I67" s="3">
+        <f>($N$48/100)*H67</f>
         <v>162.96753257730003</v>
       </c>
-      <c r="J66">
+      <c r="J67">
         <f>$Q$48</f>
         <v>2.8138000000000001</v>
       </c>
-      <c r="K66">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>182</v>
-      </c>
-      <c r="C67" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67">
-        <v>2013</v>
-      </c>
-      <c r="F67">
-        <v>1.4E-3</v>
-      </c>
-      <c r="G67">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H67" s="2">
-        <f>$O$48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I67" s="3">
-        <f t="shared" ref="I67:I71" si="9">($N$48/100)*H67</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J67">
-        <f t="shared" ref="J67:J71" si="10">$Q$48</f>
-        <v>2.8138000000000001</v>
-      </c>
       <c r="K67">
         <v>40</v>
       </c>
     </row>
     <row r="68" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C68" t="s">
         <v>13</v>
@@ -5893,10 +5881,10 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="F68">
-        <v>1.1999999999999999E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G68">
         <v>0.28999999999999998</v>
@@ -5906,11 +5894,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I68" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="I68:I72" si="9">($N$48/100)*H68</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J68">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="J68:J72" si="10">$Q$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K68">
@@ -5922,7 +5910,7 @@
     </row>
     <row r="69" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
@@ -5931,16 +5919,16 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="F69">
-        <v>1.9E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G69">
         <v>0.28999999999999998</v>
       </c>
       <c r="H69" s="2">
-        <f>O48</f>
+        <f>$O$48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I69" s="3">
@@ -5957,7 +5945,7 @@
     </row>
     <row r="70" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
@@ -5966,10 +5954,10 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="F70">
-        <v>8.9999999999999998E-4</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G70">
         <v>0.28999999999999998</v>
@@ -5992,7 +5980,7 @@
     </row>
     <row r="71" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C71" t="s">
         <v>13</v>
@@ -6001,10 +5989,10 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="F71">
-        <v>5.0000000000000001E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="G71">
         <v>0.28999999999999998</v>
@@ -6027,74 +6015,89 @@
     </row>
     <row r="72" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="C72" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D72" t="s">
         <v>14</v>
       </c>
       <c r="E72">
+        <v>2015</v>
+      </c>
+      <c r="F72">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="G72">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H72" s="2">
+        <f>O48</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I72" s="3">
+        <f t="shared" si="9"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="10"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K72">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73">
         <v>2022</v>
       </c>
-      <c r="F72">
+      <c r="F73">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G72">
+      <c r="G73">
         <v>0.33123000000000002</v>
-      </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>20</v>
-      </c>
-      <c r="C76" t="s">
-        <v>21</v>
-      </c>
-      <c r="D76" t="s">
-        <v>14</v>
-      </c>
-      <c r="E76">
-        <v>2013</v>
-      </c>
-      <c r="F76">
-        <v>0.25109999999999999</v>
-      </c>
-      <c r="G76">
-        <v>0.36049999999999999</v>
-      </c>
-      <c r="H76">
-        <v>1265</v>
-      </c>
-      <c r="I76" s="3">
-        <v>48.400000000000006</v>
-      </c>
-      <c r="J76">
-        <v>7.5075000000000003</v>
-      </c>
-      <c r="K76">
-        <v>42</v>
       </c>
     </row>
     <row r="77" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D77" t="s">
         <v>14</v>
       </c>
       <c r="E77">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="F77">
-        <v>0.21299999999999999</v>
+        <v>0.25109999999999999</v>
       </c>
       <c r="G77">
-        <v>0.33123000000000002</v>
+        <v>0.36049999999999999</v>
+      </c>
+      <c r="H77">
+        <v>1265</v>
+      </c>
+      <c r="I77" s="3">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="J77">
+        <v>7.5075000000000003</v>
+      </c>
+      <c r="K77">
+        <v>42</v>
       </c>
       <c r="T77" t="s">
         <v>69</v>
@@ -6119,6 +6122,24 @@
       </c>
     </row>
     <row r="78" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78">
+        <v>2022</v>
+      </c>
+      <c r="F78">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="G78">
+        <v>0.33123000000000002</v>
+      </c>
       <c r="T78" t="s">
         <v>69</v>
       </c>
@@ -6141,39 +6162,37 @@
         <v>74</v>
       </c>
     </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
         <v>12</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C80" t="s">
         <v>13</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D80" t="s">
         <v>14</v>
       </c>
-      <c r="E79">
+      <c r="E80">
         <v>2022</v>
       </c>
-      <c r="F79">
+      <c r="F80">
         <v>0.3</v>
       </c>
-      <c r="G79">
+      <c r="G80">
         <v>0.33990000000000004</v>
       </c>
-      <c r="H79">
+      <c r="H80">
         <v>4427.5</v>
       </c>
-      <c r="I79" s="3">
+      <c r="I80" s="3">
         <v>157.30000000000001</v>
       </c>
-      <c r="J79">
+      <c r="J80">
         <v>9.24</v>
       </c>
-      <c r="K79">
+      <c r="K80">
         <v>50</v>
       </c>
-    </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.25">
       <c r="T80" t="s">
         <v>69</v>
       </c>
@@ -6205,7 +6224,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="I58 I60" formula="1"/>
+    <ignoredError sqref="I59 I61" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FEB176-2FE1-43D5-9914-074449323CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3180BC-3EF9-4EFA-A053-EA4C7D8D5475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10340" yWindow="11740" windowWidth="19180" windowHeight="11260" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -68,11 +68,11 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={D3B26940-5207-4925-84BA-C36AB3766D74}</author>
-    <author>tc={C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}</author>
     <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
     <author>tc={5D0B02A9-24B3-4F36-8683-2AD26D1E0821}</author>
+    <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
+    <author>tc={C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}</author>
     <author>tc={C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}</author>
-    <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
     <author>tc={1905391B-2A5F-4643-B2AC-720AD8410CDA}</author>
     <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
   </authors>
@@ -85,7 +85,32 @@
     Miks daynite (hydro samuti)</t>
       </text>
     </comment>
-    <comment ref="N43" authorId="1" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Iru produces only 17 MW in 2025 not 0.207 GW</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    TODO: set their actual start date and then add how much they produce in 2025</t>
+      </text>
+    </comment>
+    <comment ref="E39" authorId="3" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Ei tea
+</t>
+      </text>
+    </comment>
+    <comment ref="N43" authorId="4" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -94,23 +119,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="F44" authorId="2" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Iru produces only 17 MW in 2025 not 0.207 GW</t>
-      </text>
-    </comment>
-    <comment ref="B45" authorId="3" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    TODO: set their actual start date and then add how much they produce in 2025</t>
-      </text>
-    </comment>
-    <comment ref="Q47" authorId="4" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+    <comment ref="Q47" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -118,16 +127,7 @@
     Took same as chp</t>
       </text>
     </comment>
-    <comment ref="E53" authorId="5" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Ei tea
-</t>
-      </text>
-    </comment>
-    <comment ref="T77" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <comment ref="T79" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -135,7 +135,7 @@
     Frequency reserve</t>
       </text>
     </comment>
-    <comment ref="J80" authorId="7" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <comment ref="J85" authorId="7" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="219">
   <si>
     <t>~fi_t</t>
   </si>
@@ -796,6 +796,15 @@
   </si>
   <si>
     <t>vom (€/MWh_e)</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_sopipurtse</t>
+  </si>
+  <si>
+    <t>ep_windon_agg</t>
+  </si>
+  <si>
+    <t>Aggregated Plant of windon except sopi plants</t>
   </si>
 </sst>
 </file>
@@ -1202,27 +1211,27 @@
   <threadedComment ref="Y11" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
     <text>Miks daynite (hydro samuti)</text>
   </threadedComment>
+  <threadedComment ref="F30" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
+  </threadedComment>
+  <threadedComment ref="B31" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+    <text>TODO: set their actual start date and then add how much they produce in 2025</text>
+  </threadedComment>
+  <threadedComment ref="E39" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
+    <text xml:space="preserve">Ei tea
+</text>
+  </threadedComment>
   <threadedComment ref="N43" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
     <text xml:space="preserve">NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)
 </text>
   </threadedComment>
-  <threadedComment ref="F44" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
-    <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
-  </threadedComment>
-  <threadedComment ref="B45" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
-    <text>TODO: set their actual start date and then add how much they produce in 2025</text>
-  </threadedComment>
   <threadedComment ref="Q47" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
     <text>Took same as chp</text>
   </threadedComment>
-  <threadedComment ref="E53" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
-    <text xml:space="preserve">Ei tea
-</text>
-  </threadedComment>
-  <threadedComment ref="T77" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+  <threadedComment ref="T79" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
   </threadedComment>
-  <threadedComment ref="J80" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+  <threadedComment ref="J85" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
     <text>From 9,24 to 6</text>
   </threadedComment>
 </ThreadedComments>
@@ -2713,7 +2722,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:Z90"/>
+  <dimension ref="B9:Z105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
@@ -3530,10 +3539,10 @@
         <v>69</v>
       </c>
       <c r="U24" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="V24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W24" t="s">
         <v>71</v>
@@ -3586,10 +3595,10 @@
         <v>69</v>
       </c>
       <c r="U25" t="s">
-        <v>47</v>
+        <v>216</v>
       </c>
       <c r="V25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W25" t="s">
         <v>71</v>
@@ -3606,34 +3615,46 @@
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
         <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E26">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F26">
-        <v>1.5040605442498314E-2</v>
+        <v>7.9699999999999993E-2</v>
       </c>
       <c r="G26">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>2024</v>
+      </c>
+      <c r="I26" s="3">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="J26">
+        <v>2.3100000000000005</v>
+      </c>
+      <c r="K26">
+        <v>31</v>
       </c>
       <c r="L26">
-        <v>0.42012333946150526</v>
+        <v>0.365520596150406</v>
       </c>
       <c r="T26" t="s">
         <v>69</v>
       </c>
       <c r="U26" t="s">
-        <v>49</v>
+        <v>217</v>
       </c>
       <c r="V26" t="s">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="W26" t="s">
         <v>71</v>
@@ -3645,87 +3666,96 @@
         <v>80</v>
       </c>
       <c r="Z26" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>47</v>
+        <v>216</v>
       </c>
       <c r="C27" t="s">
         <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E27">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F27">
-        <v>1.5497656626156837E-2</v>
+        <v>0.17519999999999999</v>
       </c>
       <c r="G27">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>2024</v>
+      </c>
+      <c r="I27" s="3">
+        <v>48.4</v>
+      </c>
+      <c r="J27">
+        <v>2.3100000000000005</v>
+      </c>
+      <c r="K27">
+        <v>30</v>
       </c>
       <c r="L27">
-        <v>0.42012333946150526</v>
+        <v>0.365520596150406</v>
       </c>
       <c r="M27">
-        <f>F26*L26*G26</f>
+        <f>F90*L90*G90</f>
         <v>2.0930123559331545E-3</v>
       </c>
       <c r="T27" t="s">
-        <v>69</v>
-      </c>
-      <c r="U27" t="s">
-        <v>51</v>
-      </c>
-      <c r="V27" t="s">
-        <v>78</v>
-      </c>
-      <c r="W27" t="s">
-        <v>71</v>
-      </c>
-      <c r="X27" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>74</v>
+        <v>140</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>49</v>
+        <v>217</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
       </c>
       <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28">
+        <v>2015</v>
+      </c>
+      <c r="F28">
+        <v>0.439</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>2376</v>
+      </c>
+      <c r="I28" s="3">
+        <v>57.20000000000001</v>
+      </c>
+      <c r="J28">
+        <v>2.52</v>
+      </c>
+      <c r="K28">
         <v>50</v>
       </c>
-      <c r="E28">
-        <v>2022</v>
-      </c>
-      <c r="F28">
-        <v>1.4461737931344828E-2</v>
-      </c>
-      <c r="G28">
-        <v>0.33123000000000002</v>
-      </c>
       <c r="L28">
-        <v>0.42012333946150526</v>
+        <v>0.41047488326249421</v>
       </c>
       <c r="T28" t="s">
         <v>69</v>
       </c>
       <c r="U28" t="s">
-        <v>53</v>
+        <v>194</v>
       </c>
       <c r="V28" t="s">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="W28" t="s">
         <v>71</v>
@@ -3742,46 +3772,23 @@
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29">
-        <v>2009</v>
-      </c>
-      <c r="F29">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>2376</v>
-      </c>
-      <c r="I29" s="3">
-        <v>57.2</v>
-      </c>
-      <c r="J29">
-        <v>2.52</v>
-      </c>
-      <c r="K29">
-        <v>46</v>
-      </c>
-      <c r="L29">
-        <v>0.47763777043344691</v>
+        <v>140</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="P29">
+        <f>SUM(F26:F28)+0.31</f>
+        <v>1.0039</v>
       </c>
       <c r="T29" t="s">
         <v>69</v>
       </c>
       <c r="U29" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="V29" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="W29" t="s">
         <v>71</v>
@@ -3798,46 +3805,46 @@
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30">
+        <v>1982</v>
+      </c>
+      <c r="F30">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="G30">
+        <f>P45</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H30" s="2">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="I30" s="3">
+        <f>(N45/100)*H31</f>
+        <v>160.216352398</v>
+      </c>
+      <c r="J30">
+        <f>Q45</f>
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="K30">
         <v>53</v>
       </c>
-      <c r="C30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30">
-        <v>2010</v>
-      </c>
-      <c r="F30">
-        <v>1.6E-2</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30">
-        <v>2376</v>
-      </c>
-      <c r="I30" s="3">
-        <v>57.2</v>
-      </c>
-      <c r="J30">
-        <v>2.52</v>
-      </c>
-      <c r="K30">
-        <v>45</v>
-      </c>
-      <c r="L30">
-        <v>0.47814004703314078</v>
-      </c>
       <c r="T30" t="s">
         <v>69</v>
       </c>
       <c r="U30" t="s">
-        <v>57</v>
+        <v>195</v>
       </c>
       <c r="V30" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="W30" t="s">
         <v>71</v>
@@ -3854,46 +3861,46 @@
     </row>
     <row r="31" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>2015</v>
+        <v>1965</v>
       </c>
       <c r="F31">
-        <v>1.7999999999999999E-2</v>
+        <v>0.77</v>
       </c>
       <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31">
-        <v>2376</v>
+        <f>$P$44</f>
+        <v>0.33</v>
+      </c>
+      <c r="H31" s="2">
+        <v>4812.0244000000002</v>
       </c>
       <c r="I31" s="3">
-        <v>57.20000000000001</v>
+        <f>(1.31/100)*H31</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J31">
-        <v>2.52</v>
+        <f>$Q$44</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K31">
-        <v>40</v>
-      </c>
-      <c r="L31">
-        <v>0.47814004703314084</v>
+        <v>70</v>
       </c>
       <c r="T31" t="s">
         <v>69</v>
       </c>
       <c r="U31" t="s">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="V31" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="W31" t="s">
         <v>71</v>
@@ -3910,46 +3917,46 @@
     </row>
     <row r="32" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>53</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="D32" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="E32">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="F32">
-        <v>1.2E-2</v>
+        <v>0.26</v>
       </c>
       <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="H32">
-        <v>2376</v>
+        <f t="shared" ref="G32:G34" si="0">$P$44</f>
+        <v>0.33</v>
+      </c>
+      <c r="H32" s="2">
+        <v>4812.0244000000002</v>
       </c>
       <c r="I32" s="3">
-        <v>57.20000000000001</v>
+        <f>(1.31/100)*H32</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J32">
-        <v>2.52</v>
+        <f t="shared" ref="J32:J48" si="1">$Q$44</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K32">
-        <v>35</v>
-      </c>
-      <c r="L32">
-        <v>0.47814004703314078</v>
+        <v>40</v>
       </c>
       <c r="T32" t="s">
         <v>69</v>
       </c>
       <c r="U32" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="V32" t="s">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="W32" t="s">
         <v>71</v>
@@ -3966,87 +3973,102 @@
     </row>
     <row r="33" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E33">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="F33">
-        <v>2.1000000000000001E-2</v>
+        <f>0.01</f>
+        <v>0.01</v>
       </c>
       <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33">
-        <v>2376</v>
+        <v>0.33</v>
+      </c>
+      <c r="H33" s="2">
+        <v>4812.0244000000002</v>
       </c>
       <c r="I33" s="3">
-        <v>57.2</v>
+        <f>(1.31/100)*H33</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J33">
-        <v>2.52</v>
+        <f>$Q$44</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K33">
-        <v>48</v>
-      </c>
-      <c r="L33">
-        <v>0.40144059976798208</v>
+        <v>40</v>
       </c>
       <c r="T33" t="s">
-        <v>140</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>141</v>
+        <v>69</v>
+      </c>
+      <c r="U33" t="s">
+        <v>143</v>
+      </c>
+      <c r="V33" t="s">
+        <v>151</v>
+      </c>
+      <c r="W33" t="s">
+        <v>71</v>
+      </c>
+      <c r="X33" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="D34" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E34">
-        <v>2011</v>
+        <v>1956</v>
       </c>
       <c r="F34">
-        <v>2.4E-2</v>
+        <v>0.185</v>
       </c>
       <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="H34">
-        <v>2376</v>
+        <f t="shared" si="0"/>
+        <v>0.33</v>
+      </c>
+      <c r="H34" s="2">
+        <v>4812.0244000000002</v>
       </c>
       <c r="I34" s="3">
-        <v>57.20000000000001</v>
+        <f>(1.31/100)*H34</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J34">
-        <v>2.52</v>
+        <f t="shared" si="1"/>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K34">
-        <v>44</v>
-      </c>
-      <c r="L34">
-        <v>0.40144059976798202</v>
+        <v>73</v>
       </c>
       <c r="T34" t="s">
         <v>69</v>
       </c>
       <c r="U34" t="s">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="V34" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="W34" t="s">
         <v>71</v>
@@ -4063,46 +4085,47 @@
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E35">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="F35">
-        <v>7.9000000000000001E-2</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G35">
-        <v>1</v>
-      </c>
-      <c r="H35">
-        <v>2376</v>
+        <f>P45</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H35" s="2">
+        <f>O45</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I35" s="3">
-        <v>57.2</v>
+        <f>(N45/100)*H35</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J35">
-        <v>2.52</v>
+        <f>$Q$45</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K35">
-        <v>43</v>
-      </c>
-      <c r="L35">
-        <v>0.40144059976798202</v>
+        <v>40</v>
       </c>
       <c r="T35" t="s">
         <v>69</v>
       </c>
       <c r="U35" t="s">
-        <v>193</v>
+        <v>145</v>
       </c>
       <c r="V35" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="W35" t="s">
         <v>71</v>
@@ -4119,46 +4142,47 @@
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E36">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="F36">
-        <v>2.1000000000000001E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>2376</v>
+        <f>P47</f>
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="H36" s="2">
+        <f>$O$47</f>
+        <v>2950.7891</v>
       </c>
       <c r="I36" s="3">
-        <v>57.2</v>
+        <f>(4.5269/100)*H36</f>
+        <v>133.5792717679</v>
       </c>
       <c r="J36">
-        <v>2.52</v>
+        <f>$Q$47</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K36">
-        <v>32</v>
-      </c>
-      <c r="L36">
-        <v>0.40144059976798208</v>
+        <v>40</v>
       </c>
       <c r="T36" t="s">
         <v>69</v>
       </c>
       <c r="U36" t="s">
-        <v>195</v>
+        <v>146</v>
       </c>
       <c r="V36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="W36" t="s">
         <v>71</v>
@@ -4175,46 +4199,46 @@
     </row>
     <row r="37" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="C37" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E37">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="F37">
-        <v>0.10199999999999999</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="G37">
-        <v>1</v>
-      </c>
-      <c r="H37">
-        <v>2024</v>
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="H37" s="2">
+        <f t="shared" ref="H37:H39" si="2">$O$47</f>
+        <v>2950.7891</v>
       </c>
       <c r="I37" s="3">
-        <v>48.4</v>
+        <f t="shared" ref="I37:I39" si="3">(4.5269/100)*H37</f>
+        <v>133.5792717679</v>
       </c>
       <c r="J37">
-        <v>2.3100000000000005</v>
+        <f t="shared" ref="J37:J39" si="4">$Q$47</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K37">
-        <v>31</v>
-      </c>
-      <c r="L37">
-        <v>0.40144059976798202</v>
+        <v>40</v>
       </c>
       <c r="T37" t="s">
         <v>69</v>
       </c>
       <c r="U37" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V37" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="W37" t="s">
         <v>71</v>
@@ -4231,46 +4255,46 @@
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>2023</v>
+        <v>2011</v>
       </c>
       <c r="F38">
-        <v>3.9E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="G38">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <v>2376</v>
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="H38" s="2">
+        <f t="shared" si="2"/>
+        <v>2950.7891</v>
       </c>
       <c r="I38" s="3">
-        <v>57.2</v>
+        <f t="shared" si="3"/>
+        <v>133.5792717679</v>
       </c>
       <c r="J38">
-        <v>2.52</v>
+        <f t="shared" si="4"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K38">
-        <v>32</v>
-      </c>
-      <c r="L38">
-        <v>0.365520596150406</v>
+        <v>40</v>
       </c>
       <c r="T38" t="s">
         <v>69</v>
       </c>
       <c r="U38" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="V38" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="W38" t="s">
         <v>71</v>
@@ -4287,46 +4311,46 @@
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="E39">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="F39">
-        <v>1.7999999999999999E-2</v>
+        <v>1.3900000000000001E-2</v>
       </c>
       <c r="G39">
-        <v>1</v>
-      </c>
-      <c r="H39">
-        <v>2376</v>
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="H39" s="2">
+        <f t="shared" si="2"/>
+        <v>2950.7891</v>
       </c>
       <c r="I39" s="3">
-        <v>57.20000000000001</v>
+        <f t="shared" si="3"/>
+        <v>133.5792717679</v>
       </c>
       <c r="J39">
-        <v>2.52</v>
+        <f t="shared" si="4"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K39">
-        <v>50</v>
-      </c>
-      <c r="L39">
-        <v>0.41047488326249421</v>
+        <v>40</v>
       </c>
       <c r="T39" t="s">
         <v>69</v>
       </c>
       <c r="U39" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="V39" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="W39" t="s">
         <v>71</v>
@@ -4343,46 +4367,47 @@
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>59</v>
+        <v>197</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="E40">
-        <v>2012</v>
+        <v>1997</v>
       </c>
       <c r="F40">
-        <v>2.1999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G40">
-        <v>1</v>
-      </c>
-      <c r="H40">
-        <v>2376</v>
+        <f>P44</f>
+        <v>0.33</v>
+      </c>
+      <c r="H40" s="2">
+        <f>O44</f>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I40" s="3">
-        <v>57.2</v>
+        <f>($N$44/100)*H40</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J40">
-        <v>2.52</v>
+        <f>$Q$44</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K40">
-        <v>43</v>
-      </c>
-      <c r="L40">
-        <v>0.41047488326249421</v>
+        <v>40</v>
       </c>
       <c r="T40" t="s">
         <v>69</v>
       </c>
       <c r="U40" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="V40" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="W40" t="s">
         <v>71</v>
@@ -4399,46 +4424,46 @@
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="E41">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="F41">
-        <v>2.1999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G41">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <v>2376</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H41" s="2">
+        <f>$O$48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I41" s="3">
-        <v>57.2</v>
+        <f>($N$48/100)*H41</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J41">
-        <v>2.52</v>
+        <f>$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K41">
-        <v>42</v>
-      </c>
-      <c r="L41">
-        <v>0.41047488326249421</v>
+        <v>40</v>
       </c>
       <c r="T41" t="s">
         <v>69</v>
       </c>
       <c r="U41" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="V41" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="W41" t="s">
         <v>71</v>
@@ -4455,46 +4480,46 @@
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="E42">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="F42">
-        <v>0.255</v>
+        <v>0.01</v>
       </c>
       <c r="G42">
-        <v>1</v>
-      </c>
-      <c r="H42">
-        <v>2024</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H42" s="2">
+        <f t="shared" ref="H42:H44" si="5">$O$48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I42" s="3">
-        <v>48.400000000000006</v>
+        <f t="shared" ref="I42:I44" si="6">($N$48/100)*H42</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J42">
-        <v>2.3100000000000005</v>
+        <f t="shared" ref="J42:J44" si="7">$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K42">
-        <v>31</v>
-      </c>
-      <c r="L42">
-        <v>0.365520596150406</v>
+        <v>40</v>
       </c>
       <c r="T42" t="s">
         <v>69</v>
       </c>
       <c r="U42" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="V42" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="W42" t="s">
         <v>71</v>
@@ -4511,10 +4536,37 @@
     </row>
     <row r="43" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>140</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>141</v>
+        <v>170</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43">
+        <v>2019</v>
+      </c>
+      <c r="F43">
+        <v>9.300000000000001E-3</v>
+      </c>
+      <c r="G43">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H43" s="2">
+        <f t="shared" si="5"/>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="6"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="7"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K43">
+        <v>40</v>
       </c>
       <c r="N43" t="s">
         <v>206</v>
@@ -4532,10 +4584,10 @@
         <v>69</v>
       </c>
       <c r="U43" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="V43" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="W43" t="s">
         <v>71</v>
@@ -4552,108 +4604,109 @@
     </row>
     <row r="44" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
         <v>14</v>
       </c>
       <c r="E44">
-        <v>1982</v>
+        <v>1963</v>
       </c>
       <c r="F44">
-        <v>1.7000000000000001E-2</v>
+        <v>7.0999999999999995E-3</v>
       </c>
       <c r="G44">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H44" s="2">
+        <f t="shared" si="5"/>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I44" s="3">
+        <f t="shared" si="6"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="7"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K44">
+        <v>72</v>
+      </c>
+      <c r="M44" t="s">
+        <v>192</v>
+      </c>
+      <c r="N44" s="4">
+        <v>1.31</v>
+      </c>
+      <c r="O44" s="2">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="P44">
+        <v>0.33</v>
+      </c>
+      <c r="Q44">
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="T44" t="s">
+        <v>69</v>
+      </c>
+      <c r="U44" t="s">
+        <v>168</v>
+      </c>
+      <c r="V44" t="s">
+        <v>166</v>
+      </c>
+      <c r="W44" t="s">
+        <v>71</v>
+      </c>
+      <c r="X44" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>169</v>
+      </c>
+      <c r="C45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45">
+        <v>2020</v>
+      </c>
+      <c r="F45">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="G45">
         <f>P45</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H45" s="2">
+        <f>O45</f>
         <v>1175.5066999999999</v>
       </c>
-      <c r="I44" s="3">
-        <f>(N45/100)*H45</f>
-        <v>160.216352398</v>
-      </c>
-      <c r="J44">
-        <f>Q45</f>
+      <c r="I45" s="3">
+        <f>($N$45/100)*H45</f>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J45">
+        <f>$Q$45</f>
         <v>5.8775000000000004</v>
       </c>
-      <c r="K44">
-        <v>53</v>
-      </c>
-      <c r="M44" t="s">
-        <v>192</v>
-      </c>
-      <c r="N44" s="4">
-        <v>1.31</v>
-      </c>
-      <c r="O44" s="2">
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="P44">
-        <v>0.33</v>
-      </c>
-      <c r="Q44">
-        <v>4.1005000000000003</v>
-      </c>
-      <c r="T44" t="s">
-        <v>69</v>
-      </c>
-      <c r="U44" t="s">
-        <v>154</v>
-      </c>
-      <c r="V44" t="s">
-        <v>155</v>
-      </c>
-      <c r="W44" t="s">
-        <v>71</v>
-      </c>
-      <c r="X44" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" t="s">
-        <v>192</v>
-      </c>
-      <c r="D45" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45">
-        <v>1965</v>
-      </c>
-      <c r="F45">
-        <v>0.77</v>
-      </c>
-      <c r="G45">
-        <f>$P$44</f>
-        <v>0.33</v>
-      </c>
-      <c r="H45" s="2">
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="I45" s="3">
-        <f>(1.31/100)*H45</f>
-        <v>63.037519640000006</v>
-      </c>
-      <c r="J45">
-        <f>$Q$44</f>
-        <v>4.1005000000000003</v>
-      </c>
       <c r="K45">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="M45" t="s">
         <v>211</v>
@@ -4674,10 +4727,10 @@
         <v>69</v>
       </c>
       <c r="U45" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="V45" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="W45" t="s">
         <v>71</v>
@@ -4694,34 +4747,34 @@
     </row>
     <row r="46" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="C46" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
       </c>
       <c r="E46">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="F46">
-        <v>0.26</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="G46">
-        <f t="shared" ref="G46:G48" si="0">$P$44</f>
-        <v>0.33</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H46" s="2">
-        <v>4812.0244000000002</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I46" s="3">
-        <f>(1.31/100)*H46</f>
-        <v>63.037519640000006</v>
+        <f>($N$48/100)*H46</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J46">
-        <f t="shared" ref="J46:J62" si="1">$Q$44</f>
-        <v>4.1005000000000003</v>
+        <f>$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K46">
         <v>40</v>
@@ -4735,10 +4788,10 @@
         <v>69</v>
       </c>
       <c r="U46" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="V46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="W46" t="s">
         <v>71</v>
@@ -4755,34 +4808,35 @@
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="C47" t="s">
-        <v>192</v>
+        <v>16</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
       </c>
       <c r="E47">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="F47">
-        <f>0.01</f>
-        <v>0.01</v>
+        <v>4.0999999999999995E-3</v>
       </c>
       <c r="G47">
-        <v>0.33</v>
+        <f>P45</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H47" s="2">
-        <v>4812.0244000000002</v>
+        <f>O45</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I47" s="3">
-        <f>(1.31/100)*H47</f>
-        <v>63.037519640000006</v>
+        <f>($N$45/100)*H47</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J47">
-        <f>$Q$44</f>
-        <v>4.1005000000000003</v>
+        <f>$Q$45</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K47">
         <v>40</v>
@@ -4806,10 +4860,10 @@
         <v>69</v>
       </c>
       <c r="U47" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="V47" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="W47" t="s">
         <v>71</v>
@@ -4826,7 +4880,7 @@
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C48" t="s">
         <v>192</v>
@@ -4835,28 +4889,29 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>1956</v>
+        <v>2012</v>
       </c>
       <c r="F48">
-        <v>0.185</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G48">
-        <f t="shared" si="0"/>
+        <f>P44</f>
         <v>0.33</v>
       </c>
       <c r="H48" s="2">
+        <f>O44</f>
         <v>4812.0244000000002</v>
       </c>
       <c r="I48" s="3">
-        <f>(1.31/100)*H48</f>
-        <v>63.037519640000006</v>
+        <f>($N$48/100)*H48</f>
+        <v>173.62265237640003</v>
       </c>
       <c r="J48">
         <f t="shared" si="1"/>
         <v>4.1005000000000003</v>
       </c>
       <c r="K48">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="M48" t="s">
         <v>210</v>
@@ -4877,10 +4932,10 @@
         <v>69</v>
       </c>
       <c r="U48" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="V48" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="W48" t="s">
         <v>71</v>
@@ -4897,35 +4952,34 @@
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
       </c>
       <c r="E49">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="F49">
-        <v>7.6999999999999999E-2</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G49">
-        <f>P45</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H49" s="2">
-        <f>O45</f>
-        <v>1175.5066999999999</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I49" s="3">
-        <f>(N45/100)*H49</f>
-        <v>39.138495576499992</v>
+        <f>($N$48/100)*H49</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J49">
-        <f>$Q$45</f>
-        <v>5.8775000000000004</v>
+        <f>$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K49">
         <v>40</v>
@@ -4936,10 +4990,10 @@
         <v>69</v>
       </c>
       <c r="U49" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="V49" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="W49" t="s">
         <v>71</v>
@@ -4956,7 +5010,7 @@
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
@@ -4965,25 +5019,24 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="F50">
-        <v>3.9E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="G50">
-        <f>P47</f>
-        <v>0.46800000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H50" s="2">
-        <f>$O$47</f>
-        <v>2950.7891</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I50" s="3">
-        <f>(4.5269/100)*H50</f>
-        <v>133.5792717679</v>
+        <f>($N$48/100)*H50</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J50">
-        <f>$Q$47</f>
+        <f>$Q$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K50">
@@ -4995,10 +5048,10 @@
         <v>69</v>
       </c>
       <c r="U50" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="V50" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="W50" t="s">
         <v>71</v>
@@ -5015,10 +5068,10 @@
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D51" t="s">
         <v>14</v>
@@ -5027,22 +5080,23 @@
         <v>2009</v>
       </c>
       <c r="F51">
-        <v>2.2100000000000002E-2</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G51">
-        <v>0.46800000000000003</v>
+        <f>P45</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H51" s="2">
-        <f t="shared" ref="H51:H53" si="2">$O$47</f>
-        <v>2950.7891</v>
+        <f>O45</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I51" s="3">
-        <f t="shared" ref="I51:I53" si="3">(4.5269/100)*H51</f>
-        <v>133.5792717679</v>
+        <f t="shared" ref="I51:I52" si="8">($N$45/100)*H51</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J51">
-        <f t="shared" ref="J51:J53" si="4">$Q$47</f>
-        <v>2.8138000000000001</v>
+        <f>$Q$45</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K51">
         <v>40</v>
@@ -5053,10 +5107,10 @@
         <v>69</v>
       </c>
       <c r="U51" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="V51" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="W51" t="s">
         <v>71</v>
@@ -5073,34 +5127,35 @@
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D52" t="s">
         <v>14</v>
       </c>
       <c r="E52">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="F52">
-        <v>2.0500000000000001E-2</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G52">
-        <v>0.46800000000000003</v>
+        <f>P45</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H52" s="2">
-        <f t="shared" si="2"/>
-        <v>2950.7891</v>
+        <f>O45</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I52" s="3">
-        <f t="shared" si="3"/>
-        <v>133.5792717679</v>
+        <f t="shared" si="8"/>
+        <v>39.138495576499992</v>
       </c>
       <c r="J52">
-        <f t="shared" si="4"/>
-        <v>2.8138000000000001</v>
+        <f>$Q$45</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K52">
         <v>40</v>
@@ -5111,10 +5166,10 @@
         <v>69</v>
       </c>
       <c r="U52" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="V52" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="W52" t="s">
         <v>71</v>
@@ -5131,7 +5186,7 @@
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
@@ -5140,24 +5195,24 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="F53">
-        <v>1.3900000000000001E-2</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G53">
-        <v>0.46800000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H53" s="2">
-        <f t="shared" si="2"/>
-        <v>2950.7891</v>
+        <f>O48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I53" s="3">
-        <f t="shared" si="3"/>
-        <v>133.5792717679</v>
+        <f>($N$48/100)*H53</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J53">
-        <f t="shared" si="4"/>
+        <f>$Q$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K53">
@@ -5167,10 +5222,10 @@
         <v>69</v>
       </c>
       <c r="U53" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="V53" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="W53" t="s">
         <v>71</v>
@@ -5187,35 +5242,34 @@
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C54" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="D54" t="s">
         <v>14</v>
       </c>
       <c r="E54">
-        <v>1997</v>
+        <v>2013</v>
       </c>
       <c r="F54">
-        <v>0.01</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G54">
-        <f>P44</f>
-        <v>0.33</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H54" s="2">
-        <f>O44</f>
-        <v>4812.0244000000002</v>
+        <f>$O$48</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I54" s="3">
-        <f>($N$44/100)*H54</f>
-        <v>63.037519640000006</v>
+        <f t="shared" ref="I54:I58" si="9">($N$48/100)*H54</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J54">
-        <f>$Q$44</f>
-        <v>4.1005000000000003</v>
+        <f t="shared" ref="J54:J58" si="10">$Q$48</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K54">
         <v>40</v>
@@ -5224,10 +5278,10 @@
         <v>69</v>
       </c>
       <c r="U54" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="V54" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="W54" t="s">
         <v>71</v>
@@ -5244,7 +5298,7 @@
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
@@ -5256,7 +5310,7 @@
         <v>2016</v>
       </c>
       <c r="F55">
-        <v>0.01</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G55">
         <v>0.28999999999999998</v>
@@ -5266,11 +5320,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I55" s="3">
-        <f>($N$48/100)*H55</f>
+        <f t="shared" si="9"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J55">
-        <f>$Q$48</f>
+        <f t="shared" si="10"/>
         <v>2.8138000000000001</v>
       </c>
       <c r="K55">
@@ -5280,10 +5334,10 @@
         <v>69</v>
       </c>
       <c r="U55" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="V55" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="W55" t="s">
         <v>71</v>
@@ -5300,7 +5354,7 @@
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -5309,24 +5363,24 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="F56">
-        <v>0.01</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G56">
         <v>0.28999999999999998</v>
       </c>
       <c r="H56" s="2">
-        <f t="shared" ref="H56:H58" si="5">$O$48</f>
+        <f>O48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I56" s="3">
-        <f t="shared" ref="I56:I58" si="6">($N$48/100)*H56</f>
+        <f t="shared" si="9"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J56">
-        <f t="shared" ref="J56:J58" si="7">$Q$48</f>
+        <f t="shared" si="10"/>
         <v>2.8138000000000001</v>
       </c>
       <c r="K56">
@@ -5336,10 +5390,10 @@
         <v>69</v>
       </c>
       <c r="U56" t="s">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="V56" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="W56" t="s">
         <v>71</v>
@@ -5348,15 +5402,15 @@
         <v>72</v>
       </c>
       <c r="Y56" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="Z56" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
@@ -5365,54 +5419,33 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="F57">
-        <v>9.300000000000001E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="G57">
         <v>0.28999999999999998</v>
       </c>
       <c r="H57" s="2">
-        <f t="shared" si="5"/>
+        <f>O48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I57" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J57">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2.8138000000000001</v>
       </c>
       <c r="K57">
         <v>40</v>
       </c>
-      <c r="T57" t="s">
-        <v>69</v>
-      </c>
-      <c r="U57" t="s">
-        <v>182</v>
-      </c>
-      <c r="V57" t="s">
-        <v>183</v>
-      </c>
-      <c r="W57" t="s">
-        <v>71</v>
-      </c>
-      <c r="X57" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y57" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z57" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="58" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="C58" t="s">
         <v>13</v>
@@ -5421,692 +5454,182 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>1963</v>
+        <v>2015</v>
       </c>
       <c r="F58">
-        <v>7.0999999999999995E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="G58">
         <v>0.28999999999999998</v>
       </c>
       <c r="H58" s="2">
-        <f t="shared" si="5"/>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I58" s="3">
-        <f t="shared" si="6"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J58">
-        <f t="shared" si="7"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K58">
-        <v>72</v>
-      </c>
-      <c r="T58" t="s">
-        <v>69</v>
-      </c>
-      <c r="U58" t="s">
-        <v>184</v>
-      </c>
-      <c r="V58" t="s">
-        <v>185</v>
-      </c>
-      <c r="W58" t="s">
-        <v>71</v>
-      </c>
-      <c r="X58" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y58" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z58" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
-        <v>169</v>
-      </c>
-      <c r="C59" t="s">
-        <v>16</v>
-      </c>
-      <c r="D59" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59">
-        <v>2020</v>
-      </c>
-      <c r="F59">
-        <v>5.7999999999999996E-3</v>
-      </c>
-      <c r="G59">
-        <f>P45</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H59" s="2">
-        <f>O45</f>
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="I59" s="3">
-        <f>($N$45/100)*H59</f>
-        <v>39.138495576499992</v>
-      </c>
-      <c r="J59">
-        <f>$Q$45</f>
-        <v>5.8775000000000004</v>
-      </c>
-      <c r="K59">
-        <v>40</v>
-      </c>
-      <c r="T59" t="s">
-        <v>69</v>
-      </c>
-      <c r="U59" t="s">
-        <v>186</v>
-      </c>
-      <c r="V59" t="s">
-        <v>188</v>
-      </c>
-      <c r="W59" t="s">
-        <v>71</v>
-      </c>
-      <c r="X59" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z59" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>164</v>
-      </c>
-      <c r="C60" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60">
-        <v>2013</v>
-      </c>
-      <c r="F60">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="G60">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H60" s="2">
         <f>O48</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I60" s="3">
-        <f>($N$48/100)*H60</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J60">
-        <f>$Q$48</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K60">
-        <v>40</v>
-      </c>
-      <c r="T60" t="s">
-        <v>69</v>
-      </c>
-      <c r="U60" t="s">
-        <v>187</v>
-      </c>
-      <c r="V60" t="s">
-        <v>189</v>
-      </c>
-      <c r="W60" t="s">
-        <v>71</v>
-      </c>
-      <c r="X60" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y60" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z60" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="61" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>168</v>
-      </c>
-      <c r="C61" t="s">
-        <v>16</v>
-      </c>
-      <c r="D61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61">
-        <v>2015</v>
-      </c>
-      <c r="F61">
-        <v>4.0999999999999995E-3</v>
-      </c>
-      <c r="G61">
-        <f>P45</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H61" s="2">
-        <f>O45</f>
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="I61" s="3">
-        <f>($N$45/100)*H61</f>
-        <v>39.138495576499992</v>
-      </c>
-      <c r="J61">
-        <f>$Q$45</f>
-        <v>5.8775000000000004</v>
-      </c>
-      <c r="K61">
-        <v>40</v>
-      </c>
-      <c r="T61" t="s">
-        <v>69</v>
-      </c>
-      <c r="U61" t="s">
-        <v>190</v>
-      </c>
-      <c r="V61" t="s">
-        <v>191</v>
-      </c>
-      <c r="W61" t="s">
-        <v>71</v>
-      </c>
-      <c r="X61" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y61" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B62" t="s">
-        <v>198</v>
-      </c>
-      <c r="C62" t="s">
-        <v>192</v>
-      </c>
-      <c r="D62" t="s">
-        <v>14</v>
-      </c>
-      <c r="E62">
-        <v>2012</v>
-      </c>
-      <c r="F62">
-        <v>1.4E-3</v>
-      </c>
-      <c r="G62">
-        <f>P44</f>
-        <v>0.33</v>
-      </c>
-      <c r="H62" s="2">
-        <f>O44</f>
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="I62" s="3">
-        <f>($N$48/100)*H62</f>
-        <v>173.62265237640003</v>
-      </c>
-      <c r="J62">
-        <f t="shared" si="1"/>
-        <v>4.1005000000000003</v>
-      </c>
-      <c r="K62">
-        <v>40</v>
-      </c>
-      <c r="T62" t="s">
-        <v>69</v>
-      </c>
-      <c r="U62" t="s">
-        <v>18</v>
-      </c>
-      <c r="V62" t="s">
-        <v>78</v>
-      </c>
-      <c r="W62" t="s">
-        <v>71</v>
-      </c>
-      <c r="X62" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y62" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z62" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="63" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
-        <v>172</v>
-      </c>
-      <c r="C63" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63">
-        <v>2013</v>
-      </c>
-      <c r="F63">
-        <v>1.8E-3</v>
-      </c>
-      <c r="G63">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H63" s="2">
-        <f>O48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I63" s="3">
-        <f>($N$48/100)*H63</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J63">
-        <f>$Q$48</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K63">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="64" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B64" t="s">
-        <v>174</v>
-      </c>
-      <c r="C64" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64">
-        <v>2015</v>
-      </c>
-      <c r="F64">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="G64">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H64" s="2">
-        <f>O48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I64" s="3">
-        <f>($N$48/100)*H64</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J64">
-        <f>$Q$48</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K64">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
-        <v>176</v>
-      </c>
-      <c r="C65" t="s">
-        <v>16</v>
-      </c>
-      <c r="D65" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65">
-        <v>2009</v>
-      </c>
-      <c r="F65">
-        <v>1.8E-3</v>
-      </c>
-      <c r="G65">
-        <f>P45</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H65" s="2">
-        <f>O45</f>
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="I65" s="3">
-        <f t="shared" ref="I65:I66" si="8">($N$45/100)*H65</f>
-        <v>39.138495576499992</v>
-      </c>
-      <c r="J65">
-        <f>$Q$45</f>
-        <v>5.8775000000000004</v>
-      </c>
-      <c r="K65">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>178</v>
-      </c>
-      <c r="C66" t="s">
-        <v>16</v>
-      </c>
-      <c r="D66" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66">
-        <v>2015</v>
-      </c>
-      <c r="F66">
-        <v>1.8E-3</v>
-      </c>
-      <c r="G66">
-        <f>P45</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H66" s="2">
-        <f>O45</f>
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="I66" s="3">
-        <f t="shared" si="8"/>
-        <v>39.138495576499992</v>
-      </c>
-      <c r="J66">
-        <f>$Q$45</f>
-        <v>5.8775000000000004</v>
-      </c>
-      <c r="K66">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>180</v>
-      </c>
-      <c r="C67" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67">
-        <v>2022</v>
-      </c>
-      <c r="F67">
-        <v>1.5E-3</v>
-      </c>
-      <c r="G67">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H67" s="2">
-        <f>O48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I67" s="3">
-        <f>($N$48/100)*H67</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J67">
-        <f>$Q$48</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K67">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>182</v>
-      </c>
-      <c r="C68" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68">
-        <v>2013</v>
-      </c>
-      <c r="F68">
-        <v>1.4E-3</v>
-      </c>
-      <c r="G68">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H68" s="2">
-        <f>$O$48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I68" s="3">
-        <f t="shared" ref="I68:I72" si="9">($N$48/100)*H68</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J68">
-        <f t="shared" ref="J68:J72" si="10">$Q$48</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K68">
-        <v>40</v>
-      </c>
-      <c r="U68" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
-        <v>184</v>
-      </c>
-      <c r="C69" t="s">
-        <v>13</v>
-      </c>
-      <c r="D69" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69">
-        <v>2016</v>
-      </c>
-      <c r="F69">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="G69">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H69" s="2">
-        <f>$O$48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I69" s="3">
+      <c r="I58" s="3">
         <f t="shared" si="9"/>
         <v>162.96753257730003</v>
       </c>
-      <c r="J69">
+      <c r="J58">
         <f t="shared" si="10"/>
         <v>2.8138000000000001</v>
       </c>
-      <c r="K69">
+      <c r="K58">
         <v>40</v>
       </c>
     </row>
     <row r="70" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B70" t="s">
-        <v>186</v>
-      </c>
-      <c r="C70" t="s">
-        <v>13</v>
-      </c>
-      <c r="D70" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70">
-        <v>2009</v>
-      </c>
-      <c r="F70">
-        <v>1.9E-3</v>
-      </c>
-      <c r="G70">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H70" s="2">
-        <f>O48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I70" s="3">
-        <f t="shared" si="9"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J70">
-        <f t="shared" si="10"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K70">
-        <v>40</v>
+      <c r="U70" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="71" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>187</v>
-      </c>
-      <c r="C71" t="s">
-        <v>13</v>
-      </c>
-      <c r="D71" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71">
-        <v>2012</v>
-      </c>
-      <c r="F71">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="G71">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H71" s="2">
-        <f>O48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I71" s="3">
-        <f t="shared" si="9"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J71">
-        <f t="shared" si="10"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K71">
-        <v>40</v>
+      <c r="T71" t="s">
+        <v>69</v>
+      </c>
+      <c r="U71" t="s">
+        <v>44</v>
+      </c>
+      <c r="V71" t="s">
+        <v>78</v>
+      </c>
+      <c r="W71" t="s">
+        <v>71</v>
+      </c>
+      <c r="X71" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
-        <v>190</v>
-      </c>
-      <c r="C72" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72">
-        <v>2015</v>
-      </c>
-      <c r="F72">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="G72">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H72" s="2">
-        <f>O48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I72" s="3">
-        <f t="shared" si="9"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J72">
-        <f t="shared" si="10"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K72">
-        <v>40</v>
+      <c r="T72" t="s">
+        <v>69</v>
+      </c>
+      <c r="U72" t="s">
+        <v>47</v>
+      </c>
+      <c r="V72" t="s">
+        <v>78</v>
+      </c>
+      <c r="W72" t="s">
+        <v>71</v>
+      </c>
+      <c r="X72" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
-        <v>18</v>
-      </c>
-      <c r="C73" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73">
-        <v>2022</v>
-      </c>
-      <c r="F73">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G73">
-        <v>0.33123000000000002</v>
+      <c r="T73" t="s">
+        <v>69</v>
+      </c>
+      <c r="U73" t="s">
+        <v>49</v>
+      </c>
+      <c r="V73" t="s">
+        <v>78</v>
+      </c>
+      <c r="W73" t="s">
+        <v>71</v>
+      </c>
+      <c r="X73" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T74" t="s">
+        <v>69</v>
+      </c>
+      <c r="U74" t="s">
+        <v>51</v>
+      </c>
+      <c r="V74" t="s">
+        <v>78</v>
+      </c>
+      <c r="W74" t="s">
+        <v>71</v>
+      </c>
+      <c r="X74" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T75" t="s">
+        <v>69</v>
+      </c>
+      <c r="U75" t="s">
+        <v>53</v>
+      </c>
+      <c r="V75" t="s">
+        <v>78</v>
+      </c>
+      <c r="W75" t="s">
+        <v>71</v>
+      </c>
+      <c r="X75" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T76" t="s">
+        <v>69</v>
+      </c>
+      <c r="U76" t="s">
+        <v>55</v>
+      </c>
+      <c r="V76" t="s">
+        <v>78</v>
+      </c>
+      <c r="W76" t="s">
+        <v>71</v>
+      </c>
+      <c r="X76" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>20</v>
-      </c>
-      <c r="C77" t="s">
-        <v>21</v>
-      </c>
-      <c r="D77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E77">
-        <v>2013</v>
-      </c>
-      <c r="F77">
-        <v>0.25109999999999999</v>
-      </c>
-      <c r="G77">
-        <v>0.36049999999999999</v>
-      </c>
-      <c r="H77">
-        <v>1265</v>
-      </c>
-      <c r="I77" s="3">
-        <v>48.400000000000006</v>
-      </c>
-      <c r="J77">
-        <v>7.5075000000000003</v>
-      </c>
-      <c r="K77">
-        <v>42</v>
-      </c>
       <c r="T77" t="s">
         <v>69</v>
       </c>
       <c r="U77" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="V77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W77" t="s">
         <v>71</v>
@@ -6115,18 +5638,18 @@
         <v>72</v>
       </c>
       <c r="Y77" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="Z77" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D78" t="s">
         <v>14</v>
@@ -6135,7 +5658,7 @@
         <v>2022</v>
       </c>
       <c r="F78">
-        <v>0.21299999999999999</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G78">
         <v>0.33123000000000002</v>
@@ -6144,10 +5667,10 @@
         <v>69</v>
       </c>
       <c r="U78" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="V78" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W78" t="s">
         <v>71</v>
@@ -6156,51 +5679,44 @@
         <v>72</v>
       </c>
       <c r="Y78" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="Z78" t="s">
         <v>74</v>
       </c>
     </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T79" t="s">
+        <v>69</v>
+      </c>
+      <c r="U79" t="s">
+        <v>20</v>
+      </c>
+      <c r="V79" t="s">
+        <v>79</v>
+      </c>
+      <c r="W79" t="s">
+        <v>71</v>
+      </c>
+      <c r="X79" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>77</v>
+      </c>
+    </row>
     <row r="80" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>12</v>
-      </c>
-      <c r="C80" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" t="s">
-        <v>14</v>
-      </c>
-      <c r="E80">
-        <v>2022</v>
-      </c>
-      <c r="F80">
-        <v>0.3</v>
-      </c>
-      <c r="G80">
-        <v>0.33990000000000004</v>
-      </c>
-      <c r="H80">
-        <v>4427.5</v>
-      </c>
-      <c r="I80" s="3">
-        <v>157.30000000000001</v>
-      </c>
-      <c r="J80">
-        <v>9.24</v>
-      </c>
-      <c r="K80">
-        <v>50</v>
-      </c>
       <c r="T80" t="s">
         <v>69</v>
       </c>
       <c r="U80" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V80" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="W80" t="s">
         <v>71</v>
@@ -6215,17 +5731,641 @@
         <v>74</v>
       </c>
     </row>
-    <row r="90" spans="16:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82">
+        <v>2013</v>
+      </c>
+      <c r="F82">
+        <v>0.25109999999999999</v>
+      </c>
+      <c r="G82">
+        <v>0.36049999999999999</v>
+      </c>
+      <c r="H82">
+        <v>1265</v>
+      </c>
+      <c r="I82" s="3">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="J82">
+        <v>7.5075000000000003</v>
+      </c>
+      <c r="K82">
+        <v>42</v>
+      </c>
+      <c r="T82" t="s">
+        <v>69</v>
+      </c>
+      <c r="U82" t="s">
+        <v>12</v>
+      </c>
+      <c r="V82" t="s">
+        <v>70</v>
+      </c>
+      <c r="W82" t="s">
+        <v>71</v>
+      </c>
+      <c r="X82" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83">
+        <v>2022</v>
+      </c>
+      <c r="F83">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="G83">
+        <v>0.33123000000000002</v>
+      </c>
+    </row>
+    <row r="85" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85">
+        <v>2022</v>
+      </c>
+      <c r="F85">
+        <v>0.3</v>
+      </c>
+      <c r="G85">
+        <v>0.33990000000000004</v>
+      </c>
+      <c r="H85">
+        <v>4427.5</v>
+      </c>
+      <c r="I85" s="3">
+        <v>157.30000000000001</v>
+      </c>
+      <c r="J85">
+        <v>9.24</v>
+      </c>
+      <c r="K85">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>44</v>
+      </c>
+      <c r="C90" t="s">
+        <v>45</v>
+      </c>
+      <c r="D90" t="s">
+        <v>46</v>
+      </c>
+      <c r="E90">
+        <v>2022</v>
+      </c>
+      <c r="F90">
+        <v>1.5040605442498314E-2</v>
+      </c>
+      <c r="G90">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L90">
+        <v>0.42012333946150526</v>
+      </c>
       <c r="P90" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="91" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>47</v>
+      </c>
+      <c r="C91" t="s">
+        <v>45</v>
+      </c>
+      <c r="D91" t="s">
+        <v>48</v>
+      </c>
+      <c r="E91">
+        <v>2022</v>
+      </c>
+      <c r="F91">
+        <v>1.5497656626156837E-2</v>
+      </c>
+      <c r="G91">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L91">
+        <v>0.42012333946150526</v>
+      </c>
+    </row>
+    <row r="92" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>49</v>
+      </c>
+      <c r="C92" t="s">
+        <v>45</v>
+      </c>
+      <c r="D92" t="s">
+        <v>50</v>
+      </c>
+      <c r="E92">
+        <v>2022</v>
+      </c>
+      <c r="F92">
+        <v>1.4461737931344828E-2</v>
+      </c>
+      <c r="G92">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L92">
+        <v>0.42012333946150526</v>
+      </c>
+    </row>
+    <row r="93" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>51</v>
+      </c>
+      <c r="C93" t="s">
+        <v>45</v>
+      </c>
+      <c r="D93" t="s">
+        <v>52</v>
+      </c>
+      <c r="E93">
+        <v>2009</v>
+      </c>
+      <c r="F93">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>2376</v>
+      </c>
+      <c r="I93" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J93">
+        <v>2.52</v>
+      </c>
+      <c r="K93">
+        <v>46</v>
+      </c>
+      <c r="L93">
+        <v>0.47763777043344691</v>
+      </c>
+    </row>
+    <row r="94" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>53</v>
+      </c>
+      <c r="C94" t="s">
+        <v>45</v>
+      </c>
+      <c r="D94" t="s">
+        <v>54</v>
+      </c>
+      <c r="E94">
+        <v>2010</v>
+      </c>
+      <c r="F94">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>2376</v>
+      </c>
+      <c r="I94" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J94">
+        <v>2.52</v>
+      </c>
+      <c r="K94">
+        <v>45</v>
+      </c>
+      <c r="L94">
+        <v>0.47814004703314078</v>
+      </c>
+    </row>
+    <row r="95" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>53</v>
+      </c>
+      <c r="C95" t="s">
+        <v>45</v>
+      </c>
+      <c r="D95" t="s">
+        <v>54</v>
+      </c>
+      <c r="E95">
+        <v>2015</v>
+      </c>
+      <c r="F95">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>2376</v>
+      </c>
+      <c r="I95" s="3">
+        <v>57.20000000000001</v>
+      </c>
+      <c r="J95">
+        <v>2.52</v>
+      </c>
+      <c r="K95">
+        <v>40</v>
+      </c>
+      <c r="L95">
+        <v>0.47814004703314084</v>
+      </c>
+    </row>
+    <row r="96" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>53</v>
+      </c>
+      <c r="C96" t="s">
+        <v>45</v>
+      </c>
+      <c r="D96" t="s">
+        <v>54</v>
+      </c>
+      <c r="E96">
+        <v>2020</v>
+      </c>
+      <c r="F96">
+        <v>1.2E-2</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>2376</v>
+      </c>
+      <c r="I96" s="3">
+        <v>57.20000000000001</v>
+      </c>
+      <c r="J96">
+        <v>2.52</v>
+      </c>
+      <c r="K96">
+        <v>35</v>
+      </c>
+      <c r="L96">
+        <v>0.47814004703314078</v>
+      </c>
+    </row>
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>55</v>
+      </c>
+      <c r="C97" t="s">
+        <v>45</v>
+      </c>
+      <c r="D97" t="s">
+        <v>56</v>
+      </c>
+      <c r="E97">
+        <v>2007</v>
+      </c>
+      <c r="F97">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>2376</v>
+      </c>
+      <c r="I97" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J97">
+        <v>2.52</v>
+      </c>
+      <c r="K97">
+        <v>48</v>
+      </c>
+      <c r="L97">
+        <v>0.40144059976798208</v>
+      </c>
+    </row>
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>55</v>
+      </c>
+      <c r="C98" t="s">
+        <v>45</v>
+      </c>
+      <c r="D98" t="s">
+        <v>56</v>
+      </c>
+      <c r="E98">
+        <v>2011</v>
+      </c>
+      <c r="F98">
+        <v>2.4E-2</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>2376</v>
+      </c>
+      <c r="I98" s="3">
+        <v>57.20000000000001</v>
+      </c>
+      <c r="J98">
+        <v>2.52</v>
+      </c>
+      <c r="K98">
+        <v>44</v>
+      </c>
+      <c r="L98">
+        <v>0.40144059976798202</v>
+      </c>
+    </row>
+    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>55</v>
+      </c>
+      <c r="C99" t="s">
+        <v>45</v>
+      </c>
+      <c r="D99" t="s">
+        <v>56</v>
+      </c>
+      <c r="E99">
+        <v>2012</v>
+      </c>
+      <c r="F99">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>2376</v>
+      </c>
+      <c r="I99" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J99">
+        <v>2.52</v>
+      </c>
+      <c r="K99">
+        <v>43</v>
+      </c>
+      <c r="L99">
+        <v>0.40144059976798202</v>
+      </c>
+    </row>
+    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>55</v>
+      </c>
+      <c r="C100" t="s">
+        <v>45</v>
+      </c>
+      <c r="D100" t="s">
+        <v>56</v>
+      </c>
+      <c r="E100">
+        <v>2023</v>
+      </c>
+      <c r="F100">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>2376</v>
+      </c>
+      <c r="I100" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J100">
+        <v>2.52</v>
+      </c>
+      <c r="K100">
+        <v>32</v>
+      </c>
+      <c r="L100">
+        <v>0.40144059976798208</v>
+      </c>
+    </row>
+    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>55</v>
+      </c>
+      <c r="C101" t="s">
+        <v>45</v>
+      </c>
+      <c r="D101" t="s">
+        <v>56</v>
+      </c>
+      <c r="E101">
+        <v>2024</v>
+      </c>
+      <c r="F101">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>2024</v>
+      </c>
+      <c r="I101" s="3">
+        <v>48.4</v>
+      </c>
+      <c r="J101">
+        <v>2.3100000000000005</v>
+      </c>
+      <c r="K101">
+        <v>31</v>
+      </c>
+      <c r="L101">
+        <v>0.40144059976798202</v>
+      </c>
+    </row>
+    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>57</v>
+      </c>
+      <c r="C102" t="s">
+        <v>45</v>
+      </c>
+      <c r="D102" t="s">
+        <v>58</v>
+      </c>
+      <c r="E102">
+        <v>2023</v>
+      </c>
+      <c r="F102">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>2376</v>
+      </c>
+      <c r="I102" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J102">
+        <v>2.52</v>
+      </c>
+      <c r="K102">
+        <v>32</v>
+      </c>
+      <c r="L102">
+        <v>0.365520596150406</v>
+      </c>
+    </row>
+    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>59</v>
+      </c>
+      <c r="C103" t="s">
+        <v>45</v>
+      </c>
+      <c r="D103" t="s">
+        <v>60</v>
+      </c>
+      <c r="E103">
+        <v>2005</v>
+      </c>
+      <c r="F103">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>2376</v>
+      </c>
+      <c r="I103" s="3">
+        <v>57.20000000000001</v>
+      </c>
+      <c r="J103">
+        <v>2.52</v>
+      </c>
+      <c r="K103">
+        <v>50</v>
+      </c>
+      <c r="L103">
+        <v>0.41047488326249421</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>59</v>
+      </c>
+      <c r="C104" t="s">
+        <v>45</v>
+      </c>
+      <c r="D104" t="s">
+        <v>60</v>
+      </c>
+      <c r="E104">
+        <v>2012</v>
+      </c>
+      <c r="F104">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>2376</v>
+      </c>
+      <c r="I104" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J104">
+        <v>2.52</v>
+      </c>
+      <c r="K104">
+        <v>43</v>
+      </c>
+      <c r="L104">
+        <v>0.41047488326249421</v>
+      </c>
+    </row>
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>59</v>
+      </c>
+      <c r="C105" t="s">
+        <v>45</v>
+      </c>
+      <c r="D105" t="s">
+        <v>60</v>
+      </c>
+      <c r="E105">
+        <v>2013</v>
+      </c>
+      <c r="F105">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>2376</v>
+      </c>
+      <c r="I105" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J105">
+        <v>2.52</v>
+      </c>
+      <c r="K105">
+        <v>42</v>
+      </c>
+      <c r="L105">
+        <v>0.41047488326249421</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="I59 I61" formula="1"/>
-  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3180BC-3EF9-4EFA-A053-EA4C7D8D5475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBF4C11-D2B5-42F7-A1D0-EF55CC0B6F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -3777,10 +3777,6 @@
       <c r="C29" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="P29">
-        <f>SUM(F26:F28)+0.31</f>
-        <v>1.0039</v>
-      </c>
       <c r="T29" t="s">
         <v>69</v>
       </c>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBF4C11-D2B5-42F7-A1D0-EF55CC0B6F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6102C45D-C416-4B55-93B6-FF26681B6690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -2911,7 +2911,7 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>3.9363662143155967E-2</v>
+        <v>0.3269999999999999</v>
       </c>
       <c r="G13">
         <v>0.33123000000000002</v>
@@ -3199,6 +3199,12 @@
       <c r="L18">
         <v>0.15309859852159369</v>
       </c>
+      <c r="O18">
+        <v>3.9363662143155967E-2</v>
+      </c>
+      <c r="P18">
+        <v>0.28763633785684395</v>
+      </c>
       <c r="T18" t="s">
         <v>69</v>
       </c>
@@ -3311,6 +3317,14 @@
       <c r="L20">
         <v>0.15619560585976827</v>
       </c>
+      <c r="O20">
+        <f>SUM(F11:F25)</f>
+        <v>0.92963633785684396</v>
+      </c>
+      <c r="P20">
+        <f>0.969-F13-O20</f>
+        <v>-0.28763633785684384</v>
+      </c>
       <c r="T20" t="s">
         <v>69</v>
       </c>
@@ -3535,6 +3549,10 @@
       <c r="L24">
         <v>0.1532628310027955</v>
       </c>
+      <c r="P24">
+        <f>SUM(O20:P20)+F13</f>
+        <v>0.96900000000000008</v>
+      </c>
       <c r="T24" t="s">
         <v>69</v>
       </c>
@@ -3804,7 +3822,7 @@
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6102C45D-C416-4B55-93B6-FF26681B6690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B151CA3A-D3EC-469B-97E4-E571A5E30242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -127,7 +127,7 @@
     Took same as chp</t>
       </text>
     </comment>
-    <comment ref="T79" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <comment ref="T84" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1228,7 +1228,7 @@
   <threadedComment ref="Q47" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
     <text>Took same as chp</text>
   </threadedComment>
-  <threadedComment ref="T79" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+  <threadedComment ref="T84" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
   </threadedComment>
   <threadedComment ref="J85" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
@@ -2879,10 +2879,10 @@
         <v>69</v>
       </c>
       <c r="U12" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="V12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W12" t="s">
         <v>71</v>
@@ -2923,10 +2923,10 @@
         <v>69</v>
       </c>
       <c r="U13" t="s">
-        <v>25</v>
+        <v>216</v>
       </c>
       <c r="V13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="W13" t="s">
         <v>71</v>
@@ -2979,10 +2979,10 @@
         <v>69</v>
       </c>
       <c r="U14" t="s">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="V14" t="s">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="W14" t="s">
         <v>71</v>
@@ -2994,7 +2994,7 @@
         <v>80</v>
       </c>
       <c r="Z14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="2:26" x14ac:dyDescent="0.25">
@@ -3032,25 +3032,10 @@
         <v>0.1461854238754417</v>
       </c>
       <c r="T15" t="s">
-        <v>69</v>
-      </c>
-      <c r="U15" t="s">
-        <v>29</v>
-      </c>
-      <c r="V15" t="s">
-        <v>78</v>
-      </c>
-      <c r="W15" t="s">
-        <v>71</v>
-      </c>
-      <c r="X15" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>74</v>
+        <v>140</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="2:26" x14ac:dyDescent="0.25">
@@ -3091,10 +3076,10 @@
         <v>69</v>
       </c>
       <c r="U16" t="s">
-        <v>30</v>
+        <v>194</v>
       </c>
       <c r="V16" t="s">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="W16" t="s">
         <v>71</v>
@@ -3147,10 +3132,10 @@
         <v>69</v>
       </c>
       <c r="U17" t="s">
-        <v>32</v>
+        <v>193</v>
       </c>
       <c r="V17" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="W17" t="s">
         <v>71</v>
@@ -3209,10 +3194,10 @@
         <v>69</v>
       </c>
       <c r="U18" t="s">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="V18" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="W18" t="s">
         <v>71</v>
@@ -3265,10 +3250,10 @@
         <v>69</v>
       </c>
       <c r="U19" t="s">
-        <v>35</v>
+        <v>196</v>
       </c>
       <c r="V19" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="W19" t="s">
         <v>71</v>
@@ -3329,10 +3314,10 @@
         <v>69</v>
       </c>
       <c r="U20" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="V20" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="W20" t="s">
         <v>71</v>
@@ -3385,10 +3370,10 @@
         <v>69</v>
       </c>
       <c r="U21" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="V21" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="W21" t="s">
         <v>71</v>
@@ -3441,10 +3426,10 @@
         <v>69</v>
       </c>
       <c r="U22" t="s">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="V22" t="s">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="W22" t="s">
         <v>71</v>
@@ -3497,10 +3482,10 @@
         <v>69</v>
       </c>
       <c r="U23" t="s">
-        <v>42</v>
+        <v>145</v>
       </c>
       <c r="V23" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="W23" t="s">
         <v>71</v>
@@ -3557,10 +3542,10 @@
         <v>69</v>
       </c>
       <c r="U24" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="V24" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="W24" t="s">
         <v>71</v>
@@ -3613,10 +3598,10 @@
         <v>69</v>
       </c>
       <c r="U25" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="V25" t="s">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="W25" t="s">
         <v>71</v>
@@ -3669,10 +3654,10 @@
         <v>69</v>
       </c>
       <c r="U26" t="s">
-        <v>217</v>
+        <v>154</v>
       </c>
       <c r="V26" t="s">
-        <v>218</v>
+        <v>155</v>
       </c>
       <c r="W26" t="s">
         <v>71</v>
@@ -3684,7 +3669,7 @@
         <v>80</v>
       </c>
       <c r="Z26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.25">
@@ -3726,10 +3711,25 @@
         <v>2.0930123559331545E-3</v>
       </c>
       <c r="T27" t="s">
-        <v>140</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>141</v>
+        <v>69</v>
+      </c>
+      <c r="U27" t="s">
+        <v>156</v>
+      </c>
+      <c r="V27" t="s">
+        <v>157</v>
+      </c>
+      <c r="W27" t="s">
+        <v>71</v>
+      </c>
+      <c r="X27" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.25">
@@ -3770,10 +3770,10 @@
         <v>69</v>
       </c>
       <c r="U28" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="V28" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="W28" t="s">
         <v>71</v>
@@ -3799,10 +3799,10 @@
         <v>69</v>
       </c>
       <c r="U29" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="V29" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="W29" t="s">
         <v>71</v>
@@ -3855,10 +3855,10 @@
         <v>69</v>
       </c>
       <c r="U30" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="V30" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="W30" t="s">
         <v>71</v>
@@ -3911,10 +3911,10 @@
         <v>69</v>
       </c>
       <c r="U31" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="V31" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="W31" t="s">
         <v>71</v>
@@ -3967,10 +3967,10 @@
         <v>69</v>
       </c>
       <c r="U32" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="V32" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="W32" t="s">
         <v>71</v>
@@ -4023,10 +4023,10 @@
         <v>69</v>
       </c>
       <c r="U33" t="s">
-        <v>143</v>
+        <v>198</v>
       </c>
       <c r="V33" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="W33" t="s">
         <v>71</v>
@@ -4079,10 +4079,10 @@
         <v>69</v>
       </c>
       <c r="U34" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="V34" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="W34" t="s">
         <v>71</v>
@@ -4136,10 +4136,10 @@
         <v>69</v>
       </c>
       <c r="U35" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="V35" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="W35" t="s">
         <v>71</v>
@@ -4193,10 +4193,10 @@
         <v>69</v>
       </c>
       <c r="U36" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="V36" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="W36" t="s">
         <v>71</v>
@@ -4249,10 +4249,10 @@
         <v>69</v>
       </c>
       <c r="U37" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="V37" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="W37" t="s">
         <v>71</v>
@@ -4305,10 +4305,10 @@
         <v>69</v>
       </c>
       <c r="U38" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="V38" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="W38" t="s">
         <v>71</v>
@@ -4361,10 +4361,10 @@
         <v>69</v>
       </c>
       <c r="U39" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="V39" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="W39" t="s">
         <v>71</v>
@@ -4418,10 +4418,10 @@
         <v>69</v>
       </c>
       <c r="U40" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="V40" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="W40" t="s">
         <v>71</v>
@@ -4474,10 +4474,10 @@
         <v>69</v>
       </c>
       <c r="U41" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="V41" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="W41" t="s">
         <v>71</v>
@@ -4530,10 +4530,10 @@
         <v>69</v>
       </c>
       <c r="U42" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="V42" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="W42" t="s">
         <v>71</v>
@@ -4598,10 +4598,10 @@
         <v>69</v>
       </c>
       <c r="U43" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="V43" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="W43" t="s">
         <v>71</v>
@@ -4669,10 +4669,10 @@
         <v>69</v>
       </c>
       <c r="U44" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="V44" t="s">
-        <v>166</v>
+        <v>78</v>
       </c>
       <c r="W44" t="s">
         <v>71</v>
@@ -4681,10 +4681,10 @@
         <v>72</v>
       </c>
       <c r="Y44" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="Z44" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
@@ -4737,27 +4737,6 @@
       <c r="Q45">
         <v>5.8775000000000004</v>
       </c>
-      <c r="T45" t="s">
-        <v>69</v>
-      </c>
-      <c r="U45" t="s">
-        <v>198</v>
-      </c>
-      <c r="V45" t="s">
-        <v>167</v>
-      </c>
-      <c r="W45" t="s">
-        <v>71</v>
-      </c>
-      <c r="X45" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="46" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
@@ -4798,27 +4777,6 @@
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="2"/>
-      <c r="T46" t="s">
-        <v>69</v>
-      </c>
-      <c r="U46" t="s">
-        <v>172</v>
-      </c>
-      <c r="V46" t="s">
-        <v>173</v>
-      </c>
-      <c r="W46" t="s">
-        <v>71</v>
-      </c>
-      <c r="X46" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z46" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
@@ -4870,27 +4828,6 @@
       <c r="Q47">
         <v>2.8138000000000001</v>
       </c>
-      <c r="T47" t="s">
-        <v>69</v>
-      </c>
-      <c r="U47" t="s">
-        <v>174</v>
-      </c>
-      <c r="V47" t="s">
-        <v>175</v>
-      </c>
-      <c r="W47" t="s">
-        <v>71</v>
-      </c>
-      <c r="X47" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
@@ -4942,27 +4879,6 @@
       <c r="Q48">
         <v>2.8138000000000001</v>
       </c>
-      <c r="T48" t="s">
-        <v>69</v>
-      </c>
-      <c r="U48" t="s">
-        <v>176</v>
-      </c>
-      <c r="V48" t="s">
-        <v>177</v>
-      </c>
-      <c r="W48" t="s">
-        <v>71</v>
-      </c>
-      <c r="X48" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y48" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
@@ -5000,27 +4916,6 @@
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="4"/>
-      <c r="T49" t="s">
-        <v>69</v>
-      </c>
-      <c r="U49" t="s">
-        <v>178</v>
-      </c>
-      <c r="V49" t="s">
-        <v>179</v>
-      </c>
-      <c r="W49" t="s">
-        <v>71</v>
-      </c>
-      <c r="X49" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y49" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z49" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
@@ -5058,27 +4953,6 @@
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="4"/>
-      <c r="T50" t="s">
-        <v>69</v>
-      </c>
-      <c r="U50" t="s">
-        <v>180</v>
-      </c>
-      <c r="V50" t="s">
-        <v>181</v>
-      </c>
-      <c r="W50" t="s">
-        <v>71</v>
-      </c>
-      <c r="X50" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
@@ -5117,27 +4991,6 @@
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="4"/>
-      <c r="T51" t="s">
-        <v>69</v>
-      </c>
-      <c r="U51" t="s">
-        <v>182</v>
-      </c>
-      <c r="V51" t="s">
-        <v>183</v>
-      </c>
-      <c r="W51" t="s">
-        <v>71</v>
-      </c>
-      <c r="X51" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
@@ -5176,27 +5029,6 @@
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="4"/>
-      <c r="T52" t="s">
-        <v>69</v>
-      </c>
-      <c r="U52" t="s">
-        <v>184</v>
-      </c>
-      <c r="V52" t="s">
-        <v>185</v>
-      </c>
-      <c r="W52" t="s">
-        <v>71</v>
-      </c>
-      <c r="X52" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y52" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z52" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
@@ -5232,27 +5064,6 @@
       <c r="K53">
         <v>40</v>
       </c>
-      <c r="T53" t="s">
-        <v>69</v>
-      </c>
-      <c r="U53" t="s">
-        <v>186</v>
-      </c>
-      <c r="V53" t="s">
-        <v>188</v>
-      </c>
-      <c r="W53" t="s">
-        <v>71</v>
-      </c>
-      <c r="X53" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z53" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
@@ -5288,27 +5099,6 @@
       <c r="K54">
         <v>40</v>
       </c>
-      <c r="T54" t="s">
-        <v>69</v>
-      </c>
-      <c r="U54" t="s">
-        <v>187</v>
-      </c>
-      <c r="V54" t="s">
-        <v>189</v>
-      </c>
-      <c r="W54" t="s">
-        <v>71</v>
-      </c>
-      <c r="X54" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
@@ -5344,27 +5134,6 @@
       <c r="K55">
         <v>40</v>
       </c>
-      <c r="T55" t="s">
-        <v>69</v>
-      </c>
-      <c r="U55" t="s">
-        <v>190</v>
-      </c>
-      <c r="V55" t="s">
-        <v>191</v>
-      </c>
-      <c r="W55" t="s">
-        <v>71</v>
-      </c>
-      <c r="X55" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
@@ -5400,27 +5169,6 @@
       <c r="K56">
         <v>40</v>
       </c>
-      <c r="T56" t="s">
-        <v>69</v>
-      </c>
-      <c r="U56" t="s">
-        <v>18</v>
-      </c>
-      <c r="V56" t="s">
-        <v>78</v>
-      </c>
-      <c r="W56" t="s">
-        <v>71</v>
-      </c>
-      <c r="X56" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y56" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z56" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
@@ -5492,9 +5240,188 @@
         <v>40</v>
       </c>
     </row>
+    <row r="63" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T63" t="s">
+        <v>69</v>
+      </c>
+      <c r="U63" t="s">
+        <v>22</v>
+      </c>
+      <c r="V63" t="s">
+        <v>78</v>
+      </c>
+      <c r="W63" t="s">
+        <v>71</v>
+      </c>
+      <c r="X63" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T64" t="s">
+        <v>69</v>
+      </c>
+      <c r="U64" t="s">
+        <v>25</v>
+      </c>
+      <c r="V64" t="s">
+        <v>78</v>
+      </c>
+      <c r="W64" t="s">
+        <v>71</v>
+      </c>
+      <c r="X64" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T65" t="s">
+        <v>69</v>
+      </c>
+      <c r="U65" t="s">
+        <v>27</v>
+      </c>
+      <c r="V65" t="s">
+        <v>78</v>
+      </c>
+      <c r="W65" t="s">
+        <v>71</v>
+      </c>
+      <c r="X65" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T66" t="s">
+        <v>69</v>
+      </c>
+      <c r="U66" t="s">
+        <v>29</v>
+      </c>
+      <c r="V66" t="s">
+        <v>78</v>
+      </c>
+      <c r="W66" t="s">
+        <v>71</v>
+      </c>
+      <c r="X66" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T67" t="s">
+        <v>69</v>
+      </c>
+      <c r="U67" t="s">
+        <v>30</v>
+      </c>
+      <c r="V67" t="s">
+        <v>78</v>
+      </c>
+      <c r="W67" t="s">
+        <v>71</v>
+      </c>
+      <c r="X67" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T68" t="s">
+        <v>69</v>
+      </c>
+      <c r="U68" t="s">
+        <v>32</v>
+      </c>
+      <c r="V68" t="s">
+        <v>78</v>
+      </c>
+      <c r="W68" t="s">
+        <v>71</v>
+      </c>
+      <c r="X68" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T69" t="s">
+        <v>69</v>
+      </c>
+      <c r="U69" t="s">
+        <v>34</v>
+      </c>
+      <c r="V69" t="s">
+        <v>78</v>
+      </c>
+      <c r="W69" t="s">
+        <v>71</v>
+      </c>
+      <c r="X69" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="70" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T70" t="s">
+        <v>69</v>
+      </c>
       <c r="U70" t="s">
-        <v>207</v>
+        <v>35</v>
+      </c>
+      <c r="V70" t="s">
+        <v>78</v>
+      </c>
+      <c r="W70" t="s">
+        <v>71</v>
+      </c>
+      <c r="X70" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="2:26" x14ac:dyDescent="0.25">
@@ -5502,7 +5429,7 @@
         <v>69</v>
       </c>
       <c r="U71" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="V71" t="s">
         <v>78</v>
@@ -5525,7 +5452,7 @@
         <v>69</v>
       </c>
       <c r="U72" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="V72" t="s">
         <v>78</v>
@@ -5548,7 +5475,7 @@
         <v>69</v>
       </c>
       <c r="U73" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="V73" t="s">
         <v>78</v>
@@ -5571,7 +5498,7 @@
         <v>69</v>
       </c>
       <c r="U74" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="V74" t="s">
         <v>78</v>
@@ -5590,26 +5517,8 @@
       </c>
     </row>
     <row r="75" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T75" t="s">
-        <v>69</v>
-      </c>
       <c r="U75" t="s">
-        <v>53</v>
-      </c>
-      <c r="V75" t="s">
-        <v>78</v>
-      </c>
-      <c r="W75" t="s">
-        <v>71</v>
-      </c>
-      <c r="X75" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y75" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z75" t="s">
-        <v>74</v>
+        <v>207</v>
       </c>
     </row>
     <row r="76" spans="2:26" x14ac:dyDescent="0.25">
@@ -5617,7 +5526,7 @@
         <v>69</v>
       </c>
       <c r="U76" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="V76" t="s">
         <v>78</v>
@@ -5640,7 +5549,7 @@
         <v>69</v>
       </c>
       <c r="U77" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="V77" t="s">
         <v>78</v>
@@ -5681,7 +5590,7 @@
         <v>69</v>
       </c>
       <c r="U78" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="V78" t="s">
         <v>78</v>
@@ -5704,10 +5613,10 @@
         <v>69</v>
       </c>
       <c r="U79" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="V79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W79" t="s">
         <v>71</v>
@@ -5716,10 +5625,10 @@
         <v>72</v>
       </c>
       <c r="Y79" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="Z79" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="2:26" x14ac:dyDescent="0.25">
@@ -5727,10 +5636,10 @@
         <v>69</v>
       </c>
       <c r="U80" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="V80" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="W80" t="s">
         <v>71</v>
@@ -5739,9 +5648,32 @@
         <v>72</v>
       </c>
       <c r="Y80" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="Z80" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T81" t="s">
+        <v>69</v>
+      </c>
+      <c r="U81" t="s">
+        <v>55</v>
+      </c>
+      <c r="V81" t="s">
+        <v>78</v>
+      </c>
+      <c r="W81" t="s">
+        <v>71</v>
+      </c>
+      <c r="X81" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z81" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5780,10 +5712,10 @@
         <v>69</v>
       </c>
       <c r="U82" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="V82" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="W82" t="s">
         <v>71</v>
@@ -5792,7 +5724,7 @@
         <v>72</v>
       </c>
       <c r="Y82" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="Z82" t="s">
         <v>74</v>
@@ -5817,6 +5749,50 @@
       <c r="G83">
         <v>0.33123000000000002</v>
       </c>
+      <c r="T83" t="s">
+        <v>69</v>
+      </c>
+      <c r="U83" t="s">
+        <v>59</v>
+      </c>
+      <c r="V83" t="s">
+        <v>78</v>
+      </c>
+      <c r="W83" t="s">
+        <v>71</v>
+      </c>
+      <c r="X83" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T84" t="s">
+        <v>69</v>
+      </c>
+      <c r="U84" t="s">
+        <v>20</v>
+      </c>
+      <c r="V84" t="s">
+        <v>79</v>
+      </c>
+      <c r="W84" t="s">
+        <v>71</v>
+      </c>
+      <c r="X84" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="85" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
@@ -5848,6 +5824,50 @@
       </c>
       <c r="K85">
         <v>50</v>
+      </c>
+      <c r="T85" t="s">
+        <v>69</v>
+      </c>
+      <c r="U85" t="s">
+        <v>15</v>
+      </c>
+      <c r="V85" t="s">
+        <v>75</v>
+      </c>
+      <c r="W85" t="s">
+        <v>71</v>
+      </c>
+      <c r="X85" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="T87" t="s">
+        <v>69</v>
+      </c>
+      <c r="U87" t="s">
+        <v>12</v>
+      </c>
+      <c r="V87" t="s">
+        <v>70</v>
+      </c>
+      <c r="W87" t="s">
+        <v>71</v>
+      </c>
+      <c r="X87" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="90" spans="2:26" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B151CA3A-D3EC-469B-97E4-E571A5E30242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9849CC3-C1F1-4279-9AD0-5DA029C188B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -77,7 +77,7 @@
     <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
   </authors>
   <commentList>
-    <comment ref="Y11" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+    <comment ref="Y23" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1208,7 +1208,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="Y11" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+  <threadedComment ref="Y23" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
     <text>Miks daynite (hydro samuti)</text>
   </threadedComment>
   <threadedComment ref="F30" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
@@ -2835,10 +2835,10 @@
         <v>69</v>
       </c>
       <c r="U11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="W11" t="s">
         <v>71</v>
@@ -2847,7 +2847,7 @@
         <v>72</v>
       </c>
       <c r="Y11" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="Z11" t="s">
         <v>74</v>
@@ -2879,10 +2879,10 @@
         <v>69</v>
       </c>
       <c r="U12" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="V12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="W12" t="s">
         <v>71</v>
@@ -2923,10 +2923,10 @@
         <v>69</v>
       </c>
       <c r="U13" t="s">
-        <v>216</v>
+        <v>27</v>
       </c>
       <c r="V13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="W13" t="s">
         <v>71</v>
@@ -2979,10 +2979,10 @@
         <v>69</v>
       </c>
       <c r="U14" t="s">
-        <v>217</v>
+        <v>29</v>
       </c>
       <c r="V14" t="s">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="W14" t="s">
         <v>71</v>
@@ -2994,7 +2994,7 @@
         <v>80</v>
       </c>
       <c r="Z14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="2:26" x14ac:dyDescent="0.25">
@@ -3032,10 +3032,25 @@
         <v>0.1461854238754417</v>
       </c>
       <c r="T15" t="s">
-        <v>140</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>141</v>
+        <v>69</v>
+      </c>
+      <c r="U15" t="s">
+        <v>30</v>
+      </c>
+      <c r="V15" t="s">
+        <v>78</v>
+      </c>
+      <c r="W15" t="s">
+        <v>71</v>
+      </c>
+      <c r="X15" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="2:26" x14ac:dyDescent="0.25">
@@ -3076,10 +3091,10 @@
         <v>69</v>
       </c>
       <c r="U16" t="s">
-        <v>194</v>
+        <v>32</v>
       </c>
       <c r="V16" t="s">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="W16" t="s">
         <v>71</v>
@@ -3132,10 +3147,10 @@
         <v>69</v>
       </c>
       <c r="U17" t="s">
-        <v>193</v>
+        <v>34</v>
       </c>
       <c r="V17" t="s">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="W17" t="s">
         <v>71</v>
@@ -3194,10 +3209,10 @@
         <v>69</v>
       </c>
       <c r="U18" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="V18" t="s">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="W18" t="s">
         <v>71</v>
@@ -3250,10 +3265,10 @@
         <v>69</v>
       </c>
       <c r="U19" t="s">
-        <v>196</v>
+        <v>37</v>
       </c>
       <c r="V19" t="s">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="W19" t="s">
         <v>71</v>
@@ -3314,10 +3329,10 @@
         <v>69</v>
       </c>
       <c r="U20" t="s">
-        <v>142</v>
+        <v>39</v>
       </c>
       <c r="V20" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="W20" t="s">
         <v>71</v>
@@ -3370,10 +3385,10 @@
         <v>69</v>
       </c>
       <c r="U21" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="V21" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="W21" t="s">
         <v>71</v>
@@ -3426,10 +3441,10 @@
         <v>69</v>
       </c>
       <c r="U22" t="s">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="V22" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="W22" t="s">
         <v>71</v>
@@ -3482,10 +3497,10 @@
         <v>69</v>
       </c>
       <c r="U23" t="s">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="V23" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="W23" t="s">
         <v>71</v>
@@ -3494,7 +3509,7 @@
         <v>72</v>
       </c>
       <c r="Y23" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="Z23" t="s">
         <v>74</v>
@@ -3542,10 +3557,10 @@
         <v>69</v>
       </c>
       <c r="U24" t="s">
-        <v>146</v>
+        <v>61</v>
       </c>
       <c r="V24" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="W24" t="s">
         <v>71</v>
@@ -3598,10 +3613,10 @@
         <v>69</v>
       </c>
       <c r="U25" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="V25" t="s">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="W25" t="s">
         <v>71</v>
@@ -3654,10 +3669,10 @@
         <v>69</v>
       </c>
       <c r="U26" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="V26" t="s">
-        <v>155</v>
+        <v>218</v>
       </c>
       <c r="W26" t="s">
         <v>71</v>
@@ -3669,7 +3684,7 @@
         <v>80</v>
       </c>
       <c r="Z26" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.25">
@@ -3711,25 +3726,10 @@
         <v>2.0930123559331545E-3</v>
       </c>
       <c r="T27" t="s">
-        <v>69</v>
-      </c>
-      <c r="U27" t="s">
-        <v>156</v>
-      </c>
-      <c r="V27" t="s">
-        <v>157</v>
-      </c>
-      <c r="W27" t="s">
-        <v>71</v>
-      </c>
-      <c r="X27" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>74</v>
+        <v>140</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.25">
@@ -3770,10 +3770,10 @@
         <v>69</v>
       </c>
       <c r="U28" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="V28" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="W28" t="s">
         <v>71</v>
@@ -3799,10 +3799,10 @@
         <v>69</v>
       </c>
       <c r="U29" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="V29" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="W29" t="s">
         <v>71</v>
@@ -3855,10 +3855,10 @@
         <v>69</v>
       </c>
       <c r="U30" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="V30" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="W30" t="s">
         <v>71</v>
@@ -3911,10 +3911,10 @@
         <v>69</v>
       </c>
       <c r="U31" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="V31" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="W31" t="s">
         <v>71</v>
@@ -3967,10 +3967,10 @@
         <v>69</v>
       </c>
       <c r="U32" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="V32" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="W32" t="s">
         <v>71</v>
@@ -4023,10 +4023,10 @@
         <v>69</v>
       </c>
       <c r="U33" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="V33" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="W33" t="s">
         <v>71</v>
@@ -4079,10 +4079,10 @@
         <v>69</v>
       </c>
       <c r="U34" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="V34" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="W34" t="s">
         <v>71</v>
@@ -4136,10 +4136,10 @@
         <v>69</v>
       </c>
       <c r="U35" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="V35" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="W35" t="s">
         <v>71</v>
@@ -4193,10 +4193,10 @@
         <v>69</v>
       </c>
       <c r="U36" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="V36" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="W36" t="s">
         <v>71</v>
@@ -4249,10 +4249,10 @@
         <v>69</v>
       </c>
       <c r="U37" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="V37" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="W37" t="s">
         <v>71</v>
@@ -4305,10 +4305,10 @@
         <v>69</v>
       </c>
       <c r="U38" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="V38" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="W38" t="s">
         <v>71</v>
@@ -4361,10 +4361,10 @@
         <v>69</v>
       </c>
       <c r="U39" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="V39" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="W39" t="s">
         <v>71</v>
@@ -4418,10 +4418,10 @@
         <v>69</v>
       </c>
       <c r="U40" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="V40" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="W40" t="s">
         <v>71</v>
@@ -4474,10 +4474,10 @@
         <v>69</v>
       </c>
       <c r="U41" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="V41" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="W41" t="s">
         <v>71</v>
@@ -4530,10 +4530,10 @@
         <v>69</v>
       </c>
       <c r="U42" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="V42" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="W42" t="s">
         <v>71</v>
@@ -4598,10 +4598,10 @@
         <v>69</v>
       </c>
       <c r="U43" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="V43" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="W43" t="s">
         <v>71</v>
@@ -4669,10 +4669,10 @@
         <v>69</v>
       </c>
       <c r="U44" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="V44" t="s">
-        <v>78</v>
+        <v>166</v>
       </c>
       <c r="W44" t="s">
         <v>71</v>
@@ -4681,10 +4681,10 @@
         <v>72</v>
       </c>
       <c r="Y44" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="Z44" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.25">
@@ -4737,6 +4737,27 @@
       <c r="Q45">
         <v>5.8775000000000004</v>
       </c>
+      <c r="T45" t="s">
+        <v>69</v>
+      </c>
+      <c r="U45" t="s">
+        <v>198</v>
+      </c>
+      <c r="V45" t="s">
+        <v>167</v>
+      </c>
+      <c r="W45" t="s">
+        <v>71</v>
+      </c>
+      <c r="X45" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="46" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
@@ -4777,6 +4798,27 @@
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="2"/>
+      <c r="T46" t="s">
+        <v>69</v>
+      </c>
+      <c r="U46" t="s">
+        <v>172</v>
+      </c>
+      <c r="V46" t="s">
+        <v>173</v>
+      </c>
+      <c r="W46" t="s">
+        <v>71</v>
+      </c>
+      <c r="X46" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
@@ -4828,6 +4870,27 @@
       <c r="Q47">
         <v>2.8138000000000001</v>
       </c>
+      <c r="T47" t="s">
+        <v>69</v>
+      </c>
+      <c r="U47" t="s">
+        <v>174</v>
+      </c>
+      <c r="V47" t="s">
+        <v>175</v>
+      </c>
+      <c r="W47" t="s">
+        <v>71</v>
+      </c>
+      <c r="X47" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
@@ -4879,6 +4942,27 @@
       <c r="Q48">
         <v>2.8138000000000001</v>
       </c>
+      <c r="T48" t="s">
+        <v>69</v>
+      </c>
+      <c r="U48" t="s">
+        <v>176</v>
+      </c>
+      <c r="V48" t="s">
+        <v>177</v>
+      </c>
+      <c r="W48" t="s">
+        <v>71</v>
+      </c>
+      <c r="X48" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
@@ -4916,6 +5000,27 @@
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="4"/>
+      <c r="T49" t="s">
+        <v>69</v>
+      </c>
+      <c r="U49" t="s">
+        <v>178</v>
+      </c>
+      <c r="V49" t="s">
+        <v>179</v>
+      </c>
+      <c r="W49" t="s">
+        <v>71</v>
+      </c>
+      <c r="X49" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
@@ -4953,6 +5058,27 @@
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="4"/>
+      <c r="T50" t="s">
+        <v>69</v>
+      </c>
+      <c r="U50" t="s">
+        <v>180</v>
+      </c>
+      <c r="V50" t="s">
+        <v>181</v>
+      </c>
+      <c r="W50" t="s">
+        <v>71</v>
+      </c>
+      <c r="X50" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
@@ -4991,6 +5117,27 @@
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="4"/>
+      <c r="T51" t="s">
+        <v>69</v>
+      </c>
+      <c r="U51" t="s">
+        <v>182</v>
+      </c>
+      <c r="V51" t="s">
+        <v>183</v>
+      </c>
+      <c r="W51" t="s">
+        <v>71</v>
+      </c>
+      <c r="X51" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
@@ -5029,6 +5176,27 @@
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="4"/>
+      <c r="T52" t="s">
+        <v>69</v>
+      </c>
+      <c r="U52" t="s">
+        <v>184</v>
+      </c>
+      <c r="V52" t="s">
+        <v>185</v>
+      </c>
+      <c r="W52" t="s">
+        <v>71</v>
+      </c>
+      <c r="X52" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
@@ -5064,6 +5232,27 @@
       <c r="K53">
         <v>40</v>
       </c>
+      <c r="T53" t="s">
+        <v>69</v>
+      </c>
+      <c r="U53" t="s">
+        <v>186</v>
+      </c>
+      <c r="V53" t="s">
+        <v>188</v>
+      </c>
+      <c r="W53" t="s">
+        <v>71</v>
+      </c>
+      <c r="X53" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
@@ -5099,6 +5288,27 @@
       <c r="K54">
         <v>40</v>
       </c>
+      <c r="T54" t="s">
+        <v>69</v>
+      </c>
+      <c r="U54" t="s">
+        <v>187</v>
+      </c>
+      <c r="V54" t="s">
+        <v>189</v>
+      </c>
+      <c r="W54" t="s">
+        <v>71</v>
+      </c>
+      <c r="X54" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
@@ -5134,6 +5344,27 @@
       <c r="K55">
         <v>40</v>
       </c>
+      <c r="T55" t="s">
+        <v>69</v>
+      </c>
+      <c r="U55" t="s">
+        <v>190</v>
+      </c>
+      <c r="V55" t="s">
+        <v>191</v>
+      </c>
+      <c r="W55" t="s">
+        <v>71</v>
+      </c>
+      <c r="X55" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
@@ -5169,6 +5400,27 @@
       <c r="K56">
         <v>40</v>
       </c>
+      <c r="T56" t="s">
+        <v>69</v>
+      </c>
+      <c r="U56" t="s">
+        <v>18</v>
+      </c>
+      <c r="V56" t="s">
+        <v>78</v>
+      </c>
+      <c r="W56" t="s">
+        <v>71</v>
+      </c>
+      <c r="X56" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
@@ -5238,282 +5490,6 @@
       </c>
       <c r="K58">
         <v>40</v>
-      </c>
-    </row>
-    <row r="63" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T63" t="s">
-        <v>69</v>
-      </c>
-      <c r="U63" t="s">
-        <v>22</v>
-      </c>
-      <c r="V63" t="s">
-        <v>78</v>
-      </c>
-      <c r="W63" t="s">
-        <v>71</v>
-      </c>
-      <c r="X63" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y63" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="64" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T64" t="s">
-        <v>69</v>
-      </c>
-      <c r="U64" t="s">
-        <v>25</v>
-      </c>
-      <c r="V64" t="s">
-        <v>78</v>
-      </c>
-      <c r="W64" t="s">
-        <v>71</v>
-      </c>
-      <c r="X64" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T65" t="s">
-        <v>69</v>
-      </c>
-      <c r="U65" t="s">
-        <v>27</v>
-      </c>
-      <c r="V65" t="s">
-        <v>78</v>
-      </c>
-      <c r="W65" t="s">
-        <v>71</v>
-      </c>
-      <c r="X65" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T66" t="s">
-        <v>69</v>
-      </c>
-      <c r="U66" t="s">
-        <v>29</v>
-      </c>
-      <c r="V66" t="s">
-        <v>78</v>
-      </c>
-      <c r="W66" t="s">
-        <v>71</v>
-      </c>
-      <c r="X66" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T67" t="s">
-        <v>69</v>
-      </c>
-      <c r="U67" t="s">
-        <v>30</v>
-      </c>
-      <c r="V67" t="s">
-        <v>78</v>
-      </c>
-      <c r="W67" t="s">
-        <v>71</v>
-      </c>
-      <c r="X67" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T68" t="s">
-        <v>69</v>
-      </c>
-      <c r="U68" t="s">
-        <v>32</v>
-      </c>
-      <c r="V68" t="s">
-        <v>78</v>
-      </c>
-      <c r="W68" t="s">
-        <v>71</v>
-      </c>
-      <c r="X68" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T69" t="s">
-        <v>69</v>
-      </c>
-      <c r="U69" t="s">
-        <v>34</v>
-      </c>
-      <c r="V69" t="s">
-        <v>78</v>
-      </c>
-      <c r="W69" t="s">
-        <v>71</v>
-      </c>
-      <c r="X69" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T70" t="s">
-        <v>69</v>
-      </c>
-      <c r="U70" t="s">
-        <v>35</v>
-      </c>
-      <c r="V70" t="s">
-        <v>78</v>
-      </c>
-      <c r="W70" t="s">
-        <v>71</v>
-      </c>
-      <c r="X70" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T71" t="s">
-        <v>69</v>
-      </c>
-      <c r="U71" t="s">
-        <v>37</v>
-      </c>
-      <c r="V71" t="s">
-        <v>78</v>
-      </c>
-      <c r="W71" t="s">
-        <v>71</v>
-      </c>
-      <c r="X71" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z71" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T72" t="s">
-        <v>69</v>
-      </c>
-      <c r="U72" t="s">
-        <v>39</v>
-      </c>
-      <c r="V72" t="s">
-        <v>78</v>
-      </c>
-      <c r="W72" t="s">
-        <v>71</v>
-      </c>
-      <c r="X72" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y72" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z72" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T73" t="s">
-        <v>69</v>
-      </c>
-      <c r="U73" t="s">
-        <v>40</v>
-      </c>
-      <c r="V73" t="s">
-        <v>78</v>
-      </c>
-      <c r="W73" t="s">
-        <v>71</v>
-      </c>
-      <c r="X73" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y73" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T74" t="s">
-        <v>69</v>
-      </c>
-      <c r="U74" t="s">
-        <v>42</v>
-      </c>
-      <c r="V74" t="s">
-        <v>78</v>
-      </c>
-      <c r="W74" t="s">
-        <v>71</v>
-      </c>
-      <c r="X74" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y74" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z74" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="75" spans="2:26" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9849CC3-C1F1-4279-9AD0-5DA029C188B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EA16F8-C75C-4769-AB37-A4A5C4D309AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="220">
   <si>
     <t>~fi_t</t>
   </si>
@@ -805,6 +805,9 @@
   </si>
   <si>
     <t>Aggregated Plant of windon except sopi plants</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_iru</t>
   </si>
 </sst>
 </file>
@@ -3497,7 +3500,7 @@
         <v>69</v>
       </c>
       <c r="U23" t="s">
-        <v>17</v>
+        <v>219</v>
       </c>
       <c r="V23" t="s">
         <v>76</v>
@@ -3819,7 +3822,7 @@
     </row>
     <row r="30" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>17</v>
+        <v>219</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EA16F8-C75C-4769-AB37-A4A5C4D309AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B26F173-5A6A-4989-8ECA-E54C352AAEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -5495,12 +5495,32 @@
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59">
+        <v>2022</v>
+      </c>
+      <c r="F59">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G59">
+        <v>0.33123000000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="20:26" x14ac:dyDescent="0.25">
       <c r="U75" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="76" spans="20:26" x14ac:dyDescent="0.25">
       <c r="T76" t="s">
         <v>69</v>
       </c>
@@ -5523,7 +5543,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="77" spans="20:26" x14ac:dyDescent="0.25">
       <c r="T77" t="s">
         <v>69</v>
       </c>
@@ -5546,25 +5566,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="78" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" t="s">
-        <v>19</v>
-      </c>
-      <c r="D78" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78">
-        <v>2022</v>
-      </c>
-      <c r="F78">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G78">
-        <v>0.33123000000000002</v>
-      </c>
+    <row r="78" spans="20:26" x14ac:dyDescent="0.25">
       <c r="T78" t="s">
         <v>69</v>
       </c>
@@ -5587,7 +5589,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="79" spans="20:26" x14ac:dyDescent="0.25">
       <c r="T79" t="s">
         <v>69</v>
       </c>
@@ -5610,7 +5612,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="80" spans="20:26" x14ac:dyDescent="0.25">
       <c r="T80" t="s">
         <v>69</v>
       </c>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B26F173-5A6A-4989-8ECA-E54C352AAEF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE08A75-8877-4E2D-8649-BCD8DF2547BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -77,7 +77,7 @@
     <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
   </authors>
   <commentList>
-    <comment ref="Y23" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+    <comment ref="Z23" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -110,7 +110,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="N43" authorId="4" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+    <comment ref="O43" authorId="4" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -119,7 +119,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="Q47" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+    <comment ref="R47" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -127,7 +127,7 @@
     Took same as chp</t>
       </text>
     </comment>
-    <comment ref="T84" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <comment ref="U84" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="221">
   <si>
     <t>~fi_t</t>
   </si>
@@ -808,6 +808,9 @@
   </si>
   <si>
     <t>ep_bioenergy_iru</t>
+  </si>
+  <si>
+    <t>ncap_af</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1214,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="Y23" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+  <threadedComment ref="Z23" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
     <text>Miks daynite (hydro samuti)</text>
   </threadedComment>
   <threadedComment ref="F30" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
@@ -1224,14 +1227,14 @@
     <text xml:space="preserve">Ei tea
 </text>
   </threadedComment>
-  <threadedComment ref="N43" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+  <threadedComment ref="O43" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
     <text xml:space="preserve">NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)
 </text>
   </threadedComment>
-  <threadedComment ref="Q47" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+  <threadedComment ref="R47" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
     <text>Took same as chp</text>
   </threadedComment>
-  <threadedComment ref="T84" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+  <threadedComment ref="U84" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
   </threadedComment>
   <threadedComment ref="J85" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
@@ -2725,7 +2728,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:Z105"/>
+  <dimension ref="B9:AA105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
@@ -2738,25 +2741,26 @@
     <col min="9" max="9" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="64.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="64.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="64.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -2788,31 +2792,31 @@
         <v>10</v>
       </c>
       <c r="L10" t="s">
-        <v>11</v>
-      </c>
-      <c r="T10" t="s">
+        <v>220</v>
+      </c>
+      <c r="U10" t="s">
         <v>63</v>
       </c>
-      <c r="U10" t="s">
+      <c r="V10" t="s">
         <v>1</v>
       </c>
-      <c r="V10" t="s">
+      <c r="W10" t="s">
         <v>64</v>
       </c>
-      <c r="W10" t="s">
+      <c r="X10" t="s">
         <v>65</v>
       </c>
-      <c r="X10" t="s">
+      <c r="Y10" t="s">
         <v>66</v>
       </c>
-      <c r="Y10" t="s">
+      <c r="Z10" t="s">
         <v>67</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="AA10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>22</v>
       </c>
@@ -2834,29 +2838,29 @@
       <c r="L11">
         <v>0.14986856628506873</v>
       </c>
-      <c r="T11" t="s">
-        <v>69</v>
-      </c>
       <c r="U11" t="s">
+        <v>69</v>
+      </c>
+      <c r="V11" t="s">
         <v>22</v>
       </c>
-      <c r="V11" t="s">
+      <c r="W11" t="s">
         <v>78</v>
       </c>
-      <c r="W11" t="s">
-        <v>71</v>
-      </c>
       <c r="X11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y11" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>25</v>
       </c>
@@ -2878,29 +2882,29 @@
       <c r="L12">
         <v>0.14986856628506873</v>
       </c>
-      <c r="T12" t="s">
-        <v>69</v>
-      </c>
       <c r="U12" t="s">
+        <v>69</v>
+      </c>
+      <c r="V12" t="s">
         <v>25</v>
       </c>
-      <c r="V12" t="s">
+      <c r="W12" t="s">
         <v>78</v>
       </c>
-      <c r="W12" t="s">
-        <v>71</v>
-      </c>
       <c r="X12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y12" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -2922,29 +2926,29 @@
       <c r="L13">
         <v>0.14986856628506873</v>
       </c>
-      <c r="T13" t="s">
-        <v>69</v>
-      </c>
       <c r="U13" t="s">
+        <v>69</v>
+      </c>
+      <c r="V13" t="s">
         <v>27</v>
       </c>
-      <c r="V13" t="s">
+      <c r="W13" t="s">
         <v>78</v>
       </c>
-      <c r="W13" t="s">
-        <v>71</v>
-      </c>
       <c r="X13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y13" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>29</v>
       </c>
@@ -2978,29 +2982,29 @@
       <c r="L14">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T14" t="s">
-        <v>69</v>
-      </c>
       <c r="U14" t="s">
+        <v>69</v>
+      </c>
+      <c r="V14" t="s">
         <v>29</v>
       </c>
-      <c r="V14" t="s">
+      <c r="W14" t="s">
         <v>78</v>
       </c>
-      <c r="W14" t="s">
-        <v>71</v>
-      </c>
       <c r="X14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y14" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z14" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>29</v>
       </c>
@@ -3034,29 +3038,29 @@
       <c r="L15">
         <v>0.1461854238754417</v>
       </c>
-      <c r="T15" t="s">
-        <v>69</v>
-      </c>
       <c r="U15" t="s">
+        <v>69</v>
+      </c>
+      <c r="V15" t="s">
         <v>30</v>
       </c>
-      <c r="V15" t="s">
+      <c r="W15" t="s">
         <v>78</v>
       </c>
-      <c r="W15" t="s">
-        <v>71</v>
-      </c>
       <c r="X15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y15" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>30</v>
       </c>
@@ -3090,29 +3094,29 @@
       <c r="L16">
         <v>0.14867925344692126</v>
       </c>
-      <c r="T16" t="s">
-        <v>69</v>
-      </c>
       <c r="U16" t="s">
+        <v>69</v>
+      </c>
+      <c r="V16" t="s">
         <v>32</v>
       </c>
-      <c r="V16" t="s">
+      <c r="W16" t="s">
         <v>78</v>
       </c>
-      <c r="W16" t="s">
-        <v>71</v>
-      </c>
       <c r="X16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y16" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z16" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA16" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>32</v>
       </c>
@@ -3146,29 +3150,29 @@
       <c r="L17">
         <v>0.14701259708091721</v>
       </c>
-      <c r="T17" t="s">
-        <v>69</v>
-      </c>
       <c r="U17" t="s">
+        <v>69</v>
+      </c>
+      <c r="V17" t="s">
         <v>34</v>
       </c>
-      <c r="V17" t="s">
+      <c r="W17" t="s">
         <v>78</v>
       </c>
-      <c r="W17" t="s">
-        <v>71</v>
-      </c>
       <c r="X17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y17" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z17" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>34</v>
       </c>
@@ -3202,35 +3206,35 @@
       <c r="L18">
         <v>0.15309859852159369</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>3.9363662143155967E-2</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0.28763633785684395</v>
       </c>
-      <c r="T18" t="s">
-        <v>69</v>
-      </c>
       <c r="U18" t="s">
+        <v>69</v>
+      </c>
+      <c r="V18" t="s">
         <v>35</v>
       </c>
-      <c r="V18" t="s">
+      <c r="W18" t="s">
         <v>78</v>
       </c>
-      <c r="W18" t="s">
-        <v>71</v>
-      </c>
       <c r="X18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y18" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z18" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3264,29 +3268,29 @@
       <c r="L19">
         <v>0.15309859852159369</v>
       </c>
-      <c r="T19" t="s">
-        <v>69</v>
-      </c>
       <c r="U19" t="s">
+        <v>69</v>
+      </c>
+      <c r="V19" t="s">
         <v>37</v>
       </c>
-      <c r="V19" t="s">
+      <c r="W19" t="s">
         <v>78</v>
       </c>
-      <c r="W19" t="s">
-        <v>71</v>
-      </c>
       <c r="X19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y19" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z19" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA19" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>35</v>
       </c>
@@ -3320,37 +3324,37 @@
       <c r="L20">
         <v>0.15619560585976827</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <f>SUM(F11:F25)</f>
         <v>0.92963633785684396</v>
       </c>
-      <c r="P20">
-        <f>0.969-F13-O20</f>
+      <c r="Q20">
+        <f>0.969-F13-P20</f>
         <v>-0.28763633785684384</v>
       </c>
-      <c r="T20" t="s">
-        <v>69</v>
-      </c>
       <c r="U20" t="s">
+        <v>69</v>
+      </c>
+      <c r="V20" t="s">
         <v>39</v>
       </c>
-      <c r="V20" t="s">
+      <c r="W20" t="s">
         <v>78</v>
       </c>
-      <c r="W20" t="s">
-        <v>71</v>
-      </c>
       <c r="X20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y20" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z20" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>37</v>
       </c>
@@ -3384,29 +3388,29 @@
       <c r="L21">
         <v>0.14537310453496291</v>
       </c>
-      <c r="T21" t="s">
-        <v>69</v>
-      </c>
       <c r="U21" t="s">
+        <v>69</v>
+      </c>
+      <c r="V21" t="s">
         <v>40</v>
       </c>
-      <c r="V21" t="s">
+      <c r="W21" t="s">
         <v>78</v>
       </c>
-      <c r="W21" t="s">
-        <v>71</v>
-      </c>
       <c r="X21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y21" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>39</v>
       </c>
@@ -3440,29 +3444,29 @@
       <c r="L22">
         <v>0.14763873655681015</v>
       </c>
-      <c r="T22" t="s">
-        <v>69</v>
-      </c>
       <c r="U22" t="s">
+        <v>69</v>
+      </c>
+      <c r="V22" t="s">
         <v>42</v>
       </c>
-      <c r="V22" t="s">
+      <c r="W22" t="s">
         <v>78</v>
       </c>
-      <c r="W22" t="s">
-        <v>71</v>
-      </c>
       <c r="X22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y22" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z22" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA22" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>40</v>
       </c>
@@ -3496,29 +3500,29 @@
       <c r="L23">
         <v>0.1532628310027955</v>
       </c>
-      <c r="T23" t="s">
-        <v>69</v>
-      </c>
       <c r="U23" t="s">
+        <v>69</v>
+      </c>
+      <c r="V23" t="s">
         <v>219</v>
       </c>
-      <c r="V23" t="s">
+      <c r="W23" t="s">
         <v>76</v>
       </c>
-      <c r="W23" t="s">
-        <v>71</v>
-      </c>
       <c r="X23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y23" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z23" t="s">
         <v>73</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="AA23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>40</v>
       </c>
@@ -3552,33 +3556,33 @@
       <c r="L24">
         <v>0.1532628310027955</v>
       </c>
-      <c r="P24">
-        <f>SUM(O20:P20)+F13</f>
+      <c r="Q24">
+        <f>SUM(P20:Q20)+F13</f>
         <v>0.96900000000000008</v>
       </c>
-      <c r="T24" t="s">
-        <v>69</v>
-      </c>
       <c r="U24" t="s">
+        <v>69</v>
+      </c>
+      <c r="V24" t="s">
         <v>61</v>
       </c>
-      <c r="V24" t="s">
+      <c r="W24" t="s">
         <v>81</v>
       </c>
-      <c r="W24" t="s">
-        <v>71</v>
-      </c>
       <c r="X24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y24" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z24" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA24" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>42</v>
       </c>
@@ -3612,29 +3616,29 @@
       <c r="L25">
         <v>0.1451997589052581</v>
       </c>
-      <c r="T25" t="s">
-        <v>69</v>
-      </c>
       <c r="U25" t="s">
+        <v>69</v>
+      </c>
+      <c r="V25" t="s">
         <v>216</v>
       </c>
-      <c r="V25" t="s">
+      <c r="W25" t="s">
         <v>81</v>
       </c>
-      <c r="W25" t="s">
-        <v>71</v>
-      </c>
       <c r="X25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y25" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z25" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA25" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>61</v>
       </c>
@@ -3668,29 +3672,29 @@
       <c r="L26">
         <v>0.365520596150406</v>
       </c>
-      <c r="T26" t="s">
-        <v>69</v>
-      </c>
       <c r="U26" t="s">
+        <v>69</v>
+      </c>
+      <c r="V26" t="s">
         <v>217</v>
       </c>
-      <c r="V26" t="s">
+      <c r="W26" t="s">
         <v>218</v>
       </c>
-      <c r="W26" t="s">
-        <v>71</v>
-      </c>
       <c r="X26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y26" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z26" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA26" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>216</v>
       </c>
@@ -3724,18 +3728,18 @@
       <c r="L27">
         <v>0.365520596150406</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <f>F90*L90*G90</f>
         <v>2.0930123559331545E-3</v>
       </c>
-      <c r="T27" t="s">
+      <c r="U27" t="s">
         <v>140</v>
       </c>
-      <c r="U27" s="1" t="s">
+      <c r="V27" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>217</v>
       </c>
@@ -3769,58 +3773,58 @@
       <c r="L28">
         <v>0.41047488326249421</v>
       </c>
-      <c r="T28" t="s">
-        <v>69</v>
-      </c>
       <c r="U28" t="s">
+        <v>69</v>
+      </c>
+      <c r="V28" t="s">
         <v>194</v>
       </c>
-      <c r="V28" t="s">
+      <c r="W28" t="s">
         <v>163</v>
       </c>
-      <c r="W28" t="s">
-        <v>71</v>
-      </c>
       <c r="X28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y28" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z28" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA28" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>140</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="T29" t="s">
-        <v>69</v>
-      </c>
       <c r="U29" t="s">
+        <v>69</v>
+      </c>
+      <c r="V29" t="s">
         <v>193</v>
       </c>
-      <c r="V29" t="s">
+      <c r="W29" t="s">
         <v>148</v>
       </c>
-      <c r="W29" t="s">
-        <v>71</v>
-      </c>
       <c r="X29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y29" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z29" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA29" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>219</v>
       </c>
@@ -3837,46 +3841,49 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="G30">
-        <f>P45</f>
+        <f>Q45</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="H30" s="2">
         <v>1175.5066999999999</v>
       </c>
       <c r="I30" s="3">
-        <f>(N45/100)*H31</f>
+        <f>(O45/100)*H31</f>
         <v>160.216352398</v>
       </c>
       <c r="J30">
-        <f>Q45</f>
+        <f>R45</f>
         <v>5.8775000000000004</v>
       </c>
       <c r="K30">
         <v>53</v>
       </c>
-      <c r="T30" t="s">
-        <v>69</v>
+      <c r="L30">
+        <v>0.8</v>
       </c>
       <c r="U30" t="s">
+        <v>69</v>
+      </c>
+      <c r="V30" t="s">
         <v>195</v>
       </c>
-      <c r="V30" t="s">
+      <c r="W30" t="s">
         <v>149</v>
       </c>
-      <c r="W30" t="s">
-        <v>71</v>
-      </c>
       <c r="X30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y30" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z30" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA30" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>196</v>
       </c>
@@ -3893,7 +3900,7 @@
         <v>0.77</v>
       </c>
       <c r="G31">
-        <f>$P$44</f>
+        <f>$Q$44</f>
         <v>0.33</v>
       </c>
       <c r="H31" s="2">
@@ -3904,35 +3911,38 @@
         <v>63.037519640000006</v>
       </c>
       <c r="J31">
-        <f>$Q$44</f>
+        <f>$R$44</f>
         <v>4.1005000000000003</v>
       </c>
       <c r="K31">
         <v>70</v>
       </c>
-      <c r="T31" t="s">
-        <v>69</v>
+      <c r="L31">
+        <v>0.8</v>
       </c>
       <c r="U31" t="s">
+        <v>69</v>
+      </c>
+      <c r="V31" t="s">
         <v>196</v>
       </c>
-      <c r="V31" t="s">
+      <c r="W31" t="s">
         <v>150</v>
       </c>
-      <c r="W31" t="s">
-        <v>71</v>
-      </c>
       <c r="X31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y31" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z31" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA31" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>194</v>
       </c>
@@ -3949,7 +3959,7 @@
         <v>0.26</v>
       </c>
       <c r="G32">
-        <f t="shared" ref="G32:G34" si="0">$P$44</f>
+        <f t="shared" ref="G32:G34" si="0">$Q$44</f>
         <v>0.33</v>
       </c>
       <c r="H32" s="2">
@@ -3960,35 +3970,38 @@
         <v>63.037519640000006</v>
       </c>
       <c r="J32">
-        <f t="shared" ref="J32:J48" si="1">$Q$44</f>
+        <f t="shared" ref="J32:J48" si="1">$R$44</f>
         <v>4.1005000000000003</v>
       </c>
       <c r="K32">
         <v>40</v>
       </c>
-      <c r="T32" t="s">
-        <v>69</v>
+      <c r="L32">
+        <v>0.7</v>
       </c>
       <c r="U32" t="s">
+        <v>69</v>
+      </c>
+      <c r="V32" t="s">
         <v>142</v>
       </c>
-      <c r="V32" t="s">
+      <c r="W32" t="s">
         <v>161</v>
       </c>
-      <c r="W32" t="s">
-        <v>71</v>
-      </c>
       <c r="X32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y32" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z32" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA32" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>195</v>
       </c>
@@ -4016,35 +4029,38 @@
         <v>63.037519640000006</v>
       </c>
       <c r="J33">
-        <f>$Q$44</f>
+        <f>$R$44</f>
         <v>4.1005000000000003</v>
       </c>
       <c r="K33">
         <v>40</v>
       </c>
-      <c r="T33" t="s">
-        <v>69</v>
+      <c r="L33">
+        <v>0.8</v>
       </c>
       <c r="U33" t="s">
+        <v>69</v>
+      </c>
+      <c r="V33" t="s">
         <v>143</v>
       </c>
-      <c r="V33" t="s">
+      <c r="W33" t="s">
         <v>151</v>
       </c>
-      <c r="W33" t="s">
-        <v>71</v>
-      </c>
       <c r="X33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y33" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z33" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA33" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>193</v>
       </c>
@@ -4078,29 +4094,32 @@
       <c r="K34">
         <v>73</v>
       </c>
-      <c r="T34" t="s">
-        <v>69</v>
+      <c r="L34">
+        <v>0.8</v>
       </c>
       <c r="U34" t="s">
+        <v>69</v>
+      </c>
+      <c r="V34" t="s">
         <v>144</v>
       </c>
-      <c r="V34" t="s">
+      <c r="W34" t="s">
         <v>152</v>
       </c>
-      <c r="W34" t="s">
-        <v>71</v>
-      </c>
       <c r="X34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y34" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA34" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>142</v>
       </c>
@@ -4117,47 +4136,50 @@
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="G35">
+        <f>Q45</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H35" s="2">
         <f>P45</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H35" s="2">
-        <f>O45</f>
         <v>1175.5066999999999</v>
       </c>
       <c r="I35" s="3">
-        <f>(N45/100)*H35</f>
+        <f>(O45/100)*H35</f>
         <v>39.138495576499992</v>
       </c>
       <c r="J35">
-        <f>$Q$45</f>
+        <f>$R$45</f>
         <v>5.8775000000000004</v>
       </c>
       <c r="K35">
         <v>40</v>
       </c>
-      <c r="T35" t="s">
-        <v>69</v>
+      <c r="L35">
+        <v>0.8</v>
       </c>
       <c r="U35" t="s">
+        <v>69</v>
+      </c>
+      <c r="V35" t="s">
         <v>145</v>
       </c>
-      <c r="V35" t="s">
+      <c r="W35" t="s">
         <v>153</v>
       </c>
-      <c r="W35" t="s">
-        <v>71</v>
-      </c>
       <c r="X35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y35" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z35" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA35" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>143</v>
       </c>
@@ -4174,11 +4196,11 @@
         <v>3.9E-2</v>
       </c>
       <c r="G36">
-        <f>P47</f>
+        <f>Q47</f>
         <v>0.46800000000000003</v>
       </c>
       <c r="H36" s="2">
-        <f>$O$47</f>
+        <f>$P$47</f>
         <v>2950.7891</v>
       </c>
       <c r="I36" s="3">
@@ -4186,35 +4208,38 @@
         <v>133.5792717679</v>
       </c>
       <c r="J36">
-        <f>$Q$47</f>
+        <f>$R$47</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K36">
         <v>40</v>
       </c>
-      <c r="T36" t="s">
-        <v>69</v>
+      <c r="L36">
+        <v>0.8</v>
       </c>
       <c r="U36" t="s">
+        <v>69</v>
+      </c>
+      <c r="V36" t="s">
         <v>146</v>
       </c>
-      <c r="V36" t="s">
+      <c r="W36" t="s">
         <v>147</v>
       </c>
-      <c r="W36" t="s">
-        <v>71</v>
-      </c>
       <c r="X36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y36" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z36" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA36" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>144</v>
       </c>
@@ -4234,7 +4259,7 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="H37" s="2">
-        <f t="shared" ref="H37:H39" si="2">$O$47</f>
+        <f t="shared" ref="H37:H39" si="2">$P$47</f>
         <v>2950.7891</v>
       </c>
       <c r="I37" s="3">
@@ -4242,35 +4267,38 @@
         <v>133.5792717679</v>
       </c>
       <c r="J37">
-        <f t="shared" ref="J37:J39" si="4">$Q$47</f>
+        <f t="shared" ref="J37:J39" si="4">$R$47</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K37">
         <v>40</v>
       </c>
-      <c r="T37" t="s">
-        <v>69</v>
+      <c r="L37">
+        <v>0.8</v>
       </c>
       <c r="U37" t="s">
+        <v>69</v>
+      </c>
+      <c r="V37" t="s">
         <v>197</v>
       </c>
-      <c r="V37" t="s">
+      <c r="W37" t="s">
         <v>162</v>
       </c>
-      <c r="W37" t="s">
-        <v>71</v>
-      </c>
       <c r="X37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y37" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z37" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA37" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>145</v>
       </c>
@@ -4304,29 +4332,32 @@
       <c r="K38">
         <v>40</v>
       </c>
-      <c r="T38" t="s">
-        <v>69</v>
+      <c r="L38">
+        <v>0.8</v>
       </c>
       <c r="U38" t="s">
+        <v>69</v>
+      </c>
+      <c r="V38" t="s">
         <v>154</v>
       </c>
-      <c r="V38" t="s">
+      <c r="W38" t="s">
         <v>155</v>
       </c>
-      <c r="W38" t="s">
-        <v>71</v>
-      </c>
       <c r="X38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y38" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z38" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA38" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>146</v>
       </c>
@@ -4360,29 +4391,32 @@
       <c r="K39">
         <v>40</v>
       </c>
-      <c r="T39" t="s">
-        <v>69</v>
+      <c r="L39">
+        <v>0.8</v>
       </c>
       <c r="U39" t="s">
+        <v>69</v>
+      </c>
+      <c r="V39" t="s">
         <v>156</v>
       </c>
-      <c r="V39" t="s">
+      <c r="W39" t="s">
         <v>157</v>
       </c>
-      <c r="W39" t="s">
-        <v>71</v>
-      </c>
       <c r="X39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y39" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z39" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA39" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>197</v>
       </c>
@@ -4399,47 +4433,50 @@
         <v>0.01</v>
       </c>
       <c r="G40">
+        <f>Q44</f>
+        <v>0.33</v>
+      </c>
+      <c r="H40" s="2">
         <f>P44</f>
-        <v>0.33</v>
-      </c>
-      <c r="H40" s="2">
-        <f>O44</f>
         <v>4812.0244000000002</v>
       </c>
       <c r="I40" s="3">
-        <f>($N$44/100)*H40</f>
+        <f>($O$44/100)*H40</f>
         <v>63.037519640000006</v>
       </c>
       <c r="J40">
-        <f>$Q$44</f>
+        <f>$R$44</f>
         <v>4.1005000000000003</v>
       </c>
       <c r="K40">
         <v>40</v>
       </c>
-      <c r="T40" t="s">
-        <v>69</v>
+      <c r="L40">
+        <v>0.8</v>
       </c>
       <c r="U40" t="s">
+        <v>69</v>
+      </c>
+      <c r="V40" t="s">
         <v>170</v>
       </c>
-      <c r="V40" t="s">
+      <c r="W40" t="s">
         <v>171</v>
       </c>
-      <c r="W40" t="s">
-        <v>71</v>
-      </c>
       <c r="X40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y40" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z40" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA40" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>154</v>
       </c>
@@ -4459,43 +4496,46 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H41" s="2">
-        <f>$O$48</f>
+        <f>$P$48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I41" s="3">
-        <f>($N$48/100)*H41</f>
+        <f>($O$48/100)*H41</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J41">
-        <f>$Q$48</f>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K41">
         <v>40</v>
       </c>
-      <c r="T41" t="s">
-        <v>69</v>
+      <c r="L41">
+        <v>0.8</v>
       </c>
       <c r="U41" t="s">
+        <v>69</v>
+      </c>
+      <c r="V41" t="s">
         <v>158</v>
       </c>
-      <c r="V41" t="s">
+      <c r="W41" t="s">
         <v>159</v>
       </c>
-      <c r="W41" t="s">
-        <v>71</v>
-      </c>
       <c r="X41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y41" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z41" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA41" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>156</v>
       </c>
@@ -4515,43 +4555,46 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H42" s="2">
-        <f t="shared" ref="H42:H44" si="5">$O$48</f>
+        <f t="shared" ref="H42:H44" si="5">$P$48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I42" s="3">
-        <f t="shared" ref="I42:I44" si="6">($N$48/100)*H42</f>
+        <f t="shared" ref="I42:I44" si="6">($O$48/100)*H42</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J42">
-        <f t="shared" ref="J42:J44" si="7">$Q$48</f>
+        <f t="shared" ref="J42:J44" si="7">$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K42">
         <v>40</v>
       </c>
-      <c r="T42" t="s">
-        <v>69</v>
+      <c r="L42">
+        <v>0.8</v>
       </c>
       <c r="U42" t="s">
+        <v>69</v>
+      </c>
+      <c r="V42" t="s">
         <v>169</v>
       </c>
-      <c r="V42" t="s">
+      <c r="W42" t="s">
         <v>160</v>
       </c>
-      <c r="W42" t="s">
-        <v>71</v>
-      </c>
       <c r="X42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y42" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z42" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA42" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>170</v>
       </c>
@@ -4585,41 +4628,44 @@
       <c r="K43">
         <v>40</v>
       </c>
-      <c r="N43" t="s">
+      <c r="L43">
+        <v>0.8</v>
+      </c>
+      <c r="O43" t="s">
         <v>206</v>
       </c>
-      <c r="O43" t="s">
+      <c r="P43" t="s">
         <v>213</v>
       </c>
-      <c r="P43" t="s">
+      <c r="Q43" t="s">
         <v>214</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
         <v>215</v>
       </c>
-      <c r="T43" t="s">
-        <v>69</v>
-      </c>
       <c r="U43" t="s">
+        <v>69</v>
+      </c>
+      <c r="V43" t="s">
         <v>164</v>
       </c>
-      <c r="V43" t="s">
+      <c r="W43" t="s">
         <v>165</v>
       </c>
-      <c r="W43" t="s">
-        <v>71</v>
-      </c>
       <c r="X43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y43" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z43" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA43" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>158</v>
       </c>
@@ -4653,44 +4699,47 @@
       <c r="K44">
         <v>72</v>
       </c>
-      <c r="M44" t="s">
+      <c r="L44">
+        <v>0.8</v>
+      </c>
+      <c r="N44" t="s">
         <v>192</v>
       </c>
-      <c r="N44" s="4">
+      <c r="O44" s="4">
         <v>1.31</v>
       </c>
-      <c r="O44" s="2">
+      <c r="P44" s="2">
         <v>4812.0244000000002</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>0.33</v>
       </c>
-      <c r="Q44">
+      <c r="R44">
         <v>4.1005000000000003</v>
       </c>
-      <c r="T44" t="s">
-        <v>69</v>
-      </c>
       <c r="U44" t="s">
+        <v>69</v>
+      </c>
+      <c r="V44" t="s">
         <v>168</v>
       </c>
-      <c r="V44" t="s">
+      <c r="W44" t="s">
         <v>166</v>
       </c>
-      <c r="W44" t="s">
-        <v>71</v>
-      </c>
       <c r="X44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y44" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z44" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA44" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>169</v>
       </c>
@@ -4707,62 +4756,65 @@
         <v>5.7999999999999996E-3</v>
       </c>
       <c r="G45">
+        <f>Q45</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H45" s="2">
         <f>P45</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H45" s="2">
-        <f>O45</f>
         <v>1175.5066999999999</v>
       </c>
       <c r="I45" s="3">
-        <f>($N$45/100)*H45</f>
+        <f>($O$45/100)*H45</f>
         <v>39.138495576499992</v>
       </c>
       <c r="J45">
-        <f>$Q$45</f>
+        <f>$R$45</f>
         <v>5.8775000000000004</v>
       </c>
       <c r="K45">
         <v>40</v>
       </c>
-      <c r="M45" t="s">
+      <c r="L45">
+        <v>0.8</v>
+      </c>
+      <c r="N45" t="s">
         <v>211</v>
       </c>
-      <c r="N45" s="4">
+      <c r="O45" s="4">
         <v>3.3294999999999999</v>
       </c>
-      <c r="O45" s="2">
+      <c r="P45" s="2">
         <v>1175.5066999999999</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>0.56000000000000005</v>
       </c>
-      <c r="Q45">
+      <c r="R45">
         <v>5.8775000000000004</v>
       </c>
-      <c r="T45" t="s">
-        <v>69</v>
-      </c>
       <c r="U45" t="s">
+        <v>69</v>
+      </c>
+      <c r="V45" t="s">
         <v>198</v>
       </c>
-      <c r="V45" t="s">
+      <c r="W45" t="s">
         <v>167</v>
       </c>
-      <c r="W45" t="s">
-        <v>71</v>
-      </c>
       <c r="X45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y45" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z45" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA45" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>164</v>
       </c>
@@ -4782,48 +4834,51 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H46" s="2">
-        <f>O48</f>
+        <f>P48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I46" s="3">
-        <f>($N$48/100)*H46</f>
+        <f>($O$48/100)*H46</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J46">
-        <f>$Q$48</f>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K46">
         <v>40</v>
       </c>
-      <c r="M46" t="s">
+      <c r="L46">
+        <v>0.8</v>
+      </c>
+      <c r="N46" t="s">
         <v>212</v>
       </c>
-      <c r="N46" s="4"/>
-      <c r="O46" s="2"/>
-      <c r="T46" t="s">
-        <v>69</v>
-      </c>
+      <c r="O46" s="4"/>
+      <c r="P46" s="2"/>
       <c r="U46" t="s">
+        <v>69</v>
+      </c>
+      <c r="V46" t="s">
         <v>172</v>
       </c>
-      <c r="V46" t="s">
+      <c r="W46" t="s">
         <v>173</v>
       </c>
-      <c r="W46" t="s">
-        <v>71</v>
-      </c>
       <c r="X46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y46" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z46" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA46" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>168</v>
       </c>
@@ -4840,62 +4895,65 @@
         <v>4.0999999999999995E-3</v>
       </c>
       <c r="G47">
+        <f>Q45</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H47" s="2">
         <f>P45</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H47" s="2">
-        <f>O45</f>
         <v>1175.5066999999999</v>
       </c>
       <c r="I47" s="3">
-        <f>($N$45/100)*H47</f>
+        <f>($O$45/100)*H47</f>
         <v>39.138495576499992</v>
       </c>
       <c r="J47">
-        <f>$Q$45</f>
+        <f>$R$45</f>
         <v>5.8775000000000004</v>
       </c>
       <c r="K47">
         <v>40</v>
       </c>
-      <c r="M47" t="s">
+      <c r="L47">
+        <v>0.8</v>
+      </c>
+      <c r="N47" t="s">
         <v>209</v>
       </c>
-      <c r="N47">
+      <c r="O47">
         <v>4.5269000000000004</v>
       </c>
-      <c r="O47" s="2">
+      <c r="P47" s="2">
         <v>2950.7891</v>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>0.46800000000000003</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <v>2.8138000000000001</v>
       </c>
-      <c r="T47" t="s">
-        <v>69</v>
-      </c>
       <c r="U47" t="s">
+        <v>69</v>
+      </c>
+      <c r="V47" t="s">
         <v>174</v>
       </c>
-      <c r="V47" t="s">
+      <c r="W47" t="s">
         <v>175</v>
       </c>
-      <c r="W47" t="s">
-        <v>71</v>
-      </c>
       <c r="X47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y47" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z47" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA47" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>198</v>
       </c>
@@ -4912,15 +4970,15 @@
         <v>1.4E-3</v>
       </c>
       <c r="G48">
+        <f>Q44</f>
+        <v>0.33</v>
+      </c>
+      <c r="H48" s="2">
         <f>P44</f>
-        <v>0.33</v>
-      </c>
-      <c r="H48" s="2">
-        <f>O44</f>
         <v>4812.0244000000002</v>
       </c>
       <c r="I48" s="3">
-        <f>($N$48/100)*H48</f>
+        <f>($O$48/100)*H48</f>
         <v>173.62265237640003</v>
       </c>
       <c r="J48">
@@ -4930,44 +4988,47 @@
       <c r="K48">
         <v>40</v>
       </c>
-      <c r="M48" t="s">
+      <c r="L48">
+        <v>0.8</v>
+      </c>
+      <c r="N48" t="s">
         <v>210</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>3.6080999999999999</v>
       </c>
-      <c r="O48" s="2">
+      <c r="P48" s="2">
         <v>4516.7133000000003</v>
       </c>
-      <c r="P48">
+      <c r="Q48">
         <v>0.2994</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <v>2.8138000000000001</v>
       </c>
-      <c r="T48" t="s">
-        <v>69</v>
-      </c>
       <c r="U48" t="s">
+        <v>69</v>
+      </c>
+      <c r="V48" t="s">
         <v>176</v>
       </c>
-      <c r="V48" t="s">
+      <c r="W48" t="s">
         <v>177</v>
       </c>
-      <c r="W48" t="s">
-        <v>71</v>
-      </c>
       <c r="X48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y48" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z48" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA48" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>172</v>
       </c>
@@ -4987,45 +5048,48 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H49" s="2">
-        <f>O48</f>
+        <f>P48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I49" s="3">
-        <f>($N$48/100)*H49</f>
+        <f>($O$48/100)*H49</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J49">
-        <f>$Q$48</f>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K49">
         <v>40</v>
       </c>
-      <c r="N49" s="3"/>
-      <c r="O49" s="4"/>
-      <c r="T49" t="s">
-        <v>69</v>
-      </c>
+      <c r="L49">
+        <v>0.8</v>
+      </c>
+      <c r="O49" s="3"/>
+      <c r="P49" s="4"/>
       <c r="U49" t="s">
+        <v>69</v>
+      </c>
+      <c r="V49" t="s">
         <v>178</v>
       </c>
-      <c r="V49" t="s">
+      <c r="W49" t="s">
         <v>179</v>
       </c>
-      <c r="W49" t="s">
-        <v>71</v>
-      </c>
       <c r="X49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y49" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z49" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA49" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>174</v>
       </c>
@@ -5045,45 +5109,48 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H50" s="2">
-        <f>O48</f>
+        <f>P48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I50" s="3">
-        <f>($N$48/100)*H50</f>
+        <f>($O$48/100)*H50</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J50">
-        <f>$Q$48</f>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K50">
         <v>40</v>
       </c>
-      <c r="N50" s="3"/>
-      <c r="O50" s="4"/>
-      <c r="T50" t="s">
-        <v>69</v>
-      </c>
+      <c r="L50">
+        <v>0.8</v>
+      </c>
+      <c r="O50" s="3"/>
+      <c r="P50" s="4"/>
       <c r="U50" t="s">
+        <v>69</v>
+      </c>
+      <c r="V50" t="s">
         <v>180</v>
       </c>
-      <c r="V50" t="s">
+      <c r="W50" t="s">
         <v>181</v>
       </c>
-      <c r="W50" t="s">
-        <v>71</v>
-      </c>
       <c r="X50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y50" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z50" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA50" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>176</v>
       </c>
@@ -5100,49 +5167,52 @@
         <v>1.8E-3</v>
       </c>
       <c r="G51">
+        <f>Q45</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H51" s="2">
         <f>P45</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H51" s="2">
-        <f>O45</f>
         <v>1175.5066999999999</v>
       </c>
       <c r="I51" s="3">
-        <f t="shared" ref="I51:I52" si="8">($N$45/100)*H51</f>
+        <f t="shared" ref="I51:I52" si="8">($O$45/100)*H51</f>
         <v>39.138495576499992</v>
       </c>
       <c r="J51">
-        <f>$Q$45</f>
+        <f>$R$45</f>
         <v>5.8775000000000004</v>
       </c>
       <c r="K51">
         <v>40</v>
       </c>
-      <c r="N51" s="3"/>
-      <c r="O51" s="4"/>
-      <c r="T51" t="s">
-        <v>69</v>
-      </c>
+      <c r="L51">
+        <v>0.8</v>
+      </c>
+      <c r="O51" s="3"/>
+      <c r="P51" s="4"/>
       <c r="U51" t="s">
+        <v>69</v>
+      </c>
+      <c r="V51" t="s">
         <v>182</v>
       </c>
-      <c r="V51" t="s">
+      <c r="W51" t="s">
         <v>183</v>
       </c>
-      <c r="W51" t="s">
-        <v>71</v>
-      </c>
       <c r="X51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y51" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z51" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA51" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>178</v>
       </c>
@@ -5159,11 +5229,11 @@
         <v>1.8E-3</v>
       </c>
       <c r="G52">
+        <f>Q45</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H52" s="2">
         <f>P45</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H52" s="2">
-        <f>O45</f>
         <v>1175.5066999999999</v>
       </c>
       <c r="I52" s="3">
@@ -5171,37 +5241,40 @@
         <v>39.138495576499992</v>
       </c>
       <c r="J52">
-        <f>$Q$45</f>
+        <f>$R$45</f>
         <v>5.8775000000000004</v>
       </c>
       <c r="K52">
         <v>40</v>
       </c>
-      <c r="N52" s="3"/>
-      <c r="O52" s="4"/>
-      <c r="T52" t="s">
-        <v>69</v>
-      </c>
+      <c r="L52">
+        <v>0.8</v>
+      </c>
+      <c r="O52" s="3"/>
+      <c r="P52" s="4"/>
       <c r="U52" t="s">
+        <v>69</v>
+      </c>
+      <c r="V52" t="s">
         <v>184</v>
       </c>
-      <c r="V52" t="s">
+      <c r="W52" t="s">
         <v>185</v>
       </c>
-      <c r="W52" t="s">
-        <v>71</v>
-      </c>
       <c r="X52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y52" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z52" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA52" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>180</v>
       </c>
@@ -5221,43 +5294,46 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H53" s="2">
-        <f>O48</f>
+        <f>P48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I53" s="3">
-        <f>($N$48/100)*H53</f>
+        <f>($O$48/100)*H53</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J53">
-        <f>$Q$48</f>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K53">
         <v>40</v>
       </c>
-      <c r="T53" t="s">
-        <v>69</v>
+      <c r="L53">
+        <v>0.8</v>
       </c>
       <c r="U53" t="s">
+        <v>69</v>
+      </c>
+      <c r="V53" t="s">
         <v>186</v>
       </c>
-      <c r="V53" t="s">
+      <c r="W53" t="s">
         <v>188</v>
       </c>
-      <c r="W53" t="s">
-        <v>71</v>
-      </c>
       <c r="X53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y53" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z53" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA53" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>182</v>
       </c>
@@ -5277,43 +5353,46 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H54" s="2">
-        <f>$O$48</f>
+        <f>$P$48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I54" s="3">
-        <f t="shared" ref="I54:I58" si="9">($N$48/100)*H54</f>
+        <f t="shared" ref="I54:I58" si="9">($O$48/100)*H54</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J54">
-        <f t="shared" ref="J54:J58" si="10">$Q$48</f>
+        <f t="shared" ref="J54:J58" si="10">$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K54">
         <v>40</v>
       </c>
-      <c r="T54" t="s">
-        <v>69</v>
+      <c r="L54">
+        <v>0.8</v>
       </c>
       <c r="U54" t="s">
+        <v>69</v>
+      </c>
+      <c r="V54" t="s">
         <v>187</v>
       </c>
-      <c r="V54" t="s">
+      <c r="W54" t="s">
         <v>189</v>
       </c>
-      <c r="W54" t="s">
-        <v>71</v>
-      </c>
       <c r="X54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y54" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z54" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA54" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="55" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>184</v>
       </c>
@@ -5333,7 +5412,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H55" s="2">
-        <f>$O$48</f>
+        <f>$P$48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I55" s="3">
@@ -5347,29 +5426,32 @@
       <c r="K55">
         <v>40</v>
       </c>
-      <c r="T55" t="s">
-        <v>69</v>
+      <c r="L55">
+        <v>0.8</v>
       </c>
       <c r="U55" t="s">
+        <v>69</v>
+      </c>
+      <c r="V55" t="s">
         <v>190</v>
       </c>
-      <c r="V55" t="s">
+      <c r="W55" t="s">
         <v>191</v>
       </c>
-      <c r="W55" t="s">
-        <v>71</v>
-      </c>
       <c r="X55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y55" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z55" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA55" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>186</v>
       </c>
@@ -5389,7 +5471,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H56" s="2">
-        <f>O48</f>
+        <f>P48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I56" s="3">
@@ -5403,29 +5485,32 @@
       <c r="K56">
         <v>40</v>
       </c>
-      <c r="T56" t="s">
-        <v>69</v>
+      <c r="L56">
+        <v>0.8</v>
       </c>
       <c r="U56" t="s">
+        <v>69</v>
+      </c>
+      <c r="V56" t="s">
         <v>18</v>
       </c>
-      <c r="V56" t="s">
+      <c r="W56" t="s">
         <v>78</v>
       </c>
-      <c r="W56" t="s">
-        <v>71</v>
-      </c>
       <c r="X56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y56" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z56" t="s">
         <v>73</v>
       </c>
-      <c r="Z56" t="s">
+      <c r="AA56" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="57" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>187</v>
       </c>
@@ -5445,7 +5530,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H57" s="2">
-        <f>O48</f>
+        <f>P48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I57" s="3">
@@ -5459,8 +5544,11 @@
       <c r="K57">
         <v>40</v>
       </c>
-    </row>
-    <row r="58" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="L57">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="58" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>190</v>
       </c>
@@ -5480,7 +5568,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H58" s="2">
-        <f>O48</f>
+        <f>P48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I58" s="3">
@@ -5494,8 +5582,11 @@
       <c r="K58">
         <v>40</v>
       </c>
-    </row>
-    <row r="59" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="L58">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>18</v>
       </c>
@@ -5514,151 +5605,154 @@
       <c r="G59">
         <v>0.33123000000000002</v>
       </c>
-    </row>
-    <row r="75" spans="20:26" x14ac:dyDescent="0.25">
-      <c r="U75" t="s">
+      <c r="L59">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="75" spans="21:27" x14ac:dyDescent="0.25">
+      <c r="V75" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="76" spans="20:26" x14ac:dyDescent="0.25">
-      <c r="T76" t="s">
-        <v>69</v>
-      </c>
+    <row r="76" spans="21:27" x14ac:dyDescent="0.25">
       <c r="U76" t="s">
+        <v>69</v>
+      </c>
+      <c r="V76" t="s">
         <v>44</v>
       </c>
-      <c r="V76" t="s">
+      <c r="W76" t="s">
         <v>78</v>
       </c>
-      <c r="W76" t="s">
-        <v>71</v>
-      </c>
       <c r="X76" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y76" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z76" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA76" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="20:26" x14ac:dyDescent="0.25">
-      <c r="T77" t="s">
-        <v>69</v>
-      </c>
+    <row r="77" spans="21:27" x14ac:dyDescent="0.25">
       <c r="U77" t="s">
+        <v>69</v>
+      </c>
+      <c r="V77" t="s">
         <v>47</v>
       </c>
-      <c r="V77" t="s">
+      <c r="W77" t="s">
         <v>78</v>
       </c>
-      <c r="W77" t="s">
-        <v>71</v>
-      </c>
       <c r="X77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y77" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z77" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA77" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="78" spans="20:26" x14ac:dyDescent="0.25">
-      <c r="T78" t="s">
-        <v>69</v>
-      </c>
+    <row r="78" spans="21:27" x14ac:dyDescent="0.25">
       <c r="U78" t="s">
+        <v>69</v>
+      </c>
+      <c r="V78" t="s">
         <v>49</v>
       </c>
-      <c r="V78" t="s">
+      <c r="W78" t="s">
         <v>78</v>
       </c>
-      <c r="W78" t="s">
-        <v>71</v>
-      </c>
       <c r="X78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y78" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z78" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA78" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="79" spans="20:26" x14ac:dyDescent="0.25">
-      <c r="T79" t="s">
-        <v>69</v>
-      </c>
+    <row r="79" spans="21:27" x14ac:dyDescent="0.25">
       <c r="U79" t="s">
+        <v>69</v>
+      </c>
+      <c r="V79" t="s">
         <v>51</v>
       </c>
-      <c r="V79" t="s">
+      <c r="W79" t="s">
         <v>78</v>
       </c>
-      <c r="W79" t="s">
-        <v>71</v>
-      </c>
       <c r="X79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y79" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z79" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA79" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="20:26" x14ac:dyDescent="0.25">
-      <c r="T80" t="s">
-        <v>69</v>
-      </c>
+    <row r="80" spans="21:27" x14ac:dyDescent="0.25">
       <c r="U80" t="s">
+        <v>69</v>
+      </c>
+      <c r="V80" t="s">
         <v>53</v>
       </c>
-      <c r="V80" t="s">
+      <c r="W80" t="s">
         <v>78</v>
       </c>
-      <c r="W80" t="s">
-        <v>71</v>
-      </c>
       <c r="X80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y80" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z80" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA80" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="81" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T81" t="s">
-        <v>69</v>
-      </c>
+    <row r="81" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U81" t="s">
+        <v>69</v>
+      </c>
+      <c r="V81" t="s">
         <v>55</v>
       </c>
-      <c r="V81" t="s">
+      <c r="W81" t="s">
         <v>78</v>
       </c>
-      <c r="W81" t="s">
-        <v>71</v>
-      </c>
       <c r="X81" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y81" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z81" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA81" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>20</v>
       </c>
@@ -5689,29 +5783,29 @@
       <c r="K82">
         <v>42</v>
       </c>
-      <c r="T82" t="s">
-        <v>69</v>
-      </c>
       <c r="U82" t="s">
+        <v>69</v>
+      </c>
+      <c r="V82" t="s">
         <v>57</v>
       </c>
-      <c r="V82" t="s">
+      <c r="W82" t="s">
         <v>78</v>
       </c>
-      <c r="W82" t="s">
-        <v>71</v>
-      </c>
       <c r="X82" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y82" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z82" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA82" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="83" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>15</v>
       </c>
@@ -5730,52 +5824,52 @@
       <c r="G83">
         <v>0.33123000000000002</v>
       </c>
-      <c r="T83" t="s">
-        <v>69</v>
-      </c>
       <c r="U83" t="s">
+        <v>69</v>
+      </c>
+      <c r="V83" t="s">
         <v>59</v>
       </c>
-      <c r="V83" t="s">
+      <c r="W83" t="s">
         <v>78</v>
       </c>
-      <c r="W83" t="s">
-        <v>71</v>
-      </c>
       <c r="X83" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y83" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="Z83" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA83" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="84" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T84" t="s">
-        <v>69</v>
-      </c>
+    <row r="84" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U84" t="s">
+        <v>69</v>
+      </c>
+      <c r="V84" t="s">
         <v>20</v>
       </c>
-      <c r="V84" t="s">
+      <c r="W84" t="s">
         <v>79</v>
       </c>
-      <c r="W84" t="s">
-        <v>71</v>
-      </c>
       <c r="X84" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y84" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z84" t="s">
         <v>73</v>
       </c>
-      <c r="Z84" t="s">
+      <c r="AA84" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="85" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>12</v>
       </c>
@@ -5806,52 +5900,52 @@
       <c r="K85">
         <v>50</v>
       </c>
-      <c r="T85" t="s">
-        <v>69</v>
-      </c>
       <c r="U85" t="s">
+        <v>69</v>
+      </c>
+      <c r="V85" t="s">
         <v>15</v>
       </c>
-      <c r="V85" t="s">
+      <c r="W85" t="s">
         <v>75</v>
       </c>
-      <c r="W85" t="s">
-        <v>71</v>
-      </c>
       <c r="X85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y85" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z85" t="s">
         <v>73</v>
       </c>
-      <c r="Z85" t="s">
+      <c r="AA85" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="87" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="T87" t="s">
-        <v>69</v>
-      </c>
+    <row r="87" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U87" t="s">
+        <v>69</v>
+      </c>
+      <c r="V87" t="s">
         <v>12</v>
       </c>
-      <c r="V87" t="s">
+      <c r="W87" t="s">
         <v>70</v>
       </c>
-      <c r="W87" t="s">
-        <v>71</v>
-      </c>
       <c r="X87" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Y87" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z87" t="s">
         <v>73</v>
       </c>
-      <c r="Z87" t="s">
+      <c r="AA87" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="90" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>44</v>
       </c>
@@ -5873,11 +5967,11 @@
       <c r="L90">
         <v>0.42012333946150526</v>
       </c>
-      <c r="P90" t="s">
+      <c r="Q90" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="91" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>47</v>
       </c>
@@ -5900,7 +5994,7 @@
         <v>0.42012333946150526</v>
       </c>
     </row>
-    <row r="92" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>49</v>
       </c>
@@ -5923,7 +6017,7 @@
         <v>0.42012333946150526</v>
       </c>
     </row>
-    <row r="93" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>51</v>
       </c>
@@ -5958,7 +6052,7 @@
         <v>0.47763777043344691</v>
       </c>
     </row>
-    <row r="94" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>53</v>
       </c>
@@ -5993,7 +6087,7 @@
         <v>0.47814004703314078</v>
       </c>
     </row>
-    <row r="95" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>53</v>
       </c>
@@ -6028,7 +6122,7 @@
         <v>0.47814004703314084</v>
       </c>
     </row>
-    <row r="96" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>53</v>
       </c>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE08A75-8877-4E2D-8649-BCD8DF2547BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B8C8CD-A3F0-4366-A18B-6B92D5A2DFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="221">
   <si>
     <t>~fi_t</t>
   </si>
@@ -2792,6 +2792,9 @@
         <v>10</v>
       </c>
       <c r="L10" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" t="s">
         <v>220</v>
       </c>
       <c r="U10" t="s">
@@ -3858,7 +3861,7 @@
       <c r="K30">
         <v>53</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>0.8</v>
       </c>
       <c r="U30" t="s">
@@ -3917,7 +3920,7 @@
       <c r="K31">
         <v>70</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>0.8</v>
       </c>
       <c r="U31" t="s">
@@ -3976,7 +3979,7 @@
       <c r="K32">
         <v>40</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>0.7</v>
       </c>
       <c r="U32" t="s">
@@ -4035,7 +4038,7 @@
       <c r="K33">
         <v>40</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>0.8</v>
       </c>
       <c r="U33" t="s">
@@ -4094,7 +4097,7 @@
       <c r="K34">
         <v>73</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>0.8</v>
       </c>
       <c r="U34" t="s">
@@ -4154,7 +4157,7 @@
       <c r="K35">
         <v>40</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>0.8</v>
       </c>
       <c r="U35" t="s">
@@ -4214,7 +4217,7 @@
       <c r="K36">
         <v>40</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>0.8</v>
       </c>
       <c r="U36" t="s">
@@ -4273,7 +4276,7 @@
       <c r="K37">
         <v>40</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>0.8</v>
       </c>
       <c r="U37" t="s">
@@ -4332,7 +4335,7 @@
       <c r="K38">
         <v>40</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>0.8</v>
       </c>
       <c r="U38" t="s">
@@ -4391,7 +4394,7 @@
       <c r="K39">
         <v>40</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>0.8</v>
       </c>
       <c r="U39" t="s">
@@ -4451,7 +4454,7 @@
       <c r="K40">
         <v>40</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>0.8</v>
       </c>
       <c r="U40" t="s">
@@ -4510,7 +4513,7 @@
       <c r="K41">
         <v>40</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>0.8</v>
       </c>
       <c r="U41" t="s">
@@ -4569,7 +4572,7 @@
       <c r="K42">
         <v>40</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>0.8</v>
       </c>
       <c r="U42" t="s">
@@ -4628,7 +4631,7 @@
       <c r="K43">
         <v>40</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>0.8</v>
       </c>
       <c r="O43" t="s">
@@ -4699,7 +4702,7 @@
       <c r="K44">
         <v>72</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>0.8</v>
       </c>
       <c r="N44" t="s">
@@ -4774,7 +4777,7 @@
       <c r="K45">
         <v>40</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>0.8</v>
       </c>
       <c r="N45" t="s">
@@ -4848,7 +4851,7 @@
       <c r="K46">
         <v>40</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>0.8</v>
       </c>
       <c r="N46" t="s">
@@ -4913,7 +4916,7 @@
       <c r="K47">
         <v>40</v>
       </c>
-      <c r="L47">
+      <c r="M47">
         <v>0.8</v>
       </c>
       <c r="N47" t="s">
@@ -4988,7 +4991,7 @@
       <c r="K48">
         <v>40</v>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>0.8</v>
       </c>
       <c r="N48" t="s">
@@ -5062,7 +5065,7 @@
       <c r="K49">
         <v>40</v>
       </c>
-      <c r="L49">
+      <c r="M49">
         <v>0.8</v>
       </c>
       <c r="O49" s="3"/>
@@ -5123,7 +5126,7 @@
       <c r="K50">
         <v>40</v>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>0.8</v>
       </c>
       <c r="O50" s="3"/>
@@ -5185,7 +5188,7 @@
       <c r="K51">
         <v>40</v>
       </c>
-      <c r="L51">
+      <c r="M51">
         <v>0.8</v>
       </c>
       <c r="O51" s="3"/>
@@ -5247,7 +5250,7 @@
       <c r="K52">
         <v>40</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>0.8</v>
       </c>
       <c r="O52" s="3"/>
@@ -5308,7 +5311,7 @@
       <c r="K53">
         <v>40</v>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>0.8</v>
       </c>
       <c r="U53" t="s">
@@ -5367,7 +5370,7 @@
       <c r="K54">
         <v>40</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>0.8</v>
       </c>
       <c r="U54" t="s">
@@ -5426,7 +5429,7 @@
       <c r="K55">
         <v>40</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>0.8</v>
       </c>
       <c r="U55" t="s">
@@ -5485,7 +5488,7 @@
       <c r="K56">
         <v>40</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>0.8</v>
       </c>
       <c r="U56" t="s">
@@ -5544,7 +5547,7 @@
       <c r="K57">
         <v>40</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>0.8</v>
       </c>
     </row>
@@ -5582,7 +5585,7 @@
       <c r="K58">
         <v>40</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>0.8</v>
       </c>
     </row>
@@ -5605,7 +5608,7 @@
       <c r="G59">
         <v>0.33123000000000002</v>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>0.8</v>
       </c>
     </row>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B8C8CD-A3F0-4366-A18B-6B92D5A2DFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E4DA6D-8148-4790-B043-8E86195F3364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -2921,7 +2921,7 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.3269999999999999</v>
+        <v>0.61136366214315596</v>
       </c>
       <c r="G13">
         <v>0.33123000000000002</v>
@@ -3209,12 +3209,6 @@
       <c r="L18">
         <v>0.15309859852159369</v>
       </c>
-      <c r="P18">
-        <v>3.9363662143155967E-2</v>
-      </c>
-      <c r="Q18">
-        <v>0.28763633785684395</v>
-      </c>
       <c r="U18" t="s">
         <v>69</v>
       </c>
@@ -3327,14 +3321,6 @@
       <c r="L20">
         <v>0.15619560585976827</v>
       </c>
-      <c r="P20">
-        <f>SUM(F11:F25)</f>
-        <v>0.92963633785684396</v>
-      </c>
-      <c r="Q20">
-        <f>0.969-F13-P20</f>
-        <v>-0.28763633785684384</v>
-      </c>
       <c r="U20" t="s">
         <v>69</v>
       </c>
@@ -3559,10 +3545,6 @@
       <c r="L24">
         <v>0.1532628310027955</v>
       </c>
-      <c r="Q24">
-        <f>SUM(P20:Q20)+F13</f>
-        <v>0.96900000000000008</v>
-      </c>
       <c r="U24" t="s">
         <v>69</v>
       </c>
@@ -3731,10 +3713,6 @@
       <c r="L27">
         <v>0.365520596150406</v>
       </c>
-      <c r="N27">
-        <f>F90*L90*G90</f>
-        <v>2.0930123559331545E-3</v>
-      </c>
       <c r="U27" t="s">
         <v>140</v>
       </c>
@@ -3962,7 +3940,7 @@
         <v>0.26</v>
       </c>
       <c r="G32">
-        <f t="shared" ref="G32:G34" si="0">$Q$44</f>
+        <f>$Q$44</f>
         <v>0.33</v>
       </c>
       <c r="H32" s="2">
@@ -3973,7 +3951,7 @@
         <v>63.037519640000006</v>
       </c>
       <c r="J32">
-        <f t="shared" ref="J32:J48" si="1">$R$44</f>
+        <f>$R$44</f>
         <v>4.1005000000000003</v>
       </c>
       <c r="K32">
@@ -4080,7 +4058,7 @@
         <v>0.185</v>
       </c>
       <c r="G34">
-        <f t="shared" si="0"/>
+        <f>$Q$44</f>
         <v>0.33</v>
       </c>
       <c r="H34" s="2">
@@ -4091,7 +4069,7 @@
         <v>63.037519640000006</v>
       </c>
       <c r="J34">
-        <f t="shared" si="1"/>
+        <f>$R$44</f>
         <v>4.1005000000000003</v>
       </c>
       <c r="K34">
@@ -4262,15 +4240,15 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="H37" s="2">
-        <f t="shared" ref="H37:H39" si="2">$P$47</f>
+        <f>$P$47</f>
         <v>2950.7891</v>
       </c>
       <c r="I37" s="3">
-        <f t="shared" ref="I37:I39" si="3">(4.5269/100)*H37</f>
+        <f t="shared" ref="I37:I39" si="0">(4.5269/100)*H37</f>
         <v>133.5792717679</v>
       </c>
       <c r="J37">
-        <f t="shared" ref="J37:J39" si="4">$R$47</f>
+        <f>$R$47</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K37">
@@ -4321,15 +4299,15 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="H38" s="2">
-        <f t="shared" si="2"/>
+        <f>$P$47</f>
         <v>2950.7891</v>
       </c>
       <c r="I38" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>133.5792717679</v>
       </c>
       <c r="J38">
-        <f t="shared" si="4"/>
+        <f>$R$47</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K38">
@@ -4380,15 +4358,15 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="H39" s="2">
-        <f t="shared" si="2"/>
+        <f>$P$47</f>
         <v>2950.7891</v>
       </c>
       <c r="I39" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>133.5792717679</v>
       </c>
       <c r="J39">
-        <f t="shared" si="4"/>
+        <f>$R$47</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K39">
@@ -4558,15 +4536,15 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H42" s="2">
-        <f t="shared" ref="H42:H44" si="5">$P$48</f>
+        <f>$P$48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I42" s="3">
-        <f t="shared" ref="I42:I44" si="6">($O$48/100)*H42</f>
+        <f t="shared" ref="I42:I44" si="1">($O$48/100)*H42</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J42">
-        <f t="shared" ref="J42:J44" si="7">$R$48</f>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K42">
@@ -4617,15 +4595,15 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H43" s="2">
-        <f t="shared" si="5"/>
+        <f>$P$48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I43" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J43">
-        <f t="shared" si="7"/>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K43">
@@ -4688,15 +4666,15 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H44" s="2">
-        <f t="shared" si="5"/>
+        <f>$P$48</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I44" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J44">
-        <f t="shared" si="7"/>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K44">
@@ -4985,7 +4963,7 @@
         <v>173.62265237640003</v>
       </c>
       <c r="J48">
-        <f t="shared" si="1"/>
+        <f>$R$44</f>
         <v>4.1005000000000003</v>
       </c>
       <c r="K48">
@@ -5178,7 +5156,7 @@
         <v>1175.5066999999999</v>
       </c>
       <c r="I51" s="3">
-        <f t="shared" ref="I51:I52" si="8">($O$45/100)*H51</f>
+        <f t="shared" ref="I51:I52" si="2">($O$45/100)*H51</f>
         <v>39.138495576499992</v>
       </c>
       <c r="J51">
@@ -5240,7 +5218,7 @@
         <v>1175.5066999999999</v>
       </c>
       <c r="I52" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="2"/>
         <v>39.138495576499992</v>
       </c>
       <c r="J52">
@@ -5360,11 +5338,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I54" s="3">
-        <f t="shared" ref="I54:I58" si="9">($O$48/100)*H54</f>
+        <f t="shared" ref="I54:I58" si="3">($O$48/100)*H54</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J54">
-        <f t="shared" ref="J54:J58" si="10">$R$48</f>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K54">
@@ -5419,11 +5397,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I55" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J55">
-        <f t="shared" si="10"/>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K55">
@@ -5478,11 +5456,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I56" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J56">
-        <f t="shared" si="10"/>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K56">
@@ -5537,11 +5515,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I57" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J57">
-        <f t="shared" si="10"/>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K57">
@@ -5575,11 +5553,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I58" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="3"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J58">
-        <f t="shared" si="10"/>
+        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K58">

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E4DA6D-8148-4790-B043-8E86195F3364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4779B7E-54F6-412B-8F7C-2C70F335E36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="222">
   <si>
     <t>~fi_t</t>
   </si>
@@ -811,6 +811,9 @@
   </si>
   <si>
     <t>ncap_af</t>
+  </si>
+  <si>
+    <t>Aggregated Plant -- operatingg</t>
   </si>
 </sst>
 </file>
@@ -5283,7 +5286,7 @@
         <v>162.96753257730003</v>
       </c>
       <c r="J53">
-        <f>$R$48</f>
+        <f t="shared" ref="J53:J58" si="3">$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K53">
@@ -5338,11 +5341,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I54" s="3">
-        <f t="shared" ref="I54:I58" si="3">($O$48/100)*H54</f>
+        <f t="shared" ref="I54:I58" si="4">($O$48/100)*H54</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J54">
-        <f>$R$48</f>
+        <f t="shared" si="3"/>
         <v>2.8138000000000001</v>
       </c>
       <c r="K54">
@@ -5397,11 +5400,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I55" s="3">
+        <f t="shared" si="4"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J55">
         <f t="shared" si="3"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J55">
-        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K55">
@@ -5456,11 +5459,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I56" s="3">
+        <f t="shared" si="4"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J56">
         <f t="shared" si="3"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J56">
-        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K56">
@@ -5476,7 +5479,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="X56" t="s">
         <v>71</v>
@@ -5515,11 +5518,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I57" s="3">
+        <f t="shared" si="4"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J57">
         <f t="shared" si="3"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J57">
-        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K57">
@@ -5553,11 +5556,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I58" s="3">
+        <f t="shared" si="4"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J58">
         <f t="shared" si="3"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J58">
-        <f>$R$48</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K58">

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4779B7E-54F6-412B-8F7C-2C70F335E36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B695A222-C6ED-44AE-9780-8B7CF5007B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -813,7 +813,7 @@
     <t>ncap_af</t>
   </si>
   <si>
-    <t>Aggregated Plant -- operatingg</t>
+    <t>Aggregated Plant -- operating agg</t>
   </si>
 </sst>
 </file>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B695A222-C6ED-44AE-9780-8B7CF5007B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB4E033-3C5E-4352-A9FC-7D64A1EB4045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="232">
   <si>
     <t>~fi_t</t>
   </si>
@@ -723,9 +723,6 @@
     <t>ep_bioenergy_tartuaardlapalu</t>
   </si>
   <si>
-    <t>Tartu Aardlapalu CHP</t>
-  </si>
-  <si>
     <t>coal</t>
   </si>
   <si>
@@ -813,7 +810,40 @@
     <t>ncap_af</t>
   </si>
   <si>
-    <t>Aggregated Plant -- operating agg</t>
+    <t>Tartu Aardlapalu CHP plant</t>
+  </si>
+  <si>
+    <t>e_harku_330</t>
+  </si>
+  <si>
+    <t>e_tartu_330</t>
+  </si>
+  <si>
+    <t>e_rakvere_330</t>
+  </si>
+  <si>
+    <t>e_paide_330</t>
+  </si>
+  <si>
+    <t>e_pussi_330</t>
+  </si>
+  <si>
+    <t>e_kilingi_nomme_330</t>
+  </si>
+  <si>
+    <t>e_sindi_330</t>
+  </si>
+  <si>
+    <t>e_tsirguliina_330</t>
+  </si>
+  <si>
+    <t>e_arukula_330</t>
+  </si>
+  <si>
+    <t>e_baltiej_330</t>
+  </si>
+  <si>
+    <t>e_viru_330</t>
   </si>
 </sst>
 </file>
@@ -1258,10 +1288,10 @@
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
@@ -1618,10 +1648,10 @@
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
@@ -1682,10 +1712,10 @@
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -1715,7 +1745,7 @@
         <v>69</v>
       </c>
       <c r="O11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P11" t="s">
         <v>108</v>
@@ -1735,10 +1765,10 @@
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -1768,7 +1798,7 @@
         <v>69</v>
       </c>
       <c r="O12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P12" t="s">
         <v>109</v>
@@ -2672,10 +2702,10 @@
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" t="s">
         <v>201</v>
-      </c>
-      <c r="C30" t="s">
-        <v>202</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2705,10 +2735,10 @@
         <v>69</v>
       </c>
       <c r="O30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q30" t="s">
         <v>71</v>
@@ -2736,7 +2766,7 @@
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -2798,7 +2828,7 @@
         <v>11</v>
       </c>
       <c r="M10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="U10" t="s">
         <v>63</v>
@@ -3496,7 +3526,7 @@
         <v>69</v>
       </c>
       <c r="V23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="W23" t="s">
         <v>76</v>
@@ -3608,7 +3638,7 @@
         <v>69</v>
       </c>
       <c r="V25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="W25" t="s">
         <v>81</v>
@@ -3664,10 +3694,10 @@
         <v>69</v>
       </c>
       <c r="V26" t="s">
+        <v>216</v>
+      </c>
+      <c r="W26" t="s">
         <v>217</v>
-      </c>
-      <c r="W26" t="s">
-        <v>218</v>
       </c>
       <c r="X26" t="s">
         <v>71</v>
@@ -3684,7 +3714,7 @@
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C27" t="s">
         <v>45</v>
@@ -3725,7 +3755,7 @@
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
@@ -3761,7 +3791,7 @@
         <v>69</v>
       </c>
       <c r="V28" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="W28" t="s">
         <v>163</v>
@@ -3790,7 +3820,7 @@
         <v>69</v>
       </c>
       <c r="V29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="W29" t="s">
         <v>148</v>
@@ -3810,13 +3840,13 @@
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>229</v>
       </c>
       <c r="E30">
         <v>1982</v>
@@ -3849,7 +3879,7 @@
         <v>69</v>
       </c>
       <c r="V30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="W30" t="s">
         <v>149</v>
@@ -3869,13 +3899,13 @@
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>231</v>
       </c>
       <c r="E31">
         <v>1965</v>
@@ -3908,7 +3938,7 @@
         <v>69</v>
       </c>
       <c r="V31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W31" t="s">
         <v>150</v>
@@ -3928,13 +3958,13 @@
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>231</v>
       </c>
       <c r="E32">
         <v>2015</v>
@@ -3987,13 +4017,13 @@
     </row>
     <row r="33" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>231</v>
       </c>
       <c r="E33">
         <v>2025</v>
@@ -4046,13 +4076,13 @@
     </row>
     <row r="34" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
       <c r="E34">
         <v>1956</v>
@@ -4111,7 +4141,7 @@
         <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E35">
         <v>2021</v>
@@ -4171,7 +4201,7 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>221</v>
       </c>
       <c r="E36">
         <v>2018</v>
@@ -4231,7 +4261,7 @@
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="E37">
         <v>2009</v>
@@ -4264,7 +4294,7 @@
         <v>69</v>
       </c>
       <c r="V37" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="W37" t="s">
         <v>162</v>
@@ -4290,7 +4320,7 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>227</v>
       </c>
       <c r="E38">
         <v>2011</v>
@@ -4349,7 +4379,7 @@
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>229</v>
       </c>
       <c r="E39">
         <v>2010</v>
@@ -4402,13 +4432,13 @@
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C40" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E40">
         <v>1997</v>
@@ -4468,7 +4498,7 @@
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>224</v>
       </c>
       <c r="E41">
         <v>2016</v>
@@ -4527,7 +4557,7 @@
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E42">
         <v>2017</v>
@@ -4586,7 +4616,7 @@
         <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>221</v>
       </c>
       <c r="E43">
         <v>2019</v>
@@ -4616,16 +4646,16 @@
         <v>0.8</v>
       </c>
       <c r="O43" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P43" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q43" t="s">
         <v>213</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
         <v>214</v>
-      </c>
-      <c r="R43" t="s">
-        <v>215</v>
       </c>
       <c r="U43" t="s">
         <v>69</v>
@@ -4657,7 +4687,7 @@
         <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E44">
         <v>1963</v>
@@ -4687,7 +4717,7 @@
         <v>0.8</v>
       </c>
       <c r="N44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O44" s="4">
         <v>1.31</v>
@@ -4731,7 +4761,7 @@
         <v>16</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E45">
         <v>2020</v>
@@ -4762,7 +4792,7 @@
         <v>0.8</v>
       </c>
       <c r="N45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O45" s="4">
         <v>3.3294999999999999</v>
@@ -4780,7 +4810,7 @@
         <v>69</v>
       </c>
       <c r="V45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="W45" t="s">
         <v>167</v>
@@ -4806,7 +4836,7 @@
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>14</v>
+        <v>226</v>
       </c>
       <c r="E46">
         <v>2013</v>
@@ -4836,7 +4866,7 @@
         <v>0.8</v>
       </c>
       <c r="N46" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O46" s="4"/>
       <c r="P46" s="2"/>
@@ -4870,7 +4900,7 @@
         <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="E47">
         <v>2015</v>
@@ -4901,7 +4931,7 @@
         <v>0.8</v>
       </c>
       <c r="N47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O47">
         <v>4.5269000000000004</v>
@@ -4939,13 +4969,13 @@
     </row>
     <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D48" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E48">
         <v>2012</v>
@@ -4976,7 +5006,7 @@
         <v>0.8</v>
       </c>
       <c r="N48" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O48">
         <v>3.6080999999999999</v>
@@ -5020,7 +5050,7 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>227</v>
       </c>
       <c r="E49">
         <v>2013</v>
@@ -5081,7 +5111,7 @@
         <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>224</v>
       </c>
       <c r="E50">
         <v>2015</v>
@@ -5142,7 +5172,7 @@
         <v>16</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>226</v>
       </c>
       <c r="E51">
         <v>2009</v>
@@ -5204,7 +5234,7 @@
         <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E52">
         <v>2015</v>
@@ -5266,7 +5296,7 @@
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="E53">
         <v>2022</v>
@@ -5325,7 +5355,7 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>223</v>
       </c>
       <c r="E54">
         <v>2013</v>
@@ -5384,7 +5414,7 @@
         <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>224</v>
       </c>
       <c r="E55">
         <v>2016</v>
@@ -5420,7 +5450,7 @@
         <v>190</v>
       </c>
       <c r="W55" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="X55" t="s">
         <v>71</v>
@@ -5443,7 +5473,7 @@
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>221</v>
       </c>
       <c r="E56">
         <v>2009</v>
@@ -5479,7 +5509,7 @@
         <v>18</v>
       </c>
       <c r="W56" t="s">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="X56" t="s">
         <v>71</v>
@@ -5502,7 +5532,7 @@
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>223</v>
       </c>
       <c r="E57">
         <v>2012</v>
@@ -5540,7 +5570,7 @@
         <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="E58">
         <v>2015</v>
@@ -5578,7 +5608,7 @@
         <v>19</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>221</v>
       </c>
       <c r="E59">
         <v>2022</v>
@@ -5595,7 +5625,7 @@
     </row>
     <row r="75" spans="21:27" x14ac:dyDescent="0.25">
       <c r="V75" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" spans="21:27" x14ac:dyDescent="0.25">
@@ -5952,7 +5982,7 @@
         <v>0.42012333946150526</v>
       </c>
       <c r="Q90" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="2:27" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB4E033-3C5E-4352-A9FC-7D64A1EB4045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC48194-AFDF-4756-A0A8-3C219FFD9F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -77,7 +77,7 @@
     <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
   </authors>
   <commentList>
-    <comment ref="Z23" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+    <comment ref="Z20" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +85,7 @@
     Miks daynite (hydro samuti)</t>
       </text>
     </comment>
-    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <comment ref="F27" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -93,7 +93,7 @@
     Iru produces only 17 MW in 2025 not 0.207 GW</t>
       </text>
     </comment>
-    <comment ref="B31" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+    <comment ref="B28" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -101,7 +101,7 @@
     TODO: set their actual start date and then add how much they produce in 2025</t>
       </text>
     </comment>
-    <comment ref="E39" authorId="3" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
+    <comment ref="E36" authorId="3" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -110,7 +110,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="O43" authorId="4" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+    <comment ref="O40" authorId="4" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -119,7 +119,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="R47" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+    <comment ref="R44" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -127,7 +127,7 @@
     Took same as chp</t>
       </text>
     </comment>
-    <comment ref="U84" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <comment ref="U81" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -135,7 +135,7 @@
     Frequency reserve</t>
       </text>
     </comment>
-    <comment ref="J85" authorId="7" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <comment ref="J82" authorId="7" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="231">
   <si>
     <t>~fi_t</t>
   </si>
@@ -216,72 +216,12 @@
     <t>oil</t>
   </si>
   <si>
-    <t>ep_solar_001__irena</t>
-  </si>
-  <si>
     <t>solar</t>
   </si>
   <si>
-    <t>elc_spv_001</t>
-  </si>
-  <si>
-    <t>ep_solar_004__irena</t>
-  </si>
-  <si>
     <t>elc_spv_004</t>
   </si>
   <si>
-    <t>ep_solar_008__irena</t>
-  </si>
-  <si>
-    <t>elc_spv_008</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_001</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_002</t>
-  </si>
-  <si>
-    <t>elc_spv_002</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_003</t>
-  </si>
-  <si>
-    <t>elc_spv_003</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_004</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_006</t>
-  </si>
-  <si>
-    <t>elc_spv_006</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_007</t>
-  </si>
-  <si>
-    <t>elc_spv_007</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_008</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_009</t>
-  </si>
-  <si>
-    <t>elc_spv_009</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_010</t>
-  </si>
-  <si>
-    <t>elc_spv_010</t>
-  </si>
-  <si>
     <t>ep_windon_006__irena</t>
   </si>
   <si>
@@ -844,6 +784,63 @@
   </si>
   <si>
     <t>e_viru_330</t>
+  </si>
+  <si>
+    <t>elc_spv_parnu</t>
+  </si>
+  <si>
+    <t>elc_spv_harju</t>
+  </si>
+  <si>
+    <t>elc_spv_tartu</t>
+  </si>
+  <si>
+    <t>elc_spv_laane_viru</t>
+  </si>
+  <si>
+    <t>elc_spv_viljandi</t>
+  </si>
+  <si>
+    <t>elc_spv_ida_viru</t>
+  </si>
+  <si>
+    <t>elc_spv_jogeva</t>
+  </si>
+  <si>
+    <t>elc_spv_polva</t>
+  </si>
+  <si>
+    <t>elc_spv_valga</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_parnu</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_tartu</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_laane_viru</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_ida_viru</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_jarva</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_polva</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_harju</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_valga</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_viljandi</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_jogeva</t>
   </si>
 </sst>
 </file>
@@ -1247,30 +1244,30 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="Z23" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+  <threadedComment ref="Z20" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
     <text>Miks daynite (hydro samuti)</text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+  <threadedComment ref="F27" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
-  <threadedComment ref="B31" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+  <threadedComment ref="B28" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
     <text>TODO: set their actual start date and then add how much they produce in 2025</text>
   </threadedComment>
-  <threadedComment ref="E39" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
+  <threadedComment ref="E36" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
     <text xml:space="preserve">Ei tea
 </text>
   </threadedComment>
-  <threadedComment ref="O43" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+  <threadedComment ref="O40" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
     <text xml:space="preserve">NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)
 </text>
   </threadedComment>
-  <threadedComment ref="R47" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+  <threadedComment ref="R44" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
     <text>Took same as chp</text>
   </threadedComment>
-  <threadedComment ref="U84" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+  <threadedComment ref="U81" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
   </threadedComment>
-  <threadedComment ref="J85" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+  <threadedComment ref="J82" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
     <text>From 9,24 to 6</text>
   </threadedComment>
 </ThreadedComments>
@@ -1288,10 +1285,10 @@
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="N9" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
@@ -1317,42 +1314,42 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="J10" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="K10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="L10" t="s">
         <v>10</v>
       </c>
       <c r="N10" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="Q10" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="R10" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="S10" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="T10" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1376,7 +1373,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J13" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1385,30 +1382,30 @@
         <v>20</v>
       </c>
       <c r="N13" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O13" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="P13" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="Q13" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R13" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S13" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="T13" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
@@ -1432,7 +1429,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1441,30 +1438,30 @@
         <v>20</v>
       </c>
       <c r="N14" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O14" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="P14" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="Q14" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R14" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S14" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="T14" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
@@ -1497,30 +1494,30 @@
         <v>20</v>
       </c>
       <c r="N15" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O15" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="Q15" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R15" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S15" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="T15" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="C16" t="s">
         <v>16</v>
@@ -1553,30 +1550,30 @@
         <v>20</v>
       </c>
       <c r="N16" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O16" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="P16" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="Q16" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R16" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S16" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="T16" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
@@ -1609,25 +1606,25 @@
         <v>20</v>
       </c>
       <c r="N17" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O17" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="P17" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="Q17" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S17" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="T17" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1648,10 +1645,10 @@
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="N9" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
@@ -1665,10 +1662,10 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
@@ -1689,33 +1686,33 @@
         <v>11</v>
       </c>
       <c r="N10" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="Q10" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="R10" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="S10" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="T10" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -1742,33 +1739,33 @@
         <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O11" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="P11" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="Q11" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R11" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S11" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="T11" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -1795,36 +1792,36 @@
         <v>50</v>
       </c>
       <c r="N12" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O12" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="P12" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="Q12" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R12" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S12" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="T12" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E13">
         <v>2025</v>
@@ -1851,36 +1848,36 @@
         <v>0.48487924617859812</v>
       </c>
       <c r="N13" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O13" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="P13" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="Q13" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R13" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S13" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T13" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E14">
         <v>2032</v>
@@ -1907,36 +1904,36 @@
         <v>0.46120613336716743</v>
       </c>
       <c r="N14" t="s">
+        <v>49</v>
+      </c>
+      <c r="O14" t="s">
         <v>69</v>
       </c>
-      <c r="O14" t="s">
-        <v>89</v>
-      </c>
       <c r="P14" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="Q14" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R14" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S14" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T14" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="E15">
         <v>2035</v>
@@ -1963,36 +1960,36 @@
         <v>0.45368618559080531</v>
       </c>
       <c r="N15" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O15" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="P15" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="Q15" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R15" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S15" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T15" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="E16">
         <v>2035</v>
@@ -2019,36 +2016,36 @@
         <v>0.45368618559080531</v>
       </c>
       <c r="N16" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O16" t="s">
+        <v>73</v>
+      </c>
+      <c r="P16" t="s">
         <v>93</v>
       </c>
-      <c r="P16" t="s">
-        <v>113</v>
-      </c>
       <c r="Q16" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R16" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S16" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T16" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E17">
         <v>2025</v>
@@ -2075,36 +2072,36 @@
         <v>0.48487924617859807</v>
       </c>
       <c r="N17" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O17" t="s">
+        <v>74</v>
+      </c>
+      <c r="P17" t="s">
         <v>94</v>
       </c>
-      <c r="P17" t="s">
-        <v>114</v>
-      </c>
       <c r="Q17" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S17" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T17" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E18">
         <v>2025</v>
@@ -2131,36 +2128,36 @@
         <v>0.48487924617859812</v>
       </c>
       <c r="N18" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O18" t="s">
+        <v>75</v>
+      </c>
+      <c r="P18" t="s">
         <v>95</v>
       </c>
-      <c r="P18" t="s">
-        <v>115</v>
-      </c>
       <c r="Q18" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R18" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S18" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T18" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E19">
         <v>2025</v>
@@ -2187,30 +2184,30 @@
         <v>0.48487924617859812</v>
       </c>
       <c r="N19" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O19" t="s">
+        <v>76</v>
+      </c>
+      <c r="P19" t="s">
         <v>96</v>
       </c>
-      <c r="P19" t="s">
-        <v>116</v>
-      </c>
       <c r="Q19" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R19" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S19" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T19" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
@@ -2237,30 +2234,30 @@
         <v>100</v>
       </c>
       <c r="N20" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="O20" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="P20" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="Q20" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R20" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S20" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="T20" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
         <v>14</v>
@@ -2287,36 +2284,36 @@
         <v>100</v>
       </c>
       <c r="N21" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="O21" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="P21" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="Q21" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R21" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S21" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="T21" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
         <v>23</v>
-      </c>
-      <c r="D22" t="s">
-        <v>26</v>
       </c>
       <c r="E22">
         <v>2025</v>
@@ -2343,36 +2340,36 @@
         <v>0.15309859852159369</v>
       </c>
       <c r="N22" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O22" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="P22" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="Q22" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R22" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S22" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T22" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E23">
         <v>2028</v>
@@ -2399,36 +2396,36 @@
         <v>0.48127681492517582</v>
       </c>
       <c r="N23" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O23" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="P23" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="Q23" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R23" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S23" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T23" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="E24">
         <v>2029</v>
@@ -2455,36 +2452,36 @@
         <v>0.47369214016582101</v>
       </c>
       <c r="N24" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O24" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="P24" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="Q24" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R24" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S24" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T24" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="E25">
         <v>2030</v>
@@ -2511,36 +2508,36 @@
         <v>0.46331764653839141</v>
       </c>
       <c r="N25" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O25" t="s">
+        <v>83</v>
+      </c>
+      <c r="P25" t="s">
         <v>103</v>
       </c>
-      <c r="P25" t="s">
-        <v>123</v>
-      </c>
       <c r="Q25" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R25" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S25" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T25" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="E26">
         <v>2028</v>
@@ -2567,36 +2564,36 @@
         <v>0.45368618559080531</v>
       </c>
       <c r="N26" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O26" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="P26" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="Q26" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R26" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S26" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T26" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="E27">
         <v>2028</v>
@@ -2623,36 +2620,36 @@
         <v>0.45368618559080537</v>
       </c>
       <c r="N27" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O27" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="P27" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="Q27" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R27" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S27" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T27" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="E28">
         <v>2030</v>
@@ -2679,33 +2676,33 @@
         <v>0.46331764653839141</v>
       </c>
       <c r="N28" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O28" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="P28" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="Q28" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R28" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S28" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T28" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C30" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2732,25 +2729,25 @@
         <v>50</v>
       </c>
       <c r="N30" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O30" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="P30" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="Q30" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="R30" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="S30" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="T30" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2761,12 +2758,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:AA105"/>
+  <dimension ref="B9:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -2790,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="2:27" x14ac:dyDescent="0.25">
@@ -2828,186 +2825,222 @@
         <v>11</v>
       </c>
       <c r="M10" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="U10" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="V10" t="s">
         <v>1</v>
       </c>
       <c r="W10" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="X10" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="Y10" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="Z10" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AA10" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>212</v>
       </c>
       <c r="E11">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F11">
-        <v>4.3091615634383719E-2</v>
+        <v>7.6700000000000004E-2</v>
       </c>
       <c r="G11">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1336.4999999999998</v>
+      </c>
+      <c r="I11" s="3">
+        <v>21.45</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>40</v>
       </c>
       <c r="L11">
-        <v>0.14986856628506873</v>
+        <v>0.1461854238754417</v>
       </c>
       <c r="U11" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V11" t="s">
-        <v>22</v>
+        <v>221</v>
       </c>
       <c r="W11" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="X11" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y11" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z11" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA11" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>25</v>
+        <v>221</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="E12">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="F12">
-        <v>4.3344722222460344E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="G12">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1336.5</v>
+      </c>
+      <c r="I12" s="3">
+        <v>21.450000000000003</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>32</v>
       </c>
       <c r="L12">
-        <v>0.14986856628506873</v>
+        <v>0.1461854238754417</v>
       </c>
       <c r="U12" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V12" t="s">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c r="W12" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="X12" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y12" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z12" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA12" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="E13">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F13">
-        <v>0.61136366214315596</v>
+        <v>5.8200000000000002E-2</v>
       </c>
       <c r="G13">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1336.5</v>
+      </c>
+      <c r="I13" s="3">
+        <v>21.450000000000003</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>40</v>
       </c>
       <c r="L13">
-        <v>0.14986856628506873</v>
+        <v>0.14867925344692126</v>
       </c>
       <c r="U13" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V13" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="W13" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="X13" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y13" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z13" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA13" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>29</v>
+        <v>223</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>215</v>
       </c>
       <c r="E14">
         <v>2015</v>
       </c>
       <c r="F14">
-        <v>7.6700000000000004E-2</v>
+        <v>2.9599999999999998E-2</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>1336.4999999999998</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I14" s="3">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3016,166 +3049,166 @@
         <v>40</v>
       </c>
       <c r="L14">
-        <v>0.1461854238754417</v>
+        <v>0.14701259708091721</v>
       </c>
       <c r="U14" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V14" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="W14" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="X14" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y14" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z14" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA14" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>217</v>
       </c>
       <c r="E15">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="F15">
-        <v>3.2000000000000001E-2</v>
+        <v>5.3800000000000008E-2</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>1336.5</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I15" s="3">
-        <v>21.450000000000003</v>
+        <v>21.45</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L15">
-        <v>0.1461854238754417</v>
+        <v>0.15309859852159369</v>
       </c>
       <c r="U15" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V15" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="W15" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="X15" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y15" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z15" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA15" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>30</v>
+        <v>224</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>217</v>
       </c>
       <c r="E16">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="F16">
-        <v>5.8200000000000002E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16">
-        <v>1336.5</v>
+        <v>1138.5</v>
       </c>
       <c r="I16" s="3">
-        <v>21.450000000000003</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L16">
-        <v>0.14867925344692126</v>
+        <v>0.15309859852159369</v>
       </c>
       <c r="U16" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V16" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="W16" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="X16" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y16" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z16" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA16" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>32</v>
+        <v>230</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>218</v>
       </c>
       <c r="E17">
         <v>2015</v>
       </c>
       <c r="F17">
-        <v>2.9599999999999998E-2</v>
+        <v>7.3000000000000009E-3</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I17" s="3">
-        <v>21.450000000000003</v>
+        <v>21.45</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3184,54 +3217,54 @@
         <v>40</v>
       </c>
       <c r="L17">
-        <v>0.14701259708091721</v>
+        <v>0.15619560585976827</v>
       </c>
       <c r="U17" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V17" t="s">
-        <v>34</v>
+        <v>227</v>
       </c>
       <c r="W17" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="X17" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y17" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z17" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA17" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>34</v>
+        <v>226</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="E18">
         <v>2015</v>
       </c>
       <c r="F18">
-        <v>5.3800000000000008E-2</v>
+        <v>2.81E-2</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>1336.4999999999998</v>
+        <v>1336.5</v>
       </c>
       <c r="I18" s="3">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3240,107 +3273,107 @@
         <v>40</v>
       </c>
       <c r="L18">
-        <v>0.15309859852159369</v>
+        <v>0.14537310453496291</v>
       </c>
       <c r="U18" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V18" t="s">
-        <v>35</v>
+        <v>228</v>
       </c>
       <c r="W18" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="X18" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y18" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z18" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA18" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>34</v>
+        <v>227</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>213</v>
       </c>
       <c r="E19">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="F19">
-        <v>7.0000000000000007E-2</v>
+        <v>8.4900000000000003E-2</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19">
-        <v>1138.5</v>
+        <v>1336.5</v>
       </c>
       <c r="I19" s="3">
-        <v>18.150000000000002</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="L19">
-        <v>0.15309859852159369</v>
+        <v>0.14763873655681015</v>
       </c>
       <c r="U19" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V19" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="W19" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="X19" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y19" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z19" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA19" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>35</v>
+        <v>228</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>220</v>
       </c>
       <c r="E20">
         <v>2015</v>
       </c>
       <c r="F20">
-        <v>7.3000000000000009E-3</v>
+        <v>5.2399999999999995E-2</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I20" s="3">
         <v>21.45</v>
@@ -3352,45 +3385,45 @@
         <v>40</v>
       </c>
       <c r="L20">
-        <v>0.15619560585976827</v>
+        <v>0.1532628310027955</v>
       </c>
       <c r="U20" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V20" t="s">
-        <v>39</v>
+        <v>198</v>
       </c>
       <c r="W20" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="X20" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y20" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z20" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="AA20" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>37</v>
+        <v>228</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="E21">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="F21">
-        <v>2.81E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -3405,48 +3438,48 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L21">
-        <v>0.14537310453496291</v>
+        <v>0.1532628310027955</v>
       </c>
       <c r="U21" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W21" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="X21" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y21" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z21" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA21" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>39</v>
+        <v>229</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>216</v>
       </c>
       <c r="E22">
         <v>2015</v>
       </c>
       <c r="F22">
-        <v>8.4900000000000003E-2</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -3464,457 +3497,466 @@
         <v>40</v>
       </c>
       <c r="L22">
-        <v>0.14763873655681015</v>
+        <v>0.1451997589052581</v>
       </c>
       <c r="U22" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V22" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="W22" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="X22" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y22" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z22" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA22" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E23">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="F23">
-        <v>5.2399999999999995E-2</v>
+        <v>7.9699999999999993E-2</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>1336.5000000000002</v>
+        <v>2024</v>
       </c>
       <c r="I23" s="3">
-        <v>21.45</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K23">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="L23">
-        <v>0.1532628310027955</v>
+        <v>0.365520596150406</v>
       </c>
       <c r="U23" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V23" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="W23" t="s">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="X23" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y23" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z23" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="AA23" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>40</v>
+        <v>195</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E24">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F24">
-        <v>0.02</v>
+        <v>0.17519999999999999</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24">
-        <v>1336.5</v>
+        <v>2024</v>
       </c>
       <c r="I24" s="3">
-        <v>21.450000000000003</v>
+        <v>48.4</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K24">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L24">
-        <v>0.1532628310027955</v>
+        <v>0.365520596150406</v>
       </c>
       <c r="U24" t="s">
-        <v>69</v>
-      </c>
-      <c r="V24" t="s">
-        <v>61</v>
-      </c>
-      <c r="W24" t="s">
-        <v>81</v>
-      </c>
-      <c r="X24" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>74</v>
+        <v>120</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>42</v>
+        <v>196</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E25">
         <v>2015</v>
       </c>
       <c r="F25">
-        <v>3.2000000000000002E-3</v>
+        <v>0.439</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25">
-        <v>1336.5</v>
+        <v>2376</v>
       </c>
       <c r="I25" s="3">
-        <v>21.450000000000003</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="K25">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L25">
-        <v>0.1451997589052581</v>
+        <v>0.41047488326249421</v>
       </c>
       <c r="U25" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V25" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="W25" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="X25" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y25" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z25" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA25" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26">
-        <v>2024</v>
-      </c>
-      <c r="F26">
-        <v>7.9699999999999993E-2</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>2024</v>
-      </c>
-      <c r="I26" s="3">
-        <v>48.400000000000006</v>
-      </c>
-      <c r="J26">
-        <v>2.3100000000000005</v>
-      </c>
-      <c r="K26">
-        <v>31</v>
-      </c>
-      <c r="L26">
-        <v>0.365520596150406</v>
+        <v>120</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="U26" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V26" t="s">
-        <v>216</v>
+        <v>172</v>
       </c>
       <c r="W26" t="s">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="X26" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y26" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z26" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA26" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="E27">
-        <v>2025</v>
+        <v>1982</v>
       </c>
       <c r="F27">
-        <v>0.17519999999999999</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>2024</v>
+        <f>Q42</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H27" s="2">
+        <v>1175.5066999999999</v>
       </c>
       <c r="I27" s="3">
-        <v>48.4</v>
+        <f>(O42/100)*H28</f>
+        <v>160.216352398</v>
       </c>
       <c r="J27">
-        <v>2.3100000000000005</v>
+        <f>R42</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K27">
-        <v>30</v>
-      </c>
-      <c r="L27">
-        <v>0.365520596150406</v>
+        <v>53</v>
+      </c>
+      <c r="M27">
+        <v>0.8</v>
       </c>
       <c r="U27" t="s">
-        <v>140</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>141</v>
+        <v>49</v>
+      </c>
+      <c r="V27" t="s">
+        <v>174</v>
+      </c>
+      <c r="W27" t="s">
+        <v>129</v>
+      </c>
+      <c r="X27" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>171</v>
       </c>
       <c r="D28" t="s">
-        <v>52</v>
+        <v>211</v>
       </c>
       <c r="E28">
-        <v>2015</v>
+        <v>1965</v>
       </c>
       <c r="F28">
-        <v>0.439</v>
+        <v>0.77</v>
       </c>
       <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28">
-        <v>2376</v>
+        <f>$Q$41</f>
+        <v>0.33</v>
+      </c>
+      <c r="H28" s="2">
+        <v>4812.0244000000002</v>
       </c>
       <c r="I28" s="3">
-        <v>57.20000000000001</v>
+        <f>(1.31/100)*H28</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J28">
-        <v>2.52</v>
+        <f>$R$41</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K28">
-        <v>50</v>
-      </c>
-      <c r="L28">
-        <v>0.41047488326249421</v>
+        <v>70</v>
+      </c>
+      <c r="M28">
+        <v>0.8</v>
       </c>
       <c r="U28" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V28" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="W28" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="X28" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y28" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z28" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA28" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" t="s">
+        <v>211</v>
+      </c>
+      <c r="E29">
+        <v>2015</v>
+      </c>
+      <c r="F29">
+        <v>0.26</v>
+      </c>
+      <c r="G29">
+        <f>$Q$41</f>
+        <v>0.33</v>
+      </c>
+      <c r="H29" s="2">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I29" s="3">
+        <f>(1.31/100)*H29</f>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J29">
+        <f>$R$41</f>
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="K29">
+        <v>40</v>
+      </c>
+      <c r="M29">
+        <v>0.7</v>
+      </c>
+      <c r="U29" t="s">
+        <v>49</v>
+      </c>
+      <c r="V29" t="s">
+        <v>122</v>
+      </c>
+      <c r="W29" t="s">
         <v>141</v>
       </c>
-      <c r="U29" t="s">
-        <v>69</v>
-      </c>
-      <c r="V29" t="s">
-        <v>192</v>
-      </c>
-      <c r="W29" t="s">
-        <v>148</v>
-      </c>
       <c r="X29" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y29" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z29" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA29" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>218</v>
+        <v>174</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="D30" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="E30">
-        <v>1982</v>
+        <v>2025</v>
       </c>
       <c r="F30">
-        <v>1.7000000000000001E-2</v>
+        <f>0.01</f>
+        <v>0.01</v>
       </c>
       <c r="G30">
-        <f>Q45</f>
-        <v>0.56000000000000005</v>
+        <v>0.33</v>
       </c>
       <c r="H30" s="2">
-        <v>1175.5066999999999</v>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I30" s="3">
-        <f>(O45/100)*H31</f>
-        <v>160.216352398</v>
+        <f>(1.31/100)*H30</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J30">
-        <f>R45</f>
-        <v>5.8775000000000004</v>
+        <f>$R$41</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K30">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="M30">
         <v>0.8</v>
       </c>
       <c r="U30" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V30" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="W30" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="X30" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y30" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z30" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA30" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="E31">
-        <v>1965</v>
+        <v>1956</v>
       </c>
       <c r="F31">
-        <v>0.77</v>
+        <v>0.185</v>
       </c>
       <c r="G31">
-        <f>$Q$44</f>
+        <f>$Q$41</f>
         <v>0.33</v>
       </c>
       <c r="H31" s="2">
@@ -3925,126 +3967,128 @@
         <v>63.037519640000006</v>
       </c>
       <c r="J31">
-        <f>$R$44</f>
+        <f>$R$41</f>
         <v>4.1005000000000003</v>
       </c>
       <c r="K31">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M31">
         <v>0.8</v>
       </c>
       <c r="U31" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V31" t="s">
-        <v>195</v>
+        <v>124</v>
       </c>
       <c r="W31" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="X31" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y31" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z31" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA31" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="E32">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="F32">
-        <v>0.26</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G32">
-        <f>$Q$44</f>
-        <v>0.33</v>
+        <f>Q42</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H32" s="2">
-        <v>4812.0244000000002</v>
+        <f>P42</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I32" s="3">
-        <f>(1.31/100)*H32</f>
-        <v>63.037519640000006</v>
+        <f>(O42/100)*H32</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J32">
-        <f>$R$44</f>
-        <v>4.1005000000000003</v>
+        <f>$R$42</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K32">
         <v>40</v>
       </c>
       <c r="M32">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="U32" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V32" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="W32" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="X32" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y32" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z32" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA32" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>194</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>191</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="E33">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="F33">
-        <f>0.01</f>
-        <v>0.01</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G33">
-        <v>0.33</v>
+        <f>Q44</f>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H33" s="2">
-        <v>4812.0244000000002</v>
+        <f>$P$44</f>
+        <v>2950.7891</v>
       </c>
       <c r="I33" s="3">
-        <f>(1.31/100)*H33</f>
-        <v>63.037519640000006</v>
+        <f>(4.5269/100)*H33</f>
+        <v>133.5792717679</v>
       </c>
       <c r="J33">
         <f>$R$44</f>
-        <v>4.1005000000000003</v>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K33">
         <v>40</v>
@@ -4053,117 +4097,116 @@
         <v>0.8</v>
       </c>
       <c r="U33" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V33" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="W33" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="X33" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y33" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z33" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA33" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>191</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="E34">
-        <v>1956</v>
+        <v>2009</v>
       </c>
       <c r="F34">
-        <v>0.185</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="G34">
-        <f>$Q$44</f>
-        <v>0.33</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H34" s="2">
-        <v>4812.0244000000002</v>
+        <f>$P$44</f>
+        <v>2950.7891</v>
       </c>
       <c r="I34" s="3">
-        <f>(1.31/100)*H34</f>
-        <v>63.037519640000006</v>
+        <f t="shared" ref="I34:I36" si="0">(4.5269/100)*H34</f>
+        <v>133.5792717679</v>
       </c>
       <c r="J34">
         <f>$R$44</f>
-        <v>4.1005000000000003</v>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K34">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="M34">
         <v>0.8</v>
       </c>
       <c r="U34" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V34" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="W34" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="X34" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y34" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z34" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA34" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="E35">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="F35">
-        <v>7.6999999999999999E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="G35">
-        <f>Q45</f>
-        <v>0.56000000000000005</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H35" s="2">
-        <f>P45</f>
-        <v>1175.5066999999999</v>
+        <f>$P$44</f>
+        <v>2950.7891</v>
       </c>
       <c r="I35" s="3">
-        <f>(O45/100)*H35</f>
-        <v>39.138495576499992</v>
+        <f t="shared" si="0"/>
+        <v>133.5792717679</v>
       </c>
       <c r="J35">
-        <f>$R$45</f>
-        <v>5.8775000000000004</v>
+        <f>$R$44</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K35">
         <v>40</v>
@@ -4172,57 +4215,56 @@
         <v>0.8</v>
       </c>
       <c r="U35" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V35" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="W35" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="X35" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y35" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z35" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA35" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="E36">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="F36">
-        <v>3.9E-2</v>
+        <v>1.3900000000000001E-2</v>
       </c>
       <c r="G36">
-        <f>Q47</f>
         <v>0.46800000000000003</v>
       </c>
       <c r="H36" s="2">
-        <f>$P$47</f>
+        <f>$P$44</f>
         <v>2950.7891</v>
       </c>
       <c r="I36" s="3">
-        <f>(4.5269/100)*H36</f>
+        <f t="shared" si="0"/>
         <v>133.5792717679</v>
       </c>
       <c r="J36">
-        <f>$R$47</f>
+        <f>$R$44</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K36">
@@ -4232,57 +4274,58 @@
         <v>0.8</v>
       </c>
       <c r="U36" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V36" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="W36" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="X36" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y36" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z36" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA36" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="D37" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="E37">
-        <v>2009</v>
+        <v>1997</v>
       </c>
       <c r="F37">
-        <v>2.2100000000000002E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G37">
-        <v>0.46800000000000003</v>
+        <f>Q41</f>
+        <v>0.33</v>
       </c>
       <c r="H37" s="2">
-        <f>$P$47</f>
-        <v>2950.7891</v>
+        <f>P41</f>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I37" s="3">
-        <f t="shared" ref="I37:I39" si="0">(4.5269/100)*H37</f>
-        <v>133.5792717679</v>
+        <f>($O$41/100)*H37</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J37">
-        <f>$R$47</f>
-        <v>2.8138000000000001</v>
+        <f>$R$41</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K37">
         <v>40</v>
@@ -4291,56 +4334,56 @@
         <v>0.8</v>
       </c>
       <c r="U37" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V37" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="W37" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="X37" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y37" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z37" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA37" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="E38">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="F38">
-        <v>2.0500000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G38">
-        <v>0.46800000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H38" s="2">
-        <f>$P$47</f>
-        <v>2950.7891</v>
+        <f>$P$45</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I38" s="3">
-        <f t="shared" si="0"/>
-        <v>133.5792717679</v>
+        <f>($O$45/100)*H38</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J38">
-        <f>$R$47</f>
+        <f>$R$45</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K38">
@@ -4350,56 +4393,56 @@
         <v>0.8</v>
       </c>
       <c r="U38" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V38" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="W38" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="X38" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y38" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z38" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA38" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="E39">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="F39">
-        <v>1.3900000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G39">
-        <v>0.46800000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H39" s="2">
-        <f>$P$47</f>
-        <v>2950.7891</v>
+        <f>$P$45</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I39" s="3">
-        <f t="shared" si="0"/>
-        <v>133.5792717679</v>
+        <f t="shared" ref="I39:I41" si="1">($O$45/100)*H39</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J39">
-        <f>$R$47</f>
+        <f>$R$45</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K39">
@@ -4409,58 +4452,57 @@
         <v>0.8</v>
       </c>
       <c r="U39" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V39" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="W39" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="X39" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y39" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z39" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA39" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>191</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="E40">
-        <v>1997</v>
+        <v>2019</v>
       </c>
       <c r="F40">
-        <v>0.01</v>
+        <v>9.300000000000001E-3</v>
       </c>
       <c r="G40">
-        <f>Q44</f>
-        <v>0.33</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H40" s="2">
-        <f>P44</f>
-        <v>4812.0244000000002</v>
+        <f>$P$45</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I40" s="3">
-        <f>($O$44/100)*H40</f>
-        <v>63.037519640000006</v>
+        <f t="shared" si="1"/>
+        <v>162.96753257730003</v>
       </c>
       <c r="J40">
-        <f>$R$44</f>
-        <v>4.1005000000000003</v>
+        <f>$R$45</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K40">
         <v>40</v>
@@ -4468,117 +4510,145 @@
       <c r="M40">
         <v>0.8</v>
       </c>
+      <c r="O40" t="s">
+        <v>185</v>
+      </c>
+      <c r="P40" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>193</v>
+      </c>
+      <c r="R40" t="s">
+        <v>194</v>
+      </c>
       <c r="U40" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V40" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="W40" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="X40" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y40" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z40" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA40" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E41">
-        <v>2016</v>
+        <v>1963</v>
       </c>
       <c r="F41">
-        <v>0.01</v>
+        <v>7.0999999999999995E-3</v>
       </c>
       <c r="G41">
         <v>0.28999999999999998</v>
       </c>
       <c r="H41" s="2">
-        <f>$P$48</f>
+        <f>$P$45</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I41" s="3">
-        <f>($O$48/100)*H41</f>
+        <f t="shared" si="1"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J41">
-        <f>$R$48</f>
+        <f>$R$45</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K41">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="M41">
         <v>0.8</v>
       </c>
+      <c r="N41" t="s">
+        <v>171</v>
+      </c>
+      <c r="O41" s="4">
+        <v>1.31</v>
+      </c>
+      <c r="P41" s="2">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="Q41">
+        <v>0.33</v>
+      </c>
+      <c r="R41">
+        <v>4.1005000000000003</v>
+      </c>
       <c r="U41" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V41" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="W41" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="X41" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y41" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z41" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA41" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="E42">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="F42">
-        <v>0.01</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="G42">
-        <v>0.28999999999999998</v>
+        <f>Q42</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H42" s="2">
-        <f>$P$48</f>
-        <v>4516.7133000000003</v>
+        <f>P42</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I42" s="3">
-        <f t="shared" ref="I42:I44" si="1">($O$48/100)*H42</f>
-        <v>162.96753257730003</v>
+        <f>($O$42/100)*H42</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J42">
-        <f>$R$48</f>
-        <v>2.8138000000000001</v>
+        <f>$R$42</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K42">
         <v>40</v>
@@ -4586,57 +4656,72 @@
       <c r="M42">
         <v>0.8</v>
       </c>
+      <c r="N42" t="s">
+        <v>190</v>
+      </c>
+      <c r="O42" s="4">
+        <v>3.3294999999999999</v>
+      </c>
+      <c r="P42" s="2">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="Q42">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R42">
+        <v>5.8775000000000004</v>
+      </c>
       <c r="U42" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V42" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="W42" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="X42" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y42" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z42" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA42" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="E43">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="F43">
-        <v>9.300000000000001E-3</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="G43">
         <v>0.28999999999999998</v>
       </c>
       <c r="H43" s="2">
-        <f>$P$48</f>
+        <f>P45</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I43" s="3">
-        <f t="shared" si="1"/>
+        <f>($O$45/100)*H43</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J43">
-        <f>$R$48</f>
+        <f>$R$45</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K43">
@@ -4645,145 +4730,139 @@
       <c r="M43">
         <v>0.8</v>
       </c>
-      <c r="O43" t="s">
-        <v>205</v>
-      </c>
-      <c r="P43" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>213</v>
-      </c>
-      <c r="R43" t="s">
-        <v>214</v>
-      </c>
+      <c r="N43" t="s">
+        <v>191</v>
+      </c>
+      <c r="O43" s="4"/>
+      <c r="P43" s="2"/>
       <c r="U43" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V43" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="W43" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="X43" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y43" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z43" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA43" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D44" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="E44">
-        <v>1963</v>
+        <v>2015</v>
       </c>
       <c r="F44">
-        <v>7.0999999999999995E-3</v>
+        <v>4.0999999999999995E-3</v>
       </c>
       <c r="G44">
-        <v>0.28999999999999998</v>
+        <f>Q42</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H44" s="2">
-        <f>$P$48</f>
-        <v>4516.7133000000003</v>
+        <f>P42</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I44" s="3">
-        <f t="shared" si="1"/>
-        <v>162.96753257730003</v>
+        <f>($O$42/100)*H44</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J44">
-        <f>$R$48</f>
-        <v>2.8138000000000001</v>
+        <f>$R$42</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K44">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M44">
         <v>0.8</v>
       </c>
       <c r="N44" t="s">
-        <v>191</v>
-      </c>
-      <c r="O44" s="4">
-        <v>1.31</v>
+        <v>188</v>
+      </c>
+      <c r="O44">
+        <v>4.5269000000000004</v>
       </c>
       <c r="P44" s="2">
-        <v>4812.0244000000002</v>
+        <v>2950.7891</v>
       </c>
       <c r="Q44">
-        <v>0.33</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="R44">
-        <v>4.1005000000000003</v>
+        <v>2.8138000000000001</v>
       </c>
       <c r="U44" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V44" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="W44" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="X44" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y44" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z44" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA44" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="D45" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="E45">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="F45">
-        <v>5.7999999999999996E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G45">
-        <f>Q45</f>
-        <v>0.56000000000000005</v>
+        <f>Q41</f>
+        <v>0.33</v>
       </c>
       <c r="H45" s="2">
-        <f>P45</f>
-        <v>1175.5066999999999</v>
+        <f>P41</f>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I45" s="3">
         <f>($O$45/100)*H45</f>
-        <v>39.138495576499992</v>
+        <v>173.62265237640003</v>
       </c>
       <c r="J45">
-        <f>$R$45</f>
-        <v>5.8775000000000004</v>
+        <f>$R$41</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K45">
         <v>40</v>
@@ -4792,71 +4871,71 @@
         <v>0.8</v>
       </c>
       <c r="N45" t="s">
-        <v>210</v>
-      </c>
-      <c r="O45" s="4">
-        <v>3.3294999999999999</v>
+        <v>189</v>
+      </c>
+      <c r="O45">
+        <v>3.6080999999999999</v>
       </c>
       <c r="P45" s="2">
-        <v>1175.5066999999999</v>
+        <v>4516.7133000000003</v>
       </c>
       <c r="Q45">
-        <v>0.56000000000000005</v>
+        <v>0.2994</v>
       </c>
       <c r="R45">
-        <v>5.8775000000000004</v>
+        <v>2.8138000000000001</v>
       </c>
       <c r="U45" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V45" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="W45" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="X45" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y45" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z45" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA45" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="E46">
         <v>2013</v>
       </c>
       <c r="F46">
-        <v>6.4999999999999997E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G46">
         <v>0.28999999999999998</v>
       </c>
       <c r="H46" s="2">
-        <f>P48</f>
+        <f>P45</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I46" s="3">
-        <f>($O$48/100)*H46</f>
+        <f>($O$45/100)*H46</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J46">
-        <f>$R$48</f>
+        <f>$R$45</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K46">
@@ -4865,64 +4944,60 @@
       <c r="M46">
         <v>0.8</v>
       </c>
-      <c r="N46" t="s">
-        <v>211</v>
-      </c>
-      <c r="O46" s="4"/>
-      <c r="P46" s="2"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="4"/>
       <c r="U46" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V46" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="W46" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="X46" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y46" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z46" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA46" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="E47">
         <v>2015</v>
       </c>
       <c r="F47">
-        <v>4.0999999999999995E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="G47">
-        <f>Q45</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H47" s="2">
         <f>P45</f>
-        <v>1175.5066999999999</v>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I47" s="3">
         <f>($O$45/100)*H47</f>
-        <v>39.138495576499992</v>
+        <v>162.96753257730003</v>
       </c>
       <c r="J47">
         <f>$R$45</f>
-        <v>5.8775000000000004</v>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K47">
         <v>40</v>
@@ -4930,74 +5005,61 @@
       <c r="M47">
         <v>0.8</v>
       </c>
-      <c r="N47" t="s">
-        <v>208</v>
-      </c>
-      <c r="O47">
-        <v>4.5269000000000004</v>
-      </c>
-      <c r="P47" s="2">
-        <v>2950.7891</v>
-      </c>
-      <c r="Q47">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="R47">
-        <v>2.8138000000000001</v>
-      </c>
+      <c r="O47" s="3"/>
+      <c r="P47" s="4"/>
       <c r="U47" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V47" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="W47" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="X47" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y47" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z47" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA47" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="C48" t="s">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="E48">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="F48">
-        <v>1.4E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G48">
-        <f>Q44</f>
-        <v>0.33</v>
+        <f>Q42</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H48" s="2">
-        <f>P44</f>
-        <v>4812.0244000000002</v>
+        <f>P42</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I48" s="3">
-        <f>($O$48/100)*H48</f>
-        <v>173.62265237640003</v>
+        <f t="shared" ref="I48:I49" si="2">($O$42/100)*H48</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J48">
-        <f>$R$44</f>
-        <v>4.1005000000000003</v>
+        <f>$R$42</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K48">
         <v>40</v>
@@ -5005,73 +5067,61 @@
       <c r="M48">
         <v>0.8</v>
       </c>
-      <c r="N48" t="s">
-        <v>209</v>
-      </c>
-      <c r="O48">
-        <v>3.6080999999999999</v>
-      </c>
-      <c r="P48" s="2">
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="Q48">
-        <v>0.2994</v>
-      </c>
-      <c r="R48">
-        <v>2.8138000000000001</v>
-      </c>
+      <c r="O48" s="3"/>
+      <c r="P48" s="4"/>
       <c r="U48" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V48" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="W48" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="X48" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y48" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z48" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA48" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="E49">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="F49">
         <v>1.8E-3</v>
       </c>
       <c r="G49">
-        <v>0.28999999999999998</v>
+        <f>Q42</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H49" s="2">
-        <f>P48</f>
-        <v>4516.7133000000003</v>
+        <f>P42</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I49" s="3">
-        <f>($O$48/100)*H49</f>
-        <v>162.96753257730003</v>
+        <f t="shared" si="2"/>
+        <v>39.138495576499992</v>
       </c>
       <c r="J49">
-        <f>$R$48</f>
-        <v>2.8138000000000001</v>
+        <f>$R$42</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K49">
         <v>40</v>
@@ -5082,56 +5132,56 @@
       <c r="O49" s="3"/>
       <c r="P49" s="4"/>
       <c r="U49" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V49" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="W49" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="X49" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y49" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z49" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA49" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="E50">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F50">
-        <v>1.6999999999999999E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G50">
         <v>0.28999999999999998</v>
       </c>
       <c r="H50" s="2">
-        <f>P48</f>
+        <f>P45</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I50" s="3">
-        <f>($O$48/100)*H50</f>
+        <f>($O$45/100)*H50</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J50">
-        <f>$R$48</f>
+        <f t="shared" ref="J50:J55" si="3">$R$45</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K50">
@@ -5140,61 +5190,58 @@
       <c r="M50">
         <v>0.8</v>
       </c>
-      <c r="O50" s="3"/>
-      <c r="P50" s="4"/>
       <c r="U50" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V50" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="W50" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="X50" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y50" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z50" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA50" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="E51">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="F51">
-        <v>1.8E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G51">
-        <f>Q45</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H51" s="2">
-        <f>P45</f>
-        <v>1175.5066999999999</v>
+        <f>$P$45</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I51" s="3">
-        <f t="shared" ref="I51:I52" si="2">($O$45/100)*H51</f>
-        <v>39.138495576499992</v>
+        <f t="shared" ref="I51:I55" si="4">($O$45/100)*H51</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J51">
-        <f>$R$45</f>
-        <v>5.8775000000000004</v>
+        <f t="shared" si="3"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K51">
         <v>40</v>
@@ -5202,61 +5249,58 @@
       <c r="M51">
         <v>0.8</v>
       </c>
-      <c r="O51" s="3"/>
-      <c r="P51" s="4"/>
       <c r="U51" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V51" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="W51" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="X51" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y51" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z51" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA51" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="E52">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F52">
-        <v>1.8E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G52">
-        <f>Q45</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H52" s="2">
-        <f>P45</f>
-        <v>1175.5066999999999</v>
+        <f>$P$45</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I52" s="3">
-        <f t="shared" si="2"/>
-        <v>39.138495576499992</v>
+        <f t="shared" si="4"/>
+        <v>162.96753257730003</v>
       </c>
       <c r="J52">
-        <f>$R$45</f>
-        <v>5.8775000000000004</v>
+        <f t="shared" si="3"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K52">
         <v>40</v>
@@ -5264,59 +5308,57 @@
       <c r="M52">
         <v>0.8</v>
       </c>
-      <c r="O52" s="3"/>
-      <c r="P52" s="4"/>
       <c r="U52" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V52" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="W52" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="X52" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y52" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z52" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA52" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="E53">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="F53">
-        <v>1.5E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G53">
         <v>0.28999999999999998</v>
       </c>
       <c r="H53" s="2">
-        <f>P48</f>
+        <f>P45</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I53" s="3">
-        <f>($O$48/100)*H53</f>
+        <f t="shared" si="4"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J53">
-        <f t="shared" ref="J53:J58" si="3">$R$48</f>
+        <f t="shared" si="3"/>
         <v>2.8138000000000001</v>
       </c>
       <c r="K53">
@@ -5326,52 +5368,52 @@
         <v>0.8</v>
       </c>
       <c r="U53" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V53" t="s">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="W53" t="s">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="X53" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y53" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z53" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="AA53" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="E54">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="F54">
-        <v>1.4E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="G54">
         <v>0.28999999999999998</v>
       </c>
       <c r="H54" s="2">
-        <f>$P$48</f>
+        <f>P45</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I54" s="3">
-        <f t="shared" ref="I54:I58" si="4">($O$48/100)*H54</f>
+        <f t="shared" si="4"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J54">
@@ -5384,49 +5426,28 @@
       <c r="M54">
         <v>0.8</v>
       </c>
-      <c r="U54" t="s">
-        <v>69</v>
-      </c>
-      <c r="V54" t="s">
-        <v>187</v>
-      </c>
-      <c r="W54" t="s">
-        <v>189</v>
-      </c>
-      <c r="X54" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA54" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="55" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="E55">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F55">
-        <v>1.1999999999999999E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="G55">
         <v>0.28999999999999998</v>
       </c>
       <c r="H55" s="2">
-        <f>$P$48</f>
+        <f>P45</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I55" s="3">
@@ -5443,609 +5464,558 @@
       <c r="M55">
         <v>0.8</v>
       </c>
-      <c r="U55" t="s">
-        <v>69</v>
-      </c>
-      <c r="V55" t="s">
-        <v>190</v>
-      </c>
-      <c r="W55" t="s">
-        <v>220</v>
-      </c>
-      <c r="X55" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA55" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="56" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D56" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E56">
-        <v>2009</v>
+        <v>2022</v>
       </c>
       <c r="F56">
-        <v>1.9E-3</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G56">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H56" s="2">
-        <f>P48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I56" s="3">
-        <f t="shared" si="4"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J56">
-        <f t="shared" si="3"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K56">
-        <v>40</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="M56">
         <v>0.8</v>
       </c>
-      <c r="U56" t="s">
-        <v>69</v>
-      </c>
-      <c r="V56" t="s">
-        <v>18</v>
-      </c>
-      <c r="W56" t="s">
-        <v>78</v>
-      </c>
-      <c r="X56" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y56" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z56" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA56" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B57" t="s">
-        <v>187</v>
-      </c>
-      <c r="C57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D57" t="s">
-        <v>223</v>
-      </c>
-      <c r="E57">
-        <v>2012</v>
-      </c>
-      <c r="F57">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="G57">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H57" s="2">
-        <f>P48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I57" s="3">
-        <f t="shared" si="4"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J57">
-        <f t="shared" si="3"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K57">
-        <v>40</v>
-      </c>
-      <c r="M57">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="58" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>190</v>
-      </c>
-      <c r="C58" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" t="s">
-        <v>222</v>
-      </c>
-      <c r="E58">
-        <v>2015</v>
-      </c>
-      <c r="F58">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="G58">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H58" s="2">
-        <f>P48</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I58" s="3">
-        <f t="shared" si="4"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J58">
-        <f t="shared" si="3"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K58">
-        <v>40</v>
-      </c>
-      <c r="M58">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
-        <v>18</v>
-      </c>
-      <c r="C59" t="s">
-        <v>19</v>
-      </c>
-      <c r="D59" t="s">
-        <v>221</v>
-      </c>
-      <c r="E59">
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="V72" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="U73" t="s">
+        <v>49</v>
+      </c>
+      <c r="V73" t="s">
+        <v>24</v>
+      </c>
+      <c r="W73" t="s">
+        <v>58</v>
+      </c>
+      <c r="X73" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="U74" t="s">
+        <v>49</v>
+      </c>
+      <c r="V74" t="s">
+        <v>27</v>
+      </c>
+      <c r="W74" t="s">
+        <v>58</v>
+      </c>
+      <c r="X74" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="U75" t="s">
+        <v>49</v>
+      </c>
+      <c r="V75" t="s">
+        <v>29</v>
+      </c>
+      <c r="W75" t="s">
+        <v>58</v>
+      </c>
+      <c r="X75" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="U76" t="s">
+        <v>49</v>
+      </c>
+      <c r="V76" t="s">
+        <v>31</v>
+      </c>
+      <c r="W76" t="s">
+        <v>58</v>
+      </c>
+      <c r="X76" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="U77" t="s">
+        <v>49</v>
+      </c>
+      <c r="V77" t="s">
+        <v>33</v>
+      </c>
+      <c r="W77" t="s">
+        <v>58</v>
+      </c>
+      <c r="X77" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="78" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="U78" t="s">
+        <v>49</v>
+      </c>
+      <c r="V78" t="s">
+        <v>35</v>
+      </c>
+      <c r="W78" t="s">
+        <v>58</v>
+      </c>
+      <c r="X78" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79">
+        <v>2013</v>
+      </c>
+      <c r="F79">
+        <v>0.25109999999999999</v>
+      </c>
+      <c r="G79">
+        <v>0.36049999999999999</v>
+      </c>
+      <c r="H79">
+        <v>1265</v>
+      </c>
+      <c r="I79" s="3">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="J79">
+        <v>7.5075000000000003</v>
+      </c>
+      <c r="K79">
+        <v>42</v>
+      </c>
+      <c r="U79" t="s">
+        <v>49</v>
+      </c>
+      <c r="V79" t="s">
+        <v>37</v>
+      </c>
+      <c r="W79" t="s">
+        <v>58</v>
+      </c>
+      <c r="X79" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="80" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80">
         <v>2022</v>
       </c>
-      <c r="F59">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G59">
+      <c r="F80">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="G80">
         <v>0.33123000000000002</v>
       </c>
-      <c r="M59">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="75" spans="21:27" x14ac:dyDescent="0.25">
-      <c r="V75" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="76" spans="21:27" x14ac:dyDescent="0.25">
-      <c r="U76" t="s">
-        <v>69</v>
-      </c>
-      <c r="V76" t="s">
-        <v>44</v>
-      </c>
-      <c r="W76" t="s">
-        <v>78</v>
-      </c>
-      <c r="X76" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y76" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z76" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA76" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="77" spans="21:27" x14ac:dyDescent="0.25">
-      <c r="U77" t="s">
-        <v>69</v>
-      </c>
-      <c r="V77" t="s">
-        <v>47</v>
-      </c>
-      <c r="W77" t="s">
-        <v>78</v>
-      </c>
-      <c r="X77" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z77" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA77" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78" spans="21:27" x14ac:dyDescent="0.25">
-      <c r="U78" t="s">
-        <v>69</v>
-      </c>
-      <c r="V78" t="s">
-        <v>49</v>
-      </c>
-      <c r="W78" t="s">
-        <v>78</v>
-      </c>
-      <c r="X78" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y78" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA78" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="79" spans="21:27" x14ac:dyDescent="0.25">
-      <c r="U79" t="s">
-        <v>69</v>
-      </c>
-      <c r="V79" t="s">
-        <v>51</v>
-      </c>
-      <c r="W79" t="s">
-        <v>78</v>
-      </c>
-      <c r="X79" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y79" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z79" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA79" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="80" spans="21:27" x14ac:dyDescent="0.25">
       <c r="U80" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V80" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="W80" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="X80" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y80" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z80" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AA80" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U81" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V81" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="W81" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="X81" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y81" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z81" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="AA81" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D82" t="s">
         <v>14</v>
       </c>
       <c r="E82">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="F82">
-        <v>0.25109999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="G82">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H82">
-        <v>1265</v>
+        <v>4427.5</v>
       </c>
       <c r="I82" s="3">
-        <v>48.400000000000006</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J82">
-        <v>7.5075000000000003</v>
+        <v>9.24</v>
       </c>
       <c r="K82">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="U82" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V82" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="W82" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="X82" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y82" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z82" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="AA82" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="83" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
-        <v>15</v>
-      </c>
-      <c r="C83" t="s">
-        <v>16</v>
-      </c>
-      <c r="D83" t="s">
-        <v>14</v>
-      </c>
-      <c r="E83">
-        <v>2022</v>
-      </c>
-      <c r="F83">
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="G83">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="U83" t="s">
-        <v>69</v>
-      </c>
-      <c r="V83" t="s">
-        <v>59</v>
-      </c>
-      <c r="W83" t="s">
-        <v>78</v>
-      </c>
-      <c r="X83" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y83" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z83" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA83" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U84" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="V84" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="W84" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="X84" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y84" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="Z84" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="AA84" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B85" t="s">
-        <v>12</v>
-      </c>
-      <c r="C85" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" t="s">
-        <v>14</v>
-      </c>
-      <c r="E85">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="87" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" t="s">
+        <v>25</v>
+      </c>
+      <c r="D87" t="s">
+        <v>26</v>
+      </c>
+      <c r="E87">
         <v>2022</v>
       </c>
-      <c r="F85">
-        <v>0.3</v>
-      </c>
-      <c r="G85">
-        <v>0.33990000000000004</v>
-      </c>
-      <c r="H85">
-        <v>4427.5</v>
-      </c>
-      <c r="I85" s="3">
-        <v>157.30000000000001</v>
-      </c>
-      <c r="J85">
-        <v>9.24</v>
-      </c>
-      <c r="K85">
-        <v>50</v>
-      </c>
-      <c r="U85" t="s">
-        <v>69</v>
-      </c>
-      <c r="V85" t="s">
-        <v>15</v>
-      </c>
-      <c r="W85" t="s">
-        <v>75</v>
-      </c>
-      <c r="X85" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y85" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z85" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA85" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="87" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="U87" t="s">
-        <v>69</v>
-      </c>
-      <c r="V87" t="s">
-        <v>12</v>
-      </c>
-      <c r="W87" t="s">
-        <v>70</v>
-      </c>
-      <c r="X87" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y87" t="s">
-        <v>72</v>
-      </c>
-      <c r="Z87" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA87" t="s">
-        <v>74</v>
+      <c r="F87">
+        <v>1.5040605442498314E-2</v>
+      </c>
+      <c r="G87">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L87">
+        <v>0.42012333946150526</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="88" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88" t="s">
+        <v>25</v>
+      </c>
+      <c r="D88" t="s">
+        <v>28</v>
+      </c>
+      <c r="E88">
+        <v>2022</v>
+      </c>
+      <c r="F88">
+        <v>1.5497656626156837E-2</v>
+      </c>
+      <c r="G88">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L88">
+        <v>0.42012333946150526</v>
+      </c>
+    </row>
+    <row r="89" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" t="s">
+        <v>30</v>
+      </c>
+      <c r="E89">
+        <v>2022</v>
+      </c>
+      <c r="F89">
+        <v>1.4461737931344828E-2</v>
+      </c>
+      <c r="G89">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L89">
+        <v>0.42012333946150526</v>
       </c>
     </row>
     <row r="90" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C90" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D90" t="s">
+        <v>32</v>
+      </c>
+      <c r="E90">
+        <v>2009</v>
+      </c>
+      <c r="F90">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>2376</v>
+      </c>
+      <c r="I90" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J90">
+        <v>2.52</v>
+      </c>
+      <c r="K90">
         <v>46</v>
       </c>
-      <c r="E90">
-        <v>2022</v>
-      </c>
-      <c r="F90">
-        <v>1.5040605442498314E-2</v>
-      </c>
-      <c r="G90">
-        <v>0.33123000000000002</v>
-      </c>
       <c r="L90">
-        <v>0.42012333946150526</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>207</v>
+        <v>0.47763777043344691</v>
       </c>
     </row>
     <row r="91" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C91" t="s">
+        <v>25</v>
+      </c>
+      <c r="D91" t="s">
+        <v>34</v>
+      </c>
+      <c r="E91">
+        <v>2010</v>
+      </c>
+      <c r="F91">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>2376</v>
+      </c>
+      <c r="I91" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J91">
+        <v>2.52</v>
+      </c>
+      <c r="K91">
         <v>45</v>
       </c>
-      <c r="D91" t="s">
-        <v>48</v>
-      </c>
-      <c r="E91">
-        <v>2022</v>
-      </c>
-      <c r="F91">
-        <v>1.5497656626156837E-2</v>
-      </c>
-      <c r="G91">
-        <v>0.33123000000000002</v>
-      </c>
       <c r="L91">
-        <v>0.42012333946150526</v>
+        <v>0.47814004703314078</v>
       </c>
     </row>
     <row r="92" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C92" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E92">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F92">
-        <v>1.4461737931344828E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G92">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>2376</v>
+      </c>
+      <c r="I92" s="3">
+        <v>57.20000000000001</v>
+      </c>
+      <c r="J92">
+        <v>2.52</v>
+      </c>
+      <c r="K92">
+        <v>40</v>
       </c>
       <c r="L92">
-        <v>0.42012333946150526</v>
+        <v>0.47814004703314084</v>
       </c>
     </row>
     <row r="93" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C93" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E93">
-        <v>2009</v>
+        <v>2020</v>
       </c>
       <c r="F93">
-        <v>3.9E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -6054,33 +6024,33 @@
         <v>2376</v>
       </c>
       <c r="I93" s="3">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J93">
         <v>2.52</v>
       </c>
       <c r="K93">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="L93">
-        <v>0.47763777043344691</v>
+        <v>0.47814004703314078</v>
       </c>
     </row>
     <row r="94" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C94" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E94">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="F94">
-        <v>1.6E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -6095,27 +6065,27 @@
         <v>2.52</v>
       </c>
       <c r="K94">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L94">
-        <v>0.47814004703314078</v>
+        <v>0.40144059976798208</v>
       </c>
     </row>
     <row r="95" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E95">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="F95">
-        <v>1.7999999999999999E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -6130,27 +6100,27 @@
         <v>2.52</v>
       </c>
       <c r="K95">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L95">
-        <v>0.47814004703314084</v>
+        <v>0.40144059976798202</v>
       </c>
     </row>
     <row r="96" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C96" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E96">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="F96">
-        <v>1.2E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -6159,30 +6129,30 @@
         <v>2376</v>
       </c>
       <c r="I96" s="3">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J96">
         <v>2.52</v>
       </c>
       <c r="K96">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L96">
-        <v>0.47814004703314078</v>
+        <v>0.40144059976798202</v>
       </c>
     </row>
     <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C97" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="E97">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="F97">
         <v>2.1000000000000001E-2</v>
@@ -6200,7 +6170,7 @@
         <v>2.52</v>
       </c>
       <c r="K97">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="L97">
         <v>0.40144059976798208</v>
@@ -6208,34 +6178,34 @@
     </row>
     <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C98" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="E98">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="F98">
-        <v>2.4E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="G98">
         <v>1</v>
       </c>
       <c r="H98">
-        <v>2376</v>
+        <v>2024</v>
       </c>
       <c r="I98" s="3">
-        <v>57.20000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="J98">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K98">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="L98">
         <v>0.40144059976798202</v>
@@ -6243,19 +6213,19 @@
     </row>
     <row r="99" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="C99" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E99">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="F99">
-        <v>7.9000000000000001E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -6270,27 +6240,27 @@
         <v>2.52</v>
       </c>
       <c r="K99">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L99">
-        <v>0.40144059976798202</v>
+        <v>0.365520596150406</v>
       </c>
     </row>
     <row r="100" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C100" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E100">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="F100">
-        <v>2.1000000000000001E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -6299,68 +6269,68 @@
         <v>2376</v>
       </c>
       <c r="I100" s="3">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J100">
         <v>2.52</v>
       </c>
       <c r="K100">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="L100">
-        <v>0.40144059976798208</v>
+        <v>0.41047488326249421</v>
       </c>
     </row>
     <row r="101" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C101" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E101">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="F101">
-        <v>0.10199999999999999</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G101">
         <v>1</v>
       </c>
       <c r="H101">
-        <v>2024</v>
+        <v>2376</v>
       </c>
       <c r="I101" s="3">
-        <v>48.4</v>
+        <v>57.2</v>
       </c>
       <c r="J101">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K101">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L101">
-        <v>0.40144059976798202</v>
+        <v>0.41047488326249421</v>
       </c>
     </row>
     <row r="102" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C102" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E102">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="F102">
-        <v>3.9E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -6375,114 +6345,9 @@
         <v>2.52</v>
       </c>
       <c r="K102">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L102">
-        <v>0.365520596150406</v>
-      </c>
-    </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
-        <v>59</v>
-      </c>
-      <c r="C103" t="s">
-        <v>45</v>
-      </c>
-      <c r="D103" t="s">
-        <v>60</v>
-      </c>
-      <c r="E103">
-        <v>2005</v>
-      </c>
-      <c r="F103">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G103">
-        <v>1</v>
-      </c>
-      <c r="H103">
-        <v>2376</v>
-      </c>
-      <c r="I103" s="3">
-        <v>57.20000000000001</v>
-      </c>
-      <c r="J103">
-        <v>2.52</v>
-      </c>
-      <c r="K103">
-        <v>50</v>
-      </c>
-      <c r="L103">
-        <v>0.41047488326249421</v>
-      </c>
-    </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
-        <v>59</v>
-      </c>
-      <c r="C104" t="s">
-        <v>45</v>
-      </c>
-      <c r="D104" t="s">
-        <v>60</v>
-      </c>
-      <c r="E104">
-        <v>2012</v>
-      </c>
-      <c r="F104">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="G104">
-        <v>1</v>
-      </c>
-      <c r="H104">
-        <v>2376</v>
-      </c>
-      <c r="I104" s="3">
-        <v>57.2</v>
-      </c>
-      <c r="J104">
-        <v>2.52</v>
-      </c>
-      <c r="K104">
-        <v>43</v>
-      </c>
-      <c r="L104">
-        <v>0.41047488326249421</v>
-      </c>
-    </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B105" t="s">
-        <v>59</v>
-      </c>
-      <c r="C105" t="s">
-        <v>45</v>
-      </c>
-      <c r="D105" t="s">
-        <v>60</v>
-      </c>
-      <c r="E105">
-        <v>2013</v>
-      </c>
-      <c r="F105">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="G105">
-        <v>1</v>
-      </c>
-      <c r="H105">
-        <v>2376</v>
-      </c>
-      <c r="I105" s="3">
-        <v>57.2</v>
-      </c>
-      <c r="J105">
-        <v>2.52</v>
-      </c>
-      <c r="K105">
-        <v>42</v>
-      </c>
-      <c r="L105">
         <v>0.41047488326249421</v>
       </c>
     </row>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC48194-AFDF-4756-A0A8-3C219FFD9F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6560CA8C-B5AB-48C8-9986-69B953E44BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -73,11 +73,11 @@
     <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
     <author>tc={C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}</author>
     <author>tc={C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}</author>
+    <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
     <author>tc={1905391B-2A5F-4643-B2AC-720AD8410CDA}</author>
-    <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
   </authors>
   <commentList>
-    <comment ref="Z20" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+    <comment ref="Z21" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +85,7 @@
     Miks daynite (hydro samuti)</t>
       </text>
     </comment>
-    <comment ref="F27" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <comment ref="F25" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -93,7 +93,7 @@
     Iru produces only 17 MW in 2025 not 0.207 GW</t>
       </text>
     </comment>
-    <comment ref="B28" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+    <comment ref="B26" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -101,7 +101,7 @@
     TODO: set their actual start date and then add how much they produce in 2025</t>
       </text>
     </comment>
-    <comment ref="E36" authorId="3" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
+    <comment ref="E34" authorId="3" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -127,7 +127,15 @@
     Took same as chp</t>
       </text>
     </comment>
-    <comment ref="U81" authorId="6" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
+    <comment ref="J79" authorId="6" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    From 9,24 to 6</t>
+      </text>
+    </comment>
+    <comment ref="U81" authorId="7" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -135,20 +143,12 @@
     Frequency reserve</t>
       </text>
     </comment>
-    <comment ref="J82" authorId="7" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    From 9,24 to 6</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="232">
   <si>
     <t>~fi_t</t>
   </si>
@@ -841,6 +841,9 @@
   </si>
   <si>
     <t>ep_solar_pv_jogeva</t>
+  </si>
+  <si>
+    <t>elc_spv_jarva</t>
   </si>
 </sst>
 </file>
@@ -1244,16 +1247,16 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="Z20" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+  <threadedComment ref="Z21" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
     <text>Miks daynite (hydro samuti)</text>
   </threadedComment>
-  <threadedComment ref="F27" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+  <threadedComment ref="F25" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
-  <threadedComment ref="B28" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+  <threadedComment ref="B26" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
     <text>TODO: set their actual start date and then add how much they produce in 2025</text>
   </threadedComment>
-  <threadedComment ref="E36" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
+  <threadedComment ref="E34" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
     <text xml:space="preserve">Ei tea
 </text>
   </threadedComment>
@@ -1264,11 +1267,11 @@
   <threadedComment ref="R44" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
     <text>Took same as chp</text>
   </threadedComment>
+  <threadedComment ref="J79" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <text>From 9,24 to 6</text>
+  </threadedComment>
   <threadedComment ref="U81" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
     <text>Frequency reserve</text>
-  </threadedComment>
-  <threadedComment ref="J82" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
-    <text>From 9,24 to 6</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -2758,7 +2761,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:AA102"/>
+  <dimension ref="B9:AA99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
@@ -2860,25 +2863,26 @@
         <v>212</v>
       </c>
       <c r="E11">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F11">
-        <v>7.6700000000000004E-2</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
-      <c r="H11">
-        <v>1336.4999999999998</v>
+      <c r="H11" s="2">
+        <v>1018</v>
       </c>
       <c r="I11" s="3">
-        <v>21.45</v>
+        <f>($O$46/100)*H11</f>
+        <v>16.064040000000002</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L11">
         <v>0.1461854238754417</v>
@@ -2907,34 +2911,35 @@
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E12">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F12">
-        <v>3.2000000000000001E-2</v>
+        <v>0.108</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
-      <c r="H12">
-        <v>1336.5</v>
+      <c r="H12" s="2">
+        <v>1018</v>
       </c>
       <c r="I12" s="3">
-        <v>21.450000000000003</v>
+        <f t="shared" ref="I12:I20" si="0">($O$46/100)*H12</f>
+        <v>16.064040000000002</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L12">
         <v>0.1461854238754417</v>
@@ -2963,34 +2968,35 @@
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E13">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F13">
-        <v>5.8200000000000002E-2</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
-      <c r="H13">
-        <v>1336.5</v>
+      <c r="H13" s="2">
+        <v>1018</v>
       </c>
       <c r="I13" s="3">
-        <v>21.450000000000003</v>
+        <f t="shared" si="0"/>
+        <v>16.064040000000002</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L13">
         <v>0.14867925344692126</v>
@@ -3019,34 +3025,35 @@
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E14">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F14">
-        <v>2.9599999999999998E-2</v>
+        <v>7.8E-2</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
-      <c r="H14">
-        <v>1336.5000000000002</v>
+      <c r="H14" s="2">
+        <v>1018</v>
       </c>
       <c r="I14" s="3">
-        <v>21.450000000000003</v>
+        <f t="shared" si="0"/>
+        <v>16.064040000000002</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L14">
         <v>0.14701259708091721</v>
@@ -3075,34 +3082,35 @@
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="E15">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F15">
-        <v>5.3800000000000008E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
-      <c r="H15">
-        <v>1336.4999999999998</v>
+      <c r="H15" s="2">
+        <v>1018</v>
       </c>
       <c r="I15" s="3">
-        <v>21.45</v>
+        <f t="shared" si="0"/>
+        <v>16.064040000000002</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L15">
         <v>0.15309859852159369</v>
@@ -3131,34 +3139,35 @@
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E16">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F16">
-        <v>7.0000000000000007E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
-      <c r="H16">
-        <v>1138.5</v>
+      <c r="H16" s="2">
+        <v>1018</v>
       </c>
       <c r="I16" s="3">
-        <v>18.150000000000002</v>
+        <f t="shared" si="0"/>
+        <v>16.064040000000002</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L16">
         <v>0.15309859852159369</v>
@@ -3167,7 +3176,7 @@
         <v>49</v>
       </c>
       <c r="V16" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="W16" t="s">
         <v>58</v>
@@ -3187,34 +3196,35 @@
     </row>
     <row r="17" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E17">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F17">
-        <v>7.3000000000000009E-3</v>
+        <v>0.04</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
-      <c r="H17">
-        <v>1336.5</v>
+      <c r="H17" s="2">
+        <v>1018</v>
       </c>
       <c r="I17" s="3">
-        <v>21.45</v>
+        <f t="shared" si="0"/>
+        <v>16.064040000000002</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L17">
         <v>0.15619560585976827</v>
@@ -3223,7 +3233,7 @@
         <v>49</v>
       </c>
       <c r="V17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="W17" t="s">
         <v>58</v>
@@ -3243,34 +3253,35 @@
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E18">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F18">
-        <v>2.81E-2</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
-      <c r="H18">
-        <v>1336.5</v>
+      <c r="H18" s="2">
+        <v>1018</v>
       </c>
       <c r="I18" s="3">
-        <v>21.450000000000003</v>
+        <f t="shared" si="0"/>
+        <v>16.064040000000002</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L18">
         <v>0.14537310453496291</v>
@@ -3279,7 +3290,7 @@
         <v>49</v>
       </c>
       <c r="V18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="W18" t="s">
         <v>58</v>
@@ -3299,34 +3310,35 @@
     </row>
     <row r="19" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E19">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F19">
-        <v>8.4900000000000003E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
-      <c r="H19">
-        <v>1336.5</v>
+      <c r="H19" s="2">
+        <v>1018</v>
       </c>
       <c r="I19" s="3">
-        <v>21.450000000000003</v>
+        <f t="shared" si="0"/>
+        <v>16.064040000000002</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L19">
         <v>0.14763873655681015</v>
@@ -3335,7 +3347,7 @@
         <v>49</v>
       </c>
       <c r="V19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="W19" t="s">
         <v>58</v>
@@ -3355,34 +3367,35 @@
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E20">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F20">
-        <v>5.2399999999999995E-2</v>
+        <v>0.08</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
-      <c r="H20">
-        <v>1336.5000000000002</v>
+      <c r="H20" s="2">
+        <v>1018</v>
       </c>
       <c r="I20" s="3">
-        <v>21.45</v>
+        <f t="shared" si="0"/>
+        <v>16.064040000000002</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L20">
         <v>0.1532628310027955</v>
@@ -3391,10 +3404,10 @@
         <v>49</v>
       </c>
       <c r="V20" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="W20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="X20" t="s">
         <v>51</v>
@@ -3403,7 +3416,7 @@
         <v>52</v>
       </c>
       <c r="Z20" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AA20" t="s">
         <v>54</v>
@@ -3411,46 +3424,46 @@
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>228</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>220</v>
+        <v>38</v>
       </c>
       <c r="E21">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F21">
-        <v>0.02</v>
+        <v>7.9699999999999993E-2</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
-      <c r="H21">
-        <v>1336.5</v>
+      <c r="H21" s="2">
+        <v>2024</v>
       </c>
       <c r="I21" s="3">
-        <v>21.450000000000003</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K21">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L21">
-        <v>0.1532628310027955</v>
+        <v>0.365520596150406</v>
       </c>
       <c r="U21" t="s">
         <v>49</v>
       </c>
       <c r="V21" t="s">
-        <v>41</v>
+        <v>198</v>
       </c>
       <c r="W21" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="X21" t="s">
         <v>51</v>
@@ -3459,7 +3472,7 @@
         <v>52</v>
       </c>
       <c r="Z21" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AA21" t="s">
         <v>54</v>
@@ -3467,43 +3480,43 @@
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>216</v>
+        <v>38</v>
       </c>
       <c r="E22">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="F22">
-        <v>3.2000000000000002E-3</v>
+        <v>0.17519999999999999</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
-      <c r="H22">
-        <v>1336.5</v>
+      <c r="H22" s="2">
+        <v>2024</v>
       </c>
       <c r="I22" s="3">
-        <v>21.450000000000003</v>
+        <v>48.4</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K22">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L22">
-        <v>0.1451997589052581</v>
+        <v>0.365520596150406</v>
       </c>
       <c r="U22" t="s">
         <v>49</v>
       </c>
       <c r="V22" t="s">
-        <v>195</v>
+        <v>41</v>
       </c>
       <c r="W22" t="s">
         <v>61</v>
@@ -3523,46 +3536,46 @@
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>41</v>
+        <v>196</v>
       </c>
       <c r="C23" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E23">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="F23">
-        <v>7.9699999999999993E-2</v>
+        <v>0.439</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
-      <c r="H23">
-        <v>2024</v>
+      <c r="H23" s="2">
+        <v>2376</v>
       </c>
       <c r="I23" s="3">
-        <v>48.400000000000006</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J23">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K23">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="L23">
-        <v>0.365520596150406</v>
+        <v>0.41047488326249421</v>
       </c>
       <c r="U23" t="s">
         <v>49</v>
       </c>
       <c r="V23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W23" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="X23" t="s">
         <v>51</v>
@@ -3574,121 +3587,128 @@
         <v>60</v>
       </c>
       <c r="AA23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>195</v>
-      </c>
-      <c r="C24" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24">
-        <v>2025</v>
-      </c>
-      <c r="F24">
-        <v>0.17519999999999999</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>2024</v>
-      </c>
-      <c r="I24" s="3">
-        <v>48.4</v>
-      </c>
-      <c r="J24">
-        <v>2.3100000000000005</v>
-      </c>
-      <c r="K24">
-        <v>30</v>
-      </c>
-      <c r="L24">
-        <v>0.365520596150406</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="2"/>
       <c r="U24" t="s">
-        <v>120</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>121</v>
+        <v>49</v>
+      </c>
+      <c r="V24" t="s">
+        <v>196</v>
+      </c>
+      <c r="W24" t="s">
+        <v>197</v>
+      </c>
+      <c r="X24" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="E25">
-        <v>2015</v>
+        <v>1982</v>
       </c>
       <c r="F25">
-        <v>0.439</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>2376</v>
+        <f>Q42</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1175.5066999999999</v>
       </c>
       <c r="I25" s="3">
-        <v>57.20000000000001</v>
+        <f>(O42/100)*H26</f>
+        <v>160.216352398</v>
       </c>
       <c r="J25">
-        <v>2.52</v>
+        <f>R42</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K25">
-        <v>50</v>
-      </c>
-      <c r="L25">
-        <v>0.41047488326249421</v>
+        <v>53</v>
+      </c>
+      <c r="M25">
+        <v>0.8</v>
       </c>
       <c r="U25" t="s">
-        <v>49</v>
-      </c>
-      <c r="V25" t="s">
-        <v>173</v>
-      </c>
-      <c r="W25" t="s">
-        <v>143</v>
-      </c>
-      <c r="X25" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>54</v>
+        <v>120</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>121</v>
+        <v>175</v>
+      </c>
+      <c r="C26" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" t="s">
+        <v>211</v>
+      </c>
+      <c r="E26">
+        <v>1965</v>
+      </c>
+      <c r="F26">
+        <v>0.77</v>
+      </c>
+      <c r="G26">
+        <f>$Q$41</f>
+        <v>0.33</v>
+      </c>
+      <c r="H26" s="2">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I26" s="3">
+        <f>(1.31/100)*H26</f>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J26">
+        <f>$R$41</f>
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="K26">
+        <v>70</v>
+      </c>
+      <c r="M26">
+        <v>0.8</v>
       </c>
       <c r="U26" t="s">
         <v>49</v>
       </c>
       <c r="V26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="W26" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="X26" t="s">
         <v>51</v>
@@ -3705,49 +3725,49 @@
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="D27" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E27">
-        <v>1982</v>
+        <v>2015</v>
       </c>
       <c r="F27">
-        <v>1.7000000000000001E-2</v>
+        <v>0.26</v>
       </c>
       <c r="G27">
-        <f>Q42</f>
-        <v>0.56000000000000005</v>
+        <f>$Q$41</f>
+        <v>0.33</v>
       </c>
       <c r="H27" s="2">
-        <v>1175.5066999999999</v>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I27" s="3">
-        <f>(O42/100)*H28</f>
-        <v>160.216352398</v>
+        <f>(1.31/100)*H27</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J27">
-        <f>R42</f>
-        <v>5.8775000000000004</v>
+        <f>$R$41</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K27">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="M27">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="U27" t="s">
         <v>49</v>
       </c>
       <c r="V27" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="W27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="X27" t="s">
         <v>51</v>
@@ -3764,7 +3784,7 @@
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C28" t="s">
         <v>171</v>
@@ -3773,13 +3793,13 @@
         <v>211</v>
       </c>
       <c r="E28">
-        <v>1965</v>
+        <v>2025</v>
       </c>
       <c r="F28">
-        <v>0.77</v>
+        <f>0.01</f>
+        <v>0.01</v>
       </c>
       <c r="G28">
-        <f>$Q$41</f>
         <v>0.33</v>
       </c>
       <c r="H28" s="2">
@@ -3794,7 +3814,7 @@
         <v>4.1005000000000003</v>
       </c>
       <c r="K28">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="M28">
         <v>0.8</v>
@@ -3803,10 +3823,10 @@
         <v>49</v>
       </c>
       <c r="V28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="W28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="X28" t="s">
         <v>51</v>
@@ -3823,19 +3843,19 @@
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
         <v>171</v>
       </c>
       <c r="D29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E29">
-        <v>2015</v>
+        <v>1956</v>
       </c>
       <c r="F29">
-        <v>0.26</v>
+        <v>0.185</v>
       </c>
       <c r="G29">
         <f>$Q$41</f>
@@ -3853,19 +3873,19 @@
         <v>4.1005000000000003</v>
       </c>
       <c r="K29">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="M29">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="U29" t="s">
         <v>49</v>
       </c>
       <c r="V29" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="W29" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="X29" t="s">
         <v>51</v>
@@ -3882,34 +3902,35 @@
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E30">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F30">
-        <f>0.01</f>
-        <v>0.01</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G30">
-        <v>0.33</v>
+        <f>Q42</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H30" s="2">
-        <v>4812.0244000000002</v>
+        <f>P42</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I30" s="3">
-        <f>(1.31/100)*H30</f>
-        <v>63.037519640000006</v>
+        <f>(O42/100)*H30</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J30">
-        <f>$R$41</f>
-        <v>4.1005000000000003</v>
+        <f>$R$42</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K30">
         <v>40</v>
@@ -3921,10 +3942,10 @@
         <v>49</v>
       </c>
       <c r="V30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W30" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="X30" t="s">
         <v>51</v>
@@ -3941,37 +3962,38 @@
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="E31">
-        <v>1956</v>
+        <v>2018</v>
       </c>
       <c r="F31">
-        <v>0.185</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G31">
-        <f>$Q$41</f>
-        <v>0.33</v>
+        <f>Q44</f>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H31" s="2">
-        <v>4812.0244000000002</v>
+        <f>$P$44</f>
+        <v>2950.7891</v>
       </c>
       <c r="I31" s="3">
-        <f>(1.31/100)*H31</f>
-        <v>63.037519640000006</v>
+        <f>(4.5269/100)*H31</f>
+        <v>133.5792717679</v>
       </c>
       <c r="J31">
-        <f>$R$41</f>
-        <v>4.1005000000000003</v>
+        <f>$R$44</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K31">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="M31">
         <v>0.8</v>
@@ -3980,10 +4002,10 @@
         <v>49</v>
       </c>
       <c r="V31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="W31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="X31" t="s">
         <v>51</v>
@@ -4000,35 +4022,34 @@
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E32">
-        <v>2021</v>
+        <v>2009</v>
       </c>
       <c r="F32">
-        <v>7.6999999999999999E-2</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="G32">
-        <f>Q42</f>
-        <v>0.56000000000000005</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H32" s="2">
-        <f>P42</f>
-        <v>1175.5066999999999</v>
+        <f>$P$44</f>
+        <v>2950.7891</v>
       </c>
       <c r="I32" s="3">
-        <f>(O42/100)*H32</f>
-        <v>39.138495576499992</v>
+        <f t="shared" ref="I32:I34" si="1">(4.5269/100)*H32</f>
+        <v>133.5792717679</v>
       </c>
       <c r="J32">
-        <f>$R$42</f>
-        <v>5.8775000000000004</v>
+        <f>$R$44</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K32">
         <v>40</v>
@@ -4040,10 +4061,10 @@
         <v>49</v>
       </c>
       <c r="V32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="W32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="X32" t="s">
         <v>51</v>
@@ -4060,22 +4081,21 @@
     </row>
     <row r="33" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E33">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="F33">
-        <v>3.9E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="G33">
-        <f>Q44</f>
         <v>0.46800000000000003</v>
       </c>
       <c r="H33" s="2">
@@ -4083,7 +4103,7 @@
         <v>2950.7891</v>
       </c>
       <c r="I33" s="3">
-        <f>(4.5269/100)*H33</f>
+        <f t="shared" si="1"/>
         <v>133.5792717679</v>
       </c>
       <c r="J33">
@@ -4100,10 +4120,10 @@
         <v>49</v>
       </c>
       <c r="V33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="W33" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="X33" t="s">
         <v>51</v>
@@ -4120,19 +4140,19 @@
     </row>
     <row r="34" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E34">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="F34">
-        <v>2.2100000000000002E-2</v>
+        <v>1.3900000000000001E-2</v>
       </c>
       <c r="G34">
         <v>0.46800000000000003</v>
@@ -4142,7 +4162,7 @@
         <v>2950.7891</v>
       </c>
       <c r="I34" s="3">
-        <f t="shared" ref="I34:I36" si="0">(4.5269/100)*H34</f>
+        <f t="shared" si="1"/>
         <v>133.5792717679</v>
       </c>
       <c r="J34">
@@ -4159,10 +4179,10 @@
         <v>49</v>
       </c>
       <c r="V34" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="W34" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="X34" t="s">
         <v>51</v>
@@ -4179,34 +4199,35 @@
     </row>
     <row r="35" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="D35" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E35">
-        <v>2011</v>
+        <v>1997</v>
       </c>
       <c r="F35">
-        <v>2.0500000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G35">
-        <v>0.46800000000000003</v>
+        <f>Q41</f>
+        <v>0.33</v>
       </c>
       <c r="H35" s="2">
-        <f>$P$44</f>
-        <v>2950.7891</v>
+        <f>P41</f>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" si="0"/>
-        <v>133.5792717679</v>
+        <f>($O$41/100)*H35</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J35">
-        <f>$R$44</f>
-        <v>2.8138000000000001</v>
+        <f>$R$41</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K35">
         <v>40</v>
@@ -4218,10 +4239,10 @@
         <v>49</v>
       </c>
       <c r="V35" t="s">
-        <v>134</v>
+        <v>176</v>
       </c>
       <c r="W35" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="X35" t="s">
         <v>51</v>
@@ -4238,33 +4259,33 @@
     </row>
     <row r="36" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E36">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="F36">
-        <v>1.3900000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G36">
-        <v>0.46800000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H36" s="2">
-        <f>$P$44</f>
-        <v>2950.7891</v>
+        <f>$P$45</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I36" s="3">
-        <f t="shared" si="0"/>
-        <v>133.5792717679</v>
+        <f>($O$45/100)*H36</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J36">
-        <f>$R$44</f>
+        <f>$R$45</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K36">
@@ -4277,10 +4298,10 @@
         <v>49</v>
       </c>
       <c r="V36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="W36" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="X36" t="s">
         <v>51</v>
@@ -4297,35 +4318,34 @@
     </row>
     <row r="37" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E37">
-        <v>1997</v>
+        <v>2017</v>
       </c>
       <c r="F37">
         <v>0.01</v>
       </c>
       <c r="G37">
-        <f>Q41</f>
-        <v>0.33</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H37" s="2">
-        <f>P41</f>
-        <v>4812.0244000000002</v>
+        <f>$P$45</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I37" s="3">
-        <f>($O$41/100)*H37</f>
-        <v>63.037519640000006</v>
+        <f t="shared" ref="I37:I39" si="2">($O$45/100)*H37</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J37">
-        <f>$R$41</f>
-        <v>4.1005000000000003</v>
+        <f>$R$45</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K37">
         <v>40</v>
@@ -4337,10 +4357,10 @@
         <v>49</v>
       </c>
       <c r="V37" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="W37" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="X37" t="s">
         <v>51</v>
@@ -4357,19 +4377,19 @@
     </row>
     <row r="38" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E38">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="F38">
-        <v>0.01</v>
+        <v>9.300000000000001E-3</v>
       </c>
       <c r="G38">
         <v>0.28999999999999998</v>
@@ -4379,7 +4399,7 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I38" s="3">
-        <f>($O$45/100)*H38</f>
+        <f t="shared" si="2"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J38">
@@ -4396,10 +4416,10 @@
         <v>49</v>
       </c>
       <c r="V38" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="W38" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="X38" t="s">
         <v>51</v>
@@ -4416,19 +4436,19 @@
     </row>
     <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E39">
-        <v>2017</v>
+        <v>1963</v>
       </c>
       <c r="F39">
-        <v>0.01</v>
+        <v>7.0999999999999995E-3</v>
       </c>
       <c r="G39">
         <v>0.28999999999999998</v>
@@ -4438,7 +4458,7 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I39" s="3">
-        <f t="shared" ref="I39:I41" si="1">($O$45/100)*H39</f>
+        <f t="shared" si="2"/>
         <v>162.96753257730003</v>
       </c>
       <c r="J39">
@@ -4446,7 +4466,7 @@
         <v>2.8138000000000001</v>
       </c>
       <c r="K39">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="M39">
         <v>0.8</v>
@@ -4455,10 +4475,10 @@
         <v>49</v>
       </c>
       <c r="V39" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="W39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="X39" t="s">
         <v>51</v>
@@ -4475,34 +4495,35 @@
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E40">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="F40">
-        <v>9.300000000000001E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="G40">
-        <v>0.28999999999999998</v>
+        <f>Q42</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H40" s="2">
-        <f>$P$45</f>
-        <v>4516.7133000000003</v>
+        <f>P42</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I40" s="3">
-        <f t="shared" si="1"/>
-        <v>162.96753257730003</v>
+        <f>($O$42/100)*H40</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J40">
-        <f>$R$45</f>
-        <v>2.8138000000000001</v>
+        <f>$R$42</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K40">
         <v>40</v>
@@ -4526,10 +4547,10 @@
         <v>49</v>
       </c>
       <c r="V40" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="W40" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="X40" t="s">
         <v>51</v>
@@ -4546,29 +4567,29 @@
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E41">
-        <v>1963</v>
+        <v>2013</v>
       </c>
       <c r="F41">
-        <v>7.0999999999999995E-3</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="G41">
         <v>0.28999999999999998</v>
       </c>
       <c r="H41" s="2">
-        <f>$P$45</f>
+        <f>P45</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I41" s="3">
-        <f t="shared" si="1"/>
+        <f>($O$45/100)*H41</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J41">
@@ -4576,7 +4597,7 @@
         <v>2.8138000000000001</v>
       </c>
       <c r="K41">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M41">
         <v>0.8</v>
@@ -4600,10 +4621,10 @@
         <v>49</v>
       </c>
       <c r="V41" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="W41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="X41" t="s">
         <v>51</v>
@@ -4620,19 +4641,19 @@
     </row>
     <row r="42" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C42" t="s">
         <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E42">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="F42">
-        <v>5.7999999999999996E-3</v>
+        <v>4.0999999999999995E-3</v>
       </c>
       <c r="G42">
         <f>Q42</f>
@@ -4675,10 +4696,10 @@
         <v>49</v>
       </c>
       <c r="V42" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="W42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="X42" t="s">
         <v>51</v>
@@ -4695,34 +4716,35 @@
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="D43" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E43">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="F43">
-        <v>6.4999999999999997E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G43">
-        <v>0.28999999999999998</v>
+        <f>Q41</f>
+        <v>0.33</v>
       </c>
       <c r="H43" s="2">
-        <f>P45</f>
-        <v>4516.7133000000003</v>
+        <f>P41</f>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I43" s="3">
         <f>($O$45/100)*H43</f>
-        <v>162.96753257730003</v>
+        <v>173.62265237640003</v>
       </c>
       <c r="J43">
-        <f>$R$45</f>
-        <v>2.8138000000000001</v>
+        <f>$R$41</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K43">
         <v>40</v>
@@ -4739,10 +4761,10 @@
         <v>49</v>
       </c>
       <c r="V43" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="W43" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="X43" t="s">
         <v>51</v>
@@ -4759,201 +4781,205 @@
     </row>
     <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>207</v>
+      </c>
+      <c r="E44">
+        <v>2013</v>
+      </c>
+      <c r="F44">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G44">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H44" s="2">
+        <f>P45</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I44" s="3">
+        <f>($O$45/100)*H44</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J44">
+        <f>$R$45</f>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K44">
+        <v>40</v>
+      </c>
+      <c r="M44">
+        <v>0.8</v>
+      </c>
+      <c r="N44" t="s">
+        <v>188</v>
+      </c>
+      <c r="O44">
+        <v>4.5269000000000004</v>
+      </c>
+      <c r="P44" s="2">
+        <v>2950.7891</v>
+      </c>
+      <c r="Q44">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="R44">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="U44" t="s">
+        <v>49</v>
+      </c>
+      <c r="V44" t="s">
+        <v>152</v>
+      </c>
+      <c r="W44" t="s">
+        <v>153</v>
+      </c>
+      <c r="X44" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s">
+        <v>204</v>
+      </c>
+      <c r="E45">
+        <v>2015</v>
+      </c>
+      <c r="F45">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="G45">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H45" s="2">
+        <f>P45</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I45" s="3">
+        <f>($O$45/100)*H45</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J45">
+        <f>$R$45</f>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K45">
+        <v>40</v>
+      </c>
+      <c r="M45">
+        <v>0.8</v>
+      </c>
+      <c r="N45" t="s">
+        <v>189</v>
+      </c>
+      <c r="O45">
+        <v>3.6080999999999999</v>
+      </c>
+      <c r="P45" s="2">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="Q45">
+        <v>0.2994</v>
+      </c>
+      <c r="R45">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="U45" t="s">
+        <v>49</v>
+      </c>
+      <c r="V45" t="s">
+        <v>154</v>
+      </c>
+      <c r="W45" t="s">
+        <v>155</v>
+      </c>
+      <c r="X45" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" t="s">
         <v>16</v>
       </c>
-      <c r="D44" t="s">
-        <v>202</v>
-      </c>
-      <c r="E44">
-        <v>2015</v>
-      </c>
-      <c r="F44">
-        <v>4.0999999999999995E-3</v>
-      </c>
-      <c r="G44">
+      <c r="D46" t="s">
+        <v>206</v>
+      </c>
+      <c r="E46">
+        <v>2009</v>
+      </c>
+      <c r="F46">
+        <v>1.8E-3</v>
+      </c>
+      <c r="G46">
         <f>Q42</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H46" s="2">
         <f>P42</f>
         <v>1175.5066999999999</v>
       </c>
-      <c r="I44" s="3">
-        <f>($O$42/100)*H44</f>
+      <c r="I46" s="3">
+        <f t="shared" ref="I46:I47" si="3">($O$42/100)*H46</f>
         <v>39.138495576499992</v>
       </c>
-      <c r="J44">
+      <c r="J46">
         <f>$R$42</f>
         <v>5.8775000000000004</v>
       </c>
-      <c r="K44">
-        <v>40</v>
-      </c>
-      <c r="M44">
-        <v>0.8</v>
-      </c>
-      <c r="N44" t="s">
-        <v>188</v>
-      </c>
-      <c r="O44">
-        <v>4.5269000000000004</v>
-      </c>
-      <c r="P44" s="2">
-        <v>2950.7891</v>
-      </c>
-      <c r="Q44">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="R44">
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="U44" t="s">
-        <v>49</v>
-      </c>
-      <c r="V44" t="s">
-        <v>154</v>
-      </c>
-      <c r="W44" t="s">
-        <v>155</v>
-      </c>
-      <c r="X44" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>177</v>
-      </c>
-      <c r="C45" t="s">
-        <v>171</v>
-      </c>
-      <c r="D45" t="s">
-        <v>205</v>
-      </c>
-      <c r="E45">
-        <v>2012</v>
-      </c>
-      <c r="F45">
-        <v>1.4E-3</v>
-      </c>
-      <c r="G45">
-        <f>Q41</f>
-        <v>0.33</v>
-      </c>
-      <c r="H45" s="2">
-        <f>P41</f>
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="I45" s="3">
-        <f>($O$45/100)*H45</f>
-        <v>173.62265237640003</v>
-      </c>
-      <c r="J45">
-        <f>$R$41</f>
-        <v>4.1005000000000003</v>
-      </c>
-      <c r="K45">
-        <v>40</v>
-      </c>
-      <c r="M45">
-        <v>0.8</v>
-      </c>
-      <c r="N45" t="s">
-        <v>189</v>
-      </c>
-      <c r="O45">
-        <v>3.6080999999999999</v>
-      </c>
-      <c r="P45" s="2">
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="Q45">
-        <v>0.2994</v>
-      </c>
-      <c r="R45">
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="U45" t="s">
-        <v>49</v>
-      </c>
-      <c r="V45" t="s">
-        <v>156</v>
-      </c>
-      <c r="W45" t="s">
-        <v>157</v>
-      </c>
-      <c r="X45" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>152</v>
-      </c>
-      <c r="C46" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" t="s">
-        <v>207</v>
-      </c>
-      <c r="E46">
-        <v>2013</v>
-      </c>
-      <c r="F46">
-        <v>1.8E-3</v>
-      </c>
-      <c r="G46">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H46" s="2">
-        <f>P45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I46" s="3">
-        <f>($O$45/100)*H46</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J46">
-        <f>$R$45</f>
-        <v>2.8138000000000001</v>
-      </c>
       <c r="K46">
         <v>40</v>
       </c>
       <c r="M46">
         <v>0.8</v>
       </c>
-      <c r="O46" s="3"/>
+      <c r="N46" t="s">
+        <v>22</v>
+      </c>
+      <c r="O46" s="3">
+        <v>1.5780000000000001</v>
+      </c>
       <c r="P46" s="4"/>
       <c r="U46" t="s">
         <v>49</v>
       </c>
       <c r="V46" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="W46" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="X46" t="s">
         <v>51</v>
@@ -4970,34 +4996,35 @@
     </row>
     <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E47">
         <v>2015</v>
       </c>
       <c r="F47">
-        <v>1.6999999999999999E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G47">
-        <v>0.28999999999999998</v>
+        <f>Q42</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H47" s="2">
-        <f>P45</f>
-        <v>4516.7133000000003</v>
+        <f>P42</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I47" s="3">
-        <f>($O$45/100)*H47</f>
-        <v>162.96753257730003</v>
+        <f t="shared" si="3"/>
+        <v>39.138495576499992</v>
       </c>
       <c r="J47">
-        <f>$R$45</f>
-        <v>2.8138000000000001</v>
+        <f>$R$42</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K47">
         <v>40</v>
@@ -5011,10 +5038,10 @@
         <v>49</v>
       </c>
       <c r="V47" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="W47" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="X47" t="s">
         <v>51</v>
@@ -5031,35 +5058,34 @@
     </row>
     <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E48">
-        <v>2009</v>
+        <v>2022</v>
       </c>
       <c r="F48">
-        <v>1.8E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G48">
-        <f>Q42</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H48" s="2">
-        <f>P42</f>
-        <v>1175.5066999999999</v>
+        <f>P45</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I48" s="3">
-        <f t="shared" ref="I48:I49" si="2">($O$42/100)*H48</f>
-        <v>39.138495576499992</v>
+        <f>($O$45/100)*H48</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J48">
-        <f>$R$42</f>
-        <v>5.8775000000000004</v>
+        <f t="shared" ref="J48:J53" si="4">$R$45</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K48">
         <v>40</v>
@@ -5073,10 +5099,10 @@
         <v>49</v>
       </c>
       <c r="V48" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="W48" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="X48" t="s">
         <v>51</v>
@@ -5093,35 +5119,34 @@
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E49">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="F49">
-        <v>1.8E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G49">
-        <f>Q42</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H49" s="2">
-        <f>P42</f>
-        <v>1175.5066999999999</v>
+        <f>$P$45</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I49" s="3">
-        <f t="shared" si="2"/>
-        <v>39.138495576499992</v>
+        <f t="shared" ref="I49:I53" si="5">($O$45/100)*H49</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J49">
-        <f>$R$42</f>
-        <v>5.8775000000000004</v>
+        <f t="shared" si="4"/>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K49">
         <v>40</v>
@@ -5135,10 +5160,10 @@
         <v>49</v>
       </c>
       <c r="V49" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="W49" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X49" t="s">
         <v>51</v>
@@ -5155,92 +5180,92 @@
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E50">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="F50">
-        <v>1.5E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G50">
         <v>0.28999999999999998</v>
       </c>
       <c r="H50" s="2">
+        <f>$P$45</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="5"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="4"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K50">
+        <v>40</v>
+      </c>
+      <c r="M50">
+        <v>0.8</v>
+      </c>
+      <c r="U50" t="s">
+        <v>49</v>
+      </c>
+      <c r="V50" t="s">
+        <v>164</v>
+      </c>
+      <c r="W50" t="s">
+        <v>165</v>
+      </c>
+      <c r="X50" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>201</v>
+      </c>
+      <c r="E51">
+        <v>2009</v>
+      </c>
+      <c r="F51">
+        <v>1.9E-3</v>
+      </c>
+      <c r="G51">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H51" s="2">
         <f>P45</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I50" s="3">
-        <f>($O$45/100)*H50</f>
+      <c r="I51" s="3">
+        <f t="shared" si="5"/>
         <v>162.96753257730003</v>
       </c>
-      <c r="J50">
-        <f t="shared" ref="J50:J55" si="3">$R$45</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K50">
-        <v>40</v>
-      </c>
-      <c r="M50">
-        <v>0.8</v>
-      </c>
-      <c r="U50" t="s">
-        <v>49</v>
-      </c>
-      <c r="V50" t="s">
-        <v>166</v>
-      </c>
-      <c r="W50" t="s">
-        <v>168</v>
-      </c>
-      <c r="X50" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
-        <v>162</v>
-      </c>
-      <c r="C51" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" t="s">
-        <v>203</v>
-      </c>
-      <c r="E51">
-        <v>2013</v>
-      </c>
-      <c r="F51">
-        <v>1.4E-3</v>
-      </c>
-      <c r="G51">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H51" s="2">
-        <f>$P$45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I51" s="3">
-        <f t="shared" ref="I51:I55" si="4">($O$45/100)*H51</f>
-        <v>162.96753257730003</v>
-      </c>
       <c r="J51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.8138000000000001</v>
       </c>
       <c r="K51">
@@ -5253,10 +5278,10 @@
         <v>49</v>
       </c>
       <c r="V51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="W51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="X51" t="s">
         <v>51</v>
@@ -5273,33 +5298,33 @@
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E52">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="F52">
-        <v>1.1999999999999999E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="G52">
         <v>0.28999999999999998</v>
       </c>
       <c r="H52" s="2">
-        <f>$P$45</f>
+        <f>P45</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I52" s="3">
+        <f t="shared" si="5"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J52">
         <f t="shared" si="4"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J52">
-        <f t="shared" si="3"/>
         <v>2.8138000000000001</v>
       </c>
       <c r="K52">
@@ -5312,10 +5337,10 @@
         <v>49</v>
       </c>
       <c r="V52" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="W52" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="X52" t="s">
         <v>51</v>
@@ -5332,19 +5357,19 @@
     </row>
     <row r="53" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E53">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="F53">
-        <v>1.9E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="G53">
         <v>0.28999999999999998</v>
@@ -5354,11 +5379,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I53" s="3">
+        <f t="shared" si="5"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J53">
         <f t="shared" si="4"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J53">
-        <f t="shared" si="3"/>
         <v>2.8138000000000001</v>
       </c>
       <c r="K53">
@@ -5371,10 +5396,10 @@
         <v>49</v>
       </c>
       <c r="V53" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="W53" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="X53" t="s">
         <v>51</v>
@@ -5383,109 +5408,54 @@
         <v>52</v>
       </c>
       <c r="Z53" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AA53" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E54">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="F54">
-        <v>8.9999999999999998E-4</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G54">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H54" s="2">
-        <f>P45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I54" s="3">
-        <f t="shared" si="4"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J54">
-        <f t="shared" si="3"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K54">
-        <v>40</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="M54">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>170</v>
-      </c>
-      <c r="C55" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" t="s">
-        <v>202</v>
-      </c>
-      <c r="E55">
-        <v>2015</v>
-      </c>
-      <c r="F55">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="G55">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H55" s="2">
-        <f>P45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I55" s="3">
-        <f t="shared" si="4"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J55">
-        <f t="shared" si="3"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K55">
-        <v>40</v>
-      </c>
-      <c r="M55">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="56" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
+      <c r="U54" t="s">
+        <v>49</v>
+      </c>
+      <c r="V54" t="s">
         <v>18</v>
       </c>
-      <c r="C56" t="s">
-        <v>19</v>
-      </c>
-      <c r="D56" t="s">
-        <v>201</v>
-      </c>
-      <c r="E56">
-        <v>2022</v>
-      </c>
-      <c r="F56">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G56">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="M56">
-        <v>0.8</v>
+      <c r="W54" t="s">
+        <v>58</v>
+      </c>
+      <c r="X54" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="2:27" x14ac:dyDescent="0.25">
@@ -5563,6 +5533,36 @@
       </c>
     </row>
     <row r="76" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>20</v>
+      </c>
+      <c r="C76" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76">
+        <v>2013</v>
+      </c>
+      <c r="F76">
+        <v>0.25109999999999999</v>
+      </c>
+      <c r="G76">
+        <v>0.36049999999999999</v>
+      </c>
+      <c r="H76">
+        <v>1265</v>
+      </c>
+      <c r="I76" s="3">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="J76">
+        <v>7.5075000000000003</v>
+      </c>
+      <c r="K76">
+        <v>42</v>
+      </c>
       <c r="U76" t="s">
         <v>49</v>
       </c>
@@ -5586,6 +5586,24 @@
       </c>
     </row>
     <row r="77" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77">
+        <v>2022</v>
+      </c>
+      <c r="F77">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="G77">
+        <v>0.33123000000000002</v>
+      </c>
       <c r="U77" t="s">
         <v>49</v>
       </c>
@@ -5633,34 +5651,34 @@
     </row>
     <row r="79" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D79" t="s">
         <v>14</v>
       </c>
       <c r="E79">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="F79">
-        <v>0.25109999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="G79">
-        <v>0.36049999999999999</v>
+        <v>0.33990000000000004</v>
       </c>
       <c r="H79">
-        <v>1265</v>
+        <v>4427.5</v>
       </c>
       <c r="I79" s="3">
-        <v>48.400000000000006</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J79">
-        <v>7.5075000000000003</v>
+        <v>9.24</v>
       </c>
       <c r="K79">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="U79" t="s">
         <v>49</v>
@@ -5685,24 +5703,6 @@
       </c>
     </row>
     <row r="80" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>15</v>
-      </c>
-      <c r="C80" t="s">
-        <v>16</v>
-      </c>
-      <c r="D80" t="s">
-        <v>14</v>
-      </c>
-      <c r="E80">
-        <v>2022</v>
-      </c>
-      <c r="F80">
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="G80">
-        <v>0.33123000000000002</v>
-      </c>
       <c r="U80" t="s">
         <v>49</v>
       </c>
@@ -5749,36 +5749,6 @@
       </c>
     </row>
     <row r="82" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" t="s">
-        <v>13</v>
-      </c>
-      <c r="D82" t="s">
-        <v>14</v>
-      </c>
-      <c r="E82">
-        <v>2022</v>
-      </c>
-      <c r="F82">
-        <v>0.3</v>
-      </c>
-      <c r="G82">
-        <v>0.33990000000000004</v>
-      </c>
-      <c r="H82">
-        <v>4427.5</v>
-      </c>
-      <c r="I82" s="3">
-        <v>157.30000000000001</v>
-      </c>
-      <c r="J82">
-        <v>9.24</v>
-      </c>
-      <c r="K82">
-        <v>50</v>
-      </c>
       <c r="U82" t="s">
         <v>49</v>
       </c>
@@ -5802,6 +5772,27 @@
       </c>
     </row>
     <row r="84" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84">
+        <v>2022</v>
+      </c>
+      <c r="F84">
+        <v>1.5040605442498314E-2</v>
+      </c>
+      <c r="G84">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L84">
+        <v>0.42012333946150526</v>
+      </c>
       <c r="U84" t="s">
         <v>49</v>
       </c>
@@ -5824,27 +5815,85 @@
         <v>54</v>
       </c>
     </row>
+    <row r="85" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85" t="s">
+        <v>25</v>
+      </c>
+      <c r="D85" t="s">
+        <v>28</v>
+      </c>
+      <c r="E85">
+        <v>2022</v>
+      </c>
+      <c r="F85">
+        <v>1.5497656626156837E-2</v>
+      </c>
+      <c r="G85">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L85">
+        <v>0.42012333946150526</v>
+      </c>
+    </row>
+    <row r="86" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" t="s">
+        <v>30</v>
+      </c>
+      <c r="E86">
+        <v>2022</v>
+      </c>
+      <c r="F86">
+        <v>1.4461737931344828E-2</v>
+      </c>
+      <c r="G86">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L86">
+        <v>0.42012333946150526</v>
+      </c>
+    </row>
     <row r="87" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C87" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E87">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="F87">
-        <v>1.5040605442498314E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G87">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>2376</v>
+      </c>
+      <c r="I87" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J87">
+        <v>2.52</v>
+      </c>
+      <c r="K87">
+        <v>46</v>
       </c>
       <c r="L87">
-        <v>0.42012333946150526</v>
+        <v>0.47763777043344691</v>
       </c>
       <c r="Q87" t="s">
         <v>187</v>
@@ -5852,65 +5901,89 @@
     </row>
     <row r="88" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C88" t="s">
         <v>25</v>
       </c>
       <c r="D88" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E88">
-        <v>2022</v>
+        <v>2010</v>
       </c>
       <c r="F88">
-        <v>1.5497656626156837E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G88">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>2376</v>
+      </c>
+      <c r="I88" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="J88">
+        <v>2.52</v>
+      </c>
+      <c r="K88">
+        <v>45</v>
       </c>
       <c r="L88">
-        <v>0.42012333946150526</v>
+        <v>0.47814004703314078</v>
       </c>
     </row>
     <row r="89" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C89" t="s">
         <v>25</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E89">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F89">
-        <v>1.4461737931344828E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G89">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>2376</v>
+      </c>
+      <c r="I89" s="3">
+        <v>57.20000000000001</v>
+      </c>
+      <c r="J89">
+        <v>2.52</v>
+      </c>
+      <c r="K89">
+        <v>40</v>
       </c>
       <c r="L89">
-        <v>0.42012333946150526</v>
+        <v>0.47814004703314084</v>
       </c>
     </row>
     <row r="90" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C90" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E90">
-        <v>2009</v>
+        <v>2020</v>
       </c>
       <c r="F90">
-        <v>3.9E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -5919,33 +5992,33 @@
         <v>2376</v>
       </c>
       <c r="I90" s="3">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J90">
         <v>2.52</v>
       </c>
       <c r="K90">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="L90">
-        <v>0.47763777043344691</v>
+        <v>0.47814004703314078</v>
       </c>
     </row>
     <row r="91" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C91" t="s">
         <v>25</v>
       </c>
       <c r="D91" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E91">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="F91">
-        <v>1.6E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -5960,27 +6033,27 @@
         <v>2.52</v>
       </c>
       <c r="K91">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L91">
-        <v>0.47814004703314078</v>
+        <v>0.40144059976798208</v>
       </c>
     </row>
     <row r="92" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C92" t="s">
         <v>25</v>
       </c>
       <c r="D92" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E92">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="F92">
-        <v>1.7999999999999999E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -5995,27 +6068,27 @@
         <v>2.52</v>
       </c>
       <c r="K92">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L92">
-        <v>0.47814004703314084</v>
+        <v>0.40144059976798202</v>
       </c>
     </row>
     <row r="93" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C93" t="s">
         <v>25</v>
       </c>
       <c r="D93" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E93">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="F93">
-        <v>1.2E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -6024,16 +6097,16 @@
         <v>2376</v>
       </c>
       <c r="I93" s="3">
-        <v>57.20000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="J93">
         <v>2.52</v>
       </c>
       <c r="K93">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L93">
-        <v>0.47814004703314078</v>
+        <v>0.40144059976798202</v>
       </c>
     </row>
     <row r="94" spans="2:27" x14ac:dyDescent="0.25">
@@ -6047,7 +6120,7 @@
         <v>36</v>
       </c>
       <c r="E94">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="F94">
         <v>2.1000000000000001E-2</v>
@@ -6065,7 +6138,7 @@
         <v>2.52</v>
       </c>
       <c r="K94">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="L94">
         <v>0.40144059976798208</v>
@@ -6082,25 +6155,25 @@
         <v>36</v>
       </c>
       <c r="E95">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="F95">
-        <v>2.4E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="G95">
         <v>1</v>
       </c>
       <c r="H95">
-        <v>2376</v>
+        <v>2024</v>
       </c>
       <c r="I95" s="3">
-        <v>57.20000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="J95">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K95">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="L95">
         <v>0.40144059976798202</v>
@@ -6108,19 +6181,19 @@
     </row>
     <row r="96" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C96" t="s">
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E96">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="F96">
-        <v>7.9000000000000001E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -6135,27 +6208,27 @@
         <v>2.52</v>
       </c>
       <c r="K96">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L96">
-        <v>0.40144059976798202</v>
+        <v>0.365520596150406</v>
       </c>
     </row>
     <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C97" t="s">
         <v>25</v>
       </c>
       <c r="D97" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E97">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="F97">
-        <v>2.1000000000000001E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -6164,68 +6237,68 @@
         <v>2376</v>
       </c>
       <c r="I97" s="3">
-        <v>57.2</v>
+        <v>57.20000000000001</v>
       </c>
       <c r="J97">
         <v>2.52</v>
       </c>
       <c r="K97">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="L97">
-        <v>0.40144059976798208</v>
+        <v>0.41047488326249421</v>
       </c>
     </row>
     <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C98" t="s">
         <v>25</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E98">
-        <v>2024</v>
+        <v>2012</v>
       </c>
       <c r="F98">
-        <v>0.10199999999999999</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G98">
         <v>1</v>
       </c>
       <c r="H98">
-        <v>2024</v>
+        <v>2376</v>
       </c>
       <c r="I98" s="3">
-        <v>48.4</v>
+        <v>57.2</v>
       </c>
       <c r="J98">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K98">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="L98">
-        <v>0.40144059976798202</v>
+        <v>0.41047488326249421</v>
       </c>
     </row>
     <row r="99" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C99" t="s">
         <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E99">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="F99">
-        <v>3.9E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -6240,114 +6313,9 @@
         <v>2.52</v>
       </c>
       <c r="K99">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L99">
-        <v>0.365520596150406</v>
-      </c>
-    </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B100" t="s">
-        <v>39</v>
-      </c>
-      <c r="C100" t="s">
-        <v>25</v>
-      </c>
-      <c r="D100" t="s">
-        <v>40</v>
-      </c>
-      <c r="E100">
-        <v>2005</v>
-      </c>
-      <c r="F100">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G100">
-        <v>1</v>
-      </c>
-      <c r="H100">
-        <v>2376</v>
-      </c>
-      <c r="I100" s="3">
-        <v>57.20000000000001</v>
-      </c>
-      <c r="J100">
-        <v>2.52</v>
-      </c>
-      <c r="K100">
-        <v>50</v>
-      </c>
-      <c r="L100">
-        <v>0.41047488326249421</v>
-      </c>
-    </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B101" t="s">
-        <v>39</v>
-      </c>
-      <c r="C101" t="s">
-        <v>25</v>
-      </c>
-      <c r="D101" t="s">
-        <v>40</v>
-      </c>
-      <c r="E101">
-        <v>2012</v>
-      </c>
-      <c r="F101">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="G101">
-        <v>1</v>
-      </c>
-      <c r="H101">
-        <v>2376</v>
-      </c>
-      <c r="I101" s="3">
-        <v>57.2</v>
-      </c>
-      <c r="J101">
-        <v>2.52</v>
-      </c>
-      <c r="K101">
-        <v>43</v>
-      </c>
-      <c r="L101">
-        <v>0.41047488326249421</v>
-      </c>
-    </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B102" t="s">
-        <v>39</v>
-      </c>
-      <c r="C102" t="s">
-        <v>25</v>
-      </c>
-      <c r="D102" t="s">
-        <v>40</v>
-      </c>
-      <c r="E102">
-        <v>2013</v>
-      </c>
-      <c r="F102">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="G102">
-        <v>1</v>
-      </c>
-      <c r="H102">
-        <v>2376</v>
-      </c>
-      <c r="I102" s="3">
-        <v>57.2</v>
-      </c>
-      <c r="J102">
-        <v>2.52</v>
-      </c>
-      <c r="K102">
-        <v>42</v>
-      </c>
-      <c r="L102">
         <v>0.41047488326249421</v>
       </c>
     </row>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6560CA8C-B5AB-48C8-9986-69B953E44BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6018FA-87A2-461C-A60D-7433BF8F90F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="221">
   <si>
     <t>~fi_t</t>
   </si>
@@ -751,39 +751,6 @@
   </si>
   <si>
     <t>Tartu Aardlapalu CHP plant</t>
-  </si>
-  <si>
-    <t>e_harku_330</t>
-  </si>
-  <si>
-    <t>e_tartu_330</t>
-  </si>
-  <si>
-    <t>e_rakvere_330</t>
-  </si>
-  <si>
-    <t>e_paide_330</t>
-  </si>
-  <si>
-    <t>e_pussi_330</t>
-  </si>
-  <si>
-    <t>e_kilingi_nomme_330</t>
-  </si>
-  <si>
-    <t>e_sindi_330</t>
-  </si>
-  <si>
-    <t>e_tsirguliina_330</t>
-  </si>
-  <si>
-    <t>e_arukula_330</t>
-  </si>
-  <si>
-    <t>e_baltiej_330</t>
-  </si>
-  <si>
-    <t>e_viru_330</t>
   </si>
   <si>
     <t>elc_spv_parnu</t>
@@ -1279,14 +1246,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047CB67-FC18-43CA-8AA0-0CA09A11D4D8}">
   <dimension ref="B9:T17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="73.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="73.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>184</v>
       </c>
@@ -1294,7 +1261,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1350,7 +1317,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>110</v>
       </c>
@@ -1406,7 +1373,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>111</v>
       </c>
@@ -1462,7 +1429,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>112</v>
       </c>
@@ -1518,7 +1485,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>113</v>
       </c>
@@ -1574,7 +1541,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>114</v>
       </c>
@@ -1638,15 +1605,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4FEF-80F2-457D-B441-6C3DD45005FF}">
   <dimension ref="B9:T30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>184</v>
       </c>
@@ -1654,7 +1621,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1710,7 +1677,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>179</v>
       </c>
@@ -1763,7 +1730,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>178</v>
       </c>
@@ -1816,7 +1783,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>66</v>
       </c>
@@ -1872,7 +1839,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>69</v>
       </c>
@@ -1928,7 +1895,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>71</v>
       </c>
@@ -1984,7 +1951,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>73</v>
       </c>
@@ -2040,7 +2007,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>74</v>
       </c>
@@ -2096,7 +2063,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>75</v>
       </c>
@@ -2152,7 +2119,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>76</v>
       </c>
@@ -2208,7 +2175,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>77</v>
       </c>
@@ -2258,7 +2225,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>78</v>
       </c>
@@ -2308,7 +2275,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>79</v>
       </c>
@@ -2364,7 +2331,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>80</v>
       </c>
@@ -2420,7 +2387,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>81</v>
       </c>
@@ -2476,7 +2443,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>83</v>
       </c>
@@ -2532,7 +2499,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>85</v>
       </c>
@@ -2588,7 +2555,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>86</v>
       </c>
@@ -2644,7 +2611,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>87</v>
       </c>
@@ -2700,7 +2667,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>180</v>
       </c>
@@ -2762,30 +2729,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
   <dimension ref="B9:AA99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.26953125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="64.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="64.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="64.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="41.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="64.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="41.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="64.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -2793,7 +2760,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -2852,15 +2819,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="E11">
         <v>2022</v>
@@ -2891,7 +2858,7 @@
         <v>49</v>
       </c>
       <c r="V11" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="W11" t="s">
         <v>58</v>
@@ -2909,15 +2876,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="E12">
         <v>2022</v>
@@ -2948,7 +2915,7 @@
         <v>49</v>
       </c>
       <c r="V12" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="W12" t="s">
         <v>58</v>
@@ -2966,15 +2933,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E13">
         <v>2022</v>
@@ -3005,7 +2972,7 @@
         <v>49</v>
       </c>
       <c r="V13" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="W13" t="s">
         <v>58</v>
@@ -3023,15 +2990,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C14" t="s">
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E14">
         <v>2022</v>
@@ -3062,7 +3029,7 @@
         <v>49</v>
       </c>
       <c r="V14" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="W14" t="s">
         <v>58</v>
@@ -3080,15 +3047,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E15">
         <v>2022</v>
@@ -3119,7 +3086,7 @@
         <v>49</v>
       </c>
       <c r="V15" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="W15" t="s">
         <v>58</v>
@@ -3137,15 +3104,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E16">
         <v>2022</v>
@@ -3176,7 +3143,7 @@
         <v>49</v>
       </c>
       <c r="V16" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="W16" t="s">
         <v>58</v>
@@ -3194,15 +3161,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E17">
         <v>2022</v>
@@ -3233,7 +3200,7 @@
         <v>49</v>
       </c>
       <c r="V17" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="W17" t="s">
         <v>58</v>
@@ -3251,15 +3218,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E18">
         <v>2022</v>
@@ -3290,7 +3257,7 @@
         <v>49</v>
       </c>
       <c r="V18" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="W18" t="s">
         <v>58</v>
@@ -3308,15 +3275,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E19">
         <v>2022</v>
@@ -3347,7 +3314,7 @@
         <v>49</v>
       </c>
       <c r="V19" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="W19" t="s">
         <v>58</v>
@@ -3365,15 +3332,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E20">
         <v>2022</v>
@@ -3404,7 +3371,7 @@
         <v>49</v>
       </c>
       <c r="V20" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="W20" t="s">
         <v>58</v>
@@ -3422,7 +3389,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>41</v>
       </c>
@@ -3478,7 +3445,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>195</v>
       </c>
@@ -3534,7 +3501,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>196</v>
       </c>
@@ -3590,7 +3557,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>120</v>
       </c>
@@ -3620,7 +3587,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>198</v>
       </c>
@@ -3628,7 +3595,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>209</v>
+        <v>14</v>
       </c>
       <c r="E25">
         <v>1982</v>
@@ -3664,7 +3631,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>175</v>
       </c>
@@ -3672,7 +3639,7 @@
         <v>171</v>
       </c>
       <c r="D26" t="s">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>1965</v>
@@ -3723,7 +3690,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>173</v>
       </c>
@@ -3731,7 +3698,7 @@
         <v>171</v>
       </c>
       <c r="D27" t="s">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="E27">
         <v>2015</v>
@@ -3782,7 +3749,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>174</v>
       </c>
@@ -3790,7 +3757,7 @@
         <v>171</v>
       </c>
       <c r="D28" t="s">
-        <v>211</v>
+        <v>14</v>
       </c>
       <c r="E28">
         <v>2025</v>
@@ -3841,7 +3808,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>172</v>
       </c>
@@ -3849,7 +3816,7 @@
         <v>171</v>
       </c>
       <c r="D29" t="s">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="E29">
         <v>1956</v>
@@ -3900,7 +3867,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>122</v>
       </c>
@@ -3908,7 +3875,7 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="E30">
         <v>2021</v>
@@ -3960,7 +3927,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>123</v>
       </c>
@@ -3968,7 +3935,7 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>201</v>
+        <v>14</v>
       </c>
       <c r="E31">
         <v>2018</v>
@@ -4020,7 +3987,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>124</v>
       </c>
@@ -4028,7 +3995,7 @@
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="E32">
         <v>2009</v>
@@ -4079,7 +4046,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>125</v>
       </c>
@@ -4087,7 +4054,7 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>207</v>
+        <v>14</v>
       </c>
       <c r="E33">
         <v>2011</v>
@@ -4138,7 +4105,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>126</v>
       </c>
@@ -4146,7 +4113,7 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>209</v>
+        <v>14</v>
       </c>
       <c r="E34">
         <v>2010</v>
@@ -4197,7 +4164,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>176</v>
       </c>
@@ -4205,7 +4172,7 @@
         <v>171</v>
       </c>
       <c r="D35" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="E35">
         <v>1997</v>
@@ -4257,7 +4224,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>134</v>
       </c>
@@ -4265,7 +4232,7 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="E36">
         <v>2016</v>
@@ -4316,7 +4283,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>136</v>
       </c>
@@ -4324,7 +4291,7 @@
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>208</v>
+        <v>14</v>
       </c>
       <c r="E37">
         <v>2017</v>
@@ -4375,7 +4342,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>150</v>
       </c>
@@ -4383,7 +4350,7 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>201</v>
+        <v>14</v>
       </c>
       <c r="E38">
         <v>2019</v>
@@ -4434,7 +4401,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>138</v>
       </c>
@@ -4442,7 +4409,7 @@
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="E39">
         <v>1963</v>
@@ -4493,7 +4460,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>149</v>
       </c>
@@ -4501,7 +4468,7 @@
         <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="E40">
         <v>2020</v>
@@ -4565,7 +4532,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>144</v>
       </c>
@@ -4573,7 +4540,7 @@
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="E41">
         <v>2013</v>
@@ -4639,7 +4606,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>148</v>
       </c>
@@ -4647,7 +4614,7 @@
         <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="E42">
         <v>2015</v>
@@ -4714,7 +4681,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>177</v>
       </c>
@@ -4722,7 +4689,7 @@
         <v>171</v>
       </c>
       <c r="D43" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="E43">
         <v>2012</v>
@@ -4779,7 +4746,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>152</v>
       </c>
@@ -4787,7 +4754,7 @@
         <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>207</v>
+        <v>14</v>
       </c>
       <c r="E44">
         <v>2013</v>
@@ -4853,7 +4820,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>154</v>
       </c>
@@ -4861,7 +4828,7 @@
         <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="E45">
         <v>2015</v>
@@ -4927,7 +4894,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>156</v>
       </c>
@@ -4935,7 +4902,7 @@
         <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>206</v>
+        <v>14</v>
       </c>
       <c r="E46">
         <v>2009</v>
@@ -4994,7 +4961,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>158</v>
       </c>
@@ -5002,7 +4969,7 @@
         <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>205</v>
+        <v>14</v>
       </c>
       <c r="E47">
         <v>2015</v>
@@ -5056,7 +5023,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>160</v>
       </c>
@@ -5064,7 +5031,7 @@
         <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="E48">
         <v>2022</v>
@@ -5117,7 +5084,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>162</v>
       </c>
@@ -5125,7 +5092,7 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="E49">
         <v>2013</v>
@@ -5178,7 +5145,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>164</v>
       </c>
@@ -5186,7 +5153,7 @@
         <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>204</v>
+        <v>14</v>
       </c>
       <c r="E50">
         <v>2016</v>
@@ -5237,7 +5204,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>166</v>
       </c>
@@ -5245,7 +5212,7 @@
         <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>201</v>
+        <v>14</v>
       </c>
       <c r="E51">
         <v>2009</v>
@@ -5296,7 +5263,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>167</v>
       </c>
@@ -5304,7 +5271,7 @@
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="E52">
         <v>2012</v>
@@ -5355,7 +5322,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>170</v>
       </c>
@@ -5363,7 +5330,7 @@
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>202</v>
+        <v>14</v>
       </c>
       <c r="E53">
         <v>2015</v>
@@ -5414,7 +5381,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>18</v>
       </c>
@@ -5422,7 +5389,7 @@
         <v>19</v>
       </c>
       <c r="D54" t="s">
-        <v>201</v>
+        <v>14</v>
       </c>
       <c r="E54">
         <v>2022</v>
@@ -5458,12 +5425,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:27" x14ac:dyDescent="0.35">
       <c r="V72" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.35">
       <c r="U73" t="s">
         <v>49</v>
       </c>
@@ -5486,7 +5453,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:27" x14ac:dyDescent="0.35">
       <c r="U74" t="s">
         <v>49</v>
       </c>
@@ -5509,7 +5476,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:27" x14ac:dyDescent="0.35">
       <c r="U75" t="s">
         <v>49</v>
       </c>
@@ -5532,7 +5499,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>20</v>
       </c>
@@ -5585,7 +5552,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>15</v>
       </c>
@@ -5626,7 +5593,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="78" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:27" x14ac:dyDescent="0.35">
       <c r="U78" t="s">
         <v>49</v>
       </c>
@@ -5649,7 +5616,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>12</v>
       </c>
@@ -5702,7 +5669,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.35">
       <c r="U80" t="s">
         <v>49</v>
       </c>
@@ -5725,7 +5692,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="81" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:27" x14ac:dyDescent="0.35">
       <c r="U81" t="s">
         <v>49</v>
       </c>
@@ -5748,7 +5715,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:27" x14ac:dyDescent="0.35">
       <c r="U82" t="s">
         <v>49</v>
       </c>
@@ -5771,7 +5738,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="84" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>24</v>
       </c>
@@ -5815,7 +5782,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="85" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>27</v>
       </c>
@@ -5838,7 +5805,7 @@
         <v>0.42012333946150526</v>
       </c>
     </row>
-    <row r="86" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>29</v>
       </c>
@@ -5861,7 +5828,7 @@
         <v>0.42012333946150526</v>
       </c>
     </row>
-    <row r="87" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>31</v>
       </c>
@@ -5899,7 +5866,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="88" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>33</v>
       </c>
@@ -5934,7 +5901,7 @@
         <v>0.47814004703314078</v>
       </c>
     </row>
-    <row r="89" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>33</v>
       </c>
@@ -5969,7 +5936,7 @@
         <v>0.47814004703314084</v>
       </c>
     </row>
-    <row r="90" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>33</v>
       </c>
@@ -6004,7 +5971,7 @@
         <v>0.47814004703314078</v>
       </c>
     </row>
-    <row r="91" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>35</v>
       </c>
@@ -6039,7 +6006,7 @@
         <v>0.40144059976798208</v>
       </c>
     </row>
-    <row r="92" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>35</v>
       </c>
@@ -6074,7 +6041,7 @@
         <v>0.40144059976798202</v>
       </c>
     </row>
-    <row r="93" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>35</v>
       </c>
@@ -6109,7 +6076,7 @@
         <v>0.40144059976798202</v>
       </c>
     </row>
-    <row r="94" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>35</v>
       </c>
@@ -6144,7 +6111,7 @@
         <v>0.40144059976798208</v>
       </c>
     </row>
-    <row r="95" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>35</v>
       </c>
@@ -6179,7 +6146,7 @@
         <v>0.40144059976798202</v>
       </c>
     </row>
-    <row r="96" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>37</v>
       </c>
@@ -6214,7 +6181,7 @@
         <v>0.365520596150406</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>39</v>
       </c>
@@ -6249,7 +6216,7 @@
         <v>0.41047488326249421</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>39</v>
       </c>
@@ -6284,7 +6251,7 @@
         <v>0.41047488326249421</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>39</v>
       </c>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6018FA-87A2-461C-A60D-7433BF8F90F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F982AB3-9134-4A83-8302-9DF00F29CB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -85,7 +85,7 @@
     Miks daynite (hydro samuti)</t>
       </text>
     </comment>
-    <comment ref="F25" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -93,7 +93,7 @@
     Iru produces only 17 MW in 2025 not 0.207 GW</t>
       </text>
     </comment>
-    <comment ref="B26" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+    <comment ref="B31" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -101,7 +101,7 @@
     TODO: set their actual start date and then add how much they produce in 2025</t>
       </text>
     </comment>
-    <comment ref="E34" authorId="3" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
+    <comment ref="E39" authorId="3" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -110,7 +110,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="O40" authorId="4" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+    <comment ref="P39" authorId="4" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -119,7 +119,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="R44" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+    <comment ref="S43" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -127,7 +127,7 @@
     Took same as chp</t>
       </text>
     </comment>
-    <comment ref="J79" authorId="6" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <comment ref="J78" authorId="6" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="232">
   <si>
     <t>~fi_t</t>
   </si>
@@ -510,12 +510,6 @@
     <t>ccs retrofit of -- Kiisa ERPP power station_1 &amp; 2 -- operating</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>Additions by Kristopher</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_pohja</t>
   </si>
   <si>
@@ -741,9 +735,6 @@
     <t>ep_windon_agg</t>
   </si>
   <si>
-    <t>Aggregated Plant of windon except sopi plants</t>
-  </si>
-  <si>
     <t>ep_bioenergy_iru</t>
   </si>
   <si>
@@ -811,6 +802,48 @@
   </si>
   <si>
     <t>elc_spv_jarva</t>
+  </si>
+  <si>
+    <t>elc_won_parnu</t>
+  </si>
+  <si>
+    <t>elc_won_harju</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_saaremaa</t>
+  </si>
+  <si>
+    <t>Aggregated Plant of windon will be put to Parnu</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_laane-viru</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_harju</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_laanemaa</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_ida_viru</t>
+  </si>
+  <si>
+    <t>elc_won_saaremaa</t>
+  </si>
+  <si>
+    <t>elc_won_laane-viru</t>
+  </si>
+  <si>
+    <t>elc_won_laanemaa</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_parnu</t>
+  </si>
+  <si>
+    <t>elc_won_ida_viru</t>
+  </si>
+  <si>
+    <t>vka tuul</t>
   </si>
 </sst>
 </file>
@@ -820,16 +853,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -857,9 +882,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1217,24 +1241,24 @@
   <threadedComment ref="Z21" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
     <text>Miks daynite (hydro samuti)</text>
   </threadedComment>
-  <threadedComment ref="F25" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+  <threadedComment ref="F30" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
-  <threadedComment ref="B26" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+  <threadedComment ref="B31" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
     <text>TODO: set their actual start date and then add how much they produce in 2025</text>
   </threadedComment>
-  <threadedComment ref="E34" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
+  <threadedComment ref="E39" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
     <text xml:space="preserve">Ei tea
 </text>
   </threadedComment>
-  <threadedComment ref="O40" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+  <threadedComment ref="P39" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
     <text xml:space="preserve">NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)
 </text>
   </threadedComment>
-  <threadedComment ref="R44" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+  <threadedComment ref="S43" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
     <text>Took same as chp</text>
   </threadedComment>
-  <threadedComment ref="J79" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+  <threadedComment ref="J78" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
     <text>From 9,24 to 6</text>
   </threadedComment>
   <threadedComment ref="U81" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
@@ -1255,10 +1279,10 @@
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
@@ -1615,10 +1639,10 @@
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
@@ -1679,10 +1703,10 @@
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -1699,7 +1723,7 @@
       <c r="H11">
         <v>2150</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <v>35.053609999999999</v>
       </c>
       <c r="J11">
@@ -1712,7 +1736,7 @@
         <v>49</v>
       </c>
       <c r="O11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P11" t="s">
         <v>88</v>
@@ -1732,10 +1756,10 @@
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -1752,7 +1776,7 @@
       <c r="H12">
         <v>2150</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <v>35.053609999999999</v>
       </c>
       <c r="J12">
@@ -1765,7 +1789,7 @@
         <v>49</v>
       </c>
       <c r="O12" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P12" t="s">
         <v>89</v>
@@ -2669,10 +2693,10 @@
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D30" t="s">
         <v>14</v>
@@ -2702,10 +2726,10 @@
         <v>49</v>
       </c>
       <c r="O30" t="s">
+        <v>178</v>
+      </c>
+      <c r="P30" t="s">
         <v>180</v>
-      </c>
-      <c r="P30" t="s">
-        <v>182</v>
       </c>
       <c r="Q30" t="s">
         <v>51</v>
@@ -2728,7 +2752,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:AA99"/>
+  <dimension ref="B9:AA98"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
@@ -2738,10 +2762,10 @@
     <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="13" max="13" width="7.6328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.26953125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="40.54296875" bestFit="1" customWidth="1"/>
@@ -2782,7 +2806,7 @@
       <c r="H10" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J10" t="s">
@@ -2795,7 +2819,7 @@
         <v>11</v>
       </c>
       <c r="M10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="U10" t="s">
         <v>43</v>
@@ -2821,13 +2845,13 @@
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E11">
         <v>2022</v>
@@ -2838,11 +2862,11 @@
       <c r="G11">
         <v>1</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>1018</v>
       </c>
-      <c r="I11" s="3">
-        <f>($O$46/100)*H11</f>
+      <c r="I11" s="2">
+        <f>($P$45/100)*H11</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J11">
@@ -2858,7 +2882,7 @@
         <v>49</v>
       </c>
       <c r="V11" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="W11" t="s">
         <v>58</v>
@@ -2878,13 +2902,13 @@
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E12">
         <v>2022</v>
@@ -2895,11 +2919,11 @@
       <c r="G12">
         <v>1</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>1018</v>
       </c>
-      <c r="I12" s="3">
-        <f t="shared" ref="I12:I20" si="0">($O$46/100)*H12</f>
+      <c r="I12" s="2">
+        <f>($P$45/100)*H12</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J12">
@@ -2915,7 +2939,7 @@
         <v>49</v>
       </c>
       <c r="V12" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="W12" t="s">
         <v>58</v>
@@ -2935,13 +2959,13 @@
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C13" t="s">
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E13">
         <v>2022</v>
@@ -2952,11 +2976,11 @@
       <c r="G13">
         <v>1</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>1018</v>
       </c>
-      <c r="I13" s="3">
-        <f t="shared" si="0"/>
+      <c r="I13" s="2">
+        <f>($P$45/100)*H13</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J13">
@@ -2972,7 +2996,7 @@
         <v>49</v>
       </c>
       <c r="V13" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="W13" t="s">
         <v>58</v>
@@ -2992,13 +3016,13 @@
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C14" t="s">
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E14">
         <v>2022</v>
@@ -3009,11 +3033,11 @@
       <c r="G14">
         <v>1</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="1">
         <v>1018</v>
       </c>
-      <c r="I14" s="3">
-        <f t="shared" si="0"/>
+      <c r="I14" s="2">
+        <f>($P$45/100)*H14</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J14">
@@ -3029,7 +3053,7 @@
         <v>49</v>
       </c>
       <c r="V14" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="W14" t="s">
         <v>58</v>
@@ -3049,13 +3073,13 @@
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E15">
         <v>2022</v>
@@ -3066,11 +3090,11 @@
       <c r="G15">
         <v>1</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="1">
         <v>1018</v>
       </c>
-      <c r="I15" s="3">
-        <f t="shared" si="0"/>
+      <c r="I15" s="2">
+        <f>($P$45/100)*H15</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J15">
@@ -3086,7 +3110,7 @@
         <v>49</v>
       </c>
       <c r="V15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="W15" t="s">
         <v>58</v>
@@ -3106,13 +3130,13 @@
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E16">
         <v>2022</v>
@@ -3123,11 +3147,11 @@
       <c r="G16">
         <v>1</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="1">
         <v>1018</v>
       </c>
-      <c r="I16" s="3">
-        <f t="shared" si="0"/>
+      <c r="I16" s="2">
+        <f>($P$45/100)*H16</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J16">
@@ -3143,7 +3167,7 @@
         <v>49</v>
       </c>
       <c r="V16" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="W16" t="s">
         <v>58</v>
@@ -3163,13 +3187,13 @@
     </row>
     <row r="17" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E17">
         <v>2022</v>
@@ -3180,11 +3204,11 @@
       <c r="G17">
         <v>1</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>1018</v>
       </c>
-      <c r="I17" s="3">
-        <f t="shared" si="0"/>
+      <c r="I17" s="2">
+        <f>($P$45/100)*H17</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J17">
@@ -3200,7 +3224,7 @@
         <v>49</v>
       </c>
       <c r="V17" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W17" t="s">
         <v>58</v>
@@ -3220,13 +3244,13 @@
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E18">
         <v>2022</v>
@@ -3237,11 +3261,11 @@
       <c r="G18">
         <v>1</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="1">
         <v>1018</v>
       </c>
-      <c r="I18" s="3">
-        <f t="shared" si="0"/>
+      <c r="I18" s="2">
+        <f>($P$45/100)*H18</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J18">
@@ -3257,7 +3281,7 @@
         <v>49</v>
       </c>
       <c r="V18" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="W18" t="s">
         <v>58</v>
@@ -3277,13 +3301,13 @@
     </row>
     <row r="19" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E19">
         <v>2022</v>
@@ -3294,11 +3318,11 @@
       <c r="G19">
         <v>1</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <v>1018</v>
       </c>
-      <c r="I19" s="3">
-        <f t="shared" si="0"/>
+      <c r="I19" s="2">
+        <f>($P$45/100)*H19</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J19">
@@ -3314,7 +3338,7 @@
         <v>49</v>
       </c>
       <c r="V19" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="W19" t="s">
         <v>58</v>
@@ -3334,13 +3358,13 @@
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E20">
         <v>2022</v>
@@ -3351,11 +3375,11 @@
       <c r="G20">
         <v>1</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>1018</v>
       </c>
-      <c r="I20" s="3">
-        <f t="shared" si="0"/>
+      <c r="I20" s="2">
+        <f>($P$45/100)*H20</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J20">
@@ -3371,7 +3395,7 @@
         <v>49</v>
       </c>
       <c r="V20" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="W20" t="s">
         <v>58</v>
@@ -3397,7 +3421,7 @@
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>218</v>
       </c>
       <c r="E21">
         <v>2024</v>
@@ -3408,26 +3432,28 @@
       <c r="G21">
         <v>1</v>
       </c>
-      <c r="H21" s="2">
-        <v>2024</v>
-      </c>
-      <c r="I21" s="3">
-        <v>48.400000000000006</v>
+      <c r="H21" s="1">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="I21" s="2">
+        <f>($P$46/100)*H21</f>
+        <v>18.701711233400001</v>
       </c>
       <c r="J21">
-        <v>2.3100000000000005</v>
+        <f>$S$46</f>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K21">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L21">
-        <v>0.365520596150406</v>
+        <v>0.4</v>
       </c>
       <c r="U21" t="s">
         <v>49</v>
       </c>
       <c r="V21" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="W21" t="s">
         <v>56</v>
@@ -3447,13 +3473,13 @@
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C22" t="s">
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>218</v>
       </c>
       <c r="E22">
         <v>2025</v>
@@ -3464,20 +3490,25 @@
       <c r="G22">
         <v>1</v>
       </c>
-      <c r="H22" s="2">
-        <v>2024</v>
-      </c>
-      <c r="I22" s="3">
-        <v>48.4</v>
+      <c r="H22" s="1">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="I22" s="2">
+        <f>($P$46/100)*H22</f>
+        <v>18.701711233400001</v>
       </c>
       <c r="J22">
-        <v>2.3100000000000005</v>
+        <f>$S$46</f>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K22">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L22">
-        <v>0.365520596150406</v>
+        <v>0.4</v>
+      </c>
+      <c r="P22" t="s">
+        <v>231</v>
       </c>
       <c r="U22" t="s">
         <v>49</v>
@@ -3503,43 +3534,57 @@
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C23" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>218</v>
       </c>
       <c r="E23">
         <v>2015</v>
       </c>
       <c r="F23">
-        <v>0.439</v>
+        <v>8.130000000000015E-2</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
-      <c r="H23" s="2">
-        <v>2376</v>
-      </c>
-      <c r="I23" s="3">
-        <v>57.20000000000001</v>
+      <c r="H23" s="1">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="I23" s="2">
+        <f>($P$46/100)*H23</f>
+        <v>18.701711233400001</v>
       </c>
       <c r="J23">
-        <v>2.52</v>
+        <f>$S$46</f>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K23">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="L23">
-        <v>0.41047488326249421</v>
+        <v>0.4</v>
+      </c>
+      <c r="O23">
+        <f>SUM(F21:F29)-F23</f>
+        <v>0.61260000000000003</v>
+      </c>
+      <c r="P23">
+        <f>693.9/1000</f>
+        <v>0.69389999999999996</v>
+      </c>
+      <c r="Q23">
+        <f>P23-O23</f>
+        <v>8.1299999999999928E-2</v>
       </c>
       <c r="U23" t="s">
         <v>49</v>
       </c>
       <c r="V23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="W23" t="s">
         <v>61</v>
@@ -3559,20 +3604,48 @@
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" t="s">
+        <v>226</v>
+      </c>
+      <c r="E24">
+        <v>2022</v>
+      </c>
+      <c r="F24">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="I24" s="2">
+        <f>($P$46/100)*H24</f>
+        <v>18.701711233400001</v>
+      </c>
+      <c r="J24">
+        <f>$S$46</f>
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="K24">
+        <v>27</v>
+      </c>
+      <c r="L24">
+        <v>0.4</v>
+      </c>
       <c r="U24" t="s">
         <v>49</v>
       </c>
       <c r="V24" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="W24" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="X24" t="s">
         <v>51</v>
@@ -3584,98 +3657,111 @@
         <v>60</v>
       </c>
       <c r="AA24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>227</v>
       </c>
       <c r="E25">
-        <v>1982</v>
+        <v>2022</v>
       </c>
       <c r="F25">
-        <v>1.7000000000000001E-2</v>
+        <v>3.27E-2</v>
       </c>
       <c r="G25">
-        <f>Q42</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H25" s="2">
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="I25" s="3">
-        <f>(O42/100)*H26</f>
-        <v>160.216352398</v>
+        <v>1</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="I25" s="2">
+        <f>($P$46/100)*H25</f>
+        <v>18.701711233400001</v>
       </c>
       <c r="J25">
-        <f>R42</f>
-        <v>5.8775000000000004</v>
+        <f>$S$46</f>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K25">
-        <v>53</v>
-      </c>
-      <c r="M25">
-        <v>0.8</v>
+        <v>27</v>
+      </c>
+      <c r="L25">
+        <v>0.4</v>
       </c>
       <c r="U25" t="s">
-        <v>120</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>121</v>
+        <v>49</v>
+      </c>
+      <c r="V25" t="s">
+        <v>220</v>
+      </c>
+      <c r="W25" t="s">
+        <v>58</v>
+      </c>
+      <c r="X25" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="C26" t="s">
-        <v>171</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>219</v>
       </c>
       <c r="E26">
-        <v>1965</v>
+        <v>2022</v>
       </c>
       <c r="F26">
-        <v>0.77</v>
+        <v>6.3399999999999998E-2</v>
       </c>
       <c r="G26">
-        <f>$Q$41</f>
-        <v>0.33</v>
-      </c>
-      <c r="H26" s="2">
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="I26" s="3">
-        <f>(1.31/100)*H26</f>
-        <v>63.037519640000006</v>
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="I26" s="2">
+        <f>($P$46/100)*H26</f>
+        <v>18.701711233400001</v>
       </c>
       <c r="J26">
-        <f>$R$41</f>
-        <v>4.1005000000000003</v>
+        <f>$S$46</f>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K26">
-        <v>70</v>
-      </c>
-      <c r="M26">
-        <v>0.8</v>
+        <v>27</v>
+      </c>
+      <c r="L26">
+        <v>0.4</v>
       </c>
       <c r="U26" t="s">
         <v>49</v>
       </c>
       <c r="V26" t="s">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="W26" t="s">
-        <v>143</v>
+        <v>58</v>
       </c>
       <c r="X26" t="s">
         <v>51</v>
@@ -3692,49 +3778,48 @@
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C27" t="s">
-        <v>171</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E27">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F27">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="G27">
-        <f>$Q$41</f>
-        <v>0.33</v>
-      </c>
-      <c r="H27" s="2">
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="I27" s="3">
-        <f>(1.31/100)*H27</f>
-        <v>63.037519640000006</v>
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="I27" s="2">
+        <f>($P$46/100)*H27</f>
+        <v>18.701711233400001</v>
       </c>
       <c r="J27">
-        <f>$R$41</f>
-        <v>4.1005000000000003</v>
+        <f>$S$46</f>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K27">
-        <v>40</v>
-      </c>
-      <c r="M27">
-        <v>0.7</v>
+        <v>27</v>
+      </c>
+      <c r="L27">
+        <v>0.4</v>
       </c>
       <c r="U27" t="s">
         <v>49</v>
       </c>
       <c r="V27" t="s">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="W27" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="X27" t="s">
         <v>51</v>
@@ -3751,346 +3836,330 @@
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>174</v>
+        <v>225</v>
       </c>
       <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
+        <v>230</v>
+      </c>
+      <c r="E28">
+        <v>2022</v>
+      </c>
+      <c r="F28">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="I28" s="2">
+        <f>($P$46/100)*H28</f>
+        <v>18.701711233400001</v>
+      </c>
+      <c r="J28">
+        <f>$S$46</f>
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="K28">
+        <v>27</v>
+      </c>
+      <c r="L28">
+        <v>0.4</v>
+      </c>
+      <c r="U28" t="s">
+        <v>49</v>
+      </c>
+      <c r="V28" t="s">
+        <v>224</v>
+      </c>
+      <c r="W28" t="s">
+        <v>58</v>
+      </c>
+      <c r="X28" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>229</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" t="s">
+        <v>218</v>
+      </c>
+      <c r="E29">
+        <v>2022</v>
+      </c>
+      <c r="F29">
+        <v>0.1036</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1494.4630999999999</v>
+      </c>
+      <c r="I29" s="2">
+        <f>($P$46/100)*H29</f>
+        <v>18.701711233400001</v>
+      </c>
+      <c r="J29">
+        <f>$S$46</f>
+        <v>2.0036999999999998</v>
+      </c>
+      <c r="K29">
+        <v>27</v>
+      </c>
+      <c r="L29">
+        <v>0.4</v>
+      </c>
+      <c r="U29" t="s">
+        <v>49</v>
+      </c>
+      <c r="V29" t="s">
+        <v>225</v>
+      </c>
+      <c r="W29" t="s">
+        <v>58</v>
+      </c>
+      <c r="X29" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30">
+        <v>1982</v>
+      </c>
+      <c r="F30">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="G30">
+        <f>R41</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="I30" s="2">
+        <f>(P41/100)*H31</f>
+        <v>160.216352398</v>
+      </c>
+      <c r="J30">
+        <f>S41</f>
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="K30">
+        <v>53</v>
+      </c>
+      <c r="U30" t="s">
+        <v>49</v>
+      </c>
+      <c r="V30" t="s">
+        <v>229</v>
+      </c>
+      <c r="W30" t="s">
+        <v>58</v>
+      </c>
+      <c r="X30" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31">
+        <v>1965</v>
+      </c>
+      <c r="F31">
+        <v>0.77</v>
+      </c>
+      <c r="G31">
+        <f>$R$40</f>
+        <v>0.33</v>
+      </c>
+      <c r="H31" s="1">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I31" s="2">
+        <f>(1.31/100)*H31</f>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J31">
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="K31">
+        <v>70</v>
+      </c>
+      <c r="U31" t="s">
+        <v>49</v>
+      </c>
+      <c r="V31" t="s">
         <v>171</v>
       </c>
-      <c r="D28" t="s">
+      <c r="W31" t="s">
+        <v>141</v>
+      </c>
+      <c r="X31" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" t="s">
+        <v>169</v>
+      </c>
+      <c r="D32" t="s">
         <v>14</v>
       </c>
-      <c r="E28">
+      <c r="E32">
+        <v>2015</v>
+      </c>
+      <c r="F32">
+        <v>0.26</v>
+      </c>
+      <c r="G32">
+        <f>$R$40</f>
+        <v>0.33</v>
+      </c>
+      <c r="H32" s="1">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I32" s="2">
+        <f>(1.31/100)*H32</f>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J32">
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="K32">
+        <v>40</v>
+      </c>
+      <c r="U32" t="s">
+        <v>49</v>
+      </c>
+      <c r="V32" t="s">
+        <v>170</v>
+      </c>
+      <c r="W32" t="s">
+        <v>126</v>
+      </c>
+      <c r="X32" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" t="s">
+        <v>169</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33">
         <v>2025</v>
       </c>
-      <c r="F28">
+      <c r="F33">
         <f>0.01</f>
         <v>0.01</v>
       </c>
-      <c r="G28">
+      <c r="G33">
         <v>0.33</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H33" s="1">
         <v>4812.0244000000002</v>
       </c>
-      <c r="I28" s="3">
-        <f>(1.31/100)*H28</f>
+      <c r="I33" s="2">
+        <f>(1.31/100)*H33</f>
         <v>63.037519640000006</v>
       </c>
-      <c r="J28">
-        <f>$R$41</f>
+      <c r="J33">
+        <f>$S$40</f>
         <v>4.1005000000000003</v>
-      </c>
-      <c r="K28">
-        <v>40</v>
-      </c>
-      <c r="M28">
-        <v>0.8</v>
-      </c>
-      <c r="U28" t="s">
-        <v>49</v>
-      </c>
-      <c r="V28" t="s">
-        <v>174</v>
-      </c>
-      <c r="W28" t="s">
-        <v>129</v>
-      </c>
-      <c r="X28" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B29" t="s">
-        <v>172</v>
-      </c>
-      <c r="C29" t="s">
-        <v>171</v>
-      </c>
-      <c r="D29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29">
-        <v>1956</v>
-      </c>
-      <c r="F29">
-        <v>0.185</v>
-      </c>
-      <c r="G29">
-        <f>$Q$41</f>
-        <v>0.33</v>
-      </c>
-      <c r="H29" s="2">
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="I29" s="3">
-        <f>(1.31/100)*H29</f>
-        <v>63.037519640000006</v>
-      </c>
-      <c r="J29">
-        <f>$R$41</f>
-        <v>4.1005000000000003</v>
-      </c>
-      <c r="K29">
-        <v>73</v>
-      </c>
-      <c r="M29">
-        <v>0.8</v>
-      </c>
-      <c r="U29" t="s">
-        <v>49</v>
-      </c>
-      <c r="V29" t="s">
-        <v>175</v>
-      </c>
-      <c r="W29" t="s">
-        <v>130</v>
-      </c>
-      <c r="X29" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30">
-        <v>2021</v>
-      </c>
-      <c r="F30">
-        <v>7.6999999999999999E-2</v>
-      </c>
-      <c r="G30">
-        <f>Q42</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H30" s="2">
-        <f>P42</f>
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="I30" s="3">
-        <f>(O42/100)*H30</f>
-        <v>39.138495576499992</v>
-      </c>
-      <c r="J30">
-        <f>$R$42</f>
-        <v>5.8775000000000004</v>
-      </c>
-      <c r="K30">
-        <v>40</v>
-      </c>
-      <c r="M30">
-        <v>0.8</v>
-      </c>
-      <c r="U30" t="s">
-        <v>49</v>
-      </c>
-      <c r="V30" t="s">
-        <v>122</v>
-      </c>
-      <c r="W30" t="s">
-        <v>141</v>
-      </c>
-      <c r="X30" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31">
-        <v>2018</v>
-      </c>
-      <c r="F31">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G31">
-        <f>Q44</f>
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="H31" s="2">
-        <f>$P$44</f>
-        <v>2950.7891</v>
-      </c>
-      <c r="I31" s="3">
-        <f>(4.5269/100)*H31</f>
-        <v>133.5792717679</v>
-      </c>
-      <c r="J31">
-        <f>$R$44</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K31">
-        <v>40</v>
-      </c>
-      <c r="M31">
-        <v>0.8</v>
-      </c>
-      <c r="U31" t="s">
-        <v>49</v>
-      </c>
-      <c r="V31" t="s">
-        <v>123</v>
-      </c>
-      <c r="W31" t="s">
-        <v>131</v>
-      </c>
-      <c r="X31" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B32" t="s">
-        <v>124</v>
-      </c>
-      <c r="C32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32">
-        <v>2009</v>
-      </c>
-      <c r="F32">
-        <v>2.2100000000000002E-2</v>
-      </c>
-      <c r="G32">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="H32" s="2">
-        <f>$P$44</f>
-        <v>2950.7891</v>
-      </c>
-      <c r="I32" s="3">
-        <f t="shared" ref="I32:I34" si="1">(4.5269/100)*H32</f>
-        <v>133.5792717679</v>
-      </c>
-      <c r="J32">
-        <f>$R$44</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K32">
-        <v>40</v>
-      </c>
-      <c r="M32">
-        <v>0.8</v>
-      </c>
-      <c r="U32" t="s">
-        <v>49</v>
-      </c>
-      <c r="V32" t="s">
-        <v>124</v>
-      </c>
-      <c r="W32" t="s">
-        <v>132</v>
-      </c>
-      <c r="X32" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B33" t="s">
-        <v>125</v>
-      </c>
-      <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E33">
-        <v>2011</v>
-      </c>
-      <c r="F33">
-        <v>2.0500000000000001E-2</v>
-      </c>
-      <c r="G33">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="H33" s="2">
-        <f>$P$44</f>
-        <v>2950.7891</v>
-      </c>
-      <c r="I33" s="3">
-        <f t="shared" si="1"/>
-        <v>133.5792717679</v>
-      </c>
-      <c r="J33">
-        <f>$R$44</f>
-        <v>2.8138000000000001</v>
       </c>
       <c r="K33">
         <v>40</v>
       </c>
-      <c r="M33">
-        <v>0.8</v>
-      </c>
       <c r="U33" t="s">
         <v>49</v>
       </c>
       <c r="V33" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="W33" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="X33" t="s">
         <v>51</v>
@@ -4107,49 +4176,46 @@
     </row>
     <row r="34" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
       </c>
       <c r="E34">
-        <v>2010</v>
+        <v>1956</v>
       </c>
       <c r="F34">
-        <v>1.3900000000000001E-2</v>
+        <v>0.185</v>
       </c>
       <c r="G34">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="H34" s="2">
-        <f>$P$44</f>
-        <v>2950.7891</v>
-      </c>
-      <c r="I34" s="3">
-        <f t="shared" si="1"/>
-        <v>133.5792717679</v>
+        <f>$R$40</f>
+        <v>0.33</v>
+      </c>
+      <c r="H34" s="1">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I34" s="2">
+        <f>(1.31/100)*H34</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J34">
-        <f>$R$44</f>
-        <v>2.8138000000000001</v>
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K34">
-        <v>40</v>
-      </c>
-      <c r="M34">
-        <v>0.8</v>
+        <v>73</v>
       </c>
       <c r="U34" t="s">
         <v>49</v>
       </c>
       <c r="V34" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="W34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="X34" t="s">
         <v>51</v>
@@ -4166,50 +4232,47 @@
     </row>
     <row r="35" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
       </c>
       <c r="E35">
-        <v>1997</v>
+        <v>2021</v>
       </c>
       <c r="F35">
-        <v>0.01</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G35">
+        <f>R41</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H35" s="1">
         <f>Q41</f>
-        <v>0.33</v>
-      </c>
-      <c r="H35" s="2">
-        <f>P41</f>
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="I35" s="3">
-        <f>($O$41/100)*H35</f>
-        <v>63.037519640000006</v>
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="I35" s="2">
+        <f>(P41/100)*H35</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J35">
-        <f>$R$41</f>
-        <v>4.1005000000000003</v>
+        <f>$S$41</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K35">
         <v>40</v>
       </c>
-      <c r="M35">
-        <v>0.8</v>
-      </c>
       <c r="U35" t="s">
         <v>49</v>
       </c>
       <c r="V35" t="s">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="W35" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="X35" t="s">
         <v>51</v>
@@ -4226,7 +4289,7 @@
     </row>
     <row r="36" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
@@ -4235,40 +4298,38 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F36">
-        <v>0.01</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G36">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H36" s="2">
-        <f>$P$45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I36" s="3">
-        <f>($O$45/100)*H36</f>
-        <v>162.96753257730003</v>
+        <f>R43</f>
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="H36" s="1">
+        <f>$Q$43</f>
+        <v>2950.7891</v>
+      </c>
+      <c r="I36" s="2">
+        <f>(4.5269/100)*H36</f>
+        <v>133.5792717679</v>
       </c>
       <c r="J36">
-        <f>$R$45</f>
+        <f>$S$43</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K36">
         <v>40</v>
       </c>
-      <c r="M36">
-        <v>0.8</v>
-      </c>
       <c r="U36" t="s">
         <v>49</v>
       </c>
       <c r="V36" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="W36" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="X36" t="s">
         <v>51</v>
@@ -4285,7 +4346,7 @@
     </row>
     <row r="37" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
@@ -4294,40 +4355,37 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="F37">
-        <v>0.01</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="G37">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H37" s="2">
-        <f>$P$45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I37" s="3">
-        <f t="shared" ref="I37:I39" si="2">($O$45/100)*H37</f>
-        <v>162.96753257730003</v>
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="H37" s="1">
+        <f>$Q$43</f>
+        <v>2950.7891</v>
+      </c>
+      <c r="I37" s="2">
+        <f t="shared" ref="I37:I39" si="0">(4.5269/100)*H37</f>
+        <v>133.5792717679</v>
       </c>
       <c r="J37">
-        <f>$R$45</f>
+        <f>$S$43</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K37">
         <v>40</v>
       </c>
-      <c r="M37">
-        <v>0.8</v>
-      </c>
       <c r="U37" t="s">
         <v>49</v>
       </c>
       <c r="V37" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="W37" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="X37" t="s">
         <v>51</v>
@@ -4344,7 +4402,7 @@
     </row>
     <row r="38" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
@@ -4353,40 +4411,37 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="F38">
-        <v>9.300000000000001E-3</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="G38">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H38" s="2">
-        <f>$P$45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I38" s="3">
-        <f t="shared" si="2"/>
-        <v>162.96753257730003</v>
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="H38" s="1">
+        <f>$Q$43</f>
+        <v>2950.7891</v>
+      </c>
+      <c r="I38" s="2">
+        <f t="shared" si="0"/>
+        <v>133.5792717679</v>
       </c>
       <c r="J38">
-        <f>$R$45</f>
+        <f>$S$43</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K38">
         <v>40</v>
       </c>
-      <c r="M38">
-        <v>0.8</v>
-      </c>
       <c r="U38" t="s">
         <v>49</v>
       </c>
       <c r="V38" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="W38" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="X38" t="s">
         <v>51</v>
@@ -4403,7 +4458,7 @@
     </row>
     <row r="39" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
@@ -4412,40 +4467,49 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>1963</v>
+        <v>2010</v>
       </c>
       <c r="F39">
-        <v>7.0999999999999995E-3</v>
+        <v>1.3900000000000001E-2</v>
       </c>
       <c r="G39">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H39" s="2">
-        <f>$P$45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I39" s="3">
-        <f t="shared" si="2"/>
-        <v>162.96753257730003</v>
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="H39" s="1">
+        <f>$Q$43</f>
+        <v>2950.7891</v>
+      </c>
+      <c r="I39" s="2">
+        <f t="shared" si="0"/>
+        <v>133.5792717679</v>
       </c>
       <c r="J39">
-        <f>$R$45</f>
+        <f>$S$43</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K39">
-        <v>72</v>
-      </c>
-      <c r="M39">
-        <v>0.8</v>
+        <v>40</v>
+      </c>
+      <c r="P39" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>190</v>
+      </c>
+      <c r="R39" t="s">
+        <v>191</v>
+      </c>
+      <c r="S39" t="s">
+        <v>192</v>
       </c>
       <c r="U39" t="s">
         <v>49</v>
       </c>
       <c r="V39" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="W39" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="X39" t="s">
         <v>51</v>
@@ -4462,59 +4526,59 @@
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
       <c r="D40" t="s">
         <v>14</v>
       </c>
       <c r="E40">
-        <v>2020</v>
+        <v>1997</v>
       </c>
       <c r="F40">
-        <v>5.7999999999999996E-3</v>
+        <v>0.01</v>
       </c>
       <c r="G40">
-        <f>Q42</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H40" s="2">
-        <f>P42</f>
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="I40" s="3">
-        <f>($O$42/100)*H40</f>
-        <v>39.138495576499992</v>
+        <f>R40</f>
+        <v>0.33</v>
+      </c>
+      <c r="H40" s="1">
+        <f>Q40</f>
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I40" s="2">
+        <f>($P$40/100)*H40</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J40">
-        <f>$R$42</f>
-        <v>5.8775000000000004</v>
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K40">
         <v>40</v>
       </c>
-      <c r="M40">
-        <v>0.8</v>
-      </c>
       <c r="O40" t="s">
-        <v>185</v>
-      </c>
-      <c r="P40" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>193</v>
-      </c>
-      <c r="R40" t="s">
-        <v>194</v>
+        <v>169</v>
+      </c>
+      <c r="P40" s="3">
+        <v>1.31</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="R40">
+        <v>0.33</v>
+      </c>
+      <c r="S40">
+        <v>4.1005000000000003</v>
       </c>
       <c r="U40" t="s">
         <v>49</v>
       </c>
       <c r="V40" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="W40" t="s">
         <v>140</v>
@@ -4534,7 +4598,7 @@
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
@@ -4543,55 +4607,52 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="F41">
-        <v>6.4999999999999997E-3</v>
+        <v>0.01</v>
       </c>
       <c r="G41">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H41" s="2">
-        <f>P45</f>
+      <c r="H41" s="1">
+        <f>$Q$44</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I41" s="3">
-        <f>($O$45/100)*H41</f>
+      <c r="I41" s="2">
+        <f>($P$44/100)*H41</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J41">
-        <f>$R$45</f>
+        <f>$S$44</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K41">
         <v>40</v>
       </c>
-      <c r="M41">
-        <v>0.8</v>
-      </c>
-      <c r="N41" t="s">
-        <v>171</v>
-      </c>
-      <c r="O41" s="4">
-        <v>1.31</v>
-      </c>
-      <c r="P41" s="2">
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="Q41">
-        <v>0.33</v>
+      <c r="O41" t="s">
+        <v>188</v>
+      </c>
+      <c r="P41" s="3">
+        <v>3.3294999999999999</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>1175.5066999999999</v>
       </c>
       <c r="R41">
-        <v>4.1005000000000003</v>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="S41">
+        <v>5.8775000000000004</v>
       </c>
       <c r="U41" t="s">
         <v>49</v>
       </c>
       <c r="V41" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="W41" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="X41" t="s">
         <v>51</v>
@@ -4608,65 +4669,51 @@
     </row>
     <row r="42" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
         <v>14</v>
       </c>
       <c r="E42">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="F42">
-        <v>4.0999999999999995E-3</v>
+        <v>0.01</v>
       </c>
       <c r="G42">
-        <f>Q42</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H42" s="2">
-        <f>P42</f>
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="I42" s="3">
-        <f>($O$42/100)*H42</f>
-        <v>39.138495576499992</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H42" s="1">
+        <f>$Q$44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I42" s="2">
+        <f>($P$44/100)*H42</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J42">
-        <f>$R$42</f>
-        <v>5.8775000000000004</v>
+        <f>$S$44</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K42">
         <v>40</v>
       </c>
-      <c r="M42">
-        <v>0.8</v>
-      </c>
-      <c r="N42" t="s">
-        <v>190</v>
-      </c>
-      <c r="O42" s="4">
-        <v>3.3294999999999999</v>
-      </c>
-      <c r="P42" s="2">
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="Q42">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="R42">
-        <v>5.8775000000000004</v>
-      </c>
+      <c r="O42" t="s">
+        <v>189</v>
+      </c>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="1"/>
       <c r="U42" t="s">
         <v>49</v>
       </c>
       <c r="V42" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="W42" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="X42" t="s">
         <v>51</v>
@@ -4683,55 +4730,61 @@
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
         <v>14</v>
       </c>
       <c r="E43">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="F43">
-        <v>1.4E-3</v>
+        <v>9.300000000000001E-3</v>
       </c>
       <c r="G43">
-        <f>Q41</f>
-        <v>0.33</v>
-      </c>
-      <c r="H43" s="2">
-        <f>P41</f>
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="I43" s="3">
-        <f>($O$45/100)*H43</f>
-        <v>173.62265237640003</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H43" s="1">
+        <f>$Q$44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I43" s="2">
+        <f>($P$44/100)*H43</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J43">
-        <f>$R$41</f>
-        <v>4.1005000000000003</v>
+        <f>$S$44</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K43">
         <v>40</v>
       </c>
-      <c r="M43">
-        <v>0.8</v>
-      </c>
-      <c r="N43" t="s">
-        <v>191</v>
-      </c>
-      <c r="O43" s="4"/>
-      <c r="P43" s="2"/>
+      <c r="O43" t="s">
+        <v>186</v>
+      </c>
+      <c r="P43">
+        <v>4.5269000000000004</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>2950.7891</v>
+      </c>
+      <c r="R43">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="S43">
+        <v>2.8138000000000001</v>
+      </c>
       <c r="U43" t="s">
         <v>49</v>
       </c>
       <c r="V43" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="W43" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="X43" t="s">
         <v>51</v>
@@ -4748,7 +4801,7 @@
     </row>
     <row r="44" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -4757,55 +4810,52 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>2013</v>
+        <v>1963</v>
       </c>
       <c r="F44">
-        <v>1.8E-3</v>
+        <v>7.0999999999999995E-3</v>
       </c>
       <c r="G44">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H44" s="2">
-        <f>P45</f>
+      <c r="H44" s="1">
+        <f>$Q$44</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I44" s="3">
-        <f>($O$45/100)*H44</f>
+      <c r="I44" s="2">
+        <f>($P$44/100)*H44</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J44">
-        <f>$R$45</f>
+        <f>$S$44</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K44">
-        <v>40</v>
-      </c>
-      <c r="M44">
-        <v>0.8</v>
-      </c>
-      <c r="N44" t="s">
-        <v>188</v>
-      </c>
-      <c r="O44">
-        <v>4.5269000000000004</v>
-      </c>
-      <c r="P44" s="2">
-        <v>2950.7891</v>
-      </c>
-      <c r="Q44">
-        <v>0.46800000000000003</v>
+        <v>72</v>
+      </c>
+      <c r="O44" t="s">
+        <v>187</v>
+      </c>
+      <c r="P44">
+        <v>3.6080999999999999</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>4516.7133000000003</v>
       </c>
       <c r="R44">
+        <v>0.2994</v>
+      </c>
+      <c r="S44">
         <v>2.8138000000000001</v>
       </c>
       <c r="U44" t="s">
         <v>49</v>
       </c>
       <c r="V44" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="W44" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="X44" t="s">
         <v>51</v>
@@ -4822,64 +4872,54 @@
     </row>
     <row r="45" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
       </c>
       <c r="E45">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="F45">
-        <v>1.6999999999999999E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="G45">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H45" s="2">
-        <f>P45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I45" s="3">
-        <f>($O$45/100)*H45</f>
-        <v>162.96753257730003</v>
+        <f>R41</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H45" s="1">
+        <f>Q41</f>
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="I45" s="2">
+        <f>($P$41/100)*H45</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J45">
-        <f>$R$45</f>
-        <v>2.8138000000000001</v>
+        <f>$S$41</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K45">
         <v>40</v>
       </c>
-      <c r="M45">
-        <v>0.8</v>
-      </c>
-      <c r="N45" t="s">
-        <v>189</v>
-      </c>
-      <c r="O45">
-        <v>3.6080999999999999</v>
+      <c r="O45" t="s">
+        <v>22</v>
       </c>
       <c r="P45" s="2">
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="Q45">
-        <v>0.2994</v>
-      </c>
-      <c r="R45">
-        <v>2.8138000000000001</v>
-      </c>
+        <v>1.5780000000000001</v>
+      </c>
+      <c r="Q45" s="3"/>
       <c r="U45" t="s">
         <v>49</v>
       </c>
       <c r="V45" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="W45" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="X45" t="s">
         <v>51</v>
@@ -4896,57 +4936,56 @@
     </row>
     <row r="46" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
         <v>14</v>
       </c>
       <c r="E46">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="F46">
-        <v>1.8E-3</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="G46">
-        <f>Q42</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H46" s="2">
-        <f>P42</f>
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="I46" s="3">
-        <f t="shared" ref="I46:I47" si="3">($O$42/100)*H46</f>
-        <v>39.138495576499992</v>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H46" s="1">
+        <f>Q44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I46" s="2">
+        <f>($P$44/100)*H46</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J46">
-        <f>$R$42</f>
-        <v>5.8775000000000004</v>
+        <f>$S$44</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K46">
         <v>40</v>
       </c>
-      <c r="M46">
-        <v>0.8</v>
-      </c>
-      <c r="N46" t="s">
-        <v>22</v>
-      </c>
-      <c r="O46" s="3">
-        <v>1.5780000000000001</v>
-      </c>
-      <c r="P46" s="4"/>
+      <c r="O46" t="s">
+        <v>25</v>
+      </c>
+      <c r="P46" s="2">
+        <v>1.2514000000000001</v>
+      </c>
+      <c r="Q46" s="3"/>
+      <c r="S46">
+        <v>2.0036999999999998</v>
+      </c>
       <c r="U46" t="s">
         <v>49</v>
       </c>
       <c r="V46" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="W46" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="X46" t="s">
         <v>51</v>
@@ -4963,7 +5002,7 @@
     </row>
     <row r="47" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C47" t="s">
         <v>16</v>
@@ -4975,40 +5014,37 @@
         <v>2015</v>
       </c>
       <c r="F47">
-        <v>1.8E-3</v>
+        <v>4.0999999999999995E-3</v>
       </c>
       <c r="G47">
-        <f>Q42</f>
+        <f>R41</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="H47" s="2">
-        <f>P42</f>
+      <c r="H47" s="1">
+        <f>Q41</f>
         <v>1175.5066999999999</v>
       </c>
-      <c r="I47" s="3">
-        <f t="shared" si="3"/>
+      <c r="I47" s="2">
+        <f>($P$41/100)*H47</f>
         <v>39.138495576499992</v>
       </c>
       <c r="J47">
-        <f>$R$42</f>
+        <f>$S$41</f>
         <v>5.8775000000000004</v>
       </c>
       <c r="K47">
         <v>40</v>
       </c>
-      <c r="M47">
-        <v>0.8</v>
-      </c>
-      <c r="O47" s="3"/>
-      <c r="P47" s="4"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="3"/>
       <c r="U47" t="s">
         <v>49</v>
       </c>
       <c r="V47" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="W47" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="X47" t="s">
         <v>51</v>
@@ -5025,51 +5061,49 @@
     </row>
     <row r="48" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="D48" t="s">
         <v>14</v>
       </c>
       <c r="E48">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="F48">
-        <v>1.5E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G48">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H48" s="2">
-        <f>P45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I48" s="3">
-        <f>($O$45/100)*H48</f>
-        <v>162.96753257730003</v>
+        <f>R40</f>
+        <v>0.33</v>
+      </c>
+      <c r="H48" s="1">
+        <f>Q40</f>
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I48" s="2">
+        <f>($P$44/100)*H48</f>
+        <v>173.62265237640003</v>
       </c>
       <c r="J48">
-        <f t="shared" ref="J48:J53" si="4">$R$45</f>
-        <v>2.8138000000000001</v>
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K48">
         <v>40</v>
       </c>
-      <c r="M48">
-        <v>0.8</v>
-      </c>
-      <c r="O48" s="3"/>
-      <c r="P48" s="4"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="3"/>
       <c r="U48" t="s">
         <v>49</v>
       </c>
       <c r="V48" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="W48" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="X48" t="s">
         <v>51</v>
@@ -5086,7 +5120,7 @@
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
@@ -5098,39 +5132,34 @@
         <v>2013</v>
       </c>
       <c r="F49">
-        <v>1.4E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G49">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H49" s="2">
-        <f>$P$45</f>
+      <c r="H49" s="1">
+        <f>Q44</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I49" s="3">
-        <f t="shared" ref="I49:I53" si="5">($O$45/100)*H49</f>
+      <c r="I49" s="2">
+        <f>($P$44/100)*H49</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J49">
-        <f t="shared" si="4"/>
+        <f>$S$44</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K49">
         <v>40</v>
       </c>
-      <c r="M49">
-        <v>0.8</v>
-      </c>
-      <c r="O49" s="3"/>
-      <c r="P49" s="4"/>
       <c r="U49" t="s">
         <v>49</v>
       </c>
       <c r="V49" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="W49" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="X49" t="s">
         <v>51</v>
@@ -5147,7 +5176,7 @@
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
@@ -5156,40 +5185,37 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F50">
-        <v>1.1999999999999999E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="G50">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H50" s="2">
-        <f>$P$45</f>
+      <c r="H50" s="1">
+        <f>Q44</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I50" s="3">
-        <f t="shared" si="5"/>
+      <c r="I50" s="2">
+        <f>($P$44/100)*H50</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J50">
-        <f t="shared" si="4"/>
+        <f>$S$44</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K50">
         <v>40</v>
       </c>
-      <c r="M50">
-        <v>0.8</v>
-      </c>
       <c r="U50" t="s">
         <v>49</v>
       </c>
       <c r="V50" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="W50" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="X50" t="s">
         <v>51</v>
@@ -5206,10 +5232,10 @@
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D51" t="s">
         <v>14</v>
@@ -5218,37 +5244,35 @@
         <v>2009</v>
       </c>
       <c r="F51">
-        <v>1.9E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G51">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H51" s="2">
-        <f>P45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I51" s="3">
-        <f t="shared" si="5"/>
-        <v>162.96753257730003</v>
+        <f>R41</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H51" s="1">
+        <f>Q41</f>
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="I51" s="2">
+        <f>($P$41/100)*H51</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J51">
-        <f t="shared" si="4"/>
-        <v>2.8138000000000001</v>
+        <f>$S$41</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K51">
         <v>40</v>
       </c>
-      <c r="M51">
-        <v>0.8</v>
-      </c>
       <c r="U51" t="s">
         <v>49</v>
       </c>
       <c r="V51" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="W51" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="X51" t="s">
         <v>51</v>
@@ -5265,49 +5289,47 @@
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D52" t="s">
         <v>14</v>
       </c>
       <c r="E52">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="F52">
-        <v>8.9999999999999998E-4</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G52">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H52" s="2">
-        <f>P45</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I52" s="3">
-        <f t="shared" si="5"/>
-        <v>162.96753257730003</v>
+        <f>R41</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H52" s="1">
+        <f>Q41</f>
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="I52" s="2">
+        <f>($P$41/100)*H52</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J52">
-        <f t="shared" si="4"/>
-        <v>2.8138000000000001</v>
+        <f>$S$41</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K52">
         <v>40</v>
       </c>
-      <c r="M52">
-        <v>0.8</v>
-      </c>
       <c r="U52" t="s">
         <v>49</v>
       </c>
       <c r="V52" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="W52" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="X52" t="s">
         <v>51</v>
@@ -5324,7 +5346,7 @@
     </row>
     <row r="53" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
@@ -5333,40 +5355,37 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F53">
-        <v>5.0000000000000001E-4</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G53">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H53" s="2">
-        <f>P45</f>
+      <c r="H53" s="1">
+        <f>Q44</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I53" s="3">
-        <f t="shared" si="5"/>
+      <c r="I53" s="2">
+        <f>($P$44/100)*H53</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J53">
-        <f t="shared" si="4"/>
+        <f>$S$44</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K53">
         <v>40</v>
       </c>
-      <c r="M53">
-        <v>0.8</v>
-      </c>
       <c r="U53" t="s">
         <v>49</v>
       </c>
       <c r="V53" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="W53" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="X53" t="s">
         <v>51</v>
@@ -5383,51 +5402,328 @@
     </row>
     <row r="54" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D54" t="s">
         <v>14</v>
       </c>
       <c r="E54">
+        <v>2013</v>
+      </c>
+      <c r="F54">
+        <v>1.4E-3</v>
+      </c>
+      <c r="G54">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H54" s="1">
+        <f>$Q$44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I54" s="2">
+        <f>($P$44/100)*H54</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J54">
+        <f>$S$44</f>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K54">
+        <v>40</v>
+      </c>
+      <c r="U54" t="s">
+        <v>49</v>
+      </c>
+      <c r="V54" t="s">
+        <v>160</v>
+      </c>
+      <c r="W54" t="s">
+        <v>161</v>
+      </c>
+      <c r="X54" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B55" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55">
+        <v>2016</v>
+      </c>
+      <c r="F55">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="G55">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H55" s="1">
+        <f>$Q$44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I55" s="2">
+        <f>($P$44/100)*H55</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J55">
+        <f>$S$44</f>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K55">
+        <v>40</v>
+      </c>
+      <c r="U55" t="s">
+        <v>49</v>
+      </c>
+      <c r="V55" t="s">
+        <v>162</v>
+      </c>
+      <c r="W55" t="s">
+        <v>163</v>
+      </c>
+      <c r="X55" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56">
+        <v>2009</v>
+      </c>
+      <c r="F56">
+        <v>1.9E-3</v>
+      </c>
+      <c r="G56">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H56" s="1">
+        <f>Q44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I56" s="2">
+        <f>($P$44/100)*H56</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J56">
+        <f>$S$44</f>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K56">
+        <v>40</v>
+      </c>
+      <c r="U56" t="s">
+        <v>49</v>
+      </c>
+      <c r="V56" t="s">
+        <v>164</v>
+      </c>
+      <c r="W56" t="s">
+        <v>166</v>
+      </c>
+      <c r="X56" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>165</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57">
+        <v>2012</v>
+      </c>
+      <c r="F57">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="G57">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H57" s="1">
+        <f>Q44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I57" s="2">
+        <f>($P$44/100)*H57</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J57">
+        <f>$S$44</f>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K57">
+        <v>40</v>
+      </c>
+      <c r="U57" t="s">
+        <v>49</v>
+      </c>
+      <c r="V57" t="s">
+        <v>165</v>
+      </c>
+      <c r="W57" t="s">
+        <v>167</v>
+      </c>
+      <c r="X57" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58">
+        <v>2015</v>
+      </c>
+      <c r="F58">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="G58">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H58" s="1">
+        <f>Q44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I58" s="2">
+        <f>($P$44/100)*H58</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J58">
+        <f>$S$44</f>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K58">
+        <v>40</v>
+      </c>
+      <c r="U58" t="s">
+        <v>49</v>
+      </c>
+      <c r="V58" t="s">
+        <v>168</v>
+      </c>
+      <c r="W58" t="s">
+        <v>197</v>
+      </c>
+      <c r="X58" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59">
         <v>2022</v>
       </c>
-      <c r="F54">
+      <c r="F59">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G54">
+      <c r="G59">
         <v>0.33123000000000002</v>
       </c>
-      <c r="M54">
-        <v>0.8</v>
-      </c>
-      <c r="U54" t="s">
-        <v>49</v>
-      </c>
-      <c r="V54" t="s">
+      <c r="U59" t="s">
+        <v>49</v>
+      </c>
+      <c r="V59" t="s">
         <v>18</v>
       </c>
-      <c r="W54" t="s">
+      <c r="W59" t="s">
         <v>58</v>
       </c>
-      <c r="X54" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z54" t="s">
+      <c r="X59" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z59" t="s">
         <v>53</v>
       </c>
-      <c r="AA54" t="s">
+      <c r="AA59" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="72" spans="2:27" x14ac:dyDescent="0.35">
       <c r="V72" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="2:27" x14ac:dyDescent="0.35">
@@ -5477,6 +5773,36 @@
       </c>
     </row>
     <row r="75" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75">
+        <v>2013</v>
+      </c>
+      <c r="F75">
+        <v>0.25109999999999999</v>
+      </c>
+      <c r="G75">
+        <v>0.36049999999999999</v>
+      </c>
+      <c r="H75">
+        <v>1265</v>
+      </c>
+      <c r="I75" s="2">
+        <v>48.400000000000006</v>
+      </c>
+      <c r="J75">
+        <v>7.5075000000000003</v>
+      </c>
+      <c r="K75">
+        <v>42</v>
+      </c>
       <c r="U75" t="s">
         <v>49</v>
       </c>
@@ -5501,34 +5827,22 @@
     </row>
     <row r="76" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D76" t="s">
         <v>14</v>
       </c>
       <c r="E76">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="F76">
-        <v>0.25109999999999999</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="G76">
-        <v>0.36049999999999999</v>
-      </c>
-      <c r="H76">
-        <v>1265</v>
-      </c>
-      <c r="I76" s="3">
-        <v>48.400000000000006</v>
-      </c>
-      <c r="J76">
-        <v>7.5075000000000003</v>
-      </c>
-      <c r="K76">
-        <v>42</v>
+        <v>0.33123000000000002</v>
       </c>
       <c r="U76" t="s">
         <v>49</v>
@@ -5553,24 +5867,6 @@
       </c>
     </row>
     <row r="77" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B77" t="s">
-        <v>15</v>
-      </c>
-      <c r="C77" t="s">
-        <v>16</v>
-      </c>
-      <c r="D77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E77">
-        <v>2022</v>
-      </c>
-      <c r="F77">
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="G77">
-        <v>0.33123000000000002</v>
-      </c>
       <c r="U77" t="s">
         <v>49</v>
       </c>
@@ -5594,6 +5890,36 @@
       </c>
     </row>
     <row r="78" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78">
+        <v>2022</v>
+      </c>
+      <c r="F78">
+        <v>0.3</v>
+      </c>
+      <c r="G78">
+        <v>0.33990000000000004</v>
+      </c>
+      <c r="H78">
+        <v>4427.5</v>
+      </c>
+      <c r="I78" s="2">
+        <v>157.30000000000001</v>
+      </c>
+      <c r="J78">
+        <v>9.24</v>
+      </c>
+      <c r="K78">
+        <v>50</v>
+      </c>
       <c r="U78" t="s">
         <v>49</v>
       </c>
@@ -5617,36 +5943,6 @@
       </c>
     </row>
     <row r="79" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B79" t="s">
-        <v>12</v>
-      </c>
-      <c r="C79" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79">
-        <v>2022</v>
-      </c>
-      <c r="F79">
-        <v>0.3</v>
-      </c>
-      <c r="G79">
-        <v>0.33990000000000004</v>
-      </c>
-      <c r="H79">
-        <v>4427.5</v>
-      </c>
-      <c r="I79" s="3">
-        <v>157.30000000000001</v>
-      </c>
-      <c r="J79">
-        <v>9.24</v>
-      </c>
-      <c r="K79">
-        <v>50</v>
-      </c>
       <c r="U79" t="s">
         <v>49</v>
       </c>
@@ -5738,21 +6034,44 @@
         <v>54</v>
       </c>
     </row>
+    <row r="83" spans="2:27" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" t="s">
+        <v>25</v>
+      </c>
+      <c r="D83" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83">
+        <v>2022</v>
+      </c>
+      <c r="F83">
+        <v>1.5040605442498314E-2</v>
+      </c>
+      <c r="G83">
+        <v>0.33123000000000002</v>
+      </c>
+      <c r="L83">
+        <v>0.42012333946150526</v>
+      </c>
+    </row>
     <row r="84" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C84" t="s">
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E84">
         <v>2022</v>
       </c>
       <c r="F84">
-        <v>1.5040605442498314E-2</v>
+        <v>1.5497656626156837E-2</v>
       </c>
       <c r="G84">
         <v>0.33123000000000002</v>
@@ -5784,19 +6103,19 @@
     </row>
     <row r="85" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C85" t="s">
         <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E85">
         <v>2022</v>
       </c>
       <c r="F85">
-        <v>1.5497656626156837E-2</v>
+        <v>1.4461737931344828E-2</v>
       </c>
       <c r="G85">
         <v>0.33123000000000002</v>
@@ -5807,42 +6126,54 @@
     </row>
     <row r="86" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C86" t="s">
         <v>25</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E86">
-        <v>2022</v>
+        <v>2009</v>
       </c>
       <c r="F86">
-        <v>1.4461737931344828E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G86">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H86">
+        <v>2376</v>
+      </c>
+      <c r="I86" s="2">
+        <v>57.2</v>
+      </c>
+      <c r="J86">
+        <v>2.52</v>
+      </c>
+      <c r="K86">
+        <v>46</v>
       </c>
       <c r="L86">
-        <v>0.42012333946150526</v>
+        <v>0.47763777043344691</v>
       </c>
     </row>
     <row r="87" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C87" t="s">
         <v>25</v>
       </c>
       <c r="D87" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E87">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="F87">
-        <v>3.9E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -5850,20 +6181,20 @@
       <c r="H87">
         <v>2376</v>
       </c>
-      <c r="I87" s="3">
+      <c r="I87" s="2">
         <v>57.2</v>
       </c>
       <c r="J87">
         <v>2.52</v>
       </c>
       <c r="K87">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L87">
-        <v>0.47763777043344691</v>
+        <v>0.47814004703314078</v>
       </c>
       <c r="Q87" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="2:27" x14ac:dyDescent="0.35">
@@ -5877,10 +6208,10 @@
         <v>34</v>
       </c>
       <c r="E88">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="F88">
-        <v>1.6E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -5888,17 +6219,17 @@
       <c r="H88">
         <v>2376</v>
       </c>
-      <c r="I88" s="3">
-        <v>57.2</v>
+      <c r="I88" s="2">
+        <v>57.20000000000001</v>
       </c>
       <c r="J88">
         <v>2.52</v>
       </c>
       <c r="K88">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L88">
-        <v>0.47814004703314078</v>
+        <v>0.47814004703314084</v>
       </c>
     </row>
     <row r="89" spans="2:27" x14ac:dyDescent="0.35">
@@ -5912,10 +6243,10 @@
         <v>34</v>
       </c>
       <c r="E89">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="F89">
-        <v>1.7999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -5923,34 +6254,34 @@
       <c r="H89">
         <v>2376</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I89" s="2">
         <v>57.20000000000001</v>
       </c>
       <c r="J89">
         <v>2.52</v>
       </c>
       <c r="K89">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L89">
-        <v>0.47814004703314084</v>
+        <v>0.47814004703314078</v>
       </c>
     </row>
     <row r="90" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C90" t="s">
         <v>25</v>
       </c>
       <c r="D90" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E90">
-        <v>2020</v>
+        <v>2007</v>
       </c>
       <c r="F90">
-        <v>1.2E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -5958,17 +6289,17 @@
       <c r="H90">
         <v>2376</v>
       </c>
-      <c r="I90" s="3">
-        <v>57.20000000000001</v>
+      <c r="I90" s="2">
+        <v>57.2</v>
       </c>
       <c r="J90">
         <v>2.52</v>
       </c>
       <c r="K90">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L90">
-        <v>0.47814004703314078</v>
+        <v>0.40144059976798208</v>
       </c>
     </row>
     <row r="91" spans="2:27" x14ac:dyDescent="0.35">
@@ -5982,10 +6313,10 @@
         <v>36</v>
       </c>
       <c r="E91">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="F91">
-        <v>2.1000000000000001E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -5993,17 +6324,17 @@
       <c r="H91">
         <v>2376</v>
       </c>
-      <c r="I91" s="3">
-        <v>57.2</v>
+      <c r="I91" s="2">
+        <v>57.20000000000001</v>
       </c>
       <c r="J91">
         <v>2.52</v>
       </c>
       <c r="K91">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L91">
-        <v>0.40144059976798208</v>
+        <v>0.40144059976798202</v>
       </c>
     </row>
     <row r="92" spans="2:27" x14ac:dyDescent="0.35">
@@ -6017,10 +6348,10 @@
         <v>36</v>
       </c>
       <c r="E92">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="F92">
-        <v>2.4E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -6028,14 +6359,14 @@
       <c r="H92">
         <v>2376</v>
       </c>
-      <c r="I92" s="3">
-        <v>57.20000000000001</v>
+      <c r="I92" s="2">
+        <v>57.2</v>
       </c>
       <c r="J92">
         <v>2.52</v>
       </c>
       <c r="K92">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L92">
         <v>0.40144059976798202</v>
@@ -6052,10 +6383,10 @@
         <v>36</v>
       </c>
       <c r="E93">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="F93">
-        <v>7.9000000000000001E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -6063,17 +6394,17 @@
       <c r="H93">
         <v>2376</v>
       </c>
-      <c r="I93" s="3">
+      <c r="I93" s="2">
         <v>57.2</v>
       </c>
       <c r="J93">
         <v>2.52</v>
       </c>
       <c r="K93">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L93">
-        <v>0.40144059976798202</v>
+        <v>0.40144059976798208</v>
       </c>
     </row>
     <row r="94" spans="2:27" x14ac:dyDescent="0.35">
@@ -6087,80 +6418,80 @@
         <v>36</v>
       </c>
       <c r="E94">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F94">
-        <v>2.1000000000000001E-2</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="G94">
         <v>1</v>
       </c>
       <c r="H94">
-        <v>2376</v>
-      </c>
-      <c r="I94" s="3">
-        <v>57.2</v>
+        <v>2024</v>
+      </c>
+      <c r="I94" s="2">
+        <v>48.4</v>
       </c>
       <c r="J94">
-        <v>2.52</v>
+        <v>2.3100000000000005</v>
       </c>
       <c r="K94">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L94">
-        <v>0.40144059976798208</v>
+        <v>0.40144059976798202</v>
       </c>
     </row>
     <row r="95" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C95" t="s">
         <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E95">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F95">
-        <v>0.10199999999999999</v>
+        <v>3.9E-2</v>
       </c>
       <c r="G95">
         <v>1</v>
       </c>
       <c r="H95">
-        <v>2024</v>
-      </c>
-      <c r="I95" s="3">
-        <v>48.4</v>
+        <v>2376</v>
+      </c>
+      <c r="I95" s="2">
+        <v>57.2</v>
       </c>
       <c r="J95">
-        <v>2.3100000000000005</v>
+        <v>2.52</v>
       </c>
       <c r="K95">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L95">
-        <v>0.40144059976798202</v>
+        <v>0.365520596150406</v>
       </c>
     </row>
     <row r="96" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C96" t="s">
         <v>25</v>
       </c>
       <c r="D96" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E96">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="F96">
-        <v>3.9E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -6168,17 +6499,17 @@
       <c r="H96">
         <v>2376</v>
       </c>
-      <c r="I96" s="3">
-        <v>57.2</v>
+      <c r="I96" s="2">
+        <v>57.20000000000001</v>
       </c>
       <c r="J96">
         <v>2.52</v>
       </c>
       <c r="K96">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="L96">
-        <v>0.365520596150406</v>
+        <v>0.41047488326249421</v>
       </c>
     </row>
     <row r="97" spans="2:12" x14ac:dyDescent="0.35">
@@ -6192,10 +6523,10 @@
         <v>40</v>
       </c>
       <c r="E97">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="F97">
-        <v>1.7999999999999999E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -6203,14 +6534,14 @@
       <c r="H97">
         <v>2376</v>
       </c>
-      <c r="I97" s="3">
-        <v>57.20000000000001</v>
+      <c r="I97" s="2">
+        <v>57.2</v>
       </c>
       <c r="J97">
         <v>2.52</v>
       </c>
       <c r="K97">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="L97">
         <v>0.41047488326249421</v>
@@ -6227,7 +6558,7 @@
         <v>40</v>
       </c>
       <c r="E98">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="F98">
         <v>2.1999999999999999E-2</v>
@@ -6238,51 +6569,16 @@
       <c r="H98">
         <v>2376</v>
       </c>
-      <c r="I98" s="3">
+      <c r="I98" s="2">
         <v>57.2</v>
       </c>
       <c r="J98">
         <v>2.52</v>
       </c>
       <c r="K98">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L98">
-        <v>0.41047488326249421</v>
-      </c>
-    </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B99" t="s">
-        <v>39</v>
-      </c>
-      <c r="C99" t="s">
-        <v>25</v>
-      </c>
-      <c r="D99" t="s">
-        <v>40</v>
-      </c>
-      <c r="E99">
-        <v>2013</v>
-      </c>
-      <c r="F99">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="G99">
-        <v>1</v>
-      </c>
-      <c r="H99">
-        <v>2376</v>
-      </c>
-      <c r="I99" s="3">
-        <v>57.2</v>
-      </c>
-      <c r="J99">
-        <v>2.52</v>
-      </c>
-      <c r="K99">
-        <v>42</v>
-      </c>
-      <c r="L99">
         <v>0.41047488326249421</v>
       </c>
     </row>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F982AB3-9134-4A83-8302-9DF00F29CB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1855B0-460A-4373-9E67-01E028CE5590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -70,14 +70,14 @@
     <author>tc={D3B26940-5207-4925-84BA-C36AB3766D74}</author>
     <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
     <author>tc={5D0B02A9-24B3-4F36-8683-2AD26D1E0821}</author>
-    <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
     <author>tc={C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}</author>
     <author>tc={C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}</author>
+    <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
     <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
     <author>tc={1905391B-2A5F-4643-B2AC-720AD8410CDA}</author>
   </authors>
   <commentList>
-    <comment ref="Z21" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+    <comment ref="Z26" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +85,7 @@
     Miks daynite (hydro samuti)</t>
       </text>
     </comment>
-    <comment ref="F30" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <comment ref="F35" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -93,7 +93,7 @@
     Iru produces only 17 MW in 2025 not 0.207 GW</t>
       </text>
     </comment>
-    <comment ref="B31" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+    <comment ref="B36" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -101,16 +101,7 @@
     TODO: set their actual start date and then add how much they produce in 2025</t>
       </text>
     </comment>
-    <comment ref="E39" authorId="3" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Ei tea
-</t>
-      </text>
-    </comment>
-    <comment ref="P39" authorId="4" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+    <comment ref="P39" authorId="3" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -119,12 +110,21 @@
 </t>
       </text>
     </comment>
-    <comment ref="S43" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+    <comment ref="S43" authorId="4" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Took same as chp</t>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="5" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Ei tea
+</t>
       </text>
     </comment>
     <comment ref="J78" authorId="6" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="242">
   <si>
     <t>~fi_t</t>
   </si>
@@ -844,6 +844,36 @@
   </si>
   <si>
     <t>vka tuul</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_voru</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_saare</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_laane</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_hiiu</t>
+  </si>
+  <si>
+    <t>elc_spv_voru</t>
+  </si>
+  <si>
+    <t>elc_spv_saare</t>
+  </si>
+  <si>
+    <t>elc_spv_rapla</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_rapla</t>
+  </si>
+  <si>
+    <t>elv_spv_laane</t>
+  </si>
+  <si>
+    <t>elv_spv_hiiu</t>
   </si>
 </sst>
 </file>
@@ -1238,18 +1268,14 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="Z21" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+  <threadedComment ref="Z26" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
     <text>Miks daynite (hydro samuti)</text>
   </threadedComment>
-  <threadedComment ref="F30" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+  <threadedComment ref="F35" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
-  <threadedComment ref="B31" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+  <threadedComment ref="B36" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
     <text>TODO: set their actual start date and then add how much they produce in 2025</text>
-  </threadedComment>
-  <threadedComment ref="E39" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
-    <text xml:space="preserve">Ei tea
-</text>
   </threadedComment>
   <threadedComment ref="P39" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
     <text xml:space="preserve">NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)
@@ -1257,6 +1283,10 @@
   </threadedComment>
   <threadedComment ref="S43" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
     <text>Took same as chp</text>
+  </threadedComment>
+  <threadedComment ref="E44" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
+    <text xml:space="preserve">Ei tea
+</text>
   </threadedComment>
   <threadedComment ref="J78" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
     <text>From 9,24 to 6</text>
@@ -1270,14 +1300,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047CB67-FC18-43CA-8AA0-0CA09A11D4D8}">
   <dimension ref="B9:T17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="46.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="73.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="73.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>182</v>
       </c>
@@ -1285,7 +1315,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1341,7 +1371,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>110</v>
       </c>
@@ -1397,7 +1427,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>111</v>
       </c>
@@ -1453,7 +1483,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>112</v>
       </c>
@@ -1509,7 +1539,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>113</v>
       </c>
@@ -1565,7 +1595,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>114</v>
       </c>
@@ -1629,15 +1659,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4FEF-80F2-457D-B441-6C3DD45005FF}">
   <dimension ref="B9:T30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="39.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="39.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="48.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>182</v>
       </c>
@@ -1645,7 +1677,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -1701,7 +1733,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>177</v>
       </c>
@@ -1754,7 +1786,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>176</v>
       </c>
@@ -1807,7 +1839,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>66</v>
       </c>
@@ -1863,7 +1895,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>69</v>
       </c>
@@ -1919,7 +1951,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>71</v>
       </c>
@@ -1975,7 +2007,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>73</v>
       </c>
@@ -2031,7 +2063,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>74</v>
       </c>
@@ -2087,7 +2119,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>75</v>
       </c>
@@ -2143,7 +2175,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>76</v>
       </c>
@@ -2199,7 +2231,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>77</v>
       </c>
@@ -2249,7 +2281,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>78</v>
       </c>
@@ -2299,7 +2331,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>79</v>
       </c>
@@ -2355,7 +2387,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>80</v>
       </c>
@@ -2411,7 +2443,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>81</v>
       </c>
@@ -2467,7 +2499,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>83</v>
       </c>
@@ -2523,7 +2555,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>85</v>
       </c>
@@ -2579,7 +2611,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>86</v>
       </c>
@@ -2635,7 +2667,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>87</v>
       </c>
@@ -2691,7 +2723,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>178</v>
       </c>
@@ -2753,30 +2785,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
   <dimension ref="B9:AA98"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="40.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="64.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="41.453125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="64.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="41.453125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="64.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="64.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>0</v>
       </c>
@@ -2784,7 +2816,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -2843,7 +2875,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>207</v>
       </c>
@@ -2866,7 +2898,7 @@
         <v>1018</v>
       </c>
       <c r="I11" s="2">
-        <f>($P$45/100)*H11</f>
+        <f t="shared" ref="I11:I25" si="0">($P$45/100)*H11</f>
         <v>16.064040000000002</v>
       </c>
       <c r="J11">
@@ -2900,7 +2932,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>208</v>
       </c>
@@ -2923,7 +2955,7 @@
         <v>1018</v>
       </c>
       <c r="I12" s="2">
-        <f>($P$45/100)*H12</f>
+        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
       <c r="J12">
@@ -2957,7 +2989,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>209</v>
       </c>
@@ -2980,7 +3012,7 @@
         <v>1018</v>
       </c>
       <c r="I13" s="2">
-        <f>($P$45/100)*H13</f>
+        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
       <c r="J13">
@@ -3014,7 +3046,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>210</v>
       </c>
@@ -3037,7 +3069,7 @@
         <v>1018</v>
       </c>
       <c r="I14" s="2">
-        <f>($P$45/100)*H14</f>
+        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
       <c r="J14">
@@ -3071,7 +3103,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>211</v>
       </c>
@@ -3094,7 +3126,7 @@
         <v>1018</v>
       </c>
       <c r="I15" s="2">
-        <f>($P$45/100)*H15</f>
+        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
       <c r="J15">
@@ -3128,7 +3160,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>216</v>
       </c>
@@ -3151,7 +3183,7 @@
         <v>1018</v>
       </c>
       <c r="I16" s="2">
-        <f>($P$45/100)*H16</f>
+        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
       <c r="J16">
@@ -3185,7 +3217,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>212</v>
       </c>
@@ -3208,7 +3240,7 @@
         <v>1018</v>
       </c>
       <c r="I17" s="2">
-        <f>($P$45/100)*H17</f>
+        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
       <c r="J17">
@@ -3220,6 +3252,10 @@
       <c r="L17">
         <v>0.15619560585976827</v>
       </c>
+      <c r="P17">
+        <f>242+242+132+108+80+78+75+47+43+40+35+31+29+11+5</f>
+        <v>1198</v>
+      </c>
       <c r="U17" t="s">
         <v>49</v>
       </c>
@@ -3242,7 +3278,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>213</v>
       </c>
@@ -3265,7 +3301,7 @@
         <v>1018</v>
       </c>
       <c r="I18" s="2">
-        <f>($P$45/100)*H18</f>
+        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
       <c r="J18">
@@ -3299,7 +3335,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>214</v>
       </c>
@@ -3322,7 +3358,7 @@
         <v>1018</v>
       </c>
       <c r="I19" s="2">
-        <f>($P$45/100)*H19</f>
+        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
       <c r="J19">
@@ -3356,7 +3392,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>215</v>
       </c>
@@ -3379,7 +3415,7 @@
         <v>1018</v>
       </c>
       <c r="I20" s="2">
-        <f>($P$45/100)*H20</f>
+        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
       <c r="J20">
@@ -3391,6 +3427,10 @@
       <c r="L20">
         <v>0.1532628310027955</v>
       </c>
+      <c r="P20">
+        <f>SUM(F11:F25)</f>
+        <v>1.1969999999999996</v>
+      </c>
       <c r="U20" t="s">
         <v>49</v>
       </c>
@@ -3413,50 +3453,49 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>41</v>
+        <v>232</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="E21">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F21">
-        <v>7.9699999999999993E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21" s="1">
-        <v>1494.4630999999999</v>
+        <v>1019</v>
       </c>
       <c r="I21" s="2">
-        <f>($P$46/100)*H21</f>
-        <v>18.701711233400001</v>
+        <f t="shared" si="0"/>
+        <v>16.079820000000002</v>
       </c>
       <c r="J21">
-        <f>$S$46</f>
-        <v>2.0036999999999998</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L21">
-        <v>0.4</v>
+        <v>0.1461854238754417</v>
       </c>
       <c r="U21" t="s">
         <v>49</v>
       </c>
       <c r="V21" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="W21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="X21" t="s">
         <v>51</v>
@@ -3465,47 +3504,46 @@
         <v>52</v>
       </c>
       <c r="Z21" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AA21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="E22">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F22">
-        <v>0.17519999999999999</v>
+        <v>3.1E-2</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" s="1">
-        <v>1494.4630999999999</v>
+        <v>1020</v>
       </c>
       <c r="I22" s="2">
-        <f>($P$46/100)*H22</f>
-        <v>18.701711233400001</v>
+        <f t="shared" si="0"/>
+        <v>16.095600000000001</v>
       </c>
       <c r="J22">
-        <f>$S$46</f>
-        <v>2.0036999999999998</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L22">
-        <v>0.4</v>
+        <v>0.1461854238754417</v>
       </c>
       <c r="P22" t="s">
         <v>231</v>
@@ -3514,10 +3552,10 @@
         <v>49</v>
       </c>
       <c r="V22" t="s">
-        <v>41</v>
+        <v>233</v>
       </c>
       <c r="W22" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="X22" t="s">
         <v>51</v>
@@ -3532,44 +3570,43 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="E23">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F23">
-        <v>8.130000000000015E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" s="1">
-        <v>1494.4630999999999</v>
+        <v>1021</v>
       </c>
       <c r="I23" s="2">
-        <f>($P$46/100)*H23</f>
-        <v>18.701711233400001</v>
+        <f t="shared" si="0"/>
+        <v>16.111380000000004</v>
       </c>
       <c r="J23">
-        <f>$S$46</f>
-        <v>2.0036999999999998</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L23">
-        <v>0.4</v>
+        <v>0.1461854238754417</v>
       </c>
       <c r="O23">
-        <f>SUM(F21:F29)-F23</f>
+        <f>SUM(F26:F34)-F28</f>
         <v>0.61260000000000003</v>
       </c>
       <c r="P23">
@@ -3584,10 +3621,10 @@
         <v>49</v>
       </c>
       <c r="V23" t="s">
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="W23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="X23" t="s">
         <v>51</v>
@@ -3602,50 +3639,49 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="E24">
         <v>2022</v>
       </c>
       <c r="F24">
-        <v>1.6E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24" s="1">
-        <v>1494.4630999999999</v>
+        <v>1022</v>
       </c>
       <c r="I24" s="2">
-        <f>($P$46/100)*H24</f>
-        <v>18.701711233400001</v>
+        <f t="shared" si="0"/>
+        <v>16.127160000000003</v>
       </c>
       <c r="J24">
-        <f>$S$46</f>
-        <v>2.0036999999999998</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L24">
-        <v>0.4</v>
+        <v>0.1461854238754417</v>
       </c>
       <c r="U24" t="s">
         <v>49</v>
       </c>
       <c r="V24" t="s">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="W24" t="s">
-        <v>221</v>
+        <v>58</v>
       </c>
       <c r="X24" t="s">
         <v>51</v>
@@ -3660,47 +3696,46 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="E25">
         <v>2022</v>
       </c>
       <c r="F25">
-        <v>3.27E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" s="1">
-        <v>1494.4630999999999</v>
+        <v>1023</v>
       </c>
       <c r="I25" s="2">
-        <f>($P$46/100)*H25</f>
-        <v>18.701711233400001</v>
+        <f t="shared" si="0"/>
+        <v>16.142940000000003</v>
       </c>
       <c r="J25">
-        <f>$S$46</f>
-        <v>2.0036999999999998</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L25">
-        <v>0.4</v>
+        <v>0.1461854238754417</v>
       </c>
       <c r="U25" t="s">
         <v>49</v>
       </c>
       <c r="V25" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="W25" t="s">
         <v>58</v>
@@ -3718,21 +3753,21 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>223</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E26">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F26">
-        <v>6.3399999999999998E-2</v>
+        <v>7.9699999999999993E-2</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3741,11 +3776,11 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I26" s="2">
-        <f>($P$46/100)*H26</f>
+        <f t="shared" ref="I26:I34" si="1">($P$46/100)*H26</f>
         <v>18.701711233400001</v>
       </c>
       <c r="J26">
-        <f>$S$46</f>
+        <f t="shared" ref="J26:J34" si="2">$S$46</f>
         <v>2.0036999999999998</v>
       </c>
       <c r="K26">
@@ -3758,10 +3793,10 @@
         <v>49</v>
       </c>
       <c r="V26" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="W26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="X26" t="s">
         <v>51</v>
@@ -3770,27 +3805,27 @@
         <v>52</v>
       </c>
       <c r="Z26" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AA26" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="C27" t="s">
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="E27">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F27">
-        <v>0.06</v>
+        <v>0.17519999999999999</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3799,11 +3834,11 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I27" s="2">
-        <f>($P$46/100)*H27</f>
+        <f t="shared" si="1"/>
         <v>18.701711233400001</v>
       </c>
       <c r="J27">
-        <f>$S$46</f>
+        <f t="shared" si="2"/>
         <v>2.0036999999999998</v>
       </c>
       <c r="K27">
@@ -3816,10 +3851,10 @@
         <v>49</v>
       </c>
       <c r="V27" t="s">
-        <v>223</v>
+        <v>41</v>
       </c>
       <c r="W27" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="X27" t="s">
         <v>51</v>
@@ -3834,21 +3869,21 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="C28" t="s">
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="E28">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F28">
-        <v>8.2000000000000003E-2</v>
+        <v>8.130000000000015E-2</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3857,11 +3892,11 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I28" s="2">
-        <f>($P$46/100)*H28</f>
+        <f t="shared" si="1"/>
         <v>18.701711233400001</v>
       </c>
       <c r="J28">
-        <f>$S$46</f>
+        <f t="shared" si="2"/>
         <v>2.0036999999999998</v>
       </c>
       <c r="K28">
@@ -3874,10 +3909,10 @@
         <v>49</v>
       </c>
       <c r="V28" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="W28" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="X28" t="s">
         <v>51</v>
@@ -3892,21 +3927,21 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C29" t="s">
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="E29">
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>0.1036</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3915,11 +3950,11 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I29" s="2">
-        <f>($P$46/100)*H29</f>
+        <f t="shared" si="1"/>
         <v>18.701711233400001</v>
       </c>
       <c r="J29">
-        <f>$S$46</f>
+        <f t="shared" si="2"/>
         <v>2.0036999999999998</v>
       </c>
       <c r="K29">
@@ -3932,10 +3967,10 @@
         <v>49</v>
       </c>
       <c r="V29" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="W29" t="s">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="X29" t="s">
         <v>51</v>
@@ -3950,45 +3985,47 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>227</v>
       </c>
       <c r="E30">
-        <v>1982</v>
+        <v>2022</v>
       </c>
       <c r="F30">
-        <v>1.7000000000000001E-2</v>
+        <v>3.27E-2</v>
       </c>
       <c r="G30">
-        <f>R41</f>
-        <v>0.56000000000000005</v>
+        <v>1</v>
       </c>
       <c r="H30" s="1">
-        <v>1175.5066999999999</v>
+        <v>1494.4630999999999</v>
       </c>
       <c r="I30" s="2">
-        <f>(P41/100)*H31</f>
-        <v>160.216352398</v>
+        <f t="shared" si="1"/>
+        <v>18.701711233400001</v>
       </c>
       <c r="J30">
-        <f>S41</f>
-        <v>5.8775000000000004</v>
+        <f t="shared" si="2"/>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K30">
-        <v>53</v>
+        <v>27</v>
+      </c>
+      <c r="L30">
+        <v>0.4</v>
       </c>
       <c r="U30" t="s">
         <v>49</v>
       </c>
       <c r="V30" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="W30" t="s">
         <v>58</v>
@@ -4006,48 +4043,50 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
       <c r="C31" t="s">
-        <v>169</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>219</v>
       </c>
       <c r="E31">
-        <v>1965</v>
+        <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.77</v>
+        <v>6.3399999999999998E-2</v>
       </c>
       <c r="G31">
-        <f>$R$40</f>
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="H31" s="1">
-        <v>4812.0244000000002</v>
+        <v>1494.4630999999999</v>
       </c>
       <c r="I31" s="2">
-        <f>(1.31/100)*H31</f>
-        <v>63.037519640000006</v>
+        <f t="shared" si="1"/>
+        <v>18.701711233400001</v>
       </c>
       <c r="J31">
-        <f>$S$40</f>
-        <v>4.1005000000000003</v>
+        <f t="shared" si="2"/>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K31">
-        <v>70</v>
+        <v>27</v>
+      </c>
+      <c r="L31">
+        <v>0.4</v>
       </c>
       <c r="U31" t="s">
         <v>49</v>
       </c>
       <c r="V31" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="W31" t="s">
-        <v>141</v>
+        <v>58</v>
       </c>
       <c r="X31" t="s">
         <v>51</v>
@@ -4062,48 +4101,50 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>171</v>
+        <v>224</v>
       </c>
       <c r="C32" t="s">
-        <v>169</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="E32">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="G32">
-        <f>$R$40</f>
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="H32" s="1">
-        <v>4812.0244000000002</v>
+        <v>1494.4630999999999</v>
       </c>
       <c r="I32" s="2">
-        <f>(1.31/100)*H32</f>
-        <v>63.037519640000006</v>
+        <f t="shared" si="1"/>
+        <v>18.701711233400001</v>
       </c>
       <c r="J32">
-        <f>$S$40</f>
-        <v>4.1005000000000003</v>
+        <f t="shared" si="2"/>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K32">
-        <v>40</v>
+        <v>27</v>
+      </c>
+      <c r="L32">
+        <v>0.4</v>
       </c>
       <c r="U32" t="s">
         <v>49</v>
       </c>
       <c r="V32" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="W32" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="X32" t="s">
         <v>51</v>
@@ -4118,48 +4159,50 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>172</v>
+        <v>225</v>
       </c>
       <c r="C33" t="s">
-        <v>169</v>
+        <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
       <c r="E33">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F33">
-        <f>0.01</f>
-        <v>0.01</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="G33">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="H33" s="1">
-        <v>4812.0244000000002</v>
+        <v>1494.4630999999999</v>
       </c>
       <c r="I33" s="2">
-        <f>(1.31/100)*H33</f>
-        <v>63.037519640000006</v>
+        <f t="shared" si="1"/>
+        <v>18.701711233400001</v>
       </c>
       <c r="J33">
-        <f>$S$40</f>
-        <v>4.1005000000000003</v>
+        <f t="shared" si="2"/>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K33">
-        <v>40</v>
+        <v>27</v>
+      </c>
+      <c r="L33">
+        <v>0.4</v>
       </c>
       <c r="U33" t="s">
         <v>49</v>
       </c>
       <c r="V33" t="s">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="W33" t="s">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="X33" t="s">
         <v>51</v>
@@ -4174,48 +4217,50 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="C34" t="s">
-        <v>169</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>218</v>
       </c>
       <c r="E34">
-        <v>1956</v>
+        <v>2022</v>
       </c>
       <c r="F34">
-        <v>0.185</v>
+        <v>0.1036</v>
       </c>
       <c r="G34">
-        <f>$R$40</f>
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1">
-        <v>4812.0244000000002</v>
+        <v>1494.4630999999999</v>
       </c>
       <c r="I34" s="2">
-        <f>(1.31/100)*H34</f>
-        <v>63.037519640000006</v>
+        <f t="shared" si="1"/>
+        <v>18.701711233400001</v>
       </c>
       <c r="J34">
-        <f>$S$40</f>
-        <v>4.1005000000000003</v>
+        <f t="shared" si="2"/>
+        <v>2.0036999999999998</v>
       </c>
       <c r="K34">
-        <v>73</v>
+        <v>27</v>
+      </c>
+      <c r="L34">
+        <v>0.4</v>
       </c>
       <c r="U34" t="s">
         <v>49</v>
       </c>
       <c r="V34" t="s">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="W34" t="s">
-        <v>128</v>
+        <v>58</v>
       </c>
       <c r="X34" t="s">
         <v>51</v>
@@ -4230,472 +4275,471 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
       </c>
       <c r="E35">
-        <v>2021</v>
+        <v>1982</v>
       </c>
       <c r="F35">
-        <v>7.6999999999999999E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G35">
         <f>R41</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="H35" s="1">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="I35" s="2">
+        <f>(P41/100)*H36</f>
+        <v>160.216352398</v>
+      </c>
+      <c r="J35">
+        <f>S41</f>
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="K35">
+        <v>53</v>
+      </c>
+      <c r="U35" t="s">
+        <v>49</v>
+      </c>
+      <c r="V35" t="s">
+        <v>229</v>
+      </c>
+      <c r="W35" t="s">
+        <v>58</v>
+      </c>
+      <c r="X35" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>173</v>
+      </c>
+      <c r="C36" t="s">
+        <v>169</v>
+      </c>
+      <c r="D36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36">
+        <v>1965</v>
+      </c>
+      <c r="F36">
+        <v>0.77</v>
+      </c>
+      <c r="G36">
+        <f>$R$40</f>
+        <v>0.33</v>
+      </c>
+      <c r="H36" s="1">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I36" s="2">
+        <f>(1.31/100)*H36</f>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J36">
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="K36">
+        <v>70</v>
+      </c>
+      <c r="U36" t="s">
+        <v>49</v>
+      </c>
+      <c r="V36" t="s">
+        <v>171</v>
+      </c>
+      <c r="W36" t="s">
+        <v>141</v>
+      </c>
+      <c r="X36" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" t="s">
+        <v>169</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37">
+        <v>2015</v>
+      </c>
+      <c r="F37">
+        <v>0.26</v>
+      </c>
+      <c r="G37">
+        <f>$R$40</f>
+        <v>0.33</v>
+      </c>
+      <c r="H37" s="1">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I37" s="2">
+        <f>(1.31/100)*H37</f>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J37">
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="K37">
+        <v>40</v>
+      </c>
+      <c r="U37" t="s">
+        <v>49</v>
+      </c>
+      <c r="V37" t="s">
+        <v>170</v>
+      </c>
+      <c r="W37" t="s">
+        <v>126</v>
+      </c>
+      <c r="X37" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38">
+        <v>2025</v>
+      </c>
+      <c r="F38">
+        <f>0.01</f>
+        <v>0.01</v>
+      </c>
+      <c r="G38">
+        <v>0.33</v>
+      </c>
+      <c r="H38" s="1">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I38" s="2">
+        <f>(1.31/100)*H38</f>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J38">
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="K38">
+        <v>40</v>
+      </c>
+      <c r="U38" t="s">
+        <v>49</v>
+      </c>
+      <c r="V38" t="s">
+        <v>172</v>
+      </c>
+      <c r="W38" t="s">
+        <v>127</v>
+      </c>
+      <c r="X38" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>170</v>
+      </c>
+      <c r="C39" t="s">
+        <v>169</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39">
+        <v>1956</v>
+      </c>
+      <c r="F39">
+        <v>0.185</v>
+      </c>
+      <c r="G39">
+        <f>$R$40</f>
+        <v>0.33</v>
+      </c>
+      <c r="H39" s="1">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="I39" s="2">
+        <f>(1.31/100)*H39</f>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J39">
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="K39">
+        <v>73</v>
+      </c>
+      <c r="P39" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>190</v>
+      </c>
+      <c r="R39" t="s">
+        <v>191</v>
+      </c>
+      <c r="S39" t="s">
+        <v>192</v>
+      </c>
+      <c r="U39" t="s">
+        <v>49</v>
+      </c>
+      <c r="V39" t="s">
+        <v>173</v>
+      </c>
+      <c r="W39" t="s">
+        <v>128</v>
+      </c>
+      <c r="X39" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40">
+        <v>2021</v>
+      </c>
+      <c r="F40">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="G40">
+        <f>R41</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H40" s="1">
         <f>Q41</f>
         <v>1175.5066999999999</v>
       </c>
-      <c r="I35" s="2">
-        <f>(P41/100)*H35</f>
+      <c r="I40" s="2">
+        <f>(P41/100)*H40</f>
         <v>39.138495576499992</v>
       </c>
-      <c r="J35">
+      <c r="J40">
         <f>$S$41</f>
         <v>5.8775000000000004</v>
       </c>
-      <c r="K35">
+      <c r="K40">
         <v>40</v>
       </c>
-      <c r="U35" t="s">
-        <v>49</v>
-      </c>
-      <c r="V35" t="s">
+      <c r="O40" t="s">
+        <v>169</v>
+      </c>
+      <c r="P40" s="3">
+        <v>1.31</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="R40">
+        <v>0.33</v>
+      </c>
+      <c r="S40">
+        <v>4.1005000000000003</v>
+      </c>
+      <c r="U40" t="s">
+        <v>49</v>
+      </c>
+      <c r="V40" t="s">
         <v>120</v>
       </c>
-      <c r="W35" t="s">
+      <c r="W40" t="s">
         <v>139</v>
       </c>
-      <c r="X35" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA35" t="s">
+      <c r="X40" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA40" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>121</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C41" t="s">
         <v>13</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D41" t="s">
         <v>14</v>
       </c>
-      <c r="E36">
+      <c r="E41">
         <v>2018</v>
       </c>
-      <c r="F36">
+      <c r="F41">
         <v>3.9E-2</v>
       </c>
-      <c r="G36">
+      <c r="G41">
         <f>R43</f>
         <v>0.46800000000000003</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H41" s="1">
         <f>$Q$43</f>
         <v>2950.7891</v>
       </c>
-      <c r="I36" s="2">
-        <f>(4.5269/100)*H36</f>
+      <c r="I41" s="2">
+        <f>(4.5269/100)*H41</f>
         <v>133.5792717679</v>
       </c>
-      <c r="J36">
+      <c r="J41">
         <f>$S$43</f>
         <v>2.8138000000000001</v>
       </c>
-      <c r="K36">
+      <c r="K41">
         <v>40</v>
       </c>
-      <c r="U36" t="s">
-        <v>49</v>
-      </c>
-      <c r="V36" t="s">
+      <c r="O41" t="s">
+        <v>188</v>
+      </c>
+      <c r="P41" s="3">
+        <v>3.3294999999999999</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="R41">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="S41">
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="U41" t="s">
+        <v>49</v>
+      </c>
+      <c r="V41" t="s">
         <v>121</v>
       </c>
-      <c r="W36" t="s">
+      <c r="W41" t="s">
         <v>129</v>
       </c>
-      <c r="X36" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA36" t="s">
+      <c r="X41" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA41" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B37" t="s">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>122</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C42" t="s">
         <v>13</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D42" t="s">
         <v>14</v>
       </c>
-      <c r="E37">
+      <c r="E42">
         <v>2009</v>
       </c>
-      <c r="F37">
+      <c r="F42">
         <v>2.2100000000000002E-2</v>
       </c>
-      <c r="G37">
+      <c r="G42">
         <v>0.46800000000000003</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H42" s="1">
         <f>$Q$43</f>
         <v>2950.7891</v>
       </c>
-      <c r="I37" s="2">
-        <f t="shared" ref="I37:I39" si="0">(4.5269/100)*H37</f>
+      <c r="I42" s="2">
+        <f t="shared" ref="I42:I44" si="3">(4.5269/100)*H42</f>
         <v>133.5792717679</v>
       </c>
-      <c r="J37">
+      <c r="J42">
         <f>$S$43</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K37">
-        <v>40</v>
-      </c>
-      <c r="U37" t="s">
-        <v>49</v>
-      </c>
-      <c r="V37" t="s">
-        <v>122</v>
-      </c>
-      <c r="W37" t="s">
-        <v>130</v>
-      </c>
-      <c r="X37" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B38" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38">
-        <v>2011</v>
-      </c>
-      <c r="F38">
-        <v>2.0500000000000001E-2</v>
-      </c>
-      <c r="G38">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="H38" s="1">
-        <f>$Q$43</f>
-        <v>2950.7891</v>
-      </c>
-      <c r="I38" s="2">
-        <f t="shared" si="0"/>
-        <v>133.5792717679</v>
-      </c>
-      <c r="J38">
-        <f>$S$43</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K38">
-        <v>40</v>
-      </c>
-      <c r="U38" t="s">
-        <v>49</v>
-      </c>
-      <c r="V38" t="s">
-        <v>123</v>
-      </c>
-      <c r="W38" t="s">
-        <v>131</v>
-      </c>
-      <c r="X38" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B39" t="s">
-        <v>124</v>
-      </c>
-      <c r="C39" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39">
-        <v>2010</v>
-      </c>
-      <c r="F39">
-        <v>1.3900000000000001E-2</v>
-      </c>
-      <c r="G39">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="H39" s="1">
-        <f>$Q$43</f>
-        <v>2950.7891</v>
-      </c>
-      <c r="I39" s="2">
-        <f t="shared" si="0"/>
-        <v>133.5792717679</v>
-      </c>
-      <c r="J39">
-        <f>$S$43</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K39">
-        <v>40</v>
-      </c>
-      <c r="P39" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>190</v>
-      </c>
-      <c r="R39" t="s">
-        <v>191</v>
-      </c>
-      <c r="S39" t="s">
-        <v>192</v>
-      </c>
-      <c r="U39" t="s">
-        <v>49</v>
-      </c>
-      <c r="V39" t="s">
-        <v>124</v>
-      </c>
-      <c r="W39" t="s">
-        <v>125</v>
-      </c>
-      <c r="X39" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B40" t="s">
-        <v>174</v>
-      </c>
-      <c r="C40" t="s">
-        <v>169</v>
-      </c>
-      <c r="D40" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40">
-        <v>1997</v>
-      </c>
-      <c r="F40">
-        <v>0.01</v>
-      </c>
-      <c r="G40">
-        <f>R40</f>
-        <v>0.33</v>
-      </c>
-      <c r="H40" s="1">
-        <f>Q40</f>
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="I40" s="2">
-        <f>($P$40/100)*H40</f>
-        <v>63.037519640000006</v>
-      </c>
-      <c r="J40">
-        <f>$S$40</f>
-        <v>4.1005000000000003</v>
-      </c>
-      <c r="K40">
-        <v>40</v>
-      </c>
-      <c r="O40" t="s">
-        <v>169</v>
-      </c>
-      <c r="P40" s="3">
-        <v>1.31</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="R40">
-        <v>0.33</v>
-      </c>
-      <c r="S40">
-        <v>4.1005000000000003</v>
-      </c>
-      <c r="U40" t="s">
-        <v>49</v>
-      </c>
-      <c r="V40" t="s">
-        <v>174</v>
-      </c>
-      <c r="W40" t="s">
-        <v>140</v>
-      </c>
-      <c r="X40" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B41" t="s">
-        <v>132</v>
-      </c>
-      <c r="C41" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41">
-        <v>2016</v>
-      </c>
-      <c r="F41">
-        <v>0.01</v>
-      </c>
-      <c r="G41">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H41" s="1">
-        <f>$Q$44</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I41" s="2">
-        <f>($P$44/100)*H41</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J41">
-        <f>$S$44</f>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K41">
-        <v>40</v>
-      </c>
-      <c r="O41" t="s">
-        <v>188</v>
-      </c>
-      <c r="P41" s="3">
-        <v>3.3294999999999999</v>
-      </c>
-      <c r="Q41" s="1">
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="R41">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="S41">
-        <v>5.8775000000000004</v>
-      </c>
-      <c r="U41" t="s">
-        <v>49</v>
-      </c>
-      <c r="V41" t="s">
-        <v>132</v>
-      </c>
-      <c r="W41" t="s">
-        <v>133</v>
-      </c>
-      <c r="X41" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B42" t="s">
-        <v>134</v>
-      </c>
-      <c r="C42" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42">
-        <v>2017</v>
-      </c>
-      <c r="F42">
-        <v>0.01</v>
-      </c>
-      <c r="G42">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H42" s="1">
-        <f>$Q$44</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I42" s="2">
-        <f>($P$44/100)*H42</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J42">
-        <f>$S$44</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K42">
@@ -4710,10 +4754,10 @@
         <v>49</v>
       </c>
       <c r="V42" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="W42" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="X42" t="s">
         <v>51</v>
@@ -4728,9 +4772,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -4739,24 +4783,24 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="F43">
-        <v>9.300000000000001E-3</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="G43">
-        <v>0.28999999999999998</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H43" s="1">
-        <f>$Q$44</f>
-        <v>4516.7133000000003</v>
+        <f>$Q$43</f>
+        <v>2950.7891</v>
       </c>
       <c r="I43" s="2">
-        <f>($P$44/100)*H43</f>
-        <v>162.96753257730003</v>
+        <f t="shared" si="3"/>
+        <v>133.5792717679</v>
       </c>
       <c r="J43">
-        <f>$S$44</f>
+        <f>$S$43</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K43">
@@ -4781,10 +4825,10 @@
         <v>49</v>
       </c>
       <c r="V43" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="W43" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="X43" t="s">
         <v>51</v>
@@ -4799,9 +4843,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -4810,28 +4854,28 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>1963</v>
+        <v>2010</v>
       </c>
       <c r="F44">
-        <v>7.0999999999999995E-3</v>
+        <v>1.3900000000000001E-2</v>
       </c>
       <c r="G44">
-        <v>0.28999999999999998</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H44" s="1">
-        <f>$Q$44</f>
-        <v>4516.7133000000003</v>
+        <f>$Q$43</f>
+        <v>2950.7891</v>
       </c>
       <c r="I44" s="2">
-        <f>($P$44/100)*H44</f>
-        <v>162.96753257730003</v>
+        <f t="shared" si="3"/>
+        <v>133.5792717679</v>
       </c>
       <c r="J44">
-        <f>$S$44</f>
+        <f>$S$43</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K44">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="O44" t="s">
         <v>187</v>
@@ -4852,10 +4896,10 @@
         <v>49</v>
       </c>
       <c r="V44" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="W44" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="X44" t="s">
         <v>51</v>
@@ -4870,37 +4914,37 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
       <c r="D45" t="s">
         <v>14</v>
       </c>
       <c r="E45">
-        <v>2020</v>
+        <v>1997</v>
       </c>
       <c r="F45">
-        <v>5.7999999999999996E-3</v>
+        <v>0.01</v>
       </c>
       <c r="G45">
-        <f>R41</f>
-        <v>0.56000000000000005</v>
+        <f>R40</f>
+        <v>0.33</v>
       </c>
       <c r="H45" s="1">
-        <f>Q41</f>
-        <v>1175.5066999999999</v>
+        <f>Q40</f>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I45" s="2">
-        <f>($P$41/100)*H45</f>
-        <v>39.138495576499992</v>
+        <f>($P$40/100)*H45</f>
+        <v>63.037519640000006</v>
       </c>
       <c r="J45">
-        <f>$S$41</f>
-        <v>5.8775000000000004</v>
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K45">
         <v>40</v>
@@ -4916,10 +4960,10 @@
         <v>49</v>
       </c>
       <c r="V45" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="W45" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="X45" t="s">
         <v>51</v>
@@ -4934,9 +4978,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
@@ -4945,16 +4989,16 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="F46">
-        <v>6.4999999999999997E-3</v>
+        <v>0.01</v>
       </c>
       <c r="G46">
         <v>0.28999999999999998</v>
       </c>
       <c r="H46" s="1">
-        <f>Q44</f>
+        <f>$Q$44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I46" s="2">
@@ -4982,10 +5026,10 @@
         <v>49</v>
       </c>
       <c r="V46" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="W46" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="X46" t="s">
         <v>51</v>
@@ -5000,37 +5044,36 @@
         <v>54</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
         <v>14</v>
       </c>
       <c r="E47">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="F47">
-        <v>4.0999999999999995E-3</v>
+        <v>0.01</v>
       </c>
       <c r="G47">
-        <f>R41</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H47" s="1">
-        <f>Q41</f>
-        <v>1175.5066999999999</v>
+        <f>$Q$44</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I47" s="2">
-        <f>($P$41/100)*H47</f>
-        <v>39.138495576499992</v>
+        <f>($P$44/100)*H47</f>
+        <v>162.96753257730003</v>
       </c>
       <c r="J47">
-        <f>$S$41</f>
-        <v>5.8775000000000004</v>
+        <f>$S$44</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K47">
         <v>40</v>
@@ -5041,10 +5084,10 @@
         <v>49</v>
       </c>
       <c r="V47" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="W47" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="X47" t="s">
         <v>51</v>
@@ -5059,37 +5102,36 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="C48" t="s">
-        <v>169</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
         <v>14</v>
       </c>
       <c r="E48">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="F48">
-        <v>1.4E-3</v>
+        <v>9.300000000000001E-3</v>
       </c>
       <c r="G48">
-        <f>R40</f>
-        <v>0.33</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H48" s="1">
-        <f>Q40</f>
-        <v>4812.0244000000002</v>
+        <f>$Q$44</f>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I48" s="2">
         <f>($P$44/100)*H48</f>
-        <v>173.62265237640003</v>
+        <v>162.96753257730003</v>
       </c>
       <c r="J48">
-        <f>$S$40</f>
-        <v>4.1005000000000003</v>
+        <f>$S$44</f>
+        <v>2.8138000000000001</v>
       </c>
       <c r="K48">
         <v>40</v>
@@ -5100,10 +5142,10 @@
         <v>49</v>
       </c>
       <c r="V48" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="W48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="X48" t="s">
         <v>51</v>
@@ -5118,9 +5160,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
@@ -5129,16 +5171,16 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>2013</v>
+        <v>1963</v>
       </c>
       <c r="F49">
-        <v>1.8E-3</v>
+        <v>7.0999999999999995E-3</v>
       </c>
       <c r="G49">
         <v>0.28999999999999998</v>
       </c>
       <c r="H49" s="1">
-        <f>Q44</f>
+        <f>$Q$44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I49" s="2">
@@ -5150,16 +5192,16 @@
         <v>2.8138000000000001</v>
       </c>
       <c r="K49">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="U49" t="s">
         <v>49</v>
       </c>
       <c r="V49" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="W49" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="X49" t="s">
         <v>51</v>
@@ -5174,94 +5216,94 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D50" t="s">
         <v>14</v>
       </c>
       <c r="E50">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="F50">
-        <v>1.6999999999999999E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="G50">
+        <f>R41</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H50" s="1">
+        <f>Q41</f>
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="I50" s="2">
+        <f>($P$41/100)*H50</f>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J50">
+        <f>$S$41</f>
+        <v>5.8775000000000004</v>
+      </c>
+      <c r="K50">
+        <v>40</v>
+      </c>
+      <c r="U50" t="s">
+        <v>49</v>
+      </c>
+      <c r="V50" t="s">
+        <v>147</v>
+      </c>
+      <c r="W50" t="s">
+        <v>138</v>
+      </c>
+      <c r="X50" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>142</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51">
+        <v>2013</v>
+      </c>
+      <c r="F51">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="G51">
         <v>0.28999999999999998</v>
       </c>
-      <c r="H50" s="1">
+      <c r="H51" s="1">
         <f>Q44</f>
         <v>4516.7133000000003</v>
       </c>
-      <c r="I50" s="2">
-        <f>($P$44/100)*H50</f>
+      <c r="I51" s="2">
+        <f>($P$44/100)*H51</f>
         <v>162.96753257730003</v>
       </c>
-      <c r="J50">
+      <c r="J51">
         <f>$S$44</f>
         <v>2.8138000000000001</v>
       </c>
-      <c r="K50">
-        <v>40</v>
-      </c>
-      <c r="U50" t="s">
-        <v>49</v>
-      </c>
-      <c r="V50" t="s">
-        <v>152</v>
-      </c>
-      <c r="W50" t="s">
-        <v>153</v>
-      </c>
-      <c r="X50" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B51" t="s">
-        <v>154</v>
-      </c>
-      <c r="C51" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51">
-        <v>2009</v>
-      </c>
-      <c r="F51">
-        <v>1.8E-3</v>
-      </c>
-      <c r="G51">
-        <f>R41</f>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H51" s="1">
-        <f>Q41</f>
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="I51" s="2">
-        <f>($P$41/100)*H51</f>
-        <v>39.138495576499992</v>
-      </c>
-      <c r="J51">
-        <f>$S$41</f>
-        <v>5.8775000000000004</v>
-      </c>
       <c r="K51">
         <v>40</v>
       </c>
@@ -5269,10 +5311,10 @@
         <v>49</v>
       </c>
       <c r="V51" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="W51" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="X51" t="s">
         <v>51</v>
@@ -5287,9 +5329,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C52" t="s">
         <v>16</v>
@@ -5301,7 +5343,7 @@
         <v>2015</v>
       </c>
       <c r="F52">
-        <v>1.8E-3</v>
+        <v>4.0999999999999995E-3</v>
       </c>
       <c r="G52">
         <f>R41</f>
@@ -5326,10 +5368,10 @@
         <v>49</v>
       </c>
       <c r="V52" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="W52" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="X52" t="s">
         <v>51</v>
@@ -5344,36 +5386,37 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="D53" t="s">
         <v>14</v>
       </c>
       <c r="E53">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="F53">
-        <v>1.5E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G53">
-        <v>0.28999999999999998</v>
+        <f>R40</f>
+        <v>0.33</v>
       </c>
       <c r="H53" s="1">
-        <f>Q44</f>
-        <v>4516.7133000000003</v>
+        <f>Q40</f>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I53" s="2">
         <f>($P$44/100)*H53</f>
-        <v>162.96753257730003</v>
+        <v>173.62265237640003</v>
       </c>
       <c r="J53">
-        <f>$S$44</f>
-        <v>2.8138000000000001</v>
+        <f>$S$40</f>
+        <v>4.1005000000000003</v>
       </c>
       <c r="K53">
         <v>40</v>
@@ -5382,10 +5425,10 @@
         <v>49</v>
       </c>
       <c r="V53" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="W53" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="X53" t="s">
         <v>51</v>
@@ -5400,9 +5443,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
@@ -5414,13 +5457,13 @@
         <v>2013</v>
       </c>
       <c r="F54">
-        <v>1.4E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G54">
         <v>0.28999999999999998</v>
       </c>
       <c r="H54" s="1">
-        <f>$Q$44</f>
+        <f>Q44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I54" s="2">
@@ -5438,10 +5481,10 @@
         <v>49</v>
       </c>
       <c r="V54" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="W54" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="X54" t="s">
         <v>51</v>
@@ -5456,9 +5499,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
@@ -5467,16 +5510,16 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F55">
-        <v>1.1999999999999999E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="G55">
         <v>0.28999999999999998</v>
       </c>
       <c r="H55" s="1">
-        <f>$Q$44</f>
+        <f>Q44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I55" s="2">
@@ -5494,10 +5537,10 @@
         <v>49</v>
       </c>
       <c r="V55" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="W55" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="X55" t="s">
         <v>51</v>
@@ -5512,12 +5555,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D56" t="s">
         <v>14</v>
@@ -5526,22 +5569,23 @@
         <v>2009</v>
       </c>
       <c r="F56">
-        <v>1.9E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G56">
-        <v>0.28999999999999998</v>
+        <f>R41</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H56" s="1">
-        <f>Q44</f>
-        <v>4516.7133000000003</v>
+        <f>Q41</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I56" s="2">
-        <f>($P$44/100)*H56</f>
-        <v>162.96753257730003</v>
+        <f>($P$41/100)*H56</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J56">
-        <f>$S$44</f>
-        <v>2.8138000000000001</v>
+        <f>$S$41</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K56">
         <v>40</v>
@@ -5550,10 +5594,10 @@
         <v>49</v>
       </c>
       <c r="V56" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="W56" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="X56" t="s">
         <v>51</v>
@@ -5568,36 +5612,37 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D57" t="s">
         <v>14</v>
       </c>
       <c r="E57">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="F57">
-        <v>8.9999999999999998E-4</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G57">
-        <v>0.28999999999999998</v>
+        <f>R41</f>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H57" s="1">
-        <f>Q44</f>
-        <v>4516.7133000000003</v>
+        <f>Q41</f>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I57" s="2">
-        <f>($P$44/100)*H57</f>
-        <v>162.96753257730003</v>
+        <f>($P$41/100)*H57</f>
+        <v>39.138495576499992</v>
       </c>
       <c r="J57">
-        <f>$S$44</f>
-        <v>2.8138000000000001</v>
+        <f>$S$41</f>
+        <v>5.8775000000000004</v>
       </c>
       <c r="K57">
         <v>40</v>
@@ -5606,10 +5651,10 @@
         <v>49</v>
       </c>
       <c r="V57" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="W57" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="X57" t="s">
         <v>51</v>
@@ -5624,9 +5669,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C58" t="s">
         <v>13</v>
@@ -5635,10 +5680,10 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F58">
-        <v>5.0000000000000001E-4</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G58">
         <v>0.28999999999999998</v>
@@ -5648,11 +5693,11 @@
         <v>4516.7133000000003</v>
       </c>
       <c r="I58" s="2">
-        <f>($P$44/100)*H58</f>
+        <f t="shared" ref="I58:I63" si="4">($P$44/100)*H58</f>
         <v>162.96753257730003</v>
       </c>
       <c r="J58">
-        <f>$S$44</f>
+        <f t="shared" ref="J58:J63" si="5">$S$44</f>
         <v>2.8138000000000001</v>
       </c>
       <c r="K58">
@@ -5662,10 +5707,10 @@
         <v>49</v>
       </c>
       <c r="V58" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="W58" t="s">
-        <v>197</v>
+        <v>159</v>
       </c>
       <c r="X58" t="s">
         <v>51</v>
@@ -5680,53 +5725,333 @@
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
         <v>14</v>
       </c>
       <c r="E59">
+        <v>2013</v>
+      </c>
+      <c r="F59">
+        <v>1.4E-3</v>
+      </c>
+      <c r="G59">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H59" s="1">
+        <f>$Q$44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I59" s="2">
+        <f t="shared" si="4"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="5"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K59">
+        <v>40</v>
+      </c>
+      <c r="U59" t="s">
+        <v>49</v>
+      </c>
+      <c r="V59" t="s">
+        <v>160</v>
+      </c>
+      <c r="W59" t="s">
+        <v>161</v>
+      </c>
+      <c r="X59" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>162</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60">
+        <v>2016</v>
+      </c>
+      <c r="F60">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="G60">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H60" s="1">
+        <f>$Q$44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I60" s="2">
+        <f t="shared" si="4"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="5"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K60">
+        <v>40</v>
+      </c>
+      <c r="U60" t="s">
+        <v>49</v>
+      </c>
+      <c r="V60" t="s">
+        <v>162</v>
+      </c>
+      <c r="W60" t="s">
+        <v>163</v>
+      </c>
+      <c r="X60" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>164</v>
+      </c>
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61">
+        <v>2009</v>
+      </c>
+      <c r="F61">
+        <v>1.9E-3</v>
+      </c>
+      <c r="G61">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H61" s="1">
+        <f>Q44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I61" s="2">
+        <f t="shared" si="4"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="5"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K61">
+        <v>40</v>
+      </c>
+      <c r="U61" t="s">
+        <v>49</v>
+      </c>
+      <c r="V61" t="s">
+        <v>164</v>
+      </c>
+      <c r="W61" t="s">
+        <v>166</v>
+      </c>
+      <c r="X61" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="62" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>165</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62">
+        <v>2012</v>
+      </c>
+      <c r="F62">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="G62">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H62" s="1">
+        <f>Q44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I62" s="2">
+        <f t="shared" si="4"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="5"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K62">
+        <v>40</v>
+      </c>
+      <c r="U62" t="s">
+        <v>49</v>
+      </c>
+      <c r="V62" t="s">
+        <v>165</v>
+      </c>
+      <c r="W62" t="s">
+        <v>167</v>
+      </c>
+      <c r="X62" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="63" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>168</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63">
+        <v>2015</v>
+      </c>
+      <c r="F63">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="G63">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H63" s="1">
+        <f>Q44</f>
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="I63" s="2">
+        <f t="shared" si="4"/>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="5"/>
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K63">
+        <v>40</v>
+      </c>
+      <c r="U63" t="s">
+        <v>49</v>
+      </c>
+      <c r="V63" t="s">
+        <v>168</v>
+      </c>
+      <c r="W63" t="s">
+        <v>197</v>
+      </c>
+      <c r="X63" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="64" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64">
         <v>2022</v>
       </c>
-      <c r="F59">
+      <c r="F64">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G59">
+      <c r="G64">
         <v>0.33123000000000002</v>
       </c>
-      <c r="U59" t="s">
-        <v>49</v>
-      </c>
-      <c r="V59" t="s">
+      <c r="U64" t="s">
+        <v>49</v>
+      </c>
+      <c r="V64" t="s">
         <v>18</v>
       </c>
-      <c r="W59" t="s">
+      <c r="W64" t="s">
         <v>58</v>
       </c>
-      <c r="X59" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z59" t="s">
+      <c r="X64" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z64" t="s">
         <v>53</v>
       </c>
-      <c r="AA59" t="s">
+      <c r="AA64" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:27" x14ac:dyDescent="0.25">
       <c r="V72" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U73" t="s">
         <v>49</v>
       </c>
@@ -5749,7 +6074,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U74" t="s">
         <v>49</v>
       </c>
@@ -5772,7 +6097,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>20</v>
       </c>
@@ -5825,7 +6150,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>15</v>
       </c>
@@ -5866,7 +6191,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U77" t="s">
         <v>49</v>
       </c>
@@ -5889,7 +6214,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="78" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>12</v>
       </c>
@@ -5942,7 +6267,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U79" t="s">
         <v>49</v>
       </c>
@@ -5965,7 +6290,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U80" t="s">
         <v>49</v>
       </c>
@@ -5988,7 +6313,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="81" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U81" t="s">
         <v>49</v>
       </c>
@@ -6011,7 +6336,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:27" x14ac:dyDescent="0.25">
       <c r="U82" t="s">
         <v>49</v>
       </c>
@@ -6034,7 +6359,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="83" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>24</v>
       </c>
@@ -6057,7 +6382,7 @@
         <v>0.42012333946150526</v>
       </c>
     </row>
-    <row r="84" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>27</v>
       </c>
@@ -6101,7 +6426,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="85" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>29</v>
       </c>
@@ -6124,7 +6449,7 @@
         <v>0.42012333946150526</v>
       </c>
     </row>
-    <row r="86" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>31</v>
       </c>
@@ -6159,7 +6484,7 @@
         <v>0.47763777043344691</v>
       </c>
     </row>
-    <row r="87" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>33</v>
       </c>
@@ -6197,7 +6522,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="88" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>33</v>
       </c>
@@ -6232,7 +6557,7 @@
         <v>0.47814004703314084</v>
       </c>
     </row>
-    <row r="89" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>33</v>
       </c>
@@ -6267,7 +6592,7 @@
         <v>0.47814004703314078</v>
       </c>
     </row>
-    <row r="90" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>35</v>
       </c>
@@ -6302,7 +6627,7 @@
         <v>0.40144059976798208</v>
       </c>
     </row>
-    <row r="91" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>35</v>
       </c>
@@ -6337,7 +6662,7 @@
         <v>0.40144059976798202</v>
       </c>
     </row>
-    <row r="92" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>35</v>
       </c>
@@ -6372,7 +6697,7 @@
         <v>0.40144059976798202</v>
       </c>
     </row>
-    <row r="93" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>35</v>
       </c>
@@ -6407,7 +6732,7 @@
         <v>0.40144059976798208</v>
       </c>
     </row>
-    <row r="94" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>35</v>
       </c>
@@ -6442,7 +6767,7 @@
         <v>0.40144059976798202</v>
       </c>
     </row>
-    <row r="95" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>37</v>
       </c>
@@ -6477,7 +6802,7 @@
         <v>0.365520596150406</v>
       </c>
     </row>
-    <row r="96" spans="2:27" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>39</v>
       </c>
@@ -6512,7 +6837,7 @@
         <v>0.41047488326249421</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>39</v>
       </c>
@@ -6547,7 +6872,7 @@
         <v>0.41047488326249421</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>39</v>
       </c>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1855B0-460A-4373-9E67-01E028CE5590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB00F012-F8E8-4350-9E8E-BDEDE3397709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10470" yWindow="10890" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
-    <sheet name="new_options" sheetId="3" r:id="rId2"/>
+    <sheet name="new_options" sheetId="3" state="hidden" r:id="rId2"/>
     <sheet name="existing_stock" sheetId="2" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="Start">[1]SETUP!$F$2</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -71,13 +77,11 @@
     <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
     <author>tc={5D0B02A9-24B3-4F36-8683-2AD26D1E0821}</author>
     <author>tc={C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}</author>
+    <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
     <author>tc={C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}</author>
-    <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
-    <author>tc={3057E3B1-7BF3-4718-B31B-0585028D4313}</author>
-    <author>tc={1905391B-2A5F-4643-B2AC-720AD8410CDA}</author>
   </authors>
   <commentList>
-    <comment ref="Z26" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+    <comment ref="Z24" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +89,7 @@
     Miks daynite (hydro samuti)</t>
       </text>
     </comment>
-    <comment ref="F35" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+    <comment ref="F33" authorId="1" shapeId="0" xr:uid="{E45DD652-654C-4828-8A13-679EDDC53E65}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -93,7 +97,7 @@
     Iru produces only 17 MW in 2025 not 0.207 GW</t>
       </text>
     </comment>
-    <comment ref="B36" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+    <comment ref="B34" authorId="2" shapeId="0" xr:uid="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -110,15 +114,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="S43" authorId="4" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Took same as chp</t>
-      </text>
-    </comment>
-    <comment ref="E44" authorId="5" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
+    <comment ref="E42" authorId="4" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -127,20 +123,12 @@
 </t>
       </text>
     </comment>
-    <comment ref="J78" authorId="6" shapeId="0" xr:uid="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
+    <comment ref="S43" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    From 9,24 to 6</t>
-      </text>
-    </comment>
-    <comment ref="U81" authorId="7" shapeId="0" xr:uid="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Frequency reserve</t>
+    Took same as chp</t>
       </text>
     </comment>
   </commentList>
@@ -148,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="234">
   <si>
     <t>~fi_t</t>
   </si>
@@ -186,9 +174,6 @@
     <t>ncap_af~fx</t>
   </si>
   <si>
-    <t>ep_bioenergy__ember</t>
-  </si>
-  <si>
     <t>bioenergy</t>
   </si>
   <si>
@@ -222,63 +207,12 @@
     <t>elc_spv_004</t>
   </si>
   <si>
-    <t>ep_windon_006__irena</t>
-  </si>
-  <si>
     <t>windon</t>
   </si>
   <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>ep_windon_009__irena</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>ep_windon_010__irena</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_001</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_003</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_005</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_007</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_008</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
     <t>ep_windon_wind_G100000923898</t>
   </si>
   <si>
-    <t>~fi_process</t>
-  </si>
-  <si>
     <t>set</t>
   </si>
   <si>
@@ -300,9 +234,6 @@
     <t>ele</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
     <t>GW</t>
   </si>
   <si>
@@ -315,9 +246,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap_Missing Gas Capacity -- operating</t>
-  </si>
-  <si>
     <t>IRU Elektrijaam power station_1 -- operating</t>
   </si>
   <si>
@@ -327,9 +255,6 @@
     <t>Aggregated Plant -- operating</t>
   </si>
   <si>
-    <t>Kiisa ERPP power station_1 &amp; 2 -- operating</t>
-  </si>
-  <si>
     <t>annual</t>
   </si>
   <si>
@@ -702,12 +627,6 @@
     <t>fom (%/year)</t>
   </si>
   <si>
-    <t>​</t>
-  </si>
-  <si>
-    <t>NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)</t>
-  </si>
-  <si>
     <t>biomass</t>
   </si>
   <si>
@@ -843,9 +762,6 @@
     <t>elc_won_ida_viru</t>
   </si>
   <si>
-    <t>vka tuul</t>
-  </si>
-  <si>
     <t>ep_solar_pv_voru</t>
   </si>
   <si>
@@ -874,16 +790,72 @@
   </si>
   <si>
     <t>elv_spv_hiiu</t>
+  </si>
+  <si>
+    <t>~FI_Process</t>
+  </si>
+  <si>
+    <t>Sets</t>
+  </si>
+  <si>
+    <t>TechName</t>
+  </si>
+  <si>
+    <t>TechDesc</t>
+  </si>
+  <si>
+    <t>Tcap</t>
+  </si>
+  <si>
+    <t>Tslvl</t>
+  </si>
+  <si>
+    <t>PrimaryCG</t>
+  </si>
+  <si>
+    <t>Vintage</t>
+  </si>
+  <si>
+    <t>* Sets</t>
+  </si>
+  <si>
+    <t>Technology Name</t>
+  </si>
+  <si>
+    <t>Technology Description</t>
+  </si>
+  <si>
+    <t>Activity Unit</t>
+  </si>
+  <si>
+    <t>TimeSlice level of Process Activity</t>
+  </si>
+  <si>
+    <t>Primary Commodity Group</t>
+  </si>
+  <si>
+    <t>Vintage Tracking</t>
+  </si>
+  <si>
+    <t>* Power Plants</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="9">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="181" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="182" formatCode="m\o\n\th\ d\,\ yyyy"/>
+    <numFmt numFmtId="183" formatCode="#.00"/>
+    <numFmt numFmtId="184" formatCode="#."/>
+    <numFmt numFmtId="185" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -891,16 +863,470 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="1"/>
+      <color indexed="8"/>
+      <name val="Courier"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="56"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="1"/>
+      <color indexed="8"/>
+      <name val="Courier"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="60"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="MS Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="63"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color indexed="56"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Courier"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="27"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="29"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="30"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="36"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="49"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="52"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -908,21 +1334,1406 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dashed">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="63"/>
+      </left>
+      <right style="double">
+        <color indexed="63"/>
+      </right>
+      <top style="double">
+        <color indexed="63"/>
+      </top>
+      <bottom style="double">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="62"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="30"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="52"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="536">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="182" fontId="21" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="21" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="21" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="21" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="21" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="21" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="21" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="21" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="40" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" applyNumberFormat="0" applyProtection="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="21" fillId="0" borderId="17">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="21" fillId="0" borderId="17">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="21" fillId="0" borderId="17">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="21" fillId="0" borderId="17">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" xfId="253" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="319" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="185" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="6" xfId="319" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="319" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="4" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="5" fillId="18" borderId="5" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="4" fillId="15" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="6" fillId="18" borderId="5" xfId="253" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="6" fillId="18" borderId="5" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="536">
+    <cellStyle name="20% - Accent1 2" xfId="18" xr:uid="{C2F6E926-9FDD-459E-B36E-F6553828C486}"/>
+    <cellStyle name="20% - Accent1 3" xfId="19" xr:uid="{D0CDC148-61B0-4F54-AFC7-80FFC7BA9DDA}"/>
+    <cellStyle name="20% - Accent1 3 2" xfId="20" xr:uid="{6B82962E-198F-48A5-9387-C43B6BACF387}"/>
+    <cellStyle name="20% - Accent1 3 3" xfId="21" xr:uid="{54718EBD-8851-4832-AA80-F1584D982BEF}"/>
+    <cellStyle name="20% - Accent1 4" xfId="22" xr:uid="{02D395A3-C917-4727-A060-4AF1B4BBD948}"/>
+    <cellStyle name="20% - Accent1 4 2" xfId="23" xr:uid="{C2F452E8-E51C-4928-AD5E-A52B5A98920D}"/>
+    <cellStyle name="20% - Accent1 4 3" xfId="24" xr:uid="{DE15865C-80E1-4488-B2CD-286593D7FA68}"/>
+    <cellStyle name="20% - Accent1 5" xfId="25" xr:uid="{B715AB6E-9975-4191-B542-EDEDB3F52195}"/>
+    <cellStyle name="20% - Accent1 6" xfId="26" xr:uid="{02E3A29E-1B58-4B64-982B-AFB056387F9D}"/>
+    <cellStyle name="20% - Accent2 2" xfId="27" xr:uid="{1F8745B0-F379-4B29-BFF7-43354186D9A9}"/>
+    <cellStyle name="20% - Accent2 3" xfId="28" xr:uid="{0EAE995D-0A79-4B68-AD97-45CCBA1F6AE1}"/>
+    <cellStyle name="20% - Accent2 3 2" xfId="29" xr:uid="{0974B237-50AD-44D5-835B-61FC4EDEE5E7}"/>
+    <cellStyle name="20% - Accent2 3 3" xfId="30" xr:uid="{8D935F9F-A016-44E4-9597-EF066FF81B55}"/>
+    <cellStyle name="20% - Accent2 4" xfId="31" xr:uid="{4E91F96A-F305-4DA3-8C78-003861A0B852}"/>
+    <cellStyle name="20% - Accent2 4 2" xfId="32" xr:uid="{FE4B1920-80FA-4DF0-9297-69AB48E66EB0}"/>
+    <cellStyle name="20% - Accent2 4 3" xfId="33" xr:uid="{A43CBCD7-CB2A-425A-A94D-49D9C309DDA8}"/>
+    <cellStyle name="20% - Accent2 5" xfId="34" xr:uid="{EB57A3A9-6FDA-4EB9-9F02-27BBEB7617FF}"/>
+    <cellStyle name="20% - Accent2 6" xfId="35" xr:uid="{BE918435-74D2-495F-B20B-F5C32F37F543}"/>
+    <cellStyle name="20% - Accent3 2" xfId="36" xr:uid="{B2B7A526-EA57-4EA7-8889-CA711D1875BF}"/>
+    <cellStyle name="20% - Accent3 3" xfId="37" xr:uid="{08031ADB-4EF8-4A20-8EB3-B95716B45690}"/>
+    <cellStyle name="20% - Accent3 3 2" xfId="38" xr:uid="{209E20FA-8CF5-499F-BCB8-C333DAC6FC1C}"/>
+    <cellStyle name="20% - Accent3 3 3" xfId="39" xr:uid="{14E42D62-82E1-44D6-8073-04237052E866}"/>
+    <cellStyle name="20% - Accent3 4" xfId="40" xr:uid="{1DA2244D-5290-427C-B55B-60F574143C85}"/>
+    <cellStyle name="20% - Accent3 4 2" xfId="41" xr:uid="{103AD0E1-E42A-4FC8-9ACA-CFB056E519E2}"/>
+    <cellStyle name="20% - Accent3 4 3" xfId="42" xr:uid="{2998309D-2A64-408A-AFC6-1AF80F774CF7}"/>
+    <cellStyle name="20% - Accent3 5" xfId="43" xr:uid="{1F50220A-6609-4023-B7AA-C303684625F5}"/>
+    <cellStyle name="20% - Accent3 6" xfId="44" xr:uid="{44FEDAC3-966A-4FD5-B230-0FE85E7F0341}"/>
+    <cellStyle name="20% - Accent4 2" xfId="45" xr:uid="{5799D3DF-38D6-45CC-A5ED-3B791D73FFEA}"/>
+    <cellStyle name="20% - Accent4 3" xfId="46" xr:uid="{539C19BD-F7C1-45B0-A513-F364DEF44EC1}"/>
+    <cellStyle name="20% - Accent4 3 2" xfId="47" xr:uid="{1D504E29-22E4-4107-BE34-4EA0423ADF3A}"/>
+    <cellStyle name="20% - Accent4 3 3" xfId="48" xr:uid="{1D4E08EA-1289-4A51-9021-1772364535CE}"/>
+    <cellStyle name="20% - Accent4 4" xfId="49" xr:uid="{9B0CF924-E0C2-43EB-B87A-7A70C6C2BC3F}"/>
+    <cellStyle name="20% - Accent4 4 2" xfId="50" xr:uid="{5C9ECBFF-5402-43F7-9C3A-8420F31F4862}"/>
+    <cellStyle name="20% - Accent4 4 3" xfId="51" xr:uid="{BD7259F1-DF2E-4B83-98AD-D915A5489907}"/>
+    <cellStyle name="20% - Accent4 5" xfId="52" xr:uid="{EAB8C525-FB94-4392-AAF1-5D2750AC3E28}"/>
+    <cellStyle name="20% - Accent4 6" xfId="53" xr:uid="{8A7A84E2-9832-4607-97D7-4ADD4F9666A4}"/>
+    <cellStyle name="20% - Accent5 2" xfId="17" xr:uid="{D48EF81F-6E1F-4D1B-9803-F076CE5A58B5}"/>
+    <cellStyle name="20% - Accent5 3" xfId="54" xr:uid="{6AAEDA1D-4470-415A-94DB-DF9DB6A7F5B7}"/>
+    <cellStyle name="20% - Accent5 3 2" xfId="55" xr:uid="{2FE4ECFC-CD8B-48F0-BDE9-AE5F3DF08E04}"/>
+    <cellStyle name="20% - Accent5 3 3" xfId="56" xr:uid="{03CA3832-6190-4F23-8AC4-E051CFE3AF75}"/>
+    <cellStyle name="20% - Accent5 4" xfId="57" xr:uid="{A048D7B8-5976-434B-9665-B373C9929B3C}"/>
+    <cellStyle name="20% - Accent5 4 2" xfId="58" xr:uid="{0ED58860-80F7-44C0-B628-8075A5237934}"/>
+    <cellStyle name="20% - Accent5 4 3" xfId="59" xr:uid="{CCB1CA17-428D-4537-85BC-58E7E1CF5189}"/>
+    <cellStyle name="20% - Accent5 5" xfId="60" xr:uid="{1AE56565-5E66-4587-9D01-7518F24A6D8E}"/>
+    <cellStyle name="20% - Accent5 6" xfId="61" xr:uid="{B83F0060-5B49-48E5-9DBF-6CBB733F25B6}"/>
+    <cellStyle name="20% - Accent6 2" xfId="62" xr:uid="{3A2C0859-31A9-4A2E-AB67-02ED0E22DE9B}"/>
+    <cellStyle name="20% - Accent6 3" xfId="63" xr:uid="{FB5A3A43-68AE-45A2-B307-C16FBE893922}"/>
+    <cellStyle name="20% - Accent6 3 2" xfId="64" xr:uid="{29FBF1AF-4D0C-4CBF-9BED-2569C1793A27}"/>
+    <cellStyle name="20% - Accent6 3 3" xfId="65" xr:uid="{36037DE2-4418-44EC-8FDC-8006FBD9E542}"/>
+    <cellStyle name="20% - Accent6 4" xfId="66" xr:uid="{61421915-B3DF-4BC0-9585-8B8C1ED27F22}"/>
+    <cellStyle name="20% - Accent6 4 2" xfId="67" xr:uid="{97C2937D-3393-4D5E-8689-E91BA4D8B298}"/>
+    <cellStyle name="20% - Accent6 4 3" xfId="68" xr:uid="{FEF7C5A1-6EBE-4CCF-9FAE-C52D0F37525B}"/>
+    <cellStyle name="20% - Accent6 5" xfId="69" xr:uid="{252D7F5C-E02E-4DAF-886A-AA06D7041054}"/>
+    <cellStyle name="20% - Accent6 6" xfId="70" xr:uid="{7A5FDCF4-585A-40F9-9AAB-D4356D81F4CC}"/>
+    <cellStyle name="40% - Accent1 2" xfId="71" xr:uid="{4ED24ED5-EB08-4B74-A88E-54E7A2936E2B}"/>
+    <cellStyle name="40% - Accent1 3" xfId="72" xr:uid="{203B437E-8C42-4C9C-99A4-5C6403263542}"/>
+    <cellStyle name="40% - Accent1 3 2" xfId="73" xr:uid="{B814D06C-1EC4-468E-9F32-AADEDA2BCF31}"/>
+    <cellStyle name="40% - Accent1 3 3" xfId="74" xr:uid="{BAB3CAEE-FF6E-4AFB-B4FD-B5EF754A9B02}"/>
+    <cellStyle name="40% - Accent1 4" xfId="75" xr:uid="{7A2552B4-5CF8-4C73-BDAC-1E5EC6C39EDF}"/>
+    <cellStyle name="40% - Accent1 4 2" xfId="76" xr:uid="{491A2DC4-E965-4BE3-91BF-013798FB71E2}"/>
+    <cellStyle name="40% - Accent1 4 3" xfId="77" xr:uid="{D1A5CAFC-CEC3-432F-8B8D-C0CFBA4D1B6E}"/>
+    <cellStyle name="40% - Accent1 5" xfId="78" xr:uid="{4EB52E36-A630-4059-BCFB-E35CFD0AB7EF}"/>
+    <cellStyle name="40% - Accent1 6" xfId="79" xr:uid="{4BCC9406-C8AA-4F1E-A233-C9631CF57ABD}"/>
+    <cellStyle name="40% - Accent2 2" xfId="80" xr:uid="{D641B17E-10C3-457E-8665-48D97587AF87}"/>
+    <cellStyle name="40% - Accent2 3" xfId="81" xr:uid="{22FD3305-462D-499F-9E91-3058B226203F}"/>
+    <cellStyle name="40% - Accent2 3 2" xfId="82" xr:uid="{3B3AE83A-9315-4D14-9211-F772251666C4}"/>
+    <cellStyle name="40% - Accent2 3 3" xfId="83" xr:uid="{DDE2F52E-F0B0-4DFF-8D6F-307495098B9D}"/>
+    <cellStyle name="40% - Accent2 4" xfId="84" xr:uid="{E1F2887A-0A81-4293-B85E-88139A19049D}"/>
+    <cellStyle name="40% - Accent2 4 2" xfId="85" xr:uid="{9A727304-9E85-4236-B77B-068F8AA258B6}"/>
+    <cellStyle name="40% - Accent2 4 3" xfId="86" xr:uid="{DE713F12-11EA-48A1-B83C-EB5062C3283A}"/>
+    <cellStyle name="40% - Accent2 5" xfId="87" xr:uid="{05D283B7-75C9-46FB-BF88-11ADB9D678FA}"/>
+    <cellStyle name="40% - Accent2 6" xfId="88" xr:uid="{4078D910-94EE-4911-B8E4-805F60F93935}"/>
+    <cellStyle name="40% - Accent3 2" xfId="89" xr:uid="{608A12D2-A95C-4D3F-8091-E5D6DAC77837}"/>
+    <cellStyle name="40% - Accent3 3" xfId="90" xr:uid="{498FB99B-EF69-4BCE-8561-DA302AB26DCA}"/>
+    <cellStyle name="40% - Accent3 3 2" xfId="91" xr:uid="{C834B6E1-ED40-4F40-9AB0-3E4972E628F5}"/>
+    <cellStyle name="40% - Accent3 3 2 2" xfId="92" xr:uid="{0A14402B-EE56-4283-81EA-48E321562DED}"/>
+    <cellStyle name="40% - Accent3 3 2 2 2" xfId="93" xr:uid="{4A67F815-5767-4745-8998-8208A3CC7B22}"/>
+    <cellStyle name="40% - Accent3 3 2 2 3" xfId="94" xr:uid="{0BB52079-FAE0-48E1-86FE-68442FB6678D}"/>
+    <cellStyle name="40% - Accent3 3 2 3" xfId="95" xr:uid="{E3CD77C7-F602-46F7-98F9-E6D0EEC0FF29}"/>
+    <cellStyle name="40% - Accent3 3 2 4" xfId="96" xr:uid="{054CC8CC-6839-46A9-87B4-B876BDEDCE76}"/>
+    <cellStyle name="40% - Accent3 3 3" xfId="97" xr:uid="{8ABCD0C6-43ED-4581-B20F-A383A615A9ED}"/>
+    <cellStyle name="40% - Accent3 3 3 2" xfId="98" xr:uid="{A664B716-744E-4665-BB0D-7299073BAE57}"/>
+    <cellStyle name="40% - Accent3 3 3 3" xfId="99" xr:uid="{AB3C0251-2FB0-4914-A573-5A5C2EBFB940}"/>
+    <cellStyle name="40% - Accent3 3 4" xfId="100" xr:uid="{48D1E7D3-C9A1-48B6-9386-0FA23AD325E2}"/>
+    <cellStyle name="40% - Accent3 3 5" xfId="101" xr:uid="{E9C2703D-BE3C-416F-89E6-DAF83B3B1B4D}"/>
+    <cellStyle name="40% - Accent3 4" xfId="102" xr:uid="{070BCF28-6044-4FBA-B919-85A180EE1998}"/>
+    <cellStyle name="40% - Accent3 4 2" xfId="103" xr:uid="{F0B37B10-C777-4264-954D-8CDC6956D016}"/>
+    <cellStyle name="40% - Accent3 4 2 2" xfId="104" xr:uid="{D577EA8B-9F16-4008-A29A-4996023B5229}"/>
+    <cellStyle name="40% - Accent3 4 2 3" xfId="105" xr:uid="{1352ACC6-4FF1-4293-AACA-AE06ACFB0B76}"/>
+    <cellStyle name="40% - Accent3 4 3" xfId="106" xr:uid="{444E68AE-29D6-476B-837A-F9991E73478E}"/>
+    <cellStyle name="40% - Accent3 4 4" xfId="107" xr:uid="{DFE7B282-AF76-4DFB-A86A-4933B6935E5C}"/>
+    <cellStyle name="40% - Accent3 5" xfId="108" xr:uid="{7713F944-4EE8-4863-840E-30D458F6C4EE}"/>
+    <cellStyle name="40% - Accent3 5 2" xfId="109" xr:uid="{86A152B5-0291-4105-9960-CAB2D1DC2DBC}"/>
+    <cellStyle name="40% - Accent3 5 2 2" xfId="110" xr:uid="{DC1A3B3E-0002-4C20-AE0A-DC7F7AC42853}"/>
+    <cellStyle name="40% - Accent3 5 2 3" xfId="111" xr:uid="{3BC3886D-60A3-4829-8C90-E2B77B43EBDF}"/>
+    <cellStyle name="40% - Accent3 5 3" xfId="112" xr:uid="{11BC02F8-C537-4BAB-8472-37ABBDD739B1}"/>
+    <cellStyle name="40% - Accent3 5 4" xfId="113" xr:uid="{14919AE6-2200-4A8C-8F61-CE7F98E2893B}"/>
+    <cellStyle name="40% - Accent3 6" xfId="114" xr:uid="{A4C1F8B8-05DE-494F-A2B3-F7C84159165E}"/>
+    <cellStyle name="40% - Accent3 6 2" xfId="115" xr:uid="{BEAEAED2-2E4E-4139-BBD1-BF8A86658E13}"/>
+    <cellStyle name="40% - Accent3 6 3" xfId="116" xr:uid="{2A91C0AD-58BA-4905-8C6D-064D79453D7F}"/>
+    <cellStyle name="40% - Accent3 7" xfId="117" xr:uid="{3E2B88F5-FCE7-4F68-BB36-E951459BBAF4}"/>
+    <cellStyle name="40% - Accent3 8" xfId="118" xr:uid="{5870A167-32FD-491D-BE58-0E136C868431}"/>
+    <cellStyle name="40% - Accent4 2" xfId="119" xr:uid="{BF474786-25CA-44A0-9BFE-A186BF980E75}"/>
+    <cellStyle name="40% - Accent4 3" xfId="120" xr:uid="{EA20FC2C-1560-46CF-9CAC-DB8834E4B262}"/>
+    <cellStyle name="40% - Accent4 3 2" xfId="121" xr:uid="{92D29F30-1B93-4A9D-BA4A-D65B4DCACA29}"/>
+    <cellStyle name="40% - Accent4 3 3" xfId="122" xr:uid="{005B492F-C01A-49F7-A369-12573291A859}"/>
+    <cellStyle name="40% - Accent4 4" xfId="123" xr:uid="{5130F80F-49BC-47A7-8862-E2EC3167FF16}"/>
+    <cellStyle name="40% - Accent4 4 2" xfId="124" xr:uid="{7994B51D-884E-44F2-9810-B70C2B63B090}"/>
+    <cellStyle name="40% - Accent4 4 3" xfId="125" xr:uid="{A591F72A-AC9C-42AE-8614-ADF888BE0646}"/>
+    <cellStyle name="40% - Accent4 5" xfId="126" xr:uid="{3E073918-ED62-47BB-9937-6A6985C2B5D2}"/>
+    <cellStyle name="40% - Accent4 6" xfId="127" xr:uid="{263B421A-A31A-4D0E-BA89-5592D6AACAB0}"/>
+    <cellStyle name="40% - Accent5 2" xfId="128" xr:uid="{BB8F5055-2275-4E1A-A9DE-98B1E56F8A2A}"/>
+    <cellStyle name="40% - Accent5 3" xfId="129" xr:uid="{890B54FE-2D52-4F81-85BA-8F50F26382F3}"/>
+    <cellStyle name="40% - Accent5 3 2" xfId="130" xr:uid="{57EACDA7-FB58-4C1C-A44C-4364A9757475}"/>
+    <cellStyle name="40% - Accent5 3 3" xfId="131" xr:uid="{93F24521-B667-497C-AE8B-FF38295C4CAD}"/>
+    <cellStyle name="40% - Accent5 4" xfId="132" xr:uid="{C9C07EC0-AC63-4900-A239-96B2B0984341}"/>
+    <cellStyle name="40% - Accent5 4 2" xfId="133" xr:uid="{67BAC47B-6182-433E-AE2F-1C01971B43FF}"/>
+    <cellStyle name="40% - Accent5 4 3" xfId="134" xr:uid="{8031E89F-AD07-4E69-9DA5-E22EF4CCB9AD}"/>
+    <cellStyle name="40% - Accent5 5" xfId="135" xr:uid="{E662DDED-0284-44B4-8FF8-8E1AC3417EB7}"/>
+    <cellStyle name="40% - Accent5 6" xfId="136" xr:uid="{C0A80A2A-AE8F-4F0A-BAB5-AFF689AF97D6}"/>
+    <cellStyle name="40% - Accent6 2" xfId="137" xr:uid="{F7490E6D-448E-46B6-8BF2-3C530CEC0AE8}"/>
+    <cellStyle name="40% - Accent6 3" xfId="138" xr:uid="{AE7839E2-D275-4C36-A5A0-29AAAACB4361}"/>
+    <cellStyle name="40% - Accent6 3 2" xfId="139" xr:uid="{6389361F-7FA8-465F-9953-48E762DF45DE}"/>
+    <cellStyle name="40% - Accent6 3 3" xfId="140" xr:uid="{FED8C062-0088-493D-B9EF-1C2269A91ADA}"/>
+    <cellStyle name="40% - Accent6 4" xfId="141" xr:uid="{447AC394-2CD8-48E5-AF88-34E0C773A4BA}"/>
+    <cellStyle name="40% - Accent6 4 2" xfId="142" xr:uid="{F53DB594-4FCC-4DFB-B5F2-D3A26666A931}"/>
+    <cellStyle name="40% - Accent6 4 3" xfId="143" xr:uid="{4DC968FA-1D73-40D7-8A92-A94E96261FB5}"/>
+    <cellStyle name="40% - Accent6 5" xfId="144" xr:uid="{C2B0BAA2-2D24-49CE-BEFF-08DE71490DEE}"/>
+    <cellStyle name="40% - Accent6 6" xfId="145" xr:uid="{46AC72E5-FE06-4B21-BA6B-8BFF709B97AF}"/>
+    <cellStyle name="60% - Accent1 2" xfId="146" xr:uid="{A91F2349-C3BE-410F-8B57-33F566930DF9}"/>
+    <cellStyle name="60% - Accent2 2" xfId="147" xr:uid="{BE3309CC-79D3-492A-ADD8-643245261CE6}"/>
+    <cellStyle name="60% - Accent3 2" xfId="148" xr:uid="{5F96E0B1-A596-4907-A66F-D72651BAC09D}"/>
+    <cellStyle name="60% - Accent4 2" xfId="149" xr:uid="{18E0D975-82DD-48A8-9FD3-FA18CF903825}"/>
+    <cellStyle name="60% - Accent5 2" xfId="150" xr:uid="{57CB5468-0EF2-494A-B71F-EA254913FB72}"/>
+    <cellStyle name="60% - Accent6 2" xfId="151" xr:uid="{02F20496-8CC9-4391-8F10-74FD8D73D251}"/>
+    <cellStyle name="Accent1 2" xfId="152" xr:uid="{7BE3FAA8-9805-4924-90CA-3E6792D200FF}"/>
+    <cellStyle name="Accent2 2" xfId="153" xr:uid="{04AE7A7E-1CF8-45DA-BC88-7D2A1530307D}"/>
+    <cellStyle name="Accent3 2" xfId="154" xr:uid="{1A560C38-3C3C-437B-AA5E-94BB53C8F23A}"/>
+    <cellStyle name="Accent4 2" xfId="155" xr:uid="{9C55096C-EAA9-44C4-93DF-CF78F7027BBB}"/>
+    <cellStyle name="Accent5 2" xfId="156" xr:uid="{24ACADBE-E858-47CE-9B9D-C20264AC1F84}"/>
+    <cellStyle name="Accent6 2" xfId="157" xr:uid="{9BE1F430-B159-4B1A-A04E-553F85FADD37}"/>
+    <cellStyle name="Bad 2" xfId="158" xr:uid="{01AAF97E-80CA-406D-B9D7-5FF10ED52B3B}"/>
+    <cellStyle name="Body: normal cell" xfId="159" xr:uid="{2B56F760-2DDB-4CAB-A89D-E1550C3A9ABD}"/>
+    <cellStyle name="Calculation 2" xfId="160" xr:uid="{CB7B7AFF-1558-4E30-98F8-DC2A754508F5}"/>
+    <cellStyle name="Check Cell 2" xfId="161" xr:uid="{B573B1CE-9120-45A0-B740-F400CA724171}"/>
+    <cellStyle name="Comma 2" xfId="8" xr:uid="{D72CCAFC-54B4-4638-85B1-6EF2BE1EF0DF}"/>
+    <cellStyle name="Comma 2 2" xfId="162" xr:uid="{4B67E48B-3B66-46EA-81AC-F8D0DB47BAF0}"/>
+    <cellStyle name="Comma 2 3" xfId="7" xr:uid="{E066D7CE-E612-491C-87A7-80EE7D004D4A}"/>
+    <cellStyle name="Comma 3" xfId="163" xr:uid="{7206B4CA-5750-4F88-9B9F-8E31F67EEDDA}"/>
+    <cellStyle name="Comma 3 2" xfId="164" xr:uid="{5D1730AA-AC69-4761-A9EF-ECE9A30E69DA}"/>
+    <cellStyle name="Comma 3 2 2" xfId="165" xr:uid="{389AB53B-EEF3-4A06-93E4-3DDF688FE040}"/>
+    <cellStyle name="Comma 3 2 2 2" xfId="166" xr:uid="{3FBF83D4-0F24-4153-B72C-840F49ABA5D3}"/>
+    <cellStyle name="Comma 3 2 2 2 2" xfId="167" xr:uid="{5491406F-306B-43FA-BFD3-390400CD8250}"/>
+    <cellStyle name="Comma 3 2 2 2 3" xfId="168" xr:uid="{398FF932-D373-4FF3-B309-F46B80298F15}"/>
+    <cellStyle name="Comma 3 2 2 3" xfId="169" xr:uid="{1515F5CC-F198-4E4F-817E-CC6B97EEE3B0}"/>
+    <cellStyle name="Comma 3 2 2 4" xfId="170" xr:uid="{8540CBFC-2342-4D7E-B70F-CAB4FD6594A5}"/>
+    <cellStyle name="Comma 3 2 3" xfId="171" xr:uid="{A99FB12A-2D3A-4743-AA0D-777595B4A3C9}"/>
+    <cellStyle name="Comma 3 2 3 2" xfId="172" xr:uid="{272F6792-4B9C-4B87-8B5C-183DBAB0183D}"/>
+    <cellStyle name="Comma 3 2 3 3" xfId="173" xr:uid="{3BD8E693-0E5D-4CB0-B35F-C77938B2A00C}"/>
+    <cellStyle name="Comma 3 2 4" xfId="174" xr:uid="{6DF15A62-3B5A-433F-B65A-E2004D2B5FE1}"/>
+    <cellStyle name="Comma 3 2 5" xfId="175" xr:uid="{5C4021DC-3934-4B79-8954-1F7B5EA32819}"/>
+    <cellStyle name="Comma 3 3" xfId="176" xr:uid="{598E6CBC-9139-4D3C-BE77-57B71F5A5615}"/>
+    <cellStyle name="Comma 3 3 2" xfId="177" xr:uid="{A7DE07E3-ECF1-4949-8283-B2053524C84D}"/>
+    <cellStyle name="Comma 3 3 2 2" xfId="178" xr:uid="{FD721038-AD9E-4870-ABCF-0755017ED17E}"/>
+    <cellStyle name="Comma 3 3 2 3" xfId="179" xr:uid="{D4AE458F-874F-45B7-99B9-B0CC6C4627CF}"/>
+    <cellStyle name="Comma 3 3 3" xfId="180" xr:uid="{A282F1F8-3410-49A5-9F78-230782E81999}"/>
+    <cellStyle name="Comma 3 3 4" xfId="181" xr:uid="{DD5C7F71-F788-4342-AE91-117F8F54864B}"/>
+    <cellStyle name="Comma 3 4" xfId="182" xr:uid="{152BF334-FEA5-4504-98E2-8FFD0CEDAD8F}"/>
+    <cellStyle name="Comma 3 4 2" xfId="183" xr:uid="{0B8E6A88-DE2B-4D5E-A426-BCF2BD0DA4C1}"/>
+    <cellStyle name="Comma 3 4 3" xfId="184" xr:uid="{63F066FD-22A0-4F15-B48E-544C739BAC93}"/>
+    <cellStyle name="Comma 3 5" xfId="185" xr:uid="{313786B1-1FBD-4485-95CD-B4B1E1F8013C}"/>
+    <cellStyle name="Comma 3 6" xfId="186" xr:uid="{B4517645-118C-40A7-BA95-BF020E6E6A9B}"/>
+    <cellStyle name="Comma 3 7" xfId="187" xr:uid="{074BA1AA-97DC-4155-BC27-A46893F44790}"/>
+    <cellStyle name="Comma 4" xfId="188" xr:uid="{54EE86C9-D490-48E9-9BF2-13CE3009F314}"/>
+    <cellStyle name="Comma 4 2" xfId="189" xr:uid="{00A6BABA-A049-4466-A0C9-B87A9033E364}"/>
+    <cellStyle name="Comma 4 2 2" xfId="190" xr:uid="{5F7F3787-5629-4542-87D6-85E20623FB95}"/>
+    <cellStyle name="Comma 4 2 2 2" xfId="191" xr:uid="{FB87929B-C102-4643-A37B-C064423B3D14}"/>
+    <cellStyle name="Comma 4 2 3" xfId="192" xr:uid="{A14C5235-33B7-4386-ABFE-E69389AFC73E}"/>
+    <cellStyle name="Comma 4 3" xfId="193" xr:uid="{2C624D9A-0F48-4AEC-80A4-CF191AFC542F}"/>
+    <cellStyle name="Comma 4 3 2" xfId="194" xr:uid="{B99E7BCC-CFCB-4F90-B22B-E1DC57548521}"/>
+    <cellStyle name="Comma 4 4" xfId="195" xr:uid="{3F083A57-6A7A-4068-9D7D-7D474CD2E5CF}"/>
+    <cellStyle name="Comma 4 4 2" xfId="196" xr:uid="{E73285EA-ECDE-40AB-817A-590E5CAD51D3}"/>
+    <cellStyle name="Comma 4 5" xfId="197" xr:uid="{702A32A4-8745-43D2-90F1-F54F728D4CAA}"/>
+    <cellStyle name="Comma 5" xfId="198" xr:uid="{ABE8F62D-A2E3-4BCB-969A-E763D140A780}"/>
+    <cellStyle name="Comma 5 2" xfId="199" xr:uid="{DE18E7E9-44B8-4C40-ACAB-A82F599A568C}"/>
+    <cellStyle name="Comma 5 2 2" xfId="200" xr:uid="{0F86954D-8E6B-4CAB-8C26-01B00555F617}"/>
+    <cellStyle name="Comma 5 2 3" xfId="201" xr:uid="{2A480666-FD68-41B0-A1D0-D31E6E382994}"/>
+    <cellStyle name="Comma 6" xfId="202" xr:uid="{C70E70BE-7F42-4352-A256-31273105DABB}"/>
+    <cellStyle name="Comma 6 2" xfId="203" xr:uid="{E5582BD7-276F-414B-8FFF-0793641C8D9A}"/>
+    <cellStyle name="Comma 6 2 2" xfId="204" xr:uid="{90F88E80-0294-4585-9B04-6C611E342E62}"/>
+    <cellStyle name="Comma 6 2 3" xfId="205" xr:uid="{03F65063-9656-4F6A-A9BB-BF305BA83C58}"/>
+    <cellStyle name="Comma 6 3" xfId="206" xr:uid="{637D2EBF-30D6-422A-A82E-869582B00BDA}"/>
+    <cellStyle name="Comma 6 4" xfId="207" xr:uid="{0A6E2952-C880-4D31-BDA9-1EE1CC2072E7}"/>
+    <cellStyle name="Comma 6 5" xfId="208" xr:uid="{4E1D2580-6E7C-4E17-8298-D77BA61B0684}"/>
+    <cellStyle name="Comma 7" xfId="209" xr:uid="{F477A207-68A1-4D10-A922-592AAB30EA61}"/>
+    <cellStyle name="Comma 8" xfId="210" xr:uid="{ABCA9420-ECF8-47BF-ADC4-A02D881C98C4}"/>
+    <cellStyle name="Currency 2" xfId="211" xr:uid="{42E30335-FA68-4578-88C5-637354CF0BF2}"/>
+    <cellStyle name="Currency 2 2" xfId="212" xr:uid="{FB1C2049-D074-4E57-BB1D-7C10F11D1DC8}"/>
+    <cellStyle name="Currency 2 2 2" xfId="213" xr:uid="{669D6EDD-F84C-4ACA-9BB8-13B3FC17317C}"/>
+    <cellStyle name="Currency 2 2 2 2" xfId="214" xr:uid="{252625CF-9C9F-413D-A58E-86FA5EF90F50}"/>
+    <cellStyle name="Currency 2 3" xfId="215" xr:uid="{B268257F-60B9-4840-801F-E5C9047CC447}"/>
+    <cellStyle name="Currency 2 3 2" xfId="216" xr:uid="{63CE2043-3B6F-456F-85F4-59193D4E9D2A}"/>
+    <cellStyle name="Currency 2 4" xfId="217" xr:uid="{B5D9C827-14D7-4B77-A626-653B4C795B5A}"/>
+    <cellStyle name="Currency 2 4 2" xfId="218" xr:uid="{38B6C841-7F26-4D6A-8514-8C2069456444}"/>
+    <cellStyle name="Currency 2 5" xfId="219" xr:uid="{D5C688E6-1A76-4D0C-A923-52749B36991B}"/>
+    <cellStyle name="Currency 3" xfId="220" xr:uid="{BA2D43BD-E99E-483B-A639-C04DDC76D4FA}"/>
+    <cellStyle name="Date" xfId="221" xr:uid="{40B41E4A-E5F1-44A3-BC21-EAD8504AE9EB}"/>
+    <cellStyle name="Date 2" xfId="222" xr:uid="{5D35B6D8-80F5-47B4-9CC2-CD62F2DA2116}"/>
+    <cellStyle name="Date 2 2" xfId="223" xr:uid="{A87EF994-1D40-4C1A-8074-601DCCC61611}"/>
+    <cellStyle name="Date 2 3" xfId="224" xr:uid="{4B13F128-2A1A-49ED-B9C7-0C92DE88EAB8}"/>
+    <cellStyle name="Explanatory Text 2" xfId="225" xr:uid="{09BB62FD-170E-4878-8365-F3BB9D7A35EA}"/>
+    <cellStyle name="Fixed" xfId="226" xr:uid="{A025D736-368A-4783-A836-DBDB7A4EDC2B}"/>
+    <cellStyle name="Fixed 2" xfId="227" xr:uid="{1E588BE2-D53C-4AC3-AD30-02C5A14BFD75}"/>
+    <cellStyle name="Fixed 2 2" xfId="228" xr:uid="{F12388DF-6498-41A0-A188-2F66E8DF055F}"/>
+    <cellStyle name="Fixed 2 3" xfId="229" xr:uid="{AC1FBF10-FF8A-4873-82B6-AFAA16AEABD0}"/>
+    <cellStyle name="Good 2" xfId="230" xr:uid="{36DF2AC2-9F5A-4DBE-9E83-EBC42DE814C0}"/>
+    <cellStyle name="Heading 1 2" xfId="231" xr:uid="{4D7A4E99-A5C7-492D-A8F4-96E9D13496FC}"/>
+    <cellStyle name="Heading 2 2" xfId="232" xr:uid="{67BA5CFB-D463-4A51-9277-9ACF5E1FE992}"/>
+    <cellStyle name="Heading 3 2" xfId="233" xr:uid="{D1280F40-2CA8-4567-B434-7B6F1AC63458}"/>
+    <cellStyle name="Heading 4 2" xfId="234" xr:uid="{3D300802-96E1-46D2-AFC5-9242FC6F6622}"/>
+    <cellStyle name="Heading1" xfId="235" xr:uid="{BAF1EF53-55CD-495E-A109-DF5D0D042238}"/>
+    <cellStyle name="Heading1 2" xfId="236" xr:uid="{10B98954-40ED-40A2-A8A5-9BB57B8C65C1}"/>
+    <cellStyle name="Heading1 2 2" xfId="237" xr:uid="{BC96D653-D76C-4CCB-92CF-99A156C2F25E}"/>
+    <cellStyle name="Heading1 2 3" xfId="238" xr:uid="{ED73029C-1108-463E-AB59-D61657CE35D0}"/>
+    <cellStyle name="Heading2" xfId="239" xr:uid="{FED2C5A4-76D2-4BD5-9E7D-E031EBB788E6}"/>
+    <cellStyle name="Heading2 2" xfId="240" xr:uid="{DE737D12-CFC6-4145-9227-63A27A6C55BD}"/>
+    <cellStyle name="Heading2 2 2" xfId="241" xr:uid="{33F348A5-5970-4F13-84DF-C6EA09CED061}"/>
+    <cellStyle name="Heading2 2 3" xfId="242" xr:uid="{931BBD26-0875-40EC-8223-06964B522F62}"/>
+    <cellStyle name="Hyperlink 2" xfId="12" xr:uid="{B89A150A-4809-4F99-95CC-C8470FE466C4}"/>
+    <cellStyle name="Hyperlink 2 2" xfId="243" xr:uid="{7F6B461D-9B05-4922-9A81-562153432FCB}"/>
+    <cellStyle name="Hyperlink 2 3" xfId="244" xr:uid="{61EE3882-5038-4715-9C3D-540BFB9F4BEF}"/>
+    <cellStyle name="Hyperlink 2 4" xfId="245" xr:uid="{EA18574B-5723-45C5-9F72-7FDFBEFBA8D5}"/>
+    <cellStyle name="Input 2" xfId="246" xr:uid="{D6CD05AD-2B1F-47ED-9773-A26AECBC3995}"/>
+    <cellStyle name="Linked Cell 2" xfId="247" xr:uid="{7A4FD870-1FDC-46E7-86E8-1D9EE3DCA220}"/>
+    <cellStyle name="Neutral 2" xfId="248" xr:uid="{1045D584-1C81-4256-85B2-2AB2B4F0AD6D}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 10" xfId="249" xr:uid="{E75EB295-36ED-436C-AF18-2B4CB2BC45CA}"/>
+    <cellStyle name="Normal 10 2" xfId="250" xr:uid="{B1FBECCF-07F0-4C75-B841-0AA035E3ED93}"/>
+    <cellStyle name="Normal 10 2 2" xfId="251" xr:uid="{8A952AA4-EC42-4AE6-8728-0C5F01243BAF}"/>
+    <cellStyle name="Normal 10 2 3" xfId="252" xr:uid="{E3BE2D62-6CC4-4F1B-8AE1-2E7945073F2E}"/>
+    <cellStyle name="Normal 10 3" xfId="253" xr:uid="{DFDAFA3C-E1B6-4AFD-AECB-D24F24B71530}"/>
+    <cellStyle name="Normal 10 4" xfId="11" xr:uid="{F1D6F347-6EA2-4B5C-800C-4D95B2BC888B}"/>
+    <cellStyle name="Normal 10 5" xfId="15" xr:uid="{451FB075-F161-4C60-92EE-A14B8BF367E1}"/>
+    <cellStyle name="Normal 11" xfId="254" xr:uid="{F0144E92-5856-469B-B81D-525FA9EFB068}"/>
+    <cellStyle name="Normal 11 2" xfId="255" xr:uid="{AA45B9AE-0C9D-46DB-940C-4B957C9487AE}"/>
+    <cellStyle name="Normal 11 2 2" xfId="256" xr:uid="{C3FEFCEF-C63D-4EAE-B84A-B08F8D3A7E45}"/>
+    <cellStyle name="Normal 11 2 3" xfId="257" xr:uid="{148E602C-35D2-4E89-961A-51A8C1952E34}"/>
+    <cellStyle name="Normal 11 3" xfId="258" xr:uid="{3199E860-9558-401E-9232-39A1848048D9}"/>
+    <cellStyle name="Normal 11 4" xfId="259" xr:uid="{81248AF5-DA84-49FE-BC19-4466FB3C71A7}"/>
+    <cellStyle name="Normal 12" xfId="260" xr:uid="{19758F5C-646F-4AE8-8B57-24FAD681FB07}"/>
+    <cellStyle name="Normal 12 2" xfId="261" xr:uid="{4DE3361E-F3FB-4201-A7CD-AB852251A8F3}"/>
+    <cellStyle name="Normal 12 2 2" xfId="262" xr:uid="{D3D583DC-79C1-48F9-BEAC-A6749D31ED2F}"/>
+    <cellStyle name="Normal 12 2 3" xfId="263" xr:uid="{71ECF31C-33A2-4FB6-A442-50190FE55A0B}"/>
+    <cellStyle name="Normal 12 3" xfId="264" xr:uid="{2ED17272-6DCC-4F2E-9E3B-DC35E9E7323D}"/>
+    <cellStyle name="Normal 12 4" xfId="265" xr:uid="{9E033D21-13D7-4E36-8DC8-01AB0B8F011C}"/>
+    <cellStyle name="Normal 13" xfId="3" xr:uid="{693AAF89-5E45-4889-9A33-29420E29484F}"/>
+    <cellStyle name="Normal 14" xfId="266" xr:uid="{E8BA516A-ECAC-43E5-B810-395E9B0FF48E}"/>
+    <cellStyle name="Normal 14 2" xfId="267" xr:uid="{19088107-96E5-450F-A359-16A7792BBD3A}"/>
+    <cellStyle name="Normal 14 3" xfId="268" xr:uid="{BCE2AA54-090F-449F-99DD-756B188CDCF5}"/>
+    <cellStyle name="Normal 15" xfId="535" xr:uid="{EF577E5C-97D9-4FCF-8A16-14A9CED50A82}"/>
+    <cellStyle name="Normal 16" xfId="1" xr:uid="{D0240B6E-35D4-41A8-A12A-747AB60D5310}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00685942-DAD9-4338-A958-CB8962F51AF3}"/>
+    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{A882DB05-9480-41D4-BF9C-F8DC76457362}"/>
+    <cellStyle name="Normal 2 2 2" xfId="4" xr:uid="{CAAE53BE-9BBC-4C93-9567-66371BA627C2}"/>
+    <cellStyle name="Normal 2 2 2 2" xfId="10" xr:uid="{F55A97E8-23D7-43F2-B27E-A3D03D9B0FC2}"/>
+    <cellStyle name="Normal 2 2 3" xfId="269" xr:uid="{44F8464B-19F9-4614-B926-FDA27F56F2AD}"/>
+    <cellStyle name="Normal 2 2 4" xfId="270" xr:uid="{165D2BE5-3E58-4C28-8129-E17189600A6B}"/>
+    <cellStyle name="Normal 2 3" xfId="271" xr:uid="{478121EA-DDD9-49EA-ADDF-FF9C5CCC9E4C}"/>
+    <cellStyle name="Normal 2 4" xfId="272" xr:uid="{AFC8557B-9612-40C8-A811-BBB0AD8DD415}"/>
+    <cellStyle name="Normal 2 4 2" xfId="273" xr:uid="{E349C70C-B921-4471-8D42-AA38B92CB7B1}"/>
+    <cellStyle name="Normal 2 4 2 2" xfId="274" xr:uid="{D0C47B11-A1DF-4983-8028-7DAF9B54FCCA}"/>
+    <cellStyle name="Normal 2 4 2 2 2" xfId="275" xr:uid="{DC77D229-41E5-4BC9-94B5-292AAE09DFC2}"/>
+    <cellStyle name="Normal 2 4 2 2 3" xfId="276" xr:uid="{2AFF85A2-B4DD-47F9-A9CA-7EA48846B709}"/>
+    <cellStyle name="Normal 2 4 2 3" xfId="277" xr:uid="{D9BF1CF8-3C66-4483-9D27-5A0C8C0B8A3F}"/>
+    <cellStyle name="Normal 2 4 2 4" xfId="278" xr:uid="{0686780C-7FA5-4D7E-94F8-E07F4173F084}"/>
+    <cellStyle name="Normal 2 4 3" xfId="279" xr:uid="{4286A3E7-DA4F-408E-944D-967FA933726E}"/>
+    <cellStyle name="Normal 2 4 3 2" xfId="280" xr:uid="{55163C9C-94C8-45E1-AB43-581DBE789EE3}"/>
+    <cellStyle name="Normal 2 4 3 3" xfId="281" xr:uid="{52EF0827-970E-4984-AFCB-7483EFB5F87B}"/>
+    <cellStyle name="Normal 2 4 4" xfId="282" xr:uid="{CC9993DA-2892-4249-AC13-D2AEA089C804}"/>
+    <cellStyle name="Normal 2 4 5" xfId="283" xr:uid="{F90F6C81-5B60-4095-951A-DFA2DF80BD96}"/>
+    <cellStyle name="Normal 3" xfId="6" xr:uid="{3C860C32-1AFD-4495-BA95-45598854A28E}"/>
+    <cellStyle name="Normal 3 2" xfId="16" xr:uid="{C6C9FC9F-5E4B-4EEF-A8BB-313B6E39035C}"/>
+    <cellStyle name="Normal 3 2 2" xfId="284" xr:uid="{9789F75D-F246-4B74-96F5-A6E77B834C54}"/>
+    <cellStyle name="Normal 3 2 2 2" xfId="285" xr:uid="{A8B52A96-D149-466D-914C-494434515AC3}"/>
+    <cellStyle name="Normal 3 2 3" xfId="286" xr:uid="{DF712B55-1CB0-49B8-9223-AE40D5808AA7}"/>
+    <cellStyle name="Normal 3 2 3 2" xfId="287" xr:uid="{377CC3E1-E020-40B2-AFDD-B239AB4321DA}"/>
+    <cellStyle name="Normal 3 2 4" xfId="288" xr:uid="{E748F44A-37AB-4F50-8E32-59E2672750EB}"/>
+    <cellStyle name="Normal 3 2 4 2" xfId="289" xr:uid="{79AA9733-16E2-42DD-BDC5-ECE355286857}"/>
+    <cellStyle name="Normal 3 2 5" xfId="290" xr:uid="{2FBDEB57-C328-45EC-A83C-419E113A9343}"/>
+    <cellStyle name="Normal 3 2 5 2" xfId="291" xr:uid="{6F69D818-55C3-4643-A07A-460C6B4A9730}"/>
+    <cellStyle name="Normal 3 2 6" xfId="292" xr:uid="{05B2147B-52FE-4CBC-BAAF-FE9B22A550D7}"/>
+    <cellStyle name="Normal 3 2 6 2" xfId="293" xr:uid="{75CDD2B0-2C6E-41B9-AEED-A7E54F7EC6D5}"/>
+    <cellStyle name="Normal 3 2 7" xfId="294" xr:uid="{80FB80BF-0721-457E-AEA3-BF14441C53A8}"/>
+    <cellStyle name="Normal 3 3" xfId="295" xr:uid="{FCBA6B11-E50B-4135-938F-2D2ADBC904CB}"/>
+    <cellStyle name="Normal 3 3 2" xfId="296" xr:uid="{AB42FAF5-10DA-4880-AA97-78CC6F86DF78}"/>
+    <cellStyle name="Normal 3 3 2 2" xfId="297" xr:uid="{1DC3D048-A40F-4BC9-A223-93F1B2954B0D}"/>
+    <cellStyle name="Normal 3 3 2 2 2" xfId="298" xr:uid="{61EF2D25-452D-45B2-9044-236C4862CC4A}"/>
+    <cellStyle name="Normal 3 3 2 2 3" xfId="299" xr:uid="{F48E3B6D-0203-4CA1-97B6-9D91BD8A3786}"/>
+    <cellStyle name="Normal 3 3 2 3" xfId="300" xr:uid="{704AE0F9-FEEE-44F6-BBC2-09654C3D5E76}"/>
+    <cellStyle name="Normal 3 3 2 4" xfId="301" xr:uid="{775B0616-1243-4DCC-8C15-BCFD10CD4BB7}"/>
+    <cellStyle name="Normal 3 3 3" xfId="302" xr:uid="{A9C23275-7408-4C9E-A125-F1E2641FDB2D}"/>
+    <cellStyle name="Normal 3 3 3 2" xfId="303" xr:uid="{00E01EA5-308C-4B0A-AE1D-F37030125805}"/>
+    <cellStyle name="Normal 3 3 3 3" xfId="304" xr:uid="{163EF135-D10A-482E-A553-C3357E16F562}"/>
+    <cellStyle name="Normal 3 3 4" xfId="305" xr:uid="{28403056-E39B-4CF7-A8FC-549B7ACE8427}"/>
+    <cellStyle name="Normal 3 3 5" xfId="306" xr:uid="{0ADB0E92-7DF8-40C9-A6EF-166A8225C976}"/>
+    <cellStyle name="Normal 3 4" xfId="307" xr:uid="{40D14846-F7FE-4695-A69A-F020051167DC}"/>
+    <cellStyle name="Normal 3 4 2" xfId="308" xr:uid="{636808A1-A6DD-4196-A07B-1AFBAC350C7F}"/>
+    <cellStyle name="Normal 3 4 2 2" xfId="309" xr:uid="{99EC6615-2970-485B-B035-7AFEC3F4B314}"/>
+    <cellStyle name="Normal 3 4 2 3" xfId="310" xr:uid="{7E3387BA-0BCA-4037-8448-4BC66254254F}"/>
+    <cellStyle name="Normal 3 4 3" xfId="311" xr:uid="{56B8A307-BB72-485D-A19B-0B675E1E5550}"/>
+    <cellStyle name="Normal 3 4 4" xfId="312" xr:uid="{D9277AD1-62A2-4525-B65B-BD364B05314E}"/>
+    <cellStyle name="Normal 3 5" xfId="313" xr:uid="{DC0EF2B8-57E8-453C-91B4-96A11F15359B}"/>
+    <cellStyle name="Normal 3 5 2" xfId="314" xr:uid="{468E2DB8-8C61-4901-A23A-70372E321F1C}"/>
+    <cellStyle name="Normal 3 5 3" xfId="315" xr:uid="{3E8133C3-743C-49F1-8A8C-3D175D511741}"/>
+    <cellStyle name="Normal 3 6" xfId="13" xr:uid="{AE501094-9899-4E9F-A396-EE3EFE88E649}"/>
+    <cellStyle name="Normal 3 7" xfId="316" xr:uid="{BDFD2824-E5D1-4E82-98B0-3E54DD71D401}"/>
+    <cellStyle name="Normal 3 8" xfId="317" xr:uid="{DC8E1A29-7AE3-4942-9DB9-9EF72B22DF9F}"/>
+    <cellStyle name="Normal 4" xfId="318" xr:uid="{FBE9C717-ADE5-4C72-9137-5CCC3990A029}"/>
+    <cellStyle name="Normal 4 2" xfId="319" xr:uid="{6517F325-D495-412E-B706-73DD89C0CE9A}"/>
+    <cellStyle name="Normal 4 2 2" xfId="14" xr:uid="{5C0C0DF1-1542-4A89-88E5-E2FC5BA1B1E0}"/>
+    <cellStyle name="Normal 4 3" xfId="320" xr:uid="{6DC036B3-76F4-4330-958A-915F3C397946}"/>
+    <cellStyle name="Normal 4 3 2" xfId="321" xr:uid="{349BCF51-2003-4858-9224-56573C6A19A6}"/>
+    <cellStyle name="Normal 4 3 2 2" xfId="322" xr:uid="{322EE34B-E514-470E-A968-6B72DDD22ED6}"/>
+    <cellStyle name="Normal 4 3 2 2 2" xfId="323" xr:uid="{1AE28573-5BB4-4C3D-96BC-26C8309AC8D2}"/>
+    <cellStyle name="Normal 4 3 2 2 2 2" xfId="324" xr:uid="{44AD9C9B-D899-40E0-A6E3-6D9C9C083AD2}"/>
+    <cellStyle name="Normal 4 3 2 2 2 3" xfId="325" xr:uid="{8F9D2563-4F07-4F83-8EB1-40C0C5143A19}"/>
+    <cellStyle name="Normal 4 3 2 2 3" xfId="326" xr:uid="{E939CEB0-0994-45ED-8D81-E0A5B7E5B6FF}"/>
+    <cellStyle name="Normal 4 3 2 2 4" xfId="327" xr:uid="{67379428-83DA-47FD-9DB9-D29076538C17}"/>
+    <cellStyle name="Normal 4 3 2 3" xfId="328" xr:uid="{37FDB980-3EB2-437B-B555-7B55C2F38223}"/>
+    <cellStyle name="Normal 4 3 2 3 2" xfId="329" xr:uid="{203ACD02-9BDA-4748-945E-C18760D397B5}"/>
+    <cellStyle name="Normal 4 3 2 3 3" xfId="330" xr:uid="{028CCE86-A517-4FF9-9C0D-5EE85A3D1B76}"/>
+    <cellStyle name="Normal 4 3 2 4" xfId="331" xr:uid="{FDC6163C-3DA9-4737-A823-B56F1BFC2FF1}"/>
+    <cellStyle name="Normal 4 3 2 5" xfId="332" xr:uid="{D370EA63-643A-4793-BA38-9CCFC436BE88}"/>
+    <cellStyle name="Normal 4 3 3" xfId="333" xr:uid="{E5A9C162-5A97-4BC1-8551-7A4EDB77C8E3}"/>
+    <cellStyle name="Normal 4 3 3 2" xfId="334" xr:uid="{2AD5C3B0-3566-4DEE-B240-9B6682B8E526}"/>
+    <cellStyle name="Normal 4 3 3 2 2" xfId="335" xr:uid="{DD7575BD-E0B6-4C08-AFA7-4AC001625413}"/>
+    <cellStyle name="Normal 4 3 3 2 3" xfId="336" xr:uid="{5D68E0FF-025C-4CD9-9E73-904A3B25676F}"/>
+    <cellStyle name="Normal 4 3 3 3" xfId="337" xr:uid="{55529725-7D98-4474-852B-6B7513DE400F}"/>
+    <cellStyle name="Normal 4 3 3 4" xfId="338" xr:uid="{17FE5811-A3C6-4B3C-AB69-DF46565FFCA1}"/>
+    <cellStyle name="Normal 4 3 4" xfId="339" xr:uid="{2B7DF7DA-A505-4798-B469-23255F93E6C3}"/>
+    <cellStyle name="Normal 4 3 4 2" xfId="340" xr:uid="{585E8A8A-6A34-48A8-92C4-8C9C74474955}"/>
+    <cellStyle name="Normal 4 3 4 3" xfId="341" xr:uid="{D22ED931-F4C2-4192-9871-6D0C7578DF60}"/>
+    <cellStyle name="Normal 4 3 5" xfId="342" xr:uid="{6D893D61-DD71-4FEB-A36E-103AFB4CA0D9}"/>
+    <cellStyle name="Normal 4 3 6" xfId="343" xr:uid="{9F703583-3607-4275-A7BD-C2BFF27CB45C}"/>
+    <cellStyle name="Normal 4 4" xfId="344" xr:uid="{5912331C-BA45-4DA2-918C-72933A1A9B5D}"/>
+    <cellStyle name="Normal 4 4 2" xfId="345" xr:uid="{12C818FE-2D0C-470B-B4E5-04FEED542C39}"/>
+    <cellStyle name="Normal 4 4 2 2" xfId="346" xr:uid="{EC9BA6F8-90F5-4351-9A54-F27FAAD1CB2A}"/>
+    <cellStyle name="Normal 4 4 2 2 2" xfId="347" xr:uid="{433C7BAC-2397-4FE7-8E3F-587A7BFEF0CD}"/>
+    <cellStyle name="Normal 4 4 2 2 3" xfId="348" xr:uid="{32D916EB-2F71-4F60-97D2-8461FC02799E}"/>
+    <cellStyle name="Normal 4 4 2 3" xfId="349" xr:uid="{41D2E069-02FA-4FFF-9D0E-A31F145C4FC0}"/>
+    <cellStyle name="Normal 4 4 2 4" xfId="350" xr:uid="{A9E8354E-1D89-41C2-9A1F-19937D160A9F}"/>
+    <cellStyle name="Normal 4 4 3" xfId="351" xr:uid="{CB855032-3C06-4496-BAD3-B92A66B93189}"/>
+    <cellStyle name="Normal 4 4 3 2" xfId="352" xr:uid="{EBC4EE92-550B-4F25-AD03-B118642C965E}"/>
+    <cellStyle name="Normal 4 4 3 3" xfId="353" xr:uid="{AA027381-41EE-481B-9674-5419B9D5F40F}"/>
+    <cellStyle name="Normal 4 4 4" xfId="354" xr:uid="{58B6C528-1A34-4B19-AC5A-BDBD05EA8746}"/>
+    <cellStyle name="Normal 4 4 5" xfId="355" xr:uid="{34EF333D-8B92-4B3C-A827-F397492024B5}"/>
+    <cellStyle name="Normal 4 5" xfId="356" xr:uid="{D2743DDF-9B4F-4073-ACA4-9E3695E1C684}"/>
+    <cellStyle name="Normal 4 5 2" xfId="357" xr:uid="{33EE09BC-A45C-4FE9-942C-9B3171A531BE}"/>
+    <cellStyle name="Normal 4 5 2 2" xfId="358" xr:uid="{450955CC-A831-419A-8248-B19FE8638FE2}"/>
+    <cellStyle name="Normal 4 5 2 3" xfId="359" xr:uid="{3443817C-9ABA-4308-B98A-E04A67EAAB2E}"/>
+    <cellStyle name="Normal 4 5 3" xfId="360" xr:uid="{1AB898CA-CCD3-4D6D-A216-C8418CA11D44}"/>
+    <cellStyle name="Normal 4 5 4" xfId="361" xr:uid="{91C35050-EA49-42E8-8071-F1A1A67E90BC}"/>
+    <cellStyle name="Normal 4 6" xfId="362" xr:uid="{23201C4A-3F3B-428E-82B1-680D222AEE3E}"/>
+    <cellStyle name="Normal 4 6 2" xfId="363" xr:uid="{994CA1F6-CF76-44F1-BCBB-7C9BA49D7FD6}"/>
+    <cellStyle name="Normal 4 6 3" xfId="364" xr:uid="{6729614C-407F-4850-B9F7-FFC8085430A0}"/>
+    <cellStyle name="Normal 4 7" xfId="365" xr:uid="{56BDC13C-59AE-4DA2-A9B4-F17AD80E359E}"/>
+    <cellStyle name="Normal 4 8" xfId="366" xr:uid="{1C8825BF-EDF7-4239-AE90-C041BCD62439}"/>
+    <cellStyle name="Normal 5" xfId="367" xr:uid="{7E82AA8A-98B1-418B-9497-8150812D0B7F}"/>
+    <cellStyle name="Normal 5 2" xfId="368" xr:uid="{00C9ADF6-235F-4B8C-A4DD-A58E4337AF74}"/>
+    <cellStyle name="Normal 5 2 2" xfId="369" xr:uid="{18345667-20A6-42D5-8E7E-F8D87D1C8E91}"/>
+    <cellStyle name="Normal 5 2 2 2" xfId="370" xr:uid="{CE7015DD-3E82-4D68-8A61-BDB8817F4247}"/>
+    <cellStyle name="Normal 5 2 2 2 2" xfId="371" xr:uid="{2414C82C-447C-4153-ABCC-26DB72212E76}"/>
+    <cellStyle name="Normal 5 2 2 2 2 2" xfId="372" xr:uid="{37A9AD0C-FD6A-4BE2-967A-2862EBBAB792}"/>
+    <cellStyle name="Normal 5 2 2 2 2 3" xfId="373" xr:uid="{7CF79685-F0AF-4962-9E03-15888478798F}"/>
+    <cellStyle name="Normal 5 2 2 2 3" xfId="374" xr:uid="{6F2D5C9D-0C39-45B6-BBEB-4F5374FD1DA3}"/>
+    <cellStyle name="Normal 5 2 2 2 4" xfId="375" xr:uid="{A40D471D-AA98-4F13-9AC5-C416DA8F5C33}"/>
+    <cellStyle name="Normal 5 2 2 3" xfId="376" xr:uid="{095ACE98-361E-4C6F-B1EF-A8A0779F8BF7}"/>
+    <cellStyle name="Normal 5 2 2 3 2" xfId="377" xr:uid="{5AB5496D-620D-4561-B38E-D11EC20654DA}"/>
+    <cellStyle name="Normal 5 2 2 3 3" xfId="378" xr:uid="{23C49D73-E7C2-4D99-B0D5-CD99D87DDD5E}"/>
+    <cellStyle name="Normal 5 2 2 4" xfId="379" xr:uid="{E27694EC-3FA3-4E87-8D00-1AABB397B872}"/>
+    <cellStyle name="Normal 5 2 2 5" xfId="380" xr:uid="{D7065C1A-0A2C-4186-8C9C-DA367D0EF8E7}"/>
+    <cellStyle name="Normal 5 2 3" xfId="381" xr:uid="{80FC1F18-BCA5-44A8-8452-BE02D55306CC}"/>
+    <cellStyle name="Normal 5 2 3 2" xfId="382" xr:uid="{95EC3EF0-5108-4AAA-8363-220A87F5E541}"/>
+    <cellStyle name="Normal 5 2 3 2 2" xfId="383" xr:uid="{B29AC855-8ECC-4325-899F-037213FF442E}"/>
+    <cellStyle name="Normal 5 2 3 2 3" xfId="384" xr:uid="{50749DE2-081C-4FAF-96FE-68BA2DE5D288}"/>
+    <cellStyle name="Normal 5 2 3 3" xfId="385" xr:uid="{336336EB-F1EC-45B6-B232-A9B5C062D106}"/>
+    <cellStyle name="Normal 5 2 3 4" xfId="386" xr:uid="{8A2E1128-AC1E-4089-8B85-1557498C9440}"/>
+    <cellStyle name="Normal 5 2 4" xfId="387" xr:uid="{ADB8E07E-CEDC-4C66-9C04-D2359F853440}"/>
+    <cellStyle name="Normal 5 2 4 2" xfId="388" xr:uid="{994706E4-E0CA-418F-9B70-32C5B4EAC41F}"/>
+    <cellStyle name="Normal 5 2 4 3" xfId="389" xr:uid="{FA0EBA0A-FB30-4A08-ABC3-2E0F8115F5C1}"/>
+    <cellStyle name="Normal 5 2 5" xfId="390" xr:uid="{D4BE914A-617C-407A-93CB-E94352C1B88F}"/>
+    <cellStyle name="Normal 5 2 6" xfId="391" xr:uid="{D10227E7-D6D7-4D7E-BED1-FDE36138BC71}"/>
+    <cellStyle name="Normal 5 3" xfId="392" xr:uid="{A4927E65-661C-49BB-A7D8-DD9FEB5A137B}"/>
+    <cellStyle name="Normal 5 3 2" xfId="393" xr:uid="{4D14722D-FEC1-4585-ADF7-738CC516E360}"/>
+    <cellStyle name="Normal 5 3 2 2" xfId="394" xr:uid="{72793141-B971-43A8-B0BD-7130EBD33474}"/>
+    <cellStyle name="Normal 5 3 2 2 2" xfId="395" xr:uid="{A7513315-859F-42F1-940C-7D1B2163DD3A}"/>
+    <cellStyle name="Normal 5 3 2 2 3" xfId="396" xr:uid="{FAA0272B-7CF3-46BB-9452-E12EA134E236}"/>
+    <cellStyle name="Normal 5 3 2 3" xfId="397" xr:uid="{32D4AC18-5C9B-4A6F-A763-AC2E801FD2A6}"/>
+    <cellStyle name="Normal 5 3 2 4" xfId="398" xr:uid="{E7737657-A71F-4C26-8292-0A01E50C3B3F}"/>
+    <cellStyle name="Normal 5 3 3" xfId="399" xr:uid="{341A3BDF-F58C-4939-A95D-670C2DB79D94}"/>
+    <cellStyle name="Normal 5 3 3 2" xfId="400" xr:uid="{535D1B67-769F-4772-A855-EB7ED1D7CCC1}"/>
+    <cellStyle name="Normal 5 3 3 3" xfId="401" xr:uid="{143AA1B3-ABF8-4999-89AE-11E17CEE6CFD}"/>
+    <cellStyle name="Normal 5 3 4" xfId="402" xr:uid="{DC04E3EE-9E6F-46D4-A2A7-631E475969CF}"/>
+    <cellStyle name="Normal 5 3 5" xfId="403" xr:uid="{17164CA4-29C1-4ADE-8B31-95E950A5A1E5}"/>
+    <cellStyle name="Normal 5 4" xfId="404" xr:uid="{83AECD3D-3E2F-4920-952F-E8388FB40AD0}"/>
+    <cellStyle name="Normal 5 4 2" xfId="405" xr:uid="{D9758FCE-C1BB-401A-ACCD-583914A2898D}"/>
+    <cellStyle name="Normal 5 4 2 2" xfId="406" xr:uid="{619AF519-1F95-4B61-ABBC-C743AFA1A02F}"/>
+    <cellStyle name="Normal 5 4 2 3" xfId="407" xr:uid="{F7065290-AB64-4048-9D80-44C6527AB187}"/>
+    <cellStyle name="Normal 5 4 3" xfId="408" xr:uid="{72D8535A-FFD7-4FD0-A79C-01C622B9DF29}"/>
+    <cellStyle name="Normal 5 4 4" xfId="409" xr:uid="{BD42A764-B356-40C1-9803-CAFB90AD4921}"/>
+    <cellStyle name="Normal 5 5" xfId="410" xr:uid="{E9403176-C010-41A9-A6F8-AEB36F7143F4}"/>
+    <cellStyle name="Normal 5 5 2" xfId="411" xr:uid="{C8ABF7C0-936E-4333-9BBA-6A02CADABB84}"/>
+    <cellStyle name="Normal 5 5 3" xfId="412" xr:uid="{B4E5D10D-3C4D-42BC-AE71-D4E9C5FB0C2B}"/>
+    <cellStyle name="Normal 5 6" xfId="413" xr:uid="{3CD049FB-2C1E-410B-BB4B-74785EAA3814}"/>
+    <cellStyle name="Normal 5 6 2" xfId="414" xr:uid="{88F99117-C327-4C91-9CFE-BCCFE472AAE2}"/>
+    <cellStyle name="Normal 5 6 3" xfId="415" xr:uid="{D13C17FF-750F-4D72-927B-686BBB38FFDB}"/>
+    <cellStyle name="Normal 5 7" xfId="416" xr:uid="{79476729-49AA-41FE-AFF4-489F46E52D0E}"/>
+    <cellStyle name="Normal 5 8" xfId="417" xr:uid="{0004AA28-691E-4217-94DD-C5354776FD88}"/>
+    <cellStyle name="Normal 6" xfId="418" xr:uid="{8DEECFD6-E837-491C-AD81-9D96B5A4F8F5}"/>
+    <cellStyle name="Normal 6 2" xfId="419" xr:uid="{F6D7B461-9998-420E-B4E9-76D0F14F6C07}"/>
+    <cellStyle name="Normal 6 2 2" xfId="420" xr:uid="{72848B8C-65E6-4E12-A598-832698643B0D}"/>
+    <cellStyle name="Normal 6 2 2 2" xfId="421" xr:uid="{E45E1C98-304B-4C10-9350-9203086FB28B}"/>
+    <cellStyle name="Normal 6 2 2 2 2" xfId="422" xr:uid="{E0373319-70C3-4655-B88A-EE7FD748F35D}"/>
+    <cellStyle name="Normal 6 2 2 2 2 2" xfId="423" xr:uid="{095140BE-CE19-4FE4-B6B1-D61B6CFA58E1}"/>
+    <cellStyle name="Normal 6 2 2 2 2 3" xfId="424" xr:uid="{70FB757F-99E4-4822-885B-FCC6CA4EB178}"/>
+    <cellStyle name="Normal 6 2 2 2 3" xfId="425" xr:uid="{A19F8F6A-A2EA-4136-A931-0FD1FF37A321}"/>
+    <cellStyle name="Normal 6 2 2 2 4" xfId="426" xr:uid="{AB1BDD49-EA2B-47E2-A992-E9687F9C38CF}"/>
+    <cellStyle name="Normal 6 2 2 3" xfId="427" xr:uid="{BEBED7C2-5082-4A9B-9EE7-335FC6269088}"/>
+    <cellStyle name="Normal 6 2 2 3 2" xfId="428" xr:uid="{57FD5061-4725-4093-B775-DE7B4EEE7A3A}"/>
+    <cellStyle name="Normal 6 2 2 3 3" xfId="429" xr:uid="{724C0ADD-7238-4EC0-8410-22B35CBE4EBB}"/>
+    <cellStyle name="Normal 6 2 2 4" xfId="430" xr:uid="{DE8C0DDE-945D-4FE7-A1B4-9E1FF0D54E9B}"/>
+    <cellStyle name="Normal 6 2 2 5" xfId="431" xr:uid="{B92FD225-6D75-4964-BE97-710CC471D150}"/>
+    <cellStyle name="Normal 6 2 3" xfId="432" xr:uid="{48A9C019-003F-4976-92CB-8040BCFAEDFB}"/>
+    <cellStyle name="Normal 6 2 3 2" xfId="433" xr:uid="{DC6F34DE-232A-42D5-98DB-BBC7299122B4}"/>
+    <cellStyle name="Normal 6 2 3 2 2" xfId="434" xr:uid="{A514D7F7-84AA-4ABF-B54E-118215B56216}"/>
+    <cellStyle name="Normal 6 2 3 2 3" xfId="435" xr:uid="{1CA0C250-63FF-4287-9C47-3E997639C2CE}"/>
+    <cellStyle name="Normal 6 2 3 3" xfId="436" xr:uid="{58FAC02E-B045-447A-BF8E-40AD9FFF7C9E}"/>
+    <cellStyle name="Normal 6 2 3 4" xfId="437" xr:uid="{B2C4A126-7E8C-4429-938E-A9277DEFCBA6}"/>
+    <cellStyle name="Normal 6 2 4" xfId="438" xr:uid="{3CF5B5A0-BAB2-4C6E-ABD2-DFB4A0B7CFCE}"/>
+    <cellStyle name="Normal 6 2 4 2" xfId="439" xr:uid="{81B803EF-1D07-424E-A419-3DA6460645BC}"/>
+    <cellStyle name="Normal 6 2 4 3" xfId="440" xr:uid="{B9D6BA33-C6B4-4AF0-9568-F99D1DCD54DB}"/>
+    <cellStyle name="Normal 6 2 5" xfId="441" xr:uid="{EDFE76DA-FB33-40CD-B79A-000DED367F94}"/>
+    <cellStyle name="Normal 6 2 6" xfId="442" xr:uid="{A53470BA-5E0C-4069-B2E0-6DE711E971F4}"/>
+    <cellStyle name="Normal 6 3" xfId="443" xr:uid="{EC7669B5-25DE-4DA1-8427-BB3DDFEE2CF0}"/>
+    <cellStyle name="Normal 6 3 2" xfId="444" xr:uid="{0A2BC3C3-3119-42C0-8F44-121A5330CC1E}"/>
+    <cellStyle name="Normal 6 3 2 2" xfId="445" xr:uid="{3834A924-92A9-4AB9-B557-AD1206D33FCA}"/>
+    <cellStyle name="Normal 6 3 2 2 2" xfId="446" xr:uid="{B6E6FCB6-84C0-4508-B348-BF102265889C}"/>
+    <cellStyle name="Normal 6 3 2 2 3" xfId="447" xr:uid="{CCFE7184-D66F-462F-B494-CF21BA56B083}"/>
+    <cellStyle name="Normal 6 3 2 3" xfId="448" xr:uid="{C992BA41-B74A-4F1D-AC0A-35C2BF031A8D}"/>
+    <cellStyle name="Normal 6 3 2 4" xfId="449" xr:uid="{765E8C5A-8F81-4864-9B55-ADDC899CEF9E}"/>
+    <cellStyle name="Normal 6 3 3" xfId="450" xr:uid="{132B5EB3-DE9D-4173-A04D-B57A78A6641B}"/>
+    <cellStyle name="Normal 6 3 3 2" xfId="451" xr:uid="{F402C7F6-6583-41CF-9C89-4CF9C6100528}"/>
+    <cellStyle name="Normal 6 3 3 3" xfId="452" xr:uid="{C2A8E1C7-D515-46BB-8051-D3740419230B}"/>
+    <cellStyle name="Normal 6 3 4" xfId="453" xr:uid="{517AD640-799E-4B7E-8F7A-D8146A54BA87}"/>
+    <cellStyle name="Normal 6 3 5" xfId="454" xr:uid="{3C8F1433-CCB2-4A77-87BD-3561E6A6C48D}"/>
+    <cellStyle name="Normal 6 4" xfId="455" xr:uid="{0BBF8D9F-E985-4A84-A548-33F173E88508}"/>
+    <cellStyle name="Normal 6 4 2" xfId="456" xr:uid="{0246973E-A95C-427E-B491-037E58E47522}"/>
+    <cellStyle name="Normal 6 4 2 2" xfId="457" xr:uid="{EA3A650E-79E0-4054-BF42-C88A7A2A46D6}"/>
+    <cellStyle name="Normal 6 4 2 3" xfId="458" xr:uid="{AB70180D-14B2-4A04-A5C6-0F4EF751E3C3}"/>
+    <cellStyle name="Normal 6 4 3" xfId="459" xr:uid="{862110A5-C458-490B-B092-B9A66CAAFC6C}"/>
+    <cellStyle name="Normal 6 4 4" xfId="460" xr:uid="{68B31236-4D10-4FFD-9E6B-0BBF9309DD9A}"/>
+    <cellStyle name="Normal 6 5" xfId="461" xr:uid="{0D604EAF-3132-4685-984B-478E4C5A4AF2}"/>
+    <cellStyle name="Normal 6 5 2" xfId="462" xr:uid="{8C10D937-97A6-43E4-9201-20C90E4D44A3}"/>
+    <cellStyle name="Normal 6 5 3" xfId="463" xr:uid="{DD1CC9EC-85AB-4A4F-9262-E95DFE29D022}"/>
+    <cellStyle name="Normal 6 6" xfId="464" xr:uid="{41151079-25CB-4490-B458-B19EE8824E40}"/>
+    <cellStyle name="Normal 6 7" xfId="465" xr:uid="{600E9178-FCF6-432E-BA74-9D384F9A24CF}"/>
+    <cellStyle name="Normal 6 8" xfId="466" xr:uid="{A2F9302D-E19D-4A5C-A0B0-D12C1ADBD136}"/>
+    <cellStyle name="Normal 7" xfId="467" xr:uid="{BD7512BB-6291-4230-A566-39CFA2830836}"/>
+    <cellStyle name="Normal 7 2" xfId="468" xr:uid="{1E7E18A6-8A03-49E9-9AF2-71E5095A2273}"/>
+    <cellStyle name="Normal 7 2 2" xfId="469" xr:uid="{AA742E4B-7D05-452D-8395-0E07BC7FA27C}"/>
+    <cellStyle name="Normal 7 2 2 2" xfId="470" xr:uid="{AED0ABAC-6F95-4913-84E2-B8C6A26671A7}"/>
+    <cellStyle name="Normal 7 2 2 3" xfId="471" xr:uid="{7160F059-19EB-45D7-A8F8-89729C7A7B67}"/>
+    <cellStyle name="Normal 7 2 3" xfId="472" xr:uid="{2CE70FF3-821D-4744-A3BD-D71241F1FAB4}"/>
+    <cellStyle name="Normal 7 2 4" xfId="473" xr:uid="{8AFA7A78-E649-4710-956B-B96DAD7F2D56}"/>
+    <cellStyle name="Normal 7 3" xfId="474" xr:uid="{97360CD3-F295-4B28-9910-CB497F94E445}"/>
+    <cellStyle name="Normal 7 3 2" xfId="475" xr:uid="{0D5EE3EC-6FB9-4376-AA89-6B0CFA1077A5}"/>
+    <cellStyle name="Normal 7 3 3" xfId="476" xr:uid="{303E26FD-0531-456C-9F62-A1A736783E51}"/>
+    <cellStyle name="Normal 7 4" xfId="477" xr:uid="{9B73BC7F-2A97-42BB-9234-A4ADDD890F4E}"/>
+    <cellStyle name="Normal 7 5" xfId="478" xr:uid="{4BFDC954-57AB-44FC-AA0E-D0AF0693A39D}"/>
+    <cellStyle name="Normal 8" xfId="479" xr:uid="{BE20F47F-1E94-497A-A2CF-0D17D475151E}"/>
+    <cellStyle name="Normal 9" xfId="480" xr:uid="{D84DACC9-F78A-42D4-9C4E-5B2634419E82}"/>
+    <cellStyle name="Normal 9 2" xfId="481" xr:uid="{A3BEEBFD-4211-4680-AF94-D000106555A0}"/>
+    <cellStyle name="Normale_B2020" xfId="534" xr:uid="{82FF9BC4-A086-4193-ABE5-C49B6460E554}"/>
+    <cellStyle name="Note 2" xfId="482" xr:uid="{A28CA507-023E-48F4-A721-BB1B04639E45}"/>
+    <cellStyle name="Note 2 2" xfId="483" xr:uid="{027D9A9E-36A3-4E5C-88E5-9AEBED4CFB5B}"/>
+    <cellStyle name="Note 2 2 2" xfId="484" xr:uid="{819108E5-9F07-4F04-A00A-A0C63125CF1B}"/>
+    <cellStyle name="Note 2 2 3" xfId="485" xr:uid="{885EF344-B911-4B2F-8AD5-FF603ABBCBFE}"/>
+    <cellStyle name="Note 3" xfId="486" xr:uid="{92ECD21D-E136-42FC-962F-AB2E11B59A1D}"/>
+    <cellStyle name="Note 3 2" xfId="487" xr:uid="{B2203E26-EB81-4403-9918-563902D32C0A}"/>
+    <cellStyle name="Note 3 2 2" xfId="488" xr:uid="{526E2384-40E6-4666-A630-9CC89C075EA4}"/>
+    <cellStyle name="Note 3 2 3" xfId="489" xr:uid="{FB4F434C-C67D-47CF-B645-B78AB2F1BA5A}"/>
+    <cellStyle name="Note 3 3" xfId="490" xr:uid="{46162079-A026-4A5B-899D-94E1C156E7E3}"/>
+    <cellStyle name="Note 3 4" xfId="491" xr:uid="{3862EA86-89B6-4C9B-8038-BDC7BF1FCEAA}"/>
+    <cellStyle name="Output 2" xfId="492" xr:uid="{6D50B91C-34F4-4073-8EAF-4EB5BE81C2AD}"/>
+    <cellStyle name="Parent row" xfId="493" xr:uid="{EE039163-66E5-41CC-AE5B-B638D4482E4E}"/>
+    <cellStyle name="Percent 2" xfId="494" xr:uid="{8770AE7A-C0B8-4655-9EB9-08F6DA0BFBCC}"/>
+    <cellStyle name="Percent 2 2" xfId="495" xr:uid="{A6834C5D-9113-4196-804A-45002B4A786B}"/>
+    <cellStyle name="Percent 3" xfId="9" xr:uid="{C449B567-5E31-4929-A7D7-F2E56365C463}"/>
+    <cellStyle name="Percent 3 2" xfId="496" xr:uid="{1A9335C7-7795-45BA-80F3-5BAA38DD9E26}"/>
+    <cellStyle name="Percent 3 2 2" xfId="497" xr:uid="{0B0A300C-63C4-45F3-A8F4-B997E1550703}"/>
+    <cellStyle name="Percent 3 2 2 2" xfId="498" xr:uid="{575CD159-B3B8-4217-B588-4D40E2116419}"/>
+    <cellStyle name="Percent 3 3" xfId="499" xr:uid="{469392EF-3307-426F-9B7B-0926DEFAD654}"/>
+    <cellStyle name="Percent 3 3 2" xfId="500" xr:uid="{C687B79C-C40A-4F99-A80B-E83FB6A44D73}"/>
+    <cellStyle name="Percent 3 4" xfId="501" xr:uid="{F635EA12-553F-495B-9A1B-B98F4BF02274}"/>
+    <cellStyle name="Percent 3 4 2" xfId="502" xr:uid="{AD1F55F7-F13B-4A57-A579-ED3F4CD3FE3E}"/>
+    <cellStyle name="Percent 4" xfId="503" xr:uid="{64F42622-16CB-4635-80A9-7AFA790BCAB1}"/>
+    <cellStyle name="Percent 4 2" xfId="504" xr:uid="{DCA89D2A-F5CF-4851-9922-8A3014A42047}"/>
+    <cellStyle name="Percent 4 3" xfId="505" xr:uid="{6754EBEA-9895-4664-94A7-BAECD9F30A92}"/>
+    <cellStyle name="Percent 4 3 2" xfId="506" xr:uid="{32F491D1-546F-457F-B2CC-538EF7BF8C09}"/>
+    <cellStyle name="Percent 4 3 3" xfId="507" xr:uid="{6C67D5F0-6F90-4F65-A834-45192E7218CA}"/>
+    <cellStyle name="Percent 5" xfId="508" xr:uid="{0C88B966-AB4C-4135-B477-8E142D47F01E}"/>
+    <cellStyle name="Percent 5 2" xfId="509" xr:uid="{DFB448FD-8362-4CF8-93DF-0C2784C0977B}"/>
+    <cellStyle name="Percent 5 2 2" xfId="510" xr:uid="{435A18DF-C5B1-40B7-B7A7-02C48686F232}"/>
+    <cellStyle name="Percent 5 2 3" xfId="511" xr:uid="{8FE72C83-E0B2-4761-A08C-D78736024022}"/>
+    <cellStyle name="Percent 5 3" xfId="512" xr:uid="{29928452-D51E-495F-8983-B89A5C752B10}"/>
+    <cellStyle name="Percent 5 4" xfId="513" xr:uid="{AABCB982-264D-426F-9429-D872206C306A}"/>
+    <cellStyle name="Percent 5 5" xfId="514" xr:uid="{80BB5DA4-43E6-4C64-8366-763BF1756277}"/>
+    <cellStyle name="Percent 6" xfId="515" xr:uid="{8CEADDF6-5D5B-48BF-A438-81FE8D8A2D05}"/>
+    <cellStyle name="Percent 6 2" xfId="516" xr:uid="{96AAE8E7-4843-49C9-8302-3FFFD402F0F9}"/>
+    <cellStyle name="Percent 6 2 2" xfId="517" xr:uid="{21259C3A-8091-4E56-95B9-8493C877D1AA}"/>
+    <cellStyle name="Percent 6 2 3" xfId="518" xr:uid="{71EA42FA-A847-47C8-897C-8BF778377379}"/>
+    <cellStyle name="Percent 6 3" xfId="519" xr:uid="{63CDAF27-A707-4AD1-BB5B-A817B2AD1A54}"/>
+    <cellStyle name="Percent 6 4" xfId="520" xr:uid="{3358A871-97F5-4AF9-926E-722150F158C6}"/>
+    <cellStyle name="Percent 7" xfId="521" xr:uid="{2D2006FE-6B15-4FF0-BACD-32CEA3BC0DFB}"/>
+    <cellStyle name="Percent 8" xfId="522" xr:uid="{635C9EF0-CE1E-46B2-B715-CBCB91BF0AB2}"/>
+    <cellStyle name="Percent 8 2" xfId="523" xr:uid="{58886E39-3BF1-4D65-83D0-0ACE8E995004}"/>
+    <cellStyle name="Percent 8 3" xfId="524" xr:uid="{CC0D4BAA-FBC5-4B80-B49C-E3FD067FFE59}"/>
+    <cellStyle name="Percent 9" xfId="533" xr:uid="{E8636AB8-3638-4A25-B2C8-C14F9EBA3478}"/>
+    <cellStyle name="Title 2" xfId="525" xr:uid="{59E88359-C580-4A1D-A360-8F925A3EB991}"/>
+    <cellStyle name="Title 3" xfId="526" xr:uid="{5E63EB0C-55C1-49E3-816D-5AD765EA5294}"/>
+    <cellStyle name="Total 2" xfId="527" xr:uid="{4C2E833D-D9D5-48C9-ACF0-5F51AE20437E}"/>
+    <cellStyle name="Total 2 2" xfId="528" xr:uid="{26F9D878-D8A8-4448-916B-B62EBFEC0400}"/>
+    <cellStyle name="Total 2 3" xfId="529" xr:uid="{02CDC54C-C1C3-4DDF-95CE-3920AE39A468}"/>
+    <cellStyle name="Total 3" xfId="530" xr:uid="{83AB8DB8-CCFE-4AB1-9C93-37D5DF16D75C}"/>
+    <cellStyle name="Total 4" xfId="531" xr:uid="{3AC170DB-963E-4C8F-BB3B-1749B94D0AD4}"/>
+    <cellStyle name="Warning Text 2" xfId="532" xr:uid="{8FCE6AFA-C168-4998-A338-7BF3B54DB3A4}"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{E2350C0A-7BC2-4891-BDA9-FE4FC79AEDF2}">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -932,6 +2743,73 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="EB"/>
+      <sheetName val="SETUP"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="Commodities"/>
+      <sheetName val="CommData"/>
+      <sheetName val="Processes"/>
+      <sheetName val="ProcData_Conventional"/>
+      <sheetName val="ProcData_Renewables"/>
+      <sheetName val="ProcData_CHP"/>
+      <sheetName val="ProcData_HPL"/>
+      <sheetName val="ProcData_XPRC"/>
+      <sheetName val="EPA-Coal"/>
+      <sheetName val="EPA-Renew"/>
+      <sheetName val="EPA-Other"/>
+      <sheetName val="EPA-CHP"/>
+      <sheetName val="Non-EPA"/>
+      <sheetName val="DEA-CHP"/>
+      <sheetName val="DEA-HPL"/>
+      <sheetName val="DEA_CHP"/>
+      <sheetName val="DEA_DHP"/>
+      <sheetName val="ProcessCharac_CoalResidCntrl"/>
+      <sheetName val="Emission"/>
+      <sheetName val="ProcessCharac_IntELC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2">
+            <v>2015</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1268,31 +3146,25 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="Z26" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+  <threadedComment ref="Z24" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
     <text>Miks daynite (hydro samuti)</text>
   </threadedComment>
-  <threadedComment ref="F35" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
+  <threadedComment ref="F33" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
     <text>Iru produces only 17 MW in 2025 not 0.207 GW</text>
   </threadedComment>
-  <threadedComment ref="B36" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
+  <threadedComment ref="B34" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
     <text>TODO: set their actual start date and then add how much they produce in 2025</text>
   </threadedComment>
   <threadedComment ref="P39" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
     <text xml:space="preserve">NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)
 </text>
   </threadedComment>
-  <threadedComment ref="S43" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
-    <text>Took same as chp</text>
-  </threadedComment>
-  <threadedComment ref="E44" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
+  <threadedComment ref="E42" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
     <text xml:space="preserve">Ei tea
 </text>
   </threadedComment>
-  <threadedComment ref="J78" dT="2026-01-27T14:26:51.36" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{3057E3B1-7BF3-4718-B31B-0585028D4313}">
-    <text>From 9,24 to 6</text>
-  </threadedComment>
-  <threadedComment ref="U81" dT="2026-01-28T08:41:02.80" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{1905391B-2A5F-4643-B2AC-720AD8410CDA}">
-    <text>Frequency reserve</text>
+  <threadedComment ref="S43" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+    <text>Took same as chp</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -1309,10 +3181,10 @@
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="N9" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
@@ -1338,48 +3210,48 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="J10" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="K10" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="L10" t="s">
         <v>10</v>
       </c>
       <c r="N10" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="R10" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="S10" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="T10" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13">
         <v>0.52272499999999988</v>
@@ -1397,7 +3269,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J13" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1406,36 +3278,36 @@
         <v>20</v>
       </c>
       <c r="N13" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O13" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="P13" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="Q13" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R13" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S13" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="T13" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14">
         <v>0.52272499999999988</v>
@@ -1453,7 +3325,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J14" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1462,36 +3334,36 @@
         <v>20</v>
       </c>
       <c r="N14" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O14" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="Q14" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R14" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S14" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="T14" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E15">
         <v>0.28982625000000001</v>
@@ -1509,7 +3381,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -1518,36 +3390,36 @@
         <v>20</v>
       </c>
       <c r="N15" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O15" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="Q15" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R15" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S15" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="T15" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E16">
         <v>0.38753750000000003</v>
@@ -1565,7 +3437,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1574,36 +3446,36 @@
         <v>20</v>
       </c>
       <c r="N16" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O16" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="P16" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="Q16" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R16" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S16" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="T16" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17">
         <v>0.31543749999999998</v>
@@ -1621,7 +3493,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -1630,25 +3502,25 @@
         <v>20</v>
       </c>
       <c r="N17" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O17" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="P17" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="Q17" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R17" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S17" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="T17" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1671,10 +3543,10 @@
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="N9" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
@@ -1688,10 +3560,10 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
@@ -1712,36 +3584,36 @@
         <v>11</v>
       </c>
       <c r="N10" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="O10" t="s">
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="R10" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="S10" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="T10" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11">
         <v>2028</v>
@@ -1765,36 +3637,36 @@
         <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O11" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="P11" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="Q11" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R11" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S11" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="T11" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12">
         <v>2025</v>
@@ -1818,36 +3690,36 @@
         <v>50</v>
       </c>
       <c r="N12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O12" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="P12" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="Q12" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R12" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S12" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="T12" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E13">
         <v>2025</v>
@@ -1874,36 +3746,36 @@
         <v>0.48487924617859812</v>
       </c>
       <c r="N13" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O13" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="P13" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="Q13" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R13" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S13" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T13" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="E14">
         <v>2032</v>
@@ -1930,36 +3802,36 @@
         <v>0.46120613336716743</v>
       </c>
       <c r="N14" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O14" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="P14" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R14" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S14" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T14" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="E15">
         <v>2035</v>
@@ -1986,36 +3858,36 @@
         <v>0.45368618559080531</v>
       </c>
       <c r="N15" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P15" t="s">
         <v>71</v>
       </c>
-      <c r="P15" t="s">
-        <v>92</v>
-      </c>
       <c r="Q15" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R15" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S15" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T15" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="E16">
         <v>2035</v>
@@ -2042,36 +3914,36 @@
         <v>0.45368618559080531</v>
       </c>
       <c r="N16" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O16" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="P16" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="Q16" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R16" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S16" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T16" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E17">
         <v>2025</v>
@@ -2098,36 +3970,36 @@
         <v>0.48487924617859807</v>
       </c>
       <c r="N17" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O17" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="P17" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="Q17" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R17" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S17" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T17" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E18">
         <v>2025</v>
@@ -2154,36 +4026,36 @@
         <v>0.48487924617859812</v>
       </c>
       <c r="N18" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O18" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="P18" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q18" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R18" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S18" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T18" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E19">
         <v>2025</v>
@@ -2210,33 +4082,33 @@
         <v>0.48487924617859812</v>
       </c>
       <c r="N19" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O19" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="P19" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="Q19" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R19" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S19" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T19" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20">
         <v>2026</v>
@@ -2260,33 +4132,33 @@
         <v>100</v>
       </c>
       <c r="N20" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="O20" t="s">
+        <v>56</v>
+      </c>
+      <c r="P20" t="s">
         <v>77</v>
       </c>
-      <c r="P20" t="s">
-        <v>98</v>
-      </c>
       <c r="Q20" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R20" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S20" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="T20" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21">
         <v>2029</v>
@@ -2310,36 +4182,36 @@
         <v>100</v>
       </c>
       <c r="N21" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="O21" t="s">
+        <v>57</v>
+      </c>
+      <c r="P21" t="s">
         <v>78</v>
       </c>
-      <c r="P21" t="s">
-        <v>99</v>
-      </c>
       <c r="Q21" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R21" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S21" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="T21" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
         <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
       </c>
       <c r="E22">
         <v>2025</v>
@@ -2366,36 +4238,36 @@
         <v>0.15309859852159369</v>
       </c>
       <c r="N22" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O22" t="s">
+        <v>58</v>
+      </c>
+      <c r="P22" t="s">
         <v>79</v>
       </c>
-      <c r="P22" t="s">
-        <v>100</v>
-      </c>
       <c r="Q22" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R22" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S22" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T22" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E23">
         <v>2028</v>
@@ -2422,36 +4294,36 @@
         <v>0.48127681492517582</v>
       </c>
       <c r="N23" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O23" t="s">
+        <v>59</v>
+      </c>
+      <c r="P23" t="s">
         <v>80</v>
       </c>
-      <c r="P23" t="s">
-        <v>101</v>
-      </c>
       <c r="Q23" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R23" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S23" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T23" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="E24">
         <v>2029</v>
@@ -2478,36 +4350,36 @@
         <v>0.47369214016582101</v>
       </c>
       <c r="N24" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O24" t="s">
+        <v>60</v>
+      </c>
+      <c r="P24" t="s">
         <v>81</v>
       </c>
-      <c r="P24" t="s">
-        <v>102</v>
-      </c>
       <c r="Q24" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R24" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S24" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T24" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E25">
         <v>2030</v>
@@ -2534,36 +4406,36 @@
         <v>0.46331764653839141</v>
       </c>
       <c r="N25" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O25" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="P25" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="Q25" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R25" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S25" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T25" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="E26">
         <v>2028</v>
@@ -2590,36 +4462,36 @@
         <v>0.45368618559080531</v>
       </c>
       <c r="N26" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O26" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="P26" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="Q26" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R26" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S26" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T26" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="E27">
         <v>2028</v>
@@ -2646,36 +4518,36 @@
         <v>0.45368618559080537</v>
       </c>
       <c r="N27" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O27" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="P27" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="Q27" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R27" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S27" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T27" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E28">
         <v>2030</v>
@@ -2702,36 +4574,36 @@
         <v>0.46331764653839141</v>
       </c>
       <c r="N28" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O28" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="P28" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="Q28" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R28" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S28" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T28" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="C30" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E30">
         <v>2035</v>
@@ -2755,25 +4627,25 @@
         <v>50</v>
       </c>
       <c r="N30" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O30" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="P30" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="Q30" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="R30" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S30" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="T30" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2784,7 +4656,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B9:AA98"/>
+  <dimension ref="B6:AB62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
@@ -2792,104 +4664,295 @@
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="40.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="64.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="64.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="E6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="7"/>
+      <c r="U6" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="V6" s="11"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="12"/>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="12"/>
+    </row>
+    <row r="7" spans="2:28" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="U7" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="V7" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="W7" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="X7" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z7" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="AA7" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="AB7" s="15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="2:28" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="U8" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="V8" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="W8" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="X8" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y8" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="Z8" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA8" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB8" s="16" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9">
+        <v>2022</v>
+      </c>
+      <c r="F9">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1018</v>
+      </c>
+      <c r="I9" s="2">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="J9" s="2">
         <v>0</v>
       </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0.1461854238754417</v>
+      </c>
       <c r="U9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="V9" t="s">
+        <v>184</v>
+      </c>
+      <c r="W9" t="s">
+        <v>38</v>
+      </c>
+      <c r="X9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10">
+        <v>2022</v>
+      </c>
+      <c r="F10">
+        <v>0.108</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" t="s">
-        <v>10</v>
-      </c>
-      <c r="L10" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" t="s">
-        <v>196</v>
+      <c r="H10" s="1">
+        <v>1018</v>
+      </c>
+      <c r="I10" s="2">
+        <v>16.064040000000002</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>35</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0.1461854238754417</v>
       </c>
       <c r="U10" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="V10" t="s">
-        <v>1</v>
+        <v>185</v>
       </c>
       <c r="W10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="X10" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="Y10" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="Z10" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="E11">
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.24199999999999999</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2898,55 +4961,54 @@
         <v>1018</v>
       </c>
       <c r="I11" s="2">
-        <f t="shared" ref="I11:I25" si="0">($P$45/100)*H11</f>
         <v>16.064040000000002</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>0</v>
       </c>
       <c r="K11">
         <v>35</v>
       </c>
-      <c r="L11">
-        <v>0.1461854238754417</v>
+      <c r="L11" s="3">
+        <v>0.14867925344692126</v>
       </c>
       <c r="U11" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V11" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="W11" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X11" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y11" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z11" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E12">
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.108</v>
+        <v>7.8E-2</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2955,55 +5017,54 @@
         <v>1018</v>
       </c>
       <c r="I12" s="2">
-        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>0</v>
       </c>
       <c r="K12">
         <v>35</v>
       </c>
-      <c r="L12">
-        <v>0.1461854238754417</v>
+      <c r="L12" s="3">
+        <v>0.14701259708091721</v>
       </c>
       <c r="U12" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V12" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="W12" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X12" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y12" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z12" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E13">
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>0.13200000000000001</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -3012,55 +5073,54 @@
         <v>1018</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>0</v>
       </c>
       <c r="K13">
         <v>35</v>
       </c>
-      <c r="L13">
-        <v>0.14867925344692126</v>
+      <c r="L13" s="3">
+        <v>0.15309859852159369</v>
       </c>
       <c r="U13" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V13" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="W13" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X13" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y13" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z13" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="E14">
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>7.8E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -3069,55 +5129,54 @@
         <v>1018</v>
       </c>
       <c r="I14" s="2">
-        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>0</v>
       </c>
       <c r="K14">
         <v>35</v>
       </c>
-      <c r="L14">
-        <v>0.14701259708091721</v>
+      <c r="L14" s="3">
+        <v>0.15309859852159369</v>
       </c>
       <c r="U14" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V14" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="W14" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X14" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y14" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z14" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="E15">
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>7.4999999999999997E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -3126,55 +5185,54 @@
         <v>1018</v>
       </c>
       <c r="I15" s="2">
-        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>0</v>
       </c>
       <c r="K15">
         <v>35</v>
       </c>
-      <c r="L15">
-        <v>0.15309859852159369</v>
+      <c r="L15" s="3">
+        <v>0.15619560585976827</v>
       </c>
       <c r="U15" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V15" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="W15" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X15" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z15" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="E16">
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>4.7E-2</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -3183,55 +5241,54 @@
         <v>1018</v>
       </c>
       <c r="I16" s="2">
-        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>0</v>
       </c>
       <c r="K16">
         <v>35</v>
       </c>
-      <c r="L16">
-        <v>0.15309859852159369</v>
+      <c r="L16" s="3">
+        <v>0.14537310453496291</v>
       </c>
       <c r="U16" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V16" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="W16" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X16" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y16" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z16" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E17">
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.04</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -3240,59 +5297,54 @@
         <v>1018</v>
       </c>
       <c r="I17" s="2">
-        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="2">
         <v>0</v>
       </c>
       <c r="K17">
         <v>35</v>
       </c>
-      <c r="L17">
-        <v>0.15619560585976827</v>
-      </c>
-      <c r="P17">
-        <f>242+242+132+108+80+78+75+47+43+40+35+31+29+11+5</f>
-        <v>1198</v>
+      <c r="L17" s="3">
+        <v>0.14763873655681015</v>
       </c>
       <c r="U17" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V17" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="W17" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X17" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y17" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z17" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="E18">
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>0.24199999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -3301,473 +5353,446 @@
         <v>1018</v>
       </c>
       <c r="I18" s="2">
-        <f t="shared" si="0"/>
         <v>16.064040000000002</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="2">
         <v>0</v>
       </c>
       <c r="K18">
         <v>35</v>
       </c>
-      <c r="L18">
-        <v>0.14537310453496291</v>
+      <c r="L18" s="3">
+        <v>0.1532628310027955</v>
       </c>
       <c r="U18" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V18" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="W18" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X18" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y18" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z18" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E19">
         <v>2022</v>
       </c>
       <c r="F19">
-        <v>4.2999999999999997E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" s="1">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="I19" s="2">
-        <f t="shared" si="0"/>
-        <v>16.064040000000002</v>
-      </c>
-      <c r="J19">
+        <v>16.079820000000002</v>
+      </c>
+      <c r="J19" s="2">
         <v>0</v>
       </c>
       <c r="K19">
         <v>35</v>
       </c>
-      <c r="L19">
-        <v>0.14763873655681015</v>
+      <c r="L19" s="3">
+        <v>0.1461854238754417</v>
       </c>
       <c r="U19" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V19" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="W19" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X19" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y19" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z19" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E20">
         <v>2022</v>
       </c>
       <c r="F20">
-        <v>0.08</v>
+        <v>3.1E-2</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" s="1">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="0"/>
-        <v>16.064040000000002</v>
-      </c>
-      <c r="J20">
+        <v>16.095600000000001</v>
+      </c>
+      <c r="J20" s="2">
         <v>0</v>
       </c>
       <c r="K20">
         <v>35</v>
       </c>
-      <c r="L20">
-        <v>0.1532628310027955</v>
-      </c>
-      <c r="P20">
-        <f>SUM(F11:F25)</f>
-        <v>1.1969999999999996</v>
+      <c r="L20" s="3">
+        <v>0.1461854238754417</v>
       </c>
       <c r="U20" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V20" t="s">
+        <v>209</v>
+      </c>
+      <c r="W20" t="s">
+        <v>38</v>
+      </c>
+      <c r="X20" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
         <v>215</v>
       </c>
-      <c r="W20" t="s">
-        <v>58</v>
-      </c>
-      <c r="X20" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>232</v>
-      </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="E21">
         <v>2022</v>
       </c>
       <c r="F21">
-        <v>3.5000000000000003E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21" s="1">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="I21" s="2">
-        <f t="shared" si="0"/>
-        <v>16.079820000000002</v>
-      </c>
-      <c r="J21">
+        <v>16.111380000000004</v>
+      </c>
+      <c r="J21" s="2">
         <v>0</v>
       </c>
       <c r="K21">
         <v>35</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="3">
         <v>0.1461854238754417</v>
       </c>
       <c r="U21" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V21" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="W21" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X21" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y21" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z21" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="E22">
         <v>2022</v>
       </c>
       <c r="F22">
-        <v>3.1E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" s="1">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="I22" s="2">
-        <f t="shared" si="0"/>
-        <v>16.095600000000001</v>
-      </c>
-      <c r="J22">
+        <v>16.127160000000003</v>
+      </c>
+      <c r="J22" s="2">
         <v>0</v>
       </c>
       <c r="K22">
         <v>35</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="3">
         <v>0.1461854238754417</v>
       </c>
-      <c r="P22" t="s">
-        <v>231</v>
-      </c>
       <c r="U22" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V22" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="W22" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X22" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y22" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z22" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="E23">
         <v>2022</v>
       </c>
       <c r="F23">
-        <v>2.9000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" s="1">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="I23" s="2">
-        <f t="shared" si="0"/>
-        <v>16.111380000000004</v>
-      </c>
-      <c r="J23">
+        <v>16.142940000000003</v>
+      </c>
+      <c r="J23" s="2">
         <v>0</v>
       </c>
       <c r="K23">
         <v>35</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="3">
         <v>0.1461854238754417</v>
       </c>
-      <c r="O23">
-        <f>SUM(F26:F34)-F28</f>
-        <v>0.61260000000000003</v>
-      </c>
-      <c r="P23">
-        <f>693.9/1000</f>
-        <v>0.69389999999999996</v>
-      </c>
-      <c r="Q23">
-        <f>P23-O23</f>
-        <v>8.1299999999999928E-2</v>
-      </c>
       <c r="U23" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V23" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="W23" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X23" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y23" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z23" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>234</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>240</v>
+        <v>195</v>
       </c>
       <c r="E24">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F24">
-        <v>0.01</v>
+        <v>7.9699999999999993E-2</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24" s="1">
-        <v>1022</v>
+        <v>1494.4630999999999</v>
       </c>
       <c r="I24" s="2">
-        <f t="shared" si="0"/>
-        <v>16.127160000000003</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
+        <v>18.701711233400001</v>
+      </c>
+      <c r="J24" s="2">
+        <v>2.0036999999999998</v>
       </c>
       <c r="K24">
+        <v>27</v>
+      </c>
+      <c r="L24">
+        <v>0.4</v>
+      </c>
+      <c r="U24" t="s">
+        <v>31</v>
+      </c>
+      <c r="V24" t="s">
+        <v>172</v>
+      </c>
+      <c r="W24" t="s">
+        <v>36</v>
+      </c>
+      <c r="X24" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB24" t="s">
         <v>35</v>
       </c>
-      <c r="L24">
-        <v>0.1461854238754417</v>
-      </c>
-      <c r="U24" t="s">
-        <v>49</v>
-      </c>
-      <c r="V24" t="s">
-        <v>234</v>
-      </c>
-      <c r="W24" t="s">
-        <v>58</v>
-      </c>
-      <c r="X24" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>241</v>
+        <v>195</v>
       </c>
       <c r="E25">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F25">
-        <v>5.0000000000000001E-3</v>
+        <v>0.17519999999999999</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" s="1">
-        <v>1023</v>
+        <v>1494.4630999999999</v>
       </c>
       <c r="I25" s="2">
-        <f t="shared" si="0"/>
-        <v>16.142940000000003</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
+        <v>18.701711233400001</v>
+      </c>
+      <c r="J25" s="2">
+        <v>2.0036999999999998</v>
       </c>
       <c r="K25">
+        <v>27</v>
+      </c>
+      <c r="L25">
+        <v>0.4</v>
+      </c>
+      <c r="U25" t="s">
+        <v>31</v>
+      </c>
+      <c r="V25" t="s">
+        <v>24</v>
+      </c>
+      <c r="W25" t="s">
+        <v>40</v>
+      </c>
+      <c r="X25" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB25" t="s">
         <v>35</v>
       </c>
-      <c r="L25">
-        <v>0.1461854238754417</v>
-      </c>
-      <c r="U25" t="s">
-        <v>49</v>
-      </c>
-      <c r="V25" t="s">
-        <v>235</v>
-      </c>
-      <c r="W25" t="s">
-        <v>58</v>
-      </c>
-      <c r="X25" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>41</v>
+        <v>171</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="E26">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="F26">
-        <v>7.9699999999999993E-2</v>
+        <v>8.130000000000015E-2</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3776,11 +5801,9 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I26" s="2">
-        <f t="shared" ref="I26:I34" si="1">($P$46/100)*H26</f>
         <v>18.701711233400001</v>
       </c>
-      <c r="J26">
-        <f t="shared" ref="J26:J34" si="2">$S$46</f>
+      <c r="J26" s="2">
         <v>2.0036999999999998</v>
       </c>
       <c r="K26">
@@ -3790,42 +5813,42 @@
         <v>0.4</v>
       </c>
       <c r="U26" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V26" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="W26" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="X26" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y26" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z26" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="E27">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="F27">
-        <v>0.17519999999999999</v>
+        <v>1.6E-2</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3834,11 +5857,9 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="1"/>
         <v>18.701711233400001</v>
       </c>
-      <c r="J27">
-        <f t="shared" si="2"/>
+      <c r="J27" s="2">
         <v>2.0036999999999998</v>
       </c>
       <c r="K27">
@@ -3848,42 +5869,42 @@
         <v>0.4</v>
       </c>
       <c r="U27" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V27" t="s">
-        <v>41</v>
+        <v>171</v>
       </c>
       <c r="W27" t="s">
-        <v>61</v>
+        <v>198</v>
       </c>
       <c r="X27" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y27" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z27" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="E28">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F28">
-        <v>8.130000000000015E-2</v>
+        <v>3.27E-2</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3892,11 +5913,9 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I28" s="2">
-        <f t="shared" si="1"/>
         <v>18.701711233400001</v>
       </c>
-      <c r="J28">
-        <f t="shared" si="2"/>
+      <c r="J28" s="2">
         <v>2.0036999999999998</v>
       </c>
       <c r="K28">
@@ -3906,42 +5925,42 @@
         <v>0.4</v>
       </c>
       <c r="U28" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V28" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="W28" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="X28" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y28" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z28" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="E29">
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>1.6E-2</v>
+        <v>6.3399999999999998E-2</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3950,11 +5969,9 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I29" s="2">
-        <f t="shared" si="1"/>
         <v>18.701711233400001</v>
       </c>
-      <c r="J29">
-        <f t="shared" si="2"/>
+      <c r="J29" s="2">
         <v>2.0036999999999998</v>
       </c>
       <c r="K29">
@@ -3964,42 +5981,42 @@
         <v>0.4</v>
       </c>
       <c r="U29" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V29" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="W29" t="s">
-        <v>221</v>
+        <v>38</v>
       </c>
       <c r="X29" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y29" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z29" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="E30">
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>3.27E-2</v>
+        <v>0.06</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -4008,11 +6025,9 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" si="1"/>
         <v>18.701711233400001</v>
       </c>
-      <c r="J30">
-        <f t="shared" si="2"/>
+      <c r="J30" s="2">
         <v>2.0036999999999998</v>
       </c>
       <c r="K30">
@@ -4022,42 +6037,42 @@
         <v>0.4</v>
       </c>
       <c r="U30" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V30" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="W30" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X30" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y30" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z30" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="E31">
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>6.3399999999999998E-2</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -4066,11 +6081,9 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I31" s="2">
-        <f t="shared" si="1"/>
         <v>18.701711233400001</v>
       </c>
-      <c r="J31">
-        <f t="shared" si="2"/>
+      <c r="J31" s="2">
         <v>2.0036999999999998</v>
       </c>
       <c r="K31">
@@ -4080,42 +6093,42 @@
         <v>0.4</v>
       </c>
       <c r="U31" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V31" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="W31" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X31" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y31" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z31" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="E32">
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>0.06</v>
+        <v>0.1036</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -4124,11 +6137,9 @@
         <v>1494.4630999999999</v>
       </c>
       <c r="I32" s="2">
-        <f t="shared" si="1"/>
         <v>18.701711233400001</v>
       </c>
-      <c r="J32">
-        <f t="shared" si="2"/>
+      <c r="J32" s="2">
         <v>2.0036999999999998</v>
       </c>
       <c r="K32">
@@ -4138,472 +6149,444 @@
         <v>0.4</v>
       </c>
       <c r="U32" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V32" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="W32" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X32" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y32" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z32" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>225</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>230</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>2022</v>
+        <v>1982</v>
       </c>
       <c r="F33">
-        <v>8.2000000000000003E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H33" s="1">
-        <v>1494.4630999999999</v>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I33" s="2">
-        <f t="shared" si="1"/>
-        <v>18.701711233400001</v>
-      </c>
-      <c r="J33">
-        <f t="shared" si="2"/>
-        <v>2.0036999999999998</v>
+        <v>160.216352398</v>
+      </c>
+      <c r="J33" s="2">
+        <v>5.8775000000000004</v>
       </c>
       <c r="K33">
-        <v>27</v>
-      </c>
-      <c r="L33">
-        <v>0.4</v>
+        <v>53</v>
       </c>
       <c r="U33" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V33" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="W33" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="X33" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y33" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z33" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>229</v>
+        <v>152</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="D34" t="s">
-        <v>218</v>
+        <v>13</v>
       </c>
       <c r="E34">
-        <v>2022</v>
+        <v>1965</v>
       </c>
       <c r="F34">
-        <v>0.1036</v>
+        <v>0.77</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="H34" s="1">
-        <v>1494.4630999999999</v>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="1"/>
-        <v>18.701711233400001</v>
-      </c>
-      <c r="J34">
-        <f t="shared" si="2"/>
-        <v>2.0036999999999998</v>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J34" s="2">
+        <v>4.1005000000000003</v>
       </c>
       <c r="K34">
-        <v>27</v>
-      </c>
-      <c r="L34">
-        <v>0.4</v>
+        <v>70</v>
       </c>
       <c r="U34" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V34" t="s">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="W34" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="X34" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y34" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z34" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="C35" t="s">
+        <v>148</v>
+      </c>
+      <c r="D35" t="s">
         <v>13</v>
       </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
       <c r="E35">
-        <v>1982</v>
+        <v>2015</v>
       </c>
       <c r="F35">
-        <v>1.7000000000000001E-2</v>
+        <v>0.26</v>
       </c>
       <c r="G35">
-        <f>R41</f>
-        <v>0.56000000000000005</v>
+        <v>0.33</v>
       </c>
       <c r="H35" s="1">
-        <v>1175.5066999999999</v>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I35" s="2">
-        <f>(P41/100)*H36</f>
-        <v>160.216352398</v>
-      </c>
-      <c r="J35">
-        <f>S41</f>
-        <v>5.8775000000000004</v>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J35" s="2">
+        <v>4.1005000000000003</v>
       </c>
       <c r="K35">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="U35" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V35" t="s">
-        <v>229</v>
+        <v>149</v>
       </c>
       <c r="W35" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="X35" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y35" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z35" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C36" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E36">
-        <v>1965</v>
+        <v>2025</v>
       </c>
       <c r="F36">
-        <v>0.77</v>
+        <f>0.01</f>
+        <v>0.01</v>
       </c>
       <c r="G36">
-        <f>$R$40</f>
         <v>0.33</v>
       </c>
       <c r="H36" s="1">
         <v>4812.0244000000002</v>
       </c>
       <c r="I36" s="2">
-        <f>(1.31/100)*H36</f>
         <v>63.037519640000006</v>
       </c>
-      <c r="J36">
-        <f>$S$40</f>
+      <c r="J36" s="2">
         <v>4.1005000000000003</v>
       </c>
       <c r="K36">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="U36" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V36" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="W36" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="X36" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y36" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z36" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C37" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E37">
-        <v>2015</v>
+        <v>1956</v>
       </c>
       <c r="F37">
-        <v>0.26</v>
+        <v>0.185</v>
       </c>
       <c r="G37">
-        <f>$R$40</f>
         <v>0.33</v>
       </c>
       <c r="H37" s="1">
         <v>4812.0244000000002</v>
       </c>
       <c r="I37" s="2">
-        <f>(1.31/100)*H37</f>
         <v>63.037519640000006</v>
       </c>
-      <c r="J37">
-        <f>$S$40</f>
+      <c r="J37" s="2">
         <v>4.1005000000000003</v>
       </c>
       <c r="K37">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="U37" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V37" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="W37" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="X37" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y37" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z37" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>169</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E38">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="F38">
-        <f>0.01</f>
-        <v>0.01</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G38">
-        <v>0.33</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H38" s="1">
-        <v>4812.0244000000002</v>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I38" s="2">
-        <f>(1.31/100)*H38</f>
-        <v>63.037519640000006</v>
-      </c>
-      <c r="J38">
-        <f>$S$40</f>
-        <v>4.1005000000000003</v>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J38" s="2">
+        <v>5.8775000000000004</v>
       </c>
       <c r="K38">
         <v>40</v>
       </c>
       <c r="U38" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V38" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="W38" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="X38" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y38" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z38" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39">
+        <v>2018</v>
+      </c>
+      <c r="F39">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G39">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2950.7891</v>
+      </c>
+      <c r="I39" s="2">
+        <v>133.5792717679</v>
+      </c>
+      <c r="J39" s="2">
+        <v>2.8138000000000001</v>
+      </c>
+      <c r="K39">
+        <v>40</v>
+      </c>
+      <c r="P39" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>167</v>
+      </c>
+      <c r="R39" t="s">
+        <v>168</v>
+      </c>
+      <c r="S39" t="s">
         <v>169</v>
       </c>
-      <c r="D39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39">
-        <v>1956</v>
-      </c>
-      <c r="F39">
-        <v>0.185</v>
-      </c>
-      <c r="G39">
-        <f>$R$40</f>
-        <v>0.33</v>
-      </c>
-      <c r="H39" s="1">
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="I39" s="2">
-        <f>(1.31/100)*H39</f>
-        <v>63.037519640000006</v>
-      </c>
-      <c r="J39">
-        <f>$S$40</f>
-        <v>4.1005000000000003</v>
-      </c>
-      <c r="K39">
-        <v>73</v>
-      </c>
-      <c r="P39" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>190</v>
-      </c>
-      <c r="R39" t="s">
-        <v>191</v>
-      </c>
-      <c r="S39" t="s">
-        <v>192</v>
-      </c>
       <c r="U39" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V39" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="W39" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="X39" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y39" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z39" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E40">
-        <v>2021</v>
+        <v>2009</v>
       </c>
       <c r="F40">
-        <v>7.6999999999999999E-2</v>
+        <v>2.2100000000000002E-2</v>
       </c>
       <c r="G40">
-        <f>R41</f>
-        <v>0.56000000000000005</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H40" s="1">
-        <f>Q41</f>
-        <v>1175.5066999999999</v>
+        <v>2950.7891</v>
       </c>
       <c r="I40" s="2">
-        <f>(P41/100)*H40</f>
-        <v>39.138495576499992</v>
-      </c>
-      <c r="J40">
-        <f>$S$41</f>
-        <v>5.8775000000000004</v>
+        <v>133.5792717679</v>
+      </c>
+      <c r="J40" s="2">
+        <v>2.8138000000000001</v>
       </c>
       <c r="K40">
         <v>40</v>
       </c>
       <c r="O40" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="P40" s="3">
         <v>1.31</v>
@@ -4618,64 +6601,60 @@
         <v>4.1005000000000003</v>
       </c>
       <c r="U40" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V40" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="W40" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="X40" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y40" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z40" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
         <v>13</v>
       </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
       <c r="E41">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="F41">
-        <v>3.9E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="G41">
-        <f>R43</f>
         <v>0.46800000000000003</v>
       </c>
       <c r="H41" s="1">
-        <f>$Q$43</f>
         <v>2950.7891</v>
       </c>
       <c r="I41" s="2">
-        <f>(4.5269/100)*H41</f>
         <v>133.5792717679</v>
       </c>
-      <c r="J41">
-        <f>$S$43</f>
+      <c r="J41" s="2">
         <v>2.8138000000000001</v>
       </c>
       <c r="K41">
         <v>40</v>
       </c>
       <c r="O41" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="P41" s="3">
         <v>3.3294999999999999</v>
@@ -4690,124 +6669,118 @@
         <v>5.8775000000000004</v>
       </c>
       <c r="U41" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V41" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="W41" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="X41" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y41" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z41" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
         <v>13</v>
       </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
       <c r="E42">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="F42">
-        <v>2.2100000000000002E-2</v>
+        <v>1.3900000000000001E-2</v>
       </c>
       <c r="G42">
         <v>0.46800000000000003</v>
       </c>
       <c r="H42" s="1">
-        <f>$Q$43</f>
         <v>2950.7891</v>
       </c>
       <c r="I42" s="2">
-        <f t="shared" ref="I42:I44" si="3">(4.5269/100)*H42</f>
         <v>133.5792717679</v>
       </c>
-      <c r="J42">
-        <f>$S$43</f>
+      <c r="J42" s="2">
         <v>2.8138000000000001</v>
       </c>
       <c r="K42">
         <v>40</v>
       </c>
       <c r="O42" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="1"/>
       <c r="U42" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V42" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="W42" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="X42" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y42" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z42" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="C43" t="s">
+        <v>148</v>
+      </c>
+      <c r="D43" t="s">
         <v>13</v>
       </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
       <c r="E43">
-        <v>2011</v>
+        <v>1997</v>
       </c>
       <c r="F43">
-        <v>2.0500000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G43">
-        <v>0.46800000000000003</v>
+        <v>0.33</v>
       </c>
       <c r="H43" s="1">
-        <f>$Q$43</f>
-        <v>2950.7891</v>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I43" s="2">
-        <f t="shared" si="3"/>
-        <v>133.5792717679</v>
-      </c>
-      <c r="J43">
-        <f>$S$43</f>
-        <v>2.8138000000000001</v>
+        <v>63.037519640000006</v>
+      </c>
+      <c r="J43" s="2">
+        <v>4.1005000000000003</v>
       </c>
       <c r="K43">
         <v>40</v>
       </c>
       <c r="O43" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="P43">
         <v>4.5269000000000004</v>
@@ -4822,63 +6795,60 @@
         <v>2.8138000000000001</v>
       </c>
       <c r="U43" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V43" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="W43" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="X43" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y43" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z43" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
         <v>13</v>
       </c>
-      <c r="D44" t="s">
-        <v>14</v>
-      </c>
       <c r="E44">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="F44">
-        <v>1.3900000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G44">
-        <v>0.46800000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H44" s="1">
-        <f>$Q$43</f>
-        <v>2950.7891</v>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I44" s="2">
-        <f t="shared" si="3"/>
-        <v>133.5792717679</v>
-      </c>
-      <c r="J44">
-        <f>$S$43</f>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J44" s="2">
         <v>2.8138000000000001</v>
       </c>
       <c r="K44">
         <v>40</v>
       </c>
       <c r="O44" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="P44">
         <v>3.6080999999999999</v>
@@ -4893,127 +6863,120 @@
         <v>2.8138000000000001</v>
       </c>
       <c r="U44" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V44" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="W44" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="X44" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y44" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z44" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
-        <v>169</v>
+        <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E45">
-        <v>1997</v>
+        <v>2017</v>
       </c>
       <c r="F45">
         <v>0.01</v>
       </c>
       <c r="G45">
-        <f>R40</f>
-        <v>0.33</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H45" s="1">
-        <f>Q40</f>
-        <v>4812.0244000000002</v>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I45" s="2">
-        <f>($P$40/100)*H45</f>
-        <v>63.037519640000006</v>
-      </c>
-      <c r="J45">
-        <f>$S$40</f>
-        <v>4.1005000000000003</v>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J45" s="2">
+        <v>2.8138000000000001</v>
       </c>
       <c r="K45">
         <v>40</v>
       </c>
       <c r="O45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P45" s="2">
         <v>1.5780000000000001</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="U45" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V45" t="s">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="W45" t="s">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="X45" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y45" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z45" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
         <v>13</v>
       </c>
-      <c r="D46" t="s">
-        <v>14</v>
-      </c>
       <c r="E46">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="F46">
-        <v>0.01</v>
+        <v>9.300000000000001E-3</v>
       </c>
       <c r="G46">
         <v>0.28999999999999998</v>
       </c>
       <c r="H46" s="1">
-        <f>$Q$44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I46" s="2">
-        <f>($P$44/100)*H46</f>
         <v>162.96753257730003</v>
       </c>
-      <c r="J46">
-        <f>$S$44</f>
+      <c r="J46" s="2">
         <v>2.8138000000000001</v>
       </c>
       <c r="K46">
         <v>40</v>
       </c>
       <c r="O46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P46" s="2">
         <v>1.2514000000000001</v>
@@ -5023,115 +6986,109 @@
         <v>2.0036999999999998</v>
       </c>
       <c r="U46" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V46" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="W46" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="X46" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y46" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z46" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" t="s">
         <v>13</v>
       </c>
-      <c r="D47" t="s">
-        <v>14</v>
-      </c>
       <c r="E47">
-        <v>2017</v>
+        <v>1963</v>
       </c>
       <c r="F47">
-        <v>0.01</v>
+        <v>7.0999999999999995E-3</v>
       </c>
       <c r="G47">
         <v>0.28999999999999998</v>
       </c>
       <c r="H47" s="1">
-        <f>$Q$44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I47" s="2">
-        <f>($P$44/100)*H47</f>
         <v>162.96753257730003</v>
       </c>
-      <c r="J47">
-        <f>$S$44</f>
+      <c r="J47" s="2">
         <v>2.8138000000000001</v>
       </c>
       <c r="K47">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" s="3"/>
       <c r="U47" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V47" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="W47" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="X47" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y47" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z47" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" t="s">
         <v>13</v>
       </c>
-      <c r="D48" t="s">
-        <v>14</v>
-      </c>
       <c r="E48">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="F48">
-        <v>9.300000000000001E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="G48">
-        <v>0.28999999999999998</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H48" s="1">
-        <f>$Q$44</f>
-        <v>4516.7133000000003</v>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I48" s="2">
-        <f>($P$44/100)*H48</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J48">
-        <f>$S$44</f>
-        <v>2.8138000000000001</v>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J48" s="2">
+        <v>5.8775000000000004</v>
       </c>
       <c r="K48">
         <v>40</v>
@@ -5139,1772 +7096,755 @@
       <c r="P48" s="2"/>
       <c r="Q48" s="3"/>
       <c r="U48" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V48" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="W48" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="X48" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y48" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z48" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA48" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
         <v>13</v>
       </c>
-      <c r="D49" t="s">
-        <v>14</v>
-      </c>
       <c r="E49">
-        <v>1963</v>
+        <v>2013</v>
       </c>
       <c r="F49">
-        <v>7.0999999999999995E-3</v>
+        <v>6.4999999999999997E-3</v>
       </c>
       <c r="G49">
         <v>0.28999999999999998</v>
       </c>
       <c r="H49" s="1">
-        <f>$Q$44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I49" s="2">
-        <f>($P$44/100)*H49</f>
         <v>162.96753257730003</v>
       </c>
-      <c r="J49">
-        <f>$S$44</f>
+      <c r="J49" s="2">
         <v>2.8138000000000001</v>
       </c>
       <c r="K49">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="U49" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V49" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="W49" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="X49" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y49" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z49" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA49" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="C50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E50">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="F50">
-        <v>5.7999999999999996E-3</v>
+        <v>4.0999999999999995E-3</v>
       </c>
       <c r="G50">
-        <f>R41</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="H50" s="1">
-        <f>Q41</f>
         <v>1175.5066999999999</v>
       </c>
       <c r="I50" s="2">
-        <f>($P$41/100)*H50</f>
         <v>39.138495576499992</v>
       </c>
-      <c r="J50">
-        <f>$S$41</f>
+      <c r="J50" s="2">
         <v>5.8775000000000004</v>
       </c>
       <c r="K50">
         <v>40</v>
       </c>
       <c r="U50" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V50" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="W50" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="X50" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y50" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z50" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C51" t="s">
+        <v>148</v>
+      </c>
+      <c r="D51" t="s">
         <v>13</v>
       </c>
-      <c r="D51" t="s">
-        <v>14</v>
-      </c>
       <c r="E51">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="F51">
-        <v>6.4999999999999997E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G51">
-        <v>0.28999999999999998</v>
+        <v>0.33</v>
       </c>
       <c r="H51" s="1">
-        <f>Q44</f>
-        <v>4516.7133000000003</v>
+        <v>4812.0244000000002</v>
       </c>
       <c r="I51" s="2">
-        <f>($P$44/100)*H51</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J51">
-        <f>$S$44</f>
-        <v>2.8138000000000001</v>
+        <v>173.62265237640003</v>
+      </c>
+      <c r="J51" s="2">
+        <v>4.1005000000000003</v>
       </c>
       <c r="K51">
         <v>40</v>
       </c>
       <c r="U51" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V51" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="W51" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="X51" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y51" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z51" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E52">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="F52">
-        <v>4.0999999999999995E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G52">
-        <f>R41</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H52" s="1">
-        <f>Q41</f>
-        <v>1175.5066999999999</v>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I52" s="2">
-        <f>($P$41/100)*H52</f>
-        <v>39.138495576499992</v>
-      </c>
-      <c r="J52">
-        <f>$S$41</f>
-        <v>5.8775000000000004</v>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J52" s="2">
+        <v>2.8138000000000001</v>
       </c>
       <c r="K52">
         <v>40</v>
       </c>
       <c r="U52" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V52" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="W52" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="X52" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y52" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z52" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA52" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="C53" t="s">
-        <v>169</v>
+        <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E53">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="F53">
-        <v>1.4E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="G53">
-        <f>R40</f>
-        <v>0.33</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H53" s="1">
-        <f>Q40</f>
-        <v>4812.0244000000002</v>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I53" s="2">
-        <f>($P$44/100)*H53</f>
-        <v>173.62265237640003</v>
-      </c>
-      <c r="J53">
-        <f>$S$40</f>
-        <v>4.1005000000000003</v>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J53" s="2">
+        <v>2.8138000000000001</v>
       </c>
       <c r="K53">
         <v>40</v>
       </c>
       <c r="U53" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V53" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="W53" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="X53" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y53" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z53" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA53" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" t="s">
         <v>13</v>
       </c>
-      <c r="D54" t="s">
-        <v>14</v>
-      </c>
       <c r="E54">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="F54">
         <v>1.8E-3</v>
       </c>
       <c r="G54">
-        <v>0.28999999999999998</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H54" s="1">
-        <f>Q44</f>
-        <v>4516.7133000000003</v>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I54" s="2">
-        <f>($P$44/100)*H54</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J54">
-        <f>$S$44</f>
-        <v>2.8138000000000001</v>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J54" s="2">
+        <v>5.8775000000000004</v>
       </c>
       <c r="K54">
         <v>40</v>
       </c>
       <c r="U54" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V54" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="W54" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="X54" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y54" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z54" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="C55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" t="s">
         <v>13</v>
-      </c>
-      <c r="D55" t="s">
-        <v>14</v>
       </c>
       <c r="E55">
         <v>2015</v>
       </c>
       <c r="F55">
-        <v>1.6999999999999999E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="G55">
-        <v>0.28999999999999998</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H55" s="1">
-        <f>Q44</f>
-        <v>4516.7133000000003</v>
+        <v>1175.5066999999999</v>
       </c>
       <c r="I55" s="2">
-        <f>($P$44/100)*H55</f>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J55">
-        <f>$S$44</f>
-        <v>2.8138000000000001</v>
+        <v>39.138495576499992</v>
+      </c>
+      <c r="J55" s="2">
+        <v>5.8775000000000004</v>
       </c>
       <c r="K55">
         <v>40</v>
       </c>
       <c r="U55" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V55" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="W55" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="X55" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y55" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z55" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E56">
-        <v>2009</v>
+        <v>2022</v>
       </c>
       <c r="F56">
-        <v>1.8E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G56">
-        <f>R41</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H56" s="1">
-        <f>Q41</f>
-        <v>1175.5066999999999</v>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I56" s="2">
-        <f>($P$41/100)*H56</f>
-        <v>39.138495576499992</v>
-      </c>
-      <c r="J56">
-        <f>$S$41</f>
-        <v>5.8775000000000004</v>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J56" s="2">
+        <v>2.8138000000000001</v>
       </c>
       <c r="K56">
         <v>40</v>
       </c>
       <c r="U56" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V56" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="W56" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="X56" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y56" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z56" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E57">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="F57">
-        <v>1.8E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="G57">
-        <f>R41</f>
-        <v>0.56000000000000005</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H57" s="1">
-        <f>Q41</f>
-        <v>1175.5066999999999</v>
+        <v>4516.7133000000003</v>
       </c>
       <c r="I57" s="2">
-        <f>($P$41/100)*H57</f>
-        <v>39.138495576499992</v>
-      </c>
-      <c r="J57">
-        <f>$S$41</f>
-        <v>5.8775000000000004</v>
+        <v>162.96753257730003</v>
+      </c>
+      <c r="J57" s="2">
+        <v>2.8138000000000001</v>
       </c>
       <c r="K57">
         <v>40</v>
       </c>
       <c r="U57" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V57" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="W57" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="X57" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y57" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z57" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA57" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="58" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
         <v>13</v>
       </c>
-      <c r="D58" t="s">
-        <v>14</v>
-      </c>
       <c r="E58">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="F58">
-        <v>1.5E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G58">
         <v>0.28999999999999998</v>
       </c>
       <c r="H58" s="1">
-        <f>Q44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I58" s="2">
-        <f t="shared" ref="I58:I63" si="4">($P$44/100)*H58</f>
         <v>162.96753257730003</v>
       </c>
-      <c r="J58">
-        <f t="shared" ref="J58:J63" si="5">$S$44</f>
+      <c r="J58" s="2">
         <v>2.8138000000000001</v>
       </c>
       <c r="K58">
         <v>40</v>
       </c>
       <c r="U58" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V58" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="W58" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="X58" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y58" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z58" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA58" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" t="s">
         <v>13</v>
       </c>
-      <c r="D59" t="s">
-        <v>14</v>
-      </c>
       <c r="E59">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="F59">
-        <v>1.4E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="G59">
         <v>0.28999999999999998</v>
       </c>
       <c r="H59" s="1">
-        <f>$Q$44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I59" s="2">
-        <f t="shared" si="4"/>
         <v>162.96753257730003</v>
       </c>
-      <c r="J59">
-        <f t="shared" si="5"/>
+      <c r="J59" s="2">
         <v>2.8138000000000001</v>
       </c>
       <c r="K59">
         <v>40</v>
       </c>
       <c r="U59" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V59" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="W59" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="X59" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y59" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z59" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA59" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
         <v>13</v>
       </c>
-      <c r="D60" t="s">
-        <v>14</v>
-      </c>
       <c r="E60">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="F60">
-        <v>1.1999999999999999E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="G60">
         <v>0.28999999999999998</v>
       </c>
       <c r="H60" s="1">
-        <f>$Q$44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I60" s="2">
-        <f t="shared" si="4"/>
         <v>162.96753257730003</v>
       </c>
-      <c r="J60">
-        <f t="shared" si="5"/>
+      <c r="J60" s="2">
         <v>2.8138000000000001</v>
       </c>
       <c r="K60">
         <v>40</v>
       </c>
       <c r="U60" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V60" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="W60" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="X60" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y60" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z60" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA60" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
         <v>13</v>
       </c>
-      <c r="D61" t="s">
-        <v>14</v>
-      </c>
       <c r="E61">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="F61">
-        <v>1.9E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="G61">
         <v>0.28999999999999998</v>
       </c>
       <c r="H61" s="1">
-        <f>Q44</f>
         <v>4516.7133000000003</v>
       </c>
       <c r="I61" s="2">
-        <f t="shared" si="4"/>
         <v>162.96753257730003</v>
       </c>
-      <c r="J61">
-        <f t="shared" si="5"/>
+      <c r="J61" s="2">
         <v>2.8138000000000001</v>
       </c>
       <c r="K61">
         <v>40</v>
       </c>
       <c r="U61" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V61" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="W61" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="X61" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y61" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z61" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA61" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="62" spans="2:27" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="C62" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" t="s">
         <v>13</v>
       </c>
-      <c r="D62" t="s">
-        <v>14</v>
-      </c>
       <c r="E62">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="F62">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="G62">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H62" s="1">
-        <f>Q44</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I62" s="2">
-        <f t="shared" si="4"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J62">
-        <f t="shared" si="5"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K62">
-        <v>40</v>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0.33123000000000002</v>
       </c>
       <c r="U62" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="V62" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="W62" t="s">
-        <v>167</v>
+        <v>38</v>
       </c>
       <c r="X62" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Y62" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="Z62" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA62" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
-        <v>168</v>
-      </c>
-      <c r="C63" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63">
-        <v>2015</v>
-      </c>
-      <c r="F63">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="G63">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="H63" s="1">
-        <f>Q44</f>
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="I63" s="2">
-        <f t="shared" si="4"/>
-        <v>162.96753257730003</v>
-      </c>
-      <c r="J63">
-        <f t="shared" si="5"/>
-        <v>2.8138000000000001</v>
-      </c>
-      <c r="K63">
-        <v>40</v>
-      </c>
-      <c r="U63" t="s">
-        <v>49</v>
-      </c>
-      <c r="V63" t="s">
-        <v>168</v>
-      </c>
-      <c r="W63" t="s">
-        <v>197</v>
-      </c>
-      <c r="X63" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y63" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA63" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="64" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B64" t="s">
-        <v>18</v>
-      </c>
-      <c r="C64" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64">
-        <v>2022</v>
-      </c>
-      <c r="F64">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G64">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="U64" t="s">
-        <v>49</v>
-      </c>
-      <c r="V64" t="s">
-        <v>18</v>
-      </c>
-      <c r="W64" t="s">
-        <v>58</v>
-      </c>
-      <c r="X64" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y64" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z64" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="V72" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="U73" t="s">
-        <v>49</v>
-      </c>
-      <c r="V73" t="s">
-        <v>24</v>
-      </c>
-      <c r="W73" t="s">
-        <v>58</v>
-      </c>
-      <c r="X73" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y73" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z73" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA73" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="U74" t="s">
-        <v>49</v>
-      </c>
-      <c r="V74" t="s">
-        <v>27</v>
-      </c>
-      <c r="W74" t="s">
-        <v>58</v>
-      </c>
-      <c r="X74" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y74" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z74" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA74" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B75" t="s">
-        <v>20</v>
-      </c>
-      <c r="C75" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75">
-        <v>2013</v>
-      </c>
-      <c r="F75">
-        <v>0.25109999999999999</v>
-      </c>
-      <c r="G75">
-        <v>0.36049999999999999</v>
-      </c>
-      <c r="H75">
-        <v>1265</v>
-      </c>
-      <c r="I75" s="2">
-        <v>48.400000000000006</v>
-      </c>
-      <c r="J75">
-        <v>7.5075000000000003</v>
-      </c>
-      <c r="K75">
-        <v>42</v>
-      </c>
-      <c r="U75" t="s">
-        <v>49</v>
-      </c>
-      <c r="V75" t="s">
-        <v>29</v>
-      </c>
-      <c r="W75" t="s">
-        <v>58</v>
-      </c>
-      <c r="X75" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y75" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z75" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA75" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76" t="s">
-        <v>16</v>
-      </c>
-      <c r="D76" t="s">
-        <v>14</v>
-      </c>
-      <c r="E76">
-        <v>2022</v>
-      </c>
-      <c r="F76">
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="G76">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="U76" t="s">
-        <v>49</v>
-      </c>
-      <c r="V76" t="s">
-        <v>31</v>
-      </c>
-      <c r="W76" t="s">
-        <v>58</v>
-      </c>
-      <c r="X76" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y76" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z76" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA76" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="U77" t="s">
-        <v>49</v>
-      </c>
-      <c r="V77" t="s">
-        <v>33</v>
-      </c>
-      <c r="W77" t="s">
-        <v>58</v>
-      </c>
-      <c r="X77" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y77" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z77" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA77" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="78" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B78" t="s">
-        <v>12</v>
-      </c>
-      <c r="C78" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78">
-        <v>2022</v>
-      </c>
-      <c r="F78">
-        <v>0.3</v>
-      </c>
-      <c r="G78">
-        <v>0.33990000000000004</v>
-      </c>
-      <c r="H78">
-        <v>4427.5</v>
-      </c>
-      <c r="I78" s="2">
-        <v>157.30000000000001</v>
-      </c>
-      <c r="J78">
-        <v>9.24</v>
-      </c>
-      <c r="K78">
-        <v>50</v>
-      </c>
-      <c r="U78" t="s">
-        <v>49</v>
-      </c>
-      <c r="V78" t="s">
-        <v>35</v>
-      </c>
-      <c r="W78" t="s">
-        <v>58</v>
-      </c>
-      <c r="X78" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y78" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z78" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA78" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="U79" t="s">
-        <v>49</v>
-      </c>
-      <c r="V79" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB62" t="s">
         <v>37</v>
-      </c>
-      <c r="W79" t="s">
-        <v>58</v>
-      </c>
-      <c r="X79" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y79" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z79" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA79" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="U80" t="s">
-        <v>49</v>
-      </c>
-      <c r="V80" t="s">
-        <v>39</v>
-      </c>
-      <c r="W80" t="s">
-        <v>58</v>
-      </c>
-      <c r="X80" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y80" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z80" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA80" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="81" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="U81" t="s">
-        <v>49</v>
-      </c>
-      <c r="V81" t="s">
-        <v>20</v>
-      </c>
-      <c r="W81" t="s">
-        <v>59</v>
-      </c>
-      <c r="X81" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y81" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z81" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA81" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="82" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="U82" t="s">
-        <v>49</v>
-      </c>
-      <c r="V82" t="s">
-        <v>15</v>
-      </c>
-      <c r="W82" t="s">
-        <v>55</v>
-      </c>
-      <c r="X82" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y82" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z82" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA82" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="83" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
-        <v>24</v>
-      </c>
-      <c r="C83" t="s">
-        <v>25</v>
-      </c>
-      <c r="D83" t="s">
-        <v>26</v>
-      </c>
-      <c r="E83">
-        <v>2022</v>
-      </c>
-      <c r="F83">
-        <v>1.5040605442498314E-2</v>
-      </c>
-      <c r="G83">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L83">
-        <v>0.42012333946150526</v>
-      </c>
-    </row>
-    <row r="84" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
-        <v>27</v>
-      </c>
-      <c r="C84" t="s">
-        <v>25</v>
-      </c>
-      <c r="D84" t="s">
-        <v>28</v>
-      </c>
-      <c r="E84">
-        <v>2022</v>
-      </c>
-      <c r="F84">
-        <v>1.5497656626156837E-2</v>
-      </c>
-      <c r="G84">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L84">
-        <v>0.42012333946150526</v>
-      </c>
-      <c r="U84" t="s">
-        <v>49</v>
-      </c>
-      <c r="V84" t="s">
-        <v>12</v>
-      </c>
-      <c r="W84" t="s">
-        <v>50</v>
-      </c>
-      <c r="X84" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y84" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z84" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA84" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="85" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B85" t="s">
-        <v>29</v>
-      </c>
-      <c r="C85" t="s">
-        <v>25</v>
-      </c>
-      <c r="D85" t="s">
-        <v>30</v>
-      </c>
-      <c r="E85">
-        <v>2022</v>
-      </c>
-      <c r="F85">
-        <v>1.4461737931344828E-2</v>
-      </c>
-      <c r="G85">
-        <v>0.33123000000000002</v>
-      </c>
-      <c r="L85">
-        <v>0.42012333946150526</v>
-      </c>
-    </row>
-    <row r="86" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B86" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" t="s">
-        <v>25</v>
-      </c>
-      <c r="D86" t="s">
-        <v>32</v>
-      </c>
-      <c r="E86">
-        <v>2009</v>
-      </c>
-      <c r="F86">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G86">
-        <v>1</v>
-      </c>
-      <c r="H86">
-        <v>2376</v>
-      </c>
-      <c r="I86" s="2">
-        <v>57.2</v>
-      </c>
-      <c r="J86">
-        <v>2.52</v>
-      </c>
-      <c r="K86">
-        <v>46</v>
-      </c>
-      <c r="L86">
-        <v>0.47763777043344691</v>
-      </c>
-    </row>
-    <row r="87" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
-        <v>33</v>
-      </c>
-      <c r="C87" t="s">
-        <v>25</v>
-      </c>
-      <c r="D87" t="s">
-        <v>34</v>
-      </c>
-      <c r="E87">
-        <v>2010</v>
-      </c>
-      <c r="F87">
-        <v>1.6E-2</v>
-      </c>
-      <c r="G87">
-        <v>1</v>
-      </c>
-      <c r="H87">
-        <v>2376</v>
-      </c>
-      <c r="I87" s="2">
-        <v>57.2</v>
-      </c>
-      <c r="J87">
-        <v>2.52</v>
-      </c>
-      <c r="K87">
-        <v>45</v>
-      </c>
-      <c r="L87">
-        <v>0.47814004703314078</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="88" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
-        <v>33</v>
-      </c>
-      <c r="C88" t="s">
-        <v>25</v>
-      </c>
-      <c r="D88" t="s">
-        <v>34</v>
-      </c>
-      <c r="E88">
-        <v>2015</v>
-      </c>
-      <c r="F88">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G88">
-        <v>1</v>
-      </c>
-      <c r="H88">
-        <v>2376</v>
-      </c>
-      <c r="I88" s="2">
-        <v>57.20000000000001</v>
-      </c>
-      <c r="J88">
-        <v>2.52</v>
-      </c>
-      <c r="K88">
-        <v>40</v>
-      </c>
-      <c r="L88">
-        <v>0.47814004703314084</v>
-      </c>
-    </row>
-    <row r="89" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
-        <v>33</v>
-      </c>
-      <c r="C89" t="s">
-        <v>25</v>
-      </c>
-      <c r="D89" t="s">
-        <v>34</v>
-      </c>
-      <c r="E89">
-        <v>2020</v>
-      </c>
-      <c r="F89">
-        <v>1.2E-2</v>
-      </c>
-      <c r="G89">
-        <v>1</v>
-      </c>
-      <c r="H89">
-        <v>2376</v>
-      </c>
-      <c r="I89" s="2">
-        <v>57.20000000000001</v>
-      </c>
-      <c r="J89">
-        <v>2.52</v>
-      </c>
-      <c r="K89">
-        <v>35</v>
-      </c>
-      <c r="L89">
-        <v>0.47814004703314078</v>
-      </c>
-    </row>
-    <row r="90" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>35</v>
-      </c>
-      <c r="C90" t="s">
-        <v>25</v>
-      </c>
-      <c r="D90" t="s">
-        <v>36</v>
-      </c>
-      <c r="E90">
-        <v>2007</v>
-      </c>
-      <c r="F90">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="G90">
-        <v>1</v>
-      </c>
-      <c r="H90">
-        <v>2376</v>
-      </c>
-      <c r="I90" s="2">
-        <v>57.2</v>
-      </c>
-      <c r="J90">
-        <v>2.52</v>
-      </c>
-      <c r="K90">
-        <v>48</v>
-      </c>
-      <c r="L90">
-        <v>0.40144059976798208</v>
-      </c>
-    </row>
-    <row r="91" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
-        <v>35</v>
-      </c>
-      <c r="C91" t="s">
-        <v>25</v>
-      </c>
-      <c r="D91" t="s">
-        <v>36</v>
-      </c>
-      <c r="E91">
-        <v>2011</v>
-      </c>
-      <c r="F91">
-        <v>2.4E-2</v>
-      </c>
-      <c r="G91">
-        <v>1</v>
-      </c>
-      <c r="H91">
-        <v>2376</v>
-      </c>
-      <c r="I91" s="2">
-        <v>57.20000000000001</v>
-      </c>
-      <c r="J91">
-        <v>2.52</v>
-      </c>
-      <c r="K91">
-        <v>44</v>
-      </c>
-      <c r="L91">
-        <v>0.40144059976798202</v>
-      </c>
-    </row>
-    <row r="92" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
-        <v>35</v>
-      </c>
-      <c r="C92" t="s">
-        <v>25</v>
-      </c>
-      <c r="D92" t="s">
-        <v>36</v>
-      </c>
-      <c r="E92">
-        <v>2012</v>
-      </c>
-      <c r="F92">
-        <v>7.9000000000000001E-2</v>
-      </c>
-      <c r="G92">
-        <v>1</v>
-      </c>
-      <c r="H92">
-        <v>2376</v>
-      </c>
-      <c r="I92" s="2">
-        <v>57.2</v>
-      </c>
-      <c r="J92">
-        <v>2.52</v>
-      </c>
-      <c r="K92">
-        <v>43</v>
-      </c>
-      <c r="L92">
-        <v>0.40144059976798202</v>
-      </c>
-    </row>
-    <row r="93" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
-        <v>35</v>
-      </c>
-      <c r="C93" t="s">
-        <v>25</v>
-      </c>
-      <c r="D93" t="s">
-        <v>36</v>
-      </c>
-      <c r="E93">
-        <v>2023</v>
-      </c>
-      <c r="F93">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="G93">
-        <v>1</v>
-      </c>
-      <c r="H93">
-        <v>2376</v>
-      </c>
-      <c r="I93" s="2">
-        <v>57.2</v>
-      </c>
-      <c r="J93">
-        <v>2.52</v>
-      </c>
-      <c r="K93">
-        <v>32</v>
-      </c>
-      <c r="L93">
-        <v>0.40144059976798208</v>
-      </c>
-    </row>
-    <row r="94" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B94" t="s">
-        <v>35</v>
-      </c>
-      <c r="C94" t="s">
-        <v>25</v>
-      </c>
-      <c r="D94" t="s">
-        <v>36</v>
-      </c>
-      <c r="E94">
-        <v>2024</v>
-      </c>
-      <c r="F94">
-        <v>0.10199999999999999</v>
-      </c>
-      <c r="G94">
-        <v>1</v>
-      </c>
-      <c r="H94">
-        <v>2024</v>
-      </c>
-      <c r="I94" s="2">
-        <v>48.4</v>
-      </c>
-      <c r="J94">
-        <v>2.3100000000000005</v>
-      </c>
-      <c r="K94">
-        <v>31</v>
-      </c>
-      <c r="L94">
-        <v>0.40144059976798202</v>
-      </c>
-    </row>
-    <row r="95" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B95" t="s">
-        <v>37</v>
-      </c>
-      <c r="C95" t="s">
-        <v>25</v>
-      </c>
-      <c r="D95" t="s">
-        <v>38</v>
-      </c>
-      <c r="E95">
-        <v>2023</v>
-      </c>
-      <c r="F95">
-        <v>3.9E-2</v>
-      </c>
-      <c r="G95">
-        <v>1</v>
-      </c>
-      <c r="H95">
-        <v>2376</v>
-      </c>
-      <c r="I95" s="2">
-        <v>57.2</v>
-      </c>
-      <c r="J95">
-        <v>2.52</v>
-      </c>
-      <c r="K95">
-        <v>32</v>
-      </c>
-      <c r="L95">
-        <v>0.365520596150406</v>
-      </c>
-    </row>
-    <row r="96" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
-        <v>39</v>
-      </c>
-      <c r="C96" t="s">
-        <v>25</v>
-      </c>
-      <c r="D96" t="s">
-        <v>40</v>
-      </c>
-      <c r="E96">
-        <v>2005</v>
-      </c>
-      <c r="F96">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="G96">
-        <v>1</v>
-      </c>
-      <c r="H96">
-        <v>2376</v>
-      </c>
-      <c r="I96" s="2">
-        <v>57.20000000000001</v>
-      </c>
-      <c r="J96">
-        <v>2.52</v>
-      </c>
-      <c r="K96">
-        <v>50</v>
-      </c>
-      <c r="L96">
-        <v>0.41047488326249421</v>
-      </c>
-    </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B97" t="s">
-        <v>39</v>
-      </c>
-      <c r="C97" t="s">
-        <v>25</v>
-      </c>
-      <c r="D97" t="s">
-        <v>40</v>
-      </c>
-      <c r="E97">
-        <v>2012</v>
-      </c>
-      <c r="F97">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="G97">
-        <v>1</v>
-      </c>
-      <c r="H97">
-        <v>2376</v>
-      </c>
-      <c r="I97" s="2">
-        <v>57.2</v>
-      </c>
-      <c r="J97">
-        <v>2.52</v>
-      </c>
-      <c r="K97">
-        <v>43</v>
-      </c>
-      <c r="L97">
-        <v>0.41047488326249421</v>
-      </c>
-    </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
-        <v>39</v>
-      </c>
-      <c r="C98" t="s">
-        <v>25</v>
-      </c>
-      <c r="D98" t="s">
-        <v>40</v>
-      </c>
-      <c r="E98">
-        <v>2013</v>
-      </c>
-      <c r="F98">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="G98">
-        <v>1</v>
-      </c>
-      <c r="H98">
-        <v>2376</v>
-      </c>
-      <c r="I98" s="2">
-        <v>57.2</v>
-      </c>
-      <c r="J98">
-        <v>2.52</v>
-      </c>
-      <c r="K98">
-        <v>42</v>
-      </c>
-      <c r="L98">
-        <v>0.41047488326249421</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB00F012-F8E8-4350-9E8E-BDEDE3397709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE97D71-D12F-4628-A099-4300B03AA15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="233">
   <si>
     <t>~fi_t</t>
   </si>
@@ -802,9 +802,6 @@
   </si>
   <si>
     <t>TechDesc</t>
-  </si>
-  <si>
-    <t>Tcap</t>
   </si>
   <si>
     <t>Tslvl</t>
@@ -855,7 +852,7 @@
     <numFmt numFmtId="184" formatCode="#."/>
     <numFmt numFmtId="185" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -920,12 +917,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -1539,7 +1530,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1547,8 +1538,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1557,7 +1548,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1566,7 +1557,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1575,7 +1566,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1592,7 +1583,7 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1601,7 +1592,7 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1610,7 +1601,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1619,7 +1610,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1649,7 +1640,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1658,7 +1649,7 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1667,7 +1658,7 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1676,24 +1667,24 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFont="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="37" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1730,7 +1721,7 @@
     <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1753,121 +1744,121 @@
     <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="174" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="174" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="182" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="182" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="182" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="182" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="183" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="27" fillId="0" borderId="0">
+    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -2053,9 +2044,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="40" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="40" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
@@ -2065,8 +2056,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="37" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="37" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2100,24 +2091,24 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="21" fillId="0" borderId="17">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="17">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="21" fillId="0" borderId="17">
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="17">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="21" fillId="0" borderId="17">
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="17">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="21" fillId="0" borderId="17">
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="17">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
@@ -4769,21 +4760,21 @@
         <v>27</v>
       </c>
       <c r="Y7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z7" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="Z7" s="15" t="s">
+      <c r="AA7" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="AA7" s="15" t="s">
+      <c r="AB7" s="15" t="s">
         <v>224</v>
-      </c>
-      <c r="AB7" s="15" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="8" spans="2:28" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="18"/>
@@ -4802,28 +4793,28 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="U8" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="V8" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="V8" s="16" t="s">
+      <c r="W8" s="16" t="s">
         <v>227</v>
-      </c>
-      <c r="W8" s="16" t="s">
-        <v>228</v>
       </c>
       <c r="X8" s="16" t="s">
         <v>27</v>
       </c>
       <c r="Y8" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="Z8" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="Z8" s="16" t="s">
+      <c r="AA8" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="AA8" s="16" t="s">
+      <c r="AB8" s="16" t="s">
         <v>231</v>
-      </c>
-      <c r="AB8" s="16" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="9" spans="2:28" x14ac:dyDescent="0.25">

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE97D71-D12F-4628-A099-4300B03AA15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DEB8E2-4934-4FBA-B652-2FDA51745DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -841,16 +841,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="173" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="182" formatCode="m\o\n\th\ d\,\ yyyy"/>
-    <numFmt numFmtId="183" formatCode="#.00"/>
-    <numFmt numFmtId="184" formatCode="#."/>
-    <numFmt numFmtId="185" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="m\o\n\th\ d\,\ yyyy"/>
+    <numFmt numFmtId="168" formatCode="#.00"/>
+    <numFmt numFmtId="169" formatCode="#."/>
+    <numFmt numFmtId="170" formatCode="\Te\x\t"/>
   </numFmts>
   <fonts count="39" x14ac:knownFonts="1">
     <font>
@@ -876,6 +875,8 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="186"/>
     </font>
     <font>
       <b/>
@@ -1526,7 +1527,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1685,7 +1686,7 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="37" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="38" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1711,15 +1712,15 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1732,41 +1733,41 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1774,28 +1775,28 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2093,17 +2094,17 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="17">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="17">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="17">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="17">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="17">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="17">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="17">
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="17">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2116,13 +2117,13 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="15" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" xfId="253" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="253" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="319" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="319" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2134,26 +2135,26 @@
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="185" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="6" xfId="319" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="319" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="185" fontId="4" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="185" fontId="5" fillId="18" borderId="5" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="5" fillId="18" borderId="5" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="185" fontId="4" fillId="15" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="15" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="185" fontId="6" fillId="18" borderId="5" xfId="253" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="18" borderId="5" xfId="253" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="185" fontId="6" fillId="18" borderId="5" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="18" borderId="5" xfId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4678,7 +4679,7 @@
   </cols>
   <sheetData>
     <row r="6" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="10"/>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DEB8E2-4934-4FBA-B652-2FDA51745DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1156D8-21F4-4FF8-B6A1-C0FC38728B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <definedName name="Start">[1]SETUP!$F$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -76,12 +77,12 @@
     <author>tc={D3B26940-5207-4925-84BA-C36AB3766D74}</author>
     <author>tc={E45DD652-654C-4828-8A13-679EDDC53E65}</author>
     <author>tc={5D0B02A9-24B3-4F36-8683-2AD26D1E0821}</author>
+    <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
     <author>tc={C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}</author>
-    <author>tc={D6875D25-4560-414C-93D8-31A6498B8282}</author>
     <author>tc={C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}</author>
   </authors>
   <commentList>
-    <comment ref="Z24" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+    <comment ref="V25" authorId="0" shapeId="0" xr:uid="{D3B26940-5207-4925-84BA-C36AB3766D74}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -105,7 +106,16 @@
     TODO: set their actual start date and then add how much they produce in 2025</t>
       </text>
     </comment>
-    <comment ref="P39" authorId="3" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+    <comment ref="E42" authorId="3" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Ei tea
+</t>
+      </text>
+    </comment>
+    <comment ref="P76" authorId="4" shapeId="0" xr:uid="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -114,16 +124,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="E42" authorId="4" shapeId="0" xr:uid="{D6875D25-4560-414C-93D8-31A6498B8282}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Ei tea
-</t>
-      </text>
-    </comment>
-    <comment ref="S43" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+    <comment ref="S80" authorId="5" shapeId="0" xr:uid="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3138,7 +3139,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="Z24" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
+  <threadedComment ref="V25" dT="2026-03-05T12:47:49.66" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D3B26940-5207-4925-84BA-C36AB3766D74}">
     <text>Miks daynite (hydro samuti)</text>
   </threadedComment>
   <threadedComment ref="F33" dT="2026-01-22T14:00:05.64" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{E45DD652-654C-4828-8A13-679EDDC53E65}">
@@ -3147,15 +3148,15 @@
   <threadedComment ref="B34" dT="2026-02-02T06:49:06.81" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{5D0B02A9-24B3-4F36-8683-2AD26D1E0821}">
     <text>TODO: set their actual start date and then add how much they produce in 2025</text>
   </threadedComment>
-  <threadedComment ref="P39" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
-    <text xml:space="preserve">NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)
-</text>
-  </threadedComment>
   <threadedComment ref="E42" dT="2026-03-04T15:33:22.35" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{D6875D25-4560-414C-93D8-31A6498B8282}">
     <text xml:space="preserve">Ei tea
 </text>
   </threadedComment>
-  <threadedComment ref="S43" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
+  <threadedComment ref="P76" dT="2026-03-05T12:22:32.07" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C9FF73F0-A53F-4E15-A8C5-00DAE5061F13}">
+    <text xml:space="preserve">NCAP_FOM (currency/GW-yr)=100/1.31​×NCAP_COST (currency/GW)
+</text>
+  </threadedComment>
+  <threadedComment ref="S80" dT="2026-03-05T12:58:31.38" personId="{9CD26280-DD25-46DF-A708-6877D8A68AD8}" id="{C2CA05C3-E9FD-442F-962C-5D4E7F1ADE70}">
     <text>Took same as chp</text>
   </threadedComment>
 </ThreadedComments>
@@ -4648,7 +4649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
-  <dimension ref="B6:AB62"/>
+  <dimension ref="B6:X85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
@@ -4669,16 +4670,16 @@
     <col min="17" max="17" width="40.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="64.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D6" s="8" t="s">
         <v>0</v>
       </c>
@@ -4695,18 +4696,8 @@
       <c r="P6" s="7"/>
       <c r="Q6" s="9"/>
       <c r="R6" s="7"/>
-      <c r="U6" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="V6" s="11"/>
-      <c r="W6" s="12"/>
-      <c r="X6" s="12"/>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
-    </row>
-    <row r="7" spans="2:28" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="2:24" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="13" t="s">
         <v>1</v>
       </c>
@@ -4746,34 +4737,18 @@
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="U7" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="V7" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="W7" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="X7" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y7" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z7" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="AA7" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB7" s="15" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="8" spans="2:28" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q7" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="R7" s="11"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+    </row>
+    <row r="8" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="19" t="s">
         <v>232</v>
       </c>
@@ -4791,34 +4766,32 @@
       <c r="N8" s="5"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="U8" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="V8" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="W8" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="X8" s="16" t="s">
+      <c r="Q8" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="T8" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="Y8" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="Z8" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="AA8" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="AB8" s="16" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="9" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="U8" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="V8" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="W8" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="X8" s="15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>184</v>
       </c>
@@ -4852,29 +4825,32 @@
       <c r="L9" s="3">
         <v>0.1461854238754417</v>
       </c>
-      <c r="U9" t="s">
-        <v>31</v>
-      </c>
-      <c r="V9" t="s">
-        <v>184</v>
-      </c>
-      <c r="W9" t="s">
-        <v>38</v>
-      </c>
-      <c r="X9" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="Q9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="S9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="T9" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="U9" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="V9" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="W9" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="X9" s="16" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>185</v>
       </c>
@@ -4908,29 +4884,29 @@
       <c r="L10" s="3">
         <v>0.1461854238754417</v>
       </c>
+      <c r="Q10" t="s">
+        <v>31</v>
+      </c>
+      <c r="R10" t="s">
+        <v>184</v>
+      </c>
+      <c r="S10" t="s">
+        <v>38</v>
+      </c>
+      <c r="T10" t="s">
+        <v>32</v>
+      </c>
       <c r="U10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V10" t="s">
-        <v>185</v>
-      </c>
-      <c r="W10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X10" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>186</v>
       </c>
@@ -4964,29 +4940,29 @@
       <c r="L11" s="3">
         <v>0.14867925344692126</v>
       </c>
+      <c r="Q11" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" t="s">
+        <v>185</v>
+      </c>
+      <c r="S11" t="s">
+        <v>38</v>
+      </c>
+      <c r="T11" t="s">
+        <v>32</v>
+      </c>
       <c r="U11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V11" t="s">
-        <v>186</v>
-      </c>
-      <c r="W11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X11" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>187</v>
       </c>
@@ -5020,29 +4996,29 @@
       <c r="L12" s="3">
         <v>0.14701259708091721</v>
       </c>
+      <c r="Q12" t="s">
+        <v>31</v>
+      </c>
+      <c r="R12" t="s">
+        <v>186</v>
+      </c>
+      <c r="S12" t="s">
+        <v>38</v>
+      </c>
+      <c r="T12" t="s">
+        <v>32</v>
+      </c>
       <c r="U12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V12" t="s">
-        <v>187</v>
-      </c>
-      <c r="W12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X12" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>188</v>
       </c>
@@ -5076,29 +5052,29 @@
       <c r="L13" s="3">
         <v>0.15309859852159369</v>
       </c>
+      <c r="Q13" t="s">
+        <v>31</v>
+      </c>
+      <c r="R13" t="s">
+        <v>187</v>
+      </c>
+      <c r="S13" t="s">
+        <v>38</v>
+      </c>
+      <c r="T13" t="s">
+        <v>32</v>
+      </c>
       <c r="U13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V13" t="s">
-        <v>188</v>
-      </c>
-      <c r="W13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X13" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>193</v>
       </c>
@@ -5132,29 +5108,29 @@
       <c r="L14" s="3">
         <v>0.15309859852159369</v>
       </c>
+      <c r="Q14" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" t="s">
+        <v>188</v>
+      </c>
+      <c r="S14" t="s">
+        <v>38</v>
+      </c>
+      <c r="T14" t="s">
+        <v>32</v>
+      </c>
       <c r="U14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V14" t="s">
-        <v>193</v>
-      </c>
-      <c r="W14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X14" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>189</v>
       </c>
@@ -5188,29 +5164,29 @@
       <c r="L15" s="3">
         <v>0.15619560585976827</v>
       </c>
+      <c r="Q15" t="s">
+        <v>31</v>
+      </c>
+      <c r="R15" t="s">
+        <v>193</v>
+      </c>
+      <c r="S15" t="s">
+        <v>38</v>
+      </c>
+      <c r="T15" t="s">
+        <v>32</v>
+      </c>
       <c r="U15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V15" t="s">
-        <v>189</v>
-      </c>
-      <c r="W15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X15" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>190</v>
       </c>
@@ -5244,29 +5220,29 @@
       <c r="L16" s="3">
         <v>0.14537310453496291</v>
       </c>
+      <c r="Q16" t="s">
+        <v>31</v>
+      </c>
+      <c r="R16" t="s">
+        <v>189</v>
+      </c>
+      <c r="S16" t="s">
+        <v>38</v>
+      </c>
+      <c r="T16" t="s">
+        <v>32</v>
+      </c>
       <c r="U16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V16" t="s">
-        <v>190</v>
-      </c>
-      <c r="W16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X16" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>191</v>
       </c>
@@ -5300,29 +5276,29 @@
       <c r="L17" s="3">
         <v>0.14763873655681015</v>
       </c>
+      <c r="Q17" t="s">
+        <v>31</v>
+      </c>
+      <c r="R17" t="s">
+        <v>190</v>
+      </c>
+      <c r="S17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T17" t="s">
+        <v>32</v>
+      </c>
       <c r="U17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V17" t="s">
-        <v>191</v>
-      </c>
-      <c r="W17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X17" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB17" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>192</v>
       </c>
@@ -5356,29 +5332,29 @@
       <c r="L18" s="3">
         <v>0.1532628310027955</v>
       </c>
+      <c r="Q18" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" t="s">
+        <v>191</v>
+      </c>
+      <c r="S18" t="s">
+        <v>38</v>
+      </c>
+      <c r="T18" t="s">
+        <v>32</v>
+      </c>
       <c r="U18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V18" t="s">
-        <v>192</v>
-      </c>
-      <c r="W18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X18" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>208</v>
       </c>
@@ -5412,29 +5388,29 @@
       <c r="L19" s="3">
         <v>0.1461854238754417</v>
       </c>
+      <c r="Q19" t="s">
+        <v>31</v>
+      </c>
+      <c r="R19" t="s">
+        <v>192</v>
+      </c>
+      <c r="S19" t="s">
+        <v>38</v>
+      </c>
+      <c r="T19" t="s">
+        <v>32</v>
+      </c>
       <c r="U19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V19" t="s">
-        <v>208</v>
-      </c>
-      <c r="W19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X19" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>209</v>
       </c>
@@ -5468,29 +5444,29 @@
       <c r="L20" s="3">
         <v>0.1461854238754417</v>
       </c>
+      <c r="Q20" t="s">
+        <v>31</v>
+      </c>
+      <c r="R20" t="s">
+        <v>208</v>
+      </c>
+      <c r="S20" t="s">
+        <v>38</v>
+      </c>
+      <c r="T20" t="s">
+        <v>32</v>
+      </c>
       <c r="U20" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V20" t="s">
-        <v>209</v>
-      </c>
-      <c r="W20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X20" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB20" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>215</v>
       </c>
@@ -5524,29 +5500,29 @@
       <c r="L21" s="3">
         <v>0.1461854238754417</v>
       </c>
+      <c r="Q21" t="s">
+        <v>31</v>
+      </c>
+      <c r="R21" t="s">
+        <v>209</v>
+      </c>
+      <c r="S21" t="s">
+        <v>38</v>
+      </c>
+      <c r="T21" t="s">
+        <v>32</v>
+      </c>
       <c r="U21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V21" t="s">
-        <v>215</v>
-      </c>
-      <c r="W21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X21" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB21" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>210</v>
       </c>
@@ -5580,29 +5556,29 @@
       <c r="L22" s="3">
         <v>0.1461854238754417</v>
       </c>
+      <c r="Q22" t="s">
+        <v>31</v>
+      </c>
+      <c r="R22" t="s">
+        <v>215</v>
+      </c>
+      <c r="S22" t="s">
+        <v>38</v>
+      </c>
+      <c r="T22" t="s">
+        <v>32</v>
+      </c>
       <c r="U22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V22" t="s">
-        <v>210</v>
-      </c>
-      <c r="W22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X22" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB22" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>211</v>
       </c>
@@ -5636,29 +5612,29 @@
       <c r="L23" s="3">
         <v>0.1461854238754417</v>
       </c>
+      <c r="Q23" t="s">
+        <v>31</v>
+      </c>
+      <c r="R23" t="s">
+        <v>210</v>
+      </c>
+      <c r="S23" t="s">
+        <v>38</v>
+      </c>
+      <c r="T23" t="s">
+        <v>32</v>
+      </c>
       <c r="U23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V23" t="s">
-        <v>211</v>
-      </c>
-      <c r="W23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X23" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB23" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>24</v>
       </c>
@@ -5692,29 +5668,29 @@
       <c r="L24">
         <v>0.4</v>
       </c>
+      <c r="Q24" t="s">
+        <v>31</v>
+      </c>
+      <c r="R24" t="s">
+        <v>211</v>
+      </c>
+      <c r="S24" t="s">
+        <v>38</v>
+      </c>
+      <c r="T24" t="s">
+        <v>32</v>
+      </c>
       <c r="U24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V24" t="s">
-        <v>172</v>
-      </c>
-      <c r="W24" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="X24" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>170</v>
       </c>
@@ -5748,29 +5724,29 @@
       <c r="L25">
         <v>0.4</v>
       </c>
+      <c r="Q25" t="s">
+        <v>31</v>
+      </c>
+      <c r="R25" t="s">
+        <v>172</v>
+      </c>
+      <c r="S25" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25" t="s">
+        <v>32</v>
+      </c>
       <c r="U25" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V25" t="s">
-        <v>24</v>
-      </c>
-      <c r="W25" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="X25" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>171</v>
       </c>
@@ -5804,29 +5780,29 @@
       <c r="L26">
         <v>0.4</v>
       </c>
+      <c r="Q26" t="s">
+        <v>31</v>
+      </c>
+      <c r="R26" t="s">
+        <v>24</v>
+      </c>
+      <c r="S26" t="s">
+        <v>40</v>
+      </c>
+      <c r="T26" t="s">
+        <v>32</v>
+      </c>
       <c r="U26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V26" t="s">
-        <v>170</v>
-      </c>
-      <c r="W26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X26" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB26" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>197</v>
       </c>
@@ -5860,29 +5836,29 @@
       <c r="L27">
         <v>0.4</v>
       </c>
+      <c r="Q27" t="s">
+        <v>31</v>
+      </c>
+      <c r="R27" t="s">
+        <v>170</v>
+      </c>
+      <c r="S27" t="s">
+        <v>40</v>
+      </c>
+      <c r="T27" t="s">
+        <v>32</v>
+      </c>
       <c r="U27" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V27" t="s">
-        <v>171</v>
-      </c>
-      <c r="W27" t="s">
-        <v>198</v>
+        <v>39</v>
       </c>
       <c r="X27" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>199</v>
       </c>
@@ -5916,29 +5892,29 @@
       <c r="L28">
         <v>0.4</v>
       </c>
+      <c r="Q28" t="s">
+        <v>31</v>
+      </c>
+      <c r="R28" t="s">
+        <v>171</v>
+      </c>
+      <c r="S28" t="s">
+        <v>198</v>
+      </c>
+      <c r="T28" t="s">
+        <v>32</v>
+      </c>
       <c r="U28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V28" t="s">
-        <v>197</v>
-      </c>
-      <c r="W28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X28" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB28" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>200</v>
       </c>
@@ -5972,29 +5948,29 @@
       <c r="L29">
         <v>0.4</v>
       </c>
+      <c r="Q29" t="s">
+        <v>31</v>
+      </c>
+      <c r="R29" t="s">
+        <v>197</v>
+      </c>
+      <c r="S29" t="s">
+        <v>38</v>
+      </c>
+      <c r="T29" t="s">
+        <v>32</v>
+      </c>
       <c r="U29" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V29" t="s">
-        <v>199</v>
-      </c>
-      <c r="W29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X29" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>201</v>
       </c>
@@ -6028,29 +6004,29 @@
       <c r="L30">
         <v>0.4</v>
       </c>
+      <c r="Q30" t="s">
+        <v>31</v>
+      </c>
+      <c r="R30" t="s">
+        <v>199</v>
+      </c>
+      <c r="S30" t="s">
+        <v>38</v>
+      </c>
+      <c r="T30" t="s">
+        <v>32</v>
+      </c>
       <c r="U30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V30" t="s">
-        <v>200</v>
-      </c>
-      <c r="W30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X30" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB30" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>202</v>
       </c>
@@ -6084,29 +6060,29 @@
       <c r="L31">
         <v>0.4</v>
       </c>
+      <c r="Q31" t="s">
+        <v>31</v>
+      </c>
+      <c r="R31" t="s">
+        <v>200</v>
+      </c>
+      <c r="S31" t="s">
+        <v>38</v>
+      </c>
+      <c r="T31" t="s">
+        <v>32</v>
+      </c>
       <c r="U31" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V31" t="s">
-        <v>201</v>
-      </c>
-      <c r="W31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X31" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>206</v>
       </c>
@@ -6140,29 +6116,29 @@
       <c r="L32">
         <v>0.4</v>
       </c>
+      <c r="Q32" t="s">
+        <v>31</v>
+      </c>
+      <c r="R32" t="s">
+        <v>201</v>
+      </c>
+      <c r="S32" t="s">
+        <v>38</v>
+      </c>
+      <c r="T32" t="s">
+        <v>32</v>
+      </c>
       <c r="U32" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V32" t="s">
-        <v>202</v>
-      </c>
-      <c r="W32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X32" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB32" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>172</v>
       </c>
@@ -6193,29 +6169,29 @@
       <c r="K33">
         <v>53</v>
       </c>
+      <c r="Q33" t="s">
+        <v>31</v>
+      </c>
+      <c r="R33" t="s">
+        <v>202</v>
+      </c>
+      <c r="S33" t="s">
+        <v>38</v>
+      </c>
+      <c r="T33" t="s">
+        <v>32</v>
+      </c>
       <c r="U33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V33" t="s">
-        <v>206</v>
-      </c>
-      <c r="W33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X33" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB33" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>152</v>
       </c>
@@ -6246,29 +6222,29 @@
       <c r="K34">
         <v>70</v>
       </c>
+      <c r="Q34" t="s">
+        <v>31</v>
+      </c>
+      <c r="R34" t="s">
+        <v>206</v>
+      </c>
+      <c r="S34" t="s">
+        <v>38</v>
+      </c>
+      <c r="T34" t="s">
+        <v>32</v>
+      </c>
       <c r="U34" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V34" t="s">
-        <v>150</v>
-      </c>
-      <c r="W34" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="X34" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z34" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB34" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>150</v>
       </c>
@@ -6299,29 +6275,29 @@
       <c r="K35">
         <v>40</v>
       </c>
+      <c r="Q35" t="s">
+        <v>31</v>
+      </c>
+      <c r="R35" t="s">
+        <v>150</v>
+      </c>
+      <c r="S35" t="s">
+        <v>120</v>
+      </c>
+      <c r="T35" t="s">
+        <v>32</v>
+      </c>
       <c r="U35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V35" t="s">
-        <v>149</v>
-      </c>
-      <c r="W35" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="X35" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z35" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>151</v>
       </c>
@@ -6353,29 +6329,29 @@
       <c r="K36">
         <v>40</v>
       </c>
+      <c r="Q36" t="s">
+        <v>31</v>
+      </c>
+      <c r="R36" t="s">
+        <v>149</v>
+      </c>
+      <c r="S36" t="s">
+        <v>105</v>
+      </c>
+      <c r="T36" t="s">
+        <v>32</v>
+      </c>
       <c r="U36" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V36" t="s">
-        <v>151</v>
-      </c>
-      <c r="W36" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="X36" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>149</v>
       </c>
@@ -6406,29 +6382,29 @@
       <c r="K37">
         <v>73</v>
       </c>
+      <c r="Q37" t="s">
+        <v>31</v>
+      </c>
+      <c r="R37" t="s">
+        <v>151</v>
+      </c>
+      <c r="S37" t="s">
+        <v>106</v>
+      </c>
+      <c r="T37" t="s">
+        <v>32</v>
+      </c>
       <c r="U37" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V37" t="s">
-        <v>152</v>
-      </c>
-      <c r="W37" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="X37" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB37" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>99</v>
       </c>
@@ -6459,29 +6435,29 @@
       <c r="K38">
         <v>40</v>
       </c>
+      <c r="Q38" t="s">
+        <v>31</v>
+      </c>
+      <c r="R38" t="s">
+        <v>152</v>
+      </c>
+      <c r="S38" t="s">
+        <v>107</v>
+      </c>
+      <c r="T38" t="s">
+        <v>32</v>
+      </c>
       <c r="U38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V38" t="s">
-        <v>99</v>
-      </c>
-      <c r="W38" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="X38" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB38" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>100</v>
       </c>
@@ -6512,41 +6488,29 @@
       <c r="K39">
         <v>40</v>
       </c>
-      <c r="P39" t="s">
-        <v>162</v>
-      </c>
       <c r="Q39" t="s">
-        <v>167</v>
+        <v>31</v>
       </c>
       <c r="R39" t="s">
-        <v>168</v>
+        <v>99</v>
       </c>
       <c r="S39" t="s">
-        <v>169</v>
+        <v>118</v>
+      </c>
+      <c r="T39" t="s">
+        <v>32</v>
       </c>
       <c r="U39" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V39" t="s">
-        <v>100</v>
-      </c>
-      <c r="W39" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="X39" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB39" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>101</v>
       </c>
@@ -6577,44 +6541,29 @@
       <c r="K40">
         <v>40</v>
       </c>
-      <c r="O40" t="s">
-        <v>148</v>
-      </c>
-      <c r="P40" s="3">
-        <v>1.31</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>4812.0244000000002</v>
-      </c>
-      <c r="R40">
-        <v>0.33</v>
-      </c>
-      <c r="S40">
-        <v>4.1005000000000003</v>
+      <c r="Q40" t="s">
+        <v>31</v>
+      </c>
+      <c r="R40" t="s">
+        <v>100</v>
+      </c>
+      <c r="S40" t="s">
+        <v>108</v>
+      </c>
+      <c r="T40" t="s">
+        <v>32</v>
       </c>
       <c r="U40" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V40" t="s">
-        <v>101</v>
-      </c>
-      <c r="W40" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="X40" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z40" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB40" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>102</v>
       </c>
@@ -6645,44 +6594,29 @@
       <c r="K41">
         <v>40</v>
       </c>
-      <c r="O41" t="s">
-        <v>165</v>
-      </c>
-      <c r="P41" s="3">
-        <v>3.3294999999999999</v>
-      </c>
-      <c r="Q41" s="1">
-        <v>1175.5066999999999</v>
-      </c>
-      <c r="R41">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="S41">
-        <v>5.8775000000000004</v>
+      <c r="Q41" t="s">
+        <v>31</v>
+      </c>
+      <c r="R41" t="s">
+        <v>101</v>
+      </c>
+      <c r="S41" t="s">
+        <v>109</v>
+      </c>
+      <c r="T41" t="s">
+        <v>32</v>
       </c>
       <c r="U41" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V41" t="s">
-        <v>102</v>
-      </c>
-      <c r="W41" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="X41" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB41" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>103</v>
       </c>
@@ -6713,34 +6647,29 @@
       <c r="K42">
         <v>40</v>
       </c>
-      <c r="O42" t="s">
-        <v>166</v>
-      </c>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="1"/>
+      <c r="Q42" t="s">
+        <v>31</v>
+      </c>
+      <c r="R42" t="s">
+        <v>102</v>
+      </c>
+      <c r="S42" t="s">
+        <v>110</v>
+      </c>
+      <c r="T42" t="s">
+        <v>32</v>
+      </c>
       <c r="U42" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V42" t="s">
-        <v>103</v>
-      </c>
-      <c r="W42" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="X42" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y42" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z42" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB42" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>153</v>
       </c>
@@ -6771,44 +6700,29 @@
       <c r="K43">
         <v>40</v>
       </c>
-      <c r="O43" t="s">
-        <v>163</v>
-      </c>
-      <c r="P43">
-        <v>4.5269000000000004</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>2950.7891</v>
-      </c>
-      <c r="R43">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="S43">
-        <v>2.8138000000000001</v>
+      <c r="Q43" t="s">
+        <v>31</v>
+      </c>
+      <c r="R43" t="s">
+        <v>103</v>
+      </c>
+      <c r="S43" t="s">
+        <v>104</v>
+      </c>
+      <c r="T43" t="s">
+        <v>32</v>
       </c>
       <c r="U43" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V43" t="s">
-        <v>153</v>
-      </c>
-      <c r="W43" t="s">
-        <v>119</v>
+        <v>39</v>
       </c>
       <c r="X43" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB43" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>111</v>
       </c>
@@ -6839,44 +6753,29 @@
       <c r="K44">
         <v>40</v>
       </c>
-      <c r="O44" t="s">
-        <v>164</v>
-      </c>
-      <c r="P44">
-        <v>3.6080999999999999</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>4516.7133000000003</v>
-      </c>
-      <c r="R44">
-        <v>0.2994</v>
-      </c>
-      <c r="S44">
-        <v>2.8138000000000001</v>
+      <c r="Q44" t="s">
+        <v>31</v>
+      </c>
+      <c r="R44" t="s">
+        <v>153</v>
+      </c>
+      <c r="S44" t="s">
+        <v>119</v>
+      </c>
+      <c r="T44" t="s">
+        <v>32</v>
       </c>
       <c r="U44" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V44" t="s">
-        <v>111</v>
-      </c>
-      <c r="W44" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="X44" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB44" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>113</v>
       </c>
@@ -6907,36 +6806,29 @@
       <c r="K45">
         <v>40</v>
       </c>
-      <c r="O45" t="s">
-        <v>21</v>
-      </c>
-      <c r="P45" s="2">
-        <v>1.5780000000000001</v>
-      </c>
-      <c r="Q45" s="3"/>
+      <c r="Q45" t="s">
+        <v>31</v>
+      </c>
+      <c r="R45" t="s">
+        <v>111</v>
+      </c>
+      <c r="S45" t="s">
+        <v>112</v>
+      </c>
+      <c r="T45" t="s">
+        <v>32</v>
+      </c>
       <c r="U45" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V45" t="s">
-        <v>113</v>
-      </c>
-      <c r="W45" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="X45" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z45" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB45" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>127</v>
       </c>
@@ -6967,39 +6859,29 @@
       <c r="K46">
         <v>40</v>
       </c>
-      <c r="O46" t="s">
-        <v>23</v>
-      </c>
-      <c r="P46" s="2">
-        <v>1.2514000000000001</v>
-      </c>
-      <c r="Q46" s="3"/>
-      <c r="S46">
-        <v>2.0036999999999998</v>
+      <c r="Q46" t="s">
+        <v>31</v>
+      </c>
+      <c r="R46" t="s">
+        <v>113</v>
+      </c>
+      <c r="S46" t="s">
+        <v>114</v>
+      </c>
+      <c r="T46" t="s">
+        <v>32</v>
       </c>
       <c r="U46" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V46" t="s">
-        <v>127</v>
-      </c>
-      <c r="W46" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="X46" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB46" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>115</v>
       </c>
@@ -7030,31 +6912,29 @@
       <c r="K47">
         <v>72</v>
       </c>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="3"/>
+      <c r="Q47" t="s">
+        <v>31</v>
+      </c>
+      <c r="R47" t="s">
+        <v>127</v>
+      </c>
+      <c r="S47" t="s">
+        <v>128</v>
+      </c>
+      <c r="T47" t="s">
+        <v>32</v>
+      </c>
       <c r="U47" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V47" t="s">
-        <v>115</v>
-      </c>
-      <c r="W47" t="s">
-        <v>116</v>
+        <v>39</v>
       </c>
       <c r="X47" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB47" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>126</v>
       </c>
@@ -7085,31 +6965,29 @@
       <c r="K48">
         <v>40</v>
       </c>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="3"/>
+      <c r="Q48" t="s">
+        <v>31</v>
+      </c>
+      <c r="R48" t="s">
+        <v>115</v>
+      </c>
+      <c r="S48" t="s">
+        <v>116</v>
+      </c>
+      <c r="T48" t="s">
+        <v>32</v>
+      </c>
       <c r="U48" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V48" t="s">
-        <v>126</v>
-      </c>
-      <c r="W48" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="X48" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y48" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB48" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>121</v>
       </c>
@@ -7140,29 +7018,29 @@
       <c r="K49">
         <v>40</v>
       </c>
+      <c r="Q49" t="s">
+        <v>31</v>
+      </c>
+      <c r="R49" t="s">
+        <v>126</v>
+      </c>
+      <c r="S49" t="s">
+        <v>117</v>
+      </c>
+      <c r="T49" t="s">
+        <v>32</v>
+      </c>
       <c r="U49" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V49" t="s">
-        <v>121</v>
-      </c>
-      <c r="W49" t="s">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="X49" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y49" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z49" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB49" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>125</v>
       </c>
@@ -7193,29 +7071,29 @@
       <c r="K50">
         <v>40</v>
       </c>
+      <c r="Q50" t="s">
+        <v>31</v>
+      </c>
+      <c r="R50" t="s">
+        <v>121</v>
+      </c>
+      <c r="S50" t="s">
+        <v>122</v>
+      </c>
+      <c r="T50" t="s">
+        <v>32</v>
+      </c>
       <c r="U50" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V50" t="s">
-        <v>125</v>
-      </c>
-      <c r="W50" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="X50" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>154</v>
       </c>
@@ -7246,29 +7124,29 @@
       <c r="K51">
         <v>40</v>
       </c>
+      <c r="Q51" t="s">
+        <v>31</v>
+      </c>
+      <c r="R51" t="s">
+        <v>125</v>
+      </c>
+      <c r="S51" t="s">
+        <v>123</v>
+      </c>
+      <c r="T51" t="s">
+        <v>32</v>
+      </c>
       <c r="U51" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V51" t="s">
-        <v>154</v>
-      </c>
-      <c r="W51" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="X51" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB51" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>129</v>
       </c>
@@ -7299,29 +7177,29 @@
       <c r="K52">
         <v>40</v>
       </c>
+      <c r="Q52" t="s">
+        <v>31</v>
+      </c>
+      <c r="R52" t="s">
+        <v>154</v>
+      </c>
+      <c r="S52" t="s">
+        <v>124</v>
+      </c>
+      <c r="T52" t="s">
+        <v>32</v>
+      </c>
       <c r="U52" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V52" t="s">
-        <v>129</v>
-      </c>
-      <c r="W52" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="X52" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y52" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z52" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB52" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>131</v>
       </c>
@@ -7352,29 +7230,29 @@
       <c r="K53">
         <v>40</v>
       </c>
+      <c r="Q53" t="s">
+        <v>31</v>
+      </c>
+      <c r="R53" t="s">
+        <v>129</v>
+      </c>
+      <c r="S53" t="s">
+        <v>130</v>
+      </c>
+      <c r="T53" t="s">
+        <v>32</v>
+      </c>
       <c r="U53" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V53" t="s">
-        <v>131</v>
-      </c>
-      <c r="W53" t="s">
-        <v>132</v>
+        <v>39</v>
       </c>
       <c r="X53" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z53" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB53" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>133</v>
       </c>
@@ -7405,29 +7283,29 @@
       <c r="K54">
         <v>40</v>
       </c>
+      <c r="Q54" t="s">
+        <v>31</v>
+      </c>
+      <c r="R54" t="s">
+        <v>131</v>
+      </c>
+      <c r="S54" t="s">
+        <v>132</v>
+      </c>
+      <c r="T54" t="s">
+        <v>32</v>
+      </c>
       <c r="U54" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V54" t="s">
-        <v>133</v>
-      </c>
-      <c r="W54" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="X54" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y54" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB54" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>135</v>
       </c>
@@ -7458,29 +7336,29 @@
       <c r="K55">
         <v>40</v>
       </c>
+      <c r="Q55" t="s">
+        <v>31</v>
+      </c>
+      <c r="R55" t="s">
+        <v>133</v>
+      </c>
+      <c r="S55" t="s">
+        <v>134</v>
+      </c>
+      <c r="T55" t="s">
+        <v>32</v>
+      </c>
       <c r="U55" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V55" t="s">
-        <v>135</v>
-      </c>
-      <c r="W55" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="X55" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z55" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB55" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>137</v>
       </c>
@@ -7511,29 +7389,29 @@
       <c r="K56">
         <v>40</v>
       </c>
+      <c r="Q56" t="s">
+        <v>31</v>
+      </c>
+      <c r="R56" t="s">
+        <v>135</v>
+      </c>
+      <c r="S56" t="s">
+        <v>136</v>
+      </c>
+      <c r="T56" t="s">
+        <v>32</v>
+      </c>
       <c r="U56" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V56" t="s">
-        <v>137</v>
-      </c>
-      <c r="W56" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="X56" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y56" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z56" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB56" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>139</v>
       </c>
@@ -7564,29 +7442,29 @@
       <c r="K57">
         <v>40</v>
       </c>
+      <c r="Q57" t="s">
+        <v>31</v>
+      </c>
+      <c r="R57" t="s">
+        <v>137</v>
+      </c>
+      <c r="S57" t="s">
+        <v>138</v>
+      </c>
+      <c r="T57" t="s">
+        <v>32</v>
+      </c>
       <c r="U57" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V57" t="s">
-        <v>139</v>
-      </c>
-      <c r="W57" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="X57" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y57" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z57" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB57" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>141</v>
       </c>
@@ -7617,29 +7495,29 @@
       <c r="K58">
         <v>40</v>
       </c>
+      <c r="Q58" t="s">
+        <v>31</v>
+      </c>
+      <c r="R58" t="s">
+        <v>139</v>
+      </c>
+      <c r="S58" t="s">
+        <v>140</v>
+      </c>
+      <c r="T58" t="s">
+        <v>32</v>
+      </c>
       <c r="U58" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V58" t="s">
-        <v>141</v>
-      </c>
-      <c r="W58" t="s">
-        <v>142</v>
+        <v>39</v>
       </c>
       <c r="X58" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y58" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z58" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB58" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>143</v>
       </c>
@@ -7670,29 +7548,29 @@
       <c r="K59">
         <v>40</v>
       </c>
+      <c r="Q59" t="s">
+        <v>31</v>
+      </c>
+      <c r="R59" t="s">
+        <v>141</v>
+      </c>
+      <c r="S59" t="s">
+        <v>142</v>
+      </c>
+      <c r="T59" t="s">
+        <v>32</v>
+      </c>
       <c r="U59" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V59" t="s">
-        <v>143</v>
-      </c>
-      <c r="W59" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="X59" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y59" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z59" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB59" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>144</v>
       </c>
@@ -7723,29 +7601,29 @@
       <c r="K60">
         <v>40</v>
       </c>
+      <c r="Q60" t="s">
+        <v>31</v>
+      </c>
+      <c r="R60" t="s">
+        <v>143</v>
+      </c>
+      <c r="S60" t="s">
+        <v>145</v>
+      </c>
+      <c r="T60" t="s">
+        <v>32</v>
+      </c>
       <c r="U60" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V60" t="s">
-        <v>144</v>
-      </c>
-      <c r="W60" t="s">
-        <v>146</v>
+        <v>39</v>
       </c>
       <c r="X60" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y60" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z60" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB60" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>147</v>
       </c>
@@ -7776,29 +7654,29 @@
       <c r="K61">
         <v>40</v>
       </c>
+      <c r="Q61" t="s">
+        <v>31</v>
+      </c>
+      <c r="R61" t="s">
+        <v>144</v>
+      </c>
+      <c r="S61" t="s">
+        <v>146</v>
+      </c>
+      <c r="T61" t="s">
+        <v>32</v>
+      </c>
       <c r="U61" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V61" t="s">
-        <v>147</v>
-      </c>
-      <c r="W61" t="s">
-        <v>174</v>
+        <v>39</v>
       </c>
       <c r="X61" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y61" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z61" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB61" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>17</v>
       </c>
@@ -7817,27 +7695,168 @@
       <c r="G62" s="3">
         <v>0.33123000000000002</v>
       </c>
+      <c r="Q62" t="s">
+        <v>31</v>
+      </c>
+      <c r="R62" t="s">
+        <v>147</v>
+      </c>
+      <c r="S62" t="s">
+        <v>174</v>
+      </c>
+      <c r="T62" t="s">
+        <v>32</v>
+      </c>
       <c r="U62" t="s">
+        <v>33</v>
+      </c>
+      <c r="V62" t="s">
+        <v>39</v>
+      </c>
+      <c r="X62" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="Q63" t="s">
         <v>31</v>
       </c>
-      <c r="V62" t="s">
+      <c r="R63" t="s">
         <v>17</v>
       </c>
-      <c r="W62" t="s">
+      <c r="S63" t="s">
         <v>38</v>
       </c>
-      <c r="X62" t="s">
+      <c r="T63" t="s">
         <v>32</v>
       </c>
-      <c r="Y62" t="s">
+      <c r="U63" t="s">
         <v>33</v>
       </c>
-      <c r="Z62" t="s">
+      <c r="V63" t="s">
         <v>34</v>
       </c>
-      <c r="AB62" t="s">
+      <c r="X63" t="s">
         <v>37</v>
       </c>
+    </row>
+    <row r="76" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="P76" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>167</v>
+      </c>
+      <c r="R76" t="s">
+        <v>168</v>
+      </c>
+      <c r="S76" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="77" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="O77" t="s">
+        <v>148</v>
+      </c>
+      <c r="P77" s="3">
+        <v>1.31</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>4812.0244000000002</v>
+      </c>
+      <c r="R77">
+        <v>0.33</v>
+      </c>
+      <c r="S77">
+        <v>4.1005000000000003</v>
+      </c>
+    </row>
+    <row r="78" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="O78" t="s">
+        <v>165</v>
+      </c>
+      <c r="P78" s="3">
+        <v>3.3294999999999999</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>1175.5066999999999</v>
+      </c>
+      <c r="R78">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="S78">
+        <v>5.8775000000000004</v>
+      </c>
+    </row>
+    <row r="79" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="O79" t="s">
+        <v>166</v>
+      </c>
+      <c r="P79" s="3"/>
+      <c r="Q79" s="1"/>
+    </row>
+    <row r="80" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="O80" t="s">
+        <v>163</v>
+      </c>
+      <c r="P80">
+        <v>4.5269000000000004</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>2950.7891</v>
+      </c>
+      <c r="R80">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="S80">
+        <v>2.8138000000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="O81" t="s">
+        <v>164</v>
+      </c>
+      <c r="P81">
+        <v>3.6080999999999999</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>4516.7133000000003</v>
+      </c>
+      <c r="R81">
+        <v>0.2994</v>
+      </c>
+      <c r="S81">
+        <v>2.8138000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="O82" t="s">
+        <v>21</v>
+      </c>
+      <c r="P82" s="2">
+        <v>1.5780000000000001</v>
+      </c>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="O83" t="s">
+        <v>23</v>
+      </c>
+      <c r="P83" s="2">
+        <v>1.2514000000000001</v>
+      </c>
+      <c r="Q83" s="3"/>
+      <c r="S83">
+        <v>2.0036999999999998</v>
+      </c>
+    </row>
+    <row r="84" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="P84" s="2"/>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="15:19" x14ac:dyDescent="0.25">
+      <c r="P85" s="2"/>
+      <c r="Q85" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1156D8-21F4-4FF8-B6A1-C0FC38728B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B08BEF-5F2F-4D00-9679-BF21899FA8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -24,7 +24,6 @@
     <definedName name="Start">[1]SETUP!$F$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4900,7 +4899,7 @@
         <v>33</v>
       </c>
       <c r="V10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X10" t="s">
         <v>35</v>
@@ -4956,7 +4955,7 @@
         <v>33</v>
       </c>
       <c r="V11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X11" t="s">
         <v>35</v>
@@ -5012,7 +5011,7 @@
         <v>33</v>
       </c>
       <c r="V12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X12" t="s">
         <v>35</v>
@@ -5068,7 +5067,7 @@
         <v>33</v>
       </c>
       <c r="V13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X13" t="s">
         <v>35</v>
@@ -5124,7 +5123,7 @@
         <v>33</v>
       </c>
       <c r="V14" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X14" t="s">
         <v>35</v>
@@ -5180,7 +5179,7 @@
         <v>33</v>
       </c>
       <c r="V15" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X15" t="s">
         <v>35</v>
@@ -5236,7 +5235,7 @@
         <v>33</v>
       </c>
       <c r="V16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X16" t="s">
         <v>35</v>
@@ -5292,7 +5291,7 @@
         <v>33</v>
       </c>
       <c r="V17" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X17" t="s">
         <v>35</v>
@@ -5348,7 +5347,7 @@
         <v>33</v>
       </c>
       <c r="V18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X18" t="s">
         <v>35</v>
@@ -5404,7 +5403,7 @@
         <v>33</v>
       </c>
       <c r="V19" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X19" t="s">
         <v>35</v>
@@ -5460,7 +5459,7 @@
         <v>33</v>
       </c>
       <c r="V20" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X20" t="s">
         <v>35</v>
@@ -5516,7 +5515,7 @@
         <v>33</v>
       </c>
       <c r="V21" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X21" t="s">
         <v>35</v>
@@ -5572,7 +5571,7 @@
         <v>33</v>
       </c>
       <c r="V22" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X22" t="s">
         <v>35</v>
@@ -5628,7 +5627,7 @@
         <v>33</v>
       </c>
       <c r="V23" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X23" t="s">
         <v>35</v>
@@ -5684,7 +5683,7 @@
         <v>33</v>
       </c>
       <c r="V24" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X24" t="s">
         <v>35</v>
@@ -5796,7 +5795,7 @@
         <v>33</v>
       </c>
       <c r="V26" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X26" t="s">
         <v>35</v>
@@ -5852,7 +5851,7 @@
         <v>33</v>
       </c>
       <c r="V27" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X27" t="s">
         <v>35</v>
@@ -5908,7 +5907,7 @@
         <v>33</v>
       </c>
       <c r="V28" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X28" t="s">
         <v>35</v>
@@ -5964,7 +5963,7 @@
         <v>33</v>
       </c>
       <c r="V29" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X29" t="s">
         <v>35</v>
@@ -6020,7 +6019,7 @@
         <v>33</v>
       </c>
       <c r="V30" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X30" t="s">
         <v>35</v>
@@ -6076,7 +6075,7 @@
         <v>33</v>
       </c>
       <c r="V31" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X31" t="s">
         <v>35</v>
@@ -6132,7 +6131,7 @@
         <v>33</v>
       </c>
       <c r="V32" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X32" t="s">
         <v>35</v>
@@ -6185,7 +6184,7 @@
         <v>33</v>
       </c>
       <c r="V33" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X33" t="s">
         <v>35</v>
@@ -6238,7 +6237,7 @@
         <v>33</v>
       </c>
       <c r="V34" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X34" t="s">
         <v>35</v>
@@ -6504,7 +6503,7 @@
         <v>33</v>
       </c>
       <c r="V39" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X39" t="s">
         <v>35</v>
@@ -6557,7 +6556,7 @@
         <v>33</v>
       </c>
       <c r="V40" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X40" t="s">
         <v>35</v>
@@ -6610,7 +6609,7 @@
         <v>33</v>
       </c>
       <c r="V41" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X41" t="s">
         <v>35</v>
@@ -6663,7 +6662,7 @@
         <v>33</v>
       </c>
       <c r="V42" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X42" t="s">
         <v>35</v>
@@ -6716,7 +6715,7 @@
         <v>33</v>
       </c>
       <c r="V43" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X43" t="s">
         <v>35</v>
@@ -6822,7 +6821,7 @@
         <v>33</v>
       </c>
       <c r="V45" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X45" t="s">
         <v>35</v>
@@ -6875,7 +6874,7 @@
         <v>33</v>
       </c>
       <c r="V46" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X46" t="s">
         <v>35</v>
@@ -6928,7 +6927,7 @@
         <v>33</v>
       </c>
       <c r="V47" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X47" t="s">
         <v>35</v>
@@ -6981,7 +6980,7 @@
         <v>33</v>
       </c>
       <c r="V48" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X48" t="s">
         <v>35</v>
@@ -7034,7 +7033,7 @@
         <v>33</v>
       </c>
       <c r="V49" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X49" t="s">
         <v>35</v>
@@ -7087,7 +7086,7 @@
         <v>33</v>
       </c>
       <c r="V50" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X50" t="s">
         <v>35</v>
@@ -7140,7 +7139,7 @@
         <v>33</v>
       </c>
       <c r="V51" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X51" t="s">
         <v>35</v>
@@ -7246,7 +7245,7 @@
         <v>33</v>
       </c>
       <c r="V53" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X53" t="s">
         <v>35</v>
@@ -7299,7 +7298,7 @@
         <v>33</v>
       </c>
       <c r="V54" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X54" t="s">
         <v>35</v>
@@ -7352,7 +7351,7 @@
         <v>33</v>
       </c>
       <c r="V55" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X55" t="s">
         <v>35</v>
@@ -7405,7 +7404,7 @@
         <v>33</v>
       </c>
       <c r="V56" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X56" t="s">
         <v>35</v>
@@ -7458,7 +7457,7 @@
         <v>33</v>
       </c>
       <c r="V57" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X57" t="s">
         <v>35</v>
@@ -7511,7 +7510,7 @@
         <v>33</v>
       </c>
       <c r="V58" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X58" t="s">
         <v>35</v>
@@ -7564,7 +7563,7 @@
         <v>33</v>
       </c>
       <c r="V59" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X59" t="s">
         <v>35</v>
@@ -7617,7 +7616,7 @@
         <v>33</v>
       </c>
       <c r="V60" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X60" t="s">
         <v>35</v>
@@ -7670,7 +7669,7 @@
         <v>33</v>
       </c>
       <c r="V61" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X61" t="s">
         <v>35</v>
@@ -7711,7 +7710,7 @@
         <v>33</v>
       </c>
       <c r="V62" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="X62" t="s">
         <v>35</v>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B08BEF-5F2F-4D00-9679-BF21899FA8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE9D3D7-A23C-43F3-BF29-E342C01ACB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" state="hidden" r:id="rId1"/>
@@ -786,12 +786,6 @@
     <t>ep_solar_pv_rapla</t>
   </si>
   <si>
-    <t>elv_spv_laane</t>
-  </si>
-  <si>
-    <t>elv_spv_hiiu</t>
-  </si>
-  <si>
     <t>~FI_Process</t>
   </si>
   <si>
@@ -835,6 +829,12 @@
   </si>
   <si>
     <t>* Power Plants</t>
+  </si>
+  <si>
+    <t>elc_spv_laane</t>
+  </si>
+  <si>
+    <t>elc_spv_hiiu</t>
   </si>
 </sst>
 </file>
@@ -3164,14 +3164,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047CB67-FC18-43CA-8AA0-0CA09A11D4D8}">
   <dimension ref="B9:T17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="73.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="73.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>161</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>89</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>90</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>91</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>92</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>93</v>
       </c>
@@ -3523,17 +3523,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41A4FEF-80F2-457D-B441-6C3DD45005FF}">
   <dimension ref="B9:T30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>161</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>1</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>156</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>155</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>45</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>48</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>50</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>52</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>53</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>54</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>55</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>56</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>57</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>58</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>59</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>60</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>62</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>64</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>65</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>66</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>157</v>
       </c>
@@ -4649,36 +4649,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79DDA4A-BC9F-4D47-BDC9-53442001A438}">
   <dimension ref="B6:X85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.26953125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="64.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="64.453125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="41.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="41.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:24" ht="15.5" x14ac:dyDescent="0.35">
       <c r="D6" s="8" t="s">
         <v>0</v>
       </c>
@@ -4696,7 +4696,7 @@
       <c r="Q6" s="9"/>
       <c r="R6" s="7"/>
     </row>
-    <row r="7" spans="2:24" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:24" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="13" t="s">
         <v>1</v>
       </c>
@@ -4737,7 +4737,7 @@
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R7" s="11"/>
       <c r="S7" s="12"/>
@@ -4747,9 +4747,9 @@
       <c r="W7" s="12"/>
       <c r="X7" s="12"/>
     </row>
-    <row r="8" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="18"/>
@@ -4766,13 +4766,13 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="S8" s="17" t="s">
         <v>219</v>
-      </c>
-      <c r="R8" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="S8" s="17" t="s">
-        <v>221</v>
       </c>
       <c r="T8" s="15" t="s">
         <v>27</v>
@@ -4781,16 +4781,16 @@
         <v>28</v>
       </c>
       <c r="V8" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="W8" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="X8" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="W8" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="X8" s="15" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="2:24" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="2:24" ht="23.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
         <v>184</v>
       </c>
@@ -4825,31 +4825,31 @@
         <v>0.1461854238754417</v>
       </c>
       <c r="Q9" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="R9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="S9" s="16" t="s">
         <v>225</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="S9" s="16" t="s">
-        <v>227</v>
       </c>
       <c r="T9" s="16" t="s">
         <v>27</v>
       </c>
       <c r="U9" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="V9" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="W9" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="V9" s="16" t="s">
+      <c r="X9" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="W9" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="X9" s="16" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>185</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>186</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>187</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>188</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>193</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>189</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>190</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>191</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>192</v>
       </c>
@@ -5353,7 +5353,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>208</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>209</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>215</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>210</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="E22">
         <v>2022</v>
@@ -5577,7 +5577,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>211</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="E23">
         <v>2022</v>
@@ -5633,7 +5633,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>24</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>170</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>171</v>
       </c>
@@ -5801,7 +5801,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>197</v>
       </c>
@@ -5857,7 +5857,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>199</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>200</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>201</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>202</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>206</v>
       </c>
@@ -6137,7 +6137,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>172</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>152</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>150</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>151</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>149</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>99</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>100</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>101</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>102</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>103</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>153</v>
       </c>
@@ -6721,7 +6721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>111</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>113</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>127</v>
       </c>
@@ -6880,7 +6880,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>115</v>
       </c>
@@ -6933,7 +6933,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>126</v>
       </c>
@@ -6986,7 +6986,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>121</v>
       </c>
@@ -7039,7 +7039,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>125</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>154</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>129</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>131</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>133</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>135</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>137</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>139</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>141</v>
       </c>
@@ -7516,7 +7516,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>143</v>
       </c>
@@ -7569,7 +7569,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>144</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>147</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>17</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:24" x14ac:dyDescent="0.35">
       <c r="Q63" t="s">
         <v>31</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="76" spans="15:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="15:19" x14ac:dyDescent="0.35">
       <c r="P76" t="s">
         <v>162</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="77" spans="15:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="15:19" x14ac:dyDescent="0.35">
       <c r="O77" t="s">
         <v>148</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>4.1005000000000003</v>
       </c>
     </row>
-    <row r="78" spans="15:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="15:19" x14ac:dyDescent="0.35">
       <c r="O78" t="s">
         <v>165</v>
       </c>
@@ -7787,14 +7787,14 @@
         <v>5.8775000000000004</v>
       </c>
     </row>
-    <row r="79" spans="15:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="15:19" x14ac:dyDescent="0.35">
       <c r="O79" t="s">
         <v>166</v>
       </c>
       <c r="P79" s="3"/>
       <c r="Q79" s="1"/>
     </row>
-    <row r="80" spans="15:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="15:19" x14ac:dyDescent="0.35">
       <c r="O80" t="s">
         <v>163</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>2.8138000000000001</v>
       </c>
     </row>
-    <row r="81" spans="15:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="15:19" x14ac:dyDescent="0.35">
       <c r="O81" t="s">
         <v>164</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>2.8138000000000001</v>
       </c>
     </row>
-    <row r="82" spans="15:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="15:19" x14ac:dyDescent="0.35">
       <c r="O82" t="s">
         <v>21</v>
       </c>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="Q82" s="3"/>
     </row>
-    <row r="83" spans="15:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="15:19" x14ac:dyDescent="0.35">
       <c r="O83" t="s">
         <v>23</v>
       </c>
@@ -7849,11 +7849,11 @@
         <v>2.0036999999999998</v>
       </c>
     </row>
-    <row r="84" spans="15:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="15:19" x14ac:dyDescent="0.35">
       <c r="P84" s="2"/>
       <c r="Q84" s="3"/>
     </row>
-    <row r="85" spans="15:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="15:19" x14ac:dyDescent="0.35">
       <c r="P85" s="2"/>
       <c r="Q85" s="3"/>
     </row>

--- a/VerveStacks_EST/vt_EST_ELC_v1.xlsx
+++ b/VerveStacks_EST/vt_EST_ELC_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\VerveStacks_EST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE9D3D7-A23C-43F3-BF29-E342C01ACB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6672C53-E1D2-4985-A2B3-B31F33C2BFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{21C51102-B905-44E2-89DF-C1A7E31F8D9F}"/>
   </bookViews>
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="234">
   <si>
     <t>~fi_t</t>
   </si>
@@ -835,6 +835,9 @@
   </si>
   <si>
     <t>elc_spv_hiiu</t>
+  </si>
+  <si>
+    <t>m</t>
   </si>
 </sst>
 </file>
@@ -7850,6 +7853,9 @@
       </c>
     </row>
     <row r="84" spans="15:19" x14ac:dyDescent="0.35">
+      <c r="O84" t="s">
+        <v>233</v>
+      </c>
       <c r="P84" s="2"/>
       <c r="Q84" s="3"/>
     </row>
